--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
@@ -9,12 +9,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$34</definedName>
+  </definedNames>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="139">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -79,49 +82,40 @@
     <t>MERCEARIA</t>
   </si>
   <si>
-    <t>PRODUTOS PET</t>
+    <t>PERECIVEIS</t>
   </si>
   <si>
     <t>PERFUMARIA E LIMPEZA</t>
   </si>
   <si>
-    <t>PERECIVEIS</t>
-  </si>
-  <si>
     <t>NICOLAS AUGUSTO P. BORGES</t>
   </si>
   <si>
+    <t>NIDAL TUBASI</t>
+  </si>
+  <si>
+    <t>SANDRO MARTINS VIANNA</t>
+  </si>
+  <si>
     <t>WETER SONNENFELDET</t>
   </si>
   <si>
-    <t>NIDAL TUBASI</t>
-  </si>
-  <si>
     <t>JOAO BATISTA</t>
   </si>
   <si>
-    <t>SANDRO MARTINS VIANNA</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
     <t>003</t>
   </si>
   <si>
-    <t>004</t>
-  </si>
-  <si>
     <t>005</t>
   </si>
   <si>
     <t>006</t>
   </si>
   <si>
-    <t>007</t>
-  </si>
-  <si>
-    <t>011</t>
+    <t>008</t>
   </si>
   <si>
     <t>013</t>
@@ -133,202 +127,187 @@
     <t>017</t>
   </si>
   <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t>764</t>
-  </si>
-  <si>
-    <t>903</t>
-  </si>
-  <si>
-    <t>1288</t>
-  </si>
-  <si>
-    <t>2814</t>
-  </si>
-  <si>
-    <t>3251</t>
-  </si>
-  <si>
-    <t>4039</t>
-  </si>
-  <si>
-    <t>5172</t>
-  </si>
-  <si>
-    <t>6791</t>
-  </si>
-  <si>
-    <t>17566</t>
-  </si>
-  <si>
-    <t>20611</t>
-  </si>
-  <si>
-    <t>20613</t>
+    <t>018</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2320</t>
+  </si>
+  <si>
+    <t>2519</t>
+  </si>
+  <si>
+    <t>6783</t>
+  </si>
+  <si>
+    <t>1486</t>
+  </si>
+  <si>
+    <t>1606</t>
+  </si>
+  <si>
+    <t>2096</t>
+  </si>
+  <si>
+    <t>2379</t>
+  </si>
+  <si>
+    <t>3153</t>
+  </si>
+  <si>
+    <t>3185</t>
+  </si>
+  <si>
+    <t>3712</t>
+  </si>
+  <si>
+    <t>10148</t>
   </si>
   <si>
     <t>23370</t>
   </si>
   <si>
-    <t>2320</t>
+    <t>36616</t>
+  </si>
+  <si>
+    <t>10144</t>
+  </si>
+  <si>
+    <t>10178</t>
+  </si>
+  <si>
+    <t>1949</t>
+  </si>
+  <si>
+    <t>3911</t>
+  </si>
+  <si>
+    <t>35687</t>
   </si>
   <si>
     <t>2398</t>
   </si>
   <si>
-    <t>3654</t>
-  </si>
-  <si>
-    <t>6783</t>
-  </si>
-  <si>
-    <t>23212</t>
-  </si>
-  <si>
-    <t>33255</t>
-  </si>
-  <si>
-    <t>2140</t>
-  </si>
-  <si>
-    <t>784</t>
-  </si>
-  <si>
-    <t>6782</t>
-  </si>
-  <si>
-    <t>904</t>
-  </si>
-  <si>
-    <t>2150</t>
-  </si>
-  <si>
-    <t>AGUARD 51 VD 965ML</t>
-  </si>
-  <si>
-    <t>ENERG MONSTER LT 473ML GREEN</t>
-  </si>
-  <si>
-    <t>REFRIG COCA COLA PET 200ML ZERO</t>
-  </si>
-  <si>
-    <t>REFRIG PEPSI BLACK LT 350ML</t>
-  </si>
-  <si>
-    <t>CHOC BARRA NESTLE 80G CLASSIC DUO</t>
-  </si>
-  <si>
-    <t>POLENTA PERDIZ 500G INST TEMP</t>
-  </si>
-  <si>
-    <t>SALG KEVYTOS SHOW 38G CEBOLA</t>
-  </si>
-  <si>
-    <t>ALIM GATO BIFFE CAT 1KG ESPECIAL</t>
-  </si>
-  <si>
-    <t>CORANTE TINGECOR 40G GUARANY MARINHO N16</t>
-  </si>
-  <si>
-    <t>LEITE UHT PET ELEGE 1L DESNATADO</t>
-  </si>
-  <si>
-    <t>ENERG RED BULL LT 250ML MELAO MARACUJA</t>
-  </si>
-  <si>
-    <t>MASSA SEMOLA GERMANI 1KG ESPAG</t>
-  </si>
-  <si>
-    <t>MAS ESPAGUETINI ISABELA SEMOLA 500G</t>
+    <t>4202</t>
+  </si>
+  <si>
+    <t>CERV ANTARCTICA SUBZERO GF 1L RETORNAVEL</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SANO OURO TP1 2KG</t>
+  </si>
+  <si>
+    <t>ARROZ BCO REQUINTE TP1 2KG</t>
+  </si>
+  <si>
+    <t>FEIJAO CARIOCA CALDO OURO 1KG</t>
+  </si>
+  <si>
+    <t>KETCHUP HELLMANNS BISN 380G TRAD</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL C TAMPA 1L INTEGRAL</t>
+  </si>
+  <si>
+    <t>BISC RECH PASSATEMPO 130G CHOC</t>
+  </si>
+  <si>
+    <t>BISC SALG CLUB SOCIAL 6UN 144G ORIGINAL</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SANO TP1 2KG</t>
+  </si>
+  <si>
+    <t>DUETO OLE LT 170G ERVILHA MILHO</t>
+  </si>
+  <si>
+    <t>SALG KEVYTOS 80G BACONYTOS</t>
+  </si>
+  <si>
+    <t>SALG KEVYTOS BATATA ONDULADA 40G</t>
+  </si>
+  <si>
+    <t>MIST P BOLO APTI 400G QUATRO LEITES</t>
+  </si>
+  <si>
+    <t>SAB FARNESE 180G PITAYA FRAMB</t>
   </si>
   <si>
     <t>SALG KRUKS 35G BACON</t>
   </si>
   <si>
-    <t>FEIJAO CARIOCA CALDO OURO 1KG</t>
+    <t>BOMBOM NESTLE ESPECIALIDADES 220G SORTIDOS</t>
+  </si>
+  <si>
+    <t>SAB FARNESE 180G AVEIA ESFOL</t>
+  </si>
+  <si>
+    <t>SABON PALMOLIVE NATURALS 85G KARITE</t>
+  </si>
+  <si>
+    <t>WAFER MINUETO ROLINHO 40G CHOC</t>
+  </si>
+  <si>
+    <t>ABS C ABAS S LIVRE LV8PG7 AD SUAVE</t>
+  </si>
+  <si>
+    <t>DESOD CREME SECRET CLEAR COTT 45G GEL</t>
   </si>
   <si>
     <t>MILHO VERDE ODERICH LT 200G</t>
   </si>
   <si>
-    <t>LEITE COCO MENINA VD 200ML</t>
-  </si>
-  <si>
-    <t>LEITE UHT TIROL C TAMPA 1L INTEGRAL</t>
-  </si>
-  <si>
-    <t>SAL MOIDO 5 ESTRELAS 1KG</t>
-  </si>
-  <si>
-    <t>REFRIG CHARRUA PET 3L GUARANA</t>
-  </si>
-  <si>
-    <t>ARROZ BCO SANO TP1 5KG</t>
-  </si>
-  <si>
-    <t>REFRIG ANTARCTICA GUARANA PET 2L</t>
-  </si>
-  <si>
-    <t>LEITE UHT TIROL C TAMPA 1L DESN</t>
-  </si>
-  <si>
-    <t>REFRIG PEPSI LT 350ML</t>
-  </si>
-  <si>
-    <t>ARROZ BCO REQUINTE TP1 5KG</t>
-  </si>
-  <si>
-    <t>04/10/2024</t>
-  </si>
-  <si>
-    <t>05/10/2024</t>
-  </si>
-  <si>
-    <t>17/10/2024</t>
-  </si>
-  <si>
-    <t>23/10/2024</t>
-  </si>
-  <si>
-    <t>07/11/2024</t>
-  </si>
-  <si>
-    <t>16/12/2024</t>
-  </si>
-  <si>
-    <t>23/12/2024</t>
+    <t>AMAC GIRANDO SOL 2L AZUL</t>
+  </si>
+  <si>
+    <t>23/09/2024</t>
+  </si>
+  <si>
+    <t>04/12/2024</t>
+  </si>
+  <si>
+    <t>07/12/2024</t>
+  </si>
+  <si>
+    <t>10/12/2024</t>
   </si>
   <si>
     <t>26/04/2025</t>
   </si>
   <si>
+    <t>13/11/2024</t>
+  </si>
+  <si>
+    <t>18/11/2024</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>20/12/2024</t>
+  </si>
+  <si>
+    <t>31/12/2024</t>
+  </si>
+  <si>
     <t>20/06/2025</t>
   </si>
   <si>
-    <t>07/12/2024</t>
-  </si>
-  <si>
-    <t>09/12/2024</t>
-  </si>
-  <si>
-    <t>30/12/2024</t>
-  </si>
-  <si>
-    <t>07/07/2025</t>
-  </si>
-  <si>
-    <t>04/12/2024</t>
-  </si>
-  <si>
-    <t>18/10/2024</t>
-  </si>
-  <si>
-    <t>05/12/2024</t>
+    <t>07/02/2026</t>
+  </si>
+  <si>
+    <t>29/11/2024</t>
+  </si>
+  <si>
+    <t>17/01/2026</t>
   </si>
   <si>
     <t>Ativo</t>
@@ -337,112 +316,124 @@
     <t>12</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>211</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>23925</t>
+  </si>
+  <si>
+    <t>42666</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>437</t>
+  </si>
+  <si>
+    <t>454</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>1272</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>29097</t>
+  </si>
+  <si>
+    <t>313</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>586</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>598</t>
-  </si>
-  <si>
-    <t>360</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>902</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>13994</t>
-  </si>
-  <si>
-    <t>781</t>
-  </si>
-  <si>
-    <t>1296</t>
-  </si>
-  <si>
-    <t>1392</t>
-  </si>
-  <si>
-    <t>28059</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>1281</t>
-  </si>
-  <si>
-    <t>576</t>
-  </si>
-  <si>
-    <t>1685</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>1735</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>507</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>1109</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>20147</t>
+  </si>
+  <si>
+    <t>52</t>
   </si>
 </sst>
 </file>
@@ -490,9 +481,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Escritório">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -530,7 +521,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Escritório">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -600,7 +591,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Escritório">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -776,6 +767,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:S34"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
@@ -838,34 +835,34 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -877,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="O2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P2">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="Q2">
         <v>90</v>
@@ -892,184 +889,184 @@
         <v>2</v>
       </c>
       <c r="S2">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I3">
         <v>6</v>
       </c>
       <c r="J3">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="O3">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="P3">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="Q3">
         <v>90</v>
       </c>
       <c r="R3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S3">
-        <v>381</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4">
+        <v>15</v>
+      </c>
+      <c r="J4">
+        <v>48</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>112</v>
+      </c>
+      <c r="O4">
+        <v>61</v>
+      </c>
+      <c r="P4">
         <v>91</v>
       </c>
-      <c r="G4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-      <c r="J4">
-        <v>-1</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>116</v>
-      </c>
-      <c r="O4">
-        <v>102</v>
-      </c>
-      <c r="P4">
-        <v>114</v>
-      </c>
       <c r="Q4">
         <v>90</v>
       </c>
       <c r="R4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="S4">
-        <v>61.17</v>
+        <v>67.67</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H5" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J5">
-        <v>-6</v>
+        <v>11</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O5">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="P5">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="Q5">
         <v>90</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>7</v>
+        <v>67.67</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1077,31 +1074,31 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="G6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H6" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -1113,22 +1110,22 @@
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="O6">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="P6">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="Q6">
         <v>90</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>28.06</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1136,58 +1133,58 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G7" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H7" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J7">
+        <v>-14</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>118</v>
+      </c>
+      <c r="O7">
+        <v>31</v>
+      </c>
+      <c r="P7">
+        <v>46</v>
+      </c>
+      <c r="Q7">
+        <v>90</v>
+      </c>
+      <c r="R7">
         <v>4</v>
       </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>119</v>
-      </c>
-      <c r="O7">
-        <v>8</v>
-      </c>
-      <c r="P7">
-        <v>20</v>
-      </c>
-      <c r="Q7">
-        <v>90</v>
-      </c>
-      <c r="R7">
-        <v>2</v>
-      </c>
       <c r="S7">
-        <v>11</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1195,31 +1192,31 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8">
         <v>70</v>
       </c>
-      <c r="F8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G8" t="s">
-        <v>105</v>
-      </c>
-      <c r="H8" t="s">
-        <v>109</v>
-      </c>
-      <c r="I8">
-        <v>20</v>
-      </c>
       <c r="J8">
-        <v>-17</v>
+        <v>26</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1231,54 +1228,54 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="O8">
         <v>48</v>
       </c>
       <c r="P8">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="Q8">
         <v>90</v>
       </c>
       <c r="R8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1290,13 +1287,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="O9">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P9">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="Q9">
         <v>90</v>
@@ -1305,63 +1302,63 @@
         <v>2</v>
       </c>
       <c r="S9">
-        <v>83.75</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G10" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>-133</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O10">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="P10">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="Q10">
         <v>90</v>
       </c>
       <c r="R10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>5</v>
@@ -1369,52 +1366,52 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>28</v>
       </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G11" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H11" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J11">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="O11">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P11">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="Q11">
         <v>90</v>
@@ -1423,39 +1420,39 @@
         <v>4</v>
       </c>
       <c r="S11">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G12" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1464,13 +1461,13 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>10</v>
@@ -1479,10 +1476,10 @@
         <v>90</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S12">
-        <v>60.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1490,31 +1487,31 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H13" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J13">
-        <v>25</v>
+        <v>-13</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1526,13 +1523,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O13">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P13">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="Q13">
         <v>90</v>
@@ -1541,7 +1538,7 @@
         <v>3</v>
       </c>
       <c r="S13">
-        <v>5.4</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1549,31 +1546,31 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="G14" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H14" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1585,22 +1582,22 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="O14">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="P14">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q14">
         <v>90</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S14">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1608,31 +1605,31 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G15" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H15" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>-4</v>
+        <v>18</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1644,22 +1641,22 @@
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="O15">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="P15">
+        <v>30</v>
+      </c>
+      <c r="Q15">
+        <v>90</v>
+      </c>
+      <c r="R15">
+        <v>12</v>
+      </c>
+      <c r="S15">
         <v>20</v>
-      </c>
-      <c r="Q15">
-        <v>90</v>
-      </c>
-      <c r="R15">
-        <v>2</v>
-      </c>
-      <c r="S15">
-        <v>24.8</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1667,31 +1664,31 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="G16" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H16" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I16">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1703,22 +1700,22 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="O16">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="P16">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="Q16">
         <v>90</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="S16">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -1726,58 +1723,58 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>17</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>128</v>
+      </c>
+      <c r="O17">
+        <v>21</v>
+      </c>
+      <c r="P17">
         <v>30</v>
       </c>
-      <c r="D17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" t="s">
-        <v>99</v>
-      </c>
-      <c r="G17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" t="s">
-        <v>113</v>
-      </c>
-      <c r="I17">
-        <v>24</v>
-      </c>
-      <c r="J17">
-        <v>182</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>127</v>
-      </c>
-      <c r="O17">
-        <v>192</v>
-      </c>
-      <c r="P17">
-        <v>288</v>
-      </c>
       <c r="Q17">
         <v>90</v>
       </c>
       <c r="R17">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S17">
-        <v>136.88</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -1785,149 +1782,149 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="G18" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H18" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>101</v>
+      </c>
+      <c r="O18">
+        <v>13</v>
+      </c>
+      <c r="P18">
+        <v>20</v>
+      </c>
+      <c r="Q18">
+        <v>90</v>
+      </c>
+      <c r="R18">
         <v>24</v>
       </c>
-      <c r="J18">
-        <v>12</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>24</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>128</v>
-      </c>
-      <c r="O18">
-        <v>46</v>
-      </c>
-      <c r="P18">
-        <v>70</v>
-      </c>
-      <c r="Q18">
-        <v>90</v>
-      </c>
-      <c r="R18">
-        <v>2</v>
-      </c>
       <c r="S18">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H19" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J19">
-        <v>-3</v>
+        <v>1341</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="O19">
-        <v>22</v>
+        <v>2040</v>
       </c>
       <c r="P19">
-        <v>34</v>
+        <v>3060</v>
       </c>
       <c r="Q19">
         <v>90</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>170</v>
       </c>
       <c r="S19">
-        <v>5</v>
+        <v>10749.83</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H20" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I20">
         <v>12</v>
       </c>
       <c r="J20">
-        <v>725</v>
+        <v>4430</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1939,140 +1936,140 @@
         <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="O20">
-        <v>1020</v>
+        <v>5100</v>
       </c>
       <c r="P20">
-        <v>2040</v>
+        <v>6120</v>
       </c>
       <c r="Q20">
         <v>90</v>
       </c>
       <c r="R20">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="S20">
-        <v>10945.83</v>
+        <v>10749.83</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H21" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J21">
-        <v>63</v>
+        <v>1928</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>40</v>
+        <v>1032</v>
       </c>
       <c r="M21">
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="O21">
-        <v>120</v>
+        <v>3060</v>
       </c>
       <c r="P21">
-        <v>180</v>
+        <v>4080</v>
       </c>
       <c r="Q21">
         <v>90</v>
       </c>
       <c r="R21">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="S21">
-        <v>1559.4</v>
+        <v>10749.83</v>
       </c>
     </row>
     <row r="22" spans="1:19">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H22" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J22">
-        <v>53</v>
+        <v>3023</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="O22">
-        <v>118</v>
+        <v>3060</v>
       </c>
       <c r="P22">
-        <v>154</v>
+        <v>4080</v>
       </c>
       <c r="Q22">
         <v>90</v>
       </c>
       <c r="R22">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="S22">
-        <v>38</v>
+        <v>10749.83</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -2080,31 +2077,31 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F23" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H23" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J23">
-        <v>64</v>
+        <v>187</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2116,54 +2113,54 @@
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O23">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="P23">
-        <v>112</v>
+        <v>288</v>
       </c>
       <c r="Q23">
         <v>90</v>
       </c>
       <c r="R23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>55</v>
+        <v>131.88</v>
       </c>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F24" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H24" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I24">
         <v>12</v>
       </c>
       <c r="J24">
-        <v>3056</v>
+        <v>2</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2175,140 +2172,140 @@
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="O24">
-        <v>3060</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>4080</v>
+        <v>22</v>
       </c>
       <c r="Q24">
         <v>90</v>
       </c>
       <c r="R24">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="S24">
-        <v>10945.83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25">
+        <v>36</v>
+      </c>
+      <c r="J25">
         <v>60</v>
       </c>
-      <c r="E25" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" t="s">
-        <v>103</v>
-      </c>
-      <c r="G25" t="s">
-        <v>105</v>
-      </c>
-      <c r="H25" t="s">
-        <v>110</v>
-      </c>
-      <c r="I25">
-        <v>8</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="O25">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="P25">
-        <v>30</v>
+        <v>306</v>
       </c>
       <c r="Q25">
         <v>90</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>15.38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F26" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" t="s">
         <v>105</v>
       </c>
-      <c r="H26" t="s">
-        <v>107</v>
-      </c>
       <c r="I26">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="J26">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>125</v>
+      </c>
+      <c r="O26">
+        <v>132</v>
+      </c>
+      <c r="P26">
+        <v>204</v>
+      </c>
+      <c r="Q26">
+        <v>90</v>
+      </c>
+      <c r="R26">
+        <v>4</v>
+      </c>
+      <c r="S26">
         <v>36</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>136</v>
-      </c>
-      <c r="O26">
-        <v>118</v>
-      </c>
-      <c r="P26">
-        <v>154</v>
-      </c>
-      <c r="Q26">
-        <v>90</v>
-      </c>
-      <c r="R26">
-        <v>9</v>
-      </c>
-      <c r="S26">
-        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -2319,34 +2316,34 @@
         <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F27" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G27" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I27">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2355,110 +2352,110 @@
         <v>106</v>
       </c>
       <c r="O27">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="P27">
-        <v>34</v>
+        <v>174</v>
       </c>
       <c r="Q27">
         <v>90</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S27">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" t="s">
+        <v>91</v>
+      </c>
+      <c r="G28" t="s">
+        <v>97</v>
+      </c>
+      <c r="H28" t="s">
+        <v>100</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+      <c r="J28">
+        <v>10</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>10</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>122</v>
+      </c>
+      <c r="O28">
         <v>24</v>
       </c>
-      <c r="C28" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28" t="s">
-        <v>103</v>
-      </c>
-      <c r="G28" t="s">
-        <v>105</v>
-      </c>
-      <c r="H28" t="s">
-        <v>110</v>
-      </c>
-      <c r="I28">
-        <v>8</v>
-      </c>
-      <c r="J28">
-        <v>-4</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>16</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28" t="s">
-        <v>137</v>
-      </c>
-      <c r="O28">
-        <v>72</v>
-      </c>
       <c r="P28">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="Q28">
         <v>90</v>
       </c>
       <c r="R28">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>15.38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F29" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G29" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H29" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I29">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J29">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -2470,72 +2467,72 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="O29">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="P29">
-        <v>168</v>
+        <v>52</v>
       </c>
       <c r="Q29">
         <v>90</v>
       </c>
       <c r="R29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>355</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" t="s">
+        <v>93</v>
+      </c>
+      <c r="G30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30" t="s">
+        <v>100</v>
+      </c>
+      <c r="I30">
+        <v>10</v>
+      </c>
+      <c r="J30">
+        <v>-1</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>126</v>
+      </c>
+      <c r="O30">
         <v>24</v>
       </c>
-      <c r="C30" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" t="s">
-        <v>62</v>
-      </c>
-      <c r="E30" t="s">
-        <v>87</v>
-      </c>
-      <c r="F30" t="s">
-        <v>92</v>
-      </c>
-      <c r="G30" t="s">
-        <v>105</v>
-      </c>
-      <c r="H30" t="s">
-        <v>106</v>
-      </c>
-      <c r="I30">
-        <v>12</v>
-      </c>
-      <c r="J30">
-        <v>17</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30" t="s">
-        <v>139</v>
-      </c>
-      <c r="O30">
-        <v>32</v>
-      </c>
       <c r="P30">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="Q30">
         <v>90</v>
@@ -2544,57 +2541,57 @@
         <v>4</v>
       </c>
       <c r="S30">
-        <v>7</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" t="s">
+        <v>101</v>
+      </c>
+      <c r="I31">
         <v>24</v>
       </c>
-      <c r="C31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" t="s">
-        <v>87</v>
-      </c>
-      <c r="F31" t="s">
-        <v>92</v>
-      </c>
-      <c r="G31" t="s">
-        <v>105</v>
-      </c>
-      <c r="H31" t="s">
-        <v>106</v>
-      </c>
-      <c r="I31">
-        <v>12</v>
-      </c>
       <c r="J31">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="O31">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="P31">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="Q31">
         <v>90</v>
@@ -2603,7 +2600,7 @@
         <v>3</v>
       </c>
       <c r="S31">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -2614,28 +2611,28 @@
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F32" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G32" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H32" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J32">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2644,25 +2641,25 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O32">
-        <v>184</v>
+        <v>26</v>
       </c>
       <c r="P32">
-        <v>280</v>
+        <v>50</v>
       </c>
       <c r="Q32">
         <v>90</v>
       </c>
       <c r="R32">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -2670,120 +2667,125 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
         <v>55</v>
       </c>
       <c r="E33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G33" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H33" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="I33">
         <v>24</v>
       </c>
       <c r="J33">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M33">
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="O33">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="P33">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="Q33">
         <v>90</v>
       </c>
       <c r="R33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:19">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G34" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H34" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J34">
+        <v>-1</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>138</v>
+      </c>
+      <c r="O34">
+        <v>52</v>
+      </c>
+      <c r="P34">
+        <v>76</v>
+      </c>
+      <c r="Q34">
+        <v>90</v>
+      </c>
+      <c r="R34">
         <v>5</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>6</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34" t="s">
-        <v>142</v>
-      </c>
-      <c r="O34">
-        <v>14</v>
-      </c>
-      <c r="P34">
-        <v>26</v>
-      </c>
-      <c r="Q34">
-        <v>90</v>
-      </c>
-      <c r="R34">
-        <v>3</v>
       </c>
       <c r="S34">
         <v>5</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S34">
+    <sortState ref="A2:S34">
+      <sortCondition ref="E1:E34"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -9,12 +9,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$124</definedName>
+  </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="319">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -73,31 +76,46 @@
     <t>Estq_CD_cx</t>
   </si>
   <si>
+    <t>MERCEARIA</t>
+  </si>
+  <si>
+    <t>PERECIVEIS</t>
+  </si>
+  <si>
+    <t>PERFUMARIA E LIMPEZA</t>
+  </si>
+  <si>
     <t>BEBIDAS</t>
   </si>
   <si>
-    <t>PERFUMARIA E LIMPEZA</t>
-  </si>
-  <si>
-    <t>MERCEARIA</t>
-  </si>
-  <si>
-    <t>PERECIVEIS</t>
+    <t>WETER SONNENFELDET</t>
+  </si>
+  <si>
+    <t>SANDRO MARTINS VIANNA</t>
+  </si>
+  <si>
+    <t>JOAO BATISTA</t>
   </si>
   <si>
     <t>NICOLAS AUGUSTO P. BORGES</t>
   </si>
   <si>
-    <t>JOAO BATISTA</t>
-  </si>
-  <si>
-    <t>WETER SONNENFELDET</t>
-  </si>
-  <si>
     <t>NIDAL TUBASI</t>
   </si>
   <si>
-    <t>SANDRO MARTINS VIANNA</t>
+    <t>001</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>005</t>
   </si>
   <si>
     <t>006</t>
@@ -127,556 +145,835 @@
     <t>018</t>
   </si>
   <si>
-    <t>7835</t>
-  </si>
-  <si>
     <t>1423</t>
   </si>
   <si>
-    <t>37429</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>2280</t>
-  </si>
-  <si>
-    <t>2510</t>
-  </si>
-  <si>
-    <t>2747</t>
-  </si>
-  <si>
-    <t>2777</t>
+    <t>17357</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>786</t>
+  </si>
+  <si>
+    <t>847</t>
+  </si>
+  <si>
+    <t>2378</t>
+  </si>
+  <si>
+    <t>2814</t>
+  </si>
+  <si>
+    <t>2940</t>
+  </si>
+  <si>
+    <t>3416</t>
+  </si>
+  <si>
+    <t>4348</t>
+  </si>
+  <si>
+    <t>6791</t>
+  </si>
+  <si>
+    <t>7241</t>
+  </si>
+  <si>
+    <t>17665</t>
+  </si>
+  <si>
+    <t>37265</t>
+  </si>
+  <si>
+    <t>764</t>
+  </si>
+  <si>
+    <t>2140</t>
+  </si>
+  <si>
+    <t>2859</t>
+  </si>
+  <si>
+    <t>3948</t>
+  </si>
+  <si>
+    <t>3969</t>
+  </si>
+  <si>
+    <t>3971</t>
+  </si>
+  <si>
+    <t>5679</t>
+  </si>
+  <si>
+    <t>6848</t>
+  </si>
+  <si>
+    <t>7797</t>
+  </si>
+  <si>
+    <t>7869</t>
+  </si>
+  <si>
+    <t>9293</t>
+  </si>
+  <si>
+    <t>12308</t>
+  </si>
+  <si>
+    <t>17347</t>
+  </si>
+  <si>
+    <t>17385</t>
+  </si>
+  <si>
+    <t>17403</t>
+  </si>
+  <si>
+    <t>22796</t>
+  </si>
+  <si>
+    <t>23397</t>
+  </si>
+  <si>
+    <t>33887</t>
+  </si>
+  <si>
+    <t>34610</t>
+  </si>
+  <si>
+    <t>35113</t>
+  </si>
+  <si>
+    <t>36264</t>
+  </si>
+  <si>
+    <t>37437</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>1238</t>
+  </si>
+  <si>
+    <t>1834</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2217</t>
+  </si>
+  <si>
+    <t>2519</t>
+  </si>
+  <si>
+    <t>3415</t>
+  </si>
+  <si>
+    <t>834</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>2096</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2568</t>
+  </si>
+  <si>
+    <t>2737</t>
+  </si>
+  <si>
+    <t>2908</t>
+  </si>
+  <si>
+    <t>9745</t>
+  </si>
+  <si>
+    <t>22654</t>
+  </si>
+  <si>
+    <t>34718</t>
+  </si>
+  <si>
+    <t>750</t>
+  </si>
+  <si>
+    <t>3191</t>
+  </si>
+  <si>
+    <t>1434</t>
+  </si>
+  <si>
+    <t>9297</t>
+  </si>
+  <si>
+    <t>3183</t>
   </si>
   <si>
     <t>279</t>
   </si>
   <si>
-    <t>784</t>
-  </si>
-  <si>
-    <t>2507</t>
-  </si>
-  <si>
-    <t>2519</t>
-  </si>
-  <si>
-    <t>6795</t>
-  </si>
-  <si>
-    <t>12289</t>
-  </si>
-  <si>
-    <t>783</t>
-  </si>
-  <si>
-    <t>2370</t>
-  </si>
-  <si>
-    <t>6689</t>
-  </si>
-  <si>
-    <t>6787</t>
-  </si>
-  <si>
-    <t>9741</t>
-  </si>
-  <si>
-    <t>17191</t>
-  </si>
-  <si>
-    <t>20391</t>
-  </si>
-  <si>
-    <t>34581</t>
-  </si>
-  <si>
-    <t>35698</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>834</t>
+    <t>2026</t>
   </si>
   <si>
     <t>1288</t>
   </si>
   <si>
-    <t>1317</t>
-  </si>
-  <si>
-    <t>1434</t>
-  </si>
-  <si>
-    <t>1647</t>
-  </si>
-  <si>
-    <t>1738</t>
-  </si>
-  <si>
-    <t>3251</t>
-  </si>
-  <si>
-    <t>3267</t>
-  </si>
-  <si>
-    <t>3831</t>
-  </si>
-  <si>
-    <t>6848</t>
-  </si>
-  <si>
-    <t>38272</t>
-  </si>
-  <si>
-    <t>38441</t>
-  </si>
-  <si>
-    <t>6799</t>
-  </si>
-  <si>
-    <t>33287</t>
+    <t>4174</t>
+  </si>
+  <si>
+    <t>8838</t>
+  </si>
+  <si>
+    <t>17348</t>
   </si>
   <si>
     <t>35126</t>
   </si>
   <si>
-    <t>7884</t>
-  </si>
-  <si>
-    <t>889</t>
-  </si>
-  <si>
-    <t>DET PO GOTA LIMPA 800G EQUILIBRIO</t>
+    <t>2398</t>
   </si>
   <si>
     <t>BISC MARIA GERMANI 690G</t>
   </si>
   <si>
-    <t>AGUA SANITARIA SUPREMA 5 L</t>
-  </si>
-  <si>
-    <t>ENERG MONSTER LT 473ML ABSOLUT ZERO</t>
-  </si>
-  <si>
-    <t>CANJICA AMARELA CBS 400G</t>
-  </si>
-  <si>
-    <t>ERVA MATE PONCHE VERDE 500G TRAD</t>
-  </si>
-  <si>
-    <t>FARINHA TRIGO ROSESOL 5KG</t>
-  </si>
-  <si>
-    <t>ACUCAR CONFEITEIRO CBS 500G</t>
+    <t>DET LIQ MINUANO 500ML CLEAR</t>
+  </si>
+  <si>
+    <t>CERV ANTARCTICA SUBZERO GF 1L RETORNAVEL</t>
+  </si>
+  <si>
+    <t>CERV ORIGINAL1L RETORNAVEL</t>
+  </si>
+  <si>
+    <t>CERV POLAR EXPORT LT 473ML</t>
+  </si>
+  <si>
+    <t>REFRIG ANTARCTICA GUARANA PET 2L ZERO</t>
+  </si>
+  <si>
+    <t>REFRIG COCA COLA PET 600ML</t>
+  </si>
+  <si>
+    <t>DUETO FUGINI SH 170G ERVILHA MILHO</t>
+  </si>
+  <si>
+    <t>POLENTA PERDIZ 500G INST TEMP</t>
+  </si>
+  <si>
+    <t>MASSA S OVOS NORDESTE 1KG ESPAGUETE</t>
+  </si>
+  <si>
+    <t>CREME LEITE ITALAC TP 200G ZERO LACTOSE</t>
+  </si>
+  <si>
+    <t>TALCO BARUEL TENYS PE 100G PO WOMAN</t>
+  </si>
+  <si>
+    <t>LEITE UHT PET ELEGE 1L DESNATADO</t>
+  </si>
+  <si>
+    <t>ESC DENTAL ORAL B INDICA BLACK L2P1</t>
+  </si>
+  <si>
+    <t>ERVA MATE CAMBONA MOIDA GROSSA 1KG</t>
+  </si>
+  <si>
+    <t>FAROFA ROCHA 250G BACON</t>
+  </si>
+  <si>
+    <t>REFRIG COCA COLA PET 200ML ZERO</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SANO TP1 5KG</t>
+  </si>
+  <si>
+    <t>MASSA C OVOS NORDESTE 500G ESPAGUETE</t>
+  </si>
+  <si>
+    <t>AGUA SANIT GOTA LIMPA 1L</t>
+  </si>
+  <si>
+    <t>ALCOOL GEL SUPER VALE 450G</t>
+  </si>
+  <si>
+    <t>ALCOOL 46 SUPER VALE 1L</t>
+  </si>
+  <si>
+    <t>DET LIQ GOTA LIMPA 500ML LIMAO</t>
+  </si>
+  <si>
+    <t>LIMP ALCOOL SUPER VALE 1L BICABORN</t>
+  </si>
+  <si>
+    <t>SABAO BARRA YPE 800G COCO TOQUE AV</t>
+  </si>
+  <si>
+    <t>SABAO PO TIXAN 800G MACIEZ PRIMAVERA</t>
+  </si>
+  <si>
+    <t>DESINF YPE BAK 500ML TURQUESA</t>
+  </si>
+  <si>
+    <t>ALCOOL ARAUCARIA 46 1L</t>
+  </si>
+  <si>
+    <t>DET LIQ GIRANDO SOL 1L COCO</t>
+  </si>
+  <si>
+    <t>DET PO APYCE SH 1 6K ROSA</t>
+  </si>
+  <si>
+    <t>DET PO BRILHANTE CUID TOT CT 800G</t>
+  </si>
+  <si>
+    <t>RATICIDA RODILON ISCA 25G</t>
+  </si>
+  <si>
+    <t>SALG SNACK DOMELLY POLV 40G QJO</t>
+  </si>
+  <si>
+    <t>KIT SH CD DOVE 350ML 175ML AMINOACIDO</t>
+  </si>
+  <si>
+    <t>SH DOVE 190ML UV REPAIR GLOW</t>
+  </si>
+  <si>
+    <t>KIT SH CD PANTENE 300 150ML BOND REPAIR</t>
+  </si>
+  <si>
+    <t>DET LIQ APYCE SUPER ACAO SH 800ML</t>
+  </si>
+  <si>
+    <t>AGUA SANITARIA SUPREMA 2 L</t>
+  </si>
+  <si>
+    <t>AGUA MIN CRYSTAL PET 500ML C GAS</t>
+  </si>
+  <si>
+    <t>CHOC BARRA NEUGEBAUER 80G MEIO AMARGO</t>
+  </si>
+  <si>
+    <t>PAST DOCILE ROLLY MINTY 29G EXTRA FORTE</t>
+  </si>
+  <si>
+    <t>ARROZ BCO PILECCO NOBRE T1 2K</t>
+  </si>
+  <si>
+    <t>ARROZ PARBO RAROZ TP1 1KG</t>
+  </si>
+  <si>
+    <t>KETCHUP HELLMANNS BISN 380G TRAD</t>
+  </si>
+  <si>
+    <t>CREME LEITE ITALAC TP 200G</t>
+  </si>
+  <si>
+    <t>REFRIG ANTARCTICA GUARANA PET 3L</t>
+  </si>
+  <si>
+    <t>BISC DOCE ZEZE RAMINHO 200G</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SANO T1 2K</t>
+  </si>
+  <si>
+    <t>ARROZ BCO REQUINTE TP1 2KG</t>
+  </si>
+  <si>
+    <t>MOLHO TOM CAJAMAR SH 300G TRAD</t>
+  </si>
+  <si>
+    <t>FARINHA TRIGO ROSESOL 1KG</t>
+  </si>
+  <si>
+    <t>MASSA C OVOS ISABELA 500G LINGUINE</t>
+  </si>
+  <si>
+    <t>LEITE UHT SANTA CLARA DESN 1L</t>
+  </si>
+  <si>
+    <t>QUENTAO S ALCOOL 2L</t>
+  </si>
+  <si>
+    <t>REFRE HAPPY TP 1L PESSEGO</t>
+  </si>
+  <si>
+    <t>ACUCAR CRISTAL GASPARIN 5KG</t>
+  </si>
+  <si>
+    <t>SALG KEVYTOS BACON 13G C 50</t>
+  </si>
+  <si>
+    <t>BISC MARIA PARATI 740G</t>
+  </si>
+  <si>
+    <t>DET LIQ GOTA LIMPA 1L MACA</t>
+  </si>
+  <si>
+    <t>SALG KEVYTOS 55G BACON</t>
   </si>
   <si>
     <t>VH QUINTA CARVALHO TINTO 750ML SV</t>
   </si>
   <si>
-    <t>REFRIG ANTARCTICA GUARANA PET 2L</t>
-  </si>
-  <si>
-    <t>KETCHUP HELLMANNS BISN 380G PICANTE</t>
-  </si>
-  <si>
-    <t>KETCHUP HELLMANNS BISN 380G TRAD</t>
-  </si>
-  <si>
-    <t>LEITE UHT TIROL 1L ZERO LAC</t>
-  </si>
-  <si>
-    <t>AGUA SANIT IMPERIAL 1L</t>
-  </si>
-  <si>
-    <t>ACHOC PO NESCAU SH 2 01KG</t>
-  </si>
-  <si>
-    <t>ERVILHA ODERICH LT 200G</t>
-  </si>
-  <si>
-    <t>LAVA ROUPA ARIEL 700ML CLASSIC REF</t>
-  </si>
-  <si>
-    <t>LEITE LV ELEGE 1L ZERO LAC SEMI DES</t>
-  </si>
-  <si>
-    <t>LEITE SANTA CLARA LV SEMI DESN 1L</t>
-  </si>
-  <si>
-    <t>DESINF IMPERIAL 5L PINHO</t>
-  </si>
-  <si>
-    <t>MAIONESE LIZA CASEIRA 450G</t>
-  </si>
-  <si>
-    <t>GRAO DE BICO SALSARETTI 170G LT</t>
-  </si>
-  <si>
-    <t>DET LIQ BARBAREX 5L NEUTRO</t>
-  </si>
-  <si>
-    <t>AGUA MIN FLORESTA PET 5L S GAS</t>
-  </si>
-  <si>
-    <t>AGUA GASEIFICADA CRYSTAL PET 510ML SPARK</t>
-  </si>
-  <si>
-    <t>REFRIG ANTARCTICA GUARANA PET 3L</t>
+    <t>MILHO PIPOCA SERRA URUGUAI TP1 400G</t>
   </si>
   <si>
     <t>CHOC BARRA NESTLE 80G CLASSIC DUO</t>
   </si>
   <si>
-    <t>BISC PAO MEL DOMELLY MINI PANE 300G</t>
-  </si>
-  <si>
-    <t>BISC MARIA PARATI 740G</t>
-  </si>
-  <si>
-    <t>WAFER GIRASSOL 60G MORANGO</t>
-  </si>
-  <si>
-    <t>DOCE N BONN 1 05KG SUSPIRO</t>
-  </si>
-  <si>
-    <t>SALG KEVYTOS SHOW 38G CEBOLA</t>
-  </si>
-  <si>
-    <t>SALG ALFITOS 35G CHURRASCO</t>
-  </si>
-  <si>
-    <t>KEEP COOLER CLASSIC CITRUS 275ML</t>
-  </si>
-  <si>
-    <t>LIMP ALCOOL SUPER VALE 1L BICABORN</t>
-  </si>
-  <si>
-    <t>MOLHO FGO SABOR CASEIRO 1 01K</t>
-  </si>
-  <si>
-    <t>MOLHO TOM DIA 340G TRAD</t>
-  </si>
-  <si>
-    <t>LEITE SANTA CLARA 1L ZERO LACTOSE</t>
-  </si>
-  <si>
-    <t>AMAC APYCE 5L JASMIM RSA</t>
+    <t>AMAC CONC FOFO LV500 PG400ML AZUL TUDAO</t>
+  </si>
+  <si>
+    <t>AMAC AQUAFAST 2L ROSA JARD FLORI</t>
+  </si>
+  <si>
+    <t>DET LIQ GIRANDO SOL 1L GLICA</t>
   </si>
   <si>
     <t>DET PO APYCE MULT SH 800G ROSA</t>
   </si>
   <si>
-    <t>SABONETE DOVE 90G PELE SENSIVEL</t>
-  </si>
-  <si>
-    <t>REFRIG COCA COLA LT 350ML</t>
+    <t>MILHO VERDE ODERICH LT 200G</t>
+  </si>
+  <si>
+    <t>11/11/2024</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>23/09/2024</t>
+  </si>
+  <si>
+    <t>24/09/2024</t>
+  </si>
+  <si>
+    <t>27/09/2024</t>
+  </si>
+  <si>
+    <t>18/10/2024</t>
   </si>
   <si>
     <t>21/10/2024</t>
   </si>
   <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>11/11/2024</t>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>16/12/2024</t>
+  </si>
+  <si>
+    <t>17/12/2024</t>
+  </si>
+  <si>
+    <t>26/12/2024</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>17/10/2024</t>
+  </si>
+  <si>
+    <t>04/12/2024</t>
+  </si>
+  <si>
+    <t>30/08/2025</t>
+  </si>
+  <si>
+    <t>11/11/2025</t>
+  </si>
+  <si>
+    <t>19/12/2025</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
   </si>
   <si>
     <t>10/03/2026</t>
   </si>
   <si>
+    <t>18/09/2024</t>
+  </si>
+  <si>
+    <t>07/11/2024</t>
+  </si>
+  <si>
+    <t>27/11/2024</t>
+  </si>
+  <si>
+    <t>05/12/2024</t>
+  </si>
+  <si>
+    <t>10/12/2024</t>
+  </si>
+  <si>
+    <t>06/11/2024</t>
+  </si>
+  <si>
+    <t>11/12/2024</t>
+  </si>
+  <si>
+    <t>13/12/2024</t>
+  </si>
+  <si>
+    <t>17/11/2025</t>
+  </si>
+  <si>
+    <t>20/12/2024</t>
+  </si>
+  <si>
     <t>01/10/2024</t>
   </si>
   <si>
-    <t>05/10/2024</t>
-  </si>
-  <si>
-    <t>06/12/2024</t>
-  </si>
-  <si>
-    <t>10/12/2024</t>
-  </si>
-  <si>
-    <t>14/12/2024</t>
-  </si>
-  <si>
-    <t>18/10/2024</t>
-  </si>
-  <si>
-    <t>09/12/2024</t>
-  </si>
-  <si>
-    <t>23/12/2024</t>
-  </si>
-  <si>
-    <t>10/07/2025</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
-    <t>17/01/2026</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>21/09/2024</t>
-  </si>
-  <si>
-    <t>07/11/2024</t>
-  </si>
-  <si>
-    <t>08/11/2024</t>
-  </si>
-  <si>
-    <t>19/11/2024</t>
-  </si>
-  <si>
-    <t>23/11/2024</t>
-  </si>
-  <si>
-    <t>03/01/2025</t>
-  </si>
-  <si>
-    <t>29/04/2026</t>
-  </si>
-  <si>
-    <t>15/05/2026</t>
+    <t>30/11/2024</t>
   </si>
   <si>
     <t>20/12/2025</t>
   </si>
   <si>
-    <t>22/10/2024</t>
-  </si>
-  <si>
     <t>Ativo</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>18</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>529</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>3542</t>
+  </si>
+  <si>
+    <t>1312</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>790</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>3758</t>
+  </si>
+  <si>
+    <t>2181</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>886</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>1466</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>527</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>734</t>
+  </si>
+  <si>
+    <t>2041</t>
+  </si>
+  <si>
+    <t>439</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>793</t>
+  </si>
+  <si>
+    <t>1218</t>
+  </si>
+  <si>
+    <t>2029</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>1467</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>2853</t>
+  </si>
+  <si>
+    <t>1480</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>2059</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>808</t>
+  </si>
+  <si>
+    <t>1445</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>250</t>
   </si>
   <si>
     <t>50</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>48</t>
+    <t>11</t>
+  </si>
+  <si>
+    <t>679</t>
+  </si>
+  <si>
+    <t>572</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>1503</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>1444</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>902</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>1411</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>383</t>
+  </si>
+  <si>
+    <t>323</t>
   </si>
   <si>
     <t>260</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>243</t>
-  </si>
-  <si>
-    <t>458</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>703</t>
-  </si>
-  <si>
-    <t>1719</t>
-  </si>
-  <si>
-    <t>358</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>6139</t>
-  </si>
-  <si>
-    <t>536</t>
-  </si>
-  <si>
-    <t>338</t>
-  </si>
-  <si>
-    <t>606</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>835</t>
-  </si>
-  <si>
-    <t>745</t>
-  </si>
-  <si>
-    <t>975</t>
-  </si>
-  <si>
-    <t>1029</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>700</t>
-  </si>
-  <si>
-    <t>226</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>576</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>1207</t>
-  </si>
-  <si>
-    <t>1183</t>
-  </si>
-  <si>
-    <t>2255</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>406</t>
-  </si>
-  <si>
-    <t>408</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>541</t>
-  </si>
-  <si>
-    <t>2032</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>1395</t>
-  </si>
-  <si>
-    <t>153</t>
-  </si>
-  <si>
-    <t>446</t>
-  </si>
-  <si>
-    <t>636</t>
+    <t>980</t>
+  </si>
+  <si>
+    <t>3205</t>
+  </si>
+  <si>
+    <t>747</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>549</t>
   </si>
 </sst>
 </file>
@@ -1008,8 +1305,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S68"/>
+  <dimension ref="A1:S124"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="5" max="5" width="44" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
@@ -1081,161 +1381,161 @@
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="G2" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H2" t="s">
-        <v>151</v>
+        <v>212</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="O2">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="P2">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="Q2">
         <v>90</v>
       </c>
       <c r="R2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="G3" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H3" t="s">
-        <v>149</v>
+        <v>214</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>228</v>
+      </c>
+      <c r="O3">
+        <v>5</v>
+      </c>
+      <c r="P3">
         <v>10</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>173</v>
-      </c>
-      <c r="O3">
-        <v>18</v>
-      </c>
-      <c r="P3">
-        <v>24</v>
-      </c>
       <c r="Q3">
         <v>90</v>
       </c>
       <c r="R3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>46</v>
+        <v>241.08</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F4" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G4" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H4" t="s">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4" t="s">
-        <v>174</v>
+        <v>229</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="Q4">
         <v>90</v>
@@ -1244,275 +1544,275 @@
         <v>4</v>
       </c>
       <c r="S4">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="F5" t="s">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="G5" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H5" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>228</v>
+      </c>
+      <c r="O5">
+        <v>12</v>
+      </c>
+      <c r="P5">
+        <v>24</v>
+      </c>
+      <c r="Q5">
+        <v>90</v>
+      </c>
+      <c r="R5">
         <v>2</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>20</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>175</v>
-      </c>
-      <c r="O5">
-        <v>24</v>
-      </c>
-      <c r="P5">
-        <v>36</v>
-      </c>
-      <c r="Q5">
-        <v>90</v>
-      </c>
-      <c r="R5">
-        <v>4</v>
-      </c>
       <c r="S5">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>121</v>
+        <v>183</v>
       </c>
       <c r="G6" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H6" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>176</v>
+        <v>230</v>
       </c>
       <c r="O6">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="P6">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="Q6">
         <v>90</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S6">
-        <v>7.25</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F7" t="s">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="G7" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H7" t="s">
-        <v>163</v>
+        <v>215</v>
       </c>
       <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7">
         <v>16</v>
       </c>
-      <c r="J7">
-        <v>26</v>
-      </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>177</v>
+        <v>231</v>
       </c>
       <c r="O7">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P7">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="Q7">
         <v>90</v>
       </c>
       <c r="R7">
+        <v>3</v>
+      </c>
+      <c r="S7">
         <v>5</v>
-      </c>
-      <c r="S7">
-        <v>30.06</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="G8" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H8" t="s">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="I8">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J8">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N8" t="s">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="O8">
-        <v>12</v>
+        <v>326</v>
       </c>
       <c r="P8">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="Q8">
         <v>90</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="S8">
-        <v>8</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="G9" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H9" t="s">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J9">
-        <v>104</v>
+        <v>-23</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1524,72 +1824,72 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="O9">
         <v>120</v>
       </c>
       <c r="P9">
-        <v>144</v>
+        <v>192</v>
       </c>
       <c r="Q9">
         <v>90</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>5.83</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F10" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="G10" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H10" t="s">
-        <v>164</v>
+        <v>213</v>
       </c>
       <c r="I10">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="J10">
-        <v>33</v>
+        <v>-64</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="O10">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="Q10">
         <v>90</v>
@@ -1598,122 +1898,122 @@
         <v>2</v>
       </c>
       <c r="S10">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F11" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="G11" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H11" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="O11">
+        <v>39</v>
+      </c>
+      <c r="P11">
+        <v>54</v>
+      </c>
+      <c r="Q11">
+        <v>90</v>
+      </c>
+      <c r="R11">
+        <v>5</v>
+      </c>
+      <c r="S11">
         <v>7</v>
-      </c>
-      <c r="P11">
-        <v>12</v>
-      </c>
-      <c r="Q11">
-        <v>90</v>
-      </c>
-      <c r="R11">
-        <v>9</v>
-      </c>
-      <c r="S11">
-        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="F12" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="G12" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H12" t="s">
-        <v>149</v>
+        <v>214</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J12">
-        <v>7</v>
+        <v>-22</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>152</v>
+        <v>236</v>
       </c>
       <c r="O12">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="P12">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="Q12">
         <v>90</v>
       </c>
       <c r="R12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S12">
         <v>7</v>
@@ -1727,46 +2027,46 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" t="s">
+        <v>179</v>
+      </c>
+      <c r="G13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H13" t="s">
+        <v>213</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>12</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>228</v>
+      </c>
+      <c r="O13">
         <v>28</v>
       </c>
-      <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" t="s">
-        <v>133</v>
-      </c>
-      <c r="G13" t="s">
-        <v>148</v>
-      </c>
-      <c r="H13" t="s">
-        <v>150</v>
-      </c>
-      <c r="I13">
-        <v>20</v>
-      </c>
-      <c r="J13">
-        <v>-14</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>181</v>
-      </c>
-      <c r="O13">
-        <v>32</v>
-      </c>
       <c r="P13">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="Q13">
         <v>90</v>
@@ -1775,113 +2075,113 @@
         <v>3</v>
       </c>
       <c r="S13">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F14" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G14" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H14" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="I14">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>171</v>
+        <v>237</v>
       </c>
       <c r="O14">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="P14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Q14">
         <v>90</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="F15" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="G15" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H15" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>228</v>
+      </c>
+      <c r="O15">
         <v>12</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>151</v>
-      </c>
-      <c r="O15">
-        <v>18</v>
       </c>
       <c r="P15">
         <v>24</v>
@@ -1893,116 +2193,116 @@
         <v>2</v>
       </c>
       <c r="S15">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
         <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="F16" t="s">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="G16" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H16" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="I16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>191</v>
+        <v>-9</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="O16">
-        <v>240</v>
+        <v>42</v>
       </c>
       <c r="P16">
-        <v>360</v>
+        <v>52</v>
       </c>
       <c r="Q16">
         <v>90</v>
       </c>
       <c r="R16">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>17</v>
+        <v>73.599999999999994</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F17" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="G17" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H17" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="I17">
         <v>12</v>
       </c>
       <c r="J17">
+        <v>-14</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>239</v>
+      </c>
+      <c r="O17">
         <v>8</v>
       </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>183</v>
-      </c>
-      <c r="O17">
-        <v>10</v>
-      </c>
       <c r="P17">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q17">
         <v>90</v>
@@ -2011,243 +2311,243 @@
         <v>2</v>
       </c>
       <c r="S17">
-        <v>54</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="F18" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="G18" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H18" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J18">
-        <v>-12</v>
+        <v>393</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>166</v>
+        <v>240</v>
       </c>
       <c r="O18">
-        <v>8</v>
+        <v>566</v>
       </c>
       <c r="P18">
-        <v>12</v>
+        <v>878</v>
       </c>
       <c r="Q18">
         <v>90</v>
       </c>
       <c r="R18">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="S18">
-        <v>6</v>
+        <v>54.17</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="F19" t="s">
-        <v>135</v>
+        <v>192</v>
       </c>
       <c r="G19" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H19" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="I19">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>158</v>
+        <v>241</v>
       </c>
       <c r="O19">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="P19">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c r="Q19">
         <v>90</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="S19">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="F20" t="s">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="G20" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H20" t="s">
-        <v>153</v>
+        <v>217</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J20">
-        <v>9</v>
+        <v>-9</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M20">
         <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="O20">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="P20">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="Q20">
         <v>90</v>
       </c>
       <c r="R20">
+        <v>5</v>
+      </c>
+      <c r="S20">
         <v>14</v>
-      </c>
-      <c r="S20">
-        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F21" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="G21" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H21" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="I21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J21">
+        <v>8</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>10</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>243</v>
+      </c>
+      <c r="O21">
+        <v>39</v>
+      </c>
+      <c r="P21">
+        <v>54</v>
+      </c>
+      <c r="Q21">
+        <v>90</v>
+      </c>
+      <c r="R21">
         <v>4</v>
       </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>185</v>
-      </c>
-      <c r="O21">
-        <v>6</v>
-      </c>
-      <c r="P21">
-        <v>12</v>
-      </c>
-      <c r="Q21">
-        <v>90</v>
-      </c>
-      <c r="R21">
-        <v>2</v>
-      </c>
       <c r="S21">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -2255,167 +2555,167 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F22" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="G22" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H22" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="I22">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J22">
+        <v>64</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>244</v>
+      </c>
+      <c r="O22">
+        <v>102</v>
+      </c>
+      <c r="P22">
+        <v>126</v>
+      </c>
+      <c r="Q22">
+        <v>90</v>
+      </c>
+      <c r="R22">
+        <v>6</v>
+      </c>
+      <c r="S22">
         <v>63</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>264</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>186</v>
-      </c>
-      <c r="O22">
-        <v>342</v>
-      </c>
-      <c r="P22">
-        <v>534</v>
-      </c>
-      <c r="Q22">
-        <v>90</v>
-      </c>
-      <c r="R22">
-        <v>9</v>
-      </c>
-      <c r="S22">
-        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="G23" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H23" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="I23">
         <v>12</v>
       </c>
       <c r="J23">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="O23">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="P23">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="Q23">
         <v>90</v>
       </c>
       <c r="R23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S23">
-        <v>9.83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="F24" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="G24" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H24" t="s">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="I24">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>188</v>
+        <v>246</v>
       </c>
       <c r="O24">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="P24">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="Q24">
         <v>90</v>
@@ -2424,7 +2724,7 @@
         <v>2</v>
       </c>
       <c r="S24">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -2432,31 +2732,31 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F25" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="G25" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H25" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="I25">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J25">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -2468,187 +2768,187 @@
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="O25">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="P25">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Q25">
         <v>90</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" t="s">
+        <v>179</v>
+      </c>
+      <c r="G26" t="s">
+        <v>211</v>
+      </c>
+      <c r="H26" t="s">
+        <v>214</v>
+      </c>
+      <c r="I26">
         <v>24</v>
       </c>
-      <c r="C26" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" t="s">
-        <v>125</v>
-      </c>
-      <c r="G26" t="s">
-        <v>148</v>
-      </c>
-      <c r="H26" t="s">
-        <v>153</v>
-      </c>
-      <c r="I26">
-        <v>3</v>
-      </c>
       <c r="J26">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>169</v>
+        <v>247</v>
       </c>
       <c r="O26">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="Q26">
         <v>90</v>
       </c>
       <c r="R26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="F27" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="G27" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H27" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="I27">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="N27" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="O27">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="P27">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="Q27">
         <v>90</v>
       </c>
       <c r="R27">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S27">
-        <v>27.38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
         <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="F28" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="G28" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H28" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J28">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="O28">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P28">
         <v>40</v>
@@ -2657,10 +2957,10 @@
         <v>90</v>
       </c>
       <c r="R28">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>7.25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -2674,43 +2974,43 @@
         <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="F29" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="G29" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H29" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="I29">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M29">
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="O29">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="P29">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="Q29">
         <v>90</v>
@@ -2719,98 +3019,98 @@
         <v>2</v>
       </c>
       <c r="S29">
-        <v>5.8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
         <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E30" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="F30" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="G30" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H30" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="I30">
         <v>12</v>
       </c>
       <c r="J30">
-        <v>-39</v>
+        <v>-6</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="O30">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="P30">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q30">
         <v>90</v>
       </c>
       <c r="R30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>9.83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
         <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="F31" t="s">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="G31" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H31" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="I31">
         <v>12</v>
       </c>
       <c r="J31">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -2822,81 +3122,81 @@
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="O31">
-        <v>240</v>
+        <v>46</v>
       </c>
       <c r="P31">
-        <v>360</v>
+        <v>58</v>
       </c>
       <c r="Q31">
         <v>90</v>
       </c>
       <c r="R31">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>17</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
         <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E32" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="F32" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="G32" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H32" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="I32">
         <v>12</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M32">
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="O32">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="P32">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q32">
         <v>90</v>
       </c>
       <c r="R32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -2904,58 +3204,58 @@
         <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
         <v>30</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F33" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="G33" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H33" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="I33">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J33">
-        <v>-31</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M33">
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="O33">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>90</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S33">
-        <v>7</v>
+        <v>241.08</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -2966,143 +3266,143 @@
         <v>25</v>
       </c>
       <c r="C34" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" t="s">
+        <v>139</v>
+      </c>
+      <c r="F34" t="s">
+        <v>180</v>
+      </c>
+      <c r="G34" t="s">
+        <v>211</v>
+      </c>
+      <c r="H34" t="s">
+        <v>218</v>
+      </c>
+      <c r="I34">
+        <v>13</v>
+      </c>
+      <c r="J34">
+        <v>30</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>253</v>
+      </c>
+      <c r="O34">
         <v>31</v>
       </c>
-      <c r="D34" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" t="s">
-        <v>86</v>
-      </c>
-      <c r="F34" t="s">
-        <v>130</v>
-      </c>
-      <c r="G34" t="s">
-        <v>148</v>
-      </c>
-      <c r="H34" t="s">
-        <v>149</v>
-      </c>
-      <c r="I34">
-        <v>6</v>
-      </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>6</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34" t="s">
-        <v>161</v>
-      </c>
-      <c r="O34">
-        <v>22</v>
-      </c>
       <c r="P34">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="Q34">
         <v>90</v>
       </c>
       <c r="R34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S34">
-        <v>7</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="35" spans="1:19">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E35" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="F35" t="s">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="G35" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H35" t="s">
-        <v>155</v>
+        <v>219</v>
       </c>
       <c r="I35">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J35">
-        <v>108</v>
+        <v>-6</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N35" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="O35">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="P35">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="Q35">
         <v>90</v>
       </c>
       <c r="R35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>10</v>
+        <v>121.7</v>
       </c>
     </row>
     <row r="36" spans="1:19">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E36" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="F36" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="G36" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H36" t="s">
-        <v>162</v>
+        <v>220</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -3111,19 +3411,19 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="M36">
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="P36">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="Q36">
         <v>90</v>
@@ -3132,7 +3432,7 @@
         <v>2</v>
       </c>
       <c r="S36">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -3143,55 +3443,55 @@
         <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="F37" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="G37" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H37" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="I37">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J37">
-        <v>22</v>
+        <v>-18</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
       <c r="N37" t="s">
-        <v>196</v>
+        <v>255</v>
       </c>
       <c r="O37">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="Q37">
         <v>90</v>
       </c>
       <c r="R37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S37">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -3199,58 +3499,58 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" t="s">
+        <v>143</v>
+      </c>
+      <c r="F38" t="s">
+        <v>193</v>
+      </c>
+      <c r="G38" t="s">
+        <v>211</v>
+      </c>
+      <c r="H38" t="s">
+        <v>215</v>
+      </c>
+      <c r="I38">
+        <v>8</v>
+      </c>
+      <c r="J38">
         <v>26</v>
       </c>
-      <c r="C38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" t="s">
-        <v>41</v>
-      </c>
-      <c r="E38" t="s">
-        <v>83</v>
-      </c>
-      <c r="F38" t="s">
-        <v>128</v>
-      </c>
-      <c r="G38" t="s">
-        <v>148</v>
-      </c>
-      <c r="H38" t="s">
-        <v>155</v>
-      </c>
-      <c r="I38">
-        <v>12</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M38">
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="O38">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="P38">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="Q38">
         <v>90</v>
       </c>
       <c r="R38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S38">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -3258,49 +3558,49 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" t="s">
+        <v>194</v>
+      </c>
+      <c r="G39" t="s">
+        <v>211</v>
+      </c>
+      <c r="H39" t="s">
+        <v>213</v>
+      </c>
+      <c r="I39">
+        <v>12</v>
+      </c>
+      <c r="J39">
         <v>26</v>
       </c>
-      <c r="C39" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" t="s">
-        <v>42</v>
-      </c>
-      <c r="E39" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" t="s">
-        <v>129</v>
-      </c>
-      <c r="G39" t="s">
-        <v>148</v>
-      </c>
-      <c r="H39" t="s">
-        <v>150</v>
-      </c>
-      <c r="I39">
-        <v>20</v>
-      </c>
-      <c r="J39">
-        <v>24</v>
-      </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M39">
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="O39">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="P39">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="Q39">
         <v>90</v>
@@ -3309,7 +3609,7 @@
         <v>2</v>
       </c>
       <c r="S39">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -3317,117 +3617,117 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="E40" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="F40" t="s">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="G40" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H40" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="O40">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P40">
+        <v>12</v>
+      </c>
+      <c r="Q40">
+        <v>90</v>
+      </c>
+      <c r="R40">
+        <v>2</v>
+      </c>
+      <c r="S40">
         <v>20</v>
-      </c>
-      <c r="Q40">
-        <v>90</v>
-      </c>
-      <c r="R40">
-        <v>8</v>
-      </c>
-      <c r="S40">
-        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E41" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="F41" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
       <c r="G41" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H41" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="I41">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J41">
-        <v>-4</v>
+        <v>11</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>199</v>
+        <v>256</v>
       </c>
       <c r="O41">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="P41">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="Q41">
         <v>90</v>
       </c>
       <c r="R41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S41">
-        <v>27.38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -3438,105 +3738,105 @@
         <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" t="s">
+        <v>197</v>
+      </c>
+      <c r="G42" t="s">
+        <v>211</v>
+      </c>
+      <c r="H42" t="s">
+        <v>216</v>
+      </c>
+      <c r="I42">
+        <v>6</v>
+      </c>
+      <c r="J42">
+        <v>36</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>6</v>
+      </c>
+      <c r="M42">
+        <v>24</v>
+      </c>
+      <c r="N42" t="s">
+        <v>257</v>
+      </c>
+      <c r="O42">
         <v>80</v>
       </c>
-      <c r="F42" t="s">
-        <v>124</v>
-      </c>
-      <c r="G42" t="s">
-        <v>148</v>
-      </c>
-      <c r="H42" t="s">
-        <v>152</v>
-      </c>
-      <c r="I42">
-        <v>10</v>
-      </c>
-      <c r="J42">
-        <v>-12</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>10</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42" t="s">
-        <v>200</v>
-      </c>
-      <c r="O42">
-        <v>14</v>
-      </c>
       <c r="P42">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="Q42">
         <v>90</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="S42">
-        <v>5.8</v>
+        <v>564</v>
       </c>
     </row>
     <row r="43" spans="1:19">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="E43" t="s">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="F43" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H43" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="I43">
         <v>12</v>
       </c>
       <c r="J43">
-        <v>-36</v>
+        <v>22</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="M43">
         <v>0</v>
       </c>
       <c r="N43" t="s">
-        <v>201</v>
+        <v>258</v>
       </c>
       <c r="O43">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="P43">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q43">
         <v>90</v>
@@ -3545,98 +3845,98 @@
         <v>2</v>
       </c>
       <c r="S43">
-        <v>7</v>
+        <v>87.42</v>
       </c>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E44" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="F44" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="G44" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H44" t="s">
-        <v>154</v>
+        <v>221</v>
       </c>
       <c r="I44">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="J44">
-        <v>92</v>
+        <v>-37</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M44">
         <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>202</v>
+        <v>259</v>
       </c>
       <c r="O44">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="P44">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="Q44">
         <v>90</v>
       </c>
       <c r="R44">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S44">
-        <v>5</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="45" spans="1:19">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="E45" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="F45" t="s">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="G45" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H45" t="s">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -3648,479 +3948,479 @@
         <v>0</v>
       </c>
       <c r="N45" t="s">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="O45">
+        <v>10</v>
+      </c>
+      <c r="P45">
         <v>22</v>
       </c>
-      <c r="P45">
-        <v>34</v>
-      </c>
       <c r="Q45">
         <v>90</v>
       </c>
       <c r="R45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:19">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B46" t="s">
         <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E46" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="F46" t="s">
-        <v>122</v>
+        <v>192</v>
       </c>
       <c r="G46" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H46" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="I46">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J46">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M46">
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="O46">
-        <v>144</v>
+        <v>31</v>
       </c>
       <c r="P46">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="Q46">
         <v>90</v>
       </c>
       <c r="R46">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S46">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B47" t="s">
         <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="E47" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="F47" t="s">
-        <v>122</v>
+        <v>201</v>
       </c>
       <c r="G47" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H47" t="s">
-        <v>155</v>
+        <v>222</v>
       </c>
       <c r="I47">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J47">
-        <v>-33</v>
+        <v>0</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M47">
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="O47">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="P47">
-        <v>168</v>
+        <v>48</v>
       </c>
       <c r="Q47">
         <v>90</v>
       </c>
       <c r="R47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S47">
-        <v>13.92</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:19">
       <c r="A48" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" t="s">
+        <v>153</v>
+      </c>
+      <c r="F48" t="s">
+        <v>202</v>
+      </c>
+      <c r="G48" t="s">
+        <v>211</v>
+      </c>
+      <c r="H48" t="s">
+        <v>214</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>-6</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>11</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48" t="s">
+        <v>222</v>
+      </c>
+      <c r="O48">
+        <v>13</v>
+      </c>
+      <c r="P48">
         <v>20</v>
       </c>
-      <c r="B48" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" t="s">
-        <v>33</v>
-      </c>
-      <c r="D48" t="s">
-        <v>56</v>
-      </c>
-      <c r="E48" t="s">
-        <v>98</v>
-      </c>
-      <c r="F48" t="s">
-        <v>123</v>
-      </c>
-      <c r="G48" t="s">
-        <v>148</v>
-      </c>
-      <c r="H48" t="s">
-        <v>151</v>
-      </c>
-      <c r="I48">
-        <v>4</v>
-      </c>
-      <c r="J48">
-        <v>-11</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>4</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48" t="s">
-        <v>205</v>
-      </c>
-      <c r="O48">
-        <v>8</v>
-      </c>
-      <c r="P48">
-        <v>12</v>
-      </c>
       <c r="Q48">
         <v>90</v>
       </c>
       <c r="R48">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S48">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:19">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C49" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="E49" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F49" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="G49" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H49" t="s">
-        <v>162</v>
+        <v>212</v>
       </c>
       <c r="I49">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49" t="s">
-        <v>206</v>
+        <v>261</v>
       </c>
       <c r="O49">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="P49">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="Q49">
         <v>90</v>
       </c>
       <c r="R49">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="S49">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:19">
       <c r="A50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" t="s">
+        <v>86</v>
+      </c>
+      <c r="E50" t="s">
+        <v>154</v>
+      </c>
+      <c r="F50" t="s">
+        <v>189</v>
+      </c>
+      <c r="G50" t="s">
+        <v>211</v>
+      </c>
+      <c r="H50" t="s">
+        <v>214</v>
+      </c>
+      <c r="I50">
         <v>24</v>
       </c>
-      <c r="C50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D50" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" t="s">
-        <v>118</v>
-      </c>
-      <c r="F50" t="s">
-        <v>146</v>
-      </c>
-      <c r="G50" t="s">
-        <v>148</v>
-      </c>
-      <c r="H50" t="s">
-        <v>165</v>
-      </c>
-      <c r="I50">
-        <v>25</v>
-      </c>
       <c r="J50">
-        <v>28</v>
+        <v>-22</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M50">
         <v>0</v>
       </c>
       <c r="N50" t="s">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="O50">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="P50">
-        <v>62</v>
+        <v>156</v>
       </c>
       <c r="Q50">
         <v>90</v>
       </c>
       <c r="R50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S50">
-        <v>35.479999999999997</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:19">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="E51" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="F51" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="G51" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H51" t="s">
-        <v>153</v>
+        <v>213</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J51">
-        <v>-11</v>
+        <v>12</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M51">
         <v>0</v>
       </c>
       <c r="N51" t="s">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="O51">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="P51">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="Q51">
         <v>90</v>
       </c>
       <c r="R51">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="S51">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:19">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E52" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F52" t="s">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="G52" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H52" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="I52">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J52">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K52">
         <v>0</v>
       </c>
       <c r="L52">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M52">
         <v>0</v>
       </c>
       <c r="N52" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="O52">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="P52">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="Q52">
         <v>90</v>
       </c>
       <c r="R52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S52">
-        <v>27.38</v>
+        <v>241.08</v>
       </c>
     </row>
     <row r="53" spans="1:19">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E53" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="F53" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="G53" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H53" t="s">
-        <v>151</v>
+        <v>223</v>
       </c>
       <c r="I53">
         <v>4</v>
       </c>
       <c r="J53">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K53">
         <v>0</v>
       </c>
       <c r="L53">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M53">
         <v>0</v>
       </c>
       <c r="N53" t="s">
-        <v>210</v>
+        <v>264</v>
       </c>
       <c r="O53">
         <v>24</v>
@@ -4132,178 +4432,178 @@
         <v>90</v>
       </c>
       <c r="R53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S53">
-        <v>7.25</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="54" spans="1:19">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C54" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D54" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="E54" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="F54" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="G54" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H54" t="s">
-        <v>154</v>
+        <v>224</v>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J54">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M54">
         <v>0</v>
       </c>
       <c r="N54" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="O54">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="P54">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="Q54">
         <v>90</v>
       </c>
       <c r="R54">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="S54">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:19">
       <c r="A55" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C55" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E55" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="F55" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="G55" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H55" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="I55">
+        <v>10</v>
+      </c>
+      <c r="J55">
+        <v>-5</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55" t="s">
+        <v>266</v>
+      </c>
+      <c r="O55">
+        <v>28</v>
+      </c>
+      <c r="P55">
+        <v>48</v>
+      </c>
+      <c r="Q55">
+        <v>90</v>
+      </c>
+      <c r="R55">
         <v>5</v>
       </c>
-      <c r="J55">
-        <v>3</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>5</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55" t="s">
-        <v>154</v>
-      </c>
-      <c r="O55">
-        <v>11</v>
-      </c>
-      <c r="P55">
-        <v>16</v>
-      </c>
-      <c r="Q55">
-        <v>90</v>
-      </c>
-      <c r="R55">
-        <v>2</v>
-      </c>
       <c r="S55">
-        <v>6</v>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="56" spans="1:19">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D56" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="E56" t="s">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="F56" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="G56" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H56" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M56">
         <v>0</v>
       </c>
       <c r="N56" t="s">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="O56">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="P56">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q56">
         <v>90</v>
@@ -4312,361 +4612,361 @@
         <v>4</v>
       </c>
       <c r="S56">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:19">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D57" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="E57" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="F57" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="G57" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H57" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="I57">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="K57">
         <v>0</v>
       </c>
       <c r="L57">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M57">
         <v>0</v>
       </c>
       <c r="N57" t="s">
-        <v>154</v>
+        <v>268</v>
       </c>
       <c r="O57">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="P57">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="Q57">
         <v>90</v>
       </c>
       <c r="R57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S57">
-        <v>6</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="58" spans="1:19">
       <c r="A58" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D58" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E58" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="F58" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="G58" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H58" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="I58">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="J58">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K58">
         <v>0</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M58">
         <v>0</v>
       </c>
       <c r="N58" t="s">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="O58">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="P58">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="Q58">
         <v>90</v>
       </c>
       <c r="R58">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="E59" t="s">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="F59" t="s">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="G59" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H59" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="I59">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="J59">
-        <v>5</v>
+        <v>-49</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="M59">
         <v>0</v>
       </c>
       <c r="N59" t="s">
-        <v>213</v>
+        <v>270</v>
       </c>
       <c r="O59">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="P59">
-        <v>51</v>
+        <v>160</v>
       </c>
       <c r="Q59">
         <v>90</v>
       </c>
       <c r="R59">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S59">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:19">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D60" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E60" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="F60" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="G60" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H60" t="s">
-        <v>166</v>
+        <v>212</v>
       </c>
       <c r="I60">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="J60">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60" t="s">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="O60">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="P60">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="Q60">
         <v>90</v>
       </c>
       <c r="R60">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S60">
-        <v>73.44</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="61" spans="1:19">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D61" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E61" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="F61" t="s">
-        <v>122</v>
+        <v>187</v>
       </c>
       <c r="G61" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H61" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="I61">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J61">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K61">
         <v>0</v>
       </c>
       <c r="L61">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61" t="s">
-        <v>215</v>
+        <v>272</v>
       </c>
       <c r="O61">
-        <v>168</v>
+        <v>9</v>
       </c>
       <c r="P61">
-        <v>180</v>
+        <v>24</v>
       </c>
       <c r="Q61">
         <v>90</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S61">
-        <v>13.92</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62" t="s">
+        <v>161</v>
+      </c>
+      <c r="F62" t="s">
+        <v>188</v>
+      </c>
+      <c r="G62" t="s">
+        <v>211</v>
+      </c>
+      <c r="H62" t="s">
+        <v>219</v>
+      </c>
+      <c r="I62">
         <v>20</v>
       </c>
-      <c r="B62" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" t="s">
-        <v>35</v>
-      </c>
-      <c r="D62" t="s">
-        <v>39</v>
-      </c>
-      <c r="E62" t="s">
-        <v>81</v>
-      </c>
-      <c r="F62" t="s">
-        <v>125</v>
-      </c>
-      <c r="G62" t="s">
-        <v>148</v>
-      </c>
-      <c r="H62" t="s">
-        <v>153</v>
-      </c>
-      <c r="I62">
-        <v>3</v>
-      </c>
       <c r="J62">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62" t="s">
-        <v>216</v>
+        <v>273</v>
       </c>
       <c r="O62">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="P62">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="Q62">
         <v>90</v>
       </c>
       <c r="R62">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S62">
-        <v>24</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4677,52 +4977,52 @@
         <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E63" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="G63" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H63" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="I63">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J63">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
       <c r="N63" t="s">
-        <v>217</v>
+        <v>274</v>
       </c>
       <c r="O63">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="P63">
-        <v>198</v>
+        <v>54</v>
       </c>
       <c r="Q63">
         <v>90</v>
       </c>
       <c r="R63">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S63">
         <v>7</v>
@@ -4730,223 +5030,223 @@
     </row>
     <row r="64" spans="1:19">
       <c r="A64" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D64" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="E64" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="F64" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="G64" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H64" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="I64">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="M64">
         <v>0</v>
       </c>
       <c r="N64" t="s">
-        <v>218</v>
+        <v>275</v>
       </c>
       <c r="O64">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="P64">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="Q64">
         <v>90</v>
       </c>
       <c r="R64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S64">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:19">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B65" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" t="s">
+        <v>32</v>
+      </c>
+      <c r="D65" t="s">
+        <v>52</v>
+      </c>
+      <c r="E65" t="s">
+        <v>120</v>
+      </c>
+      <c r="F65" t="s">
+        <v>189</v>
+      </c>
+      <c r="G65" t="s">
+        <v>211</v>
+      </c>
+      <c r="H65" t="s">
+        <v>214</v>
+      </c>
+      <c r="I65">
         <v>24</v>
       </c>
-      <c r="C65" t="s">
-        <v>36</v>
-      </c>
-      <c r="D65" t="s">
-        <v>53</v>
-      </c>
-      <c r="E65" t="s">
-        <v>95</v>
-      </c>
-      <c r="F65" t="s">
-        <v>122</v>
-      </c>
-      <c r="G65" t="s">
-        <v>148</v>
-      </c>
-      <c r="H65" t="s">
-        <v>160</v>
-      </c>
-      <c r="I65">
-        <v>10</v>
-      </c>
       <c r="J65">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M65">
         <v>0</v>
       </c>
       <c r="N65" t="s">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="O65">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="P65">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="Q65">
         <v>90</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>5.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:19">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E66" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="F66" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="G66" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H66" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="I66">
         <v>12</v>
       </c>
       <c r="J66">
-        <v>150</v>
+        <v>-8</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M66">
         <v>0</v>
       </c>
       <c r="N66" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="O66">
-        <v>240</v>
+        <v>28</v>
       </c>
       <c r="P66">
-        <v>360</v>
+        <v>52</v>
       </c>
       <c r="Q66">
         <v>90</v>
       </c>
       <c r="R66">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S66">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:19">
       <c r="A67" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C67" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E67" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="F67" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="G67" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H67" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="I67">
         <v>12</v>
       </c>
       <c r="J67">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M67">
         <v>0</v>
       </c>
       <c r="N67" t="s">
-        <v>220</v>
+        <v>276</v>
       </c>
       <c r="O67">
         <v>96</v>
@@ -4961,57 +5261,57 @@
         <v>3</v>
       </c>
       <c r="S67">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:19">
       <c r="A68" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D68" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="E68" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="F68" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="G68" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H68" t="s">
-        <v>162</v>
+        <v>216</v>
       </c>
       <c r="I68">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M68">
         <v>0</v>
       </c>
       <c r="N68" t="s">
-        <v>168</v>
+        <v>277</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q68">
         <v>90</v>
@@ -5020,10 +5320,3315 @@
         <v>2</v>
       </c>
       <c r="S68">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19">
+      <c r="A69" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69" t="s">
+        <v>96</v>
+      </c>
+      <c r="E69" t="s">
+        <v>164</v>
+      </c>
+      <c r="F69" t="s">
+        <v>206</v>
+      </c>
+      <c r="G69" t="s">
+        <v>211</v>
+      </c>
+      <c r="H69" t="s">
+        <v>213</v>
+      </c>
+      <c r="I69">
+        <v>12</v>
+      </c>
+      <c r="J69">
+        <v>10</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69" t="s">
+        <v>219</v>
+      </c>
+      <c r="O69">
+        <v>12</v>
+      </c>
+      <c r="P69">
+        <v>24</v>
+      </c>
+      <c r="Q69">
+        <v>90</v>
+      </c>
+      <c r="R69">
+        <v>2</v>
+      </c>
+      <c r="S69">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19">
+      <c r="A70" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" t="s">
+        <v>97</v>
+      </c>
+      <c r="E70" t="s">
+        <v>165</v>
+      </c>
+      <c r="F70" t="s">
+        <v>191</v>
+      </c>
+      <c r="G70" t="s">
+        <v>211</v>
+      </c>
+      <c r="H70" t="s">
+        <v>216</v>
+      </c>
+      <c r="I70">
+        <v>6</v>
+      </c>
+      <c r="J70">
+        <v>140</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70" t="s">
+        <v>278</v>
+      </c>
+      <c r="O70">
+        <v>158</v>
+      </c>
+      <c r="P70">
+        <v>248</v>
+      </c>
+      <c r="Q70">
+        <v>90</v>
+      </c>
+      <c r="R70">
+        <v>18</v>
+      </c>
+      <c r="S70">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19">
+      <c r="A71" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" t="s">
+        <v>33</v>
+      </c>
+      <c r="D71" t="s">
+        <v>59</v>
+      </c>
+      <c r="E71" t="s">
+        <v>127</v>
+      </c>
+      <c r="F71" t="s">
+        <v>192</v>
+      </c>
+      <c r="G71" t="s">
+        <v>211</v>
+      </c>
+      <c r="H71" t="s">
+        <v>216</v>
+      </c>
+      <c r="I71">
+        <v>6</v>
+      </c>
+      <c r="J71">
+        <v>-57</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71" t="s">
+        <v>279</v>
+      </c>
+      <c r="O71">
+        <v>88</v>
+      </c>
+      <c r="P71">
+        <v>112</v>
+      </c>
+      <c r="Q71">
+        <v>90</v>
+      </c>
+      <c r="R71">
+        <v>19</v>
+      </c>
+      <c r="S71">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19">
+      <c r="A72" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" t="s">
+        <v>33</v>
+      </c>
+      <c r="D72" t="s">
+        <v>51</v>
+      </c>
+      <c r="E72" t="s">
+        <v>119</v>
+      </c>
+      <c r="F72" t="s">
+        <v>188</v>
+      </c>
+      <c r="G72" t="s">
+        <v>211</v>
+      </c>
+      <c r="H72" t="s">
+        <v>212</v>
+      </c>
+      <c r="I72">
+        <v>10</v>
+      </c>
+      <c r="J72">
+        <v>-6</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>10</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72" t="s">
+        <v>219</v>
+      </c>
+      <c r="O72">
+        <v>11</v>
+      </c>
+      <c r="P72">
+        <v>26</v>
+      </c>
+      <c r="Q72">
+        <v>90</v>
+      </c>
+      <c r="R72">
+        <v>2</v>
+      </c>
+      <c r="S72">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19">
+      <c r="A73" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" t="s">
+        <v>98</v>
+      </c>
+      <c r="E73" t="s">
+        <v>166</v>
+      </c>
+      <c r="F73" t="s">
+        <v>207</v>
+      </c>
+      <c r="G73" t="s">
+        <v>211</v>
+      </c>
+      <c r="H73" t="s">
+        <v>212</v>
+      </c>
+      <c r="I73">
+        <v>10</v>
+      </c>
+      <c r="J73">
+        <v>10</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>20</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73" t="s">
+        <v>280</v>
+      </c>
+      <c r="O73">
+        <v>33</v>
+      </c>
+      <c r="P73">
+        <v>51</v>
+      </c>
+      <c r="Q73">
+        <v>90</v>
+      </c>
+      <c r="R73">
+        <v>3</v>
+      </c>
+      <c r="S73">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19">
+      <c r="A74" t="s">
+        <v>19</v>
+      </c>
+      <c r="B74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C74" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" t="s">
+        <v>86</v>
+      </c>
+      <c r="E74" t="s">
+        <v>154</v>
+      </c>
+      <c r="F74" t="s">
+        <v>189</v>
+      </c>
+      <c r="G74" t="s">
+        <v>211</v>
+      </c>
+      <c r="H74" t="s">
+        <v>214</v>
+      </c>
+      <c r="I74">
+        <v>24</v>
+      </c>
+      <c r="J74">
+        <v>282</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>48</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74" t="s">
+        <v>281</v>
+      </c>
+      <c r="O74">
+        <v>360</v>
+      </c>
+      <c r="P74">
+        <v>504</v>
+      </c>
+      <c r="Q74">
+        <v>90</v>
+      </c>
+      <c r="R74">
+        <v>8</v>
+      </c>
+      <c r="S74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19">
+      <c r="A75" t="s">
+        <v>22</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" t="s">
+        <v>47</v>
+      </c>
+      <c r="E75" t="s">
+        <v>115</v>
+      </c>
+      <c r="F75" t="s">
+        <v>184</v>
+      </c>
+      <c r="G75" t="s">
+        <v>211</v>
+      </c>
+      <c r="H75" t="s">
+        <v>215</v>
+      </c>
+      <c r="I75">
+        <v>8</v>
+      </c>
+      <c r="J75">
+        <v>9</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75" t="s">
+        <v>282</v>
+      </c>
+      <c r="O75">
+        <v>18</v>
+      </c>
+      <c r="P75">
+        <v>34</v>
+      </c>
+      <c r="Q75">
+        <v>90</v>
+      </c>
+      <c r="R75">
+        <v>4</v>
+      </c>
+      <c r="S75">
         <v>5</v>
       </c>
     </row>
+    <row r="76" spans="1:19">
+      <c r="A76" t="s">
+        <v>22</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" t="s">
+        <v>87</v>
+      </c>
+      <c r="E76" t="s">
+        <v>155</v>
+      </c>
+      <c r="F76" t="s">
+        <v>185</v>
+      </c>
+      <c r="G76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H76" t="s">
+        <v>223</v>
+      </c>
+      <c r="I76">
+        <v>4</v>
+      </c>
+      <c r="J76">
+        <v>4</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76" t="s">
+        <v>283</v>
+      </c>
+      <c r="O76">
+        <v>40</v>
+      </c>
+      <c r="P76">
+        <v>64</v>
+      </c>
+      <c r="Q76">
+        <v>90</v>
+      </c>
+      <c r="R76">
+        <v>15</v>
+      </c>
+      <c r="S76">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19">
+      <c r="A77" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" t="s">
+        <v>42</v>
+      </c>
+      <c r="E77" t="s">
+        <v>110</v>
+      </c>
+      <c r="F77" t="s">
+        <v>178</v>
+      </c>
+      <c r="G77" t="s">
+        <v>211</v>
+      </c>
+      <c r="H77" t="s">
+        <v>212</v>
+      </c>
+      <c r="I77">
+        <v>10</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77" t="s">
+        <v>284</v>
+      </c>
+      <c r="O77">
+        <v>10</v>
+      </c>
+      <c r="P77">
+        <v>20</v>
+      </c>
+      <c r="Q77">
+        <v>90</v>
+      </c>
+      <c r="R77">
+        <v>2</v>
+      </c>
+      <c r="S77">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" t="s">
+        <v>34</v>
+      </c>
+      <c r="D78" t="s">
+        <v>99</v>
+      </c>
+      <c r="E78" t="s">
+        <v>167</v>
+      </c>
+      <c r="F78" t="s">
+        <v>178</v>
+      </c>
+      <c r="G78" t="s">
+        <v>211</v>
+      </c>
+      <c r="H78" t="s">
+        <v>213</v>
+      </c>
+      <c r="I78">
+        <v>12</v>
+      </c>
+      <c r="J78">
+        <v>13</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78" t="s">
+        <v>285</v>
+      </c>
+      <c r="O78">
+        <v>36</v>
+      </c>
+      <c r="P78">
+        <v>48</v>
+      </c>
+      <c r="Q78">
+        <v>90</v>
+      </c>
+      <c r="R78">
+        <v>3</v>
+      </c>
+      <c r="S78">
+        <v>12.83</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
+      <c r="A79" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" t="s">
+        <v>49</v>
+      </c>
+      <c r="E79" t="s">
+        <v>117</v>
+      </c>
+      <c r="F79" t="s">
+        <v>186</v>
+      </c>
+      <c r="G79" t="s">
+        <v>211</v>
+      </c>
+      <c r="H79" t="s">
+        <v>80</v>
+      </c>
+      <c r="I79">
+        <v>36</v>
+      </c>
+      <c r="J79">
+        <v>16</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79" t="s">
+        <v>286</v>
+      </c>
+      <c r="O79">
+        <v>86</v>
+      </c>
+      <c r="P79">
+        <v>158</v>
+      </c>
+      <c r="Q79">
+        <v>90</v>
+      </c>
+      <c r="R79">
+        <v>4</v>
+      </c>
+      <c r="S79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19">
+      <c r="A80" t="s">
+        <v>19</v>
+      </c>
+      <c r="B80" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80" t="s">
+        <v>34</v>
+      </c>
+      <c r="D80" t="s">
+        <v>86</v>
+      </c>
+      <c r="E80" t="s">
+        <v>154</v>
+      </c>
+      <c r="F80" t="s">
+        <v>189</v>
+      </c>
+      <c r="G80" t="s">
+        <v>211</v>
+      </c>
+      <c r="H80" t="s">
+        <v>214</v>
+      </c>
+      <c r="I80">
+        <v>24</v>
+      </c>
+      <c r="J80">
+        <v>46</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>24</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80" t="s">
+        <v>287</v>
+      </c>
+      <c r="O80">
+        <v>110</v>
+      </c>
+      <c r="P80">
+        <v>182</v>
+      </c>
+      <c r="Q80">
+        <v>90</v>
+      </c>
+      <c r="R80">
+        <v>5</v>
+      </c>
+      <c r="S80">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" t="s">
+        <v>34</v>
+      </c>
+      <c r="D81" t="s">
+        <v>52</v>
+      </c>
+      <c r="E81" t="s">
+        <v>120</v>
+      </c>
+      <c r="F81" t="s">
+        <v>189</v>
+      </c>
+      <c r="G81" t="s">
+        <v>211</v>
+      </c>
+      <c r="H81" t="s">
+        <v>214</v>
+      </c>
+      <c r="I81">
+        <v>24</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>48</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81" t="s">
+        <v>288</v>
+      </c>
+      <c r="O81">
+        <v>56</v>
+      </c>
+      <c r="P81">
+        <v>104</v>
+      </c>
+      <c r="Q81">
+        <v>90</v>
+      </c>
+      <c r="R81">
+        <v>3</v>
+      </c>
+      <c r="S81">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19">
+      <c r="A82" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" t="s">
+        <v>53</v>
+      </c>
+      <c r="E82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F82" t="s">
+        <v>179</v>
+      </c>
+      <c r="G82" t="s">
+        <v>211</v>
+      </c>
+      <c r="H82" t="s">
+        <v>213</v>
+      </c>
+      <c r="I82">
+        <v>12</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>24</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82" t="s">
+        <v>289</v>
+      </c>
+      <c r="O82">
+        <v>28</v>
+      </c>
+      <c r="P82">
+        <v>52</v>
+      </c>
+      <c r="Q82">
+        <v>90</v>
+      </c>
+      <c r="R82">
+        <v>3</v>
+      </c>
+      <c r="S82">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19">
+      <c r="A83" t="s">
+        <v>21</v>
+      </c>
+      <c r="B83" t="s">
+        <v>25</v>
+      </c>
+      <c r="C83" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" t="s">
+        <v>100</v>
+      </c>
+      <c r="E83" t="s">
+        <v>168</v>
+      </c>
+      <c r="F83" t="s">
+        <v>179</v>
+      </c>
+      <c r="G83" t="s">
+        <v>211</v>
+      </c>
+      <c r="H83" t="s">
+        <v>213</v>
+      </c>
+      <c r="I83">
+        <v>12</v>
+      </c>
+      <c r="J83">
+        <v>6</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>12</v>
+      </c>
+      <c r="M83">
+        <v>24</v>
+      </c>
+      <c r="N83" t="s">
+        <v>283</v>
+      </c>
+      <c r="O83">
+        <v>48</v>
+      </c>
+      <c r="P83">
+        <v>84</v>
+      </c>
+      <c r="Q83">
+        <v>90</v>
+      </c>
+      <c r="R83">
+        <v>4</v>
+      </c>
+      <c r="S83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19">
+      <c r="A84" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" t="s">
+        <v>35</v>
+      </c>
+      <c r="D84" t="s">
+        <v>47</v>
+      </c>
+      <c r="E84" t="s">
+        <v>115</v>
+      </c>
+      <c r="F84" t="s">
+        <v>184</v>
+      </c>
+      <c r="G84" t="s">
+        <v>211</v>
+      </c>
+      <c r="H84" t="s">
+        <v>215</v>
+      </c>
+      <c r="I84">
+        <v>8</v>
+      </c>
+      <c r="J84">
+        <v>13</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84" t="s">
+        <v>290</v>
+      </c>
+      <c r="O84">
+        <v>24</v>
+      </c>
+      <c r="P84">
+        <v>40</v>
+      </c>
+      <c r="Q84">
+        <v>90</v>
+      </c>
+      <c r="R84">
+        <v>4</v>
+      </c>
+      <c r="S84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19">
+      <c r="A85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" t="s">
+        <v>35</v>
+      </c>
+      <c r="D85" t="s">
+        <v>42</v>
+      </c>
+      <c r="E85" t="s">
+        <v>110</v>
+      </c>
+      <c r="F85" t="s">
+        <v>178</v>
+      </c>
+      <c r="G85" t="s">
+        <v>211</v>
+      </c>
+      <c r="H85" t="s">
+        <v>212</v>
+      </c>
+      <c r="I85">
+        <v>10</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85" t="s">
+        <v>291</v>
+      </c>
+      <c r="O85">
+        <v>14</v>
+      </c>
+      <c r="P85">
+        <v>24</v>
+      </c>
+      <c r="Q85">
+        <v>90</v>
+      </c>
+      <c r="R85">
+        <v>3</v>
+      </c>
+      <c r="S85">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19">
+      <c r="A86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" t="s">
+        <v>35</v>
+      </c>
+      <c r="D86" t="s">
+        <v>51</v>
+      </c>
+      <c r="E86" t="s">
+        <v>119</v>
+      </c>
+      <c r="F86" t="s">
+        <v>188</v>
+      </c>
+      <c r="G86" t="s">
+        <v>211</v>
+      </c>
+      <c r="H86" t="s">
+        <v>212</v>
+      </c>
+      <c r="I86">
+        <v>10</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>10</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86" t="s">
+        <v>221</v>
+      </c>
+      <c r="O86">
+        <v>26</v>
+      </c>
+      <c r="P86">
+        <v>36</v>
+      </c>
+      <c r="Q86">
+        <v>90</v>
+      </c>
+      <c r="R86">
+        <v>3</v>
+      </c>
+      <c r="S86">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" t="s">
+        <v>35</v>
+      </c>
+      <c r="D87" t="s">
+        <v>101</v>
+      </c>
+      <c r="E87" t="s">
+        <v>169</v>
+      </c>
+      <c r="F87" t="s">
+        <v>207</v>
+      </c>
+      <c r="G87" t="s">
+        <v>211</v>
+      </c>
+      <c r="H87" t="s">
+        <v>226</v>
+      </c>
+      <c r="I87">
+        <v>25</v>
+      </c>
+      <c r="J87">
+        <v>27</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87" t="s">
+        <v>292</v>
+      </c>
+      <c r="O87">
+        <v>87</v>
+      </c>
+      <c r="P87">
+        <v>137</v>
+      </c>
+      <c r="Q87">
+        <v>90</v>
+      </c>
+      <c r="R87">
+        <v>5</v>
+      </c>
+      <c r="S87">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19">
+      <c r="A88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88" t="s">
+        <v>35</v>
+      </c>
+      <c r="D88" t="s">
+        <v>53</v>
+      </c>
+      <c r="E88" t="s">
+        <v>121</v>
+      </c>
+      <c r="F88" t="s">
+        <v>179</v>
+      </c>
+      <c r="G88" t="s">
+        <v>211</v>
+      </c>
+      <c r="H88" t="s">
+        <v>213</v>
+      </c>
+      <c r="I88">
+        <v>12</v>
+      </c>
+      <c r="J88">
+        <v>13</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>12</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88" t="s">
+        <v>293</v>
+      </c>
+      <c r="O88">
+        <v>28</v>
+      </c>
+      <c r="P88">
+        <v>40</v>
+      </c>
+      <c r="Q88">
+        <v>90</v>
+      </c>
+      <c r="R88">
+        <v>2</v>
+      </c>
+      <c r="S88">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19">
+      <c r="A89" t="s">
+        <v>21</v>
+      </c>
+      <c r="B89" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" t="s">
+        <v>35</v>
+      </c>
+      <c r="D89" t="s">
+        <v>43</v>
+      </c>
+      <c r="E89" t="s">
+        <v>111</v>
+      </c>
+      <c r="F89" t="s">
+        <v>180</v>
+      </c>
+      <c r="G89" t="s">
+        <v>211</v>
+      </c>
+      <c r="H89" t="s">
+        <v>214</v>
+      </c>
+      <c r="I89">
+        <v>24</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89" t="s">
+        <v>228</v>
+      </c>
+      <c r="O89">
+        <v>5</v>
+      </c>
+      <c r="P89">
+        <v>10</v>
+      </c>
+      <c r="Q89">
+        <v>90</v>
+      </c>
+      <c r="R89">
+        <v>1</v>
+      </c>
+      <c r="S89">
+        <v>241.08</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19">
+      <c r="A90" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s">
+        <v>36</v>
+      </c>
+      <c r="D90" t="s">
+        <v>87</v>
+      </c>
+      <c r="E90" t="s">
+        <v>155</v>
+      </c>
+      <c r="F90" t="s">
+        <v>185</v>
+      </c>
+      <c r="G90" t="s">
+        <v>211</v>
+      </c>
+      <c r="H90" t="s">
+        <v>223</v>
+      </c>
+      <c r="I90">
+        <v>4</v>
+      </c>
+      <c r="J90">
+        <v>24</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>32</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90" t="s">
+        <v>294</v>
+      </c>
+      <c r="O90">
+        <v>62</v>
+      </c>
+      <c r="P90">
+        <v>98</v>
+      </c>
+      <c r="Q90">
+        <v>90</v>
+      </c>
+      <c r="R90">
+        <v>11</v>
+      </c>
+      <c r="S90">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19">
+      <c r="A91" t="s">
+        <v>19</v>
+      </c>
+      <c r="B91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" t="s">
+        <v>36</v>
+      </c>
+      <c r="D91" t="s">
+        <v>99</v>
+      </c>
+      <c r="E91" t="s">
+        <v>167</v>
+      </c>
+      <c r="F91" t="s">
+        <v>178</v>
+      </c>
+      <c r="G91" t="s">
+        <v>211</v>
+      </c>
+      <c r="H91" t="s">
+        <v>213</v>
+      </c>
+      <c r="I91">
+        <v>12</v>
+      </c>
+      <c r="J91">
+        <v>79</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91" t="s">
+        <v>295</v>
+      </c>
+      <c r="O91">
+        <v>84</v>
+      </c>
+      <c r="P91">
+        <v>120</v>
+      </c>
+      <c r="Q91">
+        <v>90</v>
+      </c>
+      <c r="R91">
+        <v>4</v>
+      </c>
+      <c r="S91">
+        <v>12.83</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19">
+      <c r="A92" t="s">
+        <v>19</v>
+      </c>
+      <c r="B92" t="s">
+        <v>23</v>
+      </c>
+      <c r="C92" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" t="s">
+        <v>51</v>
+      </c>
+      <c r="E92" t="s">
+        <v>119</v>
+      </c>
+      <c r="F92" t="s">
+        <v>188</v>
+      </c>
+      <c r="G92" t="s">
+        <v>211</v>
+      </c>
+      <c r="H92" t="s">
+        <v>212</v>
+      </c>
+      <c r="I92">
+        <v>10</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>10</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92" t="s">
+        <v>296</v>
+      </c>
+      <c r="O92">
+        <v>39</v>
+      </c>
+      <c r="P92">
+        <v>54</v>
+      </c>
+      <c r="Q92">
+        <v>90</v>
+      </c>
+      <c r="R92">
+        <v>5</v>
+      </c>
+      <c r="S92">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19">
+      <c r="A93" t="s">
+        <v>21</v>
+      </c>
+      <c r="B93" t="s">
+        <v>25</v>
+      </c>
+      <c r="C93" t="s">
+        <v>36</v>
+      </c>
+      <c r="D93" t="s">
+        <v>53</v>
+      </c>
+      <c r="E93" t="s">
+        <v>121</v>
+      </c>
+      <c r="F93" t="s">
+        <v>179</v>
+      </c>
+      <c r="G93" t="s">
+        <v>211</v>
+      </c>
+      <c r="H93" t="s">
+        <v>213</v>
+      </c>
+      <c r="I93">
+        <v>12</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>12</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93" t="s">
+        <v>213</v>
+      </c>
+      <c r="O93">
+        <v>28</v>
+      </c>
+      <c r="P93">
+        <v>40</v>
+      </c>
+      <c r="Q93">
+        <v>90</v>
+      </c>
+      <c r="R93">
+        <v>3</v>
+      </c>
+      <c r="S93">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19">
+      <c r="A94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94" t="s">
+        <v>37</v>
+      </c>
+      <c r="D94" t="s">
+        <v>49</v>
+      </c>
+      <c r="E94" t="s">
+        <v>117</v>
+      </c>
+      <c r="F94" t="s">
+        <v>186</v>
+      </c>
+      <c r="G94" t="s">
+        <v>211</v>
+      </c>
+      <c r="H94" t="s">
+        <v>80</v>
+      </c>
+      <c r="I94">
+        <v>36</v>
+      </c>
+      <c r="J94">
+        <v>114</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>36</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94" t="s">
+        <v>297</v>
+      </c>
+      <c r="O94">
+        <v>156</v>
+      </c>
+      <c r="P94">
+        <v>264</v>
+      </c>
+      <c r="Q94">
+        <v>90</v>
+      </c>
+      <c r="R94">
+        <v>4</v>
+      </c>
+      <c r="S94">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19">
+      <c r="A95" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95" t="s">
+        <v>37</v>
+      </c>
+      <c r="D95" t="s">
+        <v>51</v>
+      </c>
+      <c r="E95" t="s">
+        <v>119</v>
+      </c>
+      <c r="F95" t="s">
+        <v>188</v>
+      </c>
+      <c r="G95" t="s">
+        <v>211</v>
+      </c>
+      <c r="H95" t="s">
+        <v>212</v>
+      </c>
+      <c r="I95">
+        <v>10</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>10</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95" t="s">
+        <v>228</v>
+      </c>
+      <c r="O95">
+        <v>39</v>
+      </c>
+      <c r="P95">
+        <v>54</v>
+      </c>
+      <c r="Q95">
+        <v>90</v>
+      </c>
+      <c r="R95">
+        <v>5</v>
+      </c>
+      <c r="S95">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19">
+      <c r="A96" t="s">
+        <v>21</v>
+      </c>
+      <c r="B96" t="s">
+        <v>25</v>
+      </c>
+      <c r="C96" t="s">
+        <v>37</v>
+      </c>
+      <c r="D96" t="s">
+        <v>53</v>
+      </c>
+      <c r="E96" t="s">
+        <v>121</v>
+      </c>
+      <c r="F96" t="s">
+        <v>179</v>
+      </c>
+      <c r="G96" t="s">
+        <v>211</v>
+      </c>
+      <c r="H96" t="s">
+        <v>213</v>
+      </c>
+      <c r="I96">
+        <v>12</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>12</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96" t="s">
+        <v>228</v>
+      </c>
+      <c r="O96">
+        <v>28</v>
+      </c>
+      <c r="P96">
+        <v>40</v>
+      </c>
+      <c r="Q96">
+        <v>90</v>
+      </c>
+      <c r="R96">
+        <v>3</v>
+      </c>
+      <c r="S96">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19">
+      <c r="A97" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" t="s">
+        <v>38</v>
+      </c>
+      <c r="D97" t="s">
+        <v>102</v>
+      </c>
+      <c r="E97" t="s">
+        <v>170</v>
+      </c>
+      <c r="F97" t="s">
+        <v>208</v>
+      </c>
+      <c r="G97" t="s">
+        <v>211</v>
+      </c>
+      <c r="H97" t="s">
+        <v>213</v>
+      </c>
+      <c r="I97">
+        <v>12</v>
+      </c>
+      <c r="J97">
+        <v>33</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>36</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97" t="s">
+        <v>298</v>
+      </c>
+      <c r="O97">
+        <v>76</v>
+      </c>
+      <c r="P97">
+        <v>112</v>
+      </c>
+      <c r="Q97">
+        <v>90</v>
+      </c>
+      <c r="R97">
+        <v>4</v>
+      </c>
+      <c r="S97">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19">
+      <c r="A98" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" t="s">
+        <v>38</v>
+      </c>
+      <c r="D98" t="s">
+        <v>103</v>
+      </c>
+      <c r="E98" t="s">
+        <v>171</v>
+      </c>
+      <c r="F98" t="s">
+        <v>209</v>
+      </c>
+      <c r="G98" t="s">
+        <v>211</v>
+      </c>
+      <c r="H98" t="s">
+        <v>219</v>
+      </c>
+      <c r="I98">
+        <v>20</v>
+      </c>
+      <c r="J98">
+        <v>4</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>80</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98" t="s">
+        <v>299</v>
+      </c>
+      <c r="O98">
+        <v>208</v>
+      </c>
+      <c r="P98">
+        <v>308</v>
+      </c>
+      <c r="Q98">
+        <v>90</v>
+      </c>
+      <c r="R98">
+        <v>12</v>
+      </c>
+      <c r="S98">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19">
+      <c r="A99" t="s">
+        <v>19</v>
+      </c>
+      <c r="B99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C99" t="s">
+        <v>38</v>
+      </c>
+      <c r="D99" t="s">
+        <v>98</v>
+      </c>
+      <c r="E99" t="s">
+        <v>166</v>
+      </c>
+      <c r="F99" t="s">
+        <v>207</v>
+      </c>
+      <c r="G99" t="s">
+        <v>211</v>
+      </c>
+      <c r="H99" t="s">
+        <v>212</v>
+      </c>
+      <c r="I99">
+        <v>10</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>30</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99" t="s">
+        <v>300</v>
+      </c>
+      <c r="O99">
+        <v>33</v>
+      </c>
+      <c r="P99">
+        <v>51</v>
+      </c>
+      <c r="Q99">
+        <v>90</v>
+      </c>
+      <c r="R99">
+        <v>3</v>
+      </c>
+      <c r="S99">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19">
+      <c r="A100" t="s">
+        <v>21</v>
+      </c>
+      <c r="B100" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" t="s">
+        <v>38</v>
+      </c>
+      <c r="D100" t="s">
+        <v>53</v>
+      </c>
+      <c r="E100" t="s">
+        <v>121</v>
+      </c>
+      <c r="F100" t="s">
+        <v>179</v>
+      </c>
+      <c r="G100" t="s">
+        <v>211</v>
+      </c>
+      <c r="H100" t="s">
+        <v>213</v>
+      </c>
+      <c r="I100">
+        <v>12</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>12</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100" t="s">
+        <v>226</v>
+      </c>
+      <c r="O100">
+        <v>28</v>
+      </c>
+      <c r="P100">
+        <v>40</v>
+      </c>
+      <c r="Q100">
+        <v>90</v>
+      </c>
+      <c r="R100">
+        <v>3</v>
+      </c>
+      <c r="S100">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19">
+      <c r="A101" t="s">
+        <v>19</v>
+      </c>
+      <c r="B101" t="s">
+        <v>23</v>
+      </c>
+      <c r="C101" t="s">
+        <v>39</v>
+      </c>
+      <c r="D101" t="s">
+        <v>104</v>
+      </c>
+      <c r="E101" t="s">
+        <v>172</v>
+      </c>
+      <c r="F101" t="s">
+        <v>199</v>
+      </c>
+      <c r="G101" t="s">
+        <v>211</v>
+      </c>
+      <c r="H101" t="s">
+        <v>227</v>
+      </c>
+      <c r="I101">
+        <v>16</v>
+      </c>
+      <c r="J101">
+        <v>37</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101" t="s">
+        <v>301</v>
+      </c>
+      <c r="O101">
+        <v>40</v>
+      </c>
+      <c r="P101">
+        <v>104</v>
+      </c>
+      <c r="Q101">
+        <v>90</v>
+      </c>
+      <c r="R101">
+        <v>5</v>
+      </c>
+      <c r="S101">
+        <v>23.06</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19">
+      <c r="A102" t="s">
+        <v>19</v>
+      </c>
+      <c r="B102" t="s">
+        <v>27</v>
+      </c>
+      <c r="C102" t="s">
+        <v>39</v>
+      </c>
+      <c r="D102" t="s">
+        <v>49</v>
+      </c>
+      <c r="E102" t="s">
+        <v>117</v>
+      </c>
+      <c r="F102" t="s">
+        <v>186</v>
+      </c>
+      <c r="G102" t="s">
+        <v>211</v>
+      </c>
+      <c r="H102" t="s">
+        <v>80</v>
+      </c>
+      <c r="I102">
+        <v>36</v>
+      </c>
+      <c r="J102">
+        <v>10</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>72</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102" t="s">
+        <v>302</v>
+      </c>
+      <c r="O102">
+        <v>84</v>
+      </c>
+      <c r="P102">
+        <v>156</v>
+      </c>
+      <c r="Q102">
+        <v>90</v>
+      </c>
+      <c r="R102">
+        <v>3</v>
+      </c>
+      <c r="S102">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19">
+      <c r="A103" t="s">
+        <v>19</v>
+      </c>
+      <c r="B103" t="s">
+        <v>23</v>
+      </c>
+      <c r="C103" t="s">
+        <v>39</v>
+      </c>
+      <c r="D103" t="s">
+        <v>101</v>
+      </c>
+      <c r="E103" t="s">
+        <v>169</v>
+      </c>
+      <c r="F103" t="s">
+        <v>207</v>
+      </c>
+      <c r="G103" t="s">
+        <v>211</v>
+      </c>
+      <c r="H103" t="s">
+        <v>226</v>
+      </c>
+      <c r="I103">
+        <v>25</v>
+      </c>
+      <c r="J103">
+        <v>38</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>25</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103" t="s">
+        <v>303</v>
+      </c>
+      <c r="O103">
+        <v>87</v>
+      </c>
+      <c r="P103">
+        <v>137</v>
+      </c>
+      <c r="Q103">
+        <v>90</v>
+      </c>
+      <c r="R103">
+        <v>3</v>
+      </c>
+      <c r="S103">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19">
+      <c r="A104" t="s">
+        <v>21</v>
+      </c>
+      <c r="B104" t="s">
+        <v>25</v>
+      </c>
+      <c r="C104" t="s">
+        <v>39</v>
+      </c>
+      <c r="D104" t="s">
+        <v>53</v>
+      </c>
+      <c r="E104" t="s">
+        <v>121</v>
+      </c>
+      <c r="F104" t="s">
+        <v>179</v>
+      </c>
+      <c r="G104" t="s">
+        <v>211</v>
+      </c>
+      <c r="H104" t="s">
+        <v>213</v>
+      </c>
+      <c r="I104">
+        <v>12</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>12</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104" t="s">
+        <v>304</v>
+      </c>
+      <c r="O104">
+        <v>28</v>
+      </c>
+      <c r="P104">
+        <v>40</v>
+      </c>
+      <c r="Q104">
+        <v>90</v>
+      </c>
+      <c r="R104">
+        <v>3</v>
+      </c>
+      <c r="S104">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19">
+      <c r="A105" t="s">
+        <v>19</v>
+      </c>
+      <c r="B105" t="s">
+        <v>23</v>
+      </c>
+      <c r="C105" t="s">
+        <v>40</v>
+      </c>
+      <c r="D105" t="s">
+        <v>42</v>
+      </c>
+      <c r="E105" t="s">
+        <v>110</v>
+      </c>
+      <c r="F105" t="s">
+        <v>178</v>
+      </c>
+      <c r="G105" t="s">
+        <v>211</v>
+      </c>
+      <c r="H105" t="s">
+        <v>212</v>
+      </c>
+      <c r="I105">
+        <v>10</v>
+      </c>
+      <c r="J105">
+        <v>-8</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>10</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105" t="s">
+        <v>305</v>
+      </c>
+      <c r="O105">
+        <v>12</v>
+      </c>
+      <c r="P105">
+        <v>32</v>
+      </c>
+      <c r="Q105">
+        <v>90</v>
+      </c>
+      <c r="R105">
+        <v>3</v>
+      </c>
+      <c r="S105">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19">
+      <c r="A106" t="s">
+        <v>19</v>
+      </c>
+      <c r="B106" t="s">
+        <v>23</v>
+      </c>
+      <c r="C106" t="s">
+        <v>40</v>
+      </c>
+      <c r="D106" t="s">
+        <v>99</v>
+      </c>
+      <c r="E106" t="s">
+        <v>167</v>
+      </c>
+      <c r="F106" t="s">
+        <v>178</v>
+      </c>
+      <c r="G106" t="s">
+        <v>211</v>
+      </c>
+      <c r="H106" t="s">
+        <v>213</v>
+      </c>
+      <c r="I106">
+        <v>12</v>
+      </c>
+      <c r="J106">
+        <v>9</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>216</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106" t="s">
+        <v>306</v>
+      </c>
+      <c r="O106">
+        <v>240</v>
+      </c>
+      <c r="P106">
+        <v>276</v>
+      </c>
+      <c r="Q106">
+        <v>90</v>
+      </c>
+      <c r="R106">
+        <v>5</v>
+      </c>
+      <c r="S106">
+        <v>12.83</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19">
+      <c r="A107" t="s">
+        <v>19</v>
+      </c>
+      <c r="B107" t="s">
+        <v>23</v>
+      </c>
+      <c r="C107" t="s">
+        <v>40</v>
+      </c>
+      <c r="D107" t="s">
+        <v>98</v>
+      </c>
+      <c r="E107" t="s">
+        <v>166</v>
+      </c>
+      <c r="F107" t="s">
+        <v>207</v>
+      </c>
+      <c r="G107" t="s">
+        <v>211</v>
+      </c>
+      <c r="H107" t="s">
+        <v>212</v>
+      </c>
+      <c r="I107">
+        <v>10</v>
+      </c>
+      <c r="J107">
+        <v>10</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>10</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107" t="s">
+        <v>214</v>
+      </c>
+      <c r="O107">
+        <v>45</v>
+      </c>
+      <c r="P107">
+        <v>68</v>
+      </c>
+      <c r="Q107">
+        <v>90</v>
+      </c>
+      <c r="R107">
+        <v>5</v>
+      </c>
+      <c r="S107">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19">
+      <c r="A108" t="s">
+        <v>21</v>
+      </c>
+      <c r="B108" t="s">
+        <v>25</v>
+      </c>
+      <c r="C108" t="s">
+        <v>40</v>
+      </c>
+      <c r="D108" t="s">
+        <v>105</v>
+      </c>
+      <c r="E108" t="s">
+        <v>173</v>
+      </c>
+      <c r="F108" t="s">
+        <v>179</v>
+      </c>
+      <c r="G108" t="s">
+        <v>211</v>
+      </c>
+      <c r="H108" t="s">
+        <v>213</v>
+      </c>
+      <c r="I108">
+        <v>12</v>
+      </c>
+      <c r="J108">
+        <v>4</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108" t="s">
+        <v>44</v>
+      </c>
+      <c r="O108">
+        <v>8</v>
+      </c>
+      <c r="P108">
+        <v>20</v>
+      </c>
+      <c r="Q108">
+        <v>90</v>
+      </c>
+      <c r="R108">
+        <v>2</v>
+      </c>
+      <c r="S108">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19">
+      <c r="A109" t="s">
+        <v>21</v>
+      </c>
+      <c r="B109" t="s">
+        <v>25</v>
+      </c>
+      <c r="C109" t="s">
+        <v>40</v>
+      </c>
+      <c r="D109" t="s">
+        <v>53</v>
+      </c>
+      <c r="E109" t="s">
+        <v>121</v>
+      </c>
+      <c r="F109" t="s">
+        <v>179</v>
+      </c>
+      <c r="G109" t="s">
+        <v>211</v>
+      </c>
+      <c r="H109" t="s">
+        <v>213</v>
+      </c>
+      <c r="I109">
+        <v>12</v>
+      </c>
+      <c r="J109">
+        <v>8</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>12</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109" t="s">
+        <v>307</v>
+      </c>
+      <c r="O109">
+        <v>28</v>
+      </c>
+      <c r="P109">
+        <v>40</v>
+      </c>
+      <c r="Q109">
+        <v>90</v>
+      </c>
+      <c r="R109">
+        <v>2</v>
+      </c>
+      <c r="S109">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19">
+      <c r="A110" t="s">
+        <v>21</v>
+      </c>
+      <c r="B110" t="s">
+        <v>25</v>
+      </c>
+      <c r="C110" t="s">
+        <v>40</v>
+      </c>
+      <c r="D110" t="s">
+        <v>106</v>
+      </c>
+      <c r="E110" t="s">
+        <v>174</v>
+      </c>
+      <c r="F110" t="s">
+        <v>179</v>
+      </c>
+      <c r="G110" t="s">
+        <v>211</v>
+      </c>
+      <c r="H110" t="s">
+        <v>216</v>
+      </c>
+      <c r="I110">
+        <v>6</v>
+      </c>
+      <c r="J110">
+        <v>11</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110" t="s">
+        <v>308</v>
+      </c>
+      <c r="O110">
+        <v>12</v>
+      </c>
+      <c r="P110">
+        <v>18</v>
+      </c>
+      <c r="Q110">
+        <v>90</v>
+      </c>
+      <c r="R110">
+        <v>2</v>
+      </c>
+      <c r="S110">
+        <v>71.83</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19">
+      <c r="A111" t="s">
+        <v>21</v>
+      </c>
+      <c r="B111" t="s">
+        <v>25</v>
+      </c>
+      <c r="C111" t="s">
+        <v>40</v>
+      </c>
+      <c r="D111" t="s">
+        <v>107</v>
+      </c>
+      <c r="E111" t="s">
+        <v>175</v>
+      </c>
+      <c r="F111" t="s">
+        <v>180</v>
+      </c>
+      <c r="G111" t="s">
+        <v>211</v>
+      </c>
+      <c r="H111" t="s">
+        <v>213</v>
+      </c>
+      <c r="I111">
+        <v>12</v>
+      </c>
+      <c r="J111">
+        <v>30</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111" t="s">
+        <v>309</v>
+      </c>
+      <c r="O111">
+        <v>36</v>
+      </c>
+      <c r="P111">
+        <v>48</v>
+      </c>
+      <c r="Q111">
+        <v>90</v>
+      </c>
+      <c r="R111">
+        <v>2</v>
+      </c>
+      <c r="S111">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19">
+      <c r="A112" t="s">
+        <v>21</v>
+      </c>
+      <c r="B112" t="s">
+        <v>25</v>
+      </c>
+      <c r="C112" t="s">
+        <v>40</v>
+      </c>
+      <c r="D112" t="s">
+        <v>108</v>
+      </c>
+      <c r="E112" t="s">
+        <v>176</v>
+      </c>
+      <c r="F112" t="s">
+        <v>210</v>
+      </c>
+      <c r="G112" t="s">
+        <v>211</v>
+      </c>
+      <c r="H112" t="s">
+        <v>226</v>
+      </c>
+      <c r="I112">
+        <v>25</v>
+      </c>
+      <c r="J112">
+        <v>-10</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112" t="s">
+        <v>310</v>
+      </c>
+      <c r="O112">
+        <v>35</v>
+      </c>
+      <c r="P112">
+        <v>60</v>
+      </c>
+      <c r="Q112">
+        <v>90</v>
+      </c>
+      <c r="R112">
+        <v>3</v>
+      </c>
+      <c r="S112">
+        <v>32.479999999999997</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19">
+      <c r="A113" t="s">
+        <v>19</v>
+      </c>
+      <c r="B113" t="s">
+        <v>23</v>
+      </c>
+      <c r="C113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D113" t="s">
+        <v>81</v>
+      </c>
+      <c r="E113" t="s">
+        <v>149</v>
+      </c>
+      <c r="F113" t="s">
+        <v>199</v>
+      </c>
+      <c r="G113" t="s">
+        <v>211</v>
+      </c>
+      <c r="H113" t="s">
+        <v>221</v>
+      </c>
+      <c r="I113">
+        <v>64</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113" t="s">
+        <v>311</v>
+      </c>
+      <c r="O113">
+        <v>86</v>
+      </c>
+      <c r="P113">
+        <v>150</v>
+      </c>
+      <c r="Q113">
+        <v>90</v>
+      </c>
+      <c r="R113">
+        <v>3</v>
+      </c>
+      <c r="S113">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19">
+      <c r="A114" t="s">
+        <v>19</v>
+      </c>
+      <c r="B114" t="s">
+        <v>23</v>
+      </c>
+      <c r="C114" t="s">
+        <v>41</v>
+      </c>
+      <c r="D114" t="s">
+        <v>104</v>
+      </c>
+      <c r="E114" t="s">
+        <v>172</v>
+      </c>
+      <c r="F114" t="s">
+        <v>199</v>
+      </c>
+      <c r="G114" t="s">
+        <v>211</v>
+      </c>
+      <c r="H114" t="s">
+        <v>227</v>
+      </c>
+      <c r="I114">
+        <v>16</v>
+      </c>
+      <c r="J114">
+        <v>23</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114" t="s">
+        <v>312</v>
+      </c>
+      <c r="O114">
+        <v>40</v>
+      </c>
+      <c r="P114">
+        <v>104</v>
+      </c>
+      <c r="Q114">
+        <v>90</v>
+      </c>
+      <c r="R114">
+        <v>6</v>
+      </c>
+      <c r="S114">
+        <v>23.06</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19">
+      <c r="A115" t="s">
+        <v>19</v>
+      </c>
+      <c r="B115" t="s">
+        <v>23</v>
+      </c>
+      <c r="C115" t="s">
+        <v>41</v>
+      </c>
+      <c r="D115" t="s">
+        <v>42</v>
+      </c>
+      <c r="E115" t="s">
+        <v>110</v>
+      </c>
+      <c r="F115" t="s">
+        <v>178</v>
+      </c>
+      <c r="G115" t="s">
+        <v>211</v>
+      </c>
+      <c r="H115" t="s">
+        <v>212</v>
+      </c>
+      <c r="I115">
+        <v>10</v>
+      </c>
+      <c r="J115">
+        <v>-10</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115" t="s">
+        <v>313</v>
+      </c>
+      <c r="O115">
+        <v>16</v>
+      </c>
+      <c r="P115">
+        <v>26</v>
+      </c>
+      <c r="Q115">
+        <v>90</v>
+      </c>
+      <c r="R115">
+        <v>3</v>
+      </c>
+      <c r="S115">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19">
+      <c r="A116" t="s">
+        <v>19</v>
+      </c>
+      <c r="B116" t="s">
+        <v>23</v>
+      </c>
+      <c r="C116" t="s">
+        <v>41</v>
+      </c>
+      <c r="D116" t="s">
+        <v>99</v>
+      </c>
+      <c r="E116" t="s">
+        <v>167</v>
+      </c>
+      <c r="F116" t="s">
+        <v>178</v>
+      </c>
+      <c r="G116" t="s">
+        <v>211</v>
+      </c>
+      <c r="H116" t="s">
+        <v>213</v>
+      </c>
+      <c r="I116">
+        <v>12</v>
+      </c>
+      <c r="J116">
+        <v>113</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116" t="s">
+        <v>314</v>
+      </c>
+      <c r="O116">
+        <v>120</v>
+      </c>
+      <c r="P116">
+        <v>144</v>
+      </c>
+      <c r="Q116">
+        <v>90</v>
+      </c>
+      <c r="R116">
+        <v>3</v>
+      </c>
+      <c r="S116">
+        <v>12.83</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19">
+      <c r="A117" t="s">
+        <v>19</v>
+      </c>
+      <c r="B117" t="s">
+        <v>27</v>
+      </c>
+      <c r="C117" t="s">
+        <v>41</v>
+      </c>
+      <c r="D117" t="s">
+        <v>103</v>
+      </c>
+      <c r="E117" t="s">
+        <v>171</v>
+      </c>
+      <c r="F117" t="s">
+        <v>209</v>
+      </c>
+      <c r="G117" t="s">
+        <v>211</v>
+      </c>
+      <c r="H117" t="s">
+        <v>219</v>
+      </c>
+      <c r="I117">
+        <v>20</v>
+      </c>
+      <c r="J117">
+        <v>191</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>60</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117" t="s">
+        <v>315</v>
+      </c>
+      <c r="O117">
+        <v>280</v>
+      </c>
+      <c r="P117">
+        <v>440</v>
+      </c>
+      <c r="Q117">
+        <v>90</v>
+      </c>
+      <c r="R117">
+        <v>10</v>
+      </c>
+      <c r="S117">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19">
+      <c r="A118" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C118" t="s">
+        <v>41</v>
+      </c>
+      <c r="D118" t="s">
+        <v>109</v>
+      </c>
+      <c r="E118" t="s">
+        <v>177</v>
+      </c>
+      <c r="F118" t="s">
+        <v>186</v>
+      </c>
+      <c r="G118" t="s">
+        <v>211</v>
+      </c>
+      <c r="H118" t="s">
+        <v>214</v>
+      </c>
+      <c r="I118">
+        <v>24</v>
+      </c>
+      <c r="J118">
+        <v>190</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118" t="s">
+        <v>316</v>
+      </c>
+      <c r="O118">
+        <v>192</v>
+      </c>
+      <c r="P118">
+        <v>288</v>
+      </c>
+      <c r="Q118">
+        <v>90</v>
+      </c>
+      <c r="R118">
+        <v>5</v>
+      </c>
+      <c r="S118">
+        <v>116.88</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19">
+      <c r="A119" t="s">
+        <v>19</v>
+      </c>
+      <c r="B119" t="s">
+        <v>23</v>
+      </c>
+      <c r="C119" t="s">
+        <v>41</v>
+      </c>
+      <c r="D119" t="s">
+        <v>51</v>
+      </c>
+      <c r="E119" t="s">
+        <v>119</v>
+      </c>
+      <c r="F119" t="s">
+        <v>188</v>
+      </c>
+      <c r="G119" t="s">
+        <v>211</v>
+      </c>
+      <c r="H119" t="s">
+        <v>212</v>
+      </c>
+      <c r="I119">
+        <v>10</v>
+      </c>
+      <c r="J119">
+        <v>2</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>10</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119" t="s">
+        <v>222</v>
+      </c>
+      <c r="O119">
+        <v>39</v>
+      </c>
+      <c r="P119">
+        <v>54</v>
+      </c>
+      <c r="Q119">
+        <v>90</v>
+      </c>
+      <c r="R119">
+        <v>5</v>
+      </c>
+      <c r="S119">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19">
+      <c r="A120" t="s">
+        <v>19</v>
+      </c>
+      <c r="B120" t="s">
+        <v>23</v>
+      </c>
+      <c r="C120" t="s">
+        <v>41</v>
+      </c>
+      <c r="D120" t="s">
+        <v>52</v>
+      </c>
+      <c r="E120" t="s">
+        <v>120</v>
+      </c>
+      <c r="F120" t="s">
+        <v>189</v>
+      </c>
+      <c r="G120" t="s">
+        <v>211</v>
+      </c>
+      <c r="H120" t="s">
+        <v>214</v>
+      </c>
+      <c r="I120">
+        <v>24</v>
+      </c>
+      <c r="J120">
+        <v>-19</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120" t="s">
+        <v>317</v>
+      </c>
+      <c r="O120">
+        <v>54</v>
+      </c>
+      <c r="P120">
+        <v>78</v>
+      </c>
+      <c r="Q120">
+        <v>90</v>
+      </c>
+      <c r="R120">
+        <v>4</v>
+      </c>
+      <c r="S120">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19">
+      <c r="A121" t="s">
+        <v>21</v>
+      </c>
+      <c r="B121" t="s">
+        <v>25</v>
+      </c>
+      <c r="C121" t="s">
+        <v>41</v>
+      </c>
+      <c r="D121" t="s">
+        <v>53</v>
+      </c>
+      <c r="E121" t="s">
+        <v>121</v>
+      </c>
+      <c r="F121" t="s">
+        <v>179</v>
+      </c>
+      <c r="G121" t="s">
+        <v>211</v>
+      </c>
+      <c r="H121" t="s">
+        <v>213</v>
+      </c>
+      <c r="I121">
+        <v>12</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>12</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121" t="s">
+        <v>225</v>
+      </c>
+      <c r="O121">
+        <v>28</v>
+      </c>
+      <c r="P121">
+        <v>40</v>
+      </c>
+      <c r="Q121">
+        <v>90</v>
+      </c>
+      <c r="R121">
+        <v>3</v>
+      </c>
+      <c r="S121">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19">
+      <c r="A122" t="s">
+        <v>21</v>
+      </c>
+      <c r="B122" t="s">
+        <v>25</v>
+      </c>
+      <c r="C122" t="s">
+        <v>41</v>
+      </c>
+      <c r="D122" t="s">
+        <v>100</v>
+      </c>
+      <c r="E122" t="s">
+        <v>168</v>
+      </c>
+      <c r="F122" t="s">
+        <v>179</v>
+      </c>
+      <c r="G122" t="s">
+        <v>211</v>
+      </c>
+      <c r="H122" t="s">
+        <v>213</v>
+      </c>
+      <c r="I122">
+        <v>12</v>
+      </c>
+      <c r="J122">
+        <v>-11</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>24</v>
+      </c>
+      <c r="M122">
+        <v>24</v>
+      </c>
+      <c r="N122" t="s">
+        <v>318</v>
+      </c>
+      <c r="O122">
+        <v>60</v>
+      </c>
+      <c r="P122">
+        <v>96</v>
+      </c>
+      <c r="Q122">
+        <v>90</v>
+      </c>
+      <c r="R122">
+        <v>4</v>
+      </c>
+      <c r="S122">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19">
+      <c r="A123" t="s">
+        <v>21</v>
+      </c>
+      <c r="B123" t="s">
+        <v>25</v>
+      </c>
+      <c r="C123" t="s">
+        <v>41</v>
+      </c>
+      <c r="D123" t="s">
+        <v>43</v>
+      </c>
+      <c r="E123" t="s">
+        <v>111</v>
+      </c>
+      <c r="F123" t="s">
+        <v>180</v>
+      </c>
+      <c r="G123" t="s">
+        <v>211</v>
+      </c>
+      <c r="H123" t="s">
+        <v>214</v>
+      </c>
+      <c r="I123">
+        <v>24</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123" t="s">
+        <v>228</v>
+      </c>
+      <c r="O123">
+        <v>5</v>
+      </c>
+      <c r="P123">
+        <v>10</v>
+      </c>
+      <c r="Q123">
+        <v>90</v>
+      </c>
+      <c r="R123">
+        <v>1</v>
+      </c>
+      <c r="S123">
+        <v>241.08</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19">
+      <c r="A124" t="s">
+        <v>19</v>
+      </c>
+      <c r="B124" t="s">
+        <v>23</v>
+      </c>
+      <c r="C124" t="s">
+        <v>41</v>
+      </c>
+      <c r="D124" t="s">
+        <v>74</v>
+      </c>
+      <c r="E124" t="s">
+        <v>142</v>
+      </c>
+      <c r="F124" t="s">
+        <v>180</v>
+      </c>
+      <c r="G124" t="s">
+        <v>211</v>
+      </c>
+      <c r="H124" t="s">
+        <v>214</v>
+      </c>
+      <c r="I124">
+        <v>24</v>
+      </c>
+      <c r="J124">
+        <v>-15</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124" t="s">
+        <v>265</v>
+      </c>
+      <c r="O124">
+        <v>18</v>
+      </c>
+      <c r="P124">
+        <v>42</v>
+      </c>
+      <c r="Q124">
+        <v>90</v>
+      </c>
+      <c r="R124">
+        <v>2</v>
+      </c>
+      <c r="S124">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:S124"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="238">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -79,34 +79,40 @@
     <t>Estq_CD_cx</t>
   </si>
   <si>
+    <t>PERECIVEIS</t>
+  </si>
+  <si>
+    <t>BEBIDAS</t>
+  </si>
+  <si>
     <t>MERCEARIA</t>
   </si>
   <si>
     <t>PERFUMARIA E LIMPEZA</t>
   </si>
   <si>
-    <t>PERECIVEIS</t>
-  </si>
-  <si>
-    <t>BEBIDAS</t>
+    <t>NAO ALIMENTO</t>
   </si>
   <si>
     <t>PRODUTOS PET</t>
   </si>
   <si>
+    <t>SANDRO MARTINS VIANNA</t>
+  </si>
+  <si>
+    <t>NICOLAS AUGUSTO P. BORGES</t>
+  </si>
+  <si>
     <t>NIDAL TUBASI</t>
   </si>
   <si>
+    <t>WETER SONNENFELDET</t>
+  </si>
+  <si>
     <t>JOAO BATISTA</t>
   </si>
   <si>
-    <t>WETER SONNENFELDET</t>
-  </si>
-  <si>
-    <t>SANDRO MARTINS VIANNA</t>
-  </si>
-  <si>
-    <t>NICOLAS AUGUSTO P. BORGES</t>
+    <t>001</t>
   </si>
   <si>
     <t>002</t>
@@ -139,745 +145,589 @@
     <t>013</t>
   </si>
   <si>
+    <t>014</t>
+  </si>
+  <si>
     <t>017</t>
   </si>
   <si>
     <t>018</t>
   </si>
   <si>
-    <t>747</t>
-  </si>
-  <si>
-    <t>2140</t>
-  </si>
-  <si>
-    <t>2749</t>
-  </si>
-  <si>
-    <t>5250</t>
-  </si>
-  <si>
-    <t>15765</t>
-  </si>
-  <si>
-    <t>1650</t>
-  </si>
-  <si>
-    <t>2320</t>
-  </si>
-  <si>
-    <t>5251</t>
+    <t>6783</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>750</t>
+  </si>
+  <si>
+    <t>840</t>
+  </si>
+  <si>
+    <t>2150</t>
+  </si>
+  <si>
+    <t>746</t>
+  </si>
+  <si>
+    <t>1247</t>
+  </si>
+  <si>
+    <t>1422</t>
+  </si>
+  <si>
+    <t>2841</t>
+  </si>
+  <si>
+    <t>3872</t>
+  </si>
+  <si>
+    <t>10145</t>
+  </si>
+  <si>
+    <t>21555</t>
+  </si>
+  <si>
+    <t>24141</t>
+  </si>
+  <si>
+    <t>37773</t>
+  </si>
+  <si>
+    <t>825</t>
+  </si>
+  <si>
+    <t>2161</t>
+  </si>
+  <si>
+    <t>2394</t>
+  </si>
+  <si>
+    <t>6784</t>
+  </si>
+  <si>
+    <t>33833</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>17337</t>
+  </si>
+  <si>
+    <t>37768</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>2396</t>
+  </si>
+  <si>
+    <t>2398</t>
+  </si>
+  <si>
+    <t>2507</t>
+  </si>
+  <si>
+    <t>2519</t>
+  </si>
+  <si>
+    <t>6782</t>
   </si>
   <si>
     <t>10144</t>
   </si>
   <si>
-    <t>17337</t>
-  </si>
-  <si>
-    <t>37768</t>
-  </si>
-  <si>
-    <t>6783</t>
-  </si>
-  <si>
-    <t>6799</t>
-  </si>
-  <si>
     <t>23212</t>
   </si>
   <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>784</t>
-  </si>
-  <si>
-    <t>916</t>
-  </si>
-  <si>
-    <t>2097</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>3229</t>
-  </si>
-  <si>
-    <t>13699</t>
-  </si>
-  <si>
-    <t>35631</t>
-  </si>
-  <si>
-    <t>2177</t>
-  </si>
-  <si>
-    <t>2977</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>484</t>
-  </si>
-  <si>
-    <t>548</t>
-  </si>
-  <si>
-    <t>575</t>
-  </si>
-  <si>
-    <t>827</t>
-  </si>
-  <si>
-    <t>874</t>
-  </si>
-  <si>
-    <t>1017</t>
-  </si>
-  <si>
-    <t>1209</t>
-  </si>
-  <si>
-    <t>1289</t>
-  </si>
-  <si>
-    <t>1506</t>
-  </si>
-  <si>
-    <t>2081</t>
-  </si>
-  <si>
-    <t>2087</t>
-  </si>
-  <si>
-    <t>2379</t>
-  </si>
-  <si>
-    <t>2738</t>
-  </si>
-  <si>
-    <t>2964</t>
-  </si>
-  <si>
-    <t>3379</t>
-  </si>
-  <si>
-    <t>3391</t>
-  </si>
-  <si>
-    <t>4210</t>
-  </si>
-  <si>
-    <t>4418</t>
-  </si>
-  <si>
-    <t>4988</t>
-  </si>
-  <si>
-    <t>5252</t>
-  </si>
-  <si>
-    <t>6931</t>
-  </si>
-  <si>
-    <t>7868</t>
-  </si>
-  <si>
-    <t>9288</t>
-  </si>
-  <si>
-    <t>12397</t>
-  </si>
-  <si>
-    <t>17181</t>
-  </si>
-  <si>
-    <t>20320</t>
-  </si>
-  <si>
-    <t>20664</t>
-  </si>
-  <si>
-    <t>22747</t>
-  </si>
-  <si>
-    <t>33265</t>
-  </si>
-  <si>
-    <t>10148</t>
-  </si>
-  <si>
-    <t>6782</t>
-  </si>
-  <si>
-    <t>38280</t>
-  </si>
-  <si>
-    <t>15764</t>
-  </si>
-  <si>
-    <t>23117</t>
-  </si>
-  <si>
-    <t>33213</t>
-  </si>
-  <si>
-    <t>ACUCAR CRISTAL GASPARIN 2KG</t>
-  </si>
-  <si>
-    <t>ARROZ BCO SANO TP1 5KG</t>
-  </si>
-  <si>
-    <t>FARINHA TRIGO MARIA INES 5KG</t>
-  </si>
-  <si>
-    <t>CR DENT CLOSE UP 70G TRIPLE HORTELA</t>
-  </si>
-  <si>
-    <t>CESTA BASICA PEQ</t>
-  </si>
-  <si>
-    <t>WAFER PARATI MINUETO 81G CHOC</t>
-  </si>
-  <si>
-    <t>FEIJAO CARIOCA CALDO OURO 1KG</t>
-  </si>
-  <si>
-    <t>CR DENT CLOSE UP 70G TRIPLE MENTA</t>
+    <t>389</t>
+  </si>
+  <si>
+    <t>786</t>
+  </si>
+  <si>
+    <t>29542</t>
+  </si>
+  <si>
+    <t>2877</t>
+  </si>
+  <si>
+    <t>2960</t>
+  </si>
+  <si>
+    <t>3560</t>
+  </si>
+  <si>
+    <t>7726</t>
+  </si>
+  <si>
+    <t>33468</t>
+  </si>
+  <si>
+    <t>4174</t>
+  </si>
+  <si>
+    <t>764</t>
+  </si>
+  <si>
+    <t>22706</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL C TAMPA 1L INTEGRAL</t>
+  </si>
+  <si>
+    <t>AGUA MIN SARANDI 5L S GAS</t>
+  </si>
+  <si>
+    <t>ACUCAR CRISTAL GASPARIN 5KG</t>
+  </si>
+  <si>
+    <t>REFRIG PEPSI PET 3L</t>
+  </si>
+  <si>
+    <t>ARROZ BCO REQUINTE TP1 5KG</t>
+  </si>
+  <si>
+    <t>ACUCAR CRISTAL GASPARIN 1KG</t>
+  </si>
+  <si>
+    <t>CHOC BARRA NEUGEBAUER 80G AO LEITE</t>
+  </si>
+  <si>
+    <t>BISC MARIA GERMANI 345G</t>
+  </si>
+  <si>
+    <t>MAIONESE HELLMANNS SH 400G</t>
+  </si>
+  <si>
+    <t>CERV STELLA ARTOIS LT 473ML P GOLD</t>
+  </si>
+  <si>
+    <t>SAB FARNESE 180G ERV DOCE VERB</t>
+  </si>
+  <si>
+    <t>PANO PANOSUL MEDIO ESTAMP 45X65 R23</t>
+  </si>
+  <si>
+    <t>SC PANOSUL SUPER SORT 55X65CM R 17</t>
+  </si>
+  <si>
+    <t>DESINF CIF BORRIF EXTERM LIMO 500ML</t>
+  </si>
+  <si>
+    <t>REFRIG PEPSI PET 2L</t>
+  </si>
+  <si>
+    <t>ARROZ BCO ALEGRETE TP1 5KG</t>
+  </si>
+  <si>
+    <t>MILHO VERDE FUGINI SH 170G</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL C TAMP 1L SEMI DESN</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL 1L BIO CICLOS</t>
+  </si>
+  <si>
+    <t>ARROZ BCO REQUINTE TP1 2KG</t>
+  </si>
+  <si>
+    <t>DET LIQ ATRIUS 5L PREMIUM</t>
+  </si>
+  <si>
+    <t>LEITE UHT BATAVO ZR LAC DESN 1L</t>
+  </si>
+  <si>
+    <t>AGUA MIN CRYSTAL PET 500ML C GAS</t>
+  </si>
+  <si>
+    <t>MILHO VERDE OLE LT 170G</t>
+  </si>
+  <si>
+    <t>MILHO VERDE ODERICH LT 200G</t>
+  </si>
+  <si>
+    <t>KETCHUP HELLMANNS BISN 380G PICANTE</t>
+  </si>
+  <si>
+    <t>KETCHUP HELLMANNS BISN 380G TRAD</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL C TAMPA 1L DESN</t>
   </si>
   <si>
     <t>SAB FARNESE 180G AVEIA ESFOL</t>
   </si>
   <si>
-    <t>DET LIQ ATRIUS 5L PREMIUM</t>
-  </si>
-  <si>
-    <t>LEITE UHT BATAVO ZR LAC DESN 1L</t>
-  </si>
-  <si>
-    <t>LEITE UHT TIROL C TAMPA 1L INTEGRAL</t>
-  </si>
-  <si>
-    <t>LEITE SANTA CLARA 1L ZERO LACTOSE</t>
-  </si>
-  <si>
     <t>SAL MOIDO 5 ESTRELAS 1KG</t>
   </si>
   <si>
-    <t>AGUA MIN SARANDI 5L S GAS</t>
-  </si>
-  <si>
-    <t>REFRIG ANTARCTICA GUARANA PET 2L</t>
-  </si>
-  <si>
-    <t>MOLHO TOM FUGINI PIZZA SH 1 7KG</t>
-  </si>
-  <si>
-    <t>CAFE SOL NESCAFE SH 40G DOLCA</t>
-  </si>
-  <si>
-    <t>CAFE SOL NESCAFE SH 40G MATINAL SUAVE</t>
-  </si>
-  <si>
-    <t>SALG BATATA PRINGLES 105G CHEDDAR BACON</t>
-  </si>
-  <si>
-    <t>BOMBOM BEL SORT 180G</t>
-  </si>
-  <si>
-    <t>SOPA DE CANECA NEILAR 18G FGO C QJO</t>
-  </si>
-  <si>
-    <t>ARROZ BCO SABOROSO TP1 5KG</t>
-  </si>
-  <si>
-    <t>AMIDO MILHO MAISCERTA 500G</t>
-  </si>
-  <si>
-    <t>REFRE PO FRISCO 18G ABACAXI</t>
-  </si>
-  <si>
-    <t>ENERG BALY LT 250ML TRADICIONAL</t>
-  </si>
-  <si>
-    <t>GATORADE 500ML UVA</t>
-  </si>
-  <si>
-    <t>ENERG HIPERTENSAO PET 2L ZERO</t>
-  </si>
-  <si>
-    <t>REFRIG PEPSI TWIST PET 2L</t>
-  </si>
-  <si>
-    <t>MAIONESE ODERICH SH 1KG</t>
-  </si>
-  <si>
-    <t>TEMP EXTREMO SABOR 1 01K C PIMENTA</t>
-  </si>
-  <si>
-    <t>BISC DOCE DOMELLY ROSCA 280G CHOCOLATE</t>
-  </si>
-  <si>
-    <t>CHOC BARRA NESTLE 80G PRESTIGIO</t>
-  </si>
-  <si>
-    <t>CHOC KI KAKAU 475G BOLI BOL</t>
-  </si>
-  <si>
-    <t>CAFE SOL 3C SH 40G TRAD</t>
-  </si>
-  <si>
-    <t>CHA PRENDA 18G PRETO</t>
-  </si>
-  <si>
-    <t>DUETO OLE LT 170G ERVILHA MILHO</t>
-  </si>
-  <si>
-    <t>MACARRAO CUP NOODLES 69G CARNE DEF</t>
-  </si>
-  <si>
-    <t>MOLHO SHOYU EXTREMO SABOR 1 01L</t>
-  </si>
-  <si>
-    <t>CALDO MAGGI 114G CARNE</t>
-  </si>
-  <si>
-    <t>CALDO GALINHA MAGGI 114G</t>
-  </si>
-  <si>
-    <t>AMAC GIRANDO SOL 5L ROSA</t>
-  </si>
-  <si>
-    <t>CERV SKOL BEATS RED LN 269ML MIX</t>
-  </si>
-  <si>
-    <t>COND JAY LUC 1L NEUTRO</t>
-  </si>
-  <si>
-    <t>CR DENT CLOSE UP 70G TRIPLE MENTA AMER</t>
-  </si>
-  <si>
-    <t>LIMP UAU 500ML REQUINTE</t>
-  </si>
-  <si>
-    <t>SABAO PO TIXAN 800G MACIEZ</t>
-  </si>
-  <si>
-    <t>DESINF YPE BAK 500ML FLORAL BAK</t>
-  </si>
-  <si>
-    <t>AMACIANTE AQUAFAST 5L F MAN</t>
-  </si>
-  <si>
-    <t>DESINF GOTA LIMPA 500ML LAVANDA</t>
-  </si>
-  <si>
-    <t>MAC INST ISABELA 70G CAR ZR FRITU</t>
-  </si>
-  <si>
-    <t>MASSA SEMOLA GERMANI 1KG PARAF</t>
-  </si>
-  <si>
-    <t>RAC SULTAO PREMIUM GATOS 500G</t>
-  </si>
-  <si>
-    <t>REFRIG FRUKI GUAR ZR PET 3L GUARANA ZERO</t>
-  </si>
-  <si>
-    <t>SAB FARNESE 180G PITAYA FRAMB</t>
-  </si>
-  <si>
-    <t>LEITE UHT TIROL C TAMPA 1L DESN</t>
-  </si>
-  <si>
-    <t>LAV ROUPA LIQ APYCE TUDO EM UM 3L</t>
-  </si>
-  <si>
-    <t>CESTA BASICA MED</t>
-  </si>
-  <si>
-    <t>SAB PALMOLIVE NATURALS 85G JASMIM</t>
-  </si>
-  <si>
-    <t>ACUCAR MASCAVO GASPARIN 1KG</t>
+    <t>ENERG MONSTER LT 473ML GREEN</t>
+  </si>
+  <si>
+    <t>REFRIG ANTARCTICA GUARANA PET 2L ZERO</t>
+  </si>
+  <si>
+    <t>CARVAO VEG CHURRASCO NA BRASA 3KG</t>
+  </si>
+  <si>
+    <t>MASSA C OVOS ISABELA 500G PARAFUSO</t>
+  </si>
+  <si>
+    <t>ACHOC TODDY PT 370G ORIGINAL</t>
+  </si>
+  <si>
+    <t>BEB 3 CORACOES POWER WHEY 250ML CHOC</t>
+  </si>
+  <si>
+    <t>SAB CLOY HIDR 80G MILK CARE</t>
+  </si>
+  <si>
+    <t>MOLHO TOMATE HEINZ 240G C PEDACOS</t>
+  </si>
+  <si>
+    <t>AMAC CONC FOFO LV500 PG400ML AZUL TUDAO</t>
+  </si>
+  <si>
+    <t>REFRIG COCA COLA PET 200ML ZERO</t>
+  </si>
+  <si>
+    <t>RACAO DODOG PREMIUM POWER MIX 5KG</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
   </si>
   <si>
     <t>17/10/2024</t>
   </si>
   <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>05/12/2024</t>
+  </si>
+  <si>
+    <t>07/11/2024</t>
+  </si>
+  <si>
+    <t>11/11/2024</t>
+  </si>
+  <si>
+    <t>16/12/2024</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
+  </si>
+  <si>
     <t>04/12/2024</t>
   </si>
   <si>
-    <t>14/12/2024</t>
-  </si>
-  <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>19/11/2024</t>
-  </si>
-  <si>
-    <t>07/12/2024</t>
-  </si>
-  <si>
-    <t>27/03/2026</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
+    <t>18/09/2024</t>
+  </si>
+  <si>
+    <t>10/12/2024</t>
+  </si>
+  <si>
+    <t>05/10/2024</t>
   </si>
   <si>
     <t>18/10/2024</t>
   </si>
   <si>
-    <t>24/10/2024</t>
-  </si>
-  <si>
-    <t>21/12/2024</t>
-  </si>
-  <si>
-    <t>16/01/2026</t>
-  </si>
-  <si>
-    <t>05/12/2024</t>
-  </si>
-  <si>
-    <t>18/12/2024</t>
-  </si>
-  <si>
-    <t>23/09/2024</t>
-  </si>
-  <si>
-    <t>08/10/2024</t>
-  </si>
-  <si>
-    <t>09/10/2024</t>
-  </si>
-  <si>
-    <t>10/10/2024</t>
-  </si>
-  <si>
-    <t>21/10/2024</t>
-  </si>
-  <si>
-    <t>22/10/2024</t>
-  </si>
-  <si>
-    <t>28/10/2024</t>
-  </si>
-  <si>
-    <t>06/11/2024</t>
-  </si>
-  <si>
-    <t>07/11/2024</t>
-  </si>
-  <si>
-    <t>13/11/2024</t>
-  </si>
-  <si>
-    <t>03/12/2024</t>
-  </si>
-  <si>
-    <t>09/12/2024</t>
-  </si>
-  <si>
-    <t>13/12/2024</t>
+    <t>21/06/2025</t>
   </si>
   <si>
     <t>17/12/2024</t>
   </si>
   <si>
-    <t>26/12/2024</t>
-  </si>
-  <si>
-    <t>08/07/2025</t>
-  </si>
-  <si>
-    <t>29/04/2026</t>
-  </si>
-  <si>
-    <t>23/06/2025</t>
+    <t>28/12/2024</t>
+  </si>
+  <si>
+    <t>06/08/2025</t>
   </si>
   <si>
     <t>Ativo</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>24</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>72</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>30</t>
+    <t>32</t>
+  </si>
+  <si>
+    <t>4660</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>2804</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>1516</t>
+  </si>
+  <si>
+    <t>25857</t>
+  </si>
+  <si>
+    <t>761</t>
+  </si>
+  <si>
+    <t>4149</t>
+  </si>
+  <si>
+    <t>4248</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>1565</t>
+  </si>
+  <si>
+    <t>1217</t>
+  </si>
+  <si>
+    <t>1206</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>561</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>899</t>
+  </si>
+  <si>
+    <t>1969</t>
+  </si>
+  <si>
+    <t>860</t>
   </si>
   <si>
     <t>180</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>2086</t>
-  </si>
-  <si>
-    <t>1893</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>941</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1673</t>
-  </si>
-  <si>
-    <t>269</t>
-  </si>
-  <si>
-    <t>1353</t>
-  </si>
-  <si>
-    <t>648</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>439</t>
-  </si>
-  <si>
-    <t>243</t>
-  </si>
-  <si>
-    <t>17992</t>
-  </si>
-  <si>
-    <t>1227</t>
+    <t>1948</t>
+  </si>
+  <si>
+    <t>351</t>
+  </si>
+  <si>
+    <t>1678</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>1191</t>
+  </si>
+  <si>
+    <t>2117</t>
+  </si>
+  <si>
+    <t>809</t>
+  </si>
+  <si>
+    <t>855</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>546</t>
+  </si>
+  <si>
+    <t>30537</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>2091</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>22669</t>
+  </si>
+  <si>
+    <t>559</t>
+  </si>
+  <si>
+    <t>1685</t>
+  </si>
+  <si>
+    <t>391</t>
+  </si>
+  <si>
+    <t>61677</t>
+  </si>
+  <si>
+    <t>670</t>
+  </si>
+  <si>
+    <t>551</t>
+  </si>
+  <si>
+    <t>898</t>
+  </si>
+  <si>
+    <t>765</t>
+  </si>
+  <si>
+    <t>40947</t>
+  </si>
+  <si>
+    <t>912</t>
+  </si>
+  <si>
+    <t>779</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>2537</t>
+  </si>
+  <si>
+    <t>272</t>
   </si>
   <si>
     <t>153</t>
   </si>
   <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>19204</t>
-  </si>
-  <si>
-    <t>1278</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>2048</t>
-  </si>
-  <si>
-    <t>234</t>
-  </si>
-  <si>
-    <t>621</t>
-  </si>
-  <si>
-    <t>433</t>
+    <t>2544</t>
+  </si>
+  <si>
+    <t>1249</t>
+  </si>
+  <si>
+    <t>2118</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>684</t>
+  </si>
+  <si>
+    <t>3598</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>28659</t>
+  </si>
+  <si>
+    <t>1054</t>
+  </si>
+  <si>
+    <t>711</t>
+  </si>
+  <si>
+    <t>2335</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>35</t>
   </si>
   <si>
     <t>87</t>
-  </si>
-  <si>
-    <t>376</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>610</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>735</t>
-  </si>
-  <si>
-    <t>965</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>512</t>
-  </si>
-  <si>
-    <t>438</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>338</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>527</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>1298</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>257</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>870</t>
-  </si>
-  <si>
-    <t>841</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>458</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>831</t>
-  </si>
-  <si>
-    <t>23350</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>2058</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>725</t>
-  </si>
-  <si>
-    <t>25381</t>
-  </si>
-  <si>
-    <t>442</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>64</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U86"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -1282,31 +1132,31 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="G2" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H2" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1318,13 +1168,13 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="O2">
-        <v>121</v>
+        <v>314</v>
       </c>
       <c r="P2">
-        <v>196</v>
+        <v>494</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1336,60 +1186,60 @@
         <v>90</v>
       </c>
       <c r="T2">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="U2">
-        <v>118.07</v>
+        <v>7329</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="G3" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H3" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="O3">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="P3">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -1401,42 +1251,42 @@
         <v>90</v>
       </c>
       <c r="T3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U3">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="G4" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H4" t="s">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -1448,13 +1298,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
       <c r="O4">
-        <v>35</v>
+        <v>156</v>
       </c>
       <c r="P4">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1466,10 +1316,10 @@
         <v>90</v>
       </c>
       <c r="T4">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="U4">
-        <v>274.8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -1477,49 +1327,49 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="F5" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="G5" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H5" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="I5">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="N5" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="O5">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1531,42 +1381,42 @@
         <v>90</v>
       </c>
       <c r="T5">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="G6" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H6" t="s">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -1578,13 +1428,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="O6">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1596,10 +1446,10 @@
         <v>90</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U6">
-        <v>17</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -1607,31 +1457,31 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="F7" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="G7" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H7" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>55</v>
+        <v>1341</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1643,13 +1493,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
       <c r="O7">
-        <v>88</v>
+        <v>1718</v>
       </c>
       <c r="P7">
-        <v>160</v>
+        <v>2654</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1661,42 +1511,42 @@
         <v>90</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>7329</v>
       </c>
     </row>
     <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="G8" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H8" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1708,13 +1558,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>222</v>
+        <v>170</v>
       </c>
       <c r="O8">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="P8">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1726,60 +1576,60 @@
         <v>90</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="U8">
-        <v>52</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="G9" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H9" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="I9">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
       <c r="O9">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="P9">
-        <v>302</v>
+        <v>384</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1791,60 +1641,60 @@
         <v>90</v>
       </c>
       <c r="T9">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F10" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="G10" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H10" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="I10">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="O10">
-        <v>74</v>
+        <v>236</v>
       </c>
       <c r="P10">
-        <v>146</v>
+        <v>260</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1856,10 +1706,10 @@
         <v>90</v>
       </c>
       <c r="T10">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1867,31 +1717,31 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="G11" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H11" t="s">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="I11">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -1903,13 +1753,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
       <c r="O11">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="P11">
-        <v>156</v>
+        <v>272</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -1921,42 +1771,42 @@
         <v>90</v>
       </c>
       <c r="T11">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="U11">
-        <v>46</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F12" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="G12" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H12" t="s">
-        <v>201</v>
+        <v>155</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1968,13 +1818,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="O12">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -1986,7 +1836,7 @@
         <v>90</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U12">
         <v>17</v>
@@ -1994,52 +1844,52 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="G13" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H13" t="s">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J13">
-        <v>11</v>
+        <v>-10</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="O13">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="P13">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2051,10 +1901,10 @@
         <v>90</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U13">
-        <v>12</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -2065,46 +1915,46 @@
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F14" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="G14" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H14" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="I14">
         <v>12</v>
       </c>
       <c r="J14">
-        <v>21</v>
+        <v>-67</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="O14">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="P14">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2116,42 +1966,42 @@
         <v>90</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <v>20</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="G15" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H15" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="I15">
         <v>12</v>
       </c>
       <c r="J15">
-        <v>1127</v>
+        <v>74</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -2163,13 +2013,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="O15">
-        <v>1186</v>
+        <v>178</v>
       </c>
       <c r="P15">
-        <v>1834</v>
+        <v>274</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2181,107 +2031,107 @@
         <v>90</v>
       </c>
       <c r="T15">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="U15">
-        <v>7657</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" t="s">
+        <v>150</v>
+      </c>
+      <c r="H16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16">
+        <v>36</v>
+      </c>
+      <c r="J16">
+        <v>62</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>178</v>
+      </c>
+      <c r="O16">
+        <v>66</v>
+      </c>
+      <c r="P16">
+        <v>102</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>90</v>
+      </c>
+      <c r="T16">
+        <v>2</v>
+      </c>
+      <c r="U16">
         <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" t="s">
-        <v>166</v>
-      </c>
-      <c r="G16" t="s">
-        <v>196</v>
-      </c>
-      <c r="H16" t="s">
-        <v>205</v>
-      </c>
-      <c r="I16">
-        <v>12</v>
-      </c>
-      <c r="J16">
-        <v>66</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>229</v>
-      </c>
-      <c r="O16">
-        <v>78</v>
-      </c>
-      <c r="P16">
-        <v>126</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>90</v>
-      </c>
-      <c r="T16">
-        <v>5</v>
-      </c>
-      <c r="U16">
-        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="G17" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H17" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="I17">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="J17">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -2293,13 +2143,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="O17">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="P17">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -2314,36 +2164,36 @@
         <v>2</v>
       </c>
       <c r="U17">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F18" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="G18" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H18" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>-4</v>
@@ -2352,19 +2202,19 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="O18">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -2376,42 +2226,42 @@
         <v>90</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>12</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="G19" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H19" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="I19">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>1083</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -2423,13 +2273,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="O19">
-        <v>1284</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>1980</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -2441,60 +2291,60 @@
         <v>90</v>
       </c>
       <c r="T19">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>7657</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="G20" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H20" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M20">
         <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="O20">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="P20">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -2506,60 +2356,60 @@
         <v>90</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="F21" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="G21" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H21" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J21">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M21">
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="O21">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="P21">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -2571,60 +2421,60 @@
         <v>90</v>
       </c>
       <c r="T21">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="U21">
-        <v>433.9</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
         <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="G22" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H22" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="O22">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="P22">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -2636,60 +2486,60 @@
         <v>90</v>
       </c>
       <c r="T22">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>422</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
         <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F23" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="G23" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H23" t="s">
-        <v>201</v>
+        <v>68</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="O23">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="P23">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -2701,10 +2551,10 @@
         <v>90</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -2712,49 +2562,49 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
         <v>35</v>
       </c>
       <c r="D24" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" t="s">
+        <v>151</v>
+      </c>
+      <c r="I24">
+        <v>12</v>
+      </c>
+      <c r="J24">
+        <v>48</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>185</v>
+      </c>
+      <c r="O24">
         <v>56</v>
       </c>
-      <c r="E24" t="s">
-        <v>116</v>
-      </c>
-      <c r="F24" t="s">
-        <v>167</v>
-      </c>
-      <c r="G24" t="s">
-        <v>196</v>
-      </c>
-      <c r="H24" t="s">
-        <v>203</v>
-      </c>
-      <c r="I24">
-        <v>10</v>
-      </c>
-      <c r="J24">
-        <v>112</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>235</v>
-      </c>
-      <c r="O24">
-        <v>120</v>
-      </c>
       <c r="P24">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -2766,60 +2616,60 @@
         <v>90</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U24">
-        <v>433.9</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25">
+        <v>12</v>
+      </c>
+      <c r="J25">
+        <v>31</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>186</v>
+      </c>
+      <c r="O25">
         <v>36</v>
       </c>
-      <c r="D25" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" t="s">
-        <v>118</v>
-      </c>
-      <c r="F25" t="s">
-        <v>172</v>
-      </c>
-      <c r="G25" t="s">
-        <v>196</v>
-      </c>
-      <c r="H25" t="s">
-        <v>206</v>
-      </c>
-      <c r="I25">
-        <v>8</v>
-      </c>
-      <c r="J25">
-        <v>5</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>8</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>236</v>
-      </c>
-      <c r="O25">
-        <v>24</v>
-      </c>
       <c r="P25">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -2831,60 +2681,60 @@
         <v>90</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U25">
-        <v>336.75</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
         <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="G26" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H26" t="s">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="I26">
         <v>6</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>-54</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="O26">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="P26">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -2896,42 +2746,42 @@
         <v>90</v>
       </c>
       <c r="T26">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="U26">
-        <v>126</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
         <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E27" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="F27" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="G27" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H27" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="I27">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J27">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -2943,13 +2793,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="O27">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="P27">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -2961,18 +2811,18 @@
         <v>90</v>
       </c>
       <c r="T27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U27">
-        <v>13</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
         <v>36</v>
@@ -2981,40 +2831,40 @@
         <v>61</v>
       </c>
       <c r="E28" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="G28" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H28" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="I28">
+        <v>6</v>
+      </c>
+      <c r="J28">
+        <v>64</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
         <v>24</v>
       </c>
-      <c r="J28">
-        <v>32</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
       <c r="M28">
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="O28">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="P28">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -3026,60 +2876,60 @@
         <v>90</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
         <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E29" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="F29" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="G29" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H29" t="s">
-        <v>208</v>
+        <v>152</v>
       </c>
       <c r="I29">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J29">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M29">
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>239</v>
+        <v>190</v>
       </c>
       <c r="O29">
         <v>12</v>
       </c>
       <c r="P29">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -3091,10 +2941,10 @@
         <v>90</v>
       </c>
       <c r="T29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -3102,31 +2952,31 @@
         <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
         <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="G30" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H30" t="s">
-        <v>209</v>
+        <v>151</v>
       </c>
       <c r="I30">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="J30">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -3138,13 +2988,13 @@
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>240</v>
+        <v>191</v>
       </c>
       <c r="O30">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P30">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -3156,60 +3006,60 @@
         <v>90</v>
       </c>
       <c r="T30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="E31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F31" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G31" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H31" t="s">
-        <v>201</v>
+        <v>151</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="O31">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -3221,60 +3071,60 @@
         <v>90</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U31">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="F32" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="G32" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H32" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M32">
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>241</v>
+        <v>193</v>
       </c>
       <c r="O32">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="P32">
-        <v>24</v>
+        <v>168</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -3286,42 +3136,42 @@
         <v>90</v>
       </c>
       <c r="T32">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="U32">
-        <v>12</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F33" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="G33" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H33" t="s">
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="I33">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J33">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -3333,13 +3183,13 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>242</v>
+        <v>194</v>
       </c>
       <c r="O33">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="P33">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -3351,42 +3201,42 @@
         <v>90</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>30</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:21">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
         <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F34" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="G34" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H34" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -3398,13 +3248,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="O34">
-        <v>7</v>
+        <v>192</v>
       </c>
       <c r="P34">
-        <v>10</v>
+        <v>288</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -3416,60 +3266,60 @@
         <v>90</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U34">
-        <v>17</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
         <v>37</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="E35" t="s">
         <v>112</v>
       </c>
       <c r="F35" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="G35" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H35" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J35">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>243</v>
+        <v>154</v>
       </c>
       <c r="O35">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="P35">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -3481,10 +3331,10 @@
         <v>90</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U35">
-        <v>12</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -3498,43 +3348,43 @@
         <v>37</v>
       </c>
       <c r="D36" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E36" t="s">
         <v>113</v>
       </c>
       <c r="F36" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="G36" t="s">
+        <v>150</v>
+      </c>
+      <c r="H36" t="s">
+        <v>160</v>
+      </c>
+      <c r="I36">
+        <v>24</v>
+      </c>
+      <c r="J36">
+        <v>8</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
         <v>196</v>
       </c>
-      <c r="H36" t="s">
-        <v>205</v>
-      </c>
-      <c r="I36">
-        <v>12</v>
-      </c>
-      <c r="J36">
-        <v>22</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36" t="s">
-        <v>244</v>
-      </c>
       <c r="O36">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="P36">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -3546,10 +3396,10 @@
         <v>90</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U36">
-        <v>20</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -3557,31 +3407,31 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E37" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F37" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="G37" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H37" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="I37">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J37">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -3593,13 +3443,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="s">
-        <v>245</v>
+        <v>197</v>
       </c>
       <c r="O37">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P37">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -3611,10 +3461,10 @@
         <v>90</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>442.17</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:21">
@@ -3622,31 +3472,31 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E38" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="F38" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="G38" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H38" t="s">
-        <v>207</v>
+        <v>151</v>
       </c>
       <c r="I38">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J38">
-        <v>17</v>
+        <v>1382</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -3658,13 +3508,13 @@
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>246</v>
+        <v>198</v>
       </c>
       <c r="O38">
-        <v>18</v>
+        <v>2112</v>
       </c>
       <c r="P38">
-        <v>42</v>
+        <v>3252</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -3676,60 +3526,60 @@
         <v>90</v>
       </c>
       <c r="T38">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="U38">
-        <v>24</v>
+        <v>7329</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="E39" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F39" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="G39" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H39" t="s">
-        <v>200</v>
+        <v>68</v>
       </c>
       <c r="I39">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M39">
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>247</v>
+        <v>199</v>
       </c>
       <c r="O39">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="P39">
-        <v>154</v>
+        <v>68</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -3744,57 +3594,57 @@
         <v>2</v>
       </c>
       <c r="U39">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E40" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F40" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="G40" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H40" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="I40">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J40">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>248</v>
+        <v>200</v>
       </c>
       <c r="O40">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="P40">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -3806,107 +3656,107 @@
         <v>90</v>
       </c>
       <c r="T40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E41" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F41" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="G41" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H41" t="s">
+        <v>154</v>
+      </c>
+      <c r="I41">
+        <v>10</v>
+      </c>
+      <c r="J41">
+        <v>42</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>70</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
         <v>201</v>
       </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41" t="s">
-        <v>220</v>
-      </c>
       <c r="O41">
+        <v>120</v>
+      </c>
+      <c r="P41">
+        <v>180</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>90</v>
+      </c>
+      <c r="T41">
         <v>7</v>
       </c>
-      <c r="P41">
-        <v>10</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>90</v>
-      </c>
-      <c r="T41">
-        <v>10</v>
-      </c>
       <c r="U41">
-        <v>17</v>
+        <v>384.9</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" t="s">
+        <v>113</v>
+      </c>
+      <c r="F42" t="s">
+        <v>143</v>
+      </c>
+      <c r="G42" t="s">
+        <v>150</v>
+      </c>
+      <c r="H42" t="s">
+        <v>160</v>
+      </c>
+      <c r="I42">
         <v>24</v>
       </c>
-      <c r="B42" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" t="s">
-        <v>67</v>
-      </c>
-      <c r="E42" t="s">
-        <v>127</v>
-      </c>
-      <c r="F42" t="s">
-        <v>178</v>
-      </c>
-      <c r="G42" t="s">
-        <v>196</v>
-      </c>
-      <c r="H42" t="s">
-        <v>210</v>
-      </c>
-      <c r="I42">
-        <v>180</v>
-      </c>
       <c r="J42">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -3918,13 +3768,13 @@
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>249</v>
+        <v>202</v>
       </c>
       <c r="O42">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="P42">
-        <v>288</v>
+        <v>20</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -3936,42 +3786,42 @@
         <v>90</v>
       </c>
       <c r="T42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U42">
-        <v>31</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D43" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="E43" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" t="s">
         <v>128</v>
       </c>
-      <c r="F43" t="s">
-        <v>179</v>
-      </c>
       <c r="G43" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H43" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="I43">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J43">
-        <v>16</v>
+        <v>1112</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -3983,13 +3833,13 @@
         <v>0</v>
       </c>
       <c r="N43" t="s">
-        <v>250</v>
+        <v>203</v>
       </c>
       <c r="O43">
-        <v>28</v>
+        <v>1504</v>
       </c>
       <c r="P43">
-        <v>40</v>
+        <v>2320</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -4001,172 +3851,172 @@
         <v>90</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="U43">
-        <v>6</v>
+        <v>7329</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
         <v>39</v>
       </c>
       <c r="D44" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E44" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
-        <v>180</v>
+        <v>131</v>
       </c>
       <c r="G44" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H44" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="I44">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J44">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M44">
         <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>251</v>
+        <v>204</v>
       </c>
       <c r="O44">
+        <v>60</v>
+      </c>
+      <c r="P44">
+        <v>76</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>90</v>
+      </c>
+      <c r="T44">
+        <v>3</v>
+      </c>
+      <c r="U44">
         <v>12</v>
-      </c>
-      <c r="P44">
-        <v>18</v>
-      </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>90</v>
-      </c>
-      <c r="T44">
-        <v>2</v>
-      </c>
-      <c r="U44">
-        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C45" t="s">
         <v>39</v>
       </c>
       <c r="D45" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E45" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="F45" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="G45" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H45" t="s">
-        <v>198</v>
+        <v>68</v>
       </c>
       <c r="I45">
+        <v>36</v>
+      </c>
+      <c r="J45">
+        <v>10</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>205</v>
+      </c>
+      <c r="O45">
+        <v>100</v>
+      </c>
+      <c r="P45">
+        <v>172</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>90</v>
+      </c>
+      <c r="T45">
+        <v>5</v>
+      </c>
+      <c r="U45">
         <v>6</v>
-      </c>
-      <c r="J45">
-        <v>4</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45" t="s">
-        <v>252</v>
-      </c>
-      <c r="O45">
-        <v>6</v>
-      </c>
-      <c r="P45">
-        <v>12</v>
-      </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>90</v>
-      </c>
-      <c r="T45">
-        <v>2</v>
-      </c>
-      <c r="U45">
-        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
         <v>39</v>
       </c>
       <c r="D46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E46" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F46" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="G46" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H46" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="I46">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J46">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -4178,13 +4028,13 @@
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>253</v>
+        <v>151</v>
       </c>
       <c r="O46">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="P46">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -4196,60 +4046,60 @@
         <v>90</v>
       </c>
       <c r="T46">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U46">
-        <v>86</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C47" t="s">
         <v>39</v>
       </c>
       <c r="D47" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E47" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="F47" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="G47" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H47" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="I47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J47">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M47">
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>254</v>
+        <v>206</v>
       </c>
       <c r="O47">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="P47">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -4261,10 +4111,10 @@
         <v>90</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U47">
-        <v>228</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -4272,49 +4122,49 @@
         <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="F48" t="s">
-        <v>184</v>
+        <v>128</v>
       </c>
       <c r="G48" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H48" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="I48">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J48">
-        <v>-1</v>
+        <v>2108</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="M48">
         <v>0</v>
       </c>
       <c r="N48" t="s">
-        <v>255</v>
+        <v>207</v>
       </c>
       <c r="O48">
-        <v>6</v>
+        <v>4060</v>
       </c>
       <c r="P48">
-        <v>12</v>
+        <v>6256</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -4326,10 +4176,10 @@
         <v>90</v>
       </c>
       <c r="T48">
-        <v>2</v>
+        <v>261</v>
       </c>
       <c r="U48">
-        <v>23</v>
+        <v>7329</v>
       </c>
     </row>
     <row r="49" spans="1:21">
@@ -4337,32 +4187,32 @@
         <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D49" t="s">
+        <v>63</v>
+      </c>
+      <c r="E49" t="s">
+        <v>104</v>
+      </c>
+      <c r="F49" t="s">
+        <v>128</v>
+      </c>
+      <c r="G49" t="s">
+        <v>150</v>
+      </c>
+      <c r="H49" t="s">
+        <v>151</v>
+      </c>
+      <c r="I49">
+        <v>12</v>
+      </c>
+      <c r="J49">
         <v>39</v>
       </c>
-      <c r="D49" t="s">
-        <v>74</v>
-      </c>
-      <c r="E49" t="s">
-        <v>134</v>
-      </c>
-      <c r="F49" t="s">
-        <v>185</v>
-      </c>
-      <c r="G49" t="s">
-        <v>196</v>
-      </c>
-      <c r="H49" t="s">
-        <v>211</v>
-      </c>
-      <c r="I49">
-        <v>20</v>
-      </c>
-      <c r="J49">
-        <v>2</v>
-      </c>
       <c r="K49">
         <v>0</v>
       </c>
@@ -4373,13 +4223,13 @@
         <v>0</v>
       </c>
       <c r="N49" t="s">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="O49">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="P49">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -4391,60 +4241,60 @@
         <v>90</v>
       </c>
       <c r="T49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>12.95</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D50" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E50" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="F50" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="G50" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H50" t="s">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="I50">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M50">
         <v>0</v>
       </c>
       <c r="N50" t="s">
-        <v>257</v>
+        <v>209</v>
       </c>
       <c r="O50">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="P50">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -4456,60 +4306,60 @@
         <v>90</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U50">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:21">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C51" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D51" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="E51" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="F51" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="G51" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H51" t="s">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="I51">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J51">
-        <v>9</v>
+        <v>-8</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M51">
         <v>0</v>
       </c>
       <c r="N51" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="O51">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="P51">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -4521,42 +4371,42 @@
         <v>90</v>
       </c>
       <c r="T51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>6</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E52" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="F52" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="G52" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H52" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
       <c r="I52">
         <v>24</v>
       </c>
       <c r="J52">
-        <v>47</v>
+        <v>186</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -4568,13 +4418,13 @@
         <v>0</v>
       </c>
       <c r="N52" t="s">
-        <v>259</v>
+        <v>211</v>
       </c>
       <c r="O52">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="P52">
-        <v>136</v>
+        <v>288</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -4586,10 +4436,10 @@
         <v>90</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U52">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -4597,31 +4447,31 @@
         <v>21</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D53" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="E53" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="F53" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="G53" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H53" t="s">
-        <v>211</v>
+        <v>151</v>
       </c>
       <c r="I53">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J53">
-        <v>33</v>
+        <v>2500</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -4633,13 +4483,13 @@
         <v>0</v>
       </c>
       <c r="N53" t="s">
-        <v>260</v>
+        <v>212</v>
       </c>
       <c r="O53">
-        <v>40</v>
+        <v>2750</v>
       </c>
       <c r="P53">
-        <v>60</v>
+        <v>4238</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -4651,60 +4501,60 @@
         <v>90</v>
       </c>
       <c r="T53">
-        <v>2</v>
+        <v>145</v>
       </c>
       <c r="U53">
-        <v>22.2</v>
+        <v>7329</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E54" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="F54" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="G54" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H54" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="I54">
+        <v>6</v>
+      </c>
+      <c r="J54">
+        <v>9</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
         <v>24</v>
       </c>
-      <c r="J54">
-        <v>62</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
       <c r="M54">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N54" t="s">
-        <v>261</v>
+        <v>209</v>
       </c>
       <c r="O54">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="P54">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -4716,60 +4566,60 @@
         <v>90</v>
       </c>
       <c r="T54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U54">
-        <v>147</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s">
         <v>28</v>
       </c>
       <c r="C55" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D55" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E55" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F55" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="G55" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H55" t="s">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="I55">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="K55">
         <v>0</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
       <c r="N55" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="O55">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="P55">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -4781,42 +4631,42 @@
         <v>90</v>
       </c>
       <c r="T55">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U55">
-        <v>19</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C56" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D56" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E56" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="F56" t="s">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="G56" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H56" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -4828,13 +4678,13 @@
         <v>0</v>
       </c>
       <c r="N56" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="O56">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="P56">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -4846,42 +4696,42 @@
         <v>90</v>
       </c>
       <c r="T56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U56">
-        <v>17</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D57" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E57" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="F57" t="s">
-        <v>192</v>
+        <v>143</v>
       </c>
       <c r="G57" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H57" t="s">
-        <v>213</v>
+        <v>160</v>
       </c>
       <c r="I57">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="J57">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -4893,13 +4743,13 @@
         <v>0</v>
       </c>
       <c r="N57" t="s">
-        <v>263</v>
+        <v>215</v>
       </c>
       <c r="O57">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="P57">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -4911,10 +4761,10 @@
         <v>90</v>
       </c>
       <c r="T57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U57">
-        <v>7</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="58" spans="1:21">
@@ -4922,31 +4772,31 @@
         <v>21</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D58" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E58" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="G58" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H58" t="s">
-        <v>213</v>
+        <v>151</v>
       </c>
       <c r="I58">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="J58">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -4955,16 +4805,16 @@
         <v>0</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N58" t="s">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="O58">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="P58">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -4976,60 +4826,60 @@
         <v>90</v>
       </c>
       <c r="T58">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U58">
-        <v>9</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B59" t="s">
         <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D59" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E59" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="F59" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="G59" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H59" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="I59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M59">
         <v>0</v>
       </c>
       <c r="N59" t="s">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="O59">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P59">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -5041,42 +4891,42 @@
         <v>90</v>
       </c>
       <c r="T59">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U59">
-        <v>11</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D60" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E60" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="F60" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="G60" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H60" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="I60">
         <v>12</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -5088,13 +4938,13 @@
         <v>0</v>
       </c>
       <c r="N60" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="O60">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P60">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -5106,10 +4956,10 @@
         <v>90</v>
       </c>
       <c r="T60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U60">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:21">
@@ -5117,49 +4967,49 @@
         <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D61" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E61" t="s">
-        <v>146</v>
+        <v>109</v>
       </c>
       <c r="F61" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="G61" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H61" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="I61">
         <v>12</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="K61">
         <v>0</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61" t="s">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="O61">
-        <v>10</v>
+        <v>212</v>
       </c>
       <c r="P61">
-        <v>22</v>
+        <v>332</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -5171,60 +5021,60 @@
         <v>90</v>
       </c>
       <c r="T61">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U61">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B62" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D62" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E62" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="F62" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="G62" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H62" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="I62">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="J62">
+        <v>28</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
         <v>6</v>
       </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>72</v>
-      </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62" t="s">
-        <v>267</v>
+        <v>220</v>
       </c>
       <c r="O62">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="P62">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -5236,60 +5086,60 @@
         <v>90</v>
       </c>
       <c r="T62">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="U62">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B63" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C63" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D63" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="E63" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="F63" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="G63" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H63" t="s">
-        <v>200</v>
+        <v>68</v>
       </c>
       <c r="I63">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
       <c r="N63" t="s">
-        <v>268</v>
+        <v>221</v>
       </c>
       <c r="O63">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="P63">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -5301,42 +5151,42 @@
         <v>90</v>
       </c>
       <c r="T63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C64" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D64" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E64" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="F64" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="G64" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H64" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="I64">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J64">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -5348,13 +5198,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="s">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="O64">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="P64">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -5369,39 +5219,39 @@
         <v>2</v>
       </c>
       <c r="U64">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C65" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D65" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E65" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="F65" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="G65" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H65" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
       <c r="I65">
         <v>24</v>
       </c>
       <c r="J65">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -5413,13 +5263,13 @@
         <v>0</v>
       </c>
       <c r="N65" t="s">
-        <v>270</v>
+        <v>223</v>
       </c>
       <c r="O65">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="P65">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -5434,39 +5284,39 @@
         <v>2</v>
       </c>
       <c r="U65">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C66" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D66" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E66" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="F66" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G66" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H66" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="I66">
         <v>12</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -5478,13 +5328,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="s">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="O66">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P66">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -5496,42 +5346,42 @@
         <v>90</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U66">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C67" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D67" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E67" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="F67" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="G67" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H67" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="J67">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -5543,13 +5393,13 @@
         <v>0</v>
       </c>
       <c r="N67" t="s">
-        <v>272</v>
+        <v>225</v>
       </c>
       <c r="O67">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="P67">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -5561,42 +5411,42 @@
         <v>90</v>
       </c>
       <c r="T67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U67">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C68" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D68" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E68" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F68" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="G68" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H68" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="I68">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -5608,13 +5458,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="O68">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P68">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -5629,7 +5479,7 @@
         <v>2</v>
       </c>
       <c r="U68">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:21">
@@ -5637,31 +5487,31 @@
         <v>21</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C69" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D69" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E69" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F69" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="G69" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H69" t="s">
-        <v>201</v>
+        <v>151</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -5673,13 +5523,13 @@
         <v>0</v>
       </c>
       <c r="N69" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="O69">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="P69">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -5691,10 +5541,10 @@
         <v>90</v>
       </c>
       <c r="T69">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U69">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:21">
@@ -5702,49 +5552,49 @@
         <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C70" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E70" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="F70" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G70" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H70" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="I70">
         <v>12</v>
       </c>
       <c r="J70">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M70">
         <v>0</v>
       </c>
       <c r="N70" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="O70">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="P70">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -5759,39 +5609,39 @@
         <v>2</v>
       </c>
       <c r="U70">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B71" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C71" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="E71" t="s">
+        <v>89</v>
+      </c>
+      <c r="F71" t="s">
+        <v>130</v>
+      </c>
+      <c r="G71" t="s">
+        <v>150</v>
+      </c>
+      <c r="H71" t="s">
         <v>153</v>
       </c>
-      <c r="F71" t="s">
-        <v>167</v>
-      </c>
-      <c r="G71" t="s">
-        <v>196</v>
-      </c>
-      <c r="H71" t="s">
-        <v>214</v>
-      </c>
       <c r="I71">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="J71">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -5803,13 +5653,13 @@
         <v>0</v>
       </c>
       <c r="N71" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
       <c r="O71">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="P71">
-        <v>200</v>
+        <v>306</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -5821,60 +5671,60 @@
         <v>90</v>
       </c>
       <c r="T71">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="U71">
-        <v>12.9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C72" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E72" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="F72" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="G72" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H72" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="I72">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J72">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M72">
         <v>0</v>
       </c>
       <c r="N72" t="s">
-        <v>67</v>
+        <v>230</v>
       </c>
       <c r="O72">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="P72">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -5889,39 +5739,39 @@
         <v>2</v>
       </c>
       <c r="U72">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B73" t="s">
         <v>27</v>
       </c>
       <c r="C73" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="E73" t="s">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c r="F73" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="G73" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H73" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="I73">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>858</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -5933,13 +5783,13 @@
         <v>0</v>
       </c>
       <c r="N73" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="O73">
-        <v>6</v>
+        <v>1872</v>
       </c>
       <c r="P73">
-        <v>16</v>
+        <v>2880</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -5951,60 +5801,60 @@
         <v>90</v>
       </c>
       <c r="T73">
-        <v>2</v>
+        <v>169</v>
       </c>
       <c r="U73">
-        <v>56</v>
+        <v>7329</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C74" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D74" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E74" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="F74" t="s">
-        <v>193</v>
+        <v>130</v>
       </c>
       <c r="G74" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H74" t="s">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J74">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K74">
         <v>0</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M74">
         <v>0</v>
       </c>
       <c r="N74" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="O74">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="P74">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -6019,122 +5869,122 @@
         <v>2</v>
       </c>
       <c r="U74">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C75" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D75" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E75" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F75" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="G75" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H75" t="s">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="I75">
+        <v>8</v>
+      </c>
+      <c r="J75">
+        <v>90</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>16</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75" t="s">
+        <v>233</v>
+      </c>
+      <c r="O75">
+        <v>116</v>
+      </c>
+      <c r="P75">
+        <v>180</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>90</v>
+      </c>
+      <c r="T75">
+        <v>10</v>
+      </c>
+      <c r="U75">
         <v>12</v>
-      </c>
-      <c r="J75">
-        <v>35</v>
-      </c>
-      <c r="K75">
-        <v>0</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75" t="s">
-        <v>277</v>
-      </c>
-      <c r="O75">
-        <v>36</v>
-      </c>
-      <c r="P75">
-        <v>72</v>
-      </c>
-      <c r="Q75">
-        <v>0</v>
-      </c>
-      <c r="R75">
-        <v>0</v>
-      </c>
-      <c r="S75">
-        <v>90</v>
-      </c>
-      <c r="T75">
-        <v>4</v>
-      </c>
-      <c r="U75">
-        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B76" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76" t="s">
+        <v>62</v>
+      </c>
+      <c r="E76" t="s">
+        <v>103</v>
+      </c>
+      <c r="F76" t="s">
+        <v>139</v>
+      </c>
+      <c r="G76" t="s">
+        <v>150</v>
+      </c>
+      <c r="H76" t="s">
+        <v>68</v>
+      </c>
+      <c r="I76">
+        <v>36</v>
+      </c>
+      <c r="J76">
         <v>27</v>
       </c>
-      <c r="C76" t="s">
-        <v>40</v>
-      </c>
-      <c r="D76" t="s">
-        <v>46</v>
-      </c>
-      <c r="E76" t="s">
-        <v>106</v>
-      </c>
-      <c r="F76" t="s">
-        <v>166</v>
-      </c>
-      <c r="G76" t="s">
-        <v>196</v>
-      </c>
-      <c r="H76" t="s">
-        <v>200</v>
-      </c>
-      <c r="I76">
-        <v>72</v>
-      </c>
-      <c r="J76">
-        <v>7</v>
-      </c>
       <c r="K76">
         <v>0</v>
       </c>
       <c r="L76">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="M76">
         <v>0</v>
       </c>
       <c r="N76" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="O76">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="P76">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -6146,60 +5996,60 @@
         <v>90</v>
       </c>
       <c r="T76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U76">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B77" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C77" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D77" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E77" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F77" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="G77" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H77" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="I77">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J77">
-        <v>1239</v>
+        <v>-15</v>
       </c>
       <c r="K77">
         <v>0</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M77">
         <v>0</v>
       </c>
       <c r="N77" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="O77">
-        <v>1584</v>
+        <v>52</v>
       </c>
       <c r="P77">
-        <v>2448</v>
+        <v>64</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -6211,42 +6061,42 @@
         <v>90</v>
       </c>
       <c r="T77">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="U77">
-        <v>7657</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B78" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C78" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D78" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E78" t="s">
+        <v>127</v>
+      </c>
+      <c r="F78" t="s">
+        <v>137</v>
+      </c>
+      <c r="G78" t="s">
+        <v>150</v>
+      </c>
+      <c r="H78" t="s">
         <v>157</v>
       </c>
-      <c r="F78" t="s">
-        <v>166</v>
-      </c>
-      <c r="G78" t="s">
-        <v>196</v>
-      </c>
-      <c r="H78" t="s">
-        <v>202</v>
-      </c>
       <c r="I78">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="J78">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="K78">
         <v>0</v>
@@ -6258,13 +6108,13 @@
         <v>0</v>
       </c>
       <c r="N78" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="O78">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="P78">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -6276,42 +6126,42 @@
         <v>90</v>
       </c>
       <c r="T78">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U78">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D79" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="F79" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="G79" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H79" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="I79">
         <v>12</v>
       </c>
       <c r="J79">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="K79">
         <v>0</v>
@@ -6323,13 +6173,13 @@
         <v>0</v>
       </c>
       <c r="N79" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="O79">
-        <v>138</v>
+        <v>36</v>
       </c>
       <c r="P79">
-        <v>222</v>
+        <v>72</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -6341,465 +6191,10 @@
         <v>90</v>
       </c>
       <c r="T79">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="U79">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21">
-      <c r="A80" t="s">
-        <v>22</v>
-      </c>
-      <c r="B80" t="s">
-        <v>27</v>
-      </c>
-      <c r="C80" t="s">
-        <v>41</v>
-      </c>
-      <c r="D80" t="s">
-        <v>99</v>
-      </c>
-      <c r="E80" t="s">
-        <v>159</v>
-      </c>
-      <c r="F80" t="s">
-        <v>194</v>
-      </c>
-      <c r="G80" t="s">
-        <v>196</v>
-      </c>
-      <c r="H80" t="s">
-        <v>206</v>
-      </c>
-      <c r="I80">
         <v>8</v>
-      </c>
-      <c r="J80">
-        <v>-1</v>
-      </c>
-      <c r="K80">
-        <v>0</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80" t="s">
-        <v>282</v>
-      </c>
-      <c r="O80">
-        <v>18</v>
-      </c>
-      <c r="P80">
-        <v>34</v>
-      </c>
-      <c r="Q80">
-        <v>0</v>
-      </c>
-      <c r="R80">
-        <v>0</v>
-      </c>
-      <c r="S80">
-        <v>90</v>
-      </c>
-      <c r="T80">
-        <v>5</v>
-      </c>
-      <c r="U80">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21">
-      <c r="A81" t="s">
-        <v>22</v>
-      </c>
-      <c r="B81" t="s">
-        <v>27</v>
-      </c>
-      <c r="C81" t="s">
-        <v>42</v>
-      </c>
-      <c r="D81" t="s">
-        <v>46</v>
-      </c>
-      <c r="E81" t="s">
-        <v>106</v>
-      </c>
-      <c r="F81" t="s">
-        <v>166</v>
-      </c>
-      <c r="G81" t="s">
-        <v>196</v>
-      </c>
-      <c r="H81" t="s">
-        <v>200</v>
-      </c>
-      <c r="I81">
-        <v>72</v>
-      </c>
-      <c r="J81">
-        <v>7</v>
-      </c>
-      <c r="K81">
-        <v>0</v>
-      </c>
-      <c r="L81">
-        <v>72</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81" t="s">
-        <v>283</v>
-      </c>
-      <c r="O81">
-        <v>88</v>
-      </c>
-      <c r="P81">
-        <v>160</v>
-      </c>
-      <c r="Q81">
-        <v>0</v>
-      </c>
-      <c r="R81">
-        <v>0</v>
-      </c>
-      <c r="S81">
-        <v>90</v>
-      </c>
-      <c r="T81">
-        <v>2</v>
-      </c>
-      <c r="U81">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21">
-      <c r="A82" t="s">
-        <v>23</v>
-      </c>
-      <c r="B82" t="s">
-        <v>29</v>
-      </c>
-      <c r="C82" t="s">
-        <v>42</v>
-      </c>
-      <c r="D82" t="s">
-        <v>54</v>
-      </c>
-      <c r="E82" t="s">
-        <v>114</v>
-      </c>
-      <c r="F82" t="s">
-        <v>166</v>
-      </c>
-      <c r="G82" t="s">
-        <v>196</v>
-      </c>
-      <c r="H82" t="s">
-        <v>205</v>
-      </c>
-      <c r="I82">
-        <v>12</v>
-      </c>
-      <c r="J82">
-        <v>1522</v>
-      </c>
-      <c r="K82">
-        <v>0</v>
-      </c>
-      <c r="L82">
-        <v>36</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82" t="s">
-        <v>284</v>
-      </c>
-      <c r="O82">
-        <v>1732</v>
-      </c>
-      <c r="P82">
-        <v>2668</v>
-      </c>
-      <c r="Q82">
-        <v>0</v>
-      </c>
-      <c r="R82">
-        <v>0</v>
-      </c>
-      <c r="S82">
-        <v>90</v>
-      </c>
-      <c r="T82">
-        <v>93</v>
-      </c>
-      <c r="U82">
-        <v>7657</v>
-      </c>
-    </row>
-    <row r="83" spans="1:21">
-      <c r="A83" t="s">
-        <v>21</v>
-      </c>
-      <c r="B83" t="s">
-        <v>26</v>
-      </c>
-      <c r="C83" t="s">
-        <v>42</v>
-      </c>
-      <c r="D83" t="s">
-        <v>100</v>
-      </c>
-      <c r="E83" t="s">
-        <v>160</v>
-      </c>
-      <c r="F83" t="s">
-        <v>167</v>
-      </c>
-      <c r="G83" t="s">
-        <v>196</v>
-      </c>
-      <c r="H83" t="s">
-        <v>201</v>
-      </c>
-      <c r="I83">
-        <v>1</v>
-      </c>
-      <c r="J83">
-        <v>4</v>
-      </c>
-      <c r="K83">
-        <v>0</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83" t="s">
-        <v>220</v>
-      </c>
-      <c r="O83">
-        <v>7</v>
-      </c>
-      <c r="P83">
-        <v>10</v>
-      </c>
-      <c r="Q83">
-        <v>0</v>
-      </c>
-      <c r="R83">
-        <v>0</v>
-      </c>
-      <c r="S83">
-        <v>90</v>
-      </c>
-      <c r="T83">
-        <v>6</v>
-      </c>
-      <c r="U83">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="84" spans="1:21">
-      <c r="A84" t="s">
-        <v>22</v>
-      </c>
-      <c r="B84" t="s">
-        <v>27</v>
-      </c>
-      <c r="C84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D84" t="s">
-        <v>52</v>
-      </c>
-      <c r="E84" t="s">
-        <v>112</v>
-      </c>
-      <c r="F84" t="s">
-        <v>167</v>
-      </c>
-      <c r="G84" t="s">
-        <v>196</v>
-      </c>
-      <c r="H84" t="s">
-        <v>204</v>
-      </c>
-      <c r="I84">
-        <v>4</v>
-      </c>
-      <c r="J84">
-        <v>-8</v>
-      </c>
-      <c r="K84">
-        <v>0</v>
-      </c>
-      <c r="L84">
-        <v>40</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84" t="s">
-        <v>285</v>
-      </c>
-      <c r="O84">
-        <v>52</v>
-      </c>
-      <c r="P84">
-        <v>64</v>
-      </c>
-      <c r="Q84">
-        <v>0</v>
-      </c>
-      <c r="R84">
-        <v>0</v>
-      </c>
-      <c r="S84">
-        <v>90</v>
-      </c>
-      <c r="T84">
-        <v>6</v>
-      </c>
-      <c r="U84">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="85" spans="1:21">
-      <c r="A85" t="s">
-        <v>22</v>
-      </c>
-      <c r="B85" t="s">
-        <v>27</v>
-      </c>
-      <c r="C85" t="s">
-        <v>42</v>
-      </c>
-      <c r="D85" t="s">
-        <v>101</v>
-      </c>
-      <c r="E85" t="s">
-        <v>161</v>
-      </c>
-      <c r="F85" t="s">
-        <v>167</v>
-      </c>
-      <c r="G85" t="s">
-        <v>196</v>
-      </c>
-      <c r="H85" t="s">
-        <v>215</v>
-      </c>
-      <c r="I85">
-        <v>108</v>
-      </c>
-      <c r="J85">
-        <v>65</v>
-      </c>
-      <c r="K85">
-        <v>0</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-      <c r="N85" t="s">
-        <v>286</v>
-      </c>
-      <c r="O85">
-        <v>66</v>
-      </c>
-      <c r="P85">
-        <v>174</v>
-      </c>
-      <c r="Q85">
-        <v>0</v>
-      </c>
-      <c r="R85">
-        <v>0</v>
-      </c>
-      <c r="S85">
-        <v>90</v>
-      </c>
-      <c r="T85">
-        <v>2</v>
-      </c>
-      <c r="U85">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21">
-      <c r="A86" t="s">
-        <v>21</v>
-      </c>
-      <c r="B86" t="s">
-        <v>26</v>
-      </c>
-      <c r="C86" t="s">
-        <v>42</v>
-      </c>
-      <c r="D86" t="s">
-        <v>102</v>
-      </c>
-      <c r="E86" t="s">
-        <v>162</v>
-      </c>
-      <c r="F86" t="s">
-        <v>195</v>
-      </c>
-      <c r="G86" t="s">
-        <v>196</v>
-      </c>
-      <c r="H86" t="s">
-        <v>203</v>
-      </c>
-      <c r="I86">
-        <v>10</v>
-      </c>
-      <c r="J86">
-        <v>3</v>
-      </c>
-      <c r="K86">
-        <v>0</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86" t="s">
-        <v>287</v>
-      </c>
-      <c r="O86">
-        <v>6</v>
-      </c>
-      <c r="P86">
-        <v>16</v>
-      </c>
-      <c r="Q86">
-        <v>0</v>
-      </c>
-      <c r="R86">
-        <v>0</v>
-      </c>
-      <c r="S86">
-        <v>90</v>
-      </c>
-      <c r="T86">
-        <v>2</v>
-      </c>
-      <c r="U86">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="271">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -85,33 +85,30 @@
     <t>BEBIDAS</t>
   </si>
   <si>
+    <t>MERCEARIA</t>
+  </si>
+  <si>
     <t>PERECIVEIS</t>
   </si>
   <si>
-    <t>MERCEARIA</t>
-  </si>
-  <si>
     <t>PERFUMARIA E LIMPEZA</t>
   </si>
   <si>
     <t>NICOLAS AUGUSTO P. BORGES</t>
   </si>
   <si>
+    <t>NIDAL TUBASI</t>
+  </si>
+  <si>
     <t>SANDRO MARTINS VIANNA</t>
   </si>
   <si>
-    <t>NIDAL TUBASI</t>
-  </si>
-  <si>
     <t>WETER SONNENFELDET</t>
   </si>
   <si>
     <t>JOAO BATISTA</t>
   </si>
   <si>
-    <t>001</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
@@ -133,6 +130,12 @@
     <t>008</t>
   </si>
   <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
     <t>013</t>
   </si>
   <si>
@@ -145,439 +148,685 @@
     <t>018</t>
   </si>
   <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>838</t>
+  </si>
+  <si>
+    <t>840</t>
+  </si>
+  <si>
+    <t>2074</t>
+  </si>
+  <si>
+    <t>6783</t>
+  </si>
+  <si>
+    <t>6801</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>746</t>
+  </si>
+  <si>
+    <t>1838</t>
+  </si>
+  <si>
+    <t>2046</t>
+  </si>
+  <si>
+    <t>2431</t>
+  </si>
+  <si>
+    <t>3872</t>
+  </si>
+  <si>
+    <t>6782</t>
+  </si>
+  <si>
+    <t>6790</t>
+  </si>
+  <si>
+    <t>6799</t>
+  </si>
+  <si>
+    <t>7872</t>
+  </si>
+  <si>
+    <t>17388</t>
+  </si>
+  <si>
+    <t>19802</t>
+  </si>
+  <si>
+    <t>9741</t>
+  </si>
+  <si>
+    <t>9745</t>
+  </si>
+  <si>
+    <t>9756</t>
+  </si>
+  <si>
+    <t>33833</t>
+  </si>
+  <si>
     <t>386</t>
   </si>
   <si>
-    <t>6783</t>
+    <t>2749</t>
+  </si>
+  <si>
+    <t>5857</t>
+  </si>
+  <si>
+    <t>37957</t>
+  </si>
+  <si>
+    <t>390</t>
   </si>
   <si>
     <t>6784</t>
   </si>
   <si>
+    <t>7817</t>
+  </si>
+  <si>
+    <t>1353</t>
+  </si>
+  <si>
+    <t>12228</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>7884</t>
+  </si>
+  <si>
+    <t>2232</t>
+  </si>
+  <si>
+    <t>3704</t>
+  </si>
+  <si>
+    <t>35687</t>
+  </si>
+  <si>
+    <t>942</t>
+  </si>
+  <si>
+    <t>1170</t>
+  </si>
+  <si>
+    <t>20317</t>
+  </si>
+  <si>
     <t>757</t>
   </si>
   <si>
-    <t>15762</t>
+    <t>2140</t>
+  </si>
+  <si>
+    <t>6276</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>2165</t>
+  </si>
+  <si>
+    <t>2351</t>
+  </si>
+  <si>
+    <t>2361</t>
   </si>
   <si>
     <t>15764</t>
   </si>
   <si>
+    <t>AGUA MIN SARANDI 5L S GAS</t>
+  </si>
+  <si>
+    <t>CERV STELLA ARTOIS LN 330ML</t>
+  </si>
+  <si>
+    <t>REFRIG FRUKI PET 3L GUARANA</t>
+  </si>
+  <si>
+    <t>REFRIG PEPSI PET 3L</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SANO TP1 1KG</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL C TAMPA 1L INTEGRAL</t>
+  </si>
+  <si>
+    <t>LEITE UHT TP NINHO 1L INTEGRAL</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML GREEN</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML MANGO LOCO</t>
+  </si>
+  <si>
+    <t>ACUCAR CRISTAL GASPARIN 1KG</t>
+  </si>
+  <si>
+    <t>PAST DOCILE ROLLY MINTY 29G HORTELA</t>
+  </si>
+  <si>
+    <t>ARROZ ARBOREO PILECCO 1KG</t>
+  </si>
+  <si>
+    <t>POPCORN YOKI 100G MANTEIGA CINEMA</t>
+  </si>
+  <si>
+    <t>CERV STELLA ARTOIS LT 473ML P GOLD</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL C TAMPA 1L DESN</t>
+  </si>
+  <si>
+    <t>LEITE UHT NINHO 1L ZERO LACTOSE</t>
+  </si>
+  <si>
+    <t>LEITE SANTA CLARA 1L ZERO LACTOSE</t>
+  </si>
+  <si>
+    <t>SABONETE DOVE 90G PROTEGE CUIDA</t>
+  </si>
+  <si>
+    <t>DET PO APYCE SH 4K AZUL</t>
+  </si>
+  <si>
+    <t>KIT SH CD PANTENE 300 150ML COLAGENO</t>
+  </si>
+  <si>
+    <t>LEITE SANTA CLARA LV SEMI DESN 1L</t>
+  </si>
+  <si>
+    <t>LEITE UHT SANTA CLARA DESN 1L</t>
+  </si>
+  <si>
+    <t>LEITE TIROL INTEGRAL ZR LACTOSE 1L</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL 1L BIO CICLOS</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML ABSOLUT ZERO</t>
+  </si>
+  <si>
+    <t>FARINHA TRIGO MARIA INES 5KG</t>
+  </si>
+  <si>
+    <t>ESC DENTAL SORRISO MACIA</t>
+  </si>
+  <si>
+    <t>CHA BARAO 13G PTO</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML GREEN ZERO</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL C TAMP 1L SEMI DESN</t>
+  </si>
+  <si>
+    <t>SABAO PO BRILHANTE 800G CX LIMPEZA TOTAL</t>
+  </si>
+  <si>
+    <t>CHOC BATON GAROTO 16G AO LEITE</t>
+  </si>
+  <si>
+    <t>ACUCAR CRISTAL DOCESUCAR 5KG</t>
+  </si>
+  <si>
+    <t>AGUARD KIKANA PET 790ML</t>
+  </si>
+  <si>
+    <t>SABONETE DOVE 90G PELE SENSIVEL</t>
+  </si>
+  <si>
+    <t>CAPSULA DOLCE GUSTO 117G C 10 CAPPUCCINO</t>
+  </si>
+  <si>
+    <t>MIST P BOLO APTI 400G CHOC</t>
+  </si>
+  <si>
+    <t>DESOD CREME SECRET CLEAR COTT 45G GEL</t>
+  </si>
+  <si>
+    <t>AZEITE OLIV BORGES EXT VG 500ML</t>
+  </si>
+  <si>
+    <t>BISC DOCE LEVIT 145G LEITE E CEREAIS</t>
+  </si>
+  <si>
+    <t>MACARRAO INST GERMANI 63G GALINHA CAIPIRA</t>
+  </si>
+  <si>
+    <t>ACUCAR CRISTAL SAO JOAO 1KG</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SANO TP1 5KG</t>
+  </si>
+  <si>
+    <t>AP VENUS INTIMA LV4 PG3</t>
+  </si>
+  <si>
+    <t>CERV ORIGINAL LT 473ML</t>
+  </si>
+  <si>
+    <t>ARROZ BCO PILECCO SUPER ECCO TP1 5K</t>
+  </si>
+  <si>
+    <t>FEIJAO PRETO CALDO OURO 1KG</t>
+  </si>
+  <si>
+    <t>FEIJAO VERMELHO ARBAZA 500G</t>
+  </si>
+  <si>
+    <t>CESTA BASICA MED</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>01/10/2024</t>
+  </si>
+  <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>03/12/2024</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>05/10/2024</t>
+  </si>
+  <si>
+    <t>17/10/2024</t>
+  </si>
+  <si>
+    <t>27/11/2024</t>
+  </si>
+  <si>
+    <t>02/12/2024</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
+  </si>
+  <si>
+    <t>14/12/2024</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>08/11/2024</t>
+  </si>
+  <si>
+    <t>07/10/2024</t>
+  </si>
+  <si>
+    <t>05/12/2024</t>
+  </si>
+  <si>
+    <t>31/12/2024</t>
+  </si>
+  <si>
+    <t>17/01/2026</t>
+  </si>
+  <si>
+    <t>24/10/2024</t>
+  </si>
+  <si>
+    <t>06/11/2024</t>
+  </si>
+  <si>
+    <t>04/12/2024</t>
+  </si>
+  <si>
+    <t>26/09/2024</t>
+  </si>
+  <si>
+    <t>07/12/2024</t>
+  </si>
+  <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>36</t>
   </si>
   <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>50</t>
   </si>
   <si>
-    <t>6799</t>
-  </si>
-  <si>
-    <t>33833</t>
-  </si>
-  <si>
-    <t>9745</t>
-  </si>
-  <si>
-    <t>9756</t>
-  </si>
-  <si>
-    <t>6790</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t>1745</t>
-  </si>
-  <si>
-    <t>2128</t>
-  </si>
-  <si>
-    <t>2140</t>
-  </si>
-  <si>
-    <t>6782</t>
-  </si>
-  <si>
-    <t>37957</t>
-  </si>
-  <si>
-    <t>838</t>
-  </si>
-  <si>
-    <t>12228</t>
-  </si>
-  <si>
-    <t>22639</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>1689</t>
-  </si>
-  <si>
-    <t>2737</t>
-  </si>
-  <si>
-    <t>4115</t>
-  </si>
-  <si>
-    <t>8838</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>2910</t>
-  </si>
-  <si>
-    <t>3281</t>
-  </si>
-  <si>
-    <t>3391</t>
-  </si>
-  <si>
-    <t>4178</t>
-  </si>
-  <si>
-    <t>4179</t>
-  </si>
-  <si>
-    <t>36681</t>
-  </si>
-  <si>
-    <t>39092</t>
-  </si>
-  <si>
-    <t>ENERG MONSTER LT 473ML ABSOLUT ZERO</t>
-  </si>
-  <si>
-    <t>LEITE UHT TIROL C TAMPA 1L INTEGRAL</t>
-  </si>
-  <si>
-    <t>LEITE UHT TIROL C TAMP 1L SEMI DESN</t>
-  </si>
-  <si>
-    <t>ACUCAR CRISTAL SAO JOAO 1KG</t>
-  </si>
-  <si>
-    <t>CESTA BASICA GRD</t>
-  </si>
-  <si>
-    <t>CESTA BASICA MED</t>
-  </si>
-  <si>
-    <t>AGUA MIN CRYSTAL PET 500ML C GAS</t>
-  </si>
-  <si>
-    <t>AGUA MIN DA PEDRA PET 5L S GAS</t>
-  </si>
-  <si>
-    <t>LEITE SANTA CLARA 1L ZERO LACTOSE</t>
-  </si>
-  <si>
-    <t>LEITE UHT TIROL 1L BIO CICLOS</t>
-  </si>
-  <si>
-    <t>LEITE UHT SANTA CLARA DESN 1L</t>
-  </si>
-  <si>
-    <t>LEITE TIROL INTEGRAL ZR LACTOSE 1L</t>
-  </si>
-  <si>
-    <t>LEITE UHT NINHO 1L ZERO LACTOSE</t>
-  </si>
-  <si>
-    <t>ENERG MONSTER LT 473ML GREEN</t>
-  </si>
-  <si>
-    <t>CHICLE FREEGELLS GUM 8G MENTA</t>
-  </si>
-  <si>
-    <t>ARROZ BCO PAMPEANO TP1 5KG</t>
-  </si>
-  <si>
-    <t>ARROZ BCO SANO TP1 5KG</t>
-  </si>
-  <si>
-    <t>LEITE UHT TIROL C TAMPA 1L DESN</t>
-  </si>
-  <si>
-    <t>CHA BARAO 13G PTO</t>
-  </si>
-  <si>
-    <t>REFRIG FRUKI PET 3L GUARANA</t>
-  </si>
-  <si>
-    <t>ACUCAR CRISTAL DOCESUCAR 5KG</t>
-  </si>
-  <si>
-    <t>QJO RAL SANTA CLARA 40G PARMESAO</t>
-  </si>
-  <si>
-    <t>BISC AGUA E SAL PARATI 740G</t>
-  </si>
-  <si>
-    <t>MARSHMALLOWS FOFS 220G BRUXOLITO PINTA</t>
-  </si>
-  <si>
-    <t>FARINHA TRIGO ROSESOL 1KG</t>
-  </si>
-  <si>
-    <t>ALVEJ GIRANDO SOL 2L S CLORO</t>
-  </si>
-  <si>
-    <t>AMAC AQUAFAST 2L ROSA JARD FLORI</t>
-  </si>
-  <si>
-    <t>AGUA MIN SARANDI 5L S GAS</t>
-  </si>
-  <si>
-    <t>MOLHO PIMENTA EXTREMO SABOR 250ML</t>
-  </si>
-  <si>
-    <t>GRANOLA NATURALE 250G CEREAIS FRUTAS</t>
-  </si>
-  <si>
-    <t>CALDO GALINHA MAGGI 114G</t>
-  </si>
-  <si>
-    <t>AMAC DOWNY 1 5L LIRIOS DO CAMPO</t>
-  </si>
-  <si>
-    <t>AMAC DOWNY 1 5L PRIMAVERA</t>
-  </si>
-  <si>
-    <t>CHANTILLY DAUS CLASSIC</t>
-  </si>
-  <si>
-    <t>KIT SEDA MEGA CRESC 300ML190ML</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>05/10/2024</t>
-  </si>
-  <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>17/10/2024</t>
-  </si>
-  <si>
-    <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>18/09/2024</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>28/08/2025</t>
-  </si>
-  <si>
-    <t>23/11/2024</t>
-  </si>
-  <si>
-    <t>04/12/2024</t>
-  </si>
-  <si>
-    <t>07/04/2026</t>
-  </si>
-  <si>
-    <t>21/10/2024</t>
-  </si>
-  <si>
-    <t>28/10/2024</t>
-  </si>
-  <si>
-    <t>21/11/2024</t>
-  </si>
-  <si>
-    <t>13/12/2024</t>
-  </si>
-  <si>
-    <t>17/12/2024</t>
-  </si>
-  <si>
-    <t>23/12/2024</t>
-  </si>
-  <si>
-    <t>26/12/2024</t>
-  </si>
-  <si>
-    <t>10/02/2026</t>
-  </si>
-  <si>
-    <t>03/08/2026</t>
-  </si>
-  <si>
-    <t>Ativo</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>4328</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>1387</t>
+    <t>279</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>1159</t>
+  </si>
+  <si>
+    <t>548</t>
+  </si>
+  <si>
+    <t>26032</t>
+  </si>
+  <si>
+    <t>1655</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>4085</t>
+  </si>
+  <si>
+    <t>2186</t>
+  </si>
+  <si>
+    <t>486</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>551</t>
+  </si>
+  <si>
+    <t>2149</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>48146</t>
+  </si>
+  <si>
+    <t>1452</t>
+  </si>
+  <si>
+    <t>1551</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>200</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>5687</t>
+    <t>697</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>931</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>561</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>1460</t>
+  </si>
+  <si>
+    <t>19890</t>
+  </si>
+  <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>658</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>681</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>30015</t>
+  </si>
+  <si>
+    <t>669</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>23034</t>
+  </si>
+  <si>
+    <t>582</t>
   </si>
   <si>
     <t>406</t>
   </si>
   <si>
-    <t>2919</t>
-  </si>
-  <si>
-    <t>1504</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>933</t>
-  </si>
-  <si>
-    <t>1280</t>
-  </si>
-  <si>
-    <t>383</t>
-  </si>
-  <si>
-    <t>946</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>661</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1854</t>
-  </si>
-  <si>
-    <t>1339</t>
-  </si>
-  <si>
-    <t>545</t>
-  </si>
-  <si>
-    <t>397</t>
-  </si>
-  <si>
-    <t>14796</t>
-  </si>
-  <si>
-    <t>333</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>23582</t>
-  </si>
-  <si>
-    <t>298</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
     <t>936</t>
   </si>
   <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>599</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>5375</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>3229</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>903</t>
-  </si>
-  <si>
-    <t>41</t>
+    <t>114</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>672</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>1390</t>
+  </si>
+  <si>
+    <t>62764</t>
+  </si>
+  <si>
+    <t>674</t>
+  </si>
+  <si>
+    <t>1962</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>744</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>527</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>962</t>
+  </si>
+  <si>
+    <t>2627</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>15433</t>
+  </si>
+  <si>
+    <t>911</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>704</t>
+  </si>
+  <si>
+    <t>773</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>2113</t>
+  </si>
+  <si>
+    <t>29610</t>
+  </si>
+  <si>
+    <t>842</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>979</t>
+  </si>
+  <si>
+    <t>2179</t>
+  </si>
+  <si>
+    <t>1650</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>5116</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>581</t>
+  </si>
+  <si>
+    <t>774</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -909,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V48"/>
+  <dimension ref="A1:V99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -991,28 +1240,28 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F2" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="G2" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="H2" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I2" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1024,13 +1273,13 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="P2">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="Q2">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -1042,45 +1291,45 @@
         <v>90</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V2">
-        <v>47</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
         <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="H3" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I3" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1092,13 +1341,13 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="P3">
-        <v>314</v>
+        <v>16</v>
       </c>
       <c r="Q3">
-        <v>494</v>
+        <v>40</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1110,45 +1359,45 @@
         <v>90</v>
       </c>
       <c r="U3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="V3">
-        <v>5103</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G4" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="H4" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I4" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="J4">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1160,13 +1409,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="P4">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="Q4">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1178,46 +1427,46 @@
         <v>90</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="V4">
-        <v>311</v>
+        <v>641</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H5" t="s">
+        <v>169</v>
+      </c>
+      <c r="I5" t="s">
+        <v>170</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
         <v>81</v>
       </c>
-      <c r="F5" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" t="s">
-        <v>117</v>
-      </c>
-      <c r="H5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I5" t="s">
-        <v>137</v>
-      </c>
-      <c r="J5">
-        <v>30</v>
-      </c>
-      <c r="K5">
-        <v>84</v>
-      </c>
       <c r="L5">
         <v>0</v>
       </c>
@@ -1228,13 +1477,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="P5">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1246,46 +1495,46 @@
         <v>90</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="V5">
-        <v>25</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I6" t="s">
+        <v>172</v>
+      </c>
+      <c r="J6">
+        <v>30</v>
+      </c>
+      <c r="K6">
         <v>118</v>
       </c>
-      <c r="H6" t="s">
-        <v>134</v>
-      </c>
-      <c r="I6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
       <c r="L6">
         <v>0</v>
       </c>
@@ -1296,13 +1545,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="P6">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="Q6">
-        <v>10</v>
+        <v>192</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1314,10 +1563,10 @@
         <v>90</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>14</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1328,99 +1577,99 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I7" t="s">
+        <v>173</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>1669</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>187</v>
+      </c>
+      <c r="P7">
+        <v>1724</v>
+      </c>
+      <c r="Q7">
+        <v>2660</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>90</v>
+      </c>
+      <c r="U7">
         <v>83</v>
       </c>
-      <c r="F7" t="s">
-        <v>114</v>
-      </c>
-      <c r="G7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H7" t="s">
-        <v>134</v>
-      </c>
-      <c r="I7" t="s">
-        <v>138</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>150</v>
-      </c>
-      <c r="P7">
-        <v>7</v>
-      </c>
-      <c r="Q7">
-        <v>10</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>90</v>
-      </c>
-      <c r="U7">
-        <v>10</v>
-      </c>
       <c r="V7">
-        <v>109</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G8" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="H8" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I8" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="J8">
         <v>12</v>
       </c>
       <c r="K8">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1432,28 +1681,28 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>151</v>
+        <v>53</v>
       </c>
       <c r="P8">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="Q8">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="R8">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1308</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <v>90</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V8">
-        <v>248.92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1464,31 +1713,31 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="G9" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="H9" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I9" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1500,13 +1749,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
+        <v>188</v>
+      </c>
+      <c r="P9">
         <v>152</v>
       </c>
-      <c r="P9">
-        <v>72</v>
-      </c>
       <c r="Q9">
-        <v>96</v>
+        <v>236</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1518,45 +1767,45 @@
         <v>90</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V9">
-        <v>612</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="G10" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="H10" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I10" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="J10">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>195</v>
+        <v>34</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1568,13 +1817,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="P10">
-        <v>208</v>
+        <v>42</v>
       </c>
       <c r="Q10">
-        <v>328</v>
+        <v>54</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1586,10 +1835,10 @@
         <v>90</v>
       </c>
       <c r="U10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="V10">
-        <v>311</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1600,31 +1849,31 @@
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G11" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="H11" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I11" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="J11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>106</v>
+        <v>244</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1636,13 +1885,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="P11">
-        <v>120</v>
+        <v>254</v>
       </c>
       <c r="Q11">
-        <v>144</v>
+        <v>384</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1654,45 +1903,45 @@
         <v>90</v>
       </c>
       <c r="U11">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G12" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="H12" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I12" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="J12">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1704,13 +1953,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="P12">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="Q12">
-        <v>72</v>
+        <v>282</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1722,10 +1971,10 @@
         <v>90</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="V12">
-        <v>18</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1733,34 +1982,34 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G13" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="H13" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I13" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="J13">
         <v>12</v>
       </c>
       <c r="K13">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1772,13 +2021,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="P13">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="Q13">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1790,10 +2039,10 @@
         <v>90</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V13">
-        <v>311</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1804,49 +2053,49 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G14" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="H14" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I14" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="P14">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="Q14">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -1858,10 +2107,10 @@
         <v>90</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1872,117 +2121,117 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="F15" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G15" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="H15" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I15" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="J15">
+        <v>36</v>
+      </c>
+      <c r="K15">
+        <v>127</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>194</v>
+      </c>
+      <c r="P15">
+        <v>132</v>
+      </c>
+      <c r="Q15">
+        <v>204</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>90</v>
+      </c>
+      <c r="U15">
+        <v>3</v>
+      </c>
+      <c r="V15">
         <v>12</v>
-      </c>
-      <c r="K15">
-        <v>-1</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>158</v>
-      </c>
-      <c r="P15">
-        <v>72</v>
-      </c>
-      <c r="Q15">
-        <v>96</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>90</v>
-      </c>
-      <c r="U15">
-        <v>8</v>
-      </c>
-      <c r="V15">
-        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="F16" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G16" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="H16" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I16" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
       <c r="K16">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="P16">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="Q16">
-        <v>180</v>
+        <v>274</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -1994,45 +2243,45 @@
         <v>90</v>
       </c>
       <c r="U16">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="V16">
-        <v>98</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="F17" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="H17" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I17" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="J17">
         <v>12</v>
       </c>
       <c r="K17">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2044,13 +2293,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="P17">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="Q17">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2062,45 +2311,45 @@
         <v>90</v>
       </c>
       <c r="U17">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>29</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F18" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="G18" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="H18" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I18" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K18">
-        <v>51</v>
+        <v>2648</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2112,13 +2361,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="P18">
-        <v>60</v>
+        <v>3344</v>
       </c>
       <c r="Q18">
-        <v>84</v>
+        <v>5156</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -2130,10 +2379,10 @@
         <v>90</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="V18">
-        <v>80.5</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2141,34 +2390,34 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="F19" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G19" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="H19" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I19" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="J19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K19">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2180,14 +2429,14 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
+        <v>198</v>
+      </c>
+      <c r="P19">
+        <v>102</v>
+      </c>
+      <c r="Q19">
         <v>162</v>
       </c>
-      <c r="P19">
-        <v>9</v>
-      </c>
-      <c r="Q19">
-        <v>24</v>
-      </c>
       <c r="R19">
         <v>0</v>
       </c>
@@ -2198,7 +2447,7 @@
         <v>90</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>27</v>
@@ -2212,49 +2461,49 @@
         <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G20" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="H20" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I20" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="J20">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K20">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="P20">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="Q20">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -2266,45 +2515,45 @@
         <v>90</v>
       </c>
       <c r="U20">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="V20">
-        <v>1266</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F21" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="H21" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I21" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="K21">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -2316,13 +2565,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="P21">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="Q21">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -2334,64 +2583,64 @@
         <v>90</v>
       </c>
       <c r="U21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V21">
-        <v>298</v>
+        <v>90.12</v>
       </c>
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="F22" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="H22" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I22" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="J22">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
+        <v>5</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>201</v>
+      </c>
+      <c r="P22">
+        <v>19</v>
+      </c>
+      <c r="Q22">
         <v>24</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>165</v>
-      </c>
-      <c r="P22">
-        <v>36</v>
-      </c>
-      <c r="Q22">
-        <v>48</v>
-      </c>
       <c r="R22">
         <v>0</v>
       </c>
@@ -2402,63 +2651,63 @@
         <v>90</v>
       </c>
       <c r="U22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V22">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E23" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="F23" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G23" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="H23" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I23" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="J23">
+        <v>6</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>12</v>
       </c>
-      <c r="K23">
-        <v>23</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="P23">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Q23">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -2470,7 +2719,7 @@
         <v>90</v>
       </c>
       <c r="U23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2478,37 +2727,37 @@
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E24" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G24" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="H24" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I24" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="J24">
         <v>12</v>
       </c>
       <c r="K24">
-        <v>792</v>
+        <v>57</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -2520,13 +2769,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="P24">
-        <v>984</v>
+        <v>60</v>
       </c>
       <c r="Q24">
-        <v>1524</v>
+        <v>72</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2538,45 +2787,45 @@
         <v>90</v>
       </c>
       <c r="U24">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="V24">
-        <v>5103</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E25" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="F25" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G25" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="H25" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I25" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="J25">
         <v>12</v>
       </c>
       <c r="K25">
-        <v>15</v>
+        <v>-1</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2588,13 +2837,13 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="P25">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="Q25">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2606,10 +2855,10 @@
         <v>90</v>
       </c>
       <c r="U25">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2620,31 +2869,31 @@
         <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="F26" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="G26" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="H26" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I26" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="J26">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K26">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2656,13 +2905,13 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="P26">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="Q26">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -2674,45 +2923,45 @@
         <v>90</v>
       </c>
       <c r="U26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>115.17</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="F27" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G27" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="H27" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I27" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="J27">
         <v>12</v>
       </c>
       <c r="K27">
-        <v>1340</v>
+        <v>35</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2724,13 +2973,13 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="P27">
-        <v>1584</v>
+        <v>36</v>
       </c>
       <c r="Q27">
-        <v>2448</v>
+        <v>48</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -2742,45 +2991,45 @@
         <v>90</v>
       </c>
       <c r="U27">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="V27">
-        <v>5103</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E28" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="G28" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="H28" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I28" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="J28">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2792,13 +3041,13 @@
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="P28">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="Q28">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -2810,10 +3059,10 @@
         <v>90</v>
       </c>
       <c r="U28">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>311</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2824,31 +3073,31 @@
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F29" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="G29" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="H29" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I29" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2860,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="P29">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Q29">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -2878,10 +3127,10 @@
         <v>90</v>
       </c>
       <c r="U29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V29">
-        <v>702</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2892,31 +3141,31 @@
         <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G30" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="H30" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I30" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="J30">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2928,13 +3177,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="P30">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -2946,64 +3195,64 @@
         <v>90</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" t="s">
+        <v>104</v>
+      </c>
+      <c r="F31" t="s">
+        <v>142</v>
+      </c>
+      <c r="G31" t="s">
+        <v>152</v>
+      </c>
+      <c r="H31" t="s">
+        <v>169</v>
+      </c>
+      <c r="I31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31">
+        <v>10</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>10</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>202</v>
+      </c>
+      <c r="P31">
+        <v>14</v>
+      </c>
+      <c r="Q31">
         <v>24</v>
       </c>
-      <c r="B31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" t="s">
-        <v>98</v>
-      </c>
-      <c r="F31" t="s">
-        <v>114</v>
-      </c>
-      <c r="G31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H31" t="s">
-        <v>134</v>
-      </c>
-      <c r="I31" t="s">
-        <v>135</v>
-      </c>
-      <c r="J31">
-        <v>6</v>
-      </c>
-      <c r="K31">
-        <v>87</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>174</v>
-      </c>
-      <c r="P31">
-        <v>96</v>
-      </c>
-      <c r="Q31">
-        <v>120</v>
-      </c>
       <c r="R31">
         <v>0</v>
       </c>
@@ -3014,10 +3263,10 @@
         <v>90</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V31">
-        <v>1320</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3025,34 +3274,34 @@
         <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F32" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G32" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="H32" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I32" t="s">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="J32">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K32">
-        <v>28</v>
+        <v>902</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -3064,13 +3313,13 @@
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="P32">
-        <v>31</v>
+        <v>1284</v>
       </c>
       <c r="Q32">
-        <v>56</v>
+        <v>1980</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -3082,63 +3331,63 @@
         <v>90</v>
       </c>
       <c r="U32">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="V32">
-        <v>52</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" t="s">
+        <v>142</v>
+      </c>
+      <c r="G33" t="s">
+        <v>148</v>
+      </c>
+      <c r="H33" t="s">
+        <v>169</v>
+      </c>
+      <c r="I33" t="s">
+        <v>173</v>
+      </c>
+      <c r="J33">
+        <v>12</v>
+      </c>
+      <c r="K33">
+        <v>21</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>211</v>
+      </c>
+      <c r="P33">
         <v>26</v>
       </c>
-      <c r="C33" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" t="s">
-        <v>91</v>
-      </c>
-      <c r="F33" t="s">
-        <v>113</v>
-      </c>
-      <c r="G33" t="s">
-        <v>115</v>
-      </c>
-      <c r="H33" t="s">
-        <v>134</v>
-      </c>
-      <c r="I33" t="s">
-        <v>135</v>
-      </c>
-      <c r="J33">
-        <v>6</v>
-      </c>
-      <c r="K33">
-        <v>34</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
-        <v>176</v>
-      </c>
-      <c r="P33">
-        <v>40</v>
-      </c>
       <c r="Q33">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -3150,10 +3399,10 @@
         <v>90</v>
       </c>
       <c r="U33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V33">
-        <v>80.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -3161,34 +3410,34 @@
         <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F34" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="H34" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I34" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="J34">
         <v>12</v>
       </c>
       <c r="K34">
-        <v>283</v>
+        <v>34</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -3200,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="P34">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="Q34">
-        <v>478</v>
+        <v>72</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -3218,45 +3467,45 @@
         <v>90</v>
       </c>
       <c r="U34">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="V34">
-        <v>51</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E35" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F35" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="G35" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="H35" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I35" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="J35">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3268,13 +3517,13 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="P35">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="Q35">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -3286,45 +3535,45 @@
         <v>90</v>
       </c>
       <c r="U35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V35">
-        <v>36.17</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F36" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="G36" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="H36" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I36" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="J36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>162</v>
+        <v>16</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3333,16 +3582,16 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O36" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="P36">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="Q36">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -3354,63 +3603,63 @@
         <v>90</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V36">
-        <v>132</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F37" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G37" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="H37" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I37" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="J37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K37">
+        <v>17</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
         <v>10</v>
       </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
       <c r="N37">
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="P37">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q37">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -3425,42 +3674,42 @@
         <v>3</v>
       </c>
       <c r="V37">
-        <v>12</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
         <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="F38" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G38" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="H38" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I38" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="J38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -3472,13 +3721,13 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="P38">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="Q38">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -3490,45 +3739,45 @@
         <v>90</v>
       </c>
       <c r="U38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V38">
-        <v>74</v>
+        <v>232.8</v>
       </c>
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
         <v>70</v>
       </c>
       <c r="E39" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="F39" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="G39" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="H39" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I39" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="J39">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K39">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -3540,14 +3789,14 @@
         <v>0</v>
       </c>
       <c r="O39" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="P39">
+        <v>10</v>
+      </c>
+      <c r="Q39">
         <v>22</v>
       </c>
-      <c r="Q39">
-        <v>34</v>
-      </c>
       <c r="R39">
         <v>0</v>
       </c>
@@ -3558,10 +3807,10 @@
         <v>90</v>
       </c>
       <c r="U39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V39">
-        <v>389</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3572,31 +3821,31 @@
         <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="E40" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F40" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G40" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="H40" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I40" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="J40">
         <v>12</v>
       </c>
       <c r="K40">
-        <v>7</v>
+        <v>1729</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -3605,16 +3854,16 @@
         <v>0</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="O40" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="P40">
-        <v>10</v>
+        <v>2112</v>
       </c>
       <c r="Q40">
-        <v>22</v>
+        <v>3252</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -3626,10 +3875,10 @@
         <v>90</v>
       </c>
       <c r="U40">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="V40">
-        <v>14.67</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3637,53 +3886,53 @@
         <v>24</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" t="s">
+        <v>109</v>
+      </c>
+      <c r="F41" t="s">
+        <v>142</v>
+      </c>
+      <c r="G41" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" t="s">
+        <v>169</v>
+      </c>
+      <c r="I41" t="s">
+        <v>173</v>
+      </c>
+      <c r="J41">
+        <v>12</v>
+      </c>
+      <c r="K41">
+        <v>38</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>218</v>
+      </c>
+      <c r="P41">
+        <v>60</v>
+      </c>
+      <c r="Q41">
         <v>72</v>
       </c>
-      <c r="E41" t="s">
-        <v>107</v>
-      </c>
-      <c r="F41" t="s">
-        <v>114</v>
-      </c>
-      <c r="G41" t="s">
-        <v>130</v>
-      </c>
-      <c r="H41" t="s">
-        <v>134</v>
-      </c>
-      <c r="I41" t="s">
-        <v>143</v>
-      </c>
-      <c r="J41">
-        <v>18</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41" t="s">
-        <v>143</v>
-      </c>
-      <c r="P41">
-        <v>14</v>
-      </c>
-      <c r="Q41">
-        <v>32</v>
-      </c>
       <c r="R41">
         <v>0</v>
       </c>
@@ -3694,63 +3943,63 @@
         <v>90</v>
       </c>
       <c r="U41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D42" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E42" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F42" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G42" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="H42" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I42" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="J42">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N42">
         <v>0</v>
       </c>
       <c r="O42" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P42">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="Q42">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -3765,110 +4014,110 @@
         <v>2</v>
       </c>
       <c r="V42">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" t="s">
+        <v>143</v>
+      </c>
+      <c r="G43" t="s">
+        <v>158</v>
+      </c>
+      <c r="H43" t="s">
+        <v>169</v>
+      </c>
+      <c r="I43" t="s">
+        <v>172</v>
+      </c>
+      <c r="J43">
         <v>30</v>
       </c>
-      <c r="C43" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43" t="s">
-        <v>74</v>
-      </c>
-      <c r="E43" t="s">
-        <v>109</v>
-      </c>
-      <c r="F43" t="s">
-        <v>114</v>
-      </c>
-      <c r="G43" t="s">
-        <v>116</v>
-      </c>
-      <c r="H43" t="s">
-        <v>134</v>
-      </c>
-      <c r="I43" t="s">
-        <v>145</v>
-      </c>
-      <c r="J43">
+      <c r="K43">
+        <v>8</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>219</v>
+      </c>
+      <c r="P43">
+        <v>18</v>
+      </c>
+      <c r="Q43">
+        <v>48</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>90</v>
+      </c>
+      <c r="U43">
+        <v>2</v>
+      </c>
+      <c r="V43">
         <v>9</v>
-      </c>
-      <c r="K43">
-        <v>2</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43" t="s">
-        <v>185</v>
-      </c>
-      <c r="P43">
-        <v>13</v>
-      </c>
-      <c r="Q43">
-        <v>22</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>90</v>
-      </c>
-      <c r="U43">
-        <v>3</v>
-      </c>
-      <c r="V43">
-        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E44" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F44" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="G44" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="H44" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I44" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="J44">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K44">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -3880,13 +4129,13 @@
         <v>0</v>
       </c>
       <c r="O44" t="s">
-        <v>136</v>
+        <v>220</v>
       </c>
       <c r="P44">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q44">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -3901,42 +4150,42 @@
         <v>2</v>
       </c>
       <c r="V44">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E45" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="F45" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="G45" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="H45" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I45" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="J45">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K45">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -3948,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="P45">
         <v>60</v>
@@ -3966,10 +4215,10 @@
         <v>90</v>
       </c>
       <c r="U45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V45">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3980,31 +4229,31 @@
         <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E46" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="F46" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G46" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="H46" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I46" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K46">
-        <v>4</v>
+        <v>989</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4016,13 +4265,13 @@
         <v>0</v>
       </c>
       <c r="O46" t="s">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="P46">
-        <v>7</v>
+        <v>1512</v>
       </c>
       <c r="Q46">
-        <v>10</v>
+        <v>2328</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -4034,10 +4283,10 @@
         <v>90</v>
       </c>
       <c r="U46">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="V46">
-        <v>109</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -4045,34 +4294,34 @@
         <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E47" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F47" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="G47" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="H47" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I47" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="J47">
         <v>12</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -4084,13 +4333,13 @@
         <v>0</v>
       </c>
       <c r="O47" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="P47">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="Q47">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -4102,78 +4351,3546 @@
         <v>90</v>
       </c>
       <c r="U47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V47">
-        <v>155</v>
+        <v>280</v>
       </c>
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" t="s">
+        <v>36</v>
+      </c>
+      <c r="D48" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F48" t="s">
+        <v>142</v>
+      </c>
+      <c r="G48" t="s">
+        <v>148</v>
+      </c>
+      <c r="H48" t="s">
+        <v>169</v>
+      </c>
+      <c r="I48" t="s">
+        <v>173</v>
+      </c>
+      <c r="J48">
+        <v>12</v>
+      </c>
+      <c r="K48">
+        <v>12</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>223</v>
+      </c>
+      <c r="P48">
+        <v>32</v>
+      </c>
+      <c r="Q48">
+        <v>56</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>90</v>
+      </c>
+      <c r="U48">
+        <v>4</v>
+      </c>
+      <c r="V48">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22">
+      <c r="A49" t="s">
         <v>25</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>30</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" t="s">
+        <v>74</v>
+      </c>
+      <c r="E49" t="s">
+        <v>123</v>
+      </c>
+      <c r="F49" t="s">
+        <v>142</v>
+      </c>
+      <c r="G49" t="s">
+        <v>148</v>
+      </c>
+      <c r="H49" t="s">
+        <v>169</v>
+      </c>
+      <c r="I49" t="s">
+        <v>179</v>
+      </c>
+      <c r="J49">
+        <v>20</v>
+      </c>
+      <c r="K49">
+        <v>105</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" t="s">
+        <v>224</v>
+      </c>
+      <c r="P49">
+        <v>106</v>
+      </c>
+      <c r="Q49">
+        <v>166</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>90</v>
+      </c>
+      <c r="U49">
+        <v>4</v>
+      </c>
+      <c r="V49">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22">
+      <c r="A50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" t="s">
+        <v>120</v>
+      </c>
+      <c r="F50" t="s">
+        <v>143</v>
+      </c>
+      <c r="G50" t="s">
+        <v>158</v>
+      </c>
+      <c r="H50" t="s">
+        <v>169</v>
+      </c>
+      <c r="I50" t="s">
+        <v>172</v>
+      </c>
+      <c r="J50">
+        <v>30</v>
+      </c>
+      <c r="K50">
+        <v>6</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50" t="s">
+        <v>225</v>
+      </c>
+      <c r="P50">
+        <v>18</v>
+      </c>
+      <c r="Q50">
+        <v>48</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>90</v>
+      </c>
+      <c r="U50">
+        <v>2</v>
+      </c>
+      <c r="V50">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22">
+      <c r="A51" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" t="s">
+        <v>124</v>
+      </c>
+      <c r="F51" t="s">
+        <v>142</v>
+      </c>
+      <c r="G51" t="s">
+        <v>159</v>
+      </c>
+      <c r="H51" t="s">
+        <v>169</v>
+      </c>
+      <c r="I51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J51">
+        <v>30</v>
+      </c>
+      <c r="K51">
+        <v>12</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51" t="s">
+        <v>226</v>
+      </c>
+      <c r="P51">
+        <v>22</v>
+      </c>
+      <c r="Q51">
+        <v>52</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>90</v>
+      </c>
+      <c r="U51">
+        <v>2</v>
+      </c>
+      <c r="V51">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22">
+      <c r="A52" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" t="s">
+        <v>37</v>
+      </c>
+      <c r="D52" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" t="s">
+        <v>107</v>
+      </c>
+      <c r="F52" t="s">
+        <v>142</v>
+      </c>
+      <c r="G52" t="s">
+        <v>148</v>
+      </c>
+      <c r="H52" t="s">
+        <v>169</v>
+      </c>
+      <c r="I52" t="s">
+        <v>173</v>
+      </c>
+      <c r="J52">
+        <v>12</v>
+      </c>
+      <c r="K52">
+        <v>44</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52" t="s">
+        <v>227</v>
+      </c>
+      <c r="P52">
+        <v>50</v>
+      </c>
+      <c r="Q52">
+        <v>86</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>90</v>
+      </c>
+      <c r="U52">
+        <v>4</v>
+      </c>
+      <c r="V52">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22">
+      <c r="A53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" t="s">
+        <v>122</v>
+      </c>
+      <c r="F53" t="s">
+        <v>142</v>
+      </c>
+      <c r="G53" t="s">
+        <v>148</v>
+      </c>
+      <c r="H53" t="s">
+        <v>169</v>
+      </c>
+      <c r="I53" t="s">
+        <v>173</v>
+      </c>
+      <c r="J53">
+        <v>12</v>
+      </c>
+      <c r="K53">
+        <v>26</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53" t="s">
+        <v>228</v>
+      </c>
+      <c r="P53">
+        <v>36</v>
+      </c>
+      <c r="Q53">
+        <v>48</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>90</v>
+      </c>
+      <c r="U53">
+        <v>2</v>
+      </c>
+      <c r="V53">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22">
+      <c r="A54" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" t="s">
+        <v>109</v>
+      </c>
+      <c r="F54" t="s">
+        <v>142</v>
+      </c>
+      <c r="G54" t="s">
+        <v>148</v>
+      </c>
+      <c r="H54" t="s">
+        <v>169</v>
+      </c>
+      <c r="I54" t="s">
+        <v>173</v>
+      </c>
+      <c r="J54">
+        <v>12</v>
+      </c>
+      <c r="K54">
+        <v>5</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54" t="s">
+        <v>229</v>
+      </c>
+      <c r="P54">
+        <v>22</v>
+      </c>
+      <c r="Q54">
+        <v>34</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>90</v>
+      </c>
+      <c r="U54">
+        <v>3</v>
+      </c>
+      <c r="V54">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22">
+      <c r="A55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" t="s">
+        <v>76</v>
+      </c>
+      <c r="E55" t="s">
+        <v>125</v>
+      </c>
+      <c r="F55" t="s">
+        <v>142</v>
+      </c>
+      <c r="G55" t="s">
+        <v>155</v>
+      </c>
+      <c r="H55" t="s">
+        <v>169</v>
+      </c>
+      <c r="I55" t="s">
+        <v>174</v>
+      </c>
+      <c r="J55">
+        <v>6</v>
+      </c>
+      <c r="K55">
+        <v>43</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55" t="s">
+        <v>230</v>
+      </c>
+      <c r="P55">
+        <v>120</v>
+      </c>
+      <c r="Q55">
+        <v>180</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>90</v>
+      </c>
+      <c r="U55">
+        <v>23</v>
+      </c>
+      <c r="V55">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22">
+      <c r="A56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>38</v>
+      </c>
+      <c r="D56" t="s">
+        <v>51</v>
+      </c>
+      <c r="E56" t="s">
+        <v>100</v>
+      </c>
+      <c r="F56" t="s">
+        <v>143</v>
+      </c>
+      <c r="G56" t="s">
+        <v>149</v>
+      </c>
+      <c r="H56" t="s">
+        <v>169</v>
+      </c>
+      <c r="I56" t="s">
+        <v>174</v>
+      </c>
+      <c r="J56">
+        <v>6</v>
+      </c>
+      <c r="K56">
+        <v>47</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>6</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56" t="s">
+        <v>229</v>
+      </c>
+      <c r="P56">
+        <v>54</v>
+      </c>
+      <c r="Q56">
+        <v>84</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>90</v>
+      </c>
+      <c r="U56">
+        <v>6</v>
+      </c>
+      <c r="V56">
+        <v>70.33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22">
+      <c r="A57" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" t="s">
+        <v>126</v>
+      </c>
+      <c r="F57" t="s">
+        <v>142</v>
+      </c>
+      <c r="G57" t="s">
+        <v>160</v>
+      </c>
+      <c r="H57" t="s">
+        <v>169</v>
+      </c>
+      <c r="I57" t="s">
+        <v>173</v>
+      </c>
+      <c r="J57">
+        <v>12</v>
+      </c>
+      <c r="K57">
+        <v>34</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57" t="s">
+        <v>231</v>
+      </c>
+      <c r="P57">
+        <v>36</v>
+      </c>
+      <c r="Q57">
+        <v>60</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>90</v>
+      </c>
+      <c r="U57">
+        <v>3</v>
+      </c>
+      <c r="V57">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22">
+      <c r="A58" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" t="s">
+        <v>38</v>
+      </c>
+      <c r="D58" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" t="s">
+        <v>107</v>
+      </c>
+      <c r="F58" t="s">
+        <v>142</v>
+      </c>
+      <c r="G58" t="s">
+        <v>148</v>
+      </c>
+      <c r="H58" t="s">
+        <v>169</v>
+      </c>
+      <c r="I58" t="s">
+        <v>173</v>
+      </c>
+      <c r="J58">
+        <v>12</v>
+      </c>
+      <c r="K58">
+        <v>72</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58" t="s">
+        <v>232</v>
+      </c>
+      <c r="P58">
+        <v>92</v>
+      </c>
+      <c r="Q58">
+        <v>152</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>90</v>
+      </c>
+      <c r="U58">
+        <v>7</v>
+      </c>
+      <c r="V58">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22">
+      <c r="A59" t="s">
+        <v>24</v>
+      </c>
+      <c r="B59" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" t="s">
+        <v>38</v>
+      </c>
+      <c r="D59" t="s">
+        <v>49</v>
+      </c>
+      <c r="E59" t="s">
+        <v>98</v>
+      </c>
+      <c r="F59" t="s">
+        <v>142</v>
+      </c>
+      <c r="G59" t="s">
+        <v>148</v>
+      </c>
+      <c r="H59" t="s">
+        <v>169</v>
+      </c>
+      <c r="I59" t="s">
+        <v>173</v>
+      </c>
+      <c r="J59">
+        <v>12</v>
+      </c>
+      <c r="K59">
+        <v>2695</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>396</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59" t="s">
+        <v>233</v>
+      </c>
+      <c r="P59">
+        <v>4112</v>
+      </c>
+      <c r="Q59">
+        <v>6332</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>90</v>
+      </c>
+      <c r="U59">
+        <v>271</v>
+      </c>
+      <c r="V59">
+        <v>4930</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22">
+      <c r="A60" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" t="s">
+        <v>122</v>
+      </c>
+      <c r="F60" t="s">
+        <v>142</v>
+      </c>
+      <c r="G60" t="s">
+        <v>148</v>
+      </c>
+      <c r="H60" t="s">
+        <v>169</v>
+      </c>
+      <c r="I60" t="s">
+        <v>173</v>
+      </c>
+      <c r="J60">
+        <v>12</v>
+      </c>
+      <c r="K60">
+        <v>28</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60" t="s">
+        <v>234</v>
+      </c>
+      <c r="P60">
+        <v>50</v>
+      </c>
+      <c r="Q60">
+        <v>86</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>90</v>
+      </c>
+      <c r="U60">
+        <v>5</v>
+      </c>
+      <c r="V60">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22">
+      <c r="A61" t="s">
+        <v>24</v>
+      </c>
+      <c r="B61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" t="s">
+        <v>38</v>
+      </c>
+      <c r="D61" t="s">
+        <v>50</v>
+      </c>
+      <c r="E61" t="s">
+        <v>99</v>
+      </c>
+      <c r="F61" t="s">
+        <v>142</v>
+      </c>
+      <c r="G61" t="s">
+        <v>148</v>
+      </c>
+      <c r="H61" t="s">
+        <v>169</v>
+      </c>
+      <c r="I61" t="s">
+        <v>173</v>
+      </c>
+      <c r="J61">
+        <v>12</v>
+      </c>
+      <c r="K61">
+        <v>111</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61" t="s">
+        <v>235</v>
+      </c>
+      <c r="P61">
+        <v>132</v>
+      </c>
+      <c r="Q61">
+        <v>204</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>90</v>
+      </c>
+      <c r="U61">
+        <v>8</v>
+      </c>
+      <c r="V61">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" t="s">
+        <v>38</v>
+      </c>
+      <c r="D62" t="s">
+        <v>78</v>
+      </c>
+      <c r="E62" t="s">
+        <v>127</v>
+      </c>
+      <c r="F62" t="s">
+        <v>143</v>
+      </c>
+      <c r="G62" t="s">
+        <v>148</v>
+      </c>
+      <c r="H62" t="s">
+        <v>169</v>
+      </c>
+      <c r="I62" t="s">
+        <v>177</v>
+      </c>
+      <c r="J62">
+        <v>48</v>
+      </c>
+      <c r="K62">
+        <v>29</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62" t="s">
+        <v>236</v>
+      </c>
+      <c r="P62">
+        <v>30</v>
+      </c>
+      <c r="Q62">
+        <v>78</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>90</v>
+      </c>
+      <c r="U62">
+        <v>2</v>
+      </c>
+      <c r="V62">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22">
+      <c r="A63" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>39</v>
+      </c>
+      <c r="D63" t="s">
+        <v>44</v>
+      </c>
+      <c r="E63" t="s">
+        <v>93</v>
+      </c>
+      <c r="F63" t="s">
+        <v>142</v>
+      </c>
+      <c r="G63" t="s">
+        <v>144</v>
+      </c>
+      <c r="H63" t="s">
+        <v>169</v>
+      </c>
+      <c r="I63" t="s">
+        <v>170</v>
+      </c>
+      <c r="J63">
+        <v>4</v>
+      </c>
+      <c r="K63">
+        <v>26</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63" t="s">
+        <v>237</v>
+      </c>
+      <c r="P63">
+        <v>32</v>
+      </c>
+      <c r="Q63">
+        <v>52</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>90</v>
+      </c>
+      <c r="U63">
+        <v>7</v>
+      </c>
+      <c r="V63">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22">
+      <c r="A64" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" t="s">
+        <v>51</v>
+      </c>
+      <c r="E64" t="s">
+        <v>100</v>
+      </c>
+      <c r="F64" t="s">
+        <v>143</v>
+      </c>
+      <c r="G64" t="s">
+        <v>149</v>
+      </c>
+      <c r="H64" t="s">
+        <v>169</v>
+      </c>
+      <c r="I64" t="s">
+        <v>174</v>
+      </c>
+      <c r="J64">
+        <v>6</v>
+      </c>
+      <c r="K64">
+        <v>29</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64" t="s">
+        <v>238</v>
+      </c>
+      <c r="P64">
         <v>42</v>
       </c>
-      <c r="D48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="Q64">
+        <v>54</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>90</v>
+      </c>
+      <c r="U64">
+        <v>5</v>
+      </c>
+      <c r="V64">
+        <v>70.33</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22">
+      <c r="A65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B65" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" t="s">
+        <v>39</v>
+      </c>
+      <c r="D65" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" t="s">
+        <v>107</v>
+      </c>
+      <c r="F65" t="s">
+        <v>142</v>
+      </c>
+      <c r="G65" t="s">
+        <v>148</v>
+      </c>
+      <c r="H65" t="s">
+        <v>169</v>
+      </c>
+      <c r="I65" t="s">
+        <v>173</v>
+      </c>
+      <c r="J65">
+        <v>12</v>
+      </c>
+      <c r="K65">
+        <v>32</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65" t="s">
+        <v>239</v>
+      </c>
+      <c r="P65">
+        <v>44</v>
+      </c>
+      <c r="Q65">
+        <v>68</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>90</v>
+      </c>
+      <c r="U65">
+        <v>3</v>
+      </c>
+      <c r="V65">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22">
+      <c r="A66" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" t="s">
+        <v>40</v>
+      </c>
+      <c r="D66" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66" t="s">
+        <v>117</v>
+      </c>
+      <c r="F66" t="s">
+        <v>143</v>
+      </c>
+      <c r="G66" t="s">
+        <v>149</v>
+      </c>
+      <c r="H66" t="s">
+        <v>169</v>
+      </c>
+      <c r="I66" t="s">
+        <v>174</v>
+      </c>
+      <c r="J66">
+        <v>6</v>
+      </c>
+      <c r="K66">
+        <v>10</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66" t="s">
+        <v>240</v>
+      </c>
+      <c r="P66">
+        <v>14</v>
+      </c>
+      <c r="Q66">
+        <v>20</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>90</v>
+      </c>
+      <c r="U66">
+        <v>2</v>
+      </c>
+      <c r="V66">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22">
+      <c r="A67" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>40</v>
+      </c>
+      <c r="D67" t="s">
+        <v>51</v>
+      </c>
+      <c r="E67" t="s">
+        <v>100</v>
+      </c>
+      <c r="F67" t="s">
+        <v>143</v>
+      </c>
+      <c r="G67" t="s">
+        <v>149</v>
+      </c>
+      <c r="H67" t="s">
+        <v>169</v>
+      </c>
+      <c r="I67" t="s">
+        <v>174</v>
+      </c>
+      <c r="J67">
+        <v>6</v>
+      </c>
+      <c r="K67">
+        <v>38</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67" t="s">
+        <v>241</v>
+      </c>
+      <c r="P67">
+        <v>50</v>
+      </c>
+      <c r="Q67">
+        <v>56</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>90</v>
+      </c>
+      <c r="U67">
+        <v>3</v>
+      </c>
+      <c r="V67">
+        <v>70.33</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22">
+      <c r="A68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" t="s">
+        <v>40</v>
+      </c>
+      <c r="D68" t="s">
+        <v>72</v>
+      </c>
+      <c r="E68" t="s">
+        <v>121</v>
+      </c>
+      <c r="F68" t="s">
+        <v>143</v>
+      </c>
+      <c r="G68" t="s">
+        <v>149</v>
+      </c>
+      <c r="H68" t="s">
+        <v>169</v>
+      </c>
+      <c r="I68" t="s">
+        <v>174</v>
+      </c>
+      <c r="J68">
+        <v>6</v>
+      </c>
+      <c r="K68">
+        <v>20</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68" t="s">
+        <v>242</v>
+      </c>
+      <c r="P68">
+        <v>22</v>
+      </c>
+      <c r="Q68">
+        <v>34</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>90</v>
+      </c>
+      <c r="U68">
+        <v>3</v>
+      </c>
+      <c r="V68">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22">
+      <c r="A69" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>40</v>
+      </c>
+      <c r="D69" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" t="s">
+        <v>101</v>
+      </c>
+      <c r="F69" t="s">
+        <v>143</v>
+      </c>
+      <c r="G69" t="s">
+        <v>149</v>
+      </c>
+      <c r="H69" t="s">
+        <v>169</v>
+      </c>
+      <c r="I69" t="s">
+        <v>174</v>
+      </c>
+      <c r="J69">
+        <v>6</v>
+      </c>
+      <c r="K69">
+        <v>7</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69" t="s">
+        <v>243</v>
+      </c>
+      <c r="P69">
+        <v>14</v>
+      </c>
+      <c r="Q69">
+        <v>20</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>90</v>
+      </c>
+      <c r="U69">
+        <v>3</v>
+      </c>
+      <c r="V69">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22">
+      <c r="A70" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" t="s">
+        <v>40</v>
+      </c>
+      <c r="D70" t="s">
+        <v>79</v>
+      </c>
+      <c r="E70" t="s">
+        <v>128</v>
+      </c>
+      <c r="F70" t="s">
+        <v>142</v>
+      </c>
+      <c r="G70" t="s">
+        <v>161</v>
+      </c>
+      <c r="H70" t="s">
+        <v>169</v>
+      </c>
+      <c r="I70" t="s">
+        <v>174</v>
+      </c>
+      <c r="J70">
+        <v>6</v>
+      </c>
+      <c r="K70">
+        <v>13</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70" t="s">
+        <v>244</v>
+      </c>
+      <c r="P70">
+        <v>18</v>
+      </c>
+      <c r="Q70">
+        <v>30</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>90</v>
+      </c>
+      <c r="U70">
+        <v>3</v>
+      </c>
+      <c r="V70">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22">
+      <c r="A71" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" t="s">
+        <v>40</v>
+      </c>
+      <c r="D71" t="s">
+        <v>80</v>
+      </c>
+      <c r="E71" t="s">
+        <v>129</v>
+      </c>
+      <c r="F71" t="s">
+        <v>142</v>
+      </c>
+      <c r="G71" t="s">
+        <v>162</v>
+      </c>
+      <c r="H71" t="s">
+        <v>169</v>
+      </c>
+      <c r="I71" t="s">
+        <v>173</v>
+      </c>
+      <c r="J71">
+        <v>12</v>
+      </c>
+      <c r="K71">
+        <v>58</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71" t="s">
+        <v>245</v>
+      </c>
+      <c r="P71">
+        <v>60</v>
+      </c>
+      <c r="Q71">
+        <v>72</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>90</v>
+      </c>
+      <c r="U71">
+        <v>2</v>
+      </c>
+      <c r="V71">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22">
+      <c r="A72" t="s">
+        <v>24</v>
+      </c>
+      <c r="B72" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" t="s">
+        <v>40</v>
+      </c>
+      <c r="D72" t="s">
+        <v>58</v>
+      </c>
+      <c r="E72" t="s">
+        <v>107</v>
+      </c>
+      <c r="F72" t="s">
+        <v>142</v>
+      </c>
+      <c r="G72" t="s">
+        <v>148</v>
+      </c>
+      <c r="H72" t="s">
+        <v>169</v>
+      </c>
+      <c r="I72" t="s">
+        <v>173</v>
+      </c>
+      <c r="J72">
+        <v>12</v>
+      </c>
+      <c r="K72">
+        <v>29</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>96</v>
+      </c>
+      <c r="O72" t="s">
+        <v>246</v>
+      </c>
+      <c r="P72">
+        <v>168</v>
+      </c>
+      <c r="Q72">
+        <v>240</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>90</v>
+      </c>
+      <c r="U72">
+        <v>10</v>
+      </c>
+      <c r="V72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" t="s">
+        <v>40</v>
+      </c>
+      <c r="D73" t="s">
+        <v>81</v>
+      </c>
+      <c r="E73" t="s">
+        <v>130</v>
+      </c>
+      <c r="F73" t="s">
+        <v>142</v>
+      </c>
+      <c r="G73" t="s">
+        <v>163</v>
+      </c>
+      <c r="H73" t="s">
+        <v>169</v>
+      </c>
+      <c r="I73" t="s">
+        <v>180</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>5</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73" t="s">
+        <v>247</v>
+      </c>
+      <c r="P73">
+        <v>7</v>
+      </c>
+      <c r="Q73">
+        <v>10</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>90</v>
+      </c>
+      <c r="U73">
+        <v>4</v>
+      </c>
+      <c r="V73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22">
+      <c r="A74" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" t="s">
+        <v>41</v>
+      </c>
+      <c r="D74" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74" t="s">
+        <v>131</v>
+      </c>
+      <c r="F74" t="s">
+        <v>142</v>
+      </c>
+      <c r="G74" t="s">
+        <v>164</v>
+      </c>
+      <c r="H74" t="s">
+        <v>169</v>
+      </c>
+      <c r="I74" t="s">
+        <v>173</v>
+      </c>
+      <c r="J74">
+        <v>12</v>
+      </c>
+      <c r="K74">
+        <v>20</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74" t="s">
+        <v>248</v>
+      </c>
+      <c r="P74">
+        <v>22</v>
+      </c>
+      <c r="Q74">
+        <v>34</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>90</v>
+      </c>
+      <c r="U74">
+        <v>2</v>
+      </c>
+      <c r="V74">
+        <v>114.92</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22">
+      <c r="A75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75" t="s">
+        <v>83</v>
+      </c>
+      <c r="E75" t="s">
+        <v>132</v>
+      </c>
+      <c r="F75" t="s">
+        <v>142</v>
+      </c>
+      <c r="G75" t="s">
+        <v>165</v>
+      </c>
+      <c r="H75" t="s">
+        <v>169</v>
+      </c>
+      <c r="I75" t="s">
+        <v>173</v>
+      </c>
+      <c r="J75">
+        <v>12</v>
+      </c>
+      <c r="K75">
+        <v>27</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75" t="s">
+        <v>249</v>
+      </c>
+      <c r="P75">
+        <v>28</v>
+      </c>
+      <c r="Q75">
+        <v>40</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>90</v>
+      </c>
+      <c r="U75">
+        <v>2</v>
+      </c>
+      <c r="V75">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22">
+      <c r="A76" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" t="s">
+        <v>41</v>
+      </c>
+      <c r="D76" t="s">
+        <v>49</v>
+      </c>
+      <c r="E76" t="s">
+        <v>98</v>
+      </c>
+      <c r="F76" t="s">
+        <v>142</v>
+      </c>
+      <c r="G76" t="s">
+        <v>148</v>
+      </c>
+      <c r="H76" t="s">
+        <v>169</v>
+      </c>
+      <c r="I76" t="s">
+        <v>173</v>
+      </c>
+      <c r="J76">
+        <v>12</v>
+      </c>
+      <c r="K76">
+        <v>760</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76" t="s">
+        <v>250</v>
+      </c>
+      <c r="P76">
+        <v>1020</v>
+      </c>
+      <c r="Q76">
+        <v>2040</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>90</v>
+      </c>
+      <c r="U76">
+        <v>107</v>
+      </c>
+      <c r="V76">
+        <v>4930</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22">
+      <c r="A77" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77" t="s">
+        <v>41</v>
+      </c>
+      <c r="D77" t="s">
+        <v>60</v>
+      </c>
+      <c r="E77" t="s">
+        <v>109</v>
+      </c>
+      <c r="F77" t="s">
+        <v>142</v>
+      </c>
+      <c r="G77" t="s">
+        <v>148</v>
+      </c>
+      <c r="H77" t="s">
+        <v>169</v>
+      </c>
+      <c r="I77" t="s">
+        <v>173</v>
+      </c>
+      <c r="J77">
+        <v>12</v>
+      </c>
+      <c r="K77">
+        <v>41</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77" t="s">
+        <v>251</v>
+      </c>
+      <c r="P77">
+        <v>68</v>
+      </c>
+      <c r="Q77">
+        <v>116</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>90</v>
+      </c>
+      <c r="U77">
+        <v>7</v>
+      </c>
+      <c r="V77">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22">
+      <c r="A78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78" t="s">
+        <v>41</v>
+      </c>
+      <c r="D78" t="s">
+        <v>76</v>
+      </c>
+      <c r="E78" t="s">
+        <v>125</v>
+      </c>
+      <c r="F78" t="s">
+        <v>142</v>
+      </c>
+      <c r="G78" t="s">
+        <v>155</v>
+      </c>
+      <c r="H78" t="s">
+        <v>169</v>
+      </c>
+      <c r="I78" t="s">
+        <v>174</v>
+      </c>
+      <c r="J78">
+        <v>6</v>
+      </c>
+      <c r="K78">
+        <v>48</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>36</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78" t="s">
+        <v>252</v>
+      </c>
+      <c r="P78">
+        <v>96</v>
+      </c>
+      <c r="Q78">
+        <v>120</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>90</v>
+      </c>
+      <c r="U78">
+        <v>6</v>
+      </c>
+      <c r="V78">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22">
+      <c r="A79" t="s">
+        <v>23</v>
+      </c>
+      <c r="B79" t="s">
+        <v>29</v>
+      </c>
+      <c r="C79" t="s">
+        <v>41</v>
+      </c>
+      <c r="D79" t="s">
+        <v>84</v>
+      </c>
+      <c r="E79" t="s">
+        <v>133</v>
+      </c>
+      <c r="F79" t="s">
+        <v>142</v>
+      </c>
+      <c r="G79" t="s">
+        <v>155</v>
+      </c>
+      <c r="H79" t="s">
+        <v>169</v>
+      </c>
+      <c r="I79" t="s">
+        <v>181</v>
+      </c>
+      <c r="J79">
+        <v>50</v>
+      </c>
+      <c r="K79">
+        <v>67</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79" t="s">
+        <v>253</v>
+      </c>
+      <c r="P79">
+        <v>86</v>
+      </c>
+      <c r="Q79">
+        <v>136</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>90</v>
+      </c>
+      <c r="U79">
+        <v>2</v>
+      </c>
+      <c r="V79">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22">
+      <c r="A80" t="s">
+        <v>24</v>
+      </c>
+      <c r="B80" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" t="s">
+        <v>41</v>
+      </c>
+      <c r="D80" t="s">
+        <v>67</v>
+      </c>
+      <c r="E80" t="s">
+        <v>116</v>
+      </c>
+      <c r="F80" t="s">
+        <v>142</v>
+      </c>
+      <c r="G80" t="s">
+        <v>156</v>
+      </c>
+      <c r="H80" t="s">
+        <v>169</v>
+      </c>
+      <c r="I80" t="s">
+        <v>173</v>
+      </c>
+      <c r="J80">
+        <v>12</v>
+      </c>
+      <c r="K80">
+        <v>9</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80" t="s">
+        <v>183</v>
+      </c>
+      <c r="P80">
+        <v>14</v>
+      </c>
+      <c r="Q80">
+        <v>26</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>90</v>
+      </c>
+      <c r="U80">
+        <v>2</v>
+      </c>
+      <c r="V80">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22">
+      <c r="A81" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" t="s">
+        <v>42</v>
+      </c>
+      <c r="D81" t="s">
+        <v>52</v>
+      </c>
+      <c r="E81" t="s">
+        <v>101</v>
+      </c>
+      <c r="F81" t="s">
+        <v>143</v>
+      </c>
+      <c r="G81" t="s">
+        <v>149</v>
+      </c>
+      <c r="H81" t="s">
+        <v>169</v>
+      </c>
+      <c r="I81" t="s">
+        <v>174</v>
+      </c>
+      <c r="J81">
+        <v>6</v>
+      </c>
+      <c r="K81">
+        <v>29</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81" t="s">
+        <v>254</v>
+      </c>
+      <c r="P81">
+        <v>30</v>
+      </c>
+      <c r="Q81">
+        <v>42</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+      <c r="S81">
+        <v>0</v>
+      </c>
+      <c r="T81">
+        <v>90</v>
+      </c>
+      <c r="U81">
+        <v>3</v>
+      </c>
+      <c r="V81">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22">
+      <c r="A82" t="s">
+        <v>23</v>
+      </c>
+      <c r="B82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82" t="s">
+        <v>42</v>
+      </c>
+      <c r="D82" t="s">
+        <v>85</v>
+      </c>
+      <c r="E82" t="s">
+        <v>134</v>
+      </c>
+      <c r="F82" t="s">
+        <v>142</v>
+      </c>
+      <c r="G82" t="s">
+        <v>150</v>
+      </c>
+      <c r="H82" t="s">
+        <v>169</v>
+      </c>
+      <c r="I82" t="s">
+        <v>172</v>
+      </c>
+      <c r="J82">
+        <v>30</v>
+      </c>
+      <c r="K82">
+        <v>65</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82" t="s">
+        <v>255</v>
+      </c>
+      <c r="P82">
+        <v>66</v>
+      </c>
+      <c r="Q82">
+        <v>96</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <v>90</v>
+      </c>
+      <c r="U82">
+        <v>2</v>
+      </c>
+      <c r="V82">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22">
+      <c r="A83" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83" t="s">
+        <v>27</v>
+      </c>
+      <c r="C83" t="s">
+        <v>42</v>
+      </c>
+      <c r="D83" t="s">
+        <v>86</v>
+      </c>
+      <c r="E83" t="s">
+        <v>135</v>
+      </c>
+      <c r="F83" t="s">
+        <v>142</v>
+      </c>
+      <c r="G83" t="s">
+        <v>166</v>
+      </c>
+      <c r="H83" t="s">
+        <v>169</v>
+      </c>
+      <c r="I83" t="s">
+        <v>174</v>
+      </c>
+      <c r="J83">
+        <v>6</v>
+      </c>
+      <c r="K83">
+        <v>39</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83" t="s">
+        <v>256</v>
+      </c>
+      <c r="P83">
+        <v>54</v>
+      </c>
+      <c r="Q83">
+        <v>84</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <v>90</v>
+      </c>
+      <c r="U83">
+        <v>8</v>
+      </c>
+      <c r="V83">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22">
+      <c r="A84" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" t="s">
+        <v>42</v>
+      </c>
+      <c r="D84" t="s">
+        <v>87</v>
+      </c>
+      <c r="E84" t="s">
+        <v>136</v>
+      </c>
+      <c r="F84" t="s">
+        <v>142</v>
+      </c>
+      <c r="G84" t="s">
+        <v>148</v>
+      </c>
+      <c r="H84" t="s">
+        <v>169</v>
+      </c>
+      <c r="I84" t="s">
+        <v>180</v>
+      </c>
+      <c r="J84">
+        <v>6</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84" t="s">
+        <v>257</v>
+      </c>
+      <c r="P84">
+        <v>6</v>
+      </c>
+      <c r="Q84">
+        <v>12</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>90</v>
+      </c>
+      <c r="U84">
+        <v>2</v>
+      </c>
+      <c r="V84">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22">
+      <c r="A85" t="s">
+        <v>24</v>
+      </c>
+      <c r="B85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" t="s">
+        <v>42</v>
+      </c>
+      <c r="D85" t="s">
+        <v>58</v>
+      </c>
+      <c r="E85" t="s">
+        <v>107</v>
+      </c>
+      <c r="F85" t="s">
+        <v>142</v>
+      </c>
+      <c r="G85" t="s">
+        <v>148</v>
+      </c>
+      <c r="H85" t="s">
+        <v>169</v>
+      </c>
+      <c r="I85" t="s">
+        <v>173</v>
+      </c>
+      <c r="J85">
+        <v>12</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>120</v>
+      </c>
+      <c r="O85" t="s">
+        <v>258</v>
+      </c>
+      <c r="P85">
+        <v>144</v>
+      </c>
+      <c r="Q85">
+        <v>228</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>90</v>
+      </c>
+      <c r="U85">
+        <v>9</v>
+      </c>
+      <c r="V85">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22">
+      <c r="A86" t="s">
+        <v>24</v>
+      </c>
+      <c r="B86" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" t="s">
+        <v>42</v>
+      </c>
+      <c r="D86" t="s">
+        <v>49</v>
+      </c>
+      <c r="E86" t="s">
+        <v>98</v>
+      </c>
+      <c r="F86" t="s">
+        <v>142</v>
+      </c>
+      <c r="G86" t="s">
+        <v>148</v>
+      </c>
+      <c r="H86" t="s">
+        <v>169</v>
+      </c>
+      <c r="I86" t="s">
+        <v>173</v>
+      </c>
+      <c r="J86">
+        <v>12</v>
+      </c>
+      <c r="K86">
+        <v>1080</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>324</v>
+      </c>
+      <c r="O86" t="s">
+        <v>259</v>
+      </c>
+      <c r="P86">
+        <v>1912</v>
+      </c>
+      <c r="Q86">
+        <v>2944</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+      <c r="S86">
+        <v>0</v>
+      </c>
+      <c r="T86">
+        <v>90</v>
+      </c>
+      <c r="U86">
+        <v>129</v>
+      </c>
+      <c r="V86">
+        <v>4930</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22">
+      <c r="A87" t="s">
+        <v>24</v>
+      </c>
+      <c r="B87" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" t="s">
+        <v>42</v>
+      </c>
+      <c r="D87" t="s">
+        <v>50</v>
+      </c>
+      <c r="E87" t="s">
+        <v>99</v>
+      </c>
+      <c r="F87" t="s">
+        <v>142</v>
+      </c>
+      <c r="G87" t="s">
+        <v>148</v>
+      </c>
+      <c r="H87" t="s">
+        <v>169</v>
+      </c>
+      <c r="I87" t="s">
+        <v>173</v>
+      </c>
+      <c r="J87">
+        <v>12</v>
+      </c>
+      <c r="K87">
+        <v>47</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87" t="s">
+        <v>260</v>
+      </c>
+      <c r="P87">
+        <v>56</v>
+      </c>
+      <c r="Q87">
+        <v>92</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>0</v>
+      </c>
+      <c r="T87">
+        <v>90</v>
+      </c>
+      <c r="U87">
+        <v>4</v>
+      </c>
+      <c r="V87">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22">
+      <c r="A88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88" t="s">
+        <v>42</v>
+      </c>
+      <c r="D88" t="s">
+        <v>64</v>
+      </c>
+      <c r="E88" t="s">
+        <v>113</v>
+      </c>
+      <c r="F88" t="s">
+        <v>142</v>
+      </c>
+      <c r="G88" t="s">
+        <v>148</v>
+      </c>
+      <c r="H88" t="s">
+        <v>169</v>
+      </c>
+      <c r="I88" t="s">
+        <v>173</v>
+      </c>
+      <c r="J88">
+        <v>12</v>
+      </c>
+      <c r="K88">
+        <v>100</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88" t="s">
+        <v>261</v>
+      </c>
+      <c r="P88">
+        <v>120</v>
+      </c>
+      <c r="Q88">
+        <v>144</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+      <c r="S88">
+        <v>0</v>
+      </c>
+      <c r="T88">
+        <v>90</v>
+      </c>
+      <c r="U88">
+        <v>4</v>
+      </c>
+      <c r="V88">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22">
+      <c r="A89" t="s">
+        <v>24</v>
+      </c>
+      <c r="B89" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89" t="s">
+        <v>42</v>
+      </c>
+      <c r="D89" t="s">
+        <v>65</v>
+      </c>
+      <c r="E89" t="s">
+        <v>114</v>
+      </c>
+      <c r="F89" t="s">
+        <v>142</v>
+      </c>
+      <c r="G89" t="s">
+        <v>148</v>
+      </c>
+      <c r="H89" t="s">
+        <v>169</v>
+      </c>
+      <c r="I89" t="s">
+        <v>173</v>
+      </c>
+      <c r="J89">
+        <v>12</v>
+      </c>
+      <c r="K89">
+        <v>75</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89" t="s">
+        <v>262</v>
+      </c>
+      <c r="P89">
+        <v>96</v>
+      </c>
+      <c r="Q89">
+        <v>120</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>0</v>
+      </c>
+      <c r="T89">
+        <v>90</v>
+      </c>
+      <c r="U89">
+        <v>4</v>
+      </c>
+      <c r="V89">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22">
+      <c r="A90" t="s">
+        <v>24</v>
+      </c>
+      <c r="B90" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" t="s">
+        <v>66</v>
+      </c>
+      <c r="E90" t="s">
+        <v>115</v>
+      </c>
+      <c r="F90" t="s">
+        <v>142</v>
+      </c>
+      <c r="G90" t="s">
+        <v>148</v>
+      </c>
+      <c r="H90" t="s">
+        <v>169</v>
+      </c>
+      <c r="I90" t="s">
+        <v>173</v>
+      </c>
+      <c r="J90">
+        <v>12</v>
+      </c>
+      <c r="K90">
+        <v>220</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90" t="s">
+        <v>263</v>
+      </c>
+      <c r="P90">
+        <v>360</v>
+      </c>
+      <c r="Q90">
+        <v>480</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>90</v>
+      </c>
+      <c r="U90">
+        <v>22</v>
+      </c>
+      <c r="V90">
+        <v>115.17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22">
+      <c r="A91" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" t="s">
+        <v>43</v>
+      </c>
+      <c r="D91" t="s">
+        <v>88</v>
+      </c>
+      <c r="E91" t="s">
+        <v>137</v>
+      </c>
+      <c r="F91" t="s">
+        <v>142</v>
+      </c>
+      <c r="G91" t="s">
+        <v>167</v>
+      </c>
+      <c r="H91" t="s">
+        <v>169</v>
+      </c>
+      <c r="I91" t="s">
+        <v>173</v>
+      </c>
+      <c r="J91">
+        <v>12</v>
+      </c>
+      <c r="K91">
+        <v>73</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91" t="s">
+        <v>264</v>
+      </c>
+      <c r="P91">
+        <v>144</v>
+      </c>
+      <c r="Q91">
+        <v>228</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+      <c r="S91">
+        <v>0</v>
+      </c>
+      <c r="T91">
+        <v>90</v>
+      </c>
+      <c r="U91">
+        <v>13</v>
+      </c>
+      <c r="V91">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22">
+      <c r="A92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B92" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92" t="s">
+        <v>43</v>
+      </c>
+      <c r="D92" t="s">
+        <v>89</v>
+      </c>
+      <c r="E92" t="s">
+        <v>138</v>
+      </c>
+      <c r="F92" t="s">
+        <v>142</v>
+      </c>
+      <c r="G92" t="s">
+        <v>161</v>
+      </c>
+      <c r="H92" t="s">
+        <v>169</v>
+      </c>
+      <c r="I92" t="s">
+        <v>174</v>
+      </c>
+      <c r="J92">
+        <v>6</v>
+      </c>
+      <c r="K92">
+        <v>5</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92" t="s">
+        <v>265</v>
+      </c>
+      <c r="P92">
+        <v>16</v>
+      </c>
+      <c r="Q92">
+        <v>34</v>
+      </c>
+      <c r="R92">
+        <v>0</v>
+      </c>
+      <c r="S92">
+        <v>0</v>
+      </c>
+      <c r="T92">
+        <v>90</v>
+      </c>
+      <c r="U92">
+        <v>5</v>
+      </c>
+      <c r="V92">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22">
+      <c r="A93" t="s">
+        <v>23</v>
+      </c>
+      <c r="B93" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93" t="s">
+        <v>43</v>
+      </c>
+      <c r="D93" t="s">
+        <v>90</v>
+      </c>
+      <c r="E93" t="s">
+        <v>139</v>
+      </c>
+      <c r="F93" t="s">
+        <v>142</v>
+      </c>
+      <c r="G93" t="s">
+        <v>168</v>
+      </c>
+      <c r="H93" t="s">
+        <v>169</v>
+      </c>
+      <c r="I93" t="s">
+        <v>175</v>
+      </c>
+      <c r="J93">
+        <v>10</v>
+      </c>
+      <c r="K93">
+        <v>274</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>20</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93" t="s">
+        <v>266</v>
+      </c>
+      <c r="P93">
+        <v>296</v>
+      </c>
+      <c r="Q93">
+        <v>336</v>
+      </c>
+      <c r="R93">
+        <v>0</v>
+      </c>
+      <c r="S93">
+        <v>0</v>
+      </c>
+      <c r="T93">
+        <v>90</v>
+      </c>
+      <c r="U93">
+        <v>5</v>
+      </c>
+      <c r="V93">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22">
+      <c r="A94" t="s">
+        <v>23</v>
+      </c>
+      <c r="B94" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94" t="s">
+        <v>43</v>
+      </c>
+      <c r="D94" t="s">
+        <v>91</v>
+      </c>
+      <c r="E94" t="s">
+        <v>140</v>
+      </c>
+      <c r="F94" t="s">
+        <v>142</v>
+      </c>
+      <c r="G94" t="s">
+        <v>153</v>
+      </c>
+      <c r="H94" t="s">
+        <v>169</v>
+      </c>
+      <c r="I94" t="s">
+        <v>173</v>
+      </c>
+      <c r="J94">
+        <v>12</v>
+      </c>
+      <c r="K94">
+        <v>6</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>12</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94" t="s">
+        <v>215</v>
+      </c>
+      <c r="P94">
+        <v>24</v>
+      </c>
+      <c r="Q94">
+        <v>36</v>
+      </c>
+      <c r="R94">
+        <v>0</v>
+      </c>
+      <c r="S94">
+        <v>0</v>
+      </c>
+      <c r="T94">
+        <v>90</v>
+      </c>
+      <c r="U94">
+        <v>2</v>
+      </c>
+      <c r="V94">
+        <v>58.75</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22">
+      <c r="A95" t="s">
+        <v>24</v>
+      </c>
+      <c r="B95" t="s">
+        <v>28</v>
+      </c>
+      <c r="C95" t="s">
+        <v>43</v>
+      </c>
+      <c r="D95" t="s">
+        <v>59</v>
+      </c>
+      <c r="E95" t="s">
+        <v>108</v>
+      </c>
+      <c r="F95" t="s">
+        <v>142</v>
+      </c>
+      <c r="G95" t="s">
+        <v>148</v>
+      </c>
+      <c r="H95" t="s">
+        <v>169</v>
+      </c>
+      <c r="I95" t="s">
+        <v>173</v>
+      </c>
+      <c r="J95">
+        <v>12</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95" t="s">
+        <v>267</v>
+      </c>
+      <c r="P95">
+        <v>14</v>
+      </c>
+      <c r="Q95">
+        <v>26</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+      <c r="S95">
+        <v>0</v>
+      </c>
+      <c r="T95">
+        <v>90</v>
+      </c>
+      <c r="U95">
+        <v>3</v>
+      </c>
+      <c r="V95">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22">
+      <c r="A96" t="s">
+        <v>24</v>
+      </c>
+      <c r="B96" t="s">
+        <v>28</v>
+      </c>
+      <c r="C96" t="s">
+        <v>43</v>
+      </c>
+      <c r="D96" t="s">
+        <v>60</v>
+      </c>
+      <c r="E96" t="s">
+        <v>109</v>
+      </c>
+      <c r="F96" t="s">
+        <v>142</v>
+      </c>
+      <c r="G96" t="s">
+        <v>148</v>
+      </c>
+      <c r="H96" t="s">
+        <v>169</v>
+      </c>
+      <c r="I96" t="s">
+        <v>173</v>
+      </c>
+      <c r="J96">
+        <v>12</v>
+      </c>
+      <c r="K96">
+        <v>43</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96" t="s">
+        <v>268</v>
+      </c>
+      <c r="P96">
+        <v>48</v>
+      </c>
+      <c r="Q96">
+        <v>72</v>
+      </c>
+      <c r="R96">
+        <v>0</v>
+      </c>
+      <c r="S96">
+        <v>0</v>
+      </c>
+      <c r="T96">
+        <v>90</v>
+      </c>
+      <c r="U96">
+        <v>3</v>
+      </c>
+      <c r="V96">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22">
+      <c r="A97" t="s">
+        <v>24</v>
+      </c>
+      <c r="B97" t="s">
+        <v>28</v>
+      </c>
+      <c r="C97" t="s">
+        <v>43</v>
+      </c>
+      <c r="D97" t="s">
+        <v>64</v>
+      </c>
+      <c r="E97" t="s">
+        <v>113</v>
+      </c>
+      <c r="F97" t="s">
+        <v>142</v>
+      </c>
+      <c r="G97" t="s">
+        <v>148</v>
+      </c>
+      <c r="H97" t="s">
+        <v>169</v>
+      </c>
+      <c r="I97" t="s">
+        <v>173</v>
+      </c>
+      <c r="J97">
+        <v>12</v>
+      </c>
+      <c r="K97">
+        <v>117</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97" t="s">
+        <v>269</v>
+      </c>
+      <c r="P97">
+        <v>120</v>
+      </c>
+      <c r="Q97">
+        <v>144</v>
+      </c>
+      <c r="R97">
+        <v>0</v>
+      </c>
+      <c r="S97">
+        <v>0</v>
+      </c>
+      <c r="T97">
+        <v>90</v>
+      </c>
+      <c r="U97">
+        <v>3</v>
+      </c>
+      <c r="V97">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22">
+      <c r="A98" t="s">
+        <v>23</v>
+      </c>
+      <c r="B98" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" t="s">
+        <v>43</v>
+      </c>
+      <c r="D98" t="s">
+        <v>92</v>
+      </c>
+      <c r="E98" t="s">
+        <v>141</v>
+      </c>
+      <c r="F98" t="s">
+        <v>142</v>
+      </c>
+      <c r="G98" t="s">
+        <v>155</v>
+      </c>
+      <c r="H98" t="s">
+        <v>169</v>
+      </c>
+      <c r="I98" t="s">
+        <v>180</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>4</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98" t="s">
+        <v>202</v>
+      </c>
+      <c r="P98">
+        <v>7</v>
+      </c>
+      <c r="Q98">
+        <v>10</v>
+      </c>
+      <c r="R98">
+        <v>0</v>
+      </c>
+      <c r="S98">
+        <v>0</v>
+      </c>
+      <c r="T98">
+        <v>90</v>
+      </c>
+      <c r="U98">
+        <v>6</v>
+      </c>
+      <c r="V98">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22">
+      <c r="A99" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>30</v>
+      </c>
+      <c r="C99" t="s">
+        <v>43</v>
+      </c>
+      <c r="D99" t="s">
+        <v>63</v>
+      </c>
+      <c r="E99" t="s">
         <v>112</v>
       </c>
-      <c r="F48" t="s">
-        <v>114</v>
-      </c>
-      <c r="G48" t="s">
-        <v>133</v>
-      </c>
-      <c r="H48" t="s">
-        <v>134</v>
-      </c>
-      <c r="I48" t="s">
-        <v>140</v>
-      </c>
-      <c r="J48">
-        <v>15</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48" t="s">
-        <v>150</v>
-      </c>
-      <c r="P48">
-        <v>9</v>
-      </c>
-      <c r="Q48">
+      <c r="F99" t="s">
+        <v>142</v>
+      </c>
+      <c r="G99" t="s">
+        <v>155</v>
+      </c>
+      <c r="H99" t="s">
+        <v>169</v>
+      </c>
+      <c r="I99" t="s">
+        <v>174</v>
+      </c>
+      <c r="J99">
+        <v>6</v>
+      </c>
+      <c r="K99">
+        <v>11</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>6</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99" t="s">
+        <v>270</v>
+      </c>
+      <c r="P99">
+        <v>18</v>
+      </c>
+      <c r="Q99">
         <v>24</v>
       </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>90</v>
-      </c>
-      <c r="U48">
+      <c r="R99">
+        <v>0</v>
+      </c>
+      <c r="S99">
+        <v>0</v>
+      </c>
+      <c r="T99">
+        <v>90</v>
+      </c>
+      <c r="U99">
         <v>2</v>
       </c>
-      <c r="V48">
-        <v>25</v>
+      <c r="V99">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Downloads\Equipes_Agentes\Aplicativos\GAM\bd_saida\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82A4BCA-3904-4B81-A6B3-D21210FB1FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E4F47B-9D07-4913-9DCF-9126650E16BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$58</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="262">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -102,33 +102,36 @@
     <t>Estq_CD_cx</t>
   </si>
   <si>
+    <t>PERECIVEIS</t>
+  </si>
+  <si>
+    <t>MERCEARIA</t>
+  </si>
+  <si>
     <t>BEBIDAS</t>
   </si>
   <si>
-    <t>MERCEARIA</t>
-  </si>
-  <si>
     <t>PERFUMARIA E LIMPEZA</t>
   </si>
   <si>
-    <t>PERECIVEIS</t>
+    <t>PRODUTOS PET</t>
+  </si>
+  <si>
+    <t>SANDRO MARTINS VIANNA</t>
+  </si>
+  <si>
+    <t>NIDAL TUBASI</t>
   </si>
   <si>
     <t>NICOLAS AUGUSTO P. BORGES</t>
   </si>
   <si>
-    <t>NIDAL TUBASI</t>
+    <t>JOAO BATISTA</t>
   </si>
   <si>
     <t>WETER SONNENFELDET</t>
   </si>
   <si>
-    <t>JOAO BATISTA</t>
-  </si>
-  <si>
-    <t>SANDRO MARTINS VIANNA</t>
-  </si>
-  <si>
     <t>001</t>
   </si>
   <si>
@@ -141,6 +144,9 @@
     <t>004</t>
   </si>
   <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>006</t>
   </si>
   <si>
@@ -150,9 +156,6 @@
     <t>008</t>
   </si>
   <si>
-    <t>011</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
@@ -168,220 +171,298 @@
     <t>018</t>
   </si>
   <si>
-    <t>759</t>
-  </si>
-  <si>
-    <t>1064</t>
-  </si>
-  <si>
-    <t>34577</t>
-  </si>
-  <si>
-    <t>36987</t>
+    <t>6781</t>
+  </si>
+  <si>
+    <t>6783</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>35112</t>
+  </si>
+  <si>
+    <t>843</t>
+  </si>
+  <si>
+    <t>908</t>
+  </si>
+  <si>
+    <t>2516</t>
+  </si>
+  <si>
+    <t>4276</t>
+  </si>
+  <si>
+    <t>6828</t>
+  </si>
+  <si>
+    <t>18812</t>
+  </si>
+  <si>
+    <t>37007</t>
+  </si>
+  <si>
+    <t>37014</t>
+  </si>
+  <si>
+    <t>37075</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>540</t>
+  </si>
+  <si>
+    <t>552</t>
+  </si>
+  <si>
+    <t>781</t>
+  </si>
+  <si>
+    <t>1468</t>
+  </si>
+  <si>
+    <t>1648</t>
+  </si>
+  <si>
+    <t>2171</t>
+  </si>
+  <si>
+    <t>2346</t>
+  </si>
+  <si>
+    <t>2369</t>
+  </si>
+  <si>
+    <t>5196</t>
+  </si>
+  <si>
+    <t>9751</t>
+  </si>
+  <si>
+    <t>17317</t>
+  </si>
+  <si>
+    <t>18815</t>
+  </si>
+  <si>
+    <t>37431</t>
+  </si>
+  <si>
+    <t>771</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>3298</t>
+  </si>
+  <si>
+    <t>5857</t>
+  </si>
+  <si>
+    <t>2266</t>
+  </si>
+  <si>
+    <t>4625</t>
+  </si>
+  <si>
+    <t>6125</t>
+  </si>
+  <si>
+    <t>13123</t>
+  </si>
+  <si>
+    <t>2076</t>
+  </si>
+  <si>
+    <t>2991</t>
+  </si>
+  <si>
+    <t>3964</t>
   </si>
   <si>
     <t>4988</t>
   </si>
   <si>
-    <t>17176</t>
-  </si>
-  <si>
-    <t>17181</t>
-  </si>
-  <si>
-    <t>1468</t>
-  </si>
-  <si>
-    <t>825</t>
-  </si>
-  <si>
-    <t>8622</t>
-  </si>
-  <si>
-    <t>3686</t>
-  </si>
-  <si>
-    <t>9751</t>
-  </si>
-  <si>
-    <t>33673</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>2396</t>
-  </si>
-  <si>
-    <t>3051</t>
-  </si>
-  <si>
-    <t>2953</t>
-  </si>
-  <si>
-    <t>22639</t>
-  </si>
-  <si>
-    <t>36474</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>942</t>
-  </si>
-  <si>
-    <t>1617</t>
-  </si>
-  <si>
-    <t>3134</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>4202</t>
+    <t>9547</t>
+  </si>
+  <si>
+    <t>33286</t>
+  </si>
+  <si>
+    <t>6121</t>
+  </si>
+  <si>
+    <t>8288</t>
+  </si>
+  <si>
+    <t>33491</t>
   </si>
   <si>
     <t>4203</t>
   </si>
   <si>
-    <t>4207</t>
-  </si>
-  <si>
-    <t>4598</t>
-  </si>
-  <si>
-    <t>5436</t>
-  </si>
-  <si>
-    <t>5437</t>
-  </si>
-  <si>
-    <t>5438</t>
-  </si>
-  <si>
-    <t>12412</t>
-  </si>
-  <si>
-    <t>17321</t>
-  </si>
-  <si>
-    <t>17450</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>12136</t>
-  </si>
-  <si>
-    <t>REFRIG ANTARCTICA GUARANA PET 200ML</t>
-  </si>
-  <si>
-    <t>BISC DOMELLY POLVILHO 80G TRAD</t>
-  </si>
-  <si>
-    <t>MOLHO SALADA SALSARETTI 235ML ITALIAN</t>
-  </si>
-  <si>
-    <t>FARINHA MANDIOCA 500G DINDA</t>
+    <t>5671</t>
+  </si>
+  <si>
+    <t>17169</t>
+  </si>
+  <si>
+    <t>34975</t>
+  </si>
+  <si>
+    <t>LEITE UHT ELEGE INT 1L</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL C TAMP INT 1L</t>
+  </si>
+  <si>
+    <t>AGUA MIN CRYSTAL PET 500ML S GAS</t>
+  </si>
+  <si>
+    <t>AGUA MIN SARANDI 5L S GAS</t>
+  </si>
+  <si>
+    <t>AMAC CONC DOWNY 750ML TROPICAL</t>
+  </si>
+  <si>
+    <t>REFRIG ANTARCTICA PET 600ML GUARANA DIET</t>
+  </si>
+  <si>
+    <t>REFRIG SODA LIMONADA LT 350ML</t>
+  </si>
+  <si>
+    <t>KETCHUP HEINZ 397G TRAD</t>
+  </si>
+  <si>
+    <t>AREIA HIG PIPICAT 4KG P GATOS</t>
+  </si>
+  <si>
+    <t>AGUA SABORIZ H2OH 500ML LIMONETO</t>
+  </si>
+  <si>
+    <t>FRALDA PAMPERS SUPERSEQUINHA C 50 XXG</t>
+  </si>
+  <si>
+    <t>FAROFA DINDA 200G BACON</t>
+  </si>
+  <si>
+    <t>FAROFA DINDA 200G PICANHA</t>
+  </si>
+  <si>
+    <t>FARINHA TAPIOCA DINDA 400G TRAD</t>
+  </si>
+  <si>
+    <t>CERV BRAHMA ZERO LT 350ML</t>
+  </si>
+  <si>
+    <t>ICE SMIRNOFF LN 275ML LIMAO</t>
+  </si>
+  <si>
+    <t>GATORADE ZERO 350ML LARANJA LIMA</t>
+  </si>
+  <si>
+    <t>REFRIG SUKITA PET 200ML</t>
+  </si>
+  <si>
+    <t>BISC RECH NESTLE NEGRESCO 90G BAUNILHA</t>
+  </si>
+  <si>
+    <t>WAFER GIRASSOL 60G CHOC</t>
+  </si>
+  <si>
+    <t>CHA PRENDA 12G HIBISCUS</t>
+  </si>
+  <si>
+    <t>AZEITONA VERDE UNIAGRO SH 500G FATIADA</t>
+  </si>
+  <si>
+    <t>ERVILHA OLE LT 170G</t>
+  </si>
+  <si>
+    <t>CR DEN COLGATE MPA 180G</t>
+  </si>
+  <si>
+    <t>LEITE UHT STA CLARA INT 1L</t>
+  </si>
+  <si>
+    <t>DESOD ROLLON REXONA 50ML XTRA COOL</t>
+  </si>
+  <si>
+    <t>FRALDA PAMPERS SUPERSEQUINHA C 68 M</t>
+  </si>
+  <si>
+    <t>DESINF SUPREMA EUCALIPITO 5L</t>
+  </si>
+  <si>
+    <t>ACUCAR CRISTAL UNIAO 1KG</t>
+  </si>
+  <si>
+    <t>BATATA PALHA YOKI TRAD 70G</t>
+  </si>
+  <si>
+    <t>SALG OBBA 100G REQUEIJAO</t>
+  </si>
+  <si>
+    <t>ESC DENTAL SORRISO MACIA</t>
+  </si>
+  <si>
+    <t>CAPSULA DOLCE GUSTO 170G C 10 CAPP DOCE LEITE</t>
+  </si>
+  <si>
+    <t>CERV PATAGONIA IPA LT 473ML</t>
+  </si>
+  <si>
+    <t>FRALDA CONFORTSEC PAMPERS XG 34UN</t>
+  </si>
+  <si>
+    <t>BATATA PALHA YOKI TRAD L105P90 105G</t>
+  </si>
+  <si>
+    <t>CHA PRENDA 10G CAMOMILA</t>
+  </si>
+  <si>
+    <t>ACUCAR MASCAVO CBS 500G</t>
+  </si>
+  <si>
+    <t>ALCOOL 46 COPERALCOOL 1L TRAD</t>
   </si>
   <si>
     <t>COND JAY LUC 1L NEUTRO</t>
   </si>
   <si>
-    <t>DESINF GOTA LIMPA 2L LIMAO</t>
-  </si>
-  <si>
-    <t>DESINF GOTA LIMPA 500ML LAVANDA</t>
-  </si>
-  <si>
-    <t>BISC RECH NESTLE NEGRESCO 90G BAUNILHA</t>
-  </si>
-  <si>
-    <t>REFRIG PEPSI PET 2L</t>
-  </si>
-  <si>
-    <t>TINT COR E TON PRETO 2 0</t>
-  </si>
-  <si>
-    <t>TEMP BICARBONATO SODIO APTI 100G</t>
-  </si>
-  <si>
-    <t>LEITE UHT STA CLARA INT 1L</t>
-  </si>
-  <si>
-    <t>CHOC BARRA LACTA 145G LAKA OREO</t>
-  </si>
-  <si>
-    <t>CERV BRAHMA CHOPP GF 1L RETORNAVEL</t>
-  </si>
-  <si>
-    <t>MILHO VERDE OLE LT 170G</t>
-  </si>
-  <si>
-    <t>CEREAL MAT NESTLE SH 210G NESTON 3 CEREAIS</t>
-  </si>
-  <si>
-    <t>ACHOC PO APTI SH 700G INSTANT POWER</t>
-  </si>
-  <si>
-    <t>QJO RAL SANTA CLARA 40G PARMESAO</t>
-  </si>
-  <si>
-    <t>BOMBOM AMOR CARIOCA 20G</t>
-  </si>
-  <si>
-    <t>AGUA MIN FLORESTA PET 500ML C GAS</t>
-  </si>
-  <si>
-    <t>AZEITE OLIV BORGES EXT VG 500ML</t>
-  </si>
-  <si>
-    <t>BISC SALG ZEZE 300G FOLHADO</t>
-  </si>
-  <si>
-    <t>CHANTILLY FLESCHMANN 200ML GRAN FINALE</t>
-  </si>
-  <si>
-    <t>CERV ANTARCTICA SUBZERO LT 473ML</t>
-  </si>
-  <si>
-    <t>AMAC GIRANDO SOL 2L AZUL</t>
+    <t>FRALDA MILI JUMBINHO M 22UN</t>
+  </si>
+  <si>
+    <t>AMAC APYCE 5L TRAD AZL</t>
+  </si>
+  <si>
+    <t>FRALDA DESC PAMPERS CONFORT G C 60</t>
+  </si>
+  <si>
+    <t>SH PANTENE 175ML EQUIL ALGA MAR</t>
+  </si>
+  <si>
+    <t>AMAC DOWNY 1 5L ALFAZEMA</t>
   </si>
   <si>
     <t>AMAC GIRANDO SOL 2L BRANCO</t>
   </si>
   <si>
-    <t>AMAC GIRANDO SOL 2L VERMELHO</t>
-  </si>
-  <si>
-    <t>CERV ITAIPAVA MALZBIER LT 350ML</t>
-  </si>
-  <si>
-    <t>DESINF GIRANDO SOL 2L LIMAO</t>
-  </si>
-  <si>
-    <t>DESINF GIRANDO SOL 2L PINHO</t>
-  </si>
-  <si>
-    <t>DESINF GIRANDO SOL 2L TALCO</t>
-  </si>
-  <si>
-    <t>AMACIANTE GIRANDO SOL 500ML HIPOAL</t>
-  </si>
-  <si>
-    <t>LAVA ROUPA LIQ APYCE 3L MULTIACAO AZUL</t>
-  </si>
-  <si>
-    <t>DOCE N BONN PEZAO 1K PE MOLEQUE</t>
-  </si>
-  <si>
-    <t>CERV ORIGINAL LT 473ML</t>
-  </si>
-  <si>
-    <t>ABACAXI TRIANGULO RODELA 400G</t>
+    <t>DETERG GIRANDO SOL 500ML COCO</t>
+  </si>
+  <si>
+    <t>DESINF GIRANDO SOL 2L EUCALIPTO</t>
+  </si>
+  <si>
+    <t>DET LIQ GIRANDO SOL 500ML HIPOAL</t>
   </si>
   <si>
     <t>M</t>
@@ -390,67 +471,85 @@
     <t>L</t>
   </si>
   <si>
-    <t>17/10/2024</t>
+    <t>26/04/2025</t>
   </si>
   <si>
     <t>20/06/2025</t>
   </si>
   <si>
-    <t>29/10/2024</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
-    <t>20/02/2026</t>
-  </si>
-  <si>
-    <t>26/04/2025</t>
+    <t>18/09/2024</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>19/12/2025</t>
+  </si>
+  <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>23/10/2024</t>
+  </si>
+  <si>
+    <t>10/12/2024</t>
+  </si>
+  <si>
+    <t>21/02/2026</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>01/10/2024</t>
+  </si>
+  <si>
+    <t>09/10/2024</t>
+  </si>
+  <si>
+    <t>18/10/2024</t>
   </si>
   <si>
     <t>12/11/2024</t>
   </si>
   <si>
-    <t>21/10/2024</t>
-  </si>
-  <si>
-    <t>31/12/2024</t>
-  </si>
-  <si>
-    <t>19/08/2025</t>
-  </si>
-  <si>
-    <t>23/09/2024</t>
+    <t>19/11/2024</t>
+  </si>
+  <si>
+    <t>05/12/2024</t>
+  </si>
+  <si>
+    <t>07/12/2024</t>
   </si>
   <si>
     <t>09/12/2024</t>
   </si>
   <si>
-    <t>19/12/2024</t>
-  </si>
-  <si>
-    <t>17/12/2024</t>
-  </si>
-  <si>
-    <t>04/02/2026</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>24/10/2024</t>
-  </si>
-  <si>
-    <t>18/11/2024</t>
-  </si>
-  <si>
-    <t>20/12/2024</t>
-  </si>
-  <si>
-    <t>25/09/2024</t>
-  </si>
-  <si>
-    <t>26/09/2024</t>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>28/10/2024</t>
+  </si>
+  <si>
+    <t>24/12/2024</t>
+  </si>
+  <si>
+    <t>06/12/2024</t>
+  </si>
+  <si>
+    <t>03/12/2024</t>
+  </si>
+  <si>
+    <t>18/12/2024</t>
+  </si>
+  <si>
+    <t>10/07/2025</t>
+  </si>
+  <si>
+    <t>07/08/2025</t>
+  </si>
+  <si>
+    <t>08/12/2025</t>
   </si>
   <si>
     <t>Ativo</t>
@@ -459,207 +558,278 @@
     <t>12</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
-    <t>6</t>
+    <t>24</t>
   </si>
   <si>
     <t>66</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>4166</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1411</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>477</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>489</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>427</t>
+  </si>
+  <si>
+    <t>3333</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>930</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>10734</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>1212</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>2502</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>565</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>421</t>
-  </si>
-  <si>
-    <t>897</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>10204</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>1195</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>1948</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>418</t>
-  </si>
-  <si>
-    <t>1619</t>
-  </si>
-  <si>
-    <t>16800</t>
-  </si>
-  <si>
-    <t>323</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>3551</t>
-  </si>
-  <si>
-    <t>334</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>507</t>
-  </si>
-  <si>
-    <t>1778</t>
+    <t>107</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
+  </si>
+  <si>
+    <t>LATICINIOS TIROL LTDA.</t>
+  </si>
+  <si>
+    <t>SPAL IND BRAS BEBIDAS AS</t>
+  </si>
+  <si>
+    <t>AGUAS MINERAIS SARANDI LTDA</t>
+  </si>
+  <si>
+    <t>ONIZ DISTRIBUID LTDA SCJ</t>
   </si>
   <si>
     <t>CRBS AS CDD PELOTAS</t>
   </si>
   <si>
-    <t>REDOL ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>STELLA DORO ALIMENTOS LTDA</t>
+    <t>KASADOCE DISTRIBUIDORA DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>DZ PETS LTDA</t>
   </si>
   <si>
     <t>ROCHA E FILHOS LTDA</t>
   </si>
   <si>
+    <t>NW DISTRIBUIDORA DE BEBIDAS LTDA EPP</t>
+  </si>
+  <si>
+    <t>NESTLE BRASIL LTDA</t>
+  </si>
+  <si>
+    <t>IND E COM DE ALIMENTOS FUCHINA LTDA</t>
+  </si>
+  <si>
+    <t>CHA PRENDA DO BRASIL IND E COM EIRELI</t>
+  </si>
+  <si>
+    <t>UNIAGRO -IND.E COM.DE PROD.ALIM.LTDA</t>
+  </si>
+  <si>
+    <t>ANGELO AURICCHIO &amp; CIA LTDA</t>
+  </si>
+  <si>
+    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
+  </si>
+  <si>
+    <t>COOP SANTA CLARA LTDA IND DE LATICINIOS</t>
+  </si>
+  <si>
+    <t>SOBEL INDUSTRIA E COMERCIO DE PRODUTOS DE LIMPEZA LTDA</t>
+  </si>
+  <si>
+    <t>ATACADAO S.A.</t>
+  </si>
+  <si>
+    <t>FABIANO ZAFFALON E CIA LTDA</t>
+  </si>
+  <si>
+    <t>FITOS ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>PODAL IND E COM DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>MENON COMERCIO E REPRESENTACOES LTDA</t>
+  </si>
+  <si>
     <t>CDC INDUSTRIA DE COSMETICOS LTDA</t>
   </si>
   <si>
-    <t>BERTOLINI INDUSTRIA QUIMICA LTDA</t>
-  </si>
-  <si>
-    <t>NESTLE BRASIL LTDA</t>
-  </si>
-  <si>
-    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
-  </si>
-  <si>
-    <t>APTI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>COOP SANTA CLARA LTDA IND DE LATICINIOS</t>
-  </si>
-  <si>
-    <t>TOPFLEX DISTRIBUIDOR DE ALIMENTOS</t>
-  </si>
-  <si>
-    <t>ANGELO AURICCHIO &amp; CIA LTDA</t>
-  </si>
-  <si>
-    <t>VONPAR ALIMENTOS S.A</t>
-  </si>
-  <si>
-    <t>AGUAS MINERAIS SARANDI LTDA</t>
-  </si>
-  <si>
-    <t>CARGIL AGRICOLA S A GOIANI</t>
-  </si>
-  <si>
-    <t>IRMAOS RUIVO LTDA</t>
-  </si>
-  <si>
-    <t>CASPER DISTR DE PROD ALIMENTICIOS LTDA</t>
+    <t>MILI S/A</t>
   </si>
   <si>
     <t>IND COM PROD LIMP GIRANDO SOL LTDA</t>
-  </si>
-  <si>
-    <t>CERVEJARIA PETROPOLIS S/A</t>
-  </si>
-  <si>
-    <t>ALIMENTOS N BONN LTDA</t>
-  </si>
-  <si>
-    <t>DOCE MINEIRO LTDA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -687,8 +857,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -993,83 +1164,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1078,126 +1249,126 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G2" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="H2" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I2" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="J2">
         <v>12</v>
       </c>
       <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>189</v>
+      </c>
+      <c r="P2">
+        <v>12</v>
+      </c>
+      <c r="Q2">
+        <v>24</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>90</v>
+      </c>
+      <c r="U2">
+        <v>9379</v>
+      </c>
+      <c r="V2" t="s">
+        <v>236</v>
+      </c>
+      <c r="W2">
         <v>2</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>36</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>153</v>
-      </c>
-      <c r="P2">
-        <v>44</v>
-      </c>
-      <c r="Q2">
-        <v>68</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>90</v>
-      </c>
-      <c r="U2">
-        <v>9638</v>
-      </c>
-      <c r="V2" t="s">
-        <v>187</v>
-      </c>
-      <c r="W2">
-        <v>3</v>
-      </c>
       <c r="X2">
-        <v>5</v>
+        <v>872</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
         <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G3" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="H3" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I3" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="J3">
         <v>12</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>294</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>145</v>
+        <v>190</v>
       </c>
       <c r="P3">
-        <v>10</v>
+        <v>480</v>
       </c>
       <c r="Q3">
-        <v>22</v>
+        <v>600</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1209,51 +1380,51 @@
         <v>90</v>
       </c>
       <c r="U3">
-        <v>15886</v>
+        <v>15208</v>
       </c>
       <c r="V3" t="s">
-        <v>188</v>
+        <v>237</v>
       </c>
       <c r="W3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="X3">
-        <v>9</v>
+        <v>5671</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="H4" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I4" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="J4">
         <v>12</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1265,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="P4">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="Q4">
-        <v>22</v>
+        <v>258</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1283,69 +1454,69 @@
         <v>90</v>
       </c>
       <c r="U4">
-        <v>11515</v>
+        <v>15441</v>
       </c>
       <c r="V4" t="s">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="W4">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" t="s">
+        <v>145</v>
+      </c>
+      <c r="G5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>30</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>193</v>
+      </c>
+      <c r="P5">
         <v>34</v>
       </c>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" t="s">
-        <v>118</v>
-      </c>
-      <c r="G5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H5" t="s">
-        <v>141</v>
-      </c>
-      <c r="I5" t="s">
-        <v>143</v>
-      </c>
-      <c r="J5">
-        <v>20</v>
-      </c>
-      <c r="K5">
-        <v>10</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>155</v>
-      </c>
-      <c r="P5">
-        <v>12</v>
-      </c>
       <c r="Q5">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1357,51 +1528,51 @@
         <v>90</v>
       </c>
       <c r="U5">
-        <v>21894</v>
+        <v>10181</v>
       </c>
       <c r="V5" t="s">
-        <v>190</v>
+        <v>239</v>
       </c>
       <c r="W5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G6" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="H6" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I6" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="J6">
         <v>12</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1413,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="P6">
         <v>10</v>
@@ -1431,16 +1602,16 @@
         <v>90</v>
       </c>
       <c r="U6">
-        <v>18958</v>
+        <v>6644</v>
       </c>
       <c r="V6" t="s">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="W6">
         <v>2</v>
       </c>
       <c r="X6">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -1451,70 +1622,70 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="H7" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I7" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>-8</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>24</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>195</v>
+      </c>
+      <c r="P7">
+        <v>32</v>
+      </c>
+      <c r="Q7">
+        <v>56</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>90</v>
+      </c>
+      <c r="U7">
+        <v>9638</v>
+      </c>
+      <c r="V7" t="s">
+        <v>241</v>
+      </c>
+      <c r="W7">
+        <v>3</v>
+      </c>
+      <c r="X7">
         <v>6</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>157</v>
-      </c>
-      <c r="P7">
-        <v>10</v>
-      </c>
-      <c r="Q7">
-        <v>16</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>90</v>
-      </c>
-      <c r="U7">
-        <v>14468</v>
-      </c>
-      <c r="V7" t="s">
-        <v>192</v>
-      </c>
-      <c r="W7">
-        <v>2</v>
-      </c>
-      <c r="X7">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -1525,31 +1696,31 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="F8" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G8" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="H8" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I8" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="J8">
         <v>12</v>
       </c>
       <c r="K8">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1561,13 +1732,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="P8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1579,16 +1750,16 @@
         <v>90</v>
       </c>
       <c r="U8">
-        <v>14468</v>
+        <v>9638</v>
       </c>
       <c r="V8" t="s">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="W8">
         <v>2</v>
       </c>
       <c r="X8">
-        <v>17.920000000000002</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -1602,47 +1773,47 @@
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="F9" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G9" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="H9" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I9" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="J9">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="K9">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N9">
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="P9">
+        <v>24</v>
+      </c>
+      <c r="Q9">
         <v>40</v>
       </c>
-      <c r="Q9">
-        <v>106</v>
-      </c>
       <c r="R9">
         <v>0</v>
       </c>
@@ -1653,69 +1824,69 @@
         <v>90</v>
       </c>
       <c r="U9">
-        <v>15134</v>
+        <v>10142</v>
       </c>
       <c r="V9" t="s">
-        <v>193</v>
+        <v>242</v>
       </c>
       <c r="W9">
         <v>2</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F10" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G10" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="H10" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I10" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="P10">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="Q10">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1727,51 +1898,51 @@
         <v>90</v>
       </c>
       <c r="U10">
-        <v>9638</v>
+        <v>8423</v>
       </c>
       <c r="V10" t="s">
-        <v>187</v>
+        <v>243</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="X10">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G11" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="H11" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I11" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="J11">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1783,13 +1954,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="P11">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="Q11">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1801,69 +1972,69 @@
         <v>90</v>
       </c>
       <c r="U11">
-        <v>21894</v>
+        <v>9638</v>
       </c>
       <c r="V11" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="W11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F12" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="G12" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="H12" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I12" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>200</v>
+      </c>
+      <c r="P12">
         <v>4</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>162</v>
-      </c>
-      <c r="P12">
-        <v>6</v>
-      </c>
       <c r="Q12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1875,16 +2046,16 @@
         <v>90</v>
       </c>
       <c r="U12">
-        <v>5894</v>
+        <v>6644</v>
       </c>
       <c r="V12" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="W12">
         <v>2</v>
       </c>
       <c r="X12">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -1895,31 +2066,31 @@
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="F13" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G13" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="H13" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I13" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="J13">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K13">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1928,16 +2099,16 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O13" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="P13">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="Q13">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1949,51 +2120,51 @@
         <v>90</v>
       </c>
       <c r="U13">
-        <v>10189</v>
+        <v>21894</v>
       </c>
       <c r="V13" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="W13">
         <v>2</v>
       </c>
       <c r="X13">
-        <v>20</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="H14" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I14" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K14">
-        <v>709</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2005,13 +2176,13 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="P14">
-        <v>720</v>
+        <v>21</v>
       </c>
       <c r="Q14">
-        <v>1020</v>
+        <v>46</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -2023,16 +2194,16 @@
         <v>90</v>
       </c>
       <c r="U14">
-        <v>10421</v>
+        <v>21894</v>
       </c>
       <c r="V14" t="s">
-        <v>196</v>
+        <v>244</v>
       </c>
       <c r="W14">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="X14">
-        <v>5717</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -2043,31 +2214,31 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="F15" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G15" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="H15" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I15" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="J15">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K15">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2079,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="P15">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Q15">
         <v>50</v>
@@ -2097,69 +2268,69 @@
         <v>90</v>
       </c>
       <c r="U15">
-        <v>13838</v>
+        <v>21894</v>
       </c>
       <c r="V15" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="W15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G16" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="H16" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I16" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
       <c r="K16">
-        <v>-65</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="P16">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="Q16">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -2174,13 +2345,13 @@
         <v>9638</v>
       </c>
       <c r="V16" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="W16">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="X16">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
@@ -2191,31 +2362,31 @@
         <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="F17" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="G17" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="H17" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I17" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2227,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Q17">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2245,51 +2416,51 @@
         <v>90</v>
       </c>
       <c r="U17">
-        <v>5894</v>
+        <v>21845</v>
       </c>
       <c r="V17" t="s">
-        <v>194</v>
+        <v>245</v>
       </c>
       <c r="W17">
         <v>2</v>
       </c>
       <c r="X17">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F18" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G18" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="H18" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I18" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="J18">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K18">
-        <v>143</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2301,13 +2472,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="P18">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -2319,143 +2490,143 @@
         <v>90</v>
       </c>
       <c r="U18">
-        <v>7715</v>
+        <v>9638</v>
       </c>
       <c r="V18" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="W18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X18">
-        <v>623</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="F19" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G19" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="H19" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I19" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="J19">
         <v>12</v>
       </c>
       <c r="K19">
+        <v>4</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>206</v>
+      </c>
+      <c r="P19">
+        <v>26</v>
+      </c>
+      <c r="Q19">
+        <v>38</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>90</v>
+      </c>
+      <c r="U19">
+        <v>9638</v>
+      </c>
+      <c r="V19" t="s">
+        <v>241</v>
+      </c>
+      <c r="W19">
+        <v>3</v>
+      </c>
+      <c r="X19">
         <v>8</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>169</v>
-      </c>
-      <c r="P19">
-        <v>10</v>
-      </c>
-      <c r="Q19">
-        <v>22</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>90</v>
-      </c>
-      <c r="U19">
-        <v>15134</v>
-      </c>
-      <c r="V19" t="s">
-        <v>193</v>
-      </c>
-      <c r="W19">
-        <v>2</v>
-      </c>
-      <c r="X19">
-        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G20" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="H20" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I20" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="J20">
         <v>12</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N20">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>170</v>
+        <v>61</v>
       </c>
       <c r="P20">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="Q20">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -2467,16 +2638,16 @@
         <v>90</v>
       </c>
       <c r="U20">
-        <v>10189</v>
+        <v>9638</v>
       </c>
       <c r="V20" t="s">
-        <v>195</v>
+        <v>241</v>
       </c>
       <c r="W20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X20">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -2484,34 +2655,34 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="F21" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G21" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="H21" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I21" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="J21">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="K21">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -2523,13 +2694,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="P21">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="Q21">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -2541,16 +2712,16 @@
         <v>90</v>
       </c>
       <c r="U21">
-        <v>10421</v>
+        <v>15134</v>
       </c>
       <c r="V21" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="W21">
         <v>2</v>
       </c>
       <c r="X21">
-        <v>107</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -2558,52 +2729,52 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="F22" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G22" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="H22" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I22" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="J22">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="K22">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="P22">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="Q22">
-        <v>480</v>
+        <v>336</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -2615,69 +2786,69 @@
         <v>90</v>
       </c>
       <c r="U22">
-        <v>6703</v>
+        <v>9613</v>
       </c>
       <c r="V22" t="s">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="W22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F23" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G23" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="H23" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I23" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="J23">
+        <v>20</v>
+      </c>
+      <c r="K23">
+        <v>10</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>209</v>
+      </c>
+      <c r="P23">
         <v>12</v>
       </c>
-      <c r="K23">
-        <v>-7</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>108</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>173</v>
-      </c>
-      <c r="P23">
-        <v>144</v>
-      </c>
       <c r="Q23">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -2689,16 +2860,16 @@
         <v>90</v>
       </c>
       <c r="U23">
-        <v>10181</v>
+        <v>10153</v>
       </c>
       <c r="V23" t="s">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X23">
-        <v>9.17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
@@ -2706,34 +2877,34 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="F24" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G24" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="H24" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I24" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="J24">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -2745,13 +2916,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="P24">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2763,16 +2934,16 @@
         <v>90</v>
       </c>
       <c r="U24">
-        <v>15139</v>
+        <v>14718</v>
       </c>
       <c r="V24" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
       <c r="W24">
         <v>2</v>
       </c>
       <c r="X24">
-        <v>106</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
@@ -2783,31 +2954,31 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G25" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="H25" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I25" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="J25">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2819,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
       <c r="P25">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="Q25">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2837,51 +3008,51 @@
         <v>90</v>
       </c>
       <c r="U25">
-        <v>14588</v>
+        <v>7715</v>
       </c>
       <c r="V25" t="s">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="W25">
         <v>2</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F26" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G26" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H26" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I26" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="J26">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="K26">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2893,13 +3064,13 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="P26">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="Q26">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -2911,51 +3082,51 @@
         <v>90</v>
       </c>
       <c r="U26">
-        <v>13762</v>
+        <v>5894</v>
       </c>
       <c r="V26" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="W26">
         <v>2</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
         <v>105</v>
       </c>
       <c r="F27" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G27" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="H27" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I27" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="J27">
         <v>12</v>
       </c>
       <c r="K27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2967,19 +3138,19 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="P27">
-        <v>360</v>
+        <v>26</v>
       </c>
       <c r="Q27">
-        <v>480</v>
+        <v>38</v>
       </c>
       <c r="R27">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>1320</v>
+        <v>0</v>
       </c>
       <c r="T27">
         <v>90</v>
@@ -2988,48 +3159,48 @@
         <v>9638</v>
       </c>
       <c r="V27" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="W27">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="X27">
-        <v>573.41999999999996</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E28" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="F28" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G28" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="H28" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I28" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="J28">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K28">
-        <v>35</v>
+        <v>699</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -3041,13 +3212,13 @@
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="P28">
-        <v>36</v>
+        <v>720</v>
       </c>
       <c r="Q28">
-        <v>60</v>
+        <v>1020</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -3059,51 +3230,51 @@
         <v>90</v>
       </c>
       <c r="U28">
-        <v>10334</v>
+        <v>10421</v>
       </c>
       <c r="V28" t="s">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="X28">
-        <v>23</v>
+        <v>7561</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="F29" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G29" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="H29" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I29" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="J29">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K29">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3115,13 +3286,13 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="P29">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q29">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -3133,51 +3304,51 @@
         <v>90</v>
       </c>
       <c r="U29">
-        <v>10334</v>
+        <v>5894</v>
       </c>
       <c r="V29" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="W29">
         <v>2</v>
       </c>
       <c r="X29">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E30" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F30" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G30" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="H30" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I30" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3189,13 +3360,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="P30">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Q30">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -3207,51 +3378,51 @@
         <v>90</v>
       </c>
       <c r="U30">
-        <v>10334</v>
+        <v>6644</v>
       </c>
       <c r="V30" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="W30">
         <v>2</v>
       </c>
       <c r="X30">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s">
         <v>73</v>
       </c>
       <c r="E31" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G31" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="H31" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I31" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="J31">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3263,13 +3434,13 @@
         <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="P31">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -3281,70 +3452,70 @@
         <v>90</v>
       </c>
       <c r="U31">
-        <v>5391</v>
+        <v>6644</v>
       </c>
       <c r="V31" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="W31">
         <v>3</v>
       </c>
       <c r="X31">
-        <v>125</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s">
         <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F32" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G32" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="H32" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I32" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="J32">
+        <v>3</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>216</v>
+      </c>
+      <c r="P32">
+        <v>3</v>
+      </c>
+      <c r="Q32">
         <v>6</v>
       </c>
-      <c r="K32">
-        <v>4</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>181</v>
-      </c>
-      <c r="P32">
-        <v>8</v>
-      </c>
-      <c r="Q32">
-        <v>14</v>
-      </c>
       <c r="R32">
         <v>0</v>
       </c>
@@ -3355,51 +3526,51 @@
         <v>90</v>
       </c>
       <c r="U32">
-        <v>10334</v>
+        <v>22168</v>
       </c>
       <c r="V32" t="s">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="W32">
         <v>2</v>
       </c>
       <c r="X32">
-        <v>36</v>
+        <v>116.33</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F33" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G33" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="H33" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I33" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3411,13 +3582,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="P33">
         <v>6</v>
       </c>
       <c r="Q33">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -3429,69 +3600,69 @@
         <v>90</v>
       </c>
       <c r="U33">
-        <v>10334</v>
+        <v>6644</v>
       </c>
       <c r="V33" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="W33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X33">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E34" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F34" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I34" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="J34">
+        <v>10</v>
+      </c>
+      <c r="K34">
+        <v>-7</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>217</v>
+      </c>
+      <c r="P34">
         <v>6</v>
       </c>
-      <c r="K34">
-        <v>6</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34" t="s">
-        <v>183</v>
-      </c>
-      <c r="P34">
-        <v>12</v>
-      </c>
       <c r="Q34">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -3503,51 +3674,51 @@
         <v>90</v>
       </c>
       <c r="U34">
-        <v>10334</v>
+        <v>11112</v>
       </c>
       <c r="V34" t="s">
-        <v>204</v>
+        <v>254</v>
       </c>
       <c r="W34">
         <v>2</v>
       </c>
       <c r="X34">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E35" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F35" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="H35" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I35" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="J35">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K35">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3559,13 +3730,13 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="P35">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="Q35">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -3577,70 +3748,70 @@
         <v>90</v>
       </c>
       <c r="U35">
-        <v>10334</v>
+        <v>3527</v>
       </c>
       <c r="V35" t="s">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="W35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E36" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F36" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G36" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="H36" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I36" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>218</v>
+      </c>
+      <c r="P36">
+        <v>14</v>
+      </c>
+      <c r="Q36">
         <v>24</v>
       </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36" t="s">
-        <v>185</v>
-      </c>
-      <c r="P36">
-        <v>52</v>
-      </c>
-      <c r="Q36">
-        <v>80</v>
-      </c>
       <c r="R36">
         <v>0</v>
       </c>
@@ -3651,16 +3822,16 @@
         <v>90</v>
       </c>
       <c r="U36">
-        <v>5894</v>
+        <v>16857</v>
       </c>
       <c r="V36" t="s">
-        <v>194</v>
+        <v>256</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="X36">
-        <v>86</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
@@ -3668,52 +3839,52 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E37" t="s">
         <v>115</v>
       </c>
       <c r="F37" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G37" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="H37" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I37" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="J37">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="K37">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N37">
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>59</v>
+        <v>219</v>
       </c>
       <c r="P37">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="Q37">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -3725,51 +3896,51 @@
         <v>90</v>
       </c>
       <c r="U37">
-        <v>3818</v>
+        <v>9613</v>
       </c>
       <c r="V37" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="W37">
         <v>2</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E38" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F38" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="G38" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H38" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I38" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="J38">
         <v>12</v>
       </c>
       <c r="K38">
-        <v>-71</v>
+        <v>8</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -3781,13 +3952,13 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="P38">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>228</v>
+        <v>22</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -3799,94 +3970,1500 @@
         <v>90</v>
       </c>
       <c r="U38">
-        <v>9638</v>
+        <v>15318</v>
       </c>
       <c r="V38" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="W38">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="X38">
-        <v>864</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" t="s">
+        <v>99</v>
+      </c>
+      <c r="F39" t="s">
+        <v>145</v>
+      </c>
+      <c r="G39" t="s">
+        <v>150</v>
+      </c>
+      <c r="H39" t="s">
+        <v>174</v>
+      </c>
+      <c r="I39" t="s">
+        <v>176</v>
+      </c>
+      <c r="J39">
+        <v>4</v>
+      </c>
+      <c r="K39">
+        <v>38</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>221</v>
+      </c>
+      <c r="P39">
+        <v>46</v>
+      </c>
+      <c r="Q39">
+        <v>74</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>90</v>
+      </c>
+      <c r="U39">
+        <v>10181</v>
+      </c>
+      <c r="V39" t="s">
+        <v>239</v>
+      </c>
+      <c r="W39">
+        <v>9</v>
+      </c>
+      <c r="X39">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>25</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40" t="s">
+        <v>145</v>
+      </c>
+      <c r="G40" t="s">
+        <v>168</v>
+      </c>
+      <c r="H40" t="s">
+        <v>174</v>
+      </c>
+      <c r="I40" t="s">
+        <v>178</v>
+      </c>
+      <c r="J40">
+        <v>6</v>
+      </c>
+      <c r="K40">
+        <v>12</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" t="s">
+        <v>222</v>
+      </c>
+      <c r="P40">
+        <v>14</v>
+      </c>
+      <c r="Q40">
+        <v>20</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>90</v>
+      </c>
+      <c r="U40">
+        <v>15134</v>
+      </c>
+      <c r="V40" t="s">
+        <v>246</v>
+      </c>
+      <c r="W40">
+        <v>2</v>
+      </c>
+      <c r="X40">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" t="s">
+        <v>129</v>
+      </c>
+      <c r="F41" t="s">
+        <v>145</v>
+      </c>
+      <c r="G41" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" t="s">
+        <v>174</v>
+      </c>
+      <c r="I41" t="s">
+        <v>178</v>
+      </c>
+      <c r="J41">
+        <v>6</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>223</v>
+      </c>
+      <c r="P41">
+        <v>6</v>
+      </c>
+      <c r="Q41">
+        <v>12</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>90</v>
+      </c>
+      <c r="U41">
+        <v>9638</v>
+      </c>
+      <c r="V41" t="s">
+        <v>241</v>
+      </c>
+      <c r="W41">
+        <v>2</v>
+      </c>
+      <c r="X41">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" t="s">
+        <v>130</v>
+      </c>
+      <c r="F42" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" t="s">
+        <v>147</v>
+      </c>
+      <c r="H42" t="s">
+        <v>174</v>
+      </c>
+      <c r="I42" t="s">
+        <v>176</v>
+      </c>
+      <c r="J42">
+        <v>4</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>188</v>
+      </c>
+      <c r="P42">
+        <v>8</v>
+      </c>
+      <c r="Q42">
+        <v>12</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>90</v>
+      </c>
+      <c r="U42">
+        <v>6644</v>
+      </c>
+      <c r="V42" t="s">
+        <v>240</v>
+      </c>
+      <c r="W42">
+        <v>3</v>
+      </c>
+      <c r="X42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" t="s">
+        <v>131</v>
+      </c>
+      <c r="F43" t="s">
+        <v>145</v>
+      </c>
+      <c r="G43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H43" t="s">
+        <v>174</v>
+      </c>
+      <c r="I43" t="s">
+        <v>180</v>
+      </c>
+      <c r="J43">
+        <v>20</v>
+      </c>
+      <c r="K43">
+        <v>76</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>224</v>
+      </c>
+      <c r="P43">
+        <v>80</v>
+      </c>
+      <c r="Q43">
+        <v>100</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>90</v>
+      </c>
+      <c r="U43">
+        <v>3527</v>
+      </c>
+      <c r="V43" t="s">
+        <v>255</v>
+      </c>
+      <c r="W43">
+        <v>2</v>
+      </c>
+      <c r="X43">
+        <v>126.85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" t="s">
+        <v>132</v>
+      </c>
+      <c r="F44" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" t="s">
+        <v>169</v>
+      </c>
+      <c r="H44" t="s">
+        <v>174</v>
+      </c>
+      <c r="I44" t="s">
+        <v>180</v>
+      </c>
+      <c r="J44">
+        <v>20</v>
+      </c>
+      <c r="K44">
+        <v>6</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>225</v>
+      </c>
+      <c r="P44">
+        <v>40</v>
+      </c>
+      <c r="Q44">
+        <v>60</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>90</v>
+      </c>
+      <c r="U44">
+        <v>10153</v>
+      </c>
+      <c r="V44" t="s">
+        <v>248</v>
+      </c>
+      <c r="W44">
+        <v>3</v>
+      </c>
+      <c r="X44">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" t="s">
+        <v>133</v>
+      </c>
+      <c r="F45" t="s">
+        <v>145</v>
+      </c>
+      <c r="G45" t="s">
+        <v>170</v>
+      </c>
+      <c r="H45" t="s">
+        <v>174</v>
+      </c>
+      <c r="I45" t="s">
+        <v>180</v>
+      </c>
+      <c r="J45">
+        <v>20</v>
+      </c>
+      <c r="K45">
+        <v>29</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>226</v>
+      </c>
+      <c r="P45">
         <v>30</v>
       </c>
-      <c r="C39" t="s">
+      <c r="Q45">
+        <v>50</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>90</v>
+      </c>
+      <c r="U45">
+        <v>5894</v>
+      </c>
+      <c r="V45" t="s">
+        <v>251</v>
+      </c>
+      <c r="W45">
+        <v>2</v>
+      </c>
+      <c r="X45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" t="s">
+        <v>134</v>
+      </c>
+      <c r="F46" t="s">
+        <v>145</v>
+      </c>
+      <c r="G46" t="s">
+        <v>147</v>
+      </c>
+      <c r="H46" t="s">
+        <v>174</v>
+      </c>
+      <c r="I46" t="s">
+        <v>175</v>
+      </c>
+      <c r="J46">
+        <v>12</v>
+      </c>
+      <c r="K46">
+        <v>31</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>220</v>
+      </c>
+      <c r="P46">
+        <v>36</v>
+      </c>
+      <c r="Q46">
+        <v>48</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>90</v>
+      </c>
+      <c r="U46">
+        <v>10617</v>
+      </c>
+      <c r="V46" t="s">
+        <v>258</v>
+      </c>
+      <c r="W46">
+        <v>2</v>
+      </c>
+      <c r="X46">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F47" t="s">
+        <v>145</v>
+      </c>
+      <c r="G47" t="s">
+        <v>147</v>
+      </c>
+      <c r="H47" t="s">
+        <v>174</v>
+      </c>
+      <c r="I47" t="s">
+        <v>178</v>
+      </c>
+      <c r="J47">
+        <v>6</v>
+      </c>
+      <c r="K47">
+        <v>5</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>227</v>
+      </c>
+      <c r="P47">
+        <v>6</v>
+      </c>
+      <c r="Q47">
+        <v>12</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>90</v>
+      </c>
+      <c r="U47">
+        <v>9638</v>
+      </c>
+      <c r="V47" t="s">
+        <v>241</v>
+      </c>
+      <c r="W47">
+        <v>2</v>
+      </c>
+      <c r="X47">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" t="s">
+        <v>135</v>
+      </c>
+      <c r="F48" t="s">
+        <v>145</v>
+      </c>
+      <c r="G48" t="s">
+        <v>147</v>
+      </c>
+      <c r="H48" t="s">
+        <v>174</v>
+      </c>
+      <c r="I48" t="s">
+        <v>175</v>
+      </c>
+      <c r="J48">
+        <v>12</v>
+      </c>
+      <c r="K48">
+        <v>3</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>177</v>
+      </c>
+      <c r="P48">
+        <v>10</v>
+      </c>
+      <c r="Q48">
+        <v>22</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>90</v>
+      </c>
+      <c r="U48">
+        <v>18958</v>
+      </c>
+      <c r="V48" t="s">
+        <v>259</v>
+      </c>
+      <c r="W48">
+        <v>2</v>
+      </c>
+      <c r="X48">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>27</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" t="s">
+        <v>87</v>
+      </c>
+      <c r="E49" t="s">
+        <v>136</v>
+      </c>
+      <c r="F49" t="s">
+        <v>145</v>
+      </c>
+      <c r="G49" t="s">
+        <v>147</v>
+      </c>
+      <c r="H49" t="s">
+        <v>174</v>
+      </c>
+      <c r="I49" t="s">
+        <v>187</v>
+      </c>
+      <c r="J49">
+        <v>9</v>
+      </c>
+      <c r="K49">
+        <v>4</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" t="s">
+        <v>179</v>
+      </c>
+      <c r="P49">
+        <v>7</v>
+      </c>
+      <c r="Q49">
+        <v>16</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>90</v>
+      </c>
+      <c r="U49">
+        <v>10190</v>
+      </c>
+      <c r="V49" t="s">
+        <v>260</v>
+      </c>
+      <c r="W49">
+        <v>2</v>
+      </c>
+      <c r="X49">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>27</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" t="s">
+        <v>88</v>
+      </c>
+      <c r="E50" t="s">
+        <v>137</v>
+      </c>
+      <c r="F50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G50" t="s">
+        <v>171</v>
+      </c>
+      <c r="H50" t="s">
+        <v>174</v>
+      </c>
+      <c r="I50" t="s">
+        <v>188</v>
+      </c>
+      <c r="J50">
+        <v>2</v>
+      </c>
+      <c r="K50">
+        <v>2</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50" t="s">
+        <v>228</v>
+      </c>
+      <c r="P50">
+        <v>4</v>
+      </c>
+      <c r="Q50">
+        <v>6</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>90</v>
+      </c>
+      <c r="U50">
+        <v>5894</v>
+      </c>
+      <c r="V50" t="s">
+        <v>251</v>
+      </c>
+      <c r="W50">
+        <v>2</v>
+      </c>
+      <c r="X50">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" t="s">
         <v>45</v>
       </c>
-      <c r="D39" t="s">
-        <v>81</v>
-      </c>
-      <c r="E39" t="s">
-        <v>117</v>
-      </c>
-      <c r="F39" t="s">
-        <v>118</v>
-      </c>
-      <c r="G39" t="s">
-        <v>121</v>
-      </c>
-      <c r="H39" t="s">
+      <c r="D51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" t="s">
+        <v>115</v>
+      </c>
+      <c r="F51" t="s">
+        <v>145</v>
+      </c>
+      <c r="G51" t="s">
+        <v>161</v>
+      </c>
+      <c r="H51" t="s">
+        <v>174</v>
+      </c>
+      <c r="I51" t="s">
+        <v>183</v>
+      </c>
+      <c r="J51">
+        <v>50</v>
+      </c>
+      <c r="K51">
+        <v>44</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>100</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51" t="s">
+        <v>229</v>
+      </c>
+      <c r="P51">
+        <v>150</v>
+      </c>
+      <c r="Q51">
+        <v>200</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>90</v>
+      </c>
+      <c r="U51">
+        <v>9613</v>
+      </c>
+      <c r="V51" t="s">
+        <v>247</v>
+      </c>
+      <c r="W51">
+        <v>2</v>
+      </c>
+      <c r="X51">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52" t="s">
+        <v>89</v>
+      </c>
+      <c r="E52" t="s">
+        <v>138</v>
+      </c>
+      <c r="F52" t="s">
+        <v>145</v>
+      </c>
+      <c r="G52" t="s">
+        <v>147</v>
+      </c>
+      <c r="H52" t="s">
+        <v>174</v>
+      </c>
+      <c r="I52" t="s">
+        <v>188</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52">
+        <v>-2</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52" t="s">
+        <v>188</v>
+      </c>
+      <c r="P52">
+        <v>2</v>
+      </c>
+      <c r="Q52">
+        <v>4</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>90</v>
+      </c>
+      <c r="U52">
+        <v>6644</v>
+      </c>
+      <c r="V52" t="s">
+        <v>240</v>
+      </c>
+      <c r="W52">
+        <v>2</v>
+      </c>
+      <c r="X52">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>27</v>
+      </c>
+      <c r="B53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" t="s">
+        <v>90</v>
+      </c>
+      <c r="E53" t="s">
+        <v>139</v>
+      </c>
+      <c r="F53" t="s">
+        <v>145</v>
+      </c>
+      <c r="G53" t="s">
+        <v>147</v>
+      </c>
+      <c r="H53" t="s">
+        <v>174</v>
+      </c>
+      <c r="I53" t="s">
+        <v>178</v>
+      </c>
+      <c r="J53">
+        <v>6</v>
+      </c>
+      <c r="K53">
+        <v>5</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53" t="s">
+        <v>230</v>
+      </c>
+      <c r="P53">
+        <v>6</v>
+      </c>
+      <c r="Q53">
+        <v>12</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>90</v>
+      </c>
+      <c r="U53">
+        <v>6644</v>
+      </c>
+      <c r="V53" t="s">
+        <v>240</v>
+      </c>
+      <c r="W53">
+        <v>2</v>
+      </c>
+      <c r="X53">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" t="s">
+        <v>45</v>
+      </c>
+      <c r="D54" t="s">
+        <v>91</v>
+      </c>
+      <c r="E54" t="s">
+        <v>140</v>
+      </c>
+      <c r="F54" t="s">
+        <v>145</v>
+      </c>
+      <c r="G54" t="s">
+        <v>172</v>
+      </c>
+      <c r="H54" t="s">
+        <v>174</v>
+      </c>
+      <c r="I54" t="s">
+        <v>187</v>
+      </c>
+      <c r="J54">
+        <v>9</v>
+      </c>
+      <c r="K54">
+        <v>15</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54" t="s">
+        <v>231</v>
+      </c>
+      <c r="P54">
+        <v>17</v>
+      </c>
+      <c r="Q54">
+        <v>26</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>90</v>
+      </c>
+      <c r="U54">
+        <v>6644</v>
+      </c>
+      <c r="V54" t="s">
+        <v>240</v>
+      </c>
+      <c r="W54">
+        <v>2</v>
+      </c>
+      <c r="X54">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55" t="s">
+        <v>92</v>
+      </c>
+      <c r="E55" t="s">
         <v>141</v>
       </c>
-      <c r="I39" t="s">
+      <c r="F55" t="s">
+        <v>145</v>
+      </c>
+      <c r="G55" t="s">
+        <v>147</v>
+      </c>
+      <c r="H55" t="s">
+        <v>174</v>
+      </c>
+      <c r="I55" t="s">
+        <v>178</v>
+      </c>
+      <c r="J55">
+        <v>6</v>
+      </c>
+      <c r="K55">
+        <v>2</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55" t="s">
+        <v>232</v>
+      </c>
+      <c r="P55">
+        <v>12</v>
+      </c>
+      <c r="Q55">
+        <v>18</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>90</v>
+      </c>
+      <c r="U55">
+        <v>10334</v>
+      </c>
+      <c r="V55" t="s">
+        <v>261</v>
+      </c>
+      <c r="W55">
+        <v>3</v>
+      </c>
+      <c r="X55">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>27</v>
+      </c>
+      <c r="B56" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" t="s">
+        <v>46</v>
+      </c>
+      <c r="D56" t="s">
+        <v>93</v>
+      </c>
+      <c r="E56" t="s">
         <v>142</v>
       </c>
-      <c r="J39">
-        <v>12</v>
-      </c>
-      <c r="K39">
-        <v>51</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39" t="s">
-        <v>142</v>
-      </c>
-      <c r="P39">
-        <v>96</v>
-      </c>
-      <c r="Q39">
-        <v>120</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
-        <v>0</v>
-      </c>
-      <c r="T39">
-        <v>90</v>
-      </c>
-      <c r="U39">
-        <v>4959</v>
-      </c>
-      <c r="V39" t="s">
-        <v>207</v>
-      </c>
-      <c r="W39">
+      <c r="F56" t="s">
+        <v>145</v>
+      </c>
+      <c r="G56" t="s">
+        <v>147</v>
+      </c>
+      <c r="H56" t="s">
+        <v>174</v>
+      </c>
+      <c r="I56" t="s">
+        <v>181</v>
+      </c>
+      <c r="J56">
+        <v>24</v>
+      </c>
+      <c r="K56">
+        <v>44</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56" t="s">
+        <v>233</v>
+      </c>
+      <c r="P56">
+        <v>56</v>
+      </c>
+      <c r="Q56">
+        <v>80</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>90</v>
+      </c>
+      <c r="U56">
+        <v>10334</v>
+      </c>
+      <c r="V56" t="s">
+        <v>261</v>
+      </c>
+      <c r="W56">
+        <v>2</v>
+      </c>
+      <c r="X56">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" t="s">
+        <v>46</v>
+      </c>
+      <c r="D57" t="s">
+        <v>94</v>
+      </c>
+      <c r="E57" t="s">
+        <v>143</v>
+      </c>
+      <c r="F57" t="s">
+        <v>145</v>
+      </c>
+      <c r="G57" t="s">
+        <v>148</v>
+      </c>
+      <c r="H57" t="s">
+        <v>174</v>
+      </c>
+      <c r="I57" t="s">
+        <v>178</v>
+      </c>
+      <c r="J57">
         <v>6</v>
       </c>
-      <c r="X39">
-        <v>141</v>
+      <c r="K57">
+        <v>6</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57" t="s">
+        <v>234</v>
+      </c>
+      <c r="P57">
+        <v>8</v>
+      </c>
+      <c r="Q57">
+        <v>14</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>90</v>
+      </c>
+      <c r="U57">
+        <v>10334</v>
+      </c>
+      <c r="V57" t="s">
+        <v>261</v>
+      </c>
+      <c r="W57">
+        <v>2</v>
+      </c>
+      <c r="X57">
+        <v>16.170000000000002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" t="s">
+        <v>95</v>
+      </c>
+      <c r="E58" t="s">
+        <v>144</v>
+      </c>
+      <c r="F58" t="s">
+        <v>145</v>
+      </c>
+      <c r="G58" t="s">
+        <v>173</v>
+      </c>
+      <c r="H58" t="s">
+        <v>174</v>
+      </c>
+      <c r="I58" t="s">
+        <v>181</v>
+      </c>
+      <c r="J58">
+        <v>24</v>
+      </c>
+      <c r="K58">
+        <v>32</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58" t="s">
+        <v>235</v>
+      </c>
+      <c r="P58">
+        <v>44</v>
+      </c>
+      <c r="Q58">
+        <v>68</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>90</v>
+      </c>
+      <c r="U58">
+        <v>10334</v>
+      </c>
+      <c r="V58" t="s">
+        <v>261</v>
+      </c>
+      <c r="W58">
+        <v>2</v>
+      </c>
+      <c r="X58">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X39" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X58" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Downloads\Equipes_Agentes\Aplicativos\GAM\bd_saida\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C6613A-0DA1-4891-9811-C0993B06772C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E01D63-5EB9-4578-8654-D7193DFBE4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$49</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="181">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -108,7 +108,7 @@
     <t>BEBIDAS</t>
   </si>
   <si>
-    <t>PRODUTOS PET</t>
+    <t>PERECIVEIS</t>
   </si>
   <si>
     <t>PERFUMARIA E LIMPEZA</t>
@@ -120,12 +120,15 @@
     <t>NICOLAS AUGUSTO P. BORGES</t>
   </si>
   <si>
+    <t>SANDRO MARTINS VIANNA</t>
+  </si>
+  <si>
+    <t>JOAO BATISTA</t>
+  </si>
+  <si>
     <t>WETER SONNENFELDET</t>
   </si>
   <si>
-    <t>JOAO BATISTA</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
@@ -141,6 +144,12 @@
     <t>006</t>
   </si>
   <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
     <t>011</t>
   </si>
   <si>
@@ -156,226 +165,163 @@
     <t>017</t>
   </si>
   <si>
-    <t>293</t>
-  </si>
-  <si>
-    <t>2396</t>
-  </si>
-  <si>
-    <t>2320</t>
-  </si>
-  <si>
-    <t>570</t>
-  </si>
-  <si>
-    <t>2096</t>
-  </si>
-  <si>
-    <t>2637</t>
+    <t>018</t>
+  </si>
+  <si>
+    <t>260</t>
+  </si>
+  <si>
+    <t>2722</t>
+  </si>
+  <si>
+    <t>2755</t>
+  </si>
+  <si>
+    <t>6781</t>
+  </si>
+  <si>
+    <t>10179</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>5509</t>
+  </si>
+  <si>
+    <t>8345</t>
+  </si>
+  <si>
+    <t>17176</t>
+  </si>
+  <si>
+    <t>17179</t>
+  </si>
+  <si>
+    <t>17183</t>
+  </si>
+  <si>
+    <t>24653</t>
+  </si>
+  <si>
+    <t>663</t>
+  </si>
+  <si>
+    <t>2688</t>
+  </si>
+  <si>
+    <t>2793</t>
+  </si>
+  <si>
+    <t>8622</t>
+  </si>
+  <si>
+    <t>1422</t>
+  </si>
+  <si>
+    <t>6125</t>
+  </si>
+  <si>
+    <t>18815</t>
   </si>
   <si>
     <t>48</t>
   </si>
   <si>
-    <t>298</t>
-  </si>
-  <si>
-    <t>432</t>
-  </si>
-  <si>
-    <t>832</t>
-  </si>
-  <si>
-    <t>3574</t>
-  </si>
-  <si>
-    <t>3635</t>
-  </si>
-  <si>
-    <t>4039</t>
-  </si>
-  <si>
-    <t>4897</t>
-  </si>
-  <si>
-    <t>5196</t>
-  </si>
-  <si>
-    <t>7834</t>
-  </si>
-  <si>
-    <t>10144</t>
-  </si>
-  <si>
-    <t>13395</t>
-  </si>
-  <si>
-    <t>13704</t>
-  </si>
-  <si>
-    <t>16930</t>
-  </si>
-  <si>
-    <t>23159</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>33871</t>
-  </si>
-  <si>
-    <t>2722</t>
-  </si>
-  <si>
-    <t>3835</t>
-  </si>
-  <si>
-    <t>33899</t>
-  </si>
-  <si>
-    <t>1689</t>
-  </si>
-  <si>
-    <t>3891</t>
-  </si>
-  <si>
-    <t>5581</t>
-  </si>
-  <si>
-    <t>5681</t>
-  </si>
-  <si>
-    <t>8227</t>
-  </si>
-  <si>
-    <t>8233</t>
-  </si>
-  <si>
-    <t>8300</t>
-  </si>
-  <si>
-    <t>16936</t>
-  </si>
-  <si>
-    <t>17321</t>
-  </si>
-  <si>
-    <t>19803</t>
-  </si>
-  <si>
-    <t>33779</t>
-  </si>
-  <si>
-    <t>CERV STELLA ARTOIS LN 330ML</t>
-  </si>
-  <si>
-    <t>MILHO VERDE OLE LT 170G</t>
-  </si>
-  <si>
-    <t>FEIJAO CARIOCA CALDO OURO 1KG</t>
-  </si>
-  <si>
-    <t>REPOS POWERADE 500ML MIX</t>
-  </si>
-  <si>
-    <t>ARROZ BCO SANO T1 2K</t>
-  </si>
-  <si>
-    <t>ERVA MATE PONCHE VERDE 1KG LAMINADO</t>
+    <t>2955</t>
+  </si>
+  <si>
+    <t>3056</t>
+  </si>
+  <si>
+    <t>8604</t>
+  </si>
+  <si>
+    <t>18812</t>
+  </si>
+  <si>
+    <t>35112</t>
+  </si>
+  <si>
+    <t>2177</t>
+  </si>
+  <si>
+    <t>CERV HEINEKEN LN 330ML</t>
+  </si>
+  <si>
+    <t>FARINHA TRIGO PANFACIL TP1 1KG</t>
+  </si>
+  <si>
+    <t>FARINHA TRIGO PANFACIL 1KG C FERM</t>
+  </si>
+  <si>
+    <t>LEITE UHT ELEGE INT 1L</t>
+  </si>
+  <si>
+    <t>SABON PALMOLIVE NATURALS 85G OLEO ARGAN</t>
+  </si>
+  <si>
+    <t>REFRE PO PROMIX 100G ABACAXI</t>
+  </si>
+  <si>
+    <t>DESOD AERO AXE 152ML 90G MARINE</t>
+  </si>
+  <si>
+    <t>SH SEDA 325ML LISO PERFEITO</t>
+  </si>
+  <si>
+    <t>DESINF GOTA LIMPA 2L LIMAO</t>
+  </si>
+  <si>
+    <t>DESINF GOTA LIMPA 500ML FLORAL</t>
+  </si>
+  <si>
+    <t>DESINF GOTA LIMPA 500ML PINHO</t>
+  </si>
+  <si>
+    <t>TCO TENYS PE BARUEL PO 100G ORIG</t>
+  </si>
+  <si>
+    <t>SUCO KAPO TP 200ML MORANGO</t>
+  </si>
+  <si>
+    <t>FARINHA MILHO SAUDAVEL 1KG MEDIA</t>
+  </si>
+  <si>
+    <t>FAROFA CASEIRISSIMA YOKI 200G CEBOLA</t>
+  </si>
+  <si>
+    <t>TINT COR E TON PRETO 2 0</t>
+  </si>
+  <si>
+    <t>BISC MARIA GERMANI 345G</t>
+  </si>
+  <si>
+    <t>FRALDA CONFORTSEC PAMPERS XG 34UN</t>
+  </si>
+  <si>
+    <t>FRALDA PAMPERS SUPERSEQUINHA C 68 M</t>
   </si>
   <si>
     <t>AGUA MIN FLORESTA PET 500ML C GAS</t>
   </si>
   <si>
-    <t>VH SANGUE BOI TINTO 750ML SC</t>
-  </si>
-  <si>
-    <t>COQUETEL BUCANERO PET 790ML</t>
-  </si>
-  <si>
-    <t>REFRIG SUKITA PET 2L LARANJA</t>
-  </si>
-  <si>
-    <t>GELATINA APTI 20G LIMAO</t>
-  </si>
-  <si>
-    <t>SAL MOIDO CBS 1KG</t>
-  </si>
-  <si>
-    <t>ALIM GATO BIFFE CAT 1KG ESPECIAL</t>
-  </si>
-  <si>
-    <t>CLORO Q BOA 1L GEL LAVANDA</t>
-  </si>
-  <si>
-    <t>CR DEN COLGATE MPA 180G</t>
-  </si>
-  <si>
-    <t>DET PO GOTA LIMPA 4KG EQUILIBRIO</t>
-  </si>
-  <si>
-    <t>SAB FARNESE 180G AVEIA ESFOL</t>
-  </si>
-  <si>
-    <t>BISC MARIA ORQUIDEA 665GR</t>
-  </si>
-  <si>
-    <t>BOMBOM GAROTO SERENATA AMOR 17 6G</t>
-  </si>
-  <si>
-    <t>CR TRAT CAPILAR HEDERA BABOSA 960G</t>
-  </si>
-  <si>
-    <t>SABAO ZAVASKI GLIC 200G</t>
-  </si>
-  <si>
-    <t>CAP 3 CORACOES CAFE ATENTO C 10</t>
-  </si>
-  <si>
-    <t>REFRE HAPPY TP 200ML ABACAXI</t>
-  </si>
-  <si>
-    <t>FARINHA TRIGO PANFACIL TP1 1KG</t>
-  </si>
-  <si>
-    <t>EXT TOM FUGINI SH 190G</t>
-  </si>
-  <si>
-    <t>MACARRAO INST GERMANI 63G CARNE PICANTE</t>
-  </si>
-  <si>
-    <t>MARSHMALLOWS FOFS 220G BRUXOLITO PINTA</t>
-  </si>
-  <si>
-    <t>ABS C ABAS ALWAYS LV32PG26 NOT SUAV</t>
-  </si>
-  <si>
-    <t>DESOD AERO OLD SPICE 93G PEGADOR</t>
-  </si>
-  <si>
-    <t>DET LIQ GOTA LIMPA 500ML MARINE</t>
-  </si>
-  <si>
-    <t>SH HEAD SHOULDERS 200ML HIDRATACAO</t>
-  </si>
-  <si>
-    <t>SH HEAD SHOULDERS 200ML REMO OLEOSIDA</t>
-  </si>
-  <si>
-    <t>SH PANTENE 300ML EQUIL ALGA MAR</t>
-  </si>
-  <si>
-    <t>CR TRAT HEDERA 960G LISS PERFEITO</t>
-  </si>
-  <si>
-    <t>LAVA ROUPA LIQ APYCE 3L MULTIACAO AZUL</t>
-  </si>
-  <si>
-    <t>KIT SH CD PANTENE 300 150ML EQUILIBRIO</t>
-  </si>
-  <si>
-    <t>CR DEN COLGATE TT12 180G ORIG MINT</t>
+    <t>MOLHO PIMENTA EXTREMO SABOR 150ML EXTRA FORTE</t>
+  </si>
+  <si>
+    <t>CEREAL MAT NESTLE CX 210G KIT KAT</t>
+  </si>
+  <si>
+    <t>TINT COR E TON CHOC 6 7</t>
+  </si>
+  <si>
+    <t>FRALDA PAMPERS SUPERSEQUINHA C 50 XXG</t>
+  </si>
+  <si>
+    <t>AMAC CONC DOWNY 750ML TROPICAL</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SABOROSO TP1 5KG</t>
   </si>
   <si>
     <t>M</t>
@@ -387,58 +333,43 @@
     <t>20/06/2025</t>
   </si>
   <si>
-    <t>01/10/2024</t>
-  </si>
-  <si>
-    <t>09/12/2024</t>
-  </si>
-  <si>
-    <t>07/12/2024</t>
-  </si>
-  <si>
-    <t>10/10/2024</t>
-  </si>
-  <si>
-    <t>04/12/2024</t>
-  </si>
-  <si>
-    <t>12/12/2024</t>
+    <t>30/09/2024</t>
+  </si>
+  <si>
+    <t>13/12/2024</t>
+  </si>
+  <si>
+    <t>14/12/2024</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>27/09/2024</t>
+  </si>
+  <si>
+    <t>15/10/2024</t>
+  </si>
+  <si>
+    <t>16/12/2024</t>
+  </si>
+  <si>
+    <t>11/11/2024</t>
   </si>
   <si>
     <t>19/09/2024</t>
   </si>
   <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>07/10/2024</t>
-  </si>
-  <si>
-    <t>21/10/2024</t>
-  </si>
-  <si>
-    <t>30/12/2024</t>
-  </si>
-  <si>
-    <t>21/06/2025</t>
-  </si>
-  <si>
-    <t>29/08/2025</t>
-  </si>
-  <si>
-    <t>13/12/2024</t>
-  </si>
-  <si>
-    <t>10/01/2025</t>
-  </si>
-  <si>
-    <t>01/09/2025</t>
-  </si>
-  <si>
-    <t>21/11/2024</t>
-  </si>
-  <si>
-    <t>26/08/2025</t>
+    <t>17/12/2024</t>
+  </si>
+  <si>
+    <t>19/12/2024</t>
+  </si>
+  <si>
+    <t>19/12/2025</t>
+  </si>
+  <si>
+    <t>05/12/2024</t>
   </si>
   <si>
     <t>Ativo</t>
@@ -450,229 +381,196 @@
     <t>10</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>2535</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>579</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33415</t>
+  </si>
+  <si>
+    <t>769</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>3263</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>100</t>
   </si>
   <si>
     <t>36</t>
   </si>
   <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>470</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>1742</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>358</t>
-  </si>
-  <si>
-    <t>952</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>33957</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>655</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>596</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>676</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>771</t>
-  </si>
-  <si>
-    <t>467</t>
-  </si>
-  <si>
-    <t>1216</t>
-  </si>
-  <si>
-    <t>15334</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>499</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>CRBS AS CDD PELOTAS</t>
-  </si>
-  <si>
-    <t>ANGELO AURICCHIO &amp; CIA LTDA</t>
-  </si>
-  <si>
-    <t>COOP AGRICOLA MISTA NOVA PALMA LTDA</t>
+    <t>35</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>673</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>15023</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>CARLOS CANCIAN E CIA LTDA</t>
+  </si>
+  <si>
+    <t>MOINHO ESTRELA LTDA</t>
+  </si>
+  <si>
+    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
+  </si>
+  <si>
+    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
+  </si>
+  <si>
+    <t>ENOVA FOODS AS</t>
+  </si>
+  <si>
+    <t>BERTOLINI INDUSTRIA QUIMICA LTDA</t>
+  </si>
+  <si>
+    <t>NILO TOZZO DISTRIBUIDORA LTDA</t>
   </si>
   <si>
     <t>SPAL IND BRAS BEBIDAS AS</t>
   </si>
   <si>
-    <t>FERRUCCI E MIRANDA LTDA-EPP</t>
-  </si>
-  <si>
-    <t>PONCHE VERDE INDL. DO MATE LTDA.</t>
+    <t>CARLOS ENRIQUE WATERMANN EIRELI</t>
+  </si>
+  <si>
+    <t>FABIANO ZAFFALON E CIA LTDA</t>
+  </si>
+  <si>
+    <t>GERMANI ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>ONIZ DISTRIBUID LTDA SCJ</t>
   </si>
   <si>
     <t>AGUAS MINERAIS SARANDI LTDA</t>
   </si>
   <si>
-    <t>COOP VINICOLA AURORA LTDA</t>
-  </si>
-  <si>
-    <t>ENGARRAFADORA BRAMBILA LTDA</t>
-  </si>
-  <si>
-    <t>APTI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
-  </si>
-  <si>
-    <t>JA TEIXEIRA VETERINARIA LTDA</t>
-  </si>
-  <si>
-    <t>INDUSTRIAS ANHEMBI LTDA.</t>
-  </si>
-  <si>
-    <t>BERTOLINI INDUSTRIA QUIMICA LTDA</t>
-  </si>
-  <si>
-    <t>ONIZ DISTRIBUID LTDA SCJ</t>
-  </si>
-  <si>
-    <t>TONDO S/A</t>
+    <t>ABRAHAM INDUSTRIA DE ESPECIARIAS LTDA</t>
   </si>
   <si>
     <t>NESTLE BRASIL LTDA</t>
   </si>
   <si>
-    <t>NOVA DISTRIBUIDORA DE COSMETICOS EIRELI</t>
-  </si>
-  <si>
-    <t>IND E COM DE SABAO ZAVASKI LTDA</t>
-  </si>
-  <si>
-    <t>CAFE TRES CORACOES S.A</t>
-  </si>
-  <si>
-    <t>COOP VITIVINICOLA ALIANCA LTDA</t>
-  </si>
-  <si>
-    <t>MOINHO ESTRELA LTDA</t>
-  </si>
-  <si>
-    <t>FUGINI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>GERMANI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>FLORESTAL ALIMENTOS S.A.</t>
-  </si>
-  <si>
-    <t>PODAL IND E COM DE ALIMENTOS LTDA</t>
+    <t>COOPERATIVA AGROINDUSTRIAL ALEGRETE LTDA</t>
   </si>
 </sst>
 </file>
@@ -1014,11 +912,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
@@ -1103,31 +1000,31 @@
         <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G2" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="H2" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I2" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="J2">
         <v>24</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1139,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="P2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -1157,16 +1054,16 @@
         <v>90</v>
       </c>
       <c r="U2">
-        <v>9638</v>
+        <v>14469</v>
       </c>
       <c r="V2" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="W2">
         <v>2</v>
       </c>
       <c r="X2">
-        <v>92</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
@@ -1177,31 +1074,31 @@
         <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" t="s">
         <v>116</v>
       </c>
-      <c r="G3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" t="s">
-        <v>137</v>
-      </c>
-      <c r="I3" t="s">
-        <v>138</v>
-      </c>
       <c r="J3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1213,13 +1110,13 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="P3">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="Q3">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1231,16 +1128,16 @@
         <v>90</v>
       </c>
       <c r="U3">
-        <v>7715</v>
+        <v>16900</v>
       </c>
       <c r="V3" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="W3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="X3">
-        <v>557</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -1254,46 +1151,46 @@
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" t="s">
         <v>116</v>
-      </c>
-      <c r="G4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H4" t="s">
-        <v>137</v>
-      </c>
-      <c r="I4" t="s">
-        <v>139</v>
       </c>
       <c r="J4">
         <v>10</v>
       </c>
       <c r="K4">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="P4">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="Q4">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1305,51 +1202,51 @@
         <v>90</v>
       </c>
       <c r="U4">
-        <v>15165</v>
+        <v>16900</v>
       </c>
       <c r="V4" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="W4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X4">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F5" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G5" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H5" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I5" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="J5">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K5">
-        <v>174</v>
+        <v>41</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1361,13 +1258,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="P5">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="Q5">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1379,125 +1276,125 @@
         <v>90</v>
       </c>
       <c r="U5">
-        <v>7715</v>
+        <v>9379</v>
       </c>
       <c r="V5" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="X5">
-        <v>557</v>
+        <v>870</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F6" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="G6" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="H6" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I6" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="J6">
+        <v>108</v>
+      </c>
+      <c r="K6">
+        <v>60</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>129</v>
+      </c>
+      <c r="P6">
+        <v>66</v>
+      </c>
+      <c r="Q6">
+        <v>174</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>90</v>
+      </c>
+      <c r="U6">
+        <v>5894</v>
+      </c>
+      <c r="V6" t="s">
+        <v>168</v>
+      </c>
+      <c r="W6">
+        <v>2</v>
+      </c>
+      <c r="X6">
         <v>6</v>
-      </c>
-      <c r="K6">
-        <v>23</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>155</v>
-      </c>
-      <c r="P6">
-        <v>24</v>
-      </c>
-      <c r="Q6">
-        <v>42</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>90</v>
-      </c>
-      <c r="U6">
-        <v>15441</v>
-      </c>
-      <c r="V6" t="s">
-        <v>192</v>
-      </c>
-      <c r="W6">
-        <v>4</v>
-      </c>
-      <c r="X6">
-        <v>240.67</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F7" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G7" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="H7" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I7" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K7">
-        <v>-2</v>
+        <v>40</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1506,16 +1403,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="P7">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q7">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1527,16 +1424,16 @@
         <v>90</v>
       </c>
       <c r="U7">
-        <v>7918</v>
+        <v>4968</v>
       </c>
       <c r="V7" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="W7">
         <v>2</v>
       </c>
       <c r="X7">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -1547,50 +1444,50 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I8" t="s">
+        <v>116</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>39</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>130</v>
+      </c>
+      <c r="P8">
+        <v>50</v>
+      </c>
+      <c r="Q8">
         <v>80</v>
       </c>
-      <c r="F8" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" t="s">
-        <v>120</v>
-      </c>
-      <c r="H8" t="s">
-        <v>137</v>
-      </c>
-      <c r="I8" t="s">
-        <v>138</v>
-      </c>
-      <c r="J8">
-        <v>24</v>
-      </c>
-      <c r="K8">
-        <v>190</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>157</v>
-      </c>
-      <c r="P8">
-        <v>192</v>
-      </c>
-      <c r="Q8">
-        <v>288</v>
-      </c>
       <c r="R8">
         <v>0</v>
       </c>
@@ -1601,69 +1498,69 @@
         <v>90</v>
       </c>
       <c r="U8">
-        <v>7715</v>
+        <v>16900</v>
       </c>
       <c r="V8" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="W8">
+        <v>4</v>
+      </c>
+      <c r="X8">
         <v>5</v>
-      </c>
-      <c r="X8">
-        <v>557</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F9" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G9" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="H9" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I9" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="J9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K9">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N9">
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="P9">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="Q9">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1675,51 +1572,51 @@
         <v>90</v>
       </c>
       <c r="U9">
-        <v>9605</v>
+        <v>5894</v>
       </c>
       <c r="V9" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="W9">
         <v>2</v>
       </c>
       <c r="X9">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G10" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="H10" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I10" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="J10">
         <v>12</v>
       </c>
       <c r="K10">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1731,13 +1628,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="P10">
-        <v>144</v>
+        <v>42</v>
       </c>
       <c r="Q10">
-        <v>180</v>
+        <v>66</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1749,69 +1646,69 @@
         <v>90</v>
       </c>
       <c r="U10">
-        <v>10181</v>
+        <v>5894</v>
       </c>
       <c r="V10" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X10">
-        <v>15</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G11" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="H11" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I11" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="J11">
         <v>6</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="P11">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1823,51 +1720,51 @@
         <v>90</v>
       </c>
       <c r="U11">
-        <v>7246</v>
+        <v>14468</v>
       </c>
       <c r="V11" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G12" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="H12" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I12" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="J12">
         <v>12</v>
       </c>
       <c r="K12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1879,13 +1776,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1897,51 +1794,51 @@
         <v>90</v>
       </c>
       <c r="U12">
-        <v>14395</v>
+        <v>14468</v>
       </c>
       <c r="V12" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="W12">
         <v>2</v>
       </c>
       <c r="X12">
-        <v>65</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F13" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G13" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I13" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1953,13 +1850,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="P13">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="Q13">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1971,51 +1868,51 @@
         <v>90</v>
       </c>
       <c r="U13">
-        <v>9638</v>
+        <v>14468</v>
       </c>
       <c r="V13" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="W13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G14" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I14" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="J14">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K14">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2027,13 +1924,13 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="P14">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Q14">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -2045,16 +1942,16 @@
         <v>90</v>
       </c>
       <c r="U14">
-        <v>10189</v>
+        <v>3266</v>
       </c>
       <c r="V14" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="W14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -2062,34 +1959,34 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="F15" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" t="s">
         <v>116</v>
-      </c>
-      <c r="G15" t="s">
-        <v>129</v>
-      </c>
-      <c r="H15" t="s">
-        <v>137</v>
-      </c>
-      <c r="I15" t="s">
-        <v>139</v>
       </c>
       <c r="J15">
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2098,16 +1995,16 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="Q15">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -2119,70 +2016,70 @@
         <v>90</v>
       </c>
       <c r="U15">
-        <v>5894</v>
+        <v>16900</v>
       </c>
       <c r="V15" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X15">
-        <v>255</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
         <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G16" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I16" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>138</v>
+      </c>
+      <c r="P16">
+        <v>4</v>
+      </c>
+      <c r="Q16">
         <v>10</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>165</v>
-      </c>
-      <c r="P16">
-        <v>16</v>
-      </c>
-      <c r="Q16">
-        <v>24</v>
-      </c>
       <c r="R16">
         <v>0</v>
       </c>
@@ -2193,16 +2090,16 @@
         <v>90</v>
       </c>
       <c r="U16">
-        <v>10951</v>
+        <v>14468</v>
       </c>
       <c r="V16" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="W16">
         <v>2</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
@@ -2213,31 +2110,31 @@
         <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
         <v>55</v>
       </c>
       <c r="E17" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F17" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I17" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="J17">
         <v>12</v>
       </c>
       <c r="K17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2249,13 +2146,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="P17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q17">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2267,10 +2164,10 @@
         <v>90</v>
       </c>
       <c r="U17">
-        <v>9499</v>
+        <v>14468</v>
       </c>
       <c r="V17" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="W17">
         <v>2</v>
@@ -2287,31 +2184,31 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
         <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G18" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="H18" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I18" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="J18">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="K18">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2323,13 +2220,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="P18">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -2341,125 +2238,125 @@
         <v>90</v>
       </c>
       <c r="U18">
-        <v>5894</v>
+        <v>14468</v>
       </c>
       <c r="V18" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="W18">
         <v>2</v>
       </c>
       <c r="X18">
-        <v>83</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G19" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="H19" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I19" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="J19">
+        <v>12</v>
+      </c>
+      <c r="K19">
+        <v>39</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>12</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>141</v>
+      </c>
+      <c r="P19">
+        <v>56</v>
+      </c>
+      <c r="Q19">
+        <v>80</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>90</v>
+      </c>
+      <c r="U19">
+        <v>15441</v>
+      </c>
+      <c r="V19" t="s">
+        <v>172</v>
+      </c>
+      <c r="W19">
+        <v>3</v>
+      </c>
+      <c r="X19">
         <v>5</v>
-      </c>
-      <c r="K19">
-        <v>3</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>5</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>168</v>
-      </c>
-      <c r="P19">
-        <v>11</v>
-      </c>
-      <c r="Q19">
-        <v>16</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>90</v>
-      </c>
-      <c r="U19">
-        <v>14468</v>
-      </c>
-      <c r="V19" t="s">
-        <v>202</v>
-      </c>
-      <c r="W19">
-        <v>2</v>
-      </c>
-      <c r="X19">
-        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G20" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="H20" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I20" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="J20">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2471,13 +2368,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="P20">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="Q20">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -2489,16 +2386,16 @@
         <v>90</v>
       </c>
       <c r="U20">
-        <v>6644</v>
+        <v>15301</v>
       </c>
       <c r="V20" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="W20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X20">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -2506,34 +2403,34 @@
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G21" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H21" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I21" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="J21">
         <v>12</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -2545,13 +2442,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="P21">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q21">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -2563,51 +2460,51 @@
         <v>90</v>
       </c>
       <c r="U21">
-        <v>10683</v>
+        <v>3527</v>
       </c>
       <c r="V21" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="W21">
         <v>2</v>
       </c>
       <c r="X21">
-        <v>60</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="G22" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="H22" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I22" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="J22">
-        <v>470</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>256</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -2619,13 +2516,13 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="P22">
-        <v>282</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>752</v>
+        <v>12</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -2637,69 +2534,69 @@
         <v>90</v>
       </c>
       <c r="U22">
-        <v>15134</v>
+        <v>5894</v>
       </c>
       <c r="V22" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="W22">
         <v>2</v>
       </c>
       <c r="X22">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" t="s">
         <v>98</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" t="s">
+        <v>114</v>
+      </c>
+      <c r="I23" t="s">
         <v>116</v>
       </c>
-      <c r="G23" t="s">
-        <v>118</v>
-      </c>
-      <c r="H23" t="s">
-        <v>137</v>
-      </c>
-      <c r="I23" t="s">
-        <v>140</v>
-      </c>
       <c r="J23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="P23">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="Q23">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -2711,51 +2608,51 @@
         <v>90</v>
       </c>
       <c r="U23">
-        <v>9164</v>
+        <v>16900</v>
       </c>
       <c r="V23" t="s">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="W23">
         <v>2</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
         <v>62</v>
       </c>
       <c r="E24" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F24" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G24" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H24" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I24" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="J24">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K24">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -2767,13 +2664,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="P24">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Q24">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2785,16 +2682,16 @@
         <v>90</v>
       </c>
       <c r="U24">
-        <v>13663</v>
+        <v>16963</v>
       </c>
       <c r="V24" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="W24">
         <v>2</v>
       </c>
       <c r="X24">
-        <v>7.96</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
@@ -2802,52 +2699,52 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" t="s">
+        <v>103</v>
+      </c>
+      <c r="H25" t="s">
+        <v>114</v>
+      </c>
+      <c r="I25" t="s">
+        <v>116</v>
+      </c>
+      <c r="J25">
+        <v>10</v>
+      </c>
+      <c r="K25">
+        <v>11</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>10</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>146</v>
+      </c>
+      <c r="P25">
         <v>30</v>
       </c>
-      <c r="C25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" t="s">
-        <v>130</v>
-      </c>
-      <c r="H25" t="s">
-        <v>137</v>
-      </c>
-      <c r="I25" t="s">
-        <v>143</v>
-      </c>
-      <c r="J25">
-        <v>8</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>150</v>
-      </c>
-      <c r="P25">
-        <v>6</v>
-      </c>
       <c r="Q25">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2859,48 +2756,48 @@
         <v>90</v>
       </c>
       <c r="U25">
-        <v>8702</v>
+        <v>16900</v>
       </c>
       <c r="V25" t="s">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="W25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X25">
-        <v>22.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G26" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="H26" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I26" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="J26">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -2915,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="P26">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -2933,69 +2830,69 @@
         <v>90</v>
       </c>
       <c r="U26">
-        <v>10224</v>
+        <v>6644</v>
       </c>
       <c r="V26" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="W26">
         <v>2</v>
       </c>
       <c r="X26">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
         <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F27" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="G27" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="H27" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I27" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="J27">
+        <v>4</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>124</v>
+      </c>
+      <c r="P27">
         <v>6</v>
       </c>
-      <c r="K27">
-        <v>19</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>175</v>
-      </c>
-      <c r="P27">
-        <v>24</v>
-      </c>
       <c r="Q27">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -3007,51 +2904,51 @@
         <v>90</v>
       </c>
       <c r="U27">
-        <v>15441</v>
+        <v>6644</v>
       </c>
       <c r="V27" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="W27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X27">
-        <v>240.67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D28" t="s">
         <v>65</v>
       </c>
       <c r="E28" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G28" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="H28" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I28" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="J28">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -3060,16 +2957,16 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="P28">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="Q28">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -3081,69 +2978,69 @@
         <v>90</v>
       </c>
       <c r="U28">
-        <v>16900</v>
+        <v>10181</v>
       </c>
       <c r="V28" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
-        <v>135</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="F29" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G29" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="H29" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I29" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="J29">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K29">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N29">
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="P29">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -3155,16 +3052,16 @@
         <v>90</v>
       </c>
       <c r="U29">
-        <v>5791</v>
+        <v>15441</v>
       </c>
       <c r="V29" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="W29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X29">
-        <v>119</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
@@ -3172,52 +3069,52 @@
         <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" t="s">
+        <v>114</v>
+      </c>
+      <c r="I30" t="s">
         <v>116</v>
       </c>
-      <c r="G30" t="s">
-        <v>134</v>
-      </c>
-      <c r="H30" t="s">
-        <v>137</v>
-      </c>
-      <c r="I30" t="s">
-        <v>148</v>
-      </c>
       <c r="J30">
+        <v>10</v>
+      </c>
+      <c r="K30">
+        <v>29</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>10</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>115</v>
+      </c>
+      <c r="P30">
         <v>50</v>
       </c>
-      <c r="K30">
-        <v>82</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
-        <v>178</v>
-      </c>
-      <c r="P30">
-        <v>86</v>
-      </c>
       <c r="Q30">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -3229,51 +3126,51 @@
         <v>90</v>
       </c>
       <c r="U30">
-        <v>16963</v>
+        <v>16900</v>
       </c>
       <c r="V30" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="W30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
         <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="E31" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G31" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="H31" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I31" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="J31">
         <v>12</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3285,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="P31">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -3303,16 +3200,16 @@
         <v>90</v>
       </c>
       <c r="U31">
-        <v>10181</v>
+        <v>8512</v>
       </c>
       <c r="V31" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="W31">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="X31">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
@@ -3320,52 +3217,52 @@
         <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F32" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G32" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" t="s">
+        <v>114</v>
+      </c>
+      <c r="I32" t="s">
+        <v>115</v>
+      </c>
+      <c r="J32">
+        <v>24</v>
+      </c>
+      <c r="K32">
+        <v>15</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
         <v>135</v>
       </c>
-      <c r="H32" t="s">
-        <v>137</v>
-      </c>
-      <c r="I32" t="s">
-        <v>142</v>
-      </c>
-      <c r="J32">
-        <v>12</v>
-      </c>
-      <c r="K32">
-        <v>6</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>180</v>
-      </c>
       <c r="P32">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Q32">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -3377,51 +3274,51 @@
         <v>90</v>
       </c>
       <c r="U32">
-        <v>7493</v>
+        <v>15134</v>
       </c>
       <c r="V32" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="W32">
         <v>2</v>
       </c>
       <c r="X32">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G33" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="H33" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I33" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3433,13 +3330,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="P33">
-        <v>4</v>
+        <v>236</v>
       </c>
       <c r="Q33">
-        <v>10</v>
+        <v>368</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -3451,16 +3348,16 @@
         <v>90</v>
       </c>
       <c r="U33">
-        <v>6644</v>
+        <v>9379</v>
       </c>
       <c r="V33" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="W33">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>870</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -3471,31 +3368,31 @@
         <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="F34" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="H34" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I34" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="J34">
         <v>6</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -3507,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="P34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -3525,16 +3422,16 @@
         <v>90</v>
       </c>
       <c r="U34">
-        <v>6644</v>
+        <v>5894</v>
       </c>
       <c r="V34" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="W34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X34">
-        <v>12.67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
@@ -3545,31 +3442,31 @@
         <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E35" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="F35" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G35" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="H35" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I35" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="J35">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3581,13 +3478,13 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="P35">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="Q35">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -3602,13 +3499,13 @@
         <v>14468</v>
       </c>
       <c r="V35" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="W35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
@@ -3619,31 +3516,31 @@
         <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E36" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="F36" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G36" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="H36" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I36" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="J36">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3655,13 +3552,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P36">
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -3673,16 +3570,16 @@
         <v>90</v>
       </c>
       <c r="U36">
-        <v>5894</v>
+        <v>14468</v>
       </c>
       <c r="V36" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="W36">
         <v>2</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
@@ -3693,28 +3590,28 @@
         <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E37" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="F37" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G37" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="H37" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I37" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="J37">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K37">
         <v>5</v>
@@ -3729,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="P37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -3747,143 +3644,143 @@
         <v>90</v>
       </c>
       <c r="U37">
-        <v>5894</v>
+        <v>14468</v>
       </c>
       <c r="V37" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="W37">
         <v>2</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
         <v>41</v>
       </c>
       <c r="D38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" t="s">
         <v>74</v>
       </c>
-      <c r="E38" t="s">
-        <v>111</v>
-      </c>
       <c r="F38" t="s">
+        <v>98</v>
+      </c>
+      <c r="G38" t="s">
+        <v>103</v>
+      </c>
+      <c r="H38" t="s">
+        <v>114</v>
+      </c>
+      <c r="I38" t="s">
         <v>116</v>
       </c>
-      <c r="G38" t="s">
-        <v>126</v>
-      </c>
-      <c r="H38" t="s">
-        <v>137</v>
-      </c>
-      <c r="I38" t="s">
-        <v>140</v>
-      </c>
       <c r="J38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K38">
+        <v>27</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>10</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
+        <v>155</v>
+      </c>
+      <c r="P38">
+        <v>50</v>
+      </c>
+      <c r="Q38">
+        <v>80</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>90</v>
+      </c>
+      <c r="U38">
+        <v>16900</v>
+      </c>
+      <c r="V38" t="s">
+        <v>166</v>
+      </c>
+      <c r="W38">
         <v>5</v>
       </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38" t="s">
-        <v>184</v>
-      </c>
-      <c r="P38">
-        <v>6</v>
-      </c>
-      <c r="Q38">
-        <v>12</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <v>90</v>
-      </c>
-      <c r="U38">
-        <v>6644</v>
-      </c>
-      <c r="V38" t="s">
-        <v>203</v>
-      </c>
-      <c r="W38">
-        <v>2</v>
-      </c>
       <c r="X38">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E39" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="F39" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G39" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H39" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I39" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N39">
         <v>0</v>
       </c>
       <c r="O39" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="P39">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="Q39">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -3895,242 +3792,760 @@
         <v>90</v>
       </c>
       <c r="U39">
-        <v>9164</v>
+        <v>15441</v>
       </c>
       <c r="V39" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
       <c r="W39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X39">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="F40" t="s">
+        <v>98</v>
+      </c>
+      <c r="G40" t="s">
+        <v>103</v>
+      </c>
+      <c r="H40" t="s">
+        <v>114</v>
+      </c>
+      <c r="I40" t="s">
         <v>116</v>
       </c>
-      <c r="G40" t="s">
-        <v>118</v>
-      </c>
-      <c r="H40" t="s">
-        <v>137</v>
-      </c>
-      <c r="I40" t="s">
-        <v>149</v>
-      </c>
       <c r="J40">
+        <v>10</v>
+      </c>
+      <c r="K40">
+        <v>10</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>10</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" t="s">
+        <v>157</v>
+      </c>
+      <c r="P40">
+        <v>40</v>
+      </c>
+      <c r="Q40">
+        <v>60</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>90</v>
+      </c>
+      <c r="U40">
+        <v>16900</v>
+      </c>
+      <c r="V40" t="s">
+        <v>166</v>
+      </c>
+      <c r="W40">
         <v>4</v>
       </c>
-      <c r="K40">
-        <v>51</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>4</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40" t="s">
-        <v>186</v>
-      </c>
-      <c r="P40">
-        <v>58</v>
-      </c>
-      <c r="Q40">
-        <v>90</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>90</v>
-      </c>
-      <c r="U40">
-        <v>5894</v>
-      </c>
-      <c r="V40" t="s">
-        <v>199</v>
-      </c>
-      <c r="W40">
-        <v>9</v>
-      </c>
       <c r="X40">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E41" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="F41" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G41" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="H41" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I41" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="J41">
+        <v>12</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>108</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>158</v>
+      </c>
+      <c r="P41">
+        <v>144</v>
+      </c>
+      <c r="Q41">
+        <v>180</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>90</v>
+      </c>
+      <c r="U41">
+        <v>10181</v>
+      </c>
+      <c r="V41" t="s">
+        <v>177</v>
+      </c>
+      <c r="W41">
         <v>6</v>
       </c>
-      <c r="K41">
-        <v>5</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41" t="s">
-        <v>187</v>
-      </c>
-      <c r="P41">
-        <v>6</v>
-      </c>
-      <c r="Q41">
-        <v>12</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
-      <c r="T41">
-        <v>90</v>
-      </c>
-      <c r="U41">
-        <v>5894</v>
-      </c>
-      <c r="V41" t="s">
-        <v>199</v>
-      </c>
-      <c r="W41">
-        <v>2</v>
-      </c>
       <c r="X41">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42" t="s">
+        <v>98</v>
+      </c>
+      <c r="G42" t="s">
+        <v>103</v>
+      </c>
+      <c r="H42" t="s">
+        <v>114</v>
+      </c>
+      <c r="I42" t="s">
+        <v>116</v>
+      </c>
+      <c r="J42">
+        <v>10</v>
+      </c>
+      <c r="K42">
+        <v>13</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>10</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>159</v>
+      </c>
+      <c r="P42">
+        <v>40</v>
+      </c>
+      <c r="Q42">
+        <v>60</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>90</v>
+      </c>
+      <c r="U42">
+        <v>16900</v>
+      </c>
+      <c r="V42" t="s">
+        <v>166</v>
+      </c>
+      <c r="W42">
+        <v>4</v>
+      </c>
+      <c r="X42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>27</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>31</v>
       </c>
-      <c r="C42" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" t="s">
-        <v>78</v>
-      </c>
-      <c r="E42" t="s">
-        <v>115</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="C43" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" t="s">
+        <v>89</v>
+      </c>
+      <c r="F43" t="s">
+        <v>98</v>
+      </c>
+      <c r="G43" t="s">
+        <v>104</v>
+      </c>
+      <c r="H43" t="s">
+        <v>114</v>
+      </c>
+      <c r="I43" t="s">
+        <v>123</v>
+      </c>
+      <c r="J43">
+        <v>4</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>124</v>
+      </c>
+      <c r="P43">
+        <v>8</v>
+      </c>
+      <c r="Q43">
+        <v>12</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>90</v>
+      </c>
+      <c r="U43">
+        <v>6644</v>
+      </c>
+      <c r="V43" t="s">
+        <v>176</v>
+      </c>
+      <c r="W43">
+        <v>3</v>
+      </c>
+      <c r="X43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" t="s">
+        <v>95</v>
+      </c>
+      <c r="F44" t="s">
+        <v>98</v>
+      </c>
+      <c r="G44" t="s">
+        <v>100</v>
+      </c>
+      <c r="H44" t="s">
+        <v>114</v>
+      </c>
+      <c r="I44" t="s">
+        <v>123</v>
+      </c>
+      <c r="J44">
+        <v>4</v>
+      </c>
+      <c r="K44">
+        <v>5</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
         <v>116</v>
       </c>
-      <c r="G42" t="s">
-        <v>136</v>
-      </c>
-      <c r="H42" t="s">
-        <v>137</v>
-      </c>
-      <c r="I42" t="s">
-        <v>142</v>
-      </c>
-      <c r="J42">
+      <c r="P44">
+        <v>6</v>
+      </c>
+      <c r="Q44">
+        <v>10</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>90</v>
+      </c>
+      <c r="U44">
+        <v>6644</v>
+      </c>
+      <c r="V44" t="s">
+        <v>176</v>
+      </c>
+      <c r="W44">
+        <v>2</v>
+      </c>
+      <c r="X44">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D45" t="s">
+        <v>70</v>
+      </c>
+      <c r="E45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F45" t="s">
+        <v>98</v>
+      </c>
+      <c r="G45" t="s">
+        <v>112</v>
+      </c>
+      <c r="H45" t="s">
+        <v>114</v>
+      </c>
+      <c r="I45" t="s">
+        <v>117</v>
+      </c>
+      <c r="J45">
         <v>12</v>
       </c>
-      <c r="K42">
+      <c r="K45">
+        <v>7</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>160</v>
+      </c>
+      <c r="P45">
+        <v>10</v>
+      </c>
+      <c r="Q45">
+        <v>22</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>90</v>
+      </c>
+      <c r="U45">
+        <v>6644</v>
+      </c>
+      <c r="V45" t="s">
+        <v>176</v>
+      </c>
+      <c r="W45">
+        <v>2</v>
+      </c>
+      <c r="X45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" t="s">
+        <v>84</v>
+      </c>
+      <c r="F46" t="s">
+        <v>98</v>
+      </c>
+      <c r="G46" t="s">
+        <v>106</v>
+      </c>
+      <c r="H46" t="s">
+        <v>114</v>
+      </c>
+      <c r="I46" t="s">
+        <v>117</v>
+      </c>
+      <c r="J46">
+        <v>12</v>
+      </c>
+      <c r="K46">
+        <v>33</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>12</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>161</v>
+      </c>
+      <c r="P46">
+        <v>52</v>
+      </c>
+      <c r="Q46">
+        <v>88</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>90</v>
+      </c>
+      <c r="U46">
+        <v>15441</v>
+      </c>
+      <c r="V46" t="s">
+        <v>172</v>
+      </c>
+      <c r="W46">
+        <v>4</v>
+      </c>
+      <c r="X46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" t="s">
+        <v>48</v>
+      </c>
+      <c r="E47" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47" t="s">
+        <v>98</v>
+      </c>
+      <c r="G47" t="s">
+        <v>103</v>
+      </c>
+      <c r="H47" t="s">
+        <v>114</v>
+      </c>
+      <c r="I47" t="s">
+        <v>116</v>
+      </c>
+      <c r="J47">
+        <v>10</v>
+      </c>
+      <c r="K47">
+        <v>2</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>30</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>162</v>
+      </c>
+      <c r="P47">
+        <v>50</v>
+      </c>
+      <c r="Q47">
+        <v>80</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>90</v>
+      </c>
+      <c r="U47">
+        <v>16900</v>
+      </c>
+      <c r="V47" t="s">
+        <v>166</v>
+      </c>
+      <c r="W47">
+        <v>5</v>
+      </c>
+      <c r="X47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G48" t="s">
+        <v>113</v>
+      </c>
+      <c r="H48" t="s">
+        <v>114</v>
+      </c>
+      <c r="I48" t="s">
+        <v>120</v>
+      </c>
+      <c r="J48">
+        <v>6</v>
+      </c>
+      <c r="K48">
+        <v>52</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>163</v>
+      </c>
+      <c r="P48">
+        <v>54</v>
+      </c>
+      <c r="Q48">
+        <v>84</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>90</v>
+      </c>
+      <c r="U48">
+        <v>10721</v>
+      </c>
+      <c r="V48" t="s">
+        <v>180</v>
+      </c>
+      <c r="W48">
+        <v>6</v>
+      </c>
+      <c r="X48">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>27</v>
       </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42" t="s">
-        <v>188</v>
-      </c>
-      <c r="P42">
-        <v>34</v>
-      </c>
-      <c r="Q42">
-        <v>46</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>90</v>
-      </c>
-      <c r="U42">
-        <v>15318</v>
-      </c>
-      <c r="V42" t="s">
-        <v>214</v>
-      </c>
-      <c r="W42">
+      <c r="B49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" t="s">
+        <v>96</v>
+      </c>
+      <c r="F49" t="s">
+        <v>98</v>
+      </c>
+      <c r="G49" t="s">
+        <v>112</v>
+      </c>
+      <c r="H49" t="s">
+        <v>114</v>
+      </c>
+      <c r="I49" t="s">
+        <v>117</v>
+      </c>
+      <c r="J49">
+        <v>12</v>
+      </c>
+      <c r="K49">
+        <v>15</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" t="s">
+        <v>164</v>
+      </c>
+      <c r="P49">
+        <v>16</v>
+      </c>
+      <c r="Q49">
+        <v>28</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>90</v>
+      </c>
+      <c r="U49">
+        <v>6644</v>
+      </c>
+      <c r="V49" t="s">
+        <v>176</v>
+      </c>
+      <c r="W49">
         <v>2</v>
       </c>
-      <c r="X42">
-        <v>11</v>
+      <c r="X49">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X42" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X49" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Downloads\Equipes_Agentes\Aplicativos\GAM\bd_saida\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3A2098-A79C-4D02-8472-6286F515268A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$54</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="264">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -94,30 +108,30 @@
     <t>PERFUMARIA E LIMPEZA</t>
   </si>
   <si>
+    <t>PERECIVEIS</t>
+  </si>
+  <si>
+    <t>PRODUTOS PET</t>
+  </si>
+  <si>
     <t>BEBIDAS</t>
   </si>
   <si>
-    <t>PRODUTOS PET</t>
-  </si>
-  <si>
-    <t>PERECIVEIS</t>
-  </si>
-  <si>
     <t>NIDAL TUBASI</t>
   </si>
   <si>
     <t>JOAO BATISTA</t>
   </si>
   <si>
+    <t>SANDRO MARTINS VIANNA</t>
+  </si>
+  <si>
     <t>NICOLAS AUGUSTO P. BORGES</t>
   </si>
   <si>
     <t>WETER SONNENFELDET</t>
   </si>
   <si>
-    <t>SANDRO MARTINS VIANNA</t>
-  </si>
-  <si>
     <t>001</t>
   </si>
   <si>
@@ -136,18 +150,12 @@
     <t>006</t>
   </si>
   <si>
-    <t>007</t>
-  </si>
-  <si>
     <t>008</t>
   </si>
   <si>
     <t>011</t>
   </si>
   <si>
-    <t>012</t>
-  </si>
-  <si>
     <t>013</t>
   </si>
   <si>
@@ -157,43 +165,40 @@
     <t>017</t>
   </si>
   <si>
-    <t>018</t>
-  </si>
-  <si>
-    <t>15765</t>
-  </si>
-  <si>
-    <t>17156</t>
-  </si>
-  <si>
-    <t>17157</t>
-  </si>
-  <si>
-    <t>17389</t>
-  </si>
-  <si>
     <t>21679</t>
   </si>
   <si>
-    <t>33458</t>
-  </si>
-  <si>
-    <t>35126</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>3535</t>
-  </si>
-  <si>
-    <t>15540</t>
-  </si>
-  <si>
-    <t>15762</t>
+    <t>2568</t>
+  </si>
+  <si>
+    <t>2586</t>
+  </si>
+  <si>
+    <t>5599</t>
+  </si>
+  <si>
+    <t>6782</t>
+  </si>
+  <si>
+    <t>17181</t>
+  </si>
+  <si>
+    <t>19844</t>
+  </si>
+  <si>
+    <t>19845</t>
+  </si>
+  <si>
+    <t>24621</t>
+  </si>
+  <si>
+    <t>33869</t>
+  </si>
+  <si>
+    <t>36326</t>
+  </si>
+  <si>
+    <t>36</t>
   </si>
   <si>
     <t>746</t>
@@ -202,501 +207,597 @@
     <t>838</t>
   </si>
   <si>
-    <t>3400</t>
-  </si>
-  <si>
-    <t>22695</t>
-  </si>
-  <si>
-    <t>22705</t>
-  </si>
-  <si>
-    <t>3952</t>
-  </si>
-  <si>
-    <t>9751</t>
+    <t>942</t>
+  </si>
+  <si>
+    <t>2322</t>
+  </si>
+  <si>
+    <t>2359</t>
+  </si>
+  <si>
+    <t>22639</t>
+  </si>
+  <si>
+    <t>37768</t>
+  </si>
+  <si>
+    <t>6781</t>
+  </si>
+  <si>
+    <t>1270</t>
+  </si>
+  <si>
+    <t>1277</t>
+  </si>
+  <si>
+    <t>2084</t>
+  </si>
+  <si>
+    <t>3835</t>
+  </si>
+  <si>
+    <t>13457</t>
+  </si>
+  <si>
+    <t>15182</t>
+  </si>
+  <si>
+    <t>18814</t>
+  </si>
+  <si>
+    <t>2396</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>1415</t>
+  </si>
+  <si>
+    <t>3181</t>
+  </si>
+  <si>
+    <t>3204</t>
+  </si>
+  <si>
+    <t>3289</t>
+  </si>
+  <si>
+    <t>3294</t>
+  </si>
+  <si>
+    <t>20613</t>
+  </si>
+  <si>
+    <t>37519</t>
+  </si>
+  <si>
+    <t>835</t>
+  </si>
+  <si>
+    <t>5431</t>
+  </si>
+  <si>
+    <t>8838</t>
+  </si>
+  <si>
+    <t>8840</t>
+  </si>
+  <si>
+    <t>12395</t>
+  </si>
+  <si>
+    <t>12398</t>
+  </si>
+  <si>
+    <t>1661</t>
+  </si>
+  <si>
+    <t>1713</t>
+  </si>
+  <si>
+    <t>2216</t>
+  </si>
+  <si>
+    <t>2232</t>
+  </si>
+  <si>
+    <t>20609</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>3720</t>
+  </si>
+  <si>
+    <t>1689</t>
+  </si>
+  <si>
+    <t>8233</t>
+  </si>
+  <si>
+    <t>PAPEL HIG MAXPEL PREMIUM FS 60M L12P11</t>
+  </si>
+  <si>
+    <t>MOLHO TOM CAJAMAR SH 300G TRAD</t>
+  </si>
+  <si>
+    <t>ERVA MATE VERDINHA 1KG MOIDA GROSSA</t>
+  </si>
+  <si>
+    <t>DESOD AERO REXONA 150ML 90G ACT EMOTION</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL C TAMP DESN 1L</t>
+  </si>
+  <si>
+    <t>DESINF GOTA LIMPA 500ML LAVANDA</t>
+  </si>
+  <si>
+    <t>L MOVEIS POLWAX 200ML JASMIN</t>
+  </si>
+  <si>
+    <t>L MOVEIS POLWAX 200ML LAVANDA</t>
+  </si>
+  <si>
+    <t>TAP HIG MR DRY C 7 80X60G</t>
+  </si>
+  <si>
+    <t>REFRE HAPPY TP 200ML LARANJA</t>
+  </si>
+  <si>
+    <t>SODA CAUSTICA ESCAMA SODABEL 1KG</t>
+  </si>
+  <si>
+    <t>AGUA MIN CRYSTAL PET 500ML C GAS</t>
+  </si>
+  <si>
+    <t>ACUCAR CRISTAL GASPARIN 1KG</t>
+  </si>
+  <si>
+    <t>REFRIG FRUKI PET 3L GUARANA</t>
+  </si>
+  <si>
+    <t>AZEITE OLIV BORGES EXT VG 500ML</t>
+  </si>
+  <si>
+    <t>AZEITONA VDE V FERTIL SH 150G C CAR</t>
+  </si>
+  <si>
+    <t>FEIJAO RAJADO SERRA URUGUAI 500GR</t>
+  </si>
+  <si>
+    <t>QJO RAL SANTA CLARA 40G PARMESAO</t>
+  </si>
+  <si>
+    <t>LEITE UHT BATAVO ZR LAC DESN 1L</t>
+  </si>
+  <si>
+    <t>LEITE UHT ELEGE INT 1L</t>
+  </si>
+  <si>
+    <t>BISC DOCE PARATI ROSCA 250G COCO</t>
+  </si>
+  <si>
+    <t>BISC DOCE PARATI ROSCA 250G CHOCOLATE</t>
+  </si>
+  <si>
+    <t>ARROZ BCO REQUINTE TP1 1KG</t>
+  </si>
+  <si>
+    <t>EXT TOM FUGINI SH 190G</t>
+  </si>
+  <si>
+    <t>BISC RECH PARATI Z CARTOON 85G FLOCOS</t>
+  </si>
+  <si>
+    <t>CAFE SOL NESCAFE MATINAL VD 200G</t>
+  </si>
+  <si>
+    <t>FRALDA PAMPERS SUPERSEQUINHA C 60 G</t>
+  </si>
+  <si>
+    <t>MILHO VERDE OLE LT 170G</t>
+  </si>
+  <si>
+    <t>AGUA MIN FLORESTA PET 500ML S GAS</t>
+  </si>
+  <si>
+    <t>BISC MAIZENA ISABELA 350G</t>
+  </si>
+  <si>
+    <t>SALG KEVYTOS SHOW 38G BACON</t>
+  </si>
+  <si>
+    <t>CHOC GRAN DORI 70G</t>
+  </si>
+  <si>
+    <t>SALG OBBA 100G PRESUNTO</t>
+  </si>
+  <si>
+    <t>SALG ALFITOS 35G QUEIJO</t>
+  </si>
+  <si>
+    <t>MAS ESPAGUETINI ISABELA SEMOLA 500G</t>
+  </si>
+  <si>
+    <t>BATATA PALHA AGITUS 70G TRAD</t>
+  </si>
+  <si>
+    <t>REFRIG PET COCA COLA 3L</t>
+  </si>
+  <si>
+    <t>DESINF AQUAFAST HARMONIA 5L LAVANDA</t>
+  </si>
+  <si>
+    <t>AMAC AQUAFAST 2L ROSA JARD FLORI</t>
+  </si>
+  <si>
+    <t>AMAC AQUAFAST EMB ECON 5L VERM SEDUCAO</t>
+  </si>
+  <si>
+    <t>AMACIANTE AQUAFAST 2L VERM SED</t>
+  </si>
+  <si>
+    <t>AMACIANTE AQUAFAST 5L JARD FLOR</t>
+  </si>
+  <si>
+    <t>WAFFER ISABELA 100G CHOC BRANCO</t>
+  </si>
+  <si>
+    <t>PIPOCA DOCE KEVYTOS 50G</t>
+  </si>
+  <si>
+    <t>CAPSULA DOLCE GUSTO 100G C 10 CAFE AU LAIT</t>
+  </si>
+  <si>
+    <t>CAPSULA DOLCE GUSTO 117G C 10 CAPPUCCINO</t>
+  </si>
+  <si>
+    <t>MAS ESPAG ISABELA SEMOLA 400G</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 5L S GAS</t>
+  </si>
+  <si>
+    <t>ALHO EM PASTA ALHOSTIN 200G</t>
+  </si>
+  <si>
+    <t>MARSHMALLOWS FOFS 220G BRUXOLITO PINTA</t>
+  </si>
+  <si>
+    <t>SH HEAD SHOULDERS 200ML REMO OLEOSIDA</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>11/12/2024</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>29/08/2025</t>
+  </si>
+  <si>
+    <t>31/01/2026</t>
+  </si>
+  <si>
+    <t>18/09/2024</t>
+  </si>
+  <si>
+    <t>17/10/2024</t>
+  </si>
+  <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>24/10/2024</t>
+  </si>
+  <si>
+    <t>07/12/2024</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>07/11/2024</t>
+  </si>
+  <si>
+    <t>03/12/2024</t>
+  </si>
+  <si>
+    <t>10/01/2025</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>11/11/2024</t>
+  </si>
+  <si>
+    <t>20/12/2024</t>
+  </si>
+  <si>
+    <t>21/12/2024</t>
+  </si>
+  <si>
+    <t>23/12/2024</t>
+  </si>
+  <si>
+    <t>24/12/2024</t>
+  </si>
+  <si>
+    <t>14/03/2026</t>
+  </si>
+  <si>
+    <t>19/11/2024</t>
+  </si>
+  <si>
+    <t>22/11/2024</t>
+  </si>
+  <si>
+    <t>05/12/2024</t>
+  </si>
+  <si>
+    <t>31/12/2024</t>
+  </si>
+  <si>
+    <t>21/11/2024</t>
+  </si>
+  <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>2084</t>
-  </si>
-  <si>
-    <t>18814</t>
-  </si>
-  <si>
-    <t>33287</t>
-  </si>
-  <si>
-    <t>1415</t>
-  </si>
-  <si>
-    <t>3181</t>
-  </si>
-  <si>
-    <t>3204</t>
-  </si>
-  <si>
-    <t>3289</t>
-  </si>
-  <si>
-    <t>3294</t>
-  </si>
-  <si>
-    <t>835</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>1713</t>
-  </si>
-  <si>
-    <t>2216</t>
-  </si>
-  <si>
-    <t>2232</t>
-  </si>
-  <si>
-    <t>2953</t>
-  </si>
-  <si>
-    <t>3092</t>
-  </si>
-  <si>
-    <t>3704</t>
-  </si>
-  <si>
-    <t>20609</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>4044</t>
-  </si>
-  <si>
-    <t>4045</t>
-  </si>
-  <si>
-    <t>1689</t>
-  </si>
-  <si>
-    <t>CESTA BASICA PEQ</t>
-  </si>
-  <si>
-    <t>DESINF APYCE 2L JASMIM</t>
-  </si>
-  <si>
-    <t>DESINF APYCE 2L LAVANDA</t>
-  </si>
-  <si>
-    <t>DET PO APYCE SH 4K ROSA</t>
-  </si>
-  <si>
-    <t>PAPEL HIG MAXPEL PREMIUM FS 60M L12P11</t>
-  </si>
-  <si>
-    <t>AMACIANTE APYCE 2L TRAD AZ</t>
-  </si>
-  <si>
-    <t>DET PO APYCE MULT SH 800G ROSA</t>
-  </si>
-  <si>
-    <t>CERV BUDWEISER GF 1L RETORNAVEL</t>
-  </si>
-  <si>
-    <t>CAPSULA DOLCE GUSTO 110G C 10 AU LAIT VANILLA</t>
-  </si>
-  <si>
-    <t>FERM QUIMICO PO ROYAL PT 250G</t>
-  </si>
-  <si>
-    <t>CAP DOLCE GUSTO LATTE MACCHIA C 10</t>
-  </si>
-  <si>
-    <t>CESTA BASICA GRD</t>
-  </si>
-  <si>
-    <t>ACUCAR CRISTAL GASPARIN 1KG</t>
-  </si>
-  <si>
-    <t>REFRIG FRUKI PET 3L GUARANA</t>
-  </si>
-  <si>
-    <t>BARRA CER RITTER 25G BAN AVEIA MEL</t>
-  </si>
-  <si>
-    <t>RAC CAO QUATRO PAT PREM 1K</t>
-  </si>
-  <si>
-    <t>RACAO DODOG RAC PEQ 1KG</t>
-  </si>
-  <si>
-    <t>AGUA SANIT Q BOA 5L</t>
-  </si>
-  <si>
-    <t>LEITE UHT STA CLARA INT 1L</t>
-  </si>
-  <si>
-    <t>REFRIG COCA COLA PET 2L</t>
-  </si>
-  <si>
-    <t>ARROZ BCO REQUINTE TP1 1KG</t>
-  </si>
-  <si>
-    <t>FRALDA PAMPERS SUPERSEQUINHA C 60 G</t>
-  </si>
-  <si>
-    <t>AMAC APYCE 5L JASMIM RSA</t>
-  </si>
-  <si>
-    <t>BISC MAIZENA ISABELA 350G</t>
-  </si>
-  <si>
-    <t>SALG KEVYTOS SHOW 38G BACON</t>
-  </si>
-  <si>
-    <t>CHOC GRAN DORI 70G</t>
-  </si>
-  <si>
-    <t>SALG OBBA 100G PRESUNTO</t>
-  </si>
-  <si>
-    <t>SALG ALFITOS 35G QUEIJO</t>
-  </si>
-  <si>
-    <t>REFRIG PET COCA COLA 3L</t>
-  </si>
-  <si>
-    <t>AGUA MIN FLORESTA PET 500ML C GAS</t>
-  </si>
-  <si>
-    <t>PIPOCA DOCE KEVYTOS 50G</t>
-  </si>
-  <si>
-    <t>CAPSULA DOLCE GUSTO 100G C 10 CAFE AU LAIT</t>
-  </si>
-  <si>
-    <t>CAPSULA DOLCE GUSTO 117G C 10 CAPPUCCINO</t>
-  </si>
-  <si>
-    <t>ACHOC PO APTI SH 700G INSTANT POWER</t>
-  </si>
-  <si>
-    <t>MOSTARDA ODERICH TRADICIONAL 190G BISNAGA</t>
-  </si>
-  <si>
-    <t>MIST P BOLO APTI 400G CHOC</t>
-  </si>
-  <si>
-    <t>MAS ESPAG ISABELA SEMOLA 400G</t>
-  </si>
-  <si>
-    <t>AGUA MIN DA PEDRA PET 5L S GAS</t>
-  </si>
-  <si>
-    <t>RACAO FRISKIES SH 85G ATUM MOLHO</t>
-  </si>
-  <si>
-    <t>RACAO FRISKIES SH 85G CARNE MOLHO</t>
-  </si>
-  <si>
-    <t>MARSHMALLOWS FOFS 220G BRUXOLITO PINTA</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>05/08/2025</t>
-  </si>
-  <si>
-    <t>20/12/2025</t>
-  </si>
-  <si>
-    <t>23/09/2024</t>
-  </si>
-  <si>
-    <t>05/12/2024</t>
-  </si>
-  <si>
-    <t>28/12/2024</t>
-  </si>
-  <si>
-    <t>17/10/2024</t>
-  </si>
-  <si>
-    <t>21/10/2024</t>
-  </si>
-  <si>
-    <t>26/12/2024</t>
-  </si>
-  <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>16/09/2024</t>
-  </si>
-  <si>
-    <t>03/12/2024</t>
-  </si>
-  <si>
-    <t>10/07/2025</t>
-  </si>
-  <si>
-    <t>11/11/2024</t>
-  </si>
-  <si>
-    <t>20/12/2024</t>
-  </si>
-  <si>
-    <t>21/12/2024</t>
-  </si>
-  <si>
-    <t>23/12/2024</t>
-  </si>
-  <si>
-    <t>24/12/2024</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>22/11/2024</t>
-  </si>
-  <si>
-    <t>17/12/2024</t>
-  </si>
-  <si>
-    <t>19/12/2024</t>
-  </si>
-  <si>
-    <t>31/12/2024</t>
-  </si>
-  <si>
-    <t>21/11/2024</t>
-  </si>
-  <si>
-    <t>Ativo</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>24</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>16</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
-    <t>106</t>
+    <t>107</t>
+  </si>
+  <si>
+    <t>1949</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>1588</t>
   </si>
   <si>
     <t>197</t>
   </si>
   <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>294</t>
-  </si>
-  <si>
-    <t>1652</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>4031</t>
-  </si>
-  <si>
-    <t>1564</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>409</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>9511</t>
-  </si>
-  <si>
-    <t>5538</t>
-  </si>
-  <si>
-    <t>532</t>
-  </si>
-  <si>
-    <t>5423</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>39</t>
+    <t>62</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>5927</t>
+  </si>
+  <si>
+    <t>4041</t>
+  </si>
+  <si>
+    <t>1574</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>1928</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>1442</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>521</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>486</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>12542</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>582</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t>204</t>
   </si>
   <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>24997</t>
-  </si>
-  <si>
-    <t>568</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>334</t>
-  </si>
-  <si>
-    <t>442</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>428</t>
-  </si>
-  <si>
-    <t>10517</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO BAKLIZI LTDA</t>
+    <t>422</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>NATURAPEL IND DE PAPEIS LTDA</t>
+  </si>
+  <si>
+    <t>STELLA DORO ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>MATEVEL-ERVA MATE VERDINHA LTDA.</t>
   </si>
   <si>
     <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
   </si>
   <si>
-    <t>NATURAPEL IND DE PAPEIS LTDA</t>
-  </si>
-  <si>
-    <t>CRBS AS CDD PELOTAS</t>
+    <t>LATICINIOS TIROL LTDA.</t>
+  </si>
+  <si>
+    <t>BERTOLINI INDUSTRIA QUIMICA LTDA</t>
+  </si>
+  <si>
+    <t>POLWAX INDUSTRIA QUIMICA LTDA</t>
+  </si>
+  <si>
+    <t>UPPER DOG COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>COOP VITIVINICOLA ALIANCA LTDA</t>
+  </si>
+  <si>
+    <t>BUSCHLE E LEPPER S.A.</t>
+  </si>
+  <si>
+    <t>SPAL IND BRAS BEBIDAS AS</t>
+  </si>
+  <si>
+    <t>GASPARIN CEREAIS LTDA ME</t>
+  </si>
+  <si>
+    <t>BEBIDAS FRUKI LTDA</t>
+  </si>
+  <si>
+    <t>CARGIL AGRICOLA S A GOIANI</t>
+  </si>
+  <si>
+    <t>TOZZO ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>CEREAIS RUVIARO LTDA</t>
+  </si>
+  <si>
+    <t>COOP SANTA CLARA LTDA IND DE LATICINIOS</t>
+  </si>
+  <si>
+    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
+  </si>
+  <si>
+    <t>PARATI IND.COM.DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>GENESIO CEOLIN E CIA LTDA</t>
+  </si>
+  <si>
+    <t>FUGINI ALIMENTOS LTDA</t>
   </si>
   <si>
     <t>NESTLE BRASIL LTDA</t>
   </si>
   <si>
-    <t>TOPFLEX DISTRIBUIDOR DE ALIMENTOS</t>
-  </si>
-  <si>
-    <t>GASPARIN CEREAIS LTDA ME</t>
-  </si>
-  <si>
-    <t>BEBIDAS FRUKI LTDA</t>
-  </si>
-  <si>
-    <t>RITTER ALIMENTOS S.A.</t>
-  </si>
-  <si>
-    <t>NUTRISUL ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>INDUSTRIAS ANHEMBI LTDA.</t>
-  </si>
-  <si>
-    <t>COOP SANTA CLARA LTDA IND DE LATICINIOS</t>
-  </si>
-  <si>
-    <t>SPAL IND BRAS BEBIDAS AS</t>
-  </si>
-  <si>
-    <t>GENESIO CEOLIN E CIA LTDA</t>
-  </si>
-  <si>
     <t>ONIZ DISTRIBUID LTDA SCJ</t>
   </si>
   <si>
+    <t>ANGELO AURICCHIO &amp; CIA LTDA</t>
+  </si>
+  <si>
+    <t>AGUAS MINERAIS SARANDI LTDA</t>
+  </si>
+  <si>
     <t>M DIAS BRANCO S.A IND E COM DE ALIMENTOS</t>
   </si>
   <si>
@@ -709,13 +810,13 @@
     <t>FITOS ALIMENTOS LTDA</t>
   </si>
   <si>
-    <t>AGUAS MINERAIS SARANDI LTDA</t>
-  </si>
-  <si>
-    <t>APTI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>CONSERVAS ODERICH SA</t>
+    <t>FRITURARTE INDUSTRIA E COMERCIO EIRELI</t>
+  </si>
+  <si>
+    <t>AQUAFAST PROD LIMPEZA/HIGIENE LTDA</t>
+  </si>
+  <si>
+    <t>DAGEMAR ANTONIO DELLAGOSTIN</t>
   </si>
   <si>
     <t>FLORESTAL ALIMENTOS S.A.</t>
@@ -724,8 +825,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -762,13 +863,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -806,7 +915,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -840,6 +949,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -874,9 +984,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1049,11 +1160,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X58"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:X54"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="44" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1127,57 +1241,57 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="G2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H2" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I2" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N2">
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="P2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Q2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -1189,51 +1303,51 @@
         <v>90</v>
       </c>
       <c r="U2">
-        <v>15</v>
+        <v>8305</v>
       </c>
       <c r="V2" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="W2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F3" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="H3" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I3" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>319</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1245,13 +1359,13 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="P3">
-        <v>8</v>
+        <v>320</v>
       </c>
       <c r="Q3">
-        <v>14</v>
+        <v>416</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1263,69 +1377,69 @@
         <v>90</v>
       </c>
       <c r="U3">
-        <v>5894</v>
+        <v>11515</v>
       </c>
       <c r="V3" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="W3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X3">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24">
+        <v>506.97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G4" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="H4" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I4" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K4">
+        <v>7</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>191</v>
+      </c>
+      <c r="P4">
         <v>12</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>172</v>
-      </c>
-      <c r="P4">
-        <v>22</v>
-      </c>
       <c r="Q4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1337,19 +1451,19 @@
         <v>90</v>
       </c>
       <c r="U4">
-        <v>5894</v>
+        <v>6189</v>
       </c>
       <c r="V4" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="W4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1357,28 +1471,28 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F5" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G5" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="H5" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I5" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K5">
         <v>8</v>
@@ -1393,13 +1507,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="P5">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1414,66 +1528,66 @@
         <v>5894</v>
       </c>
       <c r="V5" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="X5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G6" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="H6" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I6" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="P6">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="Q6">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1485,19 +1599,19 @@
         <v>90</v>
       </c>
       <c r="U6">
-        <v>8305</v>
+        <v>15208</v>
       </c>
       <c r="V6" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="W6">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="X6">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24">
+        <v>189.92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1505,31 +1619,31 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G7" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="H7" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I7" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K7">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1541,13 +1655,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="P7">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="Q7">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1559,19 +1673,19 @@
         <v>90</v>
       </c>
       <c r="U7">
-        <v>5894</v>
+        <v>14468</v>
       </c>
       <c r="V7" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X7">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1579,105 +1693,105 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F8" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G8" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="H8" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>12</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>188</v>
+      </c>
+      <c r="P8">
+        <v>18</v>
+      </c>
+      <c r="Q8">
+        <v>42</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>90</v>
+      </c>
+      <c r="U8">
+        <v>10489</v>
+      </c>
+      <c r="V8" t="s">
+        <v>237</v>
+      </c>
+      <c r="W8">
+        <v>3</v>
+      </c>
+      <c r="X8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>25</v>
       </c>
-      <c r="K8">
-        <v>26</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>176</v>
-      </c>
-      <c r="P8">
-        <v>195</v>
-      </c>
-      <c r="Q8">
-        <v>320</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>90</v>
-      </c>
-      <c r="U8">
-        <v>5894</v>
-      </c>
-      <c r="V8" t="s">
-        <v>213</v>
-      </c>
-      <c r="W8">
-        <v>12</v>
-      </c>
-      <c r="X8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F9" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="H9" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I9" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="J9">
         <v>12</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1689,13 +1803,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q9">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1707,51 +1821,51 @@
         <v>90</v>
       </c>
       <c r="U9">
-        <v>9638</v>
+        <v>10489</v>
       </c>
       <c r="V9" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="W9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X9">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F10" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H10" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I10" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1763,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1781,21 +1895,21 @@
         <v>90</v>
       </c>
       <c r="U10">
-        <v>15134</v>
+        <v>21902</v>
       </c>
       <c r="V10" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="W10">
         <v>2</v>
       </c>
       <c r="X10">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
@@ -1804,28 +1918,28 @@
         <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G11" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="H11" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I11" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1837,13 +1951,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="P11">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q11">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1855,51 +1969,51 @@
         <v>90</v>
       </c>
       <c r="U11">
-        <v>13838</v>
+        <v>10224</v>
       </c>
       <c r="V11" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="W11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X11">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
+        <v>11.83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F12" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G12" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="H12" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I12" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1911,13 +2025,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="P12">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1929,10 +2043,10 @@
         <v>90</v>
       </c>
       <c r="U12">
-        <v>15134</v>
+        <v>17054</v>
       </c>
       <c r="V12" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="W12">
         <v>2</v>
@@ -1941,39 +2055,39 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F13" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="G13" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="H13" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I13" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1985,37 +2099,37 @@
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="P13">
+        <v>76</v>
+      </c>
+      <c r="Q13">
+        <v>112</v>
+      </c>
+      <c r="R13">
+        <v>1008</v>
+      </c>
+      <c r="S13">
+        <v>1308</v>
+      </c>
+      <c r="T13">
+        <v>90</v>
+      </c>
+      <c r="U13">
+        <v>15441</v>
+      </c>
+      <c r="V13" t="s">
+        <v>241</v>
+      </c>
+      <c r="W13">
         <v>10</v>
       </c>
-      <c r="Q13">
-        <v>15</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>90</v>
-      </c>
-      <c r="U13">
-        <v>15</v>
-      </c>
-      <c r="V13" t="s">
-        <v>212</v>
-      </c>
-      <c r="W13">
-        <v>15</v>
-      </c>
       <c r="X13">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+        <v>246.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -2023,31 +2137,31 @@
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="G14" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="H14" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I14" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2059,13 +2173,13 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="P14">
-        <v>10</v>
+        <v>254</v>
       </c>
       <c r="Q14">
-        <v>15</v>
+        <v>384</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -2077,51 +2191,51 @@
         <v>90</v>
       </c>
       <c r="U14">
-        <v>15</v>
+        <v>6158</v>
       </c>
       <c r="V14" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="W14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="X14">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+        <v>552.20000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F15" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G15" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="H15" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I15" t="s">
-        <v>67</v>
+        <v>182</v>
       </c>
       <c r="J15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>253</v>
+        <v>145</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2133,13 +2247,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="s">
+        <v>199</v>
+      </c>
+      <c r="P15">
         <v>180</v>
       </c>
-      <c r="P15">
-        <v>254</v>
-      </c>
       <c r="Q15">
-        <v>384</v>
+        <v>240</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -2151,51 +2265,51 @@
         <v>90</v>
       </c>
       <c r="U15">
-        <v>6158</v>
+        <v>6424</v>
       </c>
       <c r="V15" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="W15">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="X15">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G16" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H16" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I16" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K16">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2207,13 +2321,13 @@
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="P16">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="Q16">
-        <v>240</v>
+        <v>34</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -2225,51 +2339,51 @@
         <v>90</v>
       </c>
       <c r="U16">
-        <v>6424</v>
+        <v>15139</v>
       </c>
       <c r="V16" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="W16">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="X16">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F17" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G17" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="H17" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I17" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="J17">
         <v>24</v>
       </c>
       <c r="K17">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2281,13 +2395,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="P17">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="Q17">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2299,19 +2413,19 @@
         <v>90</v>
       </c>
       <c r="U17">
-        <v>5666</v>
+        <v>2881</v>
       </c>
       <c r="V17" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="W17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X17">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -2322,28 +2436,28 @@
         <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F18" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="G18" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="H18" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I18" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2355,13 +2469,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="P18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q18">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -2373,51 +2487,51 @@
         <v>90</v>
       </c>
       <c r="U18">
-        <v>15</v>
+        <v>12743</v>
       </c>
       <c r="V18" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="X18">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
         <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="F19" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="G19" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H19" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I19" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2429,13 +2543,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="P19">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="Q19">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -2447,24 +2561,24 @@
         <v>90</v>
       </c>
       <c r="U19">
-        <v>15</v>
+        <v>10421</v>
       </c>
       <c r="V19" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="W19">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
@@ -2473,25 +2587,25 @@
         <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F20" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G20" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="H20" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I20" t="s">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="J20">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K20">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2500,16 +2614,16 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="P20">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q20">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -2521,51 +2635,51 @@
         <v>90</v>
       </c>
       <c r="U20">
-        <v>17077</v>
+        <v>9379</v>
       </c>
       <c r="V20" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="W20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
         <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F21" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G21" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="H21" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I21" t="s">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="J21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K21">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -2577,13 +2691,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="P21">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="Q21">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -2595,125 +2709,125 @@
         <v>90</v>
       </c>
       <c r="U21">
-        <v>17077</v>
+        <v>9379</v>
       </c>
       <c r="V21" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="X21">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
         <v>65</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G22" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="H22" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I22" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="P22">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q22">
+        <v>28</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>90</v>
+      </c>
+      <c r="U22">
+        <v>12257</v>
+      </c>
+      <c r="V22" t="s">
+        <v>249</v>
+      </c>
+      <c r="W22">
+        <v>2</v>
+      </c>
+      <c r="X22">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>24</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>90</v>
-      </c>
-      <c r="U22">
-        <v>9499</v>
-      </c>
-      <c r="V22" t="s">
-        <v>222</v>
-      </c>
-      <c r="W22">
-        <v>5</v>
-      </c>
-      <c r="X22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24">
-      <c r="A23" t="s">
-        <v>28</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
         <v>66</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F23" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G23" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="H23" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I23" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="J23">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K23">
-        <v>622</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -2725,13 +2839,13 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P23">
-        <v>720</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>1020</v>
+        <v>26</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -2743,24 +2857,24 @@
         <v>90</v>
       </c>
       <c r="U23">
-        <v>10421</v>
+        <v>12257</v>
       </c>
       <c r="V23" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="W23">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="X23">
-        <v>5504</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -2769,25 +2883,25 @@
         <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F24" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="G24" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="H24" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I24" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="J24">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="K24">
-        <v>366</v>
+        <v>36</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -2799,37 +2913,37 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="P24">
-        <v>406</v>
+        <v>44</v>
       </c>
       <c r="Q24">
-        <v>634</v>
+        <v>74</v>
       </c>
       <c r="R24">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="T24">
         <v>90</v>
       </c>
       <c r="U24">
-        <v>15441</v>
+        <v>13087</v>
       </c>
       <c r="V24" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="W24">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="X24">
-        <v>6128</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2843,25 +2957,25 @@
         <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F25" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G25" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I25" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="J25">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K25">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2873,13 +2987,13 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="P25">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="Q25">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2891,51 +3005,51 @@
         <v>90</v>
       </c>
       <c r="U25">
-        <v>13087</v>
+        <v>5791</v>
       </c>
       <c r="V25" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W25">
         <v>2</v>
       </c>
       <c r="X25">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
         <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="F26" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="G26" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H26" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I26" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2947,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="P26">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="Q26">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -2965,241 +3079,241 @@
         <v>90</v>
       </c>
       <c r="U26">
-        <v>15</v>
+        <v>12257</v>
       </c>
       <c r="V26" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="X26">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
         <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="F27" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G27" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H27" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I27" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J27">
+        <v>12</v>
+      </c>
+      <c r="K27">
+        <v>6</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>178</v>
+      </c>
+      <c r="P27">
+        <v>12</v>
+      </c>
+      <c r="Q27">
+        <v>24</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>90</v>
+      </c>
+      <c r="U27">
+        <v>15134</v>
+      </c>
+      <c r="V27" t="s">
+        <v>252</v>
+      </c>
+      <c r="W27">
         <v>2</v>
       </c>
-      <c r="K27">
+      <c r="X27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" t="s">
+        <v>147</v>
+      </c>
+      <c r="G28" t="s">
+        <v>148</v>
+      </c>
+      <c r="H28" t="s">
+        <v>175</v>
+      </c>
+      <c r="I28" t="s">
+        <v>187</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28">
         <v>7</v>
       </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>159</v>
-      </c>
-      <c r="P27">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>176</v>
+      </c>
+      <c r="P28">
         <v>8</v>
       </c>
-      <c r="Q27">
+      <c r="Q28">
         <v>12</v>
       </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>90</v>
-      </c>
-      <c r="U27">
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>90</v>
+      </c>
+      <c r="U28">
         <v>6644</v>
       </c>
-      <c r="V27" t="s">
-        <v>226</v>
-      </c>
-      <c r="W27">
+      <c r="V28" t="s">
+        <v>253</v>
+      </c>
+      <c r="W28">
         <v>3</v>
       </c>
-      <c r="X27">
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24">
-      <c r="A28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" t="s">
-        <v>130</v>
-      </c>
-      <c r="G28" t="s">
-        <v>133</v>
-      </c>
-      <c r="H28" t="s">
-        <v>157</v>
-      </c>
-      <c r="I28" t="s">
-        <v>158</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
-        <v>170</v>
-      </c>
-      <c r="P28">
-        <v>10</v>
-      </c>
-      <c r="Q28">
-        <v>15</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>90</v>
-      </c>
-      <c r="U28">
-        <v>15</v>
-      </c>
-      <c r="V28" t="s">
-        <v>212</v>
-      </c>
-      <c r="W28">
-        <v>15</v>
-      </c>
       <c r="X28">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="G29" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H29" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I29" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K29">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N29">
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="P29">
-        <v>394</v>
+        <v>18</v>
       </c>
       <c r="Q29">
-        <v>614</v>
+        <v>42</v>
       </c>
       <c r="R29">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="T29">
         <v>90</v>
       </c>
       <c r="U29">
-        <v>15441</v>
+        <v>10489</v>
       </c>
       <c r="V29" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="W29">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="X29">
-        <v>6128</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -3207,31 +3321,31 @@
         <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F30" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G30" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H30" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I30" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3243,69 +3357,69 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="P30">
         <v>16</v>
       </c>
       <c r="Q30">
+        <v>40</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>90</v>
+      </c>
+      <c r="U30">
+        <v>10489</v>
+      </c>
+      <c r="V30" t="s">
+        <v>237</v>
+      </c>
+      <c r="W30">
+        <v>4</v>
+      </c>
+      <c r="X30">
         <v>28</v>
       </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>90</v>
-      </c>
-      <c r="U30">
-        <v>5894</v>
-      </c>
-      <c r="V30" t="s">
-        <v>213</v>
-      </c>
-      <c r="W30">
-        <v>3</v>
-      </c>
-      <c r="X30">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24">
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F31" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G31" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="H31" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I31" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="K31">
-        <v>-5</v>
+        <v>175</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3317,13 +3431,13 @@
         <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="P31">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="Q31">
-        <v>8</v>
+        <v>288</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -3335,69 +3449,69 @@
         <v>90</v>
       </c>
       <c r="U31">
-        <v>5894</v>
+        <v>7715</v>
       </c>
       <c r="V31" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="W31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X31">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24">
+        <v>498.04</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G32" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="H32" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I32" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K32">
+        <v>-59</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>211</v>
+      </c>
+      <c r="P32">
         <v>24</v>
       </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>192</v>
-      </c>
-      <c r="P32">
-        <v>28</v>
-      </c>
       <c r="Q32">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -3409,51 +3523,51 @@
         <v>90</v>
       </c>
       <c r="U32">
-        <v>5894</v>
+        <v>10181</v>
       </c>
       <c r="V32" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="W32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X32">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24">
+        <v>35.92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="F33" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G33" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="H33" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I33" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="J33">
         <v>24</v>
       </c>
       <c r="K33">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3465,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="P33">
         <v>44</v>
@@ -3486,48 +3600,48 @@
         <v>7995</v>
       </c>
       <c r="V33" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="W33">
         <v>2</v>
       </c>
       <c r="X33">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:24">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E34" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="F34" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G34" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="H34" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I34" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="J34">
         <v>20</v>
       </c>
       <c r="K34">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -3539,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="P34">
         <v>20</v>
@@ -3560,48 +3674,48 @@
         <v>2977</v>
       </c>
       <c r="V34" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="W34">
         <v>2</v>
       </c>
       <c r="X34">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E35" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F35" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G35" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H35" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I35" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="J35">
         <v>30</v>
       </c>
       <c r="K35">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3613,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="P35">
         <v>70</v>
@@ -3634,7 +3748,7 @@
         <v>8539</v>
       </c>
       <c r="V35" t="s">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="W35">
         <v>2</v>
@@ -3643,39 +3757,39 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E36" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F36" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G36" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="H36" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I36" t="s">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="J36">
         <v>10</v>
       </c>
       <c r="K36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3687,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="P36">
         <v>10</v>
@@ -3708,48 +3822,48 @@
         <v>16857</v>
       </c>
       <c r="V36" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="W36">
         <v>2</v>
       </c>
       <c r="X36">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="F37" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G37" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="H37" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I37" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="J37">
         <v>30</v>
       </c>
       <c r="K37">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3761,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="P37">
         <v>18</v>
@@ -3782,492 +3896,492 @@
         <v>16857</v>
       </c>
       <c r="V37" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="W37">
         <v>2</v>
       </c>
       <c r="X37">
+        <v>9.9700000000000006</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" t="s">
+        <v>130</v>
+      </c>
+      <c r="F38" t="s">
+        <v>147</v>
+      </c>
+      <c r="G38" t="s">
+        <v>148</v>
+      </c>
+      <c r="H38" t="s">
+        <v>175</v>
+      </c>
+      <c r="I38" t="s">
+        <v>178</v>
+      </c>
+      <c r="J38">
+        <v>20</v>
+      </c>
+      <c r="K38">
+        <v>11</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
+        <v>216</v>
+      </c>
+      <c r="P38">
         <v>12</v>
       </c>
-    </row>
-    <row r="38" spans="1:24">
-      <c r="A38" t="s">
+      <c r="Q38">
+        <v>32</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>90</v>
+      </c>
+      <c r="U38">
+        <v>7995</v>
+      </c>
+      <c r="V38" t="s">
+        <v>256</v>
+      </c>
+      <c r="W38">
+        <v>2</v>
+      </c>
+      <c r="X38">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" t="s">
+        <v>80</v>
+      </c>
+      <c r="E39" t="s">
+        <v>131</v>
+      </c>
+      <c r="F39" t="s">
+        <v>147</v>
+      </c>
+      <c r="G39" t="s">
+        <v>169</v>
+      </c>
+      <c r="H39" t="s">
+        <v>175</v>
+      </c>
+      <c r="I39" t="s">
+        <v>185</v>
+      </c>
+      <c r="J39">
+        <v>30</v>
+      </c>
+      <c r="K39">
+        <v>29</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>217</v>
+      </c>
+      <c r="P39">
+        <v>60</v>
+      </c>
+      <c r="Q39">
+        <v>90</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>90</v>
+      </c>
+      <c r="U39">
+        <v>22017</v>
+      </c>
+      <c r="V39" t="s">
+        <v>260</v>
+      </c>
+      <c r="W39">
+        <v>3</v>
+      </c>
+      <c r="X39">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F40" t="s">
+        <v>147</v>
+      </c>
+      <c r="G40" t="s">
+        <v>155</v>
+      </c>
+      <c r="H40" t="s">
+        <v>175</v>
+      </c>
+      <c r="I40" t="s">
+        <v>176</v>
+      </c>
+      <c r="J40">
+        <v>6</v>
+      </c>
+      <c r="K40">
+        <v>34</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" t="s">
+        <v>218</v>
+      </c>
+      <c r="P40">
+        <v>54</v>
+      </c>
+      <c r="Q40">
+        <v>60</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>90</v>
+      </c>
+      <c r="U40">
+        <v>15441</v>
+      </c>
+      <c r="V40" t="s">
+        <v>241</v>
+      </c>
+      <c r="W40">
+        <v>5</v>
+      </c>
+      <c r="X40">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>25</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B41" t="s">
         <v>30</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C41" t="s">
         <v>41</v>
       </c>
-      <c r="D38" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" t="s">
-        <v>106</v>
-      </c>
-      <c r="F38" t="s">
-        <v>131</v>
-      </c>
-      <c r="G38" t="s">
-        <v>142</v>
-      </c>
-      <c r="H38" t="s">
-        <v>157</v>
-      </c>
-      <c r="I38" t="s">
-        <v>165</v>
-      </c>
-      <c r="J38">
+      <c r="D41" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" t="s">
+        <v>133</v>
+      </c>
+      <c r="F41" t="s">
+        <v>147</v>
+      </c>
+      <c r="G41" t="s">
+        <v>150</v>
+      </c>
+      <c r="H41" t="s">
+        <v>175</v>
+      </c>
+      <c r="I41" t="s">
+        <v>182</v>
+      </c>
+      <c r="J41">
+        <v>4</v>
+      </c>
+      <c r="K41">
         <v>3</v>
       </c>
-      <c r="K38">
-        <v>1</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>3</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38" t="s">
-        <v>198</v>
-      </c>
-      <c r="P38">
-        <v>9</v>
-      </c>
-      <c r="Q38">
-        <v>12</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <v>90</v>
-      </c>
-      <c r="U38">
-        <v>9499</v>
-      </c>
-      <c r="V38" t="s">
-        <v>222</v>
-      </c>
-      <c r="W38">
-        <v>3</v>
-      </c>
-      <c r="X38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24">
-      <c r="A39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" t="s">
-        <v>42</v>
-      </c>
-      <c r="D39" t="s">
-        <v>76</v>
-      </c>
-      <c r="E39" t="s">
-        <v>117</v>
-      </c>
-      <c r="F39" t="s">
-        <v>131</v>
-      </c>
-      <c r="G39" t="s">
-        <v>140</v>
-      </c>
-      <c r="H39" t="s">
-        <v>157</v>
-      </c>
-      <c r="I39" t="s">
-        <v>159</v>
-      </c>
-      <c r="J39">
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>201</v>
+      </c>
+      <c r="P41">
+        <v>4</v>
+      </c>
+      <c r="Q41">
+        <v>8</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>90</v>
+      </c>
+      <c r="U41">
+        <v>3947</v>
+      </c>
+      <c r="V41" t="s">
+        <v>261</v>
+      </c>
+      <c r="W41">
+        <v>2</v>
+      </c>
+      <c r="X41">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" t="s">
+        <v>134</v>
+      </c>
+      <c r="F42" t="s">
+        <v>147</v>
+      </c>
+      <c r="G42" t="s">
+        <v>150</v>
+      </c>
+      <c r="H42" t="s">
+        <v>175</v>
+      </c>
+      <c r="I42" t="s">
+        <v>176</v>
+      </c>
+      <c r="J42">
         <v>6</v>
       </c>
-      <c r="K39">
-        <v>51</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39" t="s">
-        <v>199</v>
-      </c>
-      <c r="P39">
-        <v>54</v>
-      </c>
-      <c r="Q39">
-        <v>60</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
-        <v>0</v>
-      </c>
-      <c r="T39">
-        <v>90</v>
-      </c>
-      <c r="U39">
-        <v>15441</v>
-      </c>
-      <c r="V39" t="s">
-        <v>224</v>
-      </c>
-      <c r="W39">
+      <c r="K42">
+        <v>7</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>219</v>
+      </c>
+      <c r="P42">
+        <v>8</v>
+      </c>
+      <c r="Q42">
+        <v>14</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>90</v>
+      </c>
+      <c r="U42">
+        <v>3947</v>
+      </c>
+      <c r="V42" t="s">
+        <v>261</v>
+      </c>
+      <c r="W42">
         <v>2</v>
       </c>
-      <c r="X39">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24">
-      <c r="A40" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" t="s">
-        <v>89</v>
-      </c>
-      <c r="F40" t="s">
-        <v>130</v>
-      </c>
-      <c r="G40" t="s">
-        <v>133</v>
-      </c>
-      <c r="H40" t="s">
-        <v>157</v>
-      </c>
-      <c r="I40" t="s">
-        <v>158</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40" t="s">
-        <v>170</v>
-      </c>
-      <c r="P40">
+      <c r="X42">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" t="s">
+        <v>135</v>
+      </c>
+      <c r="F43" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" t="s">
+        <v>150</v>
+      </c>
+      <c r="H43" t="s">
+        <v>175</v>
+      </c>
+      <c r="I43" t="s">
+        <v>182</v>
+      </c>
+      <c r="J43">
+        <v>4</v>
+      </c>
+      <c r="K43">
+        <v>6</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>220</v>
+      </c>
+      <c r="P43">
         <v>10</v>
       </c>
-      <c r="Q40">
-        <v>15</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>90</v>
-      </c>
-      <c r="U40">
-        <v>15</v>
-      </c>
-      <c r="V40" t="s">
-        <v>212</v>
-      </c>
-      <c r="W40">
-        <v>15</v>
-      </c>
-      <c r="X40">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24">
-      <c r="A41" t="s">
-        <v>24</v>
-      </c>
-      <c r="B41" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" t="s">
-        <v>100</v>
-      </c>
-      <c r="F41" t="s">
-        <v>130</v>
-      </c>
-      <c r="G41" t="s">
-        <v>133</v>
-      </c>
-      <c r="H41" t="s">
-        <v>157</v>
-      </c>
-      <c r="I41" t="s">
-        <v>158</v>
-      </c>
-      <c r="J41">
-        <v>1</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41" t="s">
-        <v>170</v>
-      </c>
-      <c r="P41">
-        <v>10</v>
-      </c>
-      <c r="Q41">
-        <v>15</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
-      <c r="T41">
-        <v>90</v>
-      </c>
-      <c r="U41">
-        <v>15</v>
-      </c>
-      <c r="V41" t="s">
-        <v>212</v>
-      </c>
-      <c r="W41">
-        <v>15</v>
-      </c>
-      <c r="X41">
+      <c r="Q43">
+        <v>14</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>90</v>
+      </c>
+      <c r="U43">
+        <v>3947</v>
+      </c>
+      <c r="V43" t="s">
+        <v>261</v>
+      </c>
+      <c r="W43">
+        <v>2</v>
+      </c>
+      <c r="X43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="42" spans="1:24">
-      <c r="A42" t="s">
-        <v>26</v>
-      </c>
-      <c r="B42" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" t="s">
-        <v>77</v>
-      </c>
-      <c r="E42" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" t="s">
-        <v>131</v>
-      </c>
-      <c r="G42" t="s">
-        <v>151</v>
-      </c>
-      <c r="H42" t="s">
-        <v>157</v>
-      </c>
-      <c r="I42" t="s">
-        <v>162</v>
-      </c>
-      <c r="J42">
-        <v>12</v>
-      </c>
-      <c r="K42">
-        <v>-107</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>12</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42" t="s">
-        <v>200</v>
-      </c>
-      <c r="P42">
-        <v>144</v>
-      </c>
-      <c r="Q42">
-        <v>180</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>90</v>
-      </c>
-      <c r="U42">
-        <v>10181</v>
-      </c>
-      <c r="V42" t="s">
-        <v>231</v>
-      </c>
-      <c r="W42">
-        <v>14</v>
-      </c>
-      <c r="X42">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24">
-      <c r="A43" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" t="s">
-        <v>78</v>
-      </c>
-      <c r="E43" t="s">
-        <v>119</v>
-      </c>
-      <c r="F43" t="s">
-        <v>131</v>
-      </c>
-      <c r="G43" t="s">
-        <v>152</v>
-      </c>
-      <c r="H43" t="s">
-        <v>157</v>
-      </c>
-      <c r="I43" t="s">
-        <v>67</v>
-      </c>
-      <c r="J43">
-        <v>10</v>
-      </c>
-      <c r="K43">
-        <v>16</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>20</v>
-      </c>
-      <c r="O43" t="s">
-        <v>201</v>
-      </c>
-      <c r="P43">
-        <v>38</v>
-      </c>
-      <c r="Q43">
-        <v>58</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>90</v>
-      </c>
-      <c r="U43">
-        <v>2977</v>
-      </c>
-      <c r="V43" t="s">
-        <v>228</v>
-      </c>
-      <c r="W43">
-        <v>3</v>
-      </c>
-      <c r="X43">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:24">
-      <c r="A44" t="s">
-        <v>24</v>
-      </c>
-      <c r="B44" t="s">
-        <v>32</v>
-      </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E44" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="F44" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G44" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H44" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I44" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="J44">
         <v>6</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4276,146 +4390,146 @@
         <v>0</v>
       </c>
       <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>221</v>
+      </c>
+      <c r="P44">
         <v>12</v>
       </c>
-      <c r="O44" t="s">
-        <v>202</v>
-      </c>
-      <c r="P44">
+      <c r="Q44">
+        <v>18</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>90</v>
+      </c>
+      <c r="U44">
+        <v>3947</v>
+      </c>
+      <c r="V44" t="s">
+        <v>261</v>
+      </c>
+      <c r="W44">
+        <v>3</v>
+      </c>
+      <c r="X44">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" t="s">
+        <v>137</v>
+      </c>
+      <c r="F45" t="s">
+        <v>147</v>
+      </c>
+      <c r="G45" t="s">
+        <v>148</v>
+      </c>
+      <c r="H45" t="s">
+        <v>175</v>
+      </c>
+      <c r="I45" t="s">
+        <v>182</v>
+      </c>
+      <c r="J45">
+        <v>4</v>
+      </c>
+      <c r="K45">
+        <v>3</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>56</v>
+      </c>
+      <c r="P45">
+        <v>4</v>
+      </c>
+      <c r="Q45">
+        <v>8</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>90</v>
+      </c>
+      <c r="U45">
+        <v>3947</v>
+      </c>
+      <c r="V45" t="s">
+        <v>261</v>
+      </c>
+      <c r="W45">
+        <v>2</v>
+      </c>
+      <c r="X45">
         <v>14</v>
       </c>
-      <c r="Q44">
-        <v>20</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>0</v>
-      </c>
-      <c r="T44">
-        <v>90</v>
-      </c>
-      <c r="U44">
-        <v>15134</v>
-      </c>
-      <c r="V44" t="s">
-        <v>216</v>
-      </c>
-      <c r="W44">
-        <v>2</v>
-      </c>
-      <c r="X44">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24">
-      <c r="A45" t="s">
-        <v>24</v>
-      </c>
-      <c r="B45" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" t="s">
-        <v>80</v>
-      </c>
-      <c r="E45" t="s">
-        <v>121</v>
-      </c>
-      <c r="F45" t="s">
-        <v>131</v>
-      </c>
-      <c r="G45" t="s">
-        <v>137</v>
-      </c>
-      <c r="H45" t="s">
-        <v>157</v>
-      </c>
-      <c r="I45" t="s">
-        <v>159</v>
-      </c>
-      <c r="J45">
-        <v>6</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>12</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45" t="s">
-        <v>192</v>
-      </c>
-      <c r="P45">
-        <v>18</v>
-      </c>
-      <c r="Q45">
-        <v>30</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>0</v>
-      </c>
-      <c r="T45">
-        <v>90</v>
-      </c>
-      <c r="U45">
-        <v>15134</v>
-      </c>
-      <c r="V45" t="s">
-        <v>216</v>
-      </c>
-      <c r="W45">
-        <v>3</v>
-      </c>
-      <c r="X45">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24">
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D46" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E46" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="F46" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G46" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="H46" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I46" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="J46">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="K46">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4427,13 +4541,13 @@
         <v>0</v>
       </c>
       <c r="O46" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="P46">
         <v>24</v>
       </c>
       <c r="Q46">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -4445,48 +4559,48 @@
         <v>90</v>
       </c>
       <c r="U46">
-        <v>10189</v>
+        <v>7995</v>
       </c>
       <c r="V46" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="W46">
         <v>2</v>
       </c>
       <c r="X46">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E47" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="F47" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G47" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="H47" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I47" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="J47">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K47">
         <v>13</v>
@@ -4495,19 +4609,19 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N47">
         <v>0</v>
       </c>
       <c r="O47" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="P47">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="Q47">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -4519,52 +4633,52 @@
         <v>90</v>
       </c>
       <c r="U47">
-        <v>15520</v>
+        <v>2977</v>
       </c>
       <c r="V47" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="W47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X47">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:24">
+        <v>69.900000000000006</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D48" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E48" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="F48" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G48" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="H48" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I48" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="J48">
+        <v>6</v>
+      </c>
+      <c r="K48">
         <v>12</v>
       </c>
-      <c r="K48">
-        <v>24</v>
-      </c>
       <c r="L48">
         <v>0</v>
       </c>
@@ -4572,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="N48">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O48" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="P48">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="Q48">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -4593,48 +4707,48 @@
         <v>90</v>
       </c>
       <c r="U48">
-        <v>10189</v>
+        <v>15134</v>
       </c>
       <c r="V48" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="W48">
         <v>2</v>
       </c>
       <c r="X48">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="E49" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="F49" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="G49" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="H49" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I49" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -4646,16 +4760,16 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O49" t="s">
-        <v>170</v>
+        <v>225</v>
       </c>
       <c r="P49">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q49">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -4667,51 +4781,51 @@
         <v>90</v>
       </c>
       <c r="U49">
-        <v>15</v>
+        <v>15134</v>
       </c>
       <c r="V49" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="W49">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="X49">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D50" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E50" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="F50" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G50" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H50" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I50" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="J50">
         <v>24</v>
       </c>
       <c r="K50">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -4723,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="O50" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="P50">
         <v>26</v>
@@ -4744,7 +4858,7 @@
         <v>7995</v>
       </c>
       <c r="V50" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="W50">
         <v>3</v>
@@ -4753,113 +4867,113 @@
         <v>67</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C51" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D51" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E51" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="F51" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G51" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="H51" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I51" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="J51">
+        <v>4</v>
+      </c>
+      <c r="K51">
+        <v>4</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51" t="s">
+        <v>227</v>
+      </c>
+      <c r="P51">
+        <v>30</v>
+      </c>
+      <c r="Q51">
+        <v>50</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>90</v>
+      </c>
+      <c r="U51">
+        <v>6424</v>
+      </c>
+      <c r="V51" t="s">
+        <v>243</v>
+      </c>
+      <c r="W51">
         <v>12</v>
       </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51" t="s">
-        <v>207</v>
-      </c>
-      <c r="P51">
+      <c r="X51">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" t="s">
+        <v>93</v>
+      </c>
+      <c r="E52" t="s">
         <v>144</v>
       </c>
-      <c r="Q51">
-        <v>180</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
-        <v>90</v>
-      </c>
-      <c r="U51">
-        <v>10181</v>
-      </c>
-      <c r="V51" t="s">
-        <v>231</v>
-      </c>
-      <c r="W51">
-        <v>15</v>
-      </c>
-      <c r="X51">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:24">
-      <c r="A52" t="s">
-        <v>26</v>
-      </c>
-      <c r="B52" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" t="s">
-        <v>45</v>
-      </c>
-      <c r="D52" t="s">
-        <v>85</v>
-      </c>
-      <c r="E52" t="s">
-        <v>126</v>
-      </c>
       <c r="F52" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G52" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="H52" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I52" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="J52">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K52">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -4871,13 +4985,13 @@
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="P52">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Q52">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -4889,51 +5003,51 @@
         <v>90</v>
       </c>
       <c r="U52">
-        <v>6424</v>
+        <v>8583</v>
       </c>
       <c r="V52" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="W52">
+        <v>2</v>
+      </c>
+      <c r="X52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" t="s">
+        <v>94</v>
+      </c>
+      <c r="E53" t="s">
+        <v>145</v>
+      </c>
+      <c r="F53" t="s">
+        <v>147</v>
+      </c>
+      <c r="G53" t="s">
+        <v>174</v>
+      </c>
+      <c r="H53" t="s">
+        <v>175</v>
+      </c>
+      <c r="I53" t="s">
+        <v>179</v>
+      </c>
+      <c r="J53">
         <v>12</v>
       </c>
-      <c r="X52">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="53" spans="1:24">
-      <c r="A53" t="s">
-        <v>27</v>
-      </c>
-      <c r="B53" t="s">
-        <v>30</v>
-      </c>
-      <c r="C53" t="s">
-        <v>45</v>
-      </c>
-      <c r="D53" t="s">
-        <v>86</v>
-      </c>
-      <c r="E53" t="s">
-        <v>127</v>
-      </c>
-      <c r="F53" t="s">
-        <v>131</v>
-      </c>
-      <c r="G53" t="s">
-        <v>142</v>
-      </c>
-      <c r="H53" t="s">
-        <v>157</v>
-      </c>
-      <c r="I53" t="s">
-        <v>169</v>
-      </c>
-      <c r="J53">
-        <v>15</v>
-      </c>
       <c r="K53">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -4945,13 +5059,13 @@
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="P53">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q53">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -4963,51 +5077,51 @@
         <v>90</v>
       </c>
       <c r="U53">
-        <v>15134</v>
+        <v>7493</v>
       </c>
       <c r="V53" t="s">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="W53">
         <v>2</v>
       </c>
       <c r="X53">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B54" t="s">
         <v>30</v>
       </c>
       <c r="C54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E54" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F54" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G54" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H54" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I54" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="J54">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K54">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5019,13 +5133,13 @@
         <v>0</v>
       </c>
       <c r="O54" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="P54">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="Q54">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -5037,315 +5151,24 @@
         <v>90</v>
       </c>
       <c r="U54">
-        <v>15134</v>
+        <v>5894</v>
       </c>
       <c r="V54" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="W54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X54">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="55" spans="1:24">
-      <c r="A55" t="s">
-        <v>24</v>
-      </c>
-      <c r="B55" t="s">
-        <v>29</v>
-      </c>
-      <c r="C55" t="s">
-        <v>45</v>
-      </c>
-      <c r="D55" t="s">
-        <v>48</v>
-      </c>
-      <c r="E55" t="s">
-        <v>89</v>
-      </c>
-      <c r="F55" t="s">
-        <v>130</v>
-      </c>
-      <c r="G55" t="s">
-        <v>133</v>
-      </c>
-      <c r="H55" t="s">
-        <v>157</v>
-      </c>
-      <c r="I55" t="s">
-        <v>158</v>
-      </c>
-      <c r="J55">
-        <v>1</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55" t="s">
-        <v>170</v>
-      </c>
-      <c r="P55">
-        <v>10</v>
-      </c>
-      <c r="Q55">
-        <v>15</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-      <c r="T55">
-        <v>90</v>
-      </c>
-      <c r="U55">
-        <v>15</v>
-      </c>
-      <c r="V55" t="s">
-        <v>212</v>
-      </c>
-      <c r="W55">
-        <v>15</v>
-      </c>
-      <c r="X55">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:24">
-      <c r="A56" t="s">
-        <v>24</v>
-      </c>
-      <c r="B56" t="s">
-        <v>32</v>
-      </c>
-      <c r="C56" t="s">
-        <v>46</v>
-      </c>
-      <c r="D56" t="s">
-        <v>88</v>
-      </c>
-      <c r="E56" t="s">
-        <v>129</v>
-      </c>
-      <c r="F56" t="s">
-        <v>131</v>
-      </c>
-      <c r="G56" t="s">
-        <v>156</v>
-      </c>
-      <c r="H56" t="s">
-        <v>157</v>
-      </c>
-      <c r="I56" t="s">
-        <v>162</v>
-      </c>
-      <c r="J56">
-        <v>12</v>
-      </c>
-      <c r="K56">
-        <v>1</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56" t="s">
-        <v>211</v>
-      </c>
-      <c r="P56">
         <v>8</v>
       </c>
-      <c r="Q56">
-        <v>20</v>
-      </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
-        <v>0</v>
-      </c>
-      <c r="T56">
-        <v>90</v>
-      </c>
-      <c r="U56">
-        <v>7493</v>
-      </c>
-      <c r="V56" t="s">
-        <v>234</v>
-      </c>
-      <c r="W56">
-        <v>2</v>
-      </c>
-      <c r="X56">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:24">
-      <c r="A57" t="s">
-        <v>24</v>
-      </c>
-      <c r="B57" t="s">
-        <v>29</v>
-      </c>
-      <c r="C57" t="s">
-        <v>46</v>
-      </c>
-      <c r="D57" t="s">
-        <v>48</v>
-      </c>
-      <c r="E57" t="s">
-        <v>89</v>
-      </c>
-      <c r="F57" t="s">
-        <v>130</v>
-      </c>
-      <c r="G57" t="s">
-        <v>133</v>
-      </c>
-      <c r="H57" t="s">
-        <v>157</v>
-      </c>
-      <c r="I57" t="s">
-        <v>158</v>
-      </c>
-      <c r="J57">
-        <v>1</v>
-      </c>
-      <c r="K57">
-        <v>0</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57" t="s">
-        <v>170</v>
-      </c>
-      <c r="P57">
-        <v>10</v>
-      </c>
-      <c r="Q57">
-        <v>15</v>
-      </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-      <c r="T57">
-        <v>90</v>
-      </c>
-      <c r="U57">
-        <v>15</v>
-      </c>
-      <c r="V57" t="s">
-        <v>212</v>
-      </c>
-      <c r="W57">
-        <v>15</v>
-      </c>
-      <c r="X57">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:24">
-      <c r="A58" t="s">
-        <v>24</v>
-      </c>
-      <c r="B58" t="s">
-        <v>29</v>
-      </c>
-      <c r="C58" t="s">
-        <v>47</v>
-      </c>
-      <c r="D58" t="s">
-        <v>48</v>
-      </c>
-      <c r="E58" t="s">
-        <v>89</v>
-      </c>
-      <c r="F58" t="s">
-        <v>130</v>
-      </c>
-      <c r="G58" t="s">
-        <v>133</v>
-      </c>
-      <c r="H58" t="s">
-        <v>157</v>
-      </c>
-      <c r="I58" t="s">
-        <v>158</v>
-      </c>
-      <c r="J58">
-        <v>1</v>
-      </c>
-      <c r="K58">
-        <v>0</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <v>0</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58" t="s">
-        <v>170</v>
-      </c>
-      <c r="P58">
-        <v>10</v>
-      </c>
-      <c r="Q58">
-        <v>15</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
-        <v>0</v>
-      </c>
-      <c r="T58">
-        <v>90</v>
-      </c>
-      <c r="U58">
-        <v>15</v>
-      </c>
-      <c r="V58" t="s">
-        <v>212</v>
-      </c>
-      <c r="W58">
-        <v>15</v>
-      </c>
-      <c r="X58">
-        <v>58</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X54" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X54">
+      <sortCondition ref="C1:C54"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Downloads\Equipes_Agentes\Aplicativos\GAM\bd_saida\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDDC212-01B5-477E-BB3A-ECC0B168C605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749973BA-586E-4370-8302-916B19F1F07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$46</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="234">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -102,33 +102,30 @@
     <t>Estq_CD_cx</t>
   </si>
   <si>
+    <t>PERECIVEIS</t>
+  </si>
+  <si>
+    <t>MERCEARIA</t>
+  </si>
+  <si>
     <t>BEBIDAS</t>
   </si>
   <si>
-    <t>MERCEARIA</t>
-  </si>
-  <si>
-    <t>PRODUTOS PET</t>
-  </si>
-  <si>
     <t>PERFUMARIA E LIMPEZA</t>
   </si>
   <si>
-    <t>PERECIVEIS</t>
+    <t>SANDRO MARTINS VIANNA</t>
+  </si>
+  <si>
+    <t>NIDAL TUBASI</t>
   </si>
   <si>
     <t>NICOLAS AUGUSTO P. BORGES</t>
   </si>
   <si>
-    <t>NIDAL TUBASI</t>
-  </si>
-  <si>
     <t>JOAO BATISTA</t>
   </si>
   <si>
-    <t>SANDRO MARTINS VIANNA</t>
-  </si>
-  <si>
     <t>WETER SONNENFELDET</t>
   </si>
   <si>
@@ -144,7 +141,13 @@
     <t>004</t>
   </si>
   <si>
-    <t>006</t>
+    <t>005</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>008</t>
   </si>
   <si>
     <t>011</t>
@@ -153,452 +156,588 @@
     <t>012</t>
   </si>
   <si>
+    <t>013</t>
+  </si>
+  <si>
     <t>014</t>
   </si>
   <si>
     <t>017</t>
   </si>
   <si>
-    <t>018</t>
+    <t>6783</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>6781</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>838</t>
+  </si>
+  <si>
+    <t>5431</t>
+  </si>
+  <si>
+    <t>49</t>
   </si>
   <si>
     <t>795</t>
   </si>
   <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>10856</t>
+  </si>
+  <si>
+    <t>806</t>
+  </si>
+  <si>
+    <t>1297</t>
+  </si>
+  <si>
+    <t>835</t>
+  </si>
+  <si>
+    <t>910</t>
+  </si>
+  <si>
+    <t>2396</t>
+  </si>
+  <si>
+    <t>5673</t>
+  </si>
+  <si>
+    <t>5678</t>
+  </si>
+  <si>
+    <t>7878</t>
+  </si>
+  <si>
+    <t>10147</t>
+  </si>
+  <si>
+    <t>10148</t>
+  </si>
+  <si>
+    <t>17341</t>
+  </si>
+  <si>
+    <t>17349</t>
+  </si>
+  <si>
+    <t>22999</t>
+  </si>
+  <si>
+    <t>23111</t>
+  </si>
+  <si>
+    <t>33265</t>
+  </si>
+  <si>
+    <t>34977</t>
+  </si>
+  <si>
+    <t>1657</t>
+  </si>
+  <si>
+    <t>1713</t>
+  </si>
+  <si>
+    <t>2499</t>
+  </si>
+  <si>
+    <t>2831</t>
+  </si>
+  <si>
+    <t>2924</t>
+  </si>
+  <si>
+    <t>3475</t>
+  </si>
+  <si>
+    <t>3531</t>
+  </si>
+  <si>
+    <t>13277</t>
+  </si>
+  <si>
+    <t>39236</t>
+  </si>
+  <si>
+    <t>2179</t>
+  </si>
+  <si>
+    <t>2232</t>
+  </si>
+  <si>
+    <t>1575</t>
+  </si>
+  <si>
+    <t>39265</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL C TAMP INT 1L</t>
+  </si>
+  <si>
+    <t>AGUA MIN CRYSTAL PET 500ML S GAS</t>
+  </si>
+  <si>
+    <t>LEITE UHT ELEGE INT 1L</t>
+  </si>
+  <si>
+    <t>AGUA MIN CRYSTAL PET 500ML C GAS</t>
+  </si>
+  <si>
+    <t>REFRIG FRUKI PET 3L GUARANA</t>
+  </si>
+  <si>
+    <t>DESINF AQUAFAST HARMONIA 5L LAVANDA</t>
+  </si>
+  <si>
+    <t>AGUA MIN FLORESTA PET 500ML S GAS</t>
+  </si>
+  <si>
+    <t>REFRIG COCA COLA PET 2L ZERO</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML GREEN</t>
+  </si>
+  <si>
+    <t>CASTANHA PARA UNIAGRO S CASCA</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA LARANJA PET 2L</t>
+  </si>
+  <si>
+    <t>CHOC BARRA NESTLE 80G CRUNCH</t>
+  </si>
+  <si>
+    <t>REFRIG PET COCA COLA 3L</t>
+  </si>
+  <si>
+    <t>REFRIG SUKITA LT 350 ML</t>
+  </si>
+  <si>
+    <t>MILHO VERDE OLE LT 170G</t>
+  </si>
+  <si>
+    <t>DET LIQ GIRANDO SOL 500ML LIMAO</t>
+  </si>
+  <si>
+    <t>DET LIQ GOTA LIMPA 500ML CRISTAL</t>
+  </si>
+  <si>
+    <t>SABONETE DOVE 90G KARITE BAUNILHA</t>
+  </si>
+  <si>
+    <t>SAB FARNESE 180G LAVANDA MENTA</t>
+  </si>
+  <si>
+    <t>SAB FARNESE 180G PITAYA FRAMB</t>
+  </si>
+  <si>
+    <t>DET LIQ BIO KRISS 500ML NEUTRO</t>
+  </si>
+  <si>
+    <t>DET LIQ GOTA LIMPA 1L NATURAL</t>
+  </si>
+  <si>
+    <t>SAB FONTANA SENSUS 150G AMANHECER PERS</t>
+  </si>
+  <si>
+    <t>SAB PALMOLIVE 85G ARGILA EUCALIP</t>
+  </si>
+  <si>
+    <t>REFRIG FRUKI GUAR ZR PET 3L GUARANA ZERO</t>
+  </si>
+  <si>
+    <t>SAB MARAN SUAVE 80G PESSEGO</t>
+  </si>
+  <si>
+    <t>WAFFER ISABELA 100G DOCE DE LEITE</t>
+  </si>
+  <si>
+    <t>PIPOCA DOCE KEVYTOS 50G</t>
+  </si>
+  <si>
+    <t>KETCHUP ODERICH BISN 400G PICANTE</t>
+  </si>
+  <si>
+    <t>MASSA C OVOS GERMANI 500G ESPAGUETE</t>
+  </si>
+  <si>
+    <t>MASSA C OVOS PARATI 500G RIGATONI</t>
+  </si>
+  <si>
+    <t>TEMP COLORIFICO APTI 100G</t>
+  </si>
+  <si>
+    <t>FERM QUIMICO PO ROYAL PT 100G</t>
+  </si>
+  <si>
+    <t>BISC AGUA SAL ORQUIDEA 665GR</t>
+  </si>
+  <si>
+    <t>CERV AMSTEL ULTRA LN 330ML</t>
+  </si>
+  <si>
+    <t>CHA PRENDA GOLD 15G CIDREIRA</t>
+  </si>
+  <si>
+    <t>CAPSULA DOLCE GUSTO 117G C 10 CAPPUCCINO</t>
+  </si>
+  <si>
+    <t>BISC SALG GERMANI GRISSINI 175G</t>
+  </si>
+  <si>
+    <t>REFRE FRUKITO PET 5L FRUTAS CITRICAS</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>18/09/2024</t>
+  </si>
+  <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>18/10/2024</t>
+  </si>
+  <si>
+    <t>05/10/2024</t>
+  </si>
+  <si>
+    <t>11/06/2025</t>
+  </si>
+  <si>
+    <t>19/10/2024</t>
+  </si>
+  <si>
+    <t>07/11/2024</t>
+  </si>
+  <si>
+    <t>23/10/2024</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>08/07/2025</t>
+  </si>
+  <si>
+    <t>08/12/2025</t>
+  </si>
+  <si>
+    <t>19/11/2024</t>
+  </si>
+  <si>
+    <t>22/11/2024</t>
+  </si>
+  <si>
+    <t>10/12/2024</t>
+  </si>
+  <si>
+    <t>16/12/2024</t>
+  </si>
+  <si>
+    <t>17/12/2024</t>
+  </si>
+  <si>
+    <t>27/12/2024</t>
+  </si>
+  <si>
+    <t>28/12/2024</t>
+  </si>
+  <si>
+    <t>24/08/2026</t>
+  </si>
+  <si>
+    <t>05/12/2024</t>
+  </si>
+  <si>
+    <t>14/11/2024</t>
+  </si>
+  <si>
+    <t>26/08/2026</t>
+  </si>
+  <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>50</t>
   </si>
   <si>
-    <t>835</t>
-  </si>
-  <si>
-    <t>840</t>
-  </si>
-  <si>
-    <t>293</t>
-  </si>
-  <si>
-    <t>3991</t>
-  </si>
-  <si>
-    <t>8840</t>
-  </si>
-  <si>
-    <t>12393</t>
-  </si>
-  <si>
-    <t>17160</t>
-  </si>
-  <si>
-    <t>37423</t>
-  </si>
-  <si>
-    <t>747</t>
-  </si>
-  <si>
-    <t>8288</t>
-  </si>
-  <si>
-    <t>4048</t>
-  </si>
-  <si>
-    <t>10173</t>
-  </si>
-  <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>5857</t>
-  </si>
-  <si>
-    <t>6781</t>
-  </si>
-  <si>
-    <t>8702</t>
-  </si>
-  <si>
-    <t>36996</t>
-  </si>
-  <si>
-    <t>20621</t>
-  </si>
-  <si>
-    <t>4052</t>
-  </si>
-  <si>
-    <t>33255</t>
-  </si>
-  <si>
-    <t>39321</t>
-  </si>
-  <si>
-    <t>749</t>
-  </si>
-  <si>
-    <t>3042</t>
-  </si>
-  <si>
-    <t>3617</t>
-  </si>
-  <si>
-    <t>19844</t>
-  </si>
-  <si>
-    <t>22794</t>
-  </si>
-  <si>
-    <t>37047</t>
-  </si>
-  <si>
-    <t>39075</t>
-  </si>
-  <si>
-    <t>39234</t>
-  </si>
-  <si>
-    <t>REFRIG COCA COLA PET 2L ZERO</t>
-  </si>
-  <si>
-    <t>AGUA MIN DA PEDRA PET 5L S GAS</t>
-  </si>
-  <si>
-    <t>REFRIG PET COCA COLA 3L</t>
-  </si>
-  <si>
-    <t>REFRIG PEPSI PET 3L</t>
-  </si>
-  <si>
-    <t>CERV STELLA ARTOIS LN 330ML</t>
-  </si>
-  <si>
-    <t>RACAO DOG CHOW SH 85G MULTI PROTEINAS</t>
-  </si>
-  <si>
-    <t>AMAC AQUAFAST EMB ECON 5L VERM SEDUCAO</t>
-  </si>
-  <si>
-    <t>AMACIANTE AQUAFAST 2L MANHA AZ</t>
-  </si>
-  <si>
-    <t>DESINF AQUAFAST 2L CHA BRANCO</t>
-  </si>
-  <si>
-    <t>DESINF AQUAFAST 2L HARMONIA NAT</t>
-  </si>
-  <si>
-    <t>ACUCAR CRISTAL GASPARIN 2KG</t>
-  </si>
-  <si>
-    <t>SH PANTENE 175ML EQUIL ALGA MAR</t>
-  </si>
-  <si>
-    <t>RACAO FRISKIES SH 85G FGO MOLHO</t>
-  </si>
-  <si>
-    <t>SABON PALMOLIVE NATURALS 85G CAMELIA AMEND</t>
-  </si>
-  <si>
-    <t>RACAO DOG CHOW SH 85G AD CAR FGO SALM</t>
-  </si>
-  <si>
-    <t>ESC DENTAL SORRISO MACIA</t>
-  </si>
-  <si>
-    <t>LEITE UHT ELEGE INT 1L</t>
-  </si>
-  <si>
-    <t>VASSOURA BETTANIN NOVICA RF167</t>
-  </si>
-  <si>
-    <t>FARINHA TAPIOCA ROCHA 500G TRAD</t>
-  </si>
-  <si>
-    <t>MAS FURADINHO ISABELA SEMOLA 400G</t>
-  </si>
-  <si>
-    <t>RACAO FRISKIES SH 85G PERU MOLHO</t>
-  </si>
-  <si>
-    <t>REFRIG CHARRUA PET 3L GUARANA</t>
-  </si>
-  <si>
-    <t>RACAO DOG CHOW SH 85G ALTA PROTEINA</t>
-  </si>
-  <si>
-    <t>REFRIG SARANDI PET 1 5L GUARANA ZERO</t>
-  </si>
-  <si>
-    <t>CEREAL MAT NESTLE CX210G NESCAU DUO</t>
-  </si>
-  <si>
-    <t>GELATINA NEILAR 20G AMORA</t>
-  </si>
-  <si>
-    <t>L MOVEIS POLWAX 200ML JASMIN</t>
-  </si>
-  <si>
-    <t>RATICIDA RATICID GRANULADO 25G</t>
-  </si>
-  <si>
-    <t>FAROFA ROCHA CASEIRA 300GBACON</t>
-  </si>
-  <si>
-    <t>MOLHO TOM SACCIALI 520G PASSATA</t>
-  </si>
-  <si>
-    <t>PALMITO PETRY PUPUNHA PICADO 300G</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>18/10/2024</t>
-  </si>
-  <si>
-    <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>21/10/2024</t>
-  </si>
-  <si>
-    <t>01/10/2024</t>
-  </si>
-  <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>17/10/2024</t>
-  </si>
-  <si>
-    <t>20/02/2026</t>
-  </si>
-  <si>
-    <t>07/07/2025</t>
-  </si>
-  <si>
-    <t>27/08/2026</t>
-  </si>
-  <si>
-    <t>19/12/2024</t>
-  </si>
-  <si>
-    <t>30/12/2024</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>31/07/2026</t>
-  </si>
-  <si>
-    <t>24/08/2026</t>
-  </si>
-  <si>
-    <t>Ativo</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>480</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>292</t>
+    <t>4038</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>250</t>
+    <t>1511</t>
+  </si>
+  <si>
+    <t>1845</t>
+  </si>
+  <si>
+    <t>5962</t>
+  </si>
+  <si>
+    <t>1629</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>13983</t>
+  </si>
+  <si>
+    <t>1391</t>
+  </si>
+  <si>
+    <t>588</t>
+  </si>
+  <si>
+    <t>,58</t>
+  </si>
+  <si>
+    <t>1081</t>
   </si>
   <si>
     <t>1413</t>
   </si>
   <si>
-    <t>1358</t>
-  </si>
-  <si>
-    <t>562</t>
-  </si>
-  <si>
-    <t>2221</t>
-  </si>
-  <si>
-    <t>63</t>
+    <t>170</t>
+  </si>
+  <si>
+    <t>654</t>
+  </si>
+  <si>
+    <t>1,57</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>1739</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>35487</t>
+  </si>
+  <si>
+    <t>3068</t>
+  </si>
+  <si>
+    <t>628</t>
+  </si>
+  <si>
+    <t>579</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>827</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1150</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>218</t>
   </si>
   <si>
     <t>37</t>
   </si>
   <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>1844</t>
-  </si>
-  <si>
-    <t>1569</t>
-  </si>
-  <si>
-    <t>263</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>2899</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>299</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>1502</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>52</t>
+    <t>LATICINIOS TIROL LTDA.</t>
   </si>
   <si>
     <t>SPAL IND BRAS BEBIDAS AS</t>
   </si>
   <si>
+    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
+  </si>
+  <si>
     <t>BEBIDAS FRUKI LTDA</t>
   </si>
   <si>
+    <t>AQUAFAST PROD LIMPEZA/HIGIENE LTDA</t>
+  </si>
+  <si>
+    <t>AGUAS MINERAIS SARANDI LTDA</t>
+  </si>
+  <si>
+    <t>UNIAGRO -IND.E COM.DE PROD.ALIM.LTDA</t>
+  </si>
+  <si>
+    <t>NESTLE BRASIL LTDA</t>
+  </si>
+  <si>
     <t>CRBS AS CDD PELOTAS</t>
   </si>
   <si>
-    <t>NESTLE BRASIL LTDA</t>
-  </si>
-  <si>
-    <t>AQUAFAST PROD LIMPEZA/HIGIENE LTDA</t>
-  </si>
-  <si>
-    <t>GASPARIN CEREAIS LTDA ME</t>
+    <t>ANGELO AURICCHIO &amp; CIA LTDA</t>
+  </si>
+  <si>
+    <t>IND COM PROD LIMP GIRANDO SOL LTDA</t>
+  </si>
+  <si>
+    <t>BERTOLINI INDUSTRIA QUIMICA LTDA</t>
+  </si>
+  <si>
+    <t>ZAFFALON E CIA LTDA</t>
   </si>
   <si>
     <t>ONIZ DISTRIBUID LTDA SCJ</t>
   </si>
   <si>
+    <t>SENIR EMBALAGENS LTDA</t>
+  </si>
+  <si>
+    <t>FONTANA S.A</t>
+  </si>
+  <si>
     <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
   </si>
   <si>
-    <t>PODAL IND E COM DE ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
-  </si>
-  <si>
-    <t>ROCHA E FILHOS LTDA</t>
+    <t>ATACADAO S.A.</t>
   </si>
   <si>
     <t>M DIAS BRANCO S.A IND E COM DE ALIMENTOS</t>
   </si>
   <si>
-    <t>AGUAS MINERAIS SARANDI LTDA</t>
-  </si>
-  <si>
-    <t>NEILAR IND COM DE ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>POLWAX INDUSTRIA QUIMICA LTDA</t>
-  </si>
-  <si>
-    <t>AGROCOMERCIAL SANDRI LTDA</t>
-  </si>
-  <si>
-    <t>STELLA DORO ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>INDUSTRIA DE ALIMENTOS PETRY LTDA</t>
+    <t>DELAVY ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>CONSERVAS ODERICH SA</t>
+  </si>
+  <si>
+    <t>GERMANI ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>PARATI IND.COM.DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>APTI ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>TOPFLEX DISTRIBUIDOR DE ALIMENTOS</t>
+  </si>
+  <si>
+    <t>TONDO S/A</t>
+  </si>
+  <si>
+    <t>CARLOS CANCIAN E CIA LTDA</t>
+  </si>
+  <si>
+    <t>CHA PRENDA DO BRASIL IND E COM EIRELI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -626,9 +765,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -933,83 +1071,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="48" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1018,34 +1156,34 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="G2" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="H2" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I2" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K2">
-        <v>13</v>
+        <v>422</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1057,13 +1195,13 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="P2">
-        <v>28</v>
+        <v>480</v>
       </c>
       <c r="Q2">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -1075,51 +1213,51 @@
         <v>90</v>
       </c>
       <c r="U2">
-        <v>15441</v>
+        <v>15208</v>
       </c>
       <c r="V2" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="W2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="X2">
-        <v>157</v>
+        <v>5958</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G3" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="H3" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I3" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1131,13 +1269,13 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="P3">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="Q3">
-        <v>72</v>
+        <v>258</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1149,16 +1287,16 @@
         <v>90</v>
       </c>
       <c r="U3">
-        <v>6424</v>
+        <v>15441</v>
       </c>
       <c r="V3" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="W3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="X3">
-        <v>535</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -1166,34 +1304,34 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G4" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="H4" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I4" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1205,13 +1343,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="P4">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q4">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1223,51 +1361,51 @@
         <v>90</v>
       </c>
       <c r="U4">
-        <v>15441</v>
+        <v>9379</v>
       </c>
       <c r="V4" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="W4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>387</v>
+        <v>776</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G5" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H5" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I5" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K5">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1279,69 +1417,69 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="P5">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="Q5">
-        <v>240</v>
+        <v>112</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1308</v>
       </c>
       <c r="T5">
         <v>90</v>
       </c>
       <c r="U5">
-        <v>9638</v>
+        <v>15441</v>
       </c>
       <c r="V5" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="W5">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>44</v>
+        <v>218.58</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G6" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="H6" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I6" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="J6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1353,13 +1491,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="P6">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="Q6">
-        <v>124</v>
+        <v>240</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1371,51 +1509,51 @@
         <v>90</v>
       </c>
       <c r="U6">
-        <v>9638</v>
+        <v>6424</v>
       </c>
       <c r="V6" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="W6">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="X6">
-        <v>99</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F7" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G7" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="H7" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I7" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>228</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1427,13 +1565,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="P7">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1445,16 +1583,16 @@
         <v>90</v>
       </c>
       <c r="U7">
-        <v>15441</v>
+        <v>3947</v>
       </c>
       <c r="V7" t="s">
-        <v>167</v>
+        <v>210</v>
       </c>
       <c r="W7">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="X7">
-        <v>387</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -1462,37 +1600,37 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="G8" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="H8" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I8" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="J8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K8">
-        <v>102</v>
+        <v>-548</v>
       </c>
       <c r="L8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -1501,13 +1639,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="P8">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="Q8">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1519,51 +1657,51 @@
         <v>90</v>
       </c>
       <c r="U8">
-        <v>15134</v>
+        <v>10181</v>
       </c>
       <c r="V8" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>30.92</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="G9" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="H9" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I9" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1575,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="P9">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="Q9">
-        <v>8</v>
+        <v>238</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1593,51 +1731,51 @@
         <v>90</v>
       </c>
       <c r="U9">
-        <v>3947</v>
+        <v>15441</v>
       </c>
       <c r="V9" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="W9">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="G10" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="H10" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I10" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
       <c r="K10">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1649,13 +1787,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="P10">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="Q10">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1667,51 +1805,51 @@
         <v>90</v>
       </c>
       <c r="U10">
-        <v>3947</v>
+        <v>15441</v>
       </c>
       <c r="V10" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="W10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F11" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="H11" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I11" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1723,13 +1861,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="P11">
-        <v>6</v>
+        <v>0.85399999999999998</v>
       </c>
       <c r="Q11">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1741,69 +1879,69 @@
         <v>90</v>
       </c>
       <c r="U11">
-        <v>3947</v>
+        <v>14718</v>
       </c>
       <c r="V11" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="W11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F12" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="G12" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="H12" t="s">
+        <v>150</v>
+      </c>
+      <c r="I12" t="s">
+        <v>154</v>
+      </c>
+      <c r="J12">
+        <v>8</v>
+      </c>
+      <c r="K12">
+        <v>111</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>176</v>
+      </c>
+      <c r="P12">
         <v>124</v>
       </c>
-      <c r="I12" t="s">
-        <v>127</v>
-      </c>
-      <c r="J12">
-        <v>6</v>
-      </c>
-      <c r="K12">
-        <v>2</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>147</v>
-      </c>
-      <c r="P12">
-        <v>6</v>
-      </c>
       <c r="Q12">
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1815,51 +1953,51 @@
         <v>90</v>
       </c>
       <c r="U12">
-        <v>3947</v>
+        <v>15441</v>
       </c>
       <c r="V12" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="W12">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="X12">
-        <v>24</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="G13" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="H13" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I13" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="J13">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1871,13 +2009,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="P13">
-        <v>105</v>
+        <v>170</v>
       </c>
       <c r="Q13">
-        <v>165</v>
+        <v>266</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1889,52 +2027,52 @@
         <v>90</v>
       </c>
       <c r="U13">
-        <v>6158</v>
+        <v>15441</v>
       </c>
       <c r="V13" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="X13">
-        <v>459</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" t="s">
+        <v>134</v>
+      </c>
+      <c r="H14" t="s">
+        <v>150</v>
+      </c>
+      <c r="I14" t="s">
+        <v>157</v>
+      </c>
+      <c r="J14">
+        <v>16</v>
+      </c>
+      <c r="K14">
         <v>27</v>
       </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" t="s">
-        <v>86</v>
-      </c>
-      <c r="F14" t="s">
-        <v>107</v>
-      </c>
-      <c r="G14" t="s">
-        <v>113</v>
-      </c>
-      <c r="H14" t="s">
-        <v>124</v>
-      </c>
-      <c r="I14" t="s">
-        <v>127</v>
-      </c>
-      <c r="J14">
-        <v>6</v>
-      </c>
-      <c r="K14">
-        <v>5</v>
-      </c>
       <c r="L14">
         <v>0</v>
       </c>
@@ -1945,13 +2083,13 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="P14">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="Q14">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -1963,51 +2101,51 @@
         <v>90</v>
       </c>
       <c r="U14">
-        <v>6644</v>
+        <v>15134</v>
       </c>
       <c r="V14" t="s">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="W14">
         <v>2</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F15" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="G15" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="H15" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I15" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2019,13 +2157,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="P15">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Q15">
-        <v>286</v>
+        <v>128</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -2040,48 +2178,48 @@
         <v>15441</v>
       </c>
       <c r="V15" t="s">
-        <v>167</v>
+        <v>207</v>
       </c>
       <c r="W15">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>387</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F16" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G16" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H16" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I16" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="J16">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K16">
-        <v>67</v>
+        <v>0.81599999999999995</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2093,13 +2231,13 @@
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="P16">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -2111,51 +2249,51 @@
         <v>90</v>
       </c>
       <c r="U16">
-        <v>15134</v>
+        <v>14718</v>
       </c>
       <c r="V16" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="W16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
         <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F17" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G17" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="H17" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I17" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="J17">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2167,13 +2305,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="P17">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="Q17">
-        <v>174</v>
+        <v>60</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2185,16 +2323,16 @@
         <v>90</v>
       </c>
       <c r="U17">
-        <v>5894</v>
+        <v>15441</v>
       </c>
       <c r="V17" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="W17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
@@ -2202,37 +2340,37 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
         <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F18" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="G18" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="H18" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I18" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="J18">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K18">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -2241,13 +2379,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="P18">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="Q18">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -2259,51 +2397,51 @@
         <v>90</v>
       </c>
       <c r="U18">
-        <v>15134</v>
+        <v>9638</v>
       </c>
       <c r="V18" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="W18">
         <v>3</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
         <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F19" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="G19" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="H19" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I19" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="J19">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K19">
-        <v>9</v>
+        <v>191</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2315,13 +2453,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="P19">
-        <v>10</v>
+        <v>192</v>
       </c>
       <c r="Q19">
-        <v>22</v>
+        <v>288</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -2333,51 +2471,51 @@
         <v>90</v>
       </c>
       <c r="U19">
-        <v>15318</v>
+        <v>7715</v>
       </c>
       <c r="V19" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="W19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>19</v>
+        <v>493.04</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
         <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F20" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G20" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="H20" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I20" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="J20">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K20">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2389,13 +2527,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="P20">
-        <v>236</v>
+        <v>40</v>
       </c>
       <c r="Q20">
-        <v>368</v>
+        <v>64</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -2407,16 +2545,16 @@
         <v>90</v>
       </c>
       <c r="U20">
-        <v>9379</v>
+        <v>10334</v>
       </c>
       <c r="V20" t="s">
-        <v>176</v>
+        <v>216</v>
       </c>
       <c r="W20">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="X20">
-        <v>796</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -2427,49 +2565,49 @@
         <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
         <v>61</v>
       </c>
       <c r="E21" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F21" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G21" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="H21" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I21" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="J21">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="P21">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="Q21">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -2481,48 +2619,48 @@
         <v>90</v>
       </c>
       <c r="U21">
-        <v>5894</v>
+        <v>14468</v>
       </c>
       <c r="V21" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="W21">
         <v>2</v>
       </c>
       <c r="X21">
-        <v>38</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
         <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="H22" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I22" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="J22">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -2537,13 +2675,13 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="P22">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="Q22">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -2555,24 +2693,24 @@
         <v>90</v>
       </c>
       <c r="U22">
-        <v>21894</v>
+        <v>17017</v>
       </c>
       <c r="V22" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="W22">
         <v>2</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>41</v>
@@ -2581,25 +2719,25 @@
         <v>63</v>
       </c>
       <c r="E23" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F23" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G23" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H23" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I23" t="s">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="J23">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K23">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -2611,13 +2749,13 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="P23">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="Q23">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -2629,51 +2767,51 @@
         <v>90</v>
       </c>
       <c r="U23">
-        <v>7995</v>
+        <v>6644</v>
       </c>
       <c r="V23" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="W23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X23">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
         <v>64</v>
       </c>
       <c r="E24" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F24" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="H24" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I24" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="J24">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="K24">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -2685,13 +2823,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="P24">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="Q24">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2703,51 +2841,51 @@
         <v>90</v>
       </c>
       <c r="U24">
-        <v>15134</v>
+        <v>6644</v>
       </c>
       <c r="V24" t="s">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="W24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
       </c>
       <c r="E25" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F25" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G25" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="H25" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I25" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K25">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2759,13 +2897,13 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P25">
-        <v>172</v>
+        <v>64</v>
       </c>
       <c r="Q25">
-        <v>268</v>
+        <v>88</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2777,51 +2915,51 @@
         <v>90</v>
       </c>
       <c r="U25">
-        <v>15441</v>
+        <v>21220</v>
       </c>
       <c r="V25" t="s">
-        <v>167</v>
+        <v>220</v>
       </c>
       <c r="W25">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="X25">
-        <v>141</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
         <v>66</v>
       </c>
       <c r="E26" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F26" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G26" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I26" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="J26">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K26">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2833,13 +2971,13 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="P26">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q26">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -2851,51 +2989,51 @@
         <v>90</v>
       </c>
       <c r="U26">
-        <v>15134</v>
+        <v>14468</v>
       </c>
       <c r="V26" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="W26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
         <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F27" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G27" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="H27" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I27" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="J27">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="K27">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2907,13 +3045,13 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="P27">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="Q27">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -2925,51 +3063,51 @@
         <v>90</v>
       </c>
       <c r="U27">
-        <v>10181</v>
+        <v>21822</v>
       </c>
       <c r="V27" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="W27">
         <v>2</v>
       </c>
       <c r="X27">
-        <v>76</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
         <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F28" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G28" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H28" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I28" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="J28">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="K28">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2981,13 +3119,13 @@
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="P28">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="Q28">
-        <v>40</v>
+        <v>174</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -2999,51 +3137,51 @@
         <v>90</v>
       </c>
       <c r="U28">
-        <v>15134</v>
+        <v>5894</v>
       </c>
       <c r="V28" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="W28">
         <v>2</v>
       </c>
       <c r="X28">
-        <v>13</v>
+        <v>30.89</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
         <v>69</v>
       </c>
       <c r="E29" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G29" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="H29" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I29" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="J29">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3055,13 +3193,13 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="P29">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -3073,51 +3211,51 @@
         <v>90</v>
       </c>
       <c r="U29">
-        <v>12447</v>
+        <v>6424</v>
       </c>
       <c r="V29" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="W29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X29">
-        <v>69</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E30" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="F30" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="G30" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="H30" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I30" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="J30">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="K30">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3129,13 +3267,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>137</v>
+        <v>191</v>
       </c>
       <c r="P30">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="Q30">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -3147,51 +3285,51 @@
         <v>90</v>
       </c>
       <c r="U30">
-        <v>15134</v>
+        <v>11112</v>
       </c>
       <c r="V30" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="W30">
         <v>3</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E31" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="F31" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G31" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="H31" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I31" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="J31">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K31">
-        <v>12</v>
+        <v>-18</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3203,13 +3341,13 @@
         <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="P31">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="Q31">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -3221,51 +3359,51 @@
         <v>90</v>
       </c>
       <c r="U31">
-        <v>10489</v>
+        <v>10181</v>
       </c>
       <c r="V31" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="W31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X31">
-        <v>12</v>
+        <v>30.92</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E32" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F32" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="G32" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="H32" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I32" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="J32">
-        <v>480</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>254</v>
+        <v>356</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -3277,13 +3415,13 @@
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="P32">
-        <v>288</v>
+        <v>358</v>
       </c>
       <c r="Q32">
-        <v>768</v>
+        <v>558</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -3295,16 +3433,16 @@
         <v>90</v>
       </c>
       <c r="U32">
-        <v>14200</v>
+        <v>15441</v>
       </c>
       <c r="V32" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="W32">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="X32">
-        <v>23</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
@@ -3312,34 +3450,34 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F33" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="H33" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I33" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="J33">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K33">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3351,13 +3489,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="P33">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="Q33">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -3369,16 +3507,16 @@
         <v>90</v>
       </c>
       <c r="U33">
-        <v>21894</v>
+        <v>7995</v>
       </c>
       <c r="V33" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="W33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X33">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -3386,52 +3524,52 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" t="s">
+        <v>123</v>
+      </c>
+      <c r="G34" t="s">
+        <v>140</v>
+      </c>
+      <c r="H34" t="s">
+        <v>150</v>
+      </c>
+      <c r="I34" t="s">
+        <v>163</v>
+      </c>
+      <c r="J34">
+        <v>10</v>
+      </c>
+      <c r="K34">
+        <v>5</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
         <v>30</v>
       </c>
-      <c r="C34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" t="s">
-        <v>73</v>
-      </c>
-      <c r="E34" t="s">
-        <v>104</v>
-      </c>
-      <c r="F34" t="s">
-        <v>107</v>
-      </c>
-      <c r="G34" t="s">
-        <v>122</v>
-      </c>
-      <c r="H34" t="s">
-        <v>124</v>
-      </c>
-      <c r="I34" t="s">
-        <v>131</v>
-      </c>
-      <c r="J34">
-        <v>12</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
       <c r="O34" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="P34">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="Q34">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -3443,16 +3581,16 @@
         <v>90</v>
       </c>
       <c r="U34">
-        <v>11515</v>
+        <v>2977</v>
       </c>
       <c r="V34" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="W34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X34">
-        <v>53</v>
+        <v>64.900000000000006</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
@@ -3460,34 +3598,34 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F35" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G35" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="H35" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I35" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="J35">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3499,13 +3637,13 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="P35">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q35">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -3517,20 +3655,834 @@
         <v>90</v>
       </c>
       <c r="U35">
-        <v>16062</v>
+        <v>14671</v>
       </c>
       <c r="V35" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="W35">
         <v>2</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" t="s">
+        <v>123</v>
+      </c>
+      <c r="G36" t="s">
+        <v>142</v>
+      </c>
+      <c r="H36" t="s">
+        <v>150</v>
+      </c>
+      <c r="I36" t="s">
+        <v>156</v>
+      </c>
+      <c r="J36">
+        <v>20</v>
+      </c>
+      <c r="K36">
+        <v>48</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>197</v>
+      </c>
+      <c r="P36">
+        <v>54</v>
+      </c>
+      <c r="Q36">
+        <v>94</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>90</v>
+      </c>
+      <c r="U36">
+        <v>16963</v>
+      </c>
+      <c r="V36" t="s">
+        <v>227</v>
+      </c>
+      <c r="W36">
+        <v>3</v>
+      </c>
+      <c r="X36">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" t="s">
+        <v>114</v>
+      </c>
+      <c r="F37" t="s">
+        <v>123</v>
+      </c>
+      <c r="G37" t="s">
+        <v>143</v>
+      </c>
+      <c r="H37" t="s">
+        <v>150</v>
+      </c>
+      <c r="I37" t="s">
+        <v>156</v>
+      </c>
+      <c r="J37">
+        <v>20</v>
+      </c>
+      <c r="K37">
+        <v>15</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" t="s">
+        <v>198</v>
+      </c>
+      <c r="P37">
+        <v>20</v>
+      </c>
+      <c r="Q37">
+        <v>40</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>90</v>
+      </c>
+      <c r="U37">
+        <v>12257</v>
+      </c>
+      <c r="V37" t="s">
+        <v>228</v>
+      </c>
+      <c r="W37">
+        <v>2</v>
+      </c>
+      <c r="X37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38" t="s">
+        <v>115</v>
+      </c>
+      <c r="F38" t="s">
+        <v>123</v>
+      </c>
+      <c r="G38" t="s">
+        <v>144</v>
+      </c>
+      <c r="H38" t="s">
+        <v>150</v>
+      </c>
+      <c r="I38" t="s">
+        <v>164</v>
+      </c>
+      <c r="J38">
+        <v>50</v>
+      </c>
+      <c r="K38">
+        <v>13</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
+        <v>199</v>
+      </c>
+      <c r="P38">
+        <v>30</v>
+      </c>
+      <c r="Q38">
+        <v>80</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>90</v>
+      </c>
+      <c r="U38">
+        <v>10189</v>
+      </c>
+      <c r="V38" t="s">
+        <v>229</v>
+      </c>
+      <c r="W38">
+        <v>2</v>
+      </c>
+      <c r="X38">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" t="s">
+        <v>116</v>
+      </c>
+      <c r="F39" t="s">
+        <v>123</v>
+      </c>
+      <c r="G39" t="s">
+        <v>145</v>
+      </c>
+      <c r="H39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I39" t="s">
+        <v>160</v>
+      </c>
+      <c r="J39">
+        <v>72</v>
+      </c>
+      <c r="K39">
+        <v>59</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>200</v>
+      </c>
+      <c r="P39">
+        <v>62</v>
+      </c>
+      <c r="Q39">
+        <v>134</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>90</v>
+      </c>
+      <c r="U39">
+        <v>13838</v>
+      </c>
+      <c r="V39" t="s">
+        <v>230</v>
+      </c>
+      <c r="W39">
+        <v>2</v>
+      </c>
+      <c r="X39">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" t="s">
+        <v>123</v>
+      </c>
+      <c r="G40" t="s">
+        <v>126</v>
+      </c>
+      <c r="H40" t="s">
+        <v>150</v>
+      </c>
+      <c r="I40" t="s">
+        <v>151</v>
+      </c>
+      <c r="J40">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>6</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" t="s">
+        <v>201</v>
+      </c>
+      <c r="P40">
+        <v>12</v>
+      </c>
+      <c r="Q40">
+        <v>24</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>90</v>
+      </c>
+      <c r="U40">
+        <v>10683</v>
+      </c>
+      <c r="V40" t="s">
+        <v>231</v>
+      </c>
+      <c r="W40">
+        <v>2</v>
+      </c>
+      <c r="X40">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" t="s">
+        <v>123</v>
+      </c>
+      <c r="G41" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" t="s">
+        <v>150</v>
+      </c>
+      <c r="I41" t="s">
+        <v>158</v>
+      </c>
+      <c r="J41">
+        <v>24</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>166</v>
+      </c>
+      <c r="P41">
+        <v>16</v>
+      </c>
+      <c r="Q41">
+        <v>40</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>90</v>
+      </c>
+      <c r="U41">
+        <v>14469</v>
+      </c>
+      <c r="V41" t="s">
+        <v>232</v>
+      </c>
+      <c r="W41">
+        <v>2</v>
+      </c>
+      <c r="X41">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" t="s">
+        <v>119</v>
+      </c>
+      <c r="F42" t="s">
+        <v>123</v>
+      </c>
+      <c r="G42" t="s">
+        <v>147</v>
+      </c>
+      <c r="H42" t="s">
+        <v>150</v>
+      </c>
+      <c r="I42" t="s">
+        <v>163</v>
+      </c>
+      <c r="J42">
+        <v>10</v>
+      </c>
+      <c r="K42">
+        <v>19</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>153</v>
+      </c>
+      <c r="P42">
+        <v>20</v>
+      </c>
+      <c r="Q42">
+        <v>30</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>90</v>
+      </c>
+      <c r="U42">
+        <v>10153</v>
+      </c>
+      <c r="V42" t="s">
+        <v>233</v>
+      </c>
+      <c r="W42">
+        <v>2</v>
+      </c>
+      <c r="X42">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" t="s">
+        <v>123</v>
+      </c>
+      <c r="G43" t="s">
+        <v>147</v>
+      </c>
+      <c r="H43" t="s">
+        <v>150</v>
+      </c>
+      <c r="I43" t="s">
+        <v>155</v>
+      </c>
+      <c r="J43">
+        <v>6</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>202</v>
+      </c>
+      <c r="P43">
+        <v>18</v>
+      </c>
+      <c r="Q43">
+        <v>30</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>90</v>
+      </c>
+      <c r="U43">
+        <v>15134</v>
+      </c>
+      <c r="V43" t="s">
+        <v>213</v>
+      </c>
+      <c r="W43">
+        <v>5</v>
+      </c>
+      <c r="X43">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" t="s">
+        <v>123</v>
+      </c>
+      <c r="G44" t="s">
+        <v>148</v>
+      </c>
+      <c r="H44" t="s">
+        <v>150</v>
+      </c>
+      <c r="I44" t="s">
+        <v>157</v>
+      </c>
+      <c r="J44">
+        <v>16</v>
+      </c>
+      <c r="K44">
+        <v>9</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>203</v>
+      </c>
+      <c r="P44">
+        <v>10</v>
+      </c>
+      <c r="Q44">
+        <v>26</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>90</v>
+      </c>
+      <c r="U44">
+        <v>16963</v>
+      </c>
+      <c r="V44" t="s">
+        <v>227</v>
+      </c>
+      <c r="W44">
+        <v>2</v>
+      </c>
+      <c r="X44">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" t="s">
+        <v>120</v>
+      </c>
+      <c r="F45" t="s">
+        <v>123</v>
+      </c>
+      <c r="G45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H45" t="s">
+        <v>150</v>
+      </c>
+      <c r="I45" t="s">
+        <v>155</v>
+      </c>
+      <c r="J45">
+        <v>6</v>
+      </c>
+      <c r="K45">
+        <v>12</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>204</v>
+      </c>
+      <c r="P45">
+        <v>14</v>
+      </c>
+      <c r="Q45">
+        <v>20</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>90</v>
+      </c>
+      <c r="U45">
+        <v>15134</v>
+      </c>
+      <c r="V45" t="s">
+        <v>213</v>
+      </c>
+      <c r="W45">
+        <v>2</v>
+      </c>
+      <c r="X45">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" t="s">
+        <v>83</v>
+      </c>
+      <c r="E46" t="s">
+        <v>122</v>
+      </c>
+      <c r="F46" t="s">
+        <v>123</v>
+      </c>
+      <c r="G46" t="s">
+        <v>149</v>
+      </c>
+      <c r="H46" t="s">
+        <v>150</v>
+      </c>
+      <c r="I46" t="s">
+        <v>153</v>
+      </c>
+      <c r="J46">
+        <v>4</v>
+      </c>
+      <c r="K46">
+        <v>11</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>24</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>205</v>
+      </c>
+      <c r="P46">
+        <v>36</v>
+      </c>
+      <c r="Q46">
+        <v>48</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>90</v>
+      </c>
+      <c r="U46">
+        <v>6424</v>
+      </c>
+      <c r="V46" t="s">
+        <v>209</v>
+      </c>
+      <c r="W46">
+        <v>4</v>
+      </c>
+      <c r="X46">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X35" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X46" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Downloads\Equipes_Agentes\Aplicativos\GAM\bd_saida\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749973BA-586E-4370-8302-916B19F1F07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$46</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="209">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -102,33 +88,36 @@
     <t>Estq_CD_cx</t>
   </si>
   <si>
+    <t>BEBIDAS</t>
+  </si>
+  <si>
     <t>PERECIVEIS</t>
   </si>
   <si>
     <t>MERCEARIA</t>
   </si>
   <si>
-    <t>BEBIDAS</t>
+    <t>PRODUTOS PET</t>
   </si>
   <si>
     <t>PERFUMARIA E LIMPEZA</t>
   </si>
   <si>
+    <t>NICOLAS AUGUSTO P. BORGES</t>
+  </si>
+  <si>
     <t>SANDRO MARTINS VIANNA</t>
   </si>
   <si>
     <t>NIDAL TUBASI</t>
   </si>
   <si>
-    <t>NICOLAS AUGUSTO P. BORGES</t>
+    <t>WETER SONNENFELDET</t>
   </si>
   <si>
     <t>JOAO BATISTA</t>
   </si>
   <si>
-    <t>WETER SONNENFELDET</t>
-  </si>
-  <si>
     <t>001</t>
   </si>
   <si>
@@ -144,6 +133,9 @@
     <t>005</t>
   </si>
   <si>
+    <t>006</t>
+  </si>
+  <si>
     <t>007</t>
   </si>
   <si>
@@ -165,578 +157,497 @@
     <t>017</t>
   </si>
   <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>806</t>
+  </si>
+  <si>
     <t>6783</t>
   </si>
   <si>
+    <t>15765</t>
+  </si>
+  <si>
+    <t>840</t>
+  </si>
+  <si>
+    <t>15764</t>
+  </si>
+  <si>
+    <t>37957</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>15762</t>
+  </si>
+  <si>
+    <t>37075</t>
+  </si>
+  <si>
+    <t>795</t>
+  </si>
+  <si>
+    <t>2974</t>
+  </si>
+  <si>
+    <t>1466</t>
+  </si>
+  <si>
+    <t>2096</t>
+  </si>
+  <si>
+    <t>11245</t>
+  </si>
+  <si>
+    <t>22703</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>3704</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>33468</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>3011</t>
+  </si>
+  <si>
+    <t>5435</t>
+  </si>
+  <si>
+    <t>6704</t>
+  </si>
+  <si>
+    <t>8806</t>
+  </si>
+  <si>
+    <t>9281</t>
+  </si>
+  <si>
+    <t>13123</t>
+  </si>
+  <si>
+    <t>15295</t>
+  </si>
+  <si>
+    <t>2960</t>
+  </si>
+  <si>
+    <t>21250</t>
+  </si>
+  <si>
+    <t>4205</t>
+  </si>
+  <si>
+    <t>812</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML MANGO LOCO</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA LARANJA PET 2L</t>
+  </si>
+  <si>
+    <t>LEITE UHT TIROL C TAMP INT 1L</t>
+  </si>
+  <si>
+    <t>CESTA BASICA PEQ</t>
+  </si>
+  <si>
+    <t>REFRIG PEPSI PET 3L</t>
+  </si>
+  <si>
+    <t>CESTA BASICA MED</t>
+  </si>
+  <si>
+    <t>CHA BARAO 13G PTO</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML GREEN</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML GREEN ZERO</t>
+  </si>
+  <si>
+    <t>CESTA BASICA GRD</t>
+  </si>
+  <si>
+    <t>FARINHA TAPIOCA DINDA 400G TRAD</t>
+  </si>
+  <si>
+    <t>REFRIG COCA COLA PET 2L ZERO</t>
+  </si>
+  <si>
+    <t>ACUCAR DEMERARA UNIAO 1KG</t>
+  </si>
+  <si>
+    <t>BISC RECH NESTLE NEGRESCO 90G CHOC</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SANO T1 2K</t>
+  </si>
+  <si>
+    <t>GOIABADA STELLA KG</t>
+  </si>
+  <si>
+    <t>RACAO DODOG ORIG ALL DAY 5KG</t>
+  </si>
+  <si>
+    <t>AGUA MIN FLORESTA PET 500ML S GAS</t>
+  </si>
+  <si>
+    <t>MIST P BOLO APTI 400G CHOC</t>
+  </si>
+  <si>
+    <t>CERV BRAHMA CHOPP GF 1L RETORNAVEL</t>
+  </si>
+  <si>
+    <t>MOLHO TOMATE HEINZ SH 240G C PEDACOS</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML ABSOLUT ZERO</t>
+  </si>
+  <si>
+    <t>AVEIA FLOCOS FINOS NATURALE 1KG</t>
+  </si>
+  <si>
+    <t>DESINF GIRANDO SOL 2L LAVANDA</t>
+  </si>
+  <si>
+    <t>LAVA ROUPA LIQ GIRANDO SOL FR 2L COCO</t>
+  </si>
+  <si>
+    <t>AGUA SANIT GIRANDO SOL 2L</t>
+  </si>
+  <si>
+    <t>DESINF GIRANDO SOL 2L JASMIM</t>
+  </si>
+  <si>
+    <t>BATATA PALHA YOKI TRAD L105P90 105G</t>
+  </si>
+  <si>
+    <t>CALDO MAGGI 57G COSTELA</t>
+  </si>
+  <si>
+    <t>ACHOC TODDY PT 370G ORIGINAL</t>
+  </si>
+  <si>
+    <t>MOSTARDA MOSTARDOG BD 1K</t>
+  </si>
+  <si>
+    <t>AMAC GIRANDO SOL 2L LILAS</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA UVA PET 2L</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>05/10/2024</t>
+  </si>
+  <si>
+    <t>19/10/2024</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>18/10/2024</t>
+  </si>
+  <si>
+    <t>18/12/2024</t>
+  </si>
+  <si>
+    <t>12/11/2024</t>
+  </si>
+  <si>
+    <t>04/12/2024</t>
+  </si>
+  <si>
+    <t>11/06/2025</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>31/12/2024</t>
+  </si>
+  <si>
+    <t>23/09/2024</t>
+  </si>
+  <si>
+    <t>06/08/2025</t>
+  </si>
+  <si>
+    <t>17/12/2024</t>
+  </si>
+  <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>4199</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1382</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>1779</t>
+  </si>
+  <si>
+    <t>1019</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>1488</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>1504</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>43</t>
   </si>
   <si>
-    <t>6781</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>838</t>
-  </si>
-  <si>
-    <t>5431</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>795</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t>10856</t>
-  </si>
-  <si>
-    <t>806</t>
-  </si>
-  <si>
-    <t>1297</t>
-  </si>
-  <si>
-    <t>835</t>
-  </si>
-  <si>
-    <t>910</t>
-  </si>
-  <si>
-    <t>2396</t>
-  </si>
-  <si>
-    <t>5673</t>
-  </si>
-  <si>
-    <t>5678</t>
-  </si>
-  <si>
-    <t>7878</t>
-  </si>
-  <si>
-    <t>10147</t>
-  </si>
-  <si>
-    <t>10148</t>
-  </si>
-  <si>
-    <t>17341</t>
-  </si>
-  <si>
-    <t>17349</t>
-  </si>
-  <si>
-    <t>22999</t>
-  </si>
-  <si>
-    <t>23111</t>
-  </si>
-  <si>
-    <t>33265</t>
-  </si>
-  <si>
-    <t>34977</t>
-  </si>
-  <si>
-    <t>1657</t>
-  </si>
-  <si>
-    <t>1713</t>
-  </si>
-  <si>
-    <t>2499</t>
-  </si>
-  <si>
-    <t>2831</t>
-  </si>
-  <si>
-    <t>2924</t>
-  </si>
-  <si>
-    <t>3475</t>
-  </si>
-  <si>
-    <t>3531</t>
-  </si>
-  <si>
-    <t>13277</t>
-  </si>
-  <si>
-    <t>39236</t>
-  </si>
-  <si>
-    <t>2179</t>
-  </si>
-  <si>
-    <t>2232</t>
-  </si>
-  <si>
-    <t>1575</t>
-  </si>
-  <si>
-    <t>39265</t>
-  </si>
-  <si>
-    <t>LEITE UHT TIROL C TAMP INT 1L</t>
-  </si>
-  <si>
-    <t>AGUA MIN CRYSTAL PET 500ML S GAS</t>
-  </si>
-  <si>
-    <t>LEITE UHT ELEGE INT 1L</t>
-  </si>
-  <si>
-    <t>AGUA MIN CRYSTAL PET 500ML C GAS</t>
-  </si>
-  <si>
-    <t>REFRIG FRUKI PET 3L GUARANA</t>
-  </si>
-  <si>
-    <t>DESINF AQUAFAST HARMONIA 5L LAVANDA</t>
-  </si>
-  <si>
-    <t>AGUA MIN FLORESTA PET 500ML S GAS</t>
-  </si>
-  <si>
-    <t>REFRIG COCA COLA PET 2L ZERO</t>
-  </si>
-  <si>
-    <t>ENERG MONSTER LT 473ML GREEN</t>
-  </si>
-  <si>
-    <t>CASTANHA PARA UNIAGRO S CASCA</t>
-  </si>
-  <si>
-    <t>REFRIG FANTA LARANJA PET 2L</t>
-  </si>
-  <si>
-    <t>CHOC BARRA NESTLE 80G CRUNCH</t>
-  </si>
-  <si>
-    <t>REFRIG PET COCA COLA 3L</t>
-  </si>
-  <si>
-    <t>REFRIG SUKITA LT 350 ML</t>
-  </si>
-  <si>
-    <t>MILHO VERDE OLE LT 170G</t>
-  </si>
-  <si>
-    <t>DET LIQ GIRANDO SOL 500ML LIMAO</t>
-  </si>
-  <si>
-    <t>DET LIQ GOTA LIMPA 500ML CRISTAL</t>
-  </si>
-  <si>
-    <t>SABONETE DOVE 90G KARITE BAUNILHA</t>
-  </si>
-  <si>
-    <t>SAB FARNESE 180G LAVANDA MENTA</t>
-  </si>
-  <si>
-    <t>SAB FARNESE 180G PITAYA FRAMB</t>
-  </si>
-  <si>
-    <t>DET LIQ BIO KRISS 500ML NEUTRO</t>
-  </si>
-  <si>
-    <t>DET LIQ GOTA LIMPA 1L NATURAL</t>
-  </si>
-  <si>
-    <t>SAB FONTANA SENSUS 150G AMANHECER PERS</t>
-  </si>
-  <si>
-    <t>SAB PALMOLIVE 85G ARGILA EUCALIP</t>
-  </si>
-  <si>
-    <t>REFRIG FRUKI GUAR ZR PET 3L GUARANA ZERO</t>
-  </si>
-  <si>
-    <t>SAB MARAN SUAVE 80G PESSEGO</t>
-  </si>
-  <si>
-    <t>WAFFER ISABELA 100G DOCE DE LEITE</t>
-  </si>
-  <si>
-    <t>PIPOCA DOCE KEVYTOS 50G</t>
-  </si>
-  <si>
-    <t>KETCHUP ODERICH BISN 400G PICANTE</t>
-  </si>
-  <si>
-    <t>MASSA C OVOS GERMANI 500G ESPAGUETE</t>
-  </si>
-  <si>
-    <t>MASSA C OVOS PARATI 500G RIGATONI</t>
-  </si>
-  <si>
-    <t>TEMP COLORIFICO APTI 100G</t>
-  </si>
-  <si>
-    <t>FERM QUIMICO PO ROYAL PT 100G</t>
-  </si>
-  <si>
-    <t>BISC AGUA SAL ORQUIDEA 665GR</t>
-  </si>
-  <si>
-    <t>CERV AMSTEL ULTRA LN 330ML</t>
-  </si>
-  <si>
-    <t>CHA PRENDA GOLD 15G CIDREIRA</t>
-  </si>
-  <si>
-    <t>CAPSULA DOLCE GUSTO 117G C 10 CAPPUCCINO</t>
-  </si>
-  <si>
-    <t>BISC SALG GERMANI GRISSINI 175G</t>
-  </si>
-  <si>
-    <t>REFRE FRUKITO PET 5L FRUTAS CITRICAS</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>18/09/2024</t>
-  </si>
-  <si>
-    <t>21/10/2024</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>18/10/2024</t>
-  </si>
-  <si>
-    <t>05/10/2024</t>
-  </si>
-  <si>
-    <t>11/06/2025</t>
-  </si>
-  <si>
-    <t>19/10/2024</t>
-  </si>
-  <si>
-    <t>07/11/2024</t>
-  </si>
-  <si>
-    <t>23/10/2024</t>
-  </si>
-  <si>
-    <t>09/12/2024</t>
-  </si>
-  <si>
-    <t>08/07/2025</t>
-  </si>
-  <si>
-    <t>08/12/2025</t>
-  </si>
-  <si>
-    <t>19/11/2024</t>
-  </si>
-  <si>
-    <t>22/11/2024</t>
-  </si>
-  <si>
-    <t>10/12/2024</t>
-  </si>
-  <si>
-    <t>16/12/2024</t>
-  </si>
-  <si>
-    <t>17/12/2024</t>
-  </si>
-  <si>
-    <t>27/12/2024</t>
-  </si>
-  <si>
-    <t>28/12/2024</t>
-  </si>
-  <si>
-    <t>24/08/2026</t>
-  </si>
-  <si>
-    <t>05/12/2024</t>
-  </si>
-  <si>
-    <t>14/11/2024</t>
-  </si>
-  <si>
-    <t>26/08/2026</t>
-  </si>
-  <si>
-    <t>Ativo</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>4038</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1511</t>
-  </si>
-  <si>
-    <t>1845</t>
-  </si>
-  <si>
-    <t>5962</t>
+    <t>49,54</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>660</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>12100</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>789</t>
+  </si>
+  <si>
+    <t>1314</t>
+  </si>
+  <si>
+    <t>1815</t>
   </si>
   <si>
     <t>1629</t>
   </si>
   <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>13983</t>
-  </si>
-  <si>
-    <t>1391</t>
-  </si>
-  <si>
-    <t>588</t>
-  </si>
-  <si>
-    <t>,58</t>
-  </si>
-  <si>
-    <t>1081</t>
-  </si>
-  <si>
-    <t>1413</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>654</t>
-  </si>
-  <si>
-    <t>1,57</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>1739</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>418</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>286</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>1016</t>
-  </si>
-  <si>
-    <t>35487</t>
-  </si>
-  <si>
-    <t>3068</t>
-  </si>
-  <si>
-    <t>628</t>
-  </si>
-  <si>
-    <t>579</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>827</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1150</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>37</t>
+    <t>211</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>597</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>495</t>
+  </si>
+  <si>
+    <t>SPAL IND BRAS BEBIDAS AS</t>
   </si>
   <si>
     <t>LATICINIOS TIROL LTDA.</t>
   </si>
   <si>
-    <t>SPAL IND BRAS BEBIDAS AS</t>
-  </si>
-  <si>
-    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
-  </si>
-  <si>
-    <t>BEBIDAS FRUKI LTDA</t>
-  </si>
-  <si>
-    <t>AQUAFAST PROD LIMPEZA/HIGIENE LTDA</t>
+    <t>SUPERMERCADO BAKLIZI LTDA</t>
+  </si>
+  <si>
+    <t>CRBS AS CDD PELOTAS</t>
+  </si>
+  <si>
+    <t>BARAO - INDUSTRIA E COMERCIO DE ERVA MATE E CHAS S.A.</t>
+  </si>
+  <si>
+    <t>ROCHA E FILHOS LTDA</t>
+  </si>
+  <si>
+    <t>ATACADAO S.A.</t>
+  </si>
+  <si>
+    <t>NESTLE BRASIL LTDA</t>
+  </si>
+  <si>
+    <t>FERRUCCI E MIRANDA LTDA-EPP</t>
+  </si>
+  <si>
+    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
+  </si>
+  <si>
+    <t>NUTRISUL ALIMENTOS LTDA</t>
   </si>
   <si>
     <t>AGUAS MINERAIS SARANDI LTDA</t>
   </si>
   <si>
-    <t>UNIAGRO -IND.E COM.DE PROD.ALIM.LTDA</t>
-  </si>
-  <si>
-    <t>NESTLE BRASIL LTDA</t>
-  </si>
-  <si>
-    <t>CRBS AS CDD PELOTAS</t>
-  </si>
-  <si>
-    <t>ANGELO AURICCHIO &amp; CIA LTDA</t>
+    <t>APTI ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>KASADOCE DISTRIBUIDORA DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>NAT CEREAIS E ALIMENTOS LTDA</t>
   </si>
   <si>
     <t>IND COM PROD LIMP GIRANDO SOL LTDA</t>
   </si>
   <si>
-    <t>BERTOLINI INDUSTRIA QUIMICA LTDA</t>
-  </si>
-  <si>
-    <t>ZAFFALON E CIA LTDA</t>
-  </si>
-  <si>
-    <t>ONIZ DISTRIBUID LTDA SCJ</t>
-  </si>
-  <si>
-    <t>SENIR EMBALAGENS LTDA</t>
-  </si>
-  <si>
-    <t>FONTANA S.A</t>
-  </si>
-  <si>
-    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
-  </si>
-  <si>
-    <t>ATACADAO S.A.</t>
-  </si>
-  <si>
-    <t>M DIAS BRANCO S.A IND E COM DE ALIMENTOS</t>
-  </si>
-  <si>
-    <t>DELAVY ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>CONSERVAS ODERICH SA</t>
-  </si>
-  <si>
-    <t>GERMANI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>PARATI IND.COM.DE ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>APTI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>TOPFLEX DISTRIBUIDOR DE ALIMENTOS</t>
-  </si>
-  <si>
-    <t>TONDO S/A</t>
-  </si>
-  <si>
-    <t>CARLOS CANCIAN E CIA LTDA</t>
-  </si>
-  <si>
-    <t>CHA PRENDA DO BRASIL IND E COM EIRELI</t>
+    <t>FABIANO ZAFFALON E CIA LTDA</t>
+  </si>
+  <si>
+    <t>PEPSICO DO BRASIL LTDA</t>
+  </si>
+  <si>
+    <t>ADI-GEL IND. E COM. DE PROD. ALIMENT.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -773,21 +684,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -825,7 +728,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -859,7 +762,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -894,10 +796,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1070,14 +971,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="43.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:X62"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1151,58 +1049,58 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H2" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I2" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>148</v>
+      </c>
+      <c r="P2">
+        <v>6</v>
+      </c>
+      <c r="Q2">
         <v>12</v>
       </c>
-      <c r="K2">
-        <v>422</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>165</v>
-      </c>
-      <c r="P2">
-        <v>480</v>
-      </c>
-      <c r="Q2">
-        <v>600</v>
-      </c>
       <c r="R2">
         <v>0</v>
       </c>
@@ -1213,51 +1111,51 @@
         <v>90</v>
       </c>
       <c r="U2">
-        <v>15208</v>
+        <v>15441</v>
       </c>
       <c r="V2" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="W2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="X2">
-        <v>5958</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
         <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H3" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I3" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K3">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1269,13 +1167,13 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="P3">
-        <v>162</v>
+        <v>32</v>
       </c>
       <c r="Q3">
-        <v>258</v>
+        <v>56</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1290,48 +1188,48 @@
         <v>15441</v>
       </c>
       <c r="V3" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="W3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="X3">
-        <v>23.08</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H4" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I4" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="J4">
         <v>12</v>
       </c>
       <c r="K4">
-        <v>156</v>
+        <v>456</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1343,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="P4">
-        <v>166</v>
+        <v>480</v>
       </c>
       <c r="Q4">
-        <v>262</v>
+        <v>600</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1361,125 +1259,125 @@
         <v>90</v>
       </c>
       <c r="U4">
-        <v>9379</v>
+        <v>15208</v>
       </c>
       <c r="V4" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X4">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
       <c r="A5" t="s">
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F5" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H5" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
         <v>151</v>
       </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
-      <c r="K5">
-        <v>23</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>169</v>
-      </c>
       <c r="P5">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1308</v>
+        <v>0</v>
       </c>
       <c r="T5">
         <v>90</v>
       </c>
       <c r="U5">
-        <v>15441</v>
+        <v>15</v>
       </c>
       <c r="V5" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>218.58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G6" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H6" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I6" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1491,10 +1389,10 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="P6">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="Q6">
         <v>240</v>
@@ -1509,21 +1407,21 @@
         <v>90</v>
       </c>
       <c r="U6">
-        <v>6424</v>
+        <v>9638</v>
       </c>
       <c r="V6" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="W6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X6">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
@@ -1532,28 +1430,28 @@
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I7" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1565,13 +1463,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="P7">
         <v>10</v>
       </c>
       <c r="Q7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1583,69 +1481,69 @@
         <v>90</v>
       </c>
       <c r="U7">
-        <v>3947</v>
+        <v>15</v>
       </c>
       <c r="V7" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="W7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="X7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
       <c r="A8" t="s">
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
         <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F8" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G8" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="H8" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I8" t="s">
+        <v>138</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
         <v>151</v>
       </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>-548</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>172</v>
-      </c>
       <c r="P8">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1657,125 +1555,125 @@
         <v>90</v>
       </c>
       <c r="U8">
-        <v>10181</v>
+        <v>15</v>
       </c>
       <c r="V8" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="W8">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="X8">
-        <v>30.92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>26</v>
       </c>
       <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" t="s">
+        <v>134</v>
+      </c>
+      <c r="I9" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
+      <c r="K9">
+        <v>17</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>153</v>
+      </c>
+      <c r="P9">
+        <v>18</v>
+      </c>
+      <c r="Q9">
+        <v>48</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>90</v>
+      </c>
+      <c r="U9">
+        <v>6798</v>
+      </c>
+      <c r="V9" t="s">
+        <v>194</v>
+      </c>
+      <c r="W9">
+        <v>2</v>
+      </c>
+      <c r="X9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" t="s">
-        <v>124</v>
-      </c>
-      <c r="G9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9" t="s">
-        <v>150</v>
-      </c>
-      <c r="I9" t="s">
-        <v>154</v>
-      </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
-      <c r="K9">
-        <v>133</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>173</v>
-      </c>
-      <c r="P9">
-        <v>150</v>
-      </c>
-      <c r="Q9">
-        <v>238</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>90</v>
-      </c>
-      <c r="U9">
-        <v>15441</v>
-      </c>
-      <c r="V9" t="s">
-        <v>207</v>
-      </c>
-      <c r="W9">
-        <v>14</v>
-      </c>
-      <c r="X9">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F10" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G10" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="H10" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I10" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
       <c r="K10">
-        <v>63</v>
+        <v>165</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1787,13 +1685,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="P10">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="Q10">
-        <v>102</v>
+        <v>306</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1808,140 +1706,140 @@
         <v>15441</v>
       </c>
       <c r="V10" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="X10">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" t="s">
+        <v>117</v>
+      </c>
+      <c r="H11" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" t="s">
+        <v>135</v>
+      </c>
+      <c r="J11">
+        <v>6</v>
+      </c>
+      <c r="K11">
+        <v>63</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>155</v>
+      </c>
+      <c r="P11">
+        <v>114</v>
+      </c>
+      <c r="Q11">
+        <v>180</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>90</v>
+      </c>
+      <c r="U11">
+        <v>15441</v>
+      </c>
+      <c r="V11" t="s">
+        <v>190</v>
+      </c>
+      <c r="W11">
+        <v>20</v>
+      </c>
+      <c r="X11">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H12" t="s">
+        <v>134</v>
+      </c>
+      <c r="I12" t="s">
+        <v>135</v>
+      </c>
+      <c r="J12">
+        <v>6</v>
+      </c>
+      <c r="K12">
+        <v>14</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>156</v>
+      </c>
+      <c r="P12">
+        <v>42</v>
+      </c>
+      <c r="Q12">
         <v>54</v>
-      </c>
-      <c r="E11" t="s">
-        <v>93</v>
-      </c>
-      <c r="F11" t="s">
-        <v>123</v>
-      </c>
-      <c r="G11" t="s">
-        <v>132</v>
-      </c>
-      <c r="H11" t="s">
-        <v>150</v>
-      </c>
-      <c r="I11" t="s">
-        <v>156</v>
-      </c>
-      <c r="J11">
-        <v>20</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>175</v>
-      </c>
-      <c r="P11">
-        <v>0.85399999999999998</v>
-      </c>
-      <c r="Q11">
-        <v>2</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>90</v>
-      </c>
-      <c r="U11">
-        <v>14718</v>
-      </c>
-      <c r="V11" t="s">
-        <v>212</v>
-      </c>
-      <c r="W11">
-        <v>1</v>
-      </c>
-      <c r="X11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" t="s">
-        <v>124</v>
-      </c>
-      <c r="G12" t="s">
-        <v>130</v>
-      </c>
-      <c r="H12" t="s">
-        <v>150</v>
-      </c>
-      <c r="I12" t="s">
-        <v>154</v>
-      </c>
-      <c r="J12">
-        <v>8</v>
-      </c>
-      <c r="K12">
-        <v>111</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>176</v>
-      </c>
-      <c r="P12">
-        <v>124</v>
-      </c>
-      <c r="Q12">
-        <v>196</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1956,48 +1854,48 @@
         <v>15441</v>
       </c>
       <c r="V12" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="W12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G13" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H13" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I13" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2009,13 +1907,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="P13">
-        <v>170</v>
+        <v>15</v>
       </c>
       <c r="Q13">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -2027,51 +1925,51 @@
         <v>90</v>
       </c>
       <c r="U13">
-        <v>15441</v>
+        <v>15</v>
       </c>
       <c r="V13" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="W13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="F14" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G14" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="H14" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I14" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="J14">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2083,13 +1981,13 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="P14">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="Q14">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -2101,69 +1999,69 @@
         <v>90</v>
       </c>
       <c r="U14">
-        <v>15134</v>
+        <v>15</v>
       </c>
       <c r="V14" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="W14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="X14">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>26</v>
       </c>
       <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H15" t="s">
+        <v>134</v>
+      </c>
+      <c r="I15" t="s">
+        <v>141</v>
+      </c>
+      <c r="J15">
+        <v>20</v>
+      </c>
+      <c r="K15">
+        <v>27</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>157</v>
+      </c>
+      <c r="P15">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15" t="s">
-        <v>124</v>
-      </c>
-      <c r="G15" t="s">
-        <v>133</v>
-      </c>
-      <c r="H15" t="s">
-        <v>150</v>
-      </c>
-      <c r="I15" t="s">
-        <v>154</v>
-      </c>
-      <c r="J15">
-        <v>8</v>
-      </c>
-      <c r="K15">
-        <v>74</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>179</v>
-      </c>
-      <c r="P15">
-        <v>80</v>
-      </c>
       <c r="Q15">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -2175,51 +2073,51 @@
         <v>90</v>
       </c>
       <c r="U15">
-        <v>15441</v>
+        <v>21894</v>
       </c>
       <c r="V15" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X15">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
       <c r="A16" t="s">
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G16" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="H16" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I16" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="J16">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>0.81599999999999995</v>
+        <v>19</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2231,13 +2129,13 @@
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="P16">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="Q16">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -2249,51 +2147,51 @@
         <v>90</v>
       </c>
       <c r="U16">
-        <v>14718</v>
+        <v>15441</v>
       </c>
       <c r="V16" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="W16">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G17" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H17" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I17" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="J17">
         <v>6</v>
       </c>
       <c r="K17">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2305,13 +2203,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="P17">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="Q17">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2326,48 +2224,48 @@
         <v>15441</v>
       </c>
       <c r="V17" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="W17">
         <v>4</v>
       </c>
       <c r="X17">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G18" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" t="s">
+        <v>134</v>
+      </c>
+      <c r="I18" t="s">
         <v>135</v>
       </c>
-      <c r="H18" t="s">
-        <v>150</v>
-      </c>
-      <c r="I18" t="s">
-        <v>151</v>
-      </c>
       <c r="J18">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2379,10 +2277,10 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="P18">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q18">
         <v>28</v>
@@ -2397,51 +2295,51 @@
         <v>90</v>
       </c>
       <c r="U18">
-        <v>9638</v>
+        <v>15441</v>
       </c>
       <c r="V18" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="W18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X18">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
         <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F19" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G19" t="s">
+        <v>124</v>
+      </c>
+      <c r="H19" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19" t="s">
         <v>136</v>
       </c>
-      <c r="H19" t="s">
-        <v>150</v>
-      </c>
-      <c r="I19" t="s">
-        <v>158</v>
-      </c>
       <c r="J19">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2453,13 +2351,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="P19">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="Q19">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -2471,48 +2369,48 @@
         <v>90</v>
       </c>
       <c r="U19">
-        <v>7715</v>
+        <v>15441</v>
       </c>
       <c r="V19" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="X19">
-        <v>493.04</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
         <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G20" t="s">
         <v>125</v>
       </c>
       <c r="H20" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I20" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="J20">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -2521,19 +2419,19 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="P20">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="Q20">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -2545,143 +2443,143 @@
         <v>90</v>
       </c>
       <c r="U20">
-        <v>10334</v>
+        <v>11112</v>
       </c>
       <c r="V20" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="W20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X20">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" t="s">
+        <v>134</v>
+      </c>
+      <c r="I21" t="s">
+        <v>138</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>151</v>
+      </c>
+      <c r="P21">
+        <v>5</v>
+      </c>
+      <c r="Q21">
+        <v>10</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>90</v>
+      </c>
+      <c r="U21">
+        <v>15</v>
+      </c>
+      <c r="V21" t="s">
+        <v>192</v>
+      </c>
+      <c r="W21">
+        <v>10</v>
+      </c>
+      <c r="X21">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
         <v>61</v>
       </c>
-      <c r="E21" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" t="s">
-        <v>123</v>
-      </c>
-      <c r="G21" t="s">
-        <v>125</v>
-      </c>
-      <c r="H21" t="s">
-        <v>150</v>
-      </c>
-      <c r="I21" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21">
-        <v>24</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>24</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>185</v>
-      </c>
-      <c r="P21">
-        <v>46</v>
-      </c>
-      <c r="Q21">
-        <v>70</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>90</v>
-      </c>
-      <c r="U21">
-        <v>14468</v>
-      </c>
-      <c r="V21" t="s">
-        <v>217</v>
-      </c>
-      <c r="W21">
-        <v>2</v>
-      </c>
-      <c r="X21">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" t="s">
-        <v>62</v>
-      </c>
       <c r="E22" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="F22" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H22" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I22" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="J22">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>-111</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="P22">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="Q22">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -2693,51 +2591,51 @@
         <v>90</v>
       </c>
       <c r="U22">
-        <v>17017</v>
+        <v>15134</v>
       </c>
       <c r="V22" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="W22">
         <v>2</v>
       </c>
       <c r="X22">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G23" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H23" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="J23">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -2749,143 +2647,143 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="P23">
+        <v>31</v>
+      </c>
+      <c r="Q23">
+        <v>46</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>90</v>
+      </c>
+      <c r="U23">
+        <v>7918</v>
+      </c>
+      <c r="V23" t="s">
+        <v>198</v>
+      </c>
+      <c r="W23">
+        <v>2</v>
+      </c>
+      <c r="X23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
         <v>38</v>
       </c>
-      <c r="Q23">
-        <v>74</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>90</v>
-      </c>
-      <c r="U23">
-        <v>6644</v>
-      </c>
-      <c r="V23" t="s">
-        <v>219</v>
-      </c>
-      <c r="W23">
-        <v>3</v>
-      </c>
-      <c r="X23">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" t="s">
-        <v>41</v>
-      </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F24" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G24" t="s">
         <v>125</v>
       </c>
       <c r="H24" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="J24">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="P24">
+        <v>88</v>
+      </c>
+      <c r="Q24">
+        <v>128</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>90</v>
+      </c>
+      <c r="U24">
+        <v>11112</v>
+      </c>
+      <c r="V24" t="s">
+        <v>196</v>
+      </c>
+      <c r="W24">
+        <v>6</v>
+      </c>
+      <c r="X24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
         <v>30</v>
       </c>
-      <c r="Q24">
-        <v>66</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>90</v>
-      </c>
-      <c r="U24">
-        <v>6644</v>
-      </c>
-      <c r="V24" t="s">
-        <v>219</v>
-      </c>
-      <c r="W24">
-        <v>2</v>
-      </c>
-      <c r="X24">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F25" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G25" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H25" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I25" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="J25">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>6.716</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2897,13 +2795,13 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="P25">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2915,48 +2813,48 @@
         <v>90</v>
       </c>
       <c r="U25">
-        <v>21220</v>
+        <v>5894</v>
       </c>
       <c r="V25" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="W25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X25">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G26" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H26" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I26" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="J26">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -2974,10 +2872,10 @@
         <v>151</v>
       </c>
       <c r="P26">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -2989,51 +2887,51 @@
         <v>90</v>
       </c>
       <c r="U26">
-        <v>14468</v>
+        <v>15</v>
       </c>
       <c r="V26" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="W26">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24">
       <c r="A27" t="s">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F27" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G27" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H27" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I27" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="J27">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3045,13 +2943,13 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="P27">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -3063,49 +2961,49 @@
         <v>90</v>
       </c>
       <c r="U27">
-        <v>21822</v>
+        <v>17077</v>
       </c>
       <c r="V27" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="W27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X27">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" t="s">
+        <v>125</v>
+      </c>
+      <c r="H28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I28" t="s">
+        <v>142</v>
+      </c>
+      <c r="J28">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E28" t="s">
-        <v>107</v>
-      </c>
-      <c r="F28" t="s">
-        <v>123</v>
-      </c>
-      <c r="G28" t="s">
-        <v>126</v>
-      </c>
-      <c r="H28" t="s">
-        <v>150</v>
-      </c>
-      <c r="I28" t="s">
-        <v>161</v>
-      </c>
-      <c r="J28">
-        <v>108</v>
-      </c>
       <c r="K28">
         <v>0</v>
       </c>
@@ -3113,19 +3011,19 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N28">
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="P28">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="Q28">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -3137,48 +3035,48 @@
         <v>90</v>
       </c>
       <c r="U28">
-        <v>5894</v>
+        <v>11112</v>
       </c>
       <c r="V28" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="W28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X28">
-        <v>30.89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24">
       <c r="A29" t="s">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="F29" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G29" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H29" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I29" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -3193,13 +3091,13 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="P29">
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -3211,126 +3109,126 @@
         <v>90</v>
       </c>
       <c r="U29">
-        <v>6424</v>
+        <v>15</v>
       </c>
       <c r="V29" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="X29">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24">
       <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" t="s">
+        <v>114</v>
+      </c>
+      <c r="G30" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" t="s">
+        <v>134</v>
+      </c>
+      <c r="I30" t="s">
+        <v>135</v>
+      </c>
+      <c r="J30">
+        <v>6</v>
+      </c>
+      <c r="K30">
+        <v>61</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>167</v>
+      </c>
+      <c r="P30">
+        <v>74</v>
+      </c>
+      <c r="Q30">
+        <v>116</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>90</v>
+      </c>
+      <c r="U30">
+        <v>15441</v>
+      </c>
+      <c r="V30" t="s">
+        <v>190</v>
+      </c>
+      <c r="W30">
+        <v>10</v>
+      </c>
+      <c r="X30">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" t="s">
+        <v>117</v>
+      </c>
+      <c r="H31" t="s">
+        <v>134</v>
+      </c>
+      <c r="I31" t="s">
+        <v>135</v>
+      </c>
+      <c r="J31">
+        <v>6</v>
+      </c>
+      <c r="K31">
         <v>27</v>
       </c>
-      <c r="B30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" t="s">
-        <v>70</v>
-      </c>
-      <c r="E30" t="s">
-        <v>109</v>
-      </c>
-      <c r="F30" t="s">
-        <v>123</v>
-      </c>
-      <c r="G30" t="s">
-        <v>138</v>
-      </c>
-      <c r="H30" t="s">
-        <v>150</v>
-      </c>
-      <c r="I30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J30">
-        <v>108</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
-        <v>191</v>
-      </c>
-      <c r="P30">
-        <v>128</v>
-      </c>
-      <c r="Q30">
-        <v>236</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>90</v>
-      </c>
-      <c r="U30">
-        <v>11112</v>
-      </c>
-      <c r="V30" t="s">
-        <v>223</v>
-      </c>
-      <c r="W30">
-        <v>3</v>
-      </c>
-      <c r="X30">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" t="s">
-        <v>90</v>
-      </c>
-      <c r="F31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G31" t="s">
-        <v>129</v>
-      </c>
-      <c r="H31" t="s">
-        <v>150</v>
-      </c>
-      <c r="I31" t="s">
-        <v>151</v>
-      </c>
-      <c r="J31">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <v>-18</v>
-      </c>
       <c r="L31">
         <v>0</v>
       </c>
@@ -3341,13 +3239,13 @@
         <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="P31">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q31">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -3359,69 +3257,69 @@
         <v>90</v>
       </c>
       <c r="U31">
-        <v>10181</v>
+        <v>15441</v>
       </c>
       <c r="V31" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="W31">
         <v>4</v>
       </c>
       <c r="X31">
-        <v>30.92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
         <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F32" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H32" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I32" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="J32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>356</v>
+        <v>27</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N32">
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="P32">
-        <v>358</v>
+        <v>88</v>
       </c>
       <c r="Q32">
-        <v>558</v>
+        <v>128</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -3433,51 +3331,51 @@
         <v>90</v>
       </c>
       <c r="U32">
-        <v>15441</v>
+        <v>11112</v>
       </c>
       <c r="V32" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="W32">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="X32">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E33" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="F33" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G33" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="H33" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I33" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="J33">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="K33">
-        <v>60</v>
+        <v>-333</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3489,13 +3387,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="P33">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="Q33">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -3507,69 +3405,69 @@
         <v>90</v>
       </c>
       <c r="U33">
-        <v>7995</v>
+        <v>10181</v>
       </c>
       <c r="V33" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="W33">
         <v>3</v>
       </c>
       <c r="X33">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E34" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F34" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G34" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="H34" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I34" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="J34">
         <v>10</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N34">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="P34">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="Q34">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -3581,52 +3479,52 @@
         <v>90</v>
       </c>
       <c r="U34">
-        <v>2977</v>
+        <v>11112</v>
       </c>
       <c r="V34" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="W34">
         <v>3</v>
       </c>
       <c r="X34">
-        <v>64.900000000000006</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" t="s">
+        <v>99</v>
+      </c>
+      <c r="F35" t="s">
+        <v>115</v>
+      </c>
+      <c r="G35" t="s">
+        <v>130</v>
+      </c>
+      <c r="H35" t="s">
+        <v>134</v>
+      </c>
+      <c r="I35" t="s">
+        <v>137</v>
+      </c>
+      <c r="J35">
+        <v>12</v>
+      </c>
+      <c r="K35">
         <v>42</v>
       </c>
-      <c r="D35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E35" t="s">
-        <v>112</v>
-      </c>
-      <c r="F35" t="s">
-        <v>123</v>
-      </c>
-      <c r="G35" t="s">
-        <v>141</v>
-      </c>
-      <c r="H35" t="s">
-        <v>150</v>
-      </c>
-      <c r="I35" t="s">
-        <v>158</v>
-      </c>
-      <c r="J35">
-        <v>24</v>
-      </c>
-      <c r="K35">
-        <v>16</v>
-      </c>
       <c r="L35">
         <v>0</v>
       </c>
@@ -3637,13 +3535,13 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="P35">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="Q35">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -3655,51 +3553,51 @@
         <v>90</v>
       </c>
       <c r="U35">
-        <v>14671</v>
+        <v>10189</v>
       </c>
       <c r="V35" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="W35">
         <v>2</v>
       </c>
       <c r="X35">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
         <v>42</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="F36" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G36" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="H36" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I36" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="J36">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K36">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3711,13 +3609,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="P36">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="Q36">
-        <v>94</v>
+        <v>230</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -3729,95 +3627,95 @@
         <v>90</v>
       </c>
       <c r="U36">
-        <v>16963</v>
+        <v>9638</v>
       </c>
       <c r="V36" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="W36">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="X36">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
         <v>42</v>
       </c>
       <c r="D37" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E37" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37" t="s">
         <v>114</v>
       </c>
-      <c r="F37" t="s">
-        <v>123</v>
-      </c>
       <c r="G37" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="H37" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I37" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="J37">
+        <v>8</v>
+      </c>
+      <c r="K37">
+        <v>149</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>8</v>
+      </c>
+      <c r="O37" t="s">
+        <v>174</v>
+      </c>
+      <c r="P37">
+        <v>202</v>
+      </c>
+      <c r="Q37">
+        <v>314</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>90</v>
+      </c>
+      <c r="U37">
+        <v>15441</v>
+      </c>
+      <c r="V37" t="s">
+        <v>190</v>
+      </c>
+      <c r="W37">
         <v>20</v>
       </c>
-      <c r="K37">
-        <v>15</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37" t="s">
-        <v>198</v>
-      </c>
-      <c r="P37">
-        <v>20</v>
-      </c>
-      <c r="Q37">
-        <v>40</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>90</v>
-      </c>
-      <c r="U37">
-        <v>12257</v>
-      </c>
-      <c r="V37" t="s">
-        <v>228</v>
-      </c>
-      <c r="W37">
-        <v>2</v>
-      </c>
       <c r="X37">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s">
         <v>32</v>
@@ -3826,46 +3724,46 @@
         <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E38" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" t="s">
         <v>115</v>
       </c>
-      <c r="F38" t="s">
-        <v>123</v>
-      </c>
       <c r="G38" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H38" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I38" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="J38">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="K38">
-        <v>13</v>
+        <v>-100</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="N38">
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="P38">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="Q38">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -3877,51 +3775,51 @@
         <v>90</v>
       </c>
       <c r="U38">
-        <v>10189</v>
+        <v>15134</v>
       </c>
       <c r="V38" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="W38">
         <v>2</v>
       </c>
       <c r="X38">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
         <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39" t="s">
         <v>116</v>
       </c>
-      <c r="F39" t="s">
-        <v>123</v>
-      </c>
       <c r="G39" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="H39" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I39" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="J39">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="K39">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -3933,13 +3831,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="P39">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -3951,51 +3849,51 @@
         <v>90</v>
       </c>
       <c r="U39">
-        <v>13838</v>
+        <v>15</v>
       </c>
       <c r="V39" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="W39">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="X39">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
+        <v>115</v>
+      </c>
+      <c r="G40" t="s">
+        <v>132</v>
+      </c>
+      <c r="H40" t="s">
+        <v>134</v>
+      </c>
+      <c r="I40" t="s">
+        <v>146</v>
+      </c>
+      <c r="J40">
         <v>32</v>
       </c>
-      <c r="C40" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" t="s">
-        <v>78</v>
-      </c>
-      <c r="E40" t="s">
-        <v>117</v>
-      </c>
-      <c r="F40" t="s">
-        <v>123</v>
-      </c>
-      <c r="G40" t="s">
-        <v>126</v>
-      </c>
-      <c r="H40" t="s">
-        <v>150</v>
-      </c>
-      <c r="I40" t="s">
-        <v>151</v>
-      </c>
-      <c r="J40">
-        <v>12</v>
-      </c>
       <c r="K40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4007,13 +3905,13 @@
         <v>0</v>
       </c>
       <c r="O40" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="P40">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q40">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -4025,51 +3923,51 @@
         <v>90</v>
       </c>
       <c r="U40">
-        <v>10683</v>
+        <v>10142</v>
       </c>
       <c r="V40" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="W40">
         <v>2</v>
       </c>
       <c r="X40">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E41" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="F41" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G41" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="H41" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I41" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="J41">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4081,13 +3979,13 @@
         <v>0</v>
       </c>
       <c r="O41" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="P41">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q41">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -4099,69 +3997,69 @@
         <v>90</v>
       </c>
       <c r="U41">
-        <v>14469</v>
+        <v>15441</v>
       </c>
       <c r="V41" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="W41">
         <v>2</v>
       </c>
       <c r="X41">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B42" t="s">
         <v>32</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E42" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="F42" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G42" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="H42" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I42" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="J42">
         <v>10</v>
       </c>
       <c r="K42">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N42">
         <v>0</v>
       </c>
       <c r="O42" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="P42">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="Q42">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -4173,51 +4071,51 @@
         <v>90</v>
       </c>
       <c r="U42">
-        <v>10153</v>
+        <v>11112</v>
       </c>
       <c r="V42" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="W42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X42">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s">
         <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E43" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="F43" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G43" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="H43" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I43" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4229,13 +4127,13 @@
         <v>0</v>
       </c>
       <c r="O43" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="P43">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q43">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -4247,21 +4145,21 @@
         <v>90</v>
       </c>
       <c r="U43">
-        <v>15134</v>
+        <v>4131</v>
       </c>
       <c r="V43" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="W43">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X43">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B44" t="s">
         <v>32</v>
@@ -4270,28 +4168,28 @@
         <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="F44" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G44" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="H44" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I44" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="J44">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K44">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4303,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="O44" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="P44">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="Q44">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -4321,51 +4219,51 @@
         <v>90</v>
       </c>
       <c r="U44">
-        <v>16963</v>
+        <v>10189</v>
       </c>
       <c r="V44" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="W44">
         <v>2</v>
       </c>
       <c r="X44">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C45" t="s">
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E45" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="F45" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G45" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="H45" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I45" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="J45">
         <v>6</v>
       </c>
       <c r="K45">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -4377,14 +4275,14 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="P45">
+        <v>8</v>
+      </c>
+      <c r="Q45">
         <v>14</v>
       </c>
-      <c r="Q45">
-        <v>20</v>
-      </c>
       <c r="R45">
         <v>0</v>
       </c>
@@ -4395,48 +4293,48 @@
         <v>90</v>
       </c>
       <c r="U45">
-        <v>15134</v>
+        <v>10334</v>
       </c>
       <c r="V45" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="W45">
         <v>2</v>
       </c>
       <c r="X45">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C46" t="s">
         <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E46" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="F46" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G46" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="H46" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I46" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K46">
         <v>11</v>
@@ -4445,44 +4343,1227 @@
         <v>0</v>
       </c>
       <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>181</v>
+      </c>
+      <c r="P46">
+        <v>12</v>
+      </c>
+      <c r="Q46">
+        <v>18</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>90</v>
+      </c>
+      <c r="U46">
+        <v>10334</v>
+      </c>
+      <c r="V46" t="s">
+        <v>205</v>
+      </c>
+      <c r="W46">
+        <v>2</v>
+      </c>
+      <c r="X46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" t="s">
+        <v>73</v>
+      </c>
+      <c r="E47" t="s">
+        <v>106</v>
+      </c>
+      <c r="F47" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" t="s">
+        <v>119</v>
+      </c>
+      <c r="H47" t="s">
+        <v>134</v>
+      </c>
+      <c r="I47" t="s">
+        <v>135</v>
+      </c>
+      <c r="J47">
+        <v>6</v>
+      </c>
+      <c r="K47">
+        <v>58</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>182</v>
+      </c>
+      <c r="P47">
+        <v>68</v>
+      </c>
+      <c r="Q47">
+        <v>110</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>90</v>
+      </c>
+      <c r="U47">
+        <v>10334</v>
+      </c>
+      <c r="V47" t="s">
+        <v>205</v>
+      </c>
+      <c r="W47">
+        <v>9</v>
+      </c>
+      <c r="X47">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24">
+      <c r="A48" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" t="s">
+        <v>74</v>
+      </c>
+      <c r="E48" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" t="s">
+        <v>115</v>
+      </c>
+      <c r="G48" t="s">
+        <v>119</v>
+      </c>
+      <c r="H48" t="s">
+        <v>134</v>
+      </c>
+      <c r="I48" t="s">
+        <v>135</v>
+      </c>
+      <c r="J48">
+        <v>6</v>
+      </c>
+      <c r="K48">
+        <v>3</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>164</v>
+      </c>
+      <c r="P48">
+        <v>4</v>
+      </c>
+      <c r="Q48">
+        <v>10</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>90</v>
+      </c>
+      <c r="U48">
+        <v>10334</v>
+      </c>
+      <c r="V48" t="s">
+        <v>205</v>
+      </c>
+      <c r="W48">
+        <v>2</v>
+      </c>
+      <c r="X48">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24">
+      <c r="A49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" t="s">
+        <v>108</v>
+      </c>
+      <c r="F49" t="s">
+        <v>115</v>
+      </c>
+      <c r="G49" t="s">
+        <v>120</v>
+      </c>
+      <c r="H49" t="s">
+        <v>134</v>
+      </c>
+      <c r="I49" t="s">
+        <v>141</v>
+      </c>
+      <c r="J49">
+        <v>20</v>
+      </c>
+      <c r="K49">
+        <v>79</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" t="s">
+        <v>183</v>
+      </c>
+      <c r="P49">
+        <v>80</v>
+      </c>
+      <c r="Q49">
+        <v>100</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>90</v>
+      </c>
+      <c r="U49">
+        <v>3527</v>
+      </c>
+      <c r="V49" t="s">
+        <v>206</v>
+      </c>
+      <c r="W49">
+        <v>2</v>
+      </c>
+      <c r="X49">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24">
+      <c r="A50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" t="s">
+        <v>109</v>
+      </c>
+      <c r="F50" t="s">
+        <v>115</v>
+      </c>
+      <c r="G50" t="s">
+        <v>120</v>
+      </c>
+      <c r="H50" t="s">
+        <v>134</v>
+      </c>
+      <c r="I50" t="s">
+        <v>142</v>
+      </c>
+      <c r="J50">
+        <v>10</v>
+      </c>
+      <c r="K50">
+        <v>23</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50" t="s">
+        <v>184</v>
+      </c>
+      <c r="P50">
         <v>24</v>
       </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46" t="s">
+      <c r="Q50">
+        <v>34</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>90</v>
+      </c>
+      <c r="U50">
+        <v>15134</v>
+      </c>
+      <c r="V50" t="s">
+        <v>197</v>
+      </c>
+      <c r="W50">
+        <v>2</v>
+      </c>
+      <c r="X50">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24">
+      <c r="A51" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" t="s">
+        <v>51</v>
+      </c>
+      <c r="E51" t="s">
+        <v>84</v>
+      </c>
+      <c r="F51" t="s">
+        <v>116</v>
+      </c>
+      <c r="G51" t="s">
+        <v>120</v>
+      </c>
+      <c r="H51" t="s">
+        <v>134</v>
+      </c>
+      <c r="I51" t="s">
+        <v>138</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51" t="s">
+        <v>151</v>
+      </c>
+      <c r="P51">
+        <v>10</v>
+      </c>
+      <c r="Q51">
+        <v>15</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>90</v>
+      </c>
+      <c r="U51">
+        <v>15</v>
+      </c>
+      <c r="V51" t="s">
+        <v>192</v>
+      </c>
+      <c r="W51">
+        <v>15</v>
+      </c>
+      <c r="X51">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24">
+      <c r="A52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" t="s">
+        <v>110</v>
+      </c>
+      <c r="F52" t="s">
+        <v>115</v>
+      </c>
+      <c r="G52" t="s">
+        <v>133</v>
+      </c>
+      <c r="H52" t="s">
+        <v>134</v>
+      </c>
+      <c r="I52" t="s">
+        <v>147</v>
+      </c>
+      <c r="J52">
+        <v>24</v>
+      </c>
+      <c r="K52">
+        <v>16</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52" t="s">
+        <v>185</v>
+      </c>
+      <c r="P52">
+        <v>18</v>
+      </c>
+      <c r="Q52">
+        <v>42</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>90</v>
+      </c>
+      <c r="U52">
+        <v>10124</v>
+      </c>
+      <c r="V52" t="s">
+        <v>207</v>
+      </c>
+      <c r="W52">
+        <v>2</v>
+      </c>
+      <c r="X52">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24">
+      <c r="A53" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" t="s">
+        <v>115</v>
+      </c>
+      <c r="G53" t="s">
+        <v>125</v>
+      </c>
+      <c r="H53" t="s">
+        <v>134</v>
+      </c>
+      <c r="I53" t="s">
+        <v>142</v>
+      </c>
+      <c r="J53">
+        <v>10</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>60</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53" t="s">
+        <v>186</v>
+      </c>
+      <c r="P53">
+        <v>66</v>
+      </c>
+      <c r="Q53">
+        <v>96</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>90</v>
+      </c>
+      <c r="U53">
+        <v>11112</v>
+      </c>
+      <c r="V53" t="s">
+        <v>196</v>
+      </c>
+      <c r="W53">
+        <v>4</v>
+      </c>
+      <c r="X53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24">
+      <c r="A54" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" t="s">
+        <v>45</v>
+      </c>
+      <c r="D54" t="s">
+        <v>51</v>
+      </c>
+      <c r="E54" t="s">
+        <v>84</v>
+      </c>
+      <c r="F54" t="s">
+        <v>116</v>
+      </c>
+      <c r="G54" t="s">
+        <v>120</v>
+      </c>
+      <c r="H54" t="s">
+        <v>134</v>
+      </c>
+      <c r="I54" t="s">
+        <v>138</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54" t="s">
+        <v>151</v>
+      </c>
+      <c r="P54">
+        <v>10</v>
+      </c>
+      <c r="Q54">
+        <v>15</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>90</v>
+      </c>
+      <c r="U54">
+        <v>15</v>
+      </c>
+      <c r="V54" t="s">
+        <v>192</v>
+      </c>
+      <c r="W54">
+        <v>15</v>
+      </c>
+      <c r="X54">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24">
+      <c r="A55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G55" t="s">
+        <v>120</v>
+      </c>
+      <c r="H55" t="s">
+        <v>134</v>
+      </c>
+      <c r="I55" t="s">
+        <v>137</v>
+      </c>
+      <c r="J55">
+        <v>12</v>
+      </c>
+      <c r="K55">
+        <v>-4</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55" t="s">
+        <v>187</v>
+      </c>
+      <c r="P55">
+        <v>4</v>
+      </c>
+      <c r="Q55">
+        <v>12</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>90</v>
+      </c>
+      <c r="U55">
+        <v>13921</v>
+      </c>
+      <c r="V55" t="s">
+        <v>208</v>
+      </c>
+      <c r="W55">
+        <v>1</v>
+      </c>
+      <c r="X55">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24">
+      <c r="A56" t="s">
+        <v>26</v>
+      </c>
+      <c r="B56" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" t="s">
+        <v>46</v>
+      </c>
+      <c r="D56" t="s">
+        <v>60</v>
+      </c>
+      <c r="E56" t="s">
+        <v>93</v>
+      </c>
+      <c r="F56" t="s">
+        <v>115</v>
+      </c>
+      <c r="G56" t="s">
+        <v>125</v>
+      </c>
+      <c r="H56" t="s">
+        <v>134</v>
+      </c>
+      <c r="I56" t="s">
+        <v>142</v>
+      </c>
+      <c r="J56">
+        <v>10</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>10</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56" t="s">
+        <v>141</v>
+      </c>
+      <c r="P56">
+        <v>22</v>
+      </c>
+      <c r="Q56">
+        <v>32</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>90</v>
+      </c>
+      <c r="U56">
+        <v>11112</v>
+      </c>
+      <c r="V56" t="s">
+        <v>196</v>
+      </c>
+      <c r="W56">
+        <v>3</v>
+      </c>
+      <c r="X56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24">
+      <c r="A57" t="s">
+        <v>28</v>
+      </c>
+      <c r="B57" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57" t="s">
+        <v>46</v>
+      </c>
+      <c r="D57" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" t="s">
+        <v>112</v>
+      </c>
+      <c r="F57" t="s">
+        <v>115</v>
+      </c>
+      <c r="G57" t="s">
+        <v>119</v>
+      </c>
+      <c r="H57" t="s">
+        <v>134</v>
+      </c>
+      <c r="I57" t="s">
+        <v>135</v>
+      </c>
+      <c r="J57">
+        <v>6</v>
+      </c>
+      <c r="K57">
+        <v>17</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57" t="s">
+        <v>184</v>
+      </c>
+      <c r="P57">
+        <v>18</v>
+      </c>
+      <c r="Q57">
+        <v>24</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>90</v>
+      </c>
+      <c r="U57">
+        <v>10334</v>
+      </c>
+      <c r="V57" t="s">
         <v>205</v>
       </c>
-      <c r="P46">
+      <c r="W57">
+        <v>2</v>
+      </c>
+      <c r="X57">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24">
+      <c r="A58" t="s">
+        <v>28</v>
+      </c>
+      <c r="B58" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" t="s">
+        <v>71</v>
+      </c>
+      <c r="E58" t="s">
+        <v>104</v>
+      </c>
+      <c r="F58" t="s">
+        <v>115</v>
+      </c>
+      <c r="G58" t="s">
+        <v>119</v>
+      </c>
+      <c r="H58" t="s">
+        <v>134</v>
+      </c>
+      <c r="I58" t="s">
+        <v>135</v>
+      </c>
+      <c r="J58">
+        <v>6</v>
+      </c>
+      <c r="K58">
+        <v>19</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58" t="s">
+        <v>188</v>
+      </c>
+      <c r="P58">
+        <v>20</v>
+      </c>
+      <c r="Q58">
+        <v>32</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>90</v>
+      </c>
+      <c r="U58">
+        <v>10334</v>
+      </c>
+      <c r="V58" t="s">
+        <v>205</v>
+      </c>
+      <c r="W58">
+        <v>3</v>
+      </c>
+      <c r="X58">
         <v>36</v>
       </c>
-      <c r="Q46">
-        <v>48</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <v>90</v>
-      </c>
-      <c r="U46">
-        <v>6424</v>
-      </c>
-      <c r="V46" t="s">
-        <v>209</v>
-      </c>
-      <c r="W46">
+    </row>
+    <row r="59" spans="1:24">
+      <c r="A59" t="s">
+        <v>26</v>
+      </c>
+      <c r="B59" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" t="s">
+        <v>51</v>
+      </c>
+      <c r="E59" t="s">
+        <v>84</v>
+      </c>
+      <c r="F59" t="s">
+        <v>116</v>
+      </c>
+      <c r="G59" t="s">
+        <v>120</v>
+      </c>
+      <c r="H59" t="s">
+        <v>134</v>
+      </c>
+      <c r="I59" t="s">
+        <v>138</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59" t="s">
+        <v>151</v>
+      </c>
+      <c r="P59">
+        <v>10</v>
+      </c>
+      <c r="Q59">
+        <v>15</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>90</v>
+      </c>
+      <c r="U59">
+        <v>15</v>
+      </c>
+      <c r="V59" t="s">
+        <v>192</v>
+      </c>
+      <c r="W59">
+        <v>15</v>
+      </c>
+      <c r="X59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24">
+      <c r="A60" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" t="s">
+        <v>47</v>
+      </c>
+      <c r="D60" t="s">
+        <v>80</v>
+      </c>
+      <c r="E60" t="s">
+        <v>113</v>
+      </c>
+      <c r="F60" t="s">
+        <v>114</v>
+      </c>
+      <c r="G60" t="s">
+        <v>118</v>
+      </c>
+      <c r="H60" t="s">
+        <v>134</v>
+      </c>
+      <c r="I60" t="s">
+        <v>136</v>
+      </c>
+      <c r="J60">
+        <v>8</v>
+      </c>
+      <c r="K60">
+        <v>43</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60" t="s">
+        <v>189</v>
+      </c>
+      <c r="P60">
+        <v>52</v>
+      </c>
+      <c r="Q60">
+        <v>84</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>90</v>
+      </c>
+      <c r="U60">
+        <v>15441</v>
+      </c>
+      <c r="V60" t="s">
+        <v>190</v>
+      </c>
+      <c r="W60">
+        <v>6</v>
+      </c>
+      <c r="X60">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24">
+      <c r="A61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" t="s">
+        <v>47</v>
+      </c>
+      <c r="D61" t="s">
+        <v>53</v>
+      </c>
+      <c r="E61" t="s">
+        <v>86</v>
+      </c>
+      <c r="F61" t="s">
+        <v>116</v>
+      </c>
+      <c r="G61" t="s">
+        <v>120</v>
+      </c>
+      <c r="H61" t="s">
+        <v>134</v>
+      </c>
+      <c r="I61" t="s">
+        <v>138</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61">
         <v>4</v>
       </c>
-      <c r="X46">
-        <v>82</v>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61" t="s">
+        <v>151</v>
+      </c>
+      <c r="P61">
+        <v>5</v>
+      </c>
+      <c r="Q61">
+        <v>10</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>90</v>
+      </c>
+      <c r="U61">
+        <v>15</v>
+      </c>
+      <c r="V61" t="s">
+        <v>192</v>
+      </c>
+      <c r="W61">
+        <v>6</v>
+      </c>
+      <c r="X61">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24">
+      <c r="A62" t="s">
+        <v>26</v>
+      </c>
+      <c r="B62" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" t="s">
+        <v>47</v>
+      </c>
+      <c r="D62" t="s">
+        <v>51</v>
+      </c>
+      <c r="E62" t="s">
+        <v>84</v>
+      </c>
+      <c r="F62" t="s">
+        <v>116</v>
+      </c>
+      <c r="G62" t="s">
+        <v>120</v>
+      </c>
+      <c r="H62" t="s">
+        <v>134</v>
+      </c>
+      <c r="I62" t="s">
+        <v>138</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62" t="s">
+        <v>151</v>
+      </c>
+      <c r="P62">
+        <v>10</v>
+      </c>
+      <c r="Q62">
+        <v>15</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>90</v>
+      </c>
+      <c r="U62">
+        <v>15</v>
+      </c>
+      <c r="V62" t="s">
+        <v>192</v>
+      </c>
+      <c r="W62">
+        <v>15</v>
+      </c>
+      <c r="X62">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X46" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="247">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -91,33 +91,33 @@
     <t>BEBIDAS</t>
   </si>
   <si>
+    <t>MERCEARIA</t>
+  </si>
+  <si>
+    <t>PERFUMARIA E LIMPEZA</t>
+  </si>
+  <si>
     <t>PERECIVEIS</t>
   </si>
   <si>
-    <t>MERCEARIA</t>
-  </si>
-  <si>
     <t>PRODUTOS PET</t>
   </si>
   <si>
-    <t>PERFUMARIA E LIMPEZA</t>
-  </si>
-  <si>
     <t>NICOLAS AUGUSTO P. BORGES</t>
   </si>
   <si>
+    <t>NIDAL TUBASI</t>
+  </si>
+  <si>
+    <t>WETER SONNENFELDET</t>
+  </si>
+  <si>
+    <t>JOAO BATISTA</t>
+  </si>
+  <si>
     <t>SANDRO MARTINS VIANNA</t>
   </si>
   <si>
-    <t>NIDAL TUBASI</t>
-  </si>
-  <si>
-    <t>WETER SONNENFELDET</t>
-  </si>
-  <si>
-    <t>JOAO BATISTA</t>
-  </si>
-  <si>
     <t>001</t>
   </si>
   <si>
@@ -166,15 +166,15 @@
     <t>806</t>
   </si>
   <si>
-    <t>6783</t>
-  </si>
-  <si>
     <t>15765</t>
   </si>
   <si>
     <t>840</t>
   </si>
   <si>
+    <t>2879</t>
+  </si>
+  <si>
     <t>15764</t>
   </si>
   <si>
@@ -190,90 +190,111 @@
     <t>15762</t>
   </si>
   <si>
+    <t>17160</t>
+  </si>
+  <si>
     <t>37075</t>
   </si>
   <si>
     <t>795</t>
   </si>
   <si>
-    <t>2974</t>
-  </si>
-  <si>
-    <t>1466</t>
-  </si>
-  <si>
-    <t>2096</t>
-  </si>
-  <si>
-    <t>11245</t>
-  </si>
-  <si>
-    <t>22703</t>
+    <t>960</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>21559</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>660</t>
+  </si>
+  <si>
+    <t>1564</t>
+  </si>
+  <si>
+    <t>1620</t>
+  </si>
+  <si>
+    <t>1695</t>
+  </si>
+  <si>
+    <t>3252</t>
+  </si>
+  <si>
+    <t>3289</t>
+  </si>
+  <si>
+    <t>3704</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>4554</t>
+  </si>
+  <si>
+    <t>6781</t>
+  </si>
+  <si>
+    <t>3994</t>
   </si>
   <si>
     <t>49</t>
   </si>
   <si>
-    <t>3704</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>33468</t>
-  </si>
-  <si>
     <t>386</t>
   </si>
   <si>
+    <t>1242</t>
+  </si>
+  <si>
+    <t>1977</t>
+  </si>
+  <si>
+    <t>2722</t>
+  </si>
+  <si>
     <t>3011</t>
   </si>
   <si>
-    <t>5435</t>
-  </si>
-  <si>
-    <t>6704</t>
-  </si>
-  <si>
-    <t>8806</t>
-  </si>
-  <si>
-    <t>9281</t>
+    <t>3092</t>
   </si>
   <si>
     <t>13123</t>
   </si>
   <si>
-    <t>15295</t>
-  </si>
-  <si>
     <t>2960</t>
   </si>
   <si>
-    <t>21250</t>
-  </si>
-  <si>
-    <t>4205</t>
-  </si>
-  <si>
     <t>812</t>
   </si>
   <si>
+    <t>21553</t>
+  </si>
+  <si>
+    <t>2760</t>
+  </si>
+  <si>
     <t>ENERG MONSTER LT 473ML MANGO LOCO</t>
   </si>
   <si>
     <t>REFRIG FANTA LARANJA PET 2L</t>
   </si>
   <si>
-    <t>LEITE UHT TIROL C TAMP INT 1L</t>
-  </si>
-  <si>
     <t>CESTA BASICA PEQ</t>
   </si>
   <si>
     <t>REFRIG PEPSI PET 3L</t>
   </si>
   <si>
+    <t>MASSA C OVOS ISABELA 500G ESPAGUETE</t>
+  </si>
+  <si>
     <t>CESTA BASICA MED</t>
   </si>
   <si>
@@ -289,135 +310,186 @@
     <t>CESTA BASICA GRD</t>
   </si>
   <si>
+    <t>DESINF AQUAFAST 2L CHA BRANCO</t>
+  </si>
+  <si>
     <t>FARINHA TAPIOCA DINDA 400G TRAD</t>
   </si>
   <si>
     <t>REFRIG COCA COLA PET 2L ZERO</t>
   </si>
   <si>
-    <t>ACUCAR DEMERARA UNIAO 1KG</t>
-  </si>
-  <si>
-    <t>BISC RECH NESTLE NEGRESCO 90G CHOC</t>
-  </si>
-  <si>
-    <t>ARROZ BCO SANO T1 2K</t>
-  </si>
-  <si>
-    <t>GOIABADA STELLA KG</t>
-  </si>
-  <si>
-    <t>RACAO DODOG ORIG ALL DAY 5KG</t>
+    <t>OLEO COCO NUTRISANTI 200ML</t>
+  </si>
+  <si>
+    <t>ARROZ BCO REQUINTE TP1 2KG</t>
+  </si>
+  <si>
+    <t>PANO SARJA PANOSUL 45X75CM</t>
+  </si>
+  <si>
+    <t>GATORADE ZERO 350ML FTAS SILVESTRES</t>
+  </si>
+  <si>
+    <t>SUCO KAPO TP 200ML FRUTAS CITRICAS</t>
+  </si>
+  <si>
+    <t>BISC SALG TUCS 100G TRAD</t>
+  </si>
+  <si>
+    <t>BISC SORT DOMELLY JOCE 300G</t>
+  </si>
+  <si>
+    <t>MARSHMALLOWS FOFS 220G TWIST COLORIDO</t>
+  </si>
+  <si>
+    <t>SALG OBBA 100G CEBOLA E SALSA</t>
+  </si>
+  <si>
+    <t>SALG OBBA 100G PRESUNTO</t>
+  </si>
+  <si>
+    <t>MIST P BOLO APTI 400G CHOC</t>
+  </si>
+  <si>
+    <t>CERV BRAHMA CHOPP GF 1L RETORNAVEL</t>
+  </si>
+  <si>
+    <t>CAPA RODO PANOSUL 35X50CM SORTIDO</t>
+  </si>
+  <si>
+    <t>LEITE UHT ELEGE INT 1L</t>
+  </si>
+  <si>
+    <t>RACAO DOG CHOW SH 85G AD CAR ARROZ</t>
   </si>
   <si>
     <t>AGUA MIN FLORESTA PET 500ML S GAS</t>
   </si>
   <si>
-    <t>MIST P BOLO APTI 400G CHOC</t>
-  </si>
-  <si>
-    <t>CERV BRAHMA CHOPP GF 1L RETORNAVEL</t>
-  </si>
-  <si>
-    <t>MOLHO TOMATE HEINZ SH 240G C PEDACOS</t>
-  </si>
-  <si>
     <t>ENERG MONSTER LT 473ML ABSOLUT ZERO</t>
   </si>
   <si>
+    <t>CHOC BARRA NEUGEBAUER 80G BCO</t>
+  </si>
+  <si>
+    <t>TURRON Y MANI ARCOR 25G</t>
+  </si>
+  <si>
+    <t>FARINHA TRIGO PANFACIL TP1 1KG</t>
+  </si>
+  <si>
     <t>AVEIA FLOCOS FINOS NATURALE 1KG</t>
   </si>
   <si>
-    <t>DESINF GIRANDO SOL 2L LAVANDA</t>
-  </si>
-  <si>
-    <t>LAVA ROUPA LIQ GIRANDO SOL FR 2L COCO</t>
-  </si>
-  <si>
-    <t>AGUA SANIT GIRANDO SOL 2L</t>
-  </si>
-  <si>
-    <t>DESINF GIRANDO SOL 2L JASMIM</t>
+    <t>MOSTARDA ODERICH TRADICIONAL 190G BISNAGA</t>
   </si>
   <si>
     <t>BATATA PALHA YOKI TRAD L105P90 105G</t>
   </si>
   <si>
-    <t>CALDO MAGGI 57G COSTELA</t>
-  </si>
-  <si>
     <t>ACHOC TODDY PT 370G ORIGINAL</t>
   </si>
   <si>
-    <t>MOSTARDA MOSTARDOG BD 1K</t>
-  </si>
-  <si>
-    <t>AMAC GIRANDO SOL 2L LILAS</t>
-  </si>
-  <si>
     <t>REFRIG FANTA UVA PET 2L</t>
   </si>
   <si>
+    <t>PANO PANOSUL FELPUDO ESTAMP 38X63CM</t>
+  </si>
+  <si>
+    <t>FARINHA TRIGO NORDESTE 5KG</t>
+  </si>
+  <si>
     <t>L</t>
   </si>
   <si>
+    <t>I</t>
+  </si>
+  <si>
     <t>M</t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
     <t>05/10/2024</t>
   </si>
   <si>
     <t>19/10/2024</t>
   </si>
   <si>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>16/12/2024</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>18/10/2024</t>
+  </si>
+  <si>
+    <t>25/10/2024</t>
+  </si>
+  <si>
+    <t>04/12/2024</t>
+  </si>
+  <si>
+    <t>09/10/2024</t>
+  </si>
+  <si>
+    <t>15/10/2024</t>
+  </si>
+  <si>
+    <t>14/11/2024</t>
+  </si>
+  <si>
+    <t>18/11/2024</t>
+  </si>
+  <si>
+    <t>21/11/2024</t>
+  </si>
+  <si>
+    <t>23/12/2024</t>
+  </si>
+  <si>
+    <t>31/12/2024</t>
+  </si>
+  <si>
+    <t>23/09/2024</t>
+  </si>
+  <si>
     <t>26/04/2025</t>
   </si>
   <si>
-    <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>21/10/2024</t>
-  </si>
-  <si>
-    <t>07/04/2026</t>
-  </si>
-  <si>
-    <t>24/02/2026</t>
-  </si>
-  <si>
-    <t>18/10/2024</t>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>07/11/2024</t>
+  </si>
+  <si>
+    <t>29/11/2024</t>
+  </si>
+  <si>
+    <t>13/12/2024</t>
   </si>
   <si>
     <t>18/12/2024</t>
   </si>
   <si>
-    <t>12/11/2024</t>
-  </si>
-  <si>
-    <t>04/12/2024</t>
-  </si>
-  <si>
-    <t>11/06/2025</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>31/12/2024</t>
-  </si>
-  <si>
-    <t>23/09/2024</t>
-  </si>
-  <si>
-    <t>06/08/2025</t>
+    <t>19/12/2024</t>
   </si>
   <si>
     <t>17/12/2024</t>
   </si>
   <si>
+    <t>14/12/2024</t>
+  </si>
+  <si>
     <t>Ativo</t>
   </si>
   <si>
@@ -427,211 +499,253 @@
     <t>8</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>32</t>
+    <t>64</t>
+  </si>
+  <si>
+    <t>50</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>293</t>
-  </si>
-  <si>
-    <t>4199</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>295</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>1382</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>1779</t>
-  </si>
-  <si>
-    <t>1019</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>451</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>1488</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>1504</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>49,54</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>660</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>12100</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>789</t>
-  </si>
-  <si>
-    <t>1314</t>
-  </si>
-  <si>
-    <t>1815</t>
-  </si>
-  <si>
-    <t>1629</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>160</t>
+    <t>1379</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>1773</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>453</t>
+  </si>
+  <si>
+    <t>1503</t>
+  </si>
+  <si>
+    <t>612</t>
+  </si>
+  <si>
+    <t>1131</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>655</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>391</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>652</t>
+  </si>
+  <si>
+    <t>1464</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>787</t>
+  </si>
+  <si>
+    <t>1306</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>1816</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>2753</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>33528</t>
+  </si>
+  <si>
+    <t>159</t>
   </si>
   <si>
     <t>200</t>
   </si>
   <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>597</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>495</t>
+    <t>3321</t>
+  </si>
+  <si>
+    <t>969</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>483</t>
+  </si>
+  <si>
+    <t>994</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>524</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>492</t>
+  </si>
+  <si>
+    <t>76</t>
   </si>
   <si>
     <t>SPAL IND BRAS BEBIDAS AS</t>
   </si>
   <si>
-    <t>LATICINIOS TIROL LTDA.</t>
-  </si>
-  <si>
     <t>SUPERMERCADO BAKLIZI LTDA</t>
   </si>
   <si>
     <t>CRBS AS CDD PELOTAS</t>
   </si>
   <si>
+    <t>M DIAS BRANCO S.A IND E COM DE ALIMENTOS</t>
+  </si>
+  <si>
     <t>BARAO - INDUSTRIA E COMERCIO DE ERVA MATE E CHAS S.A.</t>
   </si>
   <si>
+    <t>AQUAFAST PROD LIMPEZA/HIGIENE LTDA</t>
+  </si>
+  <si>
     <t>ROCHA E FILHOS LTDA</t>
   </si>
   <si>
-    <t>ATACADAO S.A.</t>
+    <t>SANTI INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>GENESIO CEOLIN E CIA LTDA</t>
+  </si>
+  <si>
+    <t>HIPER TEXTIL LTDA</t>
+  </si>
+  <si>
+    <t>CILASI ALIMENTOS S E A.</t>
+  </si>
+  <si>
+    <t>REDOL ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>FLORESTAL ALIMENTOS S.A.</t>
+  </si>
+  <si>
+    <t>FITOS ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>APTI ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
   </si>
   <si>
     <t>NESTLE BRASIL LTDA</t>
   </si>
   <si>
-    <t>FERRUCCI E MIRANDA LTDA-EPP</t>
-  </si>
-  <si>
-    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
-  </si>
-  <si>
-    <t>NUTRISUL ALIMENTOS LTDA</t>
-  </si>
-  <si>
     <t>AGUAS MINERAIS SARANDI LTDA</t>
   </si>
   <si>
-    <t>APTI ALIMENTOS LTDA</t>
+    <t>VONPAR ALIMENTOS S.A</t>
   </si>
   <si>
     <t>KASADOCE DISTRIBUIDORA DE ALIMENTOS LTDA</t>
   </si>
   <si>
+    <t>MOINHO ESTRELA LTDA</t>
+  </si>
+  <si>
     <t>NAT CEREAIS E ALIMENTOS LTDA</t>
   </si>
   <si>
-    <t>IND COM PROD LIMP GIRANDO SOL LTDA</t>
+    <t>CONSERVAS ODERICH SA</t>
   </si>
   <si>
     <t>FABIANO ZAFFALON E CIA LTDA</t>
@@ -640,7 +754,7 @@
     <t>PEPSICO DO BRASIL LTDA</t>
   </si>
   <si>
-    <t>ADI-GEL IND. E COM. DE PROD. ALIMENT.</t>
+    <t>MOINHO DO NORDESTE SA</t>
   </si>
 </sst>
 </file>
@@ -972,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -1063,19 +1177,19 @@
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H2" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I2" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -1093,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="P2">
         <v>6</v>
@@ -1114,13 +1228,13 @@
         <v>15441</v>
       </c>
       <c r="V2" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="W2">
         <v>2</v>
       </c>
       <c r="X2">
-        <v>95</v>
+        <v>94.17</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1137,25 +1251,25 @@
         <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F3" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="H3" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I3" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="J3">
         <v>8</v>
       </c>
       <c r="K3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1167,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="P3">
         <v>32</v>
@@ -1188,13 +1302,13 @@
         <v>15441</v>
       </c>
       <c r="V3" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="W3">
         <v>4</v>
       </c>
       <c r="X3">
-        <v>320</v>
+        <v>319.12</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -1211,25 +1325,25 @@
         <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F4" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G4" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="H4" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I4" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="J4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>456</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1241,13 +1355,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="P4">
-        <v>480</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1259,51 +1373,51 @@
         <v>90</v>
       </c>
       <c r="U4">
-        <v>15208</v>
+        <v>15</v>
       </c>
       <c r="V4" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="W4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>3801</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F5" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G5" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="H5" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I5" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1315,13 +1429,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>156</v>
       </c>
       <c r="Q5">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1333,24 +1447,24 @@
         <v>90</v>
       </c>
       <c r="U5">
-        <v>15</v>
+        <v>9638</v>
       </c>
       <c r="V5" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="X5">
-        <v>58</v>
+        <v>216.25</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
@@ -1359,25 +1473,25 @@
         <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F6" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G6" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="H6" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I6" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K6">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1389,13 +1503,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="P6">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="Q6">
-        <v>240</v>
+        <v>72</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1407,24 +1521,24 @@
         <v>90</v>
       </c>
       <c r="U6">
-        <v>9638</v>
+        <v>7995</v>
       </c>
       <c r="V6" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="W6">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="X6">
-        <v>226</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
@@ -1433,19 +1547,19 @@
         <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F7" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G7" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H7" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I7" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1463,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="P7">
         <v>10</v>
@@ -1484,7 +1598,7 @@
         <v>15</v>
       </c>
       <c r="V7" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="W7">
         <v>15</v>
@@ -1495,31 +1609,31 @@
     </row>
     <row r="8" spans="1:24">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G8" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H8" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I8" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1537,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="P8">
         <v>10</v>
@@ -1558,7 +1672,7 @@
         <v>15</v>
       </c>
       <c r="V8" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="W8">
         <v>15</v>
@@ -1569,10 +1683,10 @@
     </row>
     <row r="9" spans="1:24">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>35</v>
@@ -1581,25 +1695,25 @@
         <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G9" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H9" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I9" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="J9">
         <v>30</v>
       </c>
       <c r="K9">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1611,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="P9">
         <v>18</v>
@@ -1632,7 +1746,7 @@
         <v>6798</v>
       </c>
       <c r="V9" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="W9">
         <v>2</v>
@@ -1655,25 +1769,25 @@
         <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G10" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H10" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I10" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
       <c r="K10">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1685,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="P10">
         <v>198</v>
@@ -1706,13 +1820,13 @@
         <v>15441</v>
       </c>
       <c r="V10" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="W10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="X10">
-        <v>87</v>
+        <v>86.33</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1729,25 +1843,25 @@
         <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G11" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H11" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I11" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="J11">
         <v>6</v>
       </c>
       <c r="K11">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1759,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="P11">
         <v>114</v>
@@ -1780,13 +1894,13 @@
         <v>15441</v>
       </c>
       <c r="V11" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="W11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X11">
-        <v>128</v>
+        <v>127.17</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1803,19 +1917,19 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G12" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H12" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I12" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -1833,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="P12">
         <v>42</v>
@@ -1854,21 +1968,21 @@
         <v>15441</v>
       </c>
       <c r="V12" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="W12">
         <v>7</v>
       </c>
       <c r="X12">
-        <v>95</v>
+        <v>94.17</v>
       </c>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
@@ -1877,19 +1991,19 @@
         <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F13" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G13" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H13" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I13" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1907,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="P13">
         <v>15</v>
@@ -1928,7 +2042,7 @@
         <v>15</v>
       </c>
       <c r="V13" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1939,31 +2053,31 @@
     </row>
     <row r="14" spans="1:24">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
         <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F14" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G14" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H14" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I14" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1981,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="P14">
         <v>15</v>
@@ -2002,7 +2116,7 @@
         <v>15</v>
       </c>
       <c r="V14" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="W14">
         <v>20</v>
@@ -2016,7 +2130,7 @@
         <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
@@ -2025,25 +2139,25 @@
         <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F15" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G15" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="H15" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I15" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="J15">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2055,13 +2169,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="P15">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -2073,51 +2187,51 @@
         <v>90</v>
       </c>
       <c r="U15">
-        <v>21894</v>
+        <v>3947</v>
       </c>
       <c r="V15" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="W15">
         <v>2</v>
       </c>
       <c r="X15">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:24">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F16" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="G16" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="H16" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I16" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K16">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2129,13 +2243,13 @@
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>67</v>
+        <v>182</v>
       </c>
       <c r="P16">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Q16">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -2147,16 +2261,16 @@
         <v>90</v>
       </c>
       <c r="U16">
-        <v>15441</v>
+        <v>21894</v>
       </c>
       <c r="V16" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X16">
-        <v>87</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2170,28 +2284,28 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G17" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="H17" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I17" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2203,13 +2317,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="P17">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="Q17">
-        <v>42</v>
+        <v>260</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2224,48 +2338,48 @@
         <v>15441</v>
       </c>
       <c r="V17" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="W17">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="X17">
-        <v>128</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="18" spans="1:24">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
         <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="G18" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="H18" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I18" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2277,13 +2391,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="P18">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -2295,16 +2409,16 @@
         <v>90</v>
       </c>
       <c r="U18">
-        <v>15441</v>
+        <v>15</v>
       </c>
       <c r="V18" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="W18">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>95</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2315,31 +2429,31 @@
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F19" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G19" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H19" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I19" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="J19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2351,13 +2465,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="P19">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="Q19">
-        <v>260</v>
+        <v>102</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -2372,214 +2486,214 @@
         <v>15441</v>
       </c>
       <c r="V19" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="W19">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>127</v>
+        <v>86.33</v>
       </c>
     </row>
     <row r="20" spans="1:24">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G20" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H20" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I20" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="J20">
+        <v>8</v>
+      </c>
+      <c r="K20">
+        <v>123</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>185</v>
+      </c>
+      <c r="P20">
+        <v>128</v>
+      </c>
+      <c r="Q20">
+        <v>200</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>90</v>
+      </c>
+      <c r="U20">
+        <v>15441</v>
+      </c>
+      <c r="V20" t="s">
+        <v>221</v>
+      </c>
+      <c r="W20">
         <v>10</v>
       </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>60</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>161</v>
-      </c>
-      <c r="P20">
-        <v>66</v>
-      </c>
-      <c r="Q20">
-        <v>96</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>90</v>
-      </c>
-      <c r="U20">
-        <v>11112</v>
-      </c>
-      <c r="V20" t="s">
-        <v>196</v>
-      </c>
-      <c r="W20">
-        <v>4</v>
-      </c>
       <c r="X20">
-        <v>6</v>
+        <v>319.12</v>
       </c>
     </row>
     <row r="21" spans="1:24">
       <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H21" t="s">
+        <v>158</v>
+      </c>
+      <c r="I21" t="s">
+        <v>160</v>
+      </c>
+      <c r="J21">
+        <v>8</v>
+      </c>
+      <c r="K21">
         <v>26</v>
       </c>
-      <c r="B21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" t="s">
-        <v>116</v>
-      </c>
-      <c r="G21" t="s">
-        <v>120</v>
-      </c>
-      <c r="H21" t="s">
-        <v>134</v>
-      </c>
-      <c r="I21" t="s">
-        <v>138</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="P21">
+        <v>36</v>
+      </c>
+      <c r="Q21">
+        <v>52</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>90</v>
+      </c>
+      <c r="U21">
+        <v>16989</v>
+      </c>
+      <c r="V21" t="s">
+        <v>228</v>
+      </c>
+      <c r="W21">
+        <v>3</v>
+      </c>
+      <c r="X21">
         <v>5</v>
-      </c>
-      <c r="Q21">
-        <v>10</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>90</v>
-      </c>
-      <c r="U21">
-        <v>15</v>
-      </c>
-      <c r="V21" t="s">
-        <v>192</v>
-      </c>
-      <c r="W21">
-        <v>10</v>
-      </c>
-      <c r="X21">
-        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:24">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
         <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G22" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="H22" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I22" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="J22">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="K22">
-        <v>-111</v>
+        <v>41</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="P22">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="Q22">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -2591,90 +2705,90 @@
         <v>90</v>
       </c>
       <c r="U22">
-        <v>15134</v>
+        <v>13087</v>
       </c>
       <c r="V22" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="W22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="23" spans="1:24">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G23" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H23" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I23" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>174</v>
+      </c>
+      <c r="P23">
+        <v>5</v>
+      </c>
+      <c r="Q23">
+        <v>10</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>90</v>
+      </c>
+      <c r="U23">
         <v>15</v>
       </c>
-      <c r="K23">
-        <v>28</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>163</v>
-      </c>
-      <c r="P23">
-        <v>31</v>
-      </c>
-      <c r="Q23">
-        <v>46</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>90</v>
-      </c>
-      <c r="U23">
-        <v>7918</v>
-      </c>
       <c r="V23" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="W23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:24">
@@ -2688,46 +2802,46 @@
         <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F24" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G24" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H24" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I24" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="J24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K24">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="P24">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2739,51 +2853,51 @@
         <v>90</v>
       </c>
       <c r="U24">
-        <v>11112</v>
+        <v>10885</v>
       </c>
       <c r="V24" t="s">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:24">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E25" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F25" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G25" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="H25" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I25" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="J25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K25">
-        <v>6.716</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2795,13 +2909,13 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2813,51 +2927,51 @@
         <v>90</v>
       </c>
       <c r="U25">
-        <v>5894</v>
+        <v>9638</v>
       </c>
       <c r="V25" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="W25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X25">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:24">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E26" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="F26" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G26" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="H26" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I26" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2869,13 +2983,13 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="P26">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="Q26">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -2887,51 +3001,51 @@
         <v>90</v>
       </c>
       <c r="U26">
-        <v>15</v>
+        <v>15441</v>
       </c>
       <c r="V26" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="X26">
-        <v>58</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:24">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E27" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F27" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G27" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="H27" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I27" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2943,13 +3057,13 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="P27">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Q27">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -2961,48 +3075,48 @@
         <v>90</v>
       </c>
       <c r="U27">
-        <v>17077</v>
+        <v>4296</v>
       </c>
       <c r="V27" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X27">
-        <v>419</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:24">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
         <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="F28" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G28" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="H28" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I28" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="J28">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -3011,19 +3125,19 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="N28">
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>142</v>
+        <v>191</v>
       </c>
       <c r="P28">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="Q28">
-        <v>128</v>
+        <v>34</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -3035,21 +3149,21 @@
         <v>90</v>
       </c>
       <c r="U28">
-        <v>11112</v>
+        <v>15886</v>
       </c>
       <c r="V28" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:24">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
@@ -3058,25 +3172,25 @@
         <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E29" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G29" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="H29" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I29" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -3091,13 +3205,13 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="P29">
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -3109,51 +3223,51 @@
         <v>90</v>
       </c>
       <c r="U29">
-        <v>15</v>
+        <v>7493</v>
       </c>
       <c r="V29" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="W29">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="X29">
-        <v>58</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:24">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F30" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="G30" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="H30" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I30" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3165,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="P30">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>116</v>
+        <v>15</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -3183,70 +3297,70 @@
         <v>90</v>
       </c>
       <c r="U30">
-        <v>15441</v>
+        <v>15</v>
       </c>
       <c r="V30" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="X30">
-        <v>128</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:24">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
+        <v>54</v>
+      </c>
+      <c r="E31" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" t="s">
+        <v>136</v>
+      </c>
+      <c r="H31" t="s">
+        <v>158</v>
+      </c>
+      <c r="I31" t="s">
+        <v>164</v>
+      </c>
+      <c r="J31">
+        <v>30</v>
+      </c>
+      <c r="K31">
+        <v>16</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>193</v>
+      </c>
+      <c r="P31">
+        <v>18</v>
+      </c>
+      <c r="Q31">
         <v>48</v>
       </c>
-      <c r="E31" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" t="s">
-        <v>114</v>
-      </c>
-      <c r="G31" t="s">
-        <v>117</v>
-      </c>
-      <c r="H31" t="s">
-        <v>134</v>
-      </c>
-      <c r="I31" t="s">
-        <v>135</v>
-      </c>
-      <c r="J31">
-        <v>6</v>
-      </c>
-      <c r="K31">
-        <v>27</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>168</v>
-      </c>
-      <c r="P31">
-        <v>28</v>
-      </c>
-      <c r="Q31">
-        <v>46</v>
-      </c>
       <c r="R31">
         <v>0</v>
       </c>
@@ -3257,90 +3371,90 @@
         <v>90</v>
       </c>
       <c r="U31">
-        <v>15441</v>
+        <v>6798</v>
       </c>
       <c r="V31" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="W31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X31">
-        <v>95</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:24">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F32" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G32" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H32" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I32" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="J32">
+        <v>6</v>
+      </c>
+      <c r="K32">
+        <v>56</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>194</v>
+      </c>
+      <c r="P32">
+        <v>74</v>
+      </c>
+      <c r="Q32">
+        <v>116</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>90</v>
+      </c>
+      <c r="U32">
+        <v>15441</v>
+      </c>
+      <c r="V32" t="s">
+        <v>221</v>
+      </c>
+      <c r="W32">
         <v>10</v>
       </c>
-      <c r="K32">
-        <v>27</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>60</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>169</v>
-      </c>
-      <c r="P32">
-        <v>88</v>
-      </c>
-      <c r="Q32">
-        <v>128</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>90</v>
-      </c>
-      <c r="U32">
-        <v>11112</v>
-      </c>
-      <c r="V32" t="s">
-        <v>196</v>
-      </c>
-      <c r="W32">
-        <v>5</v>
-      </c>
       <c r="X32">
-        <v>6</v>
+        <v>127.17</v>
       </c>
     </row>
     <row r="33" spans="1:24">
@@ -3351,31 +3465,31 @@
         <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E33" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F33" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G33" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="H33" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I33" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="J33">
         <v>12</v>
       </c>
       <c r="K33">
-        <v>-333</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3387,13 +3501,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P33">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -3405,69 +3519,69 @@
         <v>90</v>
       </c>
       <c r="U33">
-        <v>10181</v>
+        <v>9638</v>
       </c>
       <c r="V33" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="W33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X33">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:24">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E34" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H34" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I34" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="J34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N34">
         <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="P34">
-        <v>22</v>
+        <v>162</v>
       </c>
       <c r="Q34">
-        <v>32</v>
+        <v>250</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -3479,69 +3593,69 @@
         <v>90</v>
       </c>
       <c r="U34">
-        <v>11112</v>
+        <v>15441</v>
       </c>
       <c r="V34" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="W34">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>319.12</v>
       </c>
     </row>
     <row r="35" spans="1:24">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
         <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E35" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F35" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G35" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="H35" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I35" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="J35">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="P35">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Q35">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -3553,51 +3667,51 @@
         <v>90</v>
       </c>
       <c r="U35">
-        <v>10189</v>
+        <v>16989</v>
       </c>
       <c r="V35" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="W35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X35">
-        <v>133</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:24">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E36" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F36" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G36" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="H36" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I36" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="J36">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3609,13 +3723,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="P36">
-        <v>146</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -3627,51 +3741,51 @@
         <v>90</v>
       </c>
       <c r="U36">
-        <v>9638</v>
+        <v>16857</v>
       </c>
       <c r="V36" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="W36">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="X36">
-        <v>105</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:24">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E37" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="F37" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="G37" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="H37" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I37" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="J37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>149</v>
+        <v>5</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3680,16 +3794,16 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="P37">
-        <v>202</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -3701,69 +3815,69 @@
         <v>90</v>
       </c>
       <c r="U37">
-        <v>15441</v>
+        <v>16857</v>
       </c>
       <c r="V37" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="W37">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="X37">
-        <v>127</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:24">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E38" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="F38" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G38" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="H38" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I38" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="J38">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="K38">
-        <v>-100</v>
+        <v>37</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="N38">
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="P38">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="Q38">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -3775,51 +3889,51 @@
         <v>90</v>
       </c>
       <c r="U38">
-        <v>15134</v>
+        <v>10189</v>
       </c>
       <c r="V38" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="W38">
         <v>2</v>
       </c>
       <c r="X38">
-        <v>9</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:24">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s">
         <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E39" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="F39" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G39" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="H39" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I39" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -3831,13 +3945,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="P39">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="Q39">
-        <v>15</v>
+        <v>230</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -3849,51 +3963,51 @@
         <v>90</v>
       </c>
       <c r="U39">
-        <v>15</v>
+        <v>9638</v>
       </c>
       <c r="V39" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="W39">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X39">
-        <v>58</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:24">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H40" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I40" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="J40">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -3905,10 +4019,10 @@
         <v>0</v>
       </c>
       <c r="O40" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="P40">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="Q40">
         <v>56</v>
@@ -3923,16 +4037,16 @@
         <v>90</v>
       </c>
       <c r="U40">
-        <v>10142</v>
+        <v>15441</v>
       </c>
       <c r="V40" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="W40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X40">
-        <v>10</v>
+        <v>94.17</v>
       </c>
     </row>
     <row r="41" spans="1:24">
@@ -3943,31 +4057,31 @@
         <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E41" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G41" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="H41" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I41" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K41">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -3979,13 +4093,13 @@
         <v>0</v>
       </c>
       <c r="O41" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="P41">
-        <v>14</v>
+        <v>202</v>
       </c>
       <c r="Q41">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -4000,13 +4114,13 @@
         <v>15441</v>
       </c>
       <c r="V41" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="W41">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="X41">
-        <v>20</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="42" spans="1:24">
@@ -4017,49 +4131,49 @@
         <v>32</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E42" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="F42" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G42" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="H42" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I42" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="J42">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N42">
         <v>0</v>
       </c>
       <c r="O42" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="P42">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="Q42">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -4071,51 +4185,51 @@
         <v>90</v>
       </c>
       <c r="U42">
-        <v>11112</v>
+        <v>10885</v>
       </c>
       <c r="V42" t="s">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="W42">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X42">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:24">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E43" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F43" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G43" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="H43" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I43" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="J43">
         <v>12</v>
       </c>
       <c r="K43">
-        <v>11</v>
+        <v>181</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4127,13 +4241,13 @@
         <v>0</v>
       </c>
       <c r="O43" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="P43">
-        <v>12</v>
+        <v>236</v>
       </c>
       <c r="Q43">
-        <v>24</v>
+        <v>368</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -4145,51 +4259,51 @@
         <v>90</v>
       </c>
       <c r="U43">
-        <v>4131</v>
+        <v>9379</v>
       </c>
       <c r="V43" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="W43">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="X43">
-        <v>38</v>
+        <v>760</v>
       </c>
     </row>
     <row r="44" spans="1:24">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F44" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G44" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H44" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I44" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="J44">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4201,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="O44" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="P44">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="Q44">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -4219,16 +4333,16 @@
         <v>90</v>
       </c>
       <c r="U44">
-        <v>10189</v>
+        <v>15</v>
       </c>
       <c r="V44" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="W44">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="X44">
-        <v>133</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:24">
@@ -4236,34 +4350,34 @@
         <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E45" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="F45" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G45" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="H45" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I45" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -4275,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="P45">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="Q45">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -4293,51 +4407,51 @@
         <v>90</v>
       </c>
       <c r="U45">
-        <v>10334</v>
+        <v>15134</v>
       </c>
       <c r="V45" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="W45">
         <v>2</v>
       </c>
       <c r="X45">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:24">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
         <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E46" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F46" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G46" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="H46" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I46" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="J46">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K46">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4349,13 +4463,13 @@
         <v>0</v>
       </c>
       <c r="O46" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="P46">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="Q46">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -4367,51 +4481,51 @@
         <v>90</v>
       </c>
       <c r="U46">
-        <v>10334</v>
+        <v>10181</v>
       </c>
       <c r="V46" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="W46">
         <v>2</v>
       </c>
       <c r="X46">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:24">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C47" t="s">
         <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E47" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F47" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G47" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="H47" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I47" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="J47">
         <v>6</v>
       </c>
       <c r="K47">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -4423,13 +4537,13 @@
         <v>0</v>
       </c>
       <c r="O47" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="P47">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="Q47">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -4441,51 +4555,51 @@
         <v>90</v>
       </c>
       <c r="U47">
-        <v>10334</v>
+        <v>15441</v>
       </c>
       <c r="V47" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="W47">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="X47">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:24">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C48" t="s">
         <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E48" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F48" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G48" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="H48" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I48" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="J48">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="K48">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4497,13 +4611,13 @@
         <v>0</v>
       </c>
       <c r="O48" t="s">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="P48">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="Q48">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -4515,51 +4629,51 @@
         <v>90</v>
       </c>
       <c r="U48">
-        <v>10334</v>
+        <v>6703</v>
       </c>
       <c r="V48" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="W48">
         <v>2</v>
       </c>
       <c r="X48">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:24">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C49" t="s">
         <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E49" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F49" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G49" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="H49" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I49" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="J49">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K49">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -4571,13 +4685,13 @@
         <v>0</v>
       </c>
       <c r="O49" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="P49">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="Q49">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -4589,51 +4703,51 @@
         <v>90</v>
       </c>
       <c r="U49">
-        <v>3527</v>
+        <v>10142</v>
       </c>
       <c r="V49" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="W49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X49">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:24">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C50" t="s">
         <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E50" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F50" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G50" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="H50" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I50" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="J50">
         <v>10</v>
       </c>
       <c r="K50">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -4645,13 +4759,13 @@
         <v>0</v>
       </c>
       <c r="O50" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="P50">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="Q50">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -4663,21 +4777,21 @@
         <v>90</v>
       </c>
       <c r="U50">
-        <v>15134</v>
+        <v>16900</v>
       </c>
       <c r="V50" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="W50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X50">
-        <v>17</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="51" spans="1:24">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B51" t="s">
         <v>31</v>
@@ -4686,28 +4800,28 @@
         <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E51" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="F51" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G51" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="H51" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I51" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -4719,13 +4833,13 @@
         <v>0</v>
       </c>
       <c r="O51" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
       <c r="P51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q51">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -4737,51 +4851,51 @@
         <v>90</v>
       </c>
       <c r="U51">
-        <v>15</v>
+        <v>4131</v>
       </c>
       <c r="V51" t="s">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="W51">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="X51">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:24">
       <c r="A52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E52" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F52" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G52" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="H52" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I52" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="J52">
         <v>24</v>
       </c>
       <c r="K52">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -4793,13 +4907,13 @@
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="P52">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q52">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -4811,70 +4925,70 @@
         <v>90</v>
       </c>
       <c r="U52">
-        <v>10124</v>
+        <v>15520</v>
       </c>
       <c r="V52" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="W52">
         <v>2</v>
       </c>
       <c r="X52">
-        <v>56</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:24">
       <c r="A53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E53" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="F53" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G53" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="H53" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I53" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="J53">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
       <c r="M53">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N53">
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="P53">
+        <v>54</v>
+      </c>
+      <c r="Q53">
         <v>66</v>
       </c>
-      <c r="Q53">
-        <v>96</v>
-      </c>
       <c r="R53">
         <v>0</v>
       </c>
@@ -4885,51 +4999,51 @@
         <v>90</v>
       </c>
       <c r="U53">
-        <v>11112</v>
+        <v>10189</v>
       </c>
       <c r="V53" t="s">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="W53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X53">
-        <v>6</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:24">
       <c r="A54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B54" t="s">
         <v>31</v>
       </c>
       <c r="C54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="E54" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="F54" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G54" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H54" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I54" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="J54">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -4941,13 +5055,13 @@
         <v>0</v>
       </c>
       <c r="O54" t="s">
-        <v>151</v>
+        <v>214</v>
       </c>
       <c r="P54">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="Q54">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -4959,51 +5073,51 @@
         <v>90</v>
       </c>
       <c r="U54">
-        <v>15</v>
+        <v>3527</v>
       </c>
       <c r="V54" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="W54">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="X54">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" spans="1:24">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E55" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G55" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H55" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I55" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="J55">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K55">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5015,13 +5129,13 @@
         <v>0</v>
       </c>
       <c r="O55" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="P55">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q55">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -5033,69 +5147,69 @@
         <v>90</v>
       </c>
       <c r="U55">
-        <v>13921</v>
+        <v>15</v>
       </c>
       <c r="V55" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="W55">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="X55">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:24">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E56" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G56" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="H56" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I56" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="J56">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L56">
         <v>0</v>
       </c>
       <c r="M56">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N56">
         <v>0</v>
       </c>
       <c r="O56" t="s">
-        <v>141</v>
+        <v>215</v>
       </c>
       <c r="P56">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q56">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -5107,51 +5221,51 @@
         <v>90</v>
       </c>
       <c r="U56">
-        <v>11112</v>
+        <v>10124</v>
       </c>
       <c r="V56" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="W56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X56">
-        <v>6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:24">
       <c r="A57" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D57" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E57" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="F57" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G57" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="H57" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I57" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="J57">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K57">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5163,13 +5277,13 @@
         <v>0</v>
       </c>
       <c r="O57" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="P57">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="Q57">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -5181,51 +5295,51 @@
         <v>90</v>
       </c>
       <c r="U57">
-        <v>10334</v>
+        <v>15</v>
       </c>
       <c r="V57" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="W57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X57">
-        <v>98</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:24">
       <c r="A58" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
         <v>46</v>
       </c>
       <c r="D58" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="E58" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H58" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I58" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K58">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5237,13 +5351,13 @@
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="P58">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="Q58">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -5255,45 +5369,45 @@
         <v>90</v>
       </c>
       <c r="U58">
-        <v>10334</v>
+        <v>15441</v>
       </c>
       <c r="V58" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="W58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X58">
-        <v>36</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="59" spans="1:24">
       <c r="A59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C59" t="s">
         <v>46</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E59" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F59" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G59" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H59" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I59" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -5311,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="P59">
         <v>10</v>
@@ -5332,7 +5446,7 @@
         <v>15</v>
       </c>
       <c r="V59" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="W59">
         <v>15</v>
@@ -5343,56 +5457,56 @@
     </row>
     <row r="60" spans="1:24">
       <c r="A60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" t="s">
+        <v>86</v>
+      </c>
+      <c r="E60" t="s">
+        <v>126</v>
+      </c>
+      <c r="F60" t="s">
+        <v>129</v>
+      </c>
+      <c r="G60" t="s">
+        <v>133</v>
+      </c>
+      <c r="H60" t="s">
+        <v>158</v>
+      </c>
+      <c r="I60" t="s">
+        <v>166</v>
+      </c>
+      <c r="J60">
+        <v>12</v>
+      </c>
+      <c r="K60">
+        <v>11</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60" t="s">
+        <v>217</v>
+      </c>
+      <c r="P60">
+        <v>12</v>
+      </c>
+      <c r="Q60">
         <v>24</v>
       </c>
-      <c r="B60" t="s">
-        <v>29</v>
-      </c>
-      <c r="C60" t="s">
-        <v>47</v>
-      </c>
-      <c r="D60" t="s">
-        <v>80</v>
-      </c>
-      <c r="E60" t="s">
-        <v>113</v>
-      </c>
-      <c r="F60" t="s">
-        <v>114</v>
-      </c>
-      <c r="G60" t="s">
-        <v>118</v>
-      </c>
-      <c r="H60" t="s">
-        <v>134</v>
-      </c>
-      <c r="I60" t="s">
-        <v>136</v>
-      </c>
-      <c r="J60">
-        <v>8</v>
-      </c>
-      <c r="K60">
-        <v>43</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60" t="s">
-        <v>189</v>
-      </c>
-      <c r="P60">
-        <v>52</v>
-      </c>
-      <c r="Q60">
-        <v>84</v>
-      </c>
       <c r="R60">
         <v>0</v>
       </c>
@@ -5403,16 +5517,16 @@
         <v>90</v>
       </c>
       <c r="U60">
-        <v>15441</v>
+        <v>10885</v>
       </c>
       <c r="V60" t="s">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="W60">
+        <v>2</v>
+      </c>
+      <c r="X60">
         <v>6</v>
-      </c>
-      <c r="X60">
-        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:24">
@@ -5420,34 +5534,34 @@
         <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D61" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E61" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="F61" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G61" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H61" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I61" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -5459,13 +5573,13 @@
         <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>151</v>
+        <v>218</v>
       </c>
       <c r="P61">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q61">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R61">
         <v>0</v>
@@ -5477,89 +5591,311 @@
         <v>90</v>
       </c>
       <c r="U61">
-        <v>15</v>
+        <v>10885</v>
       </c>
       <c r="V61" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="W61">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X61">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:24">
       <c r="A62" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
         <v>47</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E62" t="s">
+        <v>125</v>
+      </c>
+      <c r="F62" t="s">
+        <v>128</v>
+      </c>
+      <c r="G62" t="s">
+        <v>132</v>
+      </c>
+      <c r="H62" t="s">
+        <v>158</v>
+      </c>
+      <c r="I62" t="s">
+        <v>160</v>
+      </c>
+      <c r="J62">
+        <v>8</v>
+      </c>
+      <c r="K62">
+        <v>42</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62" t="s">
+        <v>219</v>
+      </c>
+      <c r="P62">
+        <v>52</v>
+      </c>
+      <c r="Q62">
         <v>84</v>
       </c>
-      <c r="F62" t="s">
-        <v>116</v>
-      </c>
-      <c r="G62" t="s">
-        <v>120</v>
-      </c>
-      <c r="H62" t="s">
-        <v>134</v>
-      </c>
-      <c r="I62" t="s">
-        <v>138</v>
-      </c>
-      <c r="J62">
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>90</v>
+      </c>
+      <c r="U62">
+        <v>15441</v>
+      </c>
+      <c r="V62" t="s">
+        <v>221</v>
+      </c>
+      <c r="W62">
+        <v>6</v>
+      </c>
+      <c r="X62">
+        <v>50.25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" t="s">
+        <v>47</v>
+      </c>
+      <c r="D63" t="s">
+        <v>87</v>
+      </c>
+      <c r="E63" t="s">
+        <v>127</v>
+      </c>
+      <c r="F63" t="s">
+        <v>130</v>
+      </c>
+      <c r="G63" t="s">
+        <v>157</v>
+      </c>
+      <c r="H63" t="s">
+        <v>158</v>
+      </c>
+      <c r="I63" t="s">
+        <v>171</v>
+      </c>
+      <c r="J63">
+        <v>5</v>
+      </c>
+      <c r="K63">
+        <v>9</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63" t="s">
+        <v>220</v>
+      </c>
+      <c r="P63">
+        <v>11</v>
+      </c>
+      <c r="Q63">
+        <v>16</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>90</v>
+      </c>
+      <c r="U63">
+        <v>10321</v>
+      </c>
+      <c r="V63" t="s">
+        <v>246</v>
+      </c>
+      <c r="W63">
+        <v>2</v>
+      </c>
+      <c r="X63">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" t="s">
+        <v>47</v>
+      </c>
+      <c r="D64" t="s">
+        <v>53</v>
+      </c>
+      <c r="E64" t="s">
+        <v>93</v>
+      </c>
+      <c r="F64" t="s">
+        <v>129</v>
+      </c>
+      <c r="G64" t="s">
+        <v>133</v>
+      </c>
+      <c r="H64" t="s">
+        <v>158</v>
+      </c>
+      <c r="I64" t="s">
+        <v>161</v>
+      </c>
+      <c r="J64">
         <v>1</v>
       </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62" t="s">
-        <v>151</v>
-      </c>
-      <c r="P62">
+      <c r="K64">
+        <v>4</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64" t="s">
+        <v>174</v>
+      </c>
+      <c r="P64">
+        <v>5</v>
+      </c>
+      <c r="Q64">
         <v>10</v>
       </c>
-      <c r="Q62">
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>90</v>
+      </c>
+      <c r="U64">
         <v>15</v>
       </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
-        <v>0</v>
-      </c>
-      <c r="T62">
-        <v>90</v>
-      </c>
-      <c r="U62">
+      <c r="V64" t="s">
+        <v>222</v>
+      </c>
+      <c r="W64">
+        <v>6</v>
+      </c>
+      <c r="X64">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" t="s">
+        <v>47</v>
+      </c>
+      <c r="D65" t="s">
+        <v>50</v>
+      </c>
+      <c r="E65" t="s">
+        <v>90</v>
+      </c>
+      <c r="F65" t="s">
+        <v>129</v>
+      </c>
+      <c r="G65" t="s">
+        <v>133</v>
+      </c>
+      <c r="H65" t="s">
+        <v>158</v>
+      </c>
+      <c r="I65" t="s">
+        <v>161</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65" t="s">
+        <v>174</v>
+      </c>
+      <c r="P65">
+        <v>10</v>
+      </c>
+      <c r="Q65">
         <v>15</v>
       </c>
-      <c r="V62" t="s">
-        <v>192</v>
-      </c>
-      <c r="W62">
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>90</v>
+      </c>
+      <c r="U65">
         <v>15</v>
       </c>
-      <c r="X62">
+      <c r="V65" t="s">
+        <v>222</v>
+      </c>
+      <c r="W65">
+        <v>15</v>
+      </c>
+      <c r="X65">
         <v>58</v>
       </c>
     </row>

--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="242">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -169,58 +169,61 @@
     <t>15765</t>
   </si>
   <si>
+    <t>835</t>
+  </si>
+  <si>
+    <t>838</t>
+  </si>
+  <si>
     <t>840</t>
   </si>
   <si>
-    <t>2879</t>
-  </si>
-  <si>
     <t>15764</t>
   </si>
   <si>
     <t>37957</t>
   </si>
   <si>
+    <t>39520</t>
+  </si>
+  <si>
+    <t>1305</t>
+  </si>
+  <si>
+    <t>15762</t>
+  </si>
+  <si>
+    <t>17160</t>
+  </si>
+  <si>
+    <t>37075</t>
+  </si>
+  <si>
+    <t>795</t>
+  </si>
+  <si>
     <t>389</t>
   </si>
   <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>11245</t>
+  </si>
+  <si>
+    <t>812</t>
+  </si>
+  <si>
     <t>390</t>
   </si>
   <si>
-    <t>15762</t>
-  </si>
-  <si>
-    <t>17160</t>
-  </si>
-  <si>
-    <t>37075</t>
-  </si>
-  <si>
-    <t>795</t>
-  </si>
-  <si>
-    <t>960</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>21559</t>
-  </si>
-  <si>
-    <t>550</t>
-  </si>
-  <si>
-    <t>660</t>
-  </si>
-  <si>
-    <t>1564</t>
-  </si>
-  <si>
-    <t>1620</t>
-  </si>
-  <si>
-    <t>1695</t>
+    <t>3181</t>
+  </si>
+  <si>
+    <t>38808</t>
+  </si>
+  <si>
+    <t>2434</t>
   </si>
   <si>
     <t>3252</t>
@@ -229,36 +232,27 @@
     <t>3289</t>
   </si>
   <si>
-    <t>3704</t>
+    <t>3997</t>
   </si>
   <si>
     <t>109</t>
   </si>
   <si>
-    <t>4554</t>
-  </si>
-  <si>
     <t>6781</t>
   </si>
   <si>
     <t>3994</t>
   </si>
   <si>
-    <t>49</t>
-  </si>
-  <si>
     <t>386</t>
   </si>
   <si>
-    <t>1242</t>
-  </si>
-  <si>
-    <t>1977</t>
-  </si>
-  <si>
     <t>2722</t>
   </si>
   <si>
+    <t>2881</t>
+  </si>
+  <si>
     <t>3011</t>
   </si>
   <si>
@@ -268,15 +262,21 @@
     <t>13123</t>
   </si>
   <si>
+    <t>20621</t>
+  </si>
+  <si>
     <t>2960</t>
   </si>
   <si>
-    <t>812</t>
-  </si>
-  <si>
     <t>21553</t>
   </si>
   <si>
+    <t>33255</t>
+  </si>
+  <si>
+    <t>2177</t>
+  </si>
+  <si>
     <t>2760</t>
   </si>
   <si>
@@ -289,58 +289,61 @@
     <t>CESTA BASICA PEQ</t>
   </si>
   <si>
+    <t>REFRIG PET COCA COLA 3L</t>
+  </si>
+  <si>
+    <t>REFRIG FRUKI PET 3L GUARANA</t>
+  </si>
+  <si>
     <t>REFRIG PEPSI PET 3L</t>
   </si>
   <si>
-    <t>MASSA C OVOS ISABELA 500G ESPAGUETE</t>
-  </si>
-  <si>
     <t>CESTA BASICA MED</t>
   </si>
   <si>
     <t>CHA BARAO 13G PTO</t>
   </si>
   <si>
+    <t>WHISKY GOLD PINE VD 900ML FIRE</t>
+  </si>
+  <si>
+    <t>BISC DOCE DOMELLY PAO DE MEL 250G CHOC</t>
+  </si>
+  <si>
+    <t>CESTA BASICA GRD</t>
+  </si>
+  <si>
+    <t>DESINF AQUAFAST 2L CHA BRANCO</t>
+  </si>
+  <si>
+    <t>FARINHA TAPIOCA DINDA 400G TRAD</t>
+  </si>
+  <si>
+    <t>REFRIG COCA COLA PET 2L ZERO</t>
+  </si>
+  <si>
     <t>ENERG MONSTER LT 473ML GREEN</t>
   </si>
   <si>
+    <t>ARROZ BCO REQUINTE TP1 2KG</t>
+  </si>
+  <si>
+    <t>GOIABADA STELLA KG</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA UVA PET 2L</t>
+  </si>
+  <si>
     <t>ENERG MONSTER LT 473ML GREEN ZERO</t>
   </si>
   <si>
-    <t>CESTA BASICA GRD</t>
-  </si>
-  <si>
-    <t>DESINF AQUAFAST 2L CHA BRANCO</t>
-  </si>
-  <si>
-    <t>FARINHA TAPIOCA DINDA 400G TRAD</t>
-  </si>
-  <si>
-    <t>REFRIG COCA COLA PET 2L ZERO</t>
-  </si>
-  <si>
-    <t>OLEO COCO NUTRISANTI 200ML</t>
-  </si>
-  <si>
-    <t>ARROZ BCO REQUINTE TP1 2KG</t>
-  </si>
-  <si>
-    <t>PANO SARJA PANOSUL 45X75CM</t>
-  </si>
-  <si>
-    <t>GATORADE ZERO 350ML FTAS SILVESTRES</t>
-  </si>
-  <si>
-    <t>SUCO KAPO TP 200ML FRUTAS CITRICAS</t>
-  </si>
-  <si>
-    <t>BISC SALG TUCS 100G TRAD</t>
-  </si>
-  <si>
-    <t>BISC SORT DOMELLY JOCE 300G</t>
-  </si>
-  <si>
-    <t>MARSHMALLOWS FOFS 220G TWIST COLORIDO</t>
+    <t>SALG KEVYTOS SHOW 38G BACON</t>
+  </si>
+  <si>
+    <t>SALG BATATA PRINGLES CEBOLA 37G</t>
+  </si>
+  <si>
+    <t>PEPINO CONSERVA DA SERRA VD 300G</t>
   </si>
   <si>
     <t>SALG OBBA 100G CEBOLA E SALSA</t>
@@ -349,36 +352,27 @@
     <t>SALG OBBA 100G PRESUNTO</t>
   </si>
   <si>
-    <t>MIST P BOLO APTI 400G CHOC</t>
+    <t>RACAO DOG CHOW SH 85G FILH FGO LEITE</t>
   </si>
   <si>
     <t>CERV BRAHMA CHOPP GF 1L RETORNAVEL</t>
   </si>
   <si>
-    <t>CAPA RODO PANOSUL 35X50CM SORTIDO</t>
-  </si>
-  <si>
     <t>LEITE UHT ELEGE INT 1L</t>
   </si>
   <si>
     <t>RACAO DOG CHOW SH 85G AD CAR ARROZ</t>
   </si>
   <si>
-    <t>AGUA MIN FLORESTA PET 500ML S GAS</t>
-  </si>
-  <si>
     <t>ENERG MONSTER LT 473ML ABSOLUT ZERO</t>
   </si>
   <si>
-    <t>CHOC BARRA NEUGEBAUER 80G BCO</t>
-  </si>
-  <si>
-    <t>TURRON Y MANI ARCOR 25G</t>
-  </si>
-  <si>
     <t>FARINHA TRIGO PANFACIL TP1 1KG</t>
   </si>
   <si>
+    <t>MASSA C OVOS PARATI 400G ESPAGUETE</t>
+  </si>
+  <si>
     <t>AVEIA FLOCOS FINOS NATURALE 1KG</t>
   </si>
   <si>
@@ -388,15 +382,21 @@
     <t>BATATA PALHA YOKI TRAD L105P90 105G</t>
   </si>
   <si>
+    <t>MAS FURADINHO ISABELA SEMOLA 400G</t>
+  </si>
+  <si>
     <t>ACHOC TODDY PT 370G ORIGINAL</t>
   </si>
   <si>
-    <t>REFRIG FANTA UVA PET 2L</t>
-  </si>
-  <si>
     <t>PANO PANOSUL FELPUDO ESTAMP 38X63CM</t>
   </si>
   <si>
+    <t>REFRIG CHARRUA PET 3L GUARANA</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SABOROSO TP1 5KG</t>
+  </si>
+  <si>
     <t>FARINHA TRIGO NORDESTE 5KG</t>
   </si>
   <si>
@@ -421,63 +421,51 @@
     <t>21/10/2024</t>
   </si>
   <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
+  </si>
+  <si>
+    <t>08/11/2024</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>18/10/2024</t>
+  </si>
+  <si>
+    <t>04/12/2024</t>
+  </si>
+  <si>
+    <t>11/06/2025</t>
+  </si>
+  <si>
+    <t>20/12/2024</t>
+  </si>
+  <si>
+    <t>03/07/2026</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>23/12/2024</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>23/09/2024</t>
+  </si>
+  <si>
+    <t>13/12/2024</t>
+  </si>
+  <si>
     <t>16/12/2024</t>
   </si>
   <si>
-    <t>07/04/2026</t>
-  </si>
-  <si>
-    <t>24/02/2026</t>
-  </si>
-  <si>
-    <t>18/10/2024</t>
-  </si>
-  <si>
-    <t>25/10/2024</t>
-  </si>
-  <si>
-    <t>04/12/2024</t>
-  </si>
-  <si>
-    <t>09/10/2024</t>
-  </si>
-  <si>
-    <t>15/10/2024</t>
-  </si>
-  <si>
-    <t>14/11/2024</t>
-  </si>
-  <si>
-    <t>18/11/2024</t>
-  </si>
-  <si>
-    <t>21/11/2024</t>
-  </si>
-  <si>
-    <t>23/12/2024</t>
-  </si>
-  <si>
-    <t>31/12/2024</t>
-  </si>
-  <si>
-    <t>23/09/2024</t>
-  </si>
-  <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>07/11/2024</t>
-  </si>
-  <si>
-    <t>29/11/2024</t>
-  </si>
-  <si>
-    <t>13/12/2024</t>
-  </si>
-  <si>
     <t>18/12/2024</t>
   </si>
   <si>
@@ -487,6 +475,12 @@
     <t>17/12/2024</t>
   </si>
   <si>
+    <t>07/07/2025</t>
+  </si>
+  <si>
+    <t>05/12/2024</t>
+  </si>
+  <si>
     <t>14/12/2024</t>
   </si>
   <si>
@@ -505,175 +499,166 @@
     <t>4</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>15</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>64</t>
+    <t>25</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1412</t>
+  </si>
+  <si>
+    <t>693</t>
+  </si>
+  <si>
+    <t>1365</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>1521</t>
+  </si>
+  <si>
+    <t>611</t>
+  </si>
+  <si>
+    <t>1121</t>
+  </si>
+  <si>
+    <t>662</t>
+  </si>
+  <si>
+    <t>49,64</t>
+  </si>
+  <si>
+    <t>717</t>
+  </si>
+  <si>
+    <t>1565</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>655</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>1461</t>
+  </si>
+  <si>
+    <t>763</t>
   </si>
   <si>
     <t>50</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1379</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>1773</t>
-  </si>
-  <si>
-    <t>1016</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>453</t>
-  </si>
-  <si>
-    <t>1503</t>
-  </si>
-  <si>
-    <t>612</t>
-  </si>
-  <si>
-    <t>1131</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>655</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>391</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>652</t>
-  </si>
-  <si>
-    <t>1464</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>115</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>787</t>
-  </si>
-  <si>
-    <t>1306</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>1816</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>2753</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>33528</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>3321</t>
-  </si>
-  <si>
-    <t>969</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>483</t>
-  </si>
-  <si>
-    <t>994</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>524</t>
+    <t>139</t>
+  </si>
+  <si>
+    <t>1300</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>1819</t>
+  </si>
+  <si>
+    <t>2745</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>972</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>487</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>526</t>
+  </si>
+  <si>
+    <t>1689</t>
   </si>
   <si>
     <t>61</t>
   </si>
   <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>492</t>
+    <t>1510</t>
+  </si>
+  <si>
+    <t>494</t>
+  </si>
+  <si>
+    <t>413</t>
   </si>
   <si>
     <t>76</t>
@@ -685,73 +670,73 @@
     <t>SUPERMERCADO BAKLIZI LTDA</t>
   </si>
   <si>
+    <t>BEBIDAS FRUKI LTDA</t>
+  </si>
+  <si>
     <t>CRBS AS CDD PELOTAS</t>
   </si>
   <si>
+    <t>BARAO - INDUSTRIA E COMERCIO DE ERVA MATE E CHAS S.A.</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA MAXIMILIANO LTDA</t>
+  </si>
+  <si>
+    <t>REDOL ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>AQUAFAST PROD LIMPEZA/HIGIENE LTDA</t>
+  </si>
+  <si>
+    <t>ROCHA E FILHOS LTDA</t>
+  </si>
+  <si>
+    <t>GENESIO CEOLIN E CIA LTDA</t>
+  </si>
+  <si>
+    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
+  </si>
+  <si>
+    <t>DELAVY ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>PARATI IND.COM.DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>INDUSTRIA DE ALIMENTOS PETRY LTDA</t>
+  </si>
+  <si>
+    <t>FITOS ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>NESTLE BRASIL LTDA</t>
+  </si>
+  <si>
+    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
+  </si>
+  <si>
+    <t>MOINHO ESTRELA LTDA</t>
+  </si>
+  <si>
+    <t>NAT CEREAIS E ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>CONSERVAS ODERICH SA</t>
+  </si>
+  <si>
+    <t>FABIANO ZAFFALON E CIA LTDA</t>
+  </si>
+  <si>
     <t>M DIAS BRANCO S.A IND E COM DE ALIMENTOS</t>
   </si>
   <si>
-    <t>BARAO - INDUSTRIA E COMERCIO DE ERVA MATE E CHAS S.A.</t>
-  </si>
-  <si>
-    <t>AQUAFAST PROD LIMPEZA/HIGIENE LTDA</t>
-  </si>
-  <si>
-    <t>ROCHA E FILHOS LTDA</t>
-  </si>
-  <si>
-    <t>SANTI INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>GENESIO CEOLIN E CIA LTDA</t>
+    <t>PEPSICO DO BRASIL LTDA</t>
   </si>
   <si>
     <t>HIPER TEXTIL LTDA</t>
   </si>
   <si>
-    <t>CILASI ALIMENTOS S E A.</t>
-  </si>
-  <si>
-    <t>REDOL ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>FLORESTAL ALIMENTOS S.A.</t>
-  </si>
-  <si>
-    <t>FITOS ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>APTI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
-  </si>
-  <si>
-    <t>NESTLE BRASIL LTDA</t>
-  </si>
-  <si>
-    <t>AGUAS MINERAIS SARANDI LTDA</t>
-  </si>
-  <si>
-    <t>VONPAR ALIMENTOS S.A</t>
-  </si>
-  <si>
-    <t>KASADOCE DISTRIBUIDORA DE ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>MOINHO ESTRELA LTDA</t>
-  </si>
-  <si>
-    <t>NAT CEREAIS E ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>CONSERVAS ODERICH SA</t>
-  </si>
-  <si>
-    <t>FABIANO ZAFFALON E CIA LTDA</t>
-  </si>
-  <si>
-    <t>PEPSICO DO BRASIL LTDA</t>
+    <t>COOPERATIVA AGROINDUSTRIAL ALEGRETE LTDA</t>
   </si>
   <si>
     <t>MOINHO DO NORDESTE SA</t>
@@ -1086,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -1186,16 +1171,16 @@
         <v>131</v>
       </c>
       <c r="H2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J2">
         <v>6</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1207,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="P2">
         <v>6</v>
@@ -1228,13 +1213,13 @@
         <v>15441</v>
       </c>
       <c r="V2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="W2">
         <v>2</v>
       </c>
       <c r="X2">
-        <v>94.17</v>
+        <v>214.17</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1260,16 +1245,16 @@
         <v>132</v>
       </c>
       <c r="H3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I3" t="s">
         <v>158</v>
-      </c>
-      <c r="I3" t="s">
-        <v>160</v>
       </c>
       <c r="J3">
         <v>8</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1281,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P3">
         <v>32</v>
@@ -1302,10 +1287,10 @@
         <v>15441</v>
       </c>
       <c r="V3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="W3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X3">
         <v>319.12</v>
@@ -1334,10 +1319,10 @@
         <v>133</v>
       </c>
       <c r="H4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1355,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P4">
         <v>5</v>
@@ -1376,7 +1361,7 @@
         <v>15</v>
       </c>
       <c r="V4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1408,34 +1393,34 @@
         <v>134</v>
       </c>
       <c r="H5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>156</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>173</v>
+      </c>
+      <c r="P5">
         <v>158</v>
       </c>
-      <c r="I5" t="s">
-        <v>162</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>141</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>175</v>
-      </c>
-      <c r="P5">
-        <v>156</v>
-      </c>
       <c r="Q5">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1447,24 +1432,24 @@
         <v>90</v>
       </c>
       <c r="U5">
-        <v>9638</v>
+        <v>15441</v>
       </c>
       <c r="V5" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="W5">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="X5">
-        <v>216.25</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
@@ -1479,19 +1464,19 @@
         <v>130</v>
       </c>
       <c r="G6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1503,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="P6">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="Q6">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1521,24 +1506,24 @@
         <v>90</v>
       </c>
       <c r="U6">
-        <v>7995</v>
+        <v>6424</v>
       </c>
       <c r="V6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="W6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="X6">
-        <v>25</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
@@ -1550,22 +1535,22 @@
         <v>93</v>
       </c>
       <c r="F7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1577,13 +1562,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P7">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="Q7">
-        <v>15</v>
+        <v>240</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1595,16 +1580,16 @@
         <v>90</v>
       </c>
       <c r="U7">
-        <v>15</v>
+        <v>9638</v>
       </c>
       <c r="V7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="W7">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="X7">
-        <v>39</v>
+        <v>213.25</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1618,10 +1603,10 @@
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F8" t="s">
         <v>129</v>
@@ -1630,10 +1615,10 @@
         <v>133</v>
       </c>
       <c r="H8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1651,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P8">
         <v>10</v>
@@ -1672,13 +1657,13 @@
         <v>15</v>
       </c>
       <c r="V8" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="W8">
         <v>15</v>
       </c>
       <c r="X8">
-        <v>58</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1692,47 +1677,47 @@
         <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I9" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>172</v>
+      </c>
+      <c r="P9">
+        <v>10</v>
+      </c>
+      <c r="Q9">
         <v>15</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>177</v>
-      </c>
-      <c r="P9">
-        <v>18</v>
-      </c>
-      <c r="Q9">
-        <v>48</v>
-      </c>
       <c r="R9">
         <v>0</v>
       </c>
@@ -1743,27 +1728,27 @@
         <v>90</v>
       </c>
       <c r="U9">
-        <v>6798</v>
+        <v>15</v>
       </c>
       <c r="V9" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="W9">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="X9">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
         <v>55</v>
@@ -1775,19 +1760,19 @@
         <v>128</v>
       </c>
       <c r="G10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K10">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1799,13 +1784,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P10">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="Q10">
-        <v>306</v>
+        <v>48</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1817,16 +1802,16 @@
         <v>90</v>
       </c>
       <c r="U10">
-        <v>15441</v>
+        <v>6798</v>
       </c>
       <c r="V10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="W10">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="X10">
-        <v>86.33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1837,7 +1822,7 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -1846,22 +1831,22 @@
         <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G11" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I11" t="s">
         <v>159</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1873,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="P11">
-        <v>114</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1891,51 +1876,51 @@
         <v>90</v>
       </c>
       <c r="U11">
-        <v>15441</v>
+        <v>16951</v>
       </c>
       <c r="V11" t="s">
         <v>221</v>
       </c>
       <c r="W11">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>127.17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G12" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K12">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1947,13 +1932,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P12">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="Q12">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1965,16 +1950,16 @@
         <v>90</v>
       </c>
       <c r="U12">
-        <v>15441</v>
+        <v>15886</v>
       </c>
       <c r="V12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X12">
-        <v>94.17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1988,10 +1973,10 @@
         <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F13" t="s">
         <v>129</v>
@@ -2000,10 +1985,10 @@
         <v>133</v>
       </c>
       <c r="H13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -2021,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P13">
         <v>15</v>
@@ -2042,7 +2027,7 @@
         <v>15</v>
       </c>
       <c r="V13" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -2074,10 +2059,10 @@
         <v>133</v>
       </c>
       <c r="H14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2095,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P14">
         <v>15</v>
@@ -2116,7 +2101,7 @@
         <v>15</v>
       </c>
       <c r="V14" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="W14">
         <v>20</v>
@@ -2136,10 +2121,10 @@
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F15" t="s">
         <v>130</v>
@@ -2148,10 +2133,10 @@
         <v>133</v>
       </c>
       <c r="H15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -2169,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -2190,7 +2175,7 @@
         <v>3947</v>
       </c>
       <c r="V15" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="W15">
         <v>2</v>
@@ -2210,28 +2195,28 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F16" t="s">
         <v>130</v>
       </c>
       <c r="G16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J16">
         <v>20</v>
       </c>
       <c r="K16">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2243,13 +2228,13 @@
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P16">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Q16">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -2264,7 +2249,7 @@
         <v>21894</v>
       </c>
       <c r="V16" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="W16">
         <v>2</v>
@@ -2284,28 +2269,28 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F17" t="s">
         <v>128</v>
       </c>
       <c r="G17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H17" t="s">
+        <v>156</v>
+      </c>
+      <c r="I17" t="s">
         <v>158</v>
-      </c>
-      <c r="I17" t="s">
-        <v>160</v>
       </c>
       <c r="J17">
         <v>8</v>
       </c>
       <c r="K17">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2317,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P17">
         <v>164</v>
@@ -2338,13 +2323,13 @@
         <v>15441</v>
       </c>
       <c r="V17" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="W17">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="X17">
-        <v>50.25</v>
+        <v>500.25</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2358,10 +2343,10 @@
         <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F18" t="s">
         <v>129</v>
@@ -2370,10 +2355,10 @@
         <v>133</v>
       </c>
       <c r="H18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I18" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2391,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -2412,7 +2397,7 @@
         <v>15</v>
       </c>
       <c r="V18" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2432,10 +2417,10 @@
         <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F19" t="s">
         <v>128</v>
@@ -2444,16 +2429,16 @@
         <v>131</v>
       </c>
       <c r="H19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
       <c r="K19">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2465,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P19">
         <v>66</v>
@@ -2486,13 +2471,13 @@
         <v>15441</v>
       </c>
       <c r="V19" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>86.33</v>
+        <v>196.33</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2518,16 +2503,16 @@
         <v>132</v>
       </c>
       <c r="H20" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" t="s">
         <v>158</v>
-      </c>
-      <c r="I20" t="s">
-        <v>160</v>
       </c>
       <c r="J20">
         <v>8</v>
       </c>
       <c r="K20">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2539,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P20">
         <v>128</v>
@@ -2560,7 +2545,7 @@
         <v>15441</v>
       </c>
       <c r="V20" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2580,46 +2565,46 @@
         <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F21" t="s">
         <v>130</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I21" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J21">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K21">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P21">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="Q21">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -2631,90 +2616,90 @@
         <v>90</v>
       </c>
       <c r="U21">
-        <v>16989</v>
+        <v>13087</v>
       </c>
       <c r="V21" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="W21">
         <v>3</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>47.93</v>
       </c>
     </row>
     <row r="22" spans="1:24">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
         <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s">
         <v>130</v>
       </c>
       <c r="G22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H22" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J22">
+        <v>14</v>
+      </c>
+      <c r="K22">
+        <v>6.802</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>184</v>
+      </c>
+      <c r="P22">
+        <v>7</v>
+      </c>
+      <c r="Q22">
+        <v>12</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>90</v>
+      </c>
+      <c r="U22">
+        <v>5894</v>
+      </c>
+      <c r="V22" t="s">
+        <v>226</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
         <v>15</v>
-      </c>
-      <c r="K22">
-        <v>41</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>187</v>
-      </c>
-      <c r="P22">
-        <v>45</v>
-      </c>
-      <c r="Q22">
-        <v>75</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>90</v>
-      </c>
-      <c r="U22">
-        <v>13087</v>
-      </c>
-      <c r="V22" t="s">
-        <v>229</v>
-      </c>
-      <c r="W22">
-        <v>3</v>
-      </c>
-      <c r="X22">
-        <v>53.93</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2740,10 +2725,10 @@
         <v>133</v>
       </c>
       <c r="H23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I23" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2761,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P23">
         <v>5</v>
@@ -2782,7 +2767,7 @@
         <v>15</v>
       </c>
       <c r="V23" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2793,37 +2778,37 @@
     </row>
     <row r="24" spans="1:24">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H24" t="s">
+        <v>156</v>
+      </c>
+      <c r="I24" t="s">
         <v>158</v>
       </c>
-      <c r="I24" t="s">
-        <v>161</v>
-      </c>
       <c r="J24">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -2835,13 +2820,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P24">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="Q24">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2853,16 +2838,16 @@
         <v>90</v>
       </c>
       <c r="U24">
-        <v>10885</v>
+        <v>15441</v>
       </c>
       <c r="V24" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="W24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>23</v>
+        <v>200.25</v>
       </c>
     </row>
     <row r="25" spans="1:24">
@@ -2876,28 +2861,28 @@
         <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E25" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F25" t="s">
         <v>130</v>
       </c>
       <c r="G25" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I25" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J25">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2909,13 +2894,13 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="P25">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="Q25">
-        <v>22</v>
+        <v>274</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2927,51 +2912,51 @@
         <v>90</v>
       </c>
       <c r="U25">
-        <v>9638</v>
+        <v>15441</v>
       </c>
       <c r="V25" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="W25">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="X25">
-        <v>20</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:24">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
         <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G26" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="H26" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I26" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J26">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2983,13 +2968,13 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -3001,16 +2986,16 @@
         <v>90</v>
       </c>
       <c r="U26">
-        <v>15441</v>
+        <v>15</v>
       </c>
       <c r="V26" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="W26">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="X26">
-        <v>20</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:24">
@@ -3018,34 +3003,34 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
         <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G27" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H27" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I27" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J27">
         <v>30</v>
       </c>
       <c r="K27">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3057,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P27">
         <v>18</v>
@@ -3075,51 +3060,51 @@
         <v>90</v>
       </c>
       <c r="U27">
-        <v>4296</v>
+        <v>6798</v>
       </c>
       <c r="V27" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="W27">
         <v>2</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:24">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G28" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="H28" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I28" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="J28">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -3131,13 +3116,13 @@
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P28">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="Q28">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -3149,51 +3134,51 @@
         <v>90</v>
       </c>
       <c r="U28">
-        <v>15886</v>
+        <v>15441</v>
       </c>
       <c r="V28" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="W28">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="X28">
-        <v>31</v>
+        <v>182.17</v>
       </c>
     </row>
     <row r="29" spans="1:24">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G29" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H29" t="s">
+        <v>156</v>
+      </c>
+      <c r="I29" t="s">
         <v>158</v>
       </c>
-      <c r="I29" t="s">
-        <v>166</v>
-      </c>
       <c r="J29">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3205,69 +3190,69 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P29">
+        <v>124</v>
+      </c>
+      <c r="Q29">
+        <v>196</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>90</v>
+      </c>
+      <c r="U29">
+        <v>15441</v>
+      </c>
+      <c r="V29" t="s">
+        <v>216</v>
+      </c>
+      <c r="W29">
         <v>10</v>
       </c>
-      <c r="Q29">
-        <v>22</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>90</v>
-      </c>
-      <c r="U29">
-        <v>7493</v>
-      </c>
-      <c r="V29" t="s">
-        <v>233</v>
-      </c>
-      <c r="W29">
-        <v>2</v>
-      </c>
       <c r="X29">
-        <v>28</v>
+        <v>500.25</v>
       </c>
     </row>
     <row r="30" spans="1:24">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H30" t="s">
+        <v>156</v>
+      </c>
+      <c r="I30" t="s">
         <v>158</v>
       </c>
-      <c r="I30" t="s">
-        <v>161</v>
-      </c>
       <c r="J30">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3279,13 +3264,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="P30">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="Q30">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -3297,16 +3282,16 @@
         <v>90</v>
       </c>
       <c r="U30">
-        <v>15</v>
+        <v>15441</v>
       </c>
       <c r="V30" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="W30">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X30">
-        <v>58</v>
+        <v>319.12</v>
       </c>
     </row>
     <row r="31" spans="1:24">
@@ -3314,53 +3299,53 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" t="s">
+        <v>107</v>
+      </c>
+      <c r="F31" t="s">
+        <v>130</v>
+      </c>
+      <c r="G31" t="s">
+        <v>142</v>
+      </c>
+      <c r="H31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I31" t="s">
+        <v>162</v>
+      </c>
+      <c r="J31">
+        <v>20</v>
+      </c>
+      <c r="K31">
+        <v>33</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>191</v>
+      </c>
+      <c r="P31">
+        <v>34</v>
+      </c>
+      <c r="Q31">
         <v>54</v>
       </c>
-      <c r="E31" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" t="s">
-        <v>128</v>
-      </c>
-      <c r="G31" t="s">
-        <v>136</v>
-      </c>
-      <c r="H31" t="s">
-        <v>158</v>
-      </c>
-      <c r="I31" t="s">
-        <v>164</v>
-      </c>
-      <c r="J31">
-        <v>30</v>
-      </c>
-      <c r="K31">
-        <v>16</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>193</v>
-      </c>
-      <c r="P31">
-        <v>18</v>
-      </c>
-      <c r="Q31">
-        <v>48</v>
-      </c>
       <c r="R31">
         <v>0</v>
       </c>
@@ -3371,51 +3356,51 @@
         <v>90</v>
       </c>
       <c r="U31">
-        <v>6798</v>
+        <v>2977</v>
       </c>
       <c r="V31" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="W31">
         <v>2</v>
       </c>
       <c r="X31">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:24">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G32" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="H32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I32" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K32">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -3427,13 +3412,13 @@
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P32">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -3445,51 +3430,51 @@
         <v>90</v>
       </c>
       <c r="U32">
-        <v>15441</v>
+        <v>12257</v>
       </c>
       <c r="V32" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="X32">
-        <v>127.17</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="33" spans="1:24">
       <c r="A33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E33" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F33" t="s">
         <v>130</v>
       </c>
       <c r="G33" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H33" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I33" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J33">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3501,13 +3486,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="P33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -3519,69 +3504,69 @@
         <v>90</v>
       </c>
       <c r="U33">
-        <v>9638</v>
+        <v>16062</v>
       </c>
       <c r="V33" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="W33">
         <v>2</v>
       </c>
       <c r="X33">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:24">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="F34" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G34" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="H34" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I34" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="J34">
+        <v>10</v>
+      </c>
+      <c r="K34">
+        <v>7</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>193</v>
+      </c>
+      <c r="P34">
         <v>8</v>
       </c>
-      <c r="K34">
-        <v>154</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34" t="s">
-        <v>195</v>
-      </c>
-      <c r="P34">
-        <v>162</v>
-      </c>
       <c r="Q34">
-        <v>250</v>
+        <v>18</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -3593,16 +3578,16 @@
         <v>90</v>
       </c>
       <c r="U34">
-        <v>15441</v>
+        <v>16857</v>
       </c>
       <c r="V34" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="W34">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="X34">
-        <v>319.12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:24">
@@ -3610,52 +3595,52 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
         <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E35" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F35" t="s">
         <v>130</v>
       </c>
       <c r="G35" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H35" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I35" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="J35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N35">
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P35">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -3667,54 +3652,54 @@
         <v>90</v>
       </c>
       <c r="U35">
-        <v>16989</v>
+        <v>16857</v>
       </c>
       <c r="V35" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="W35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:24">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
         <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E36" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G36" t="s">
         <v>146</v>
       </c>
       <c r="H36" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I36" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J36">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K36">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -3723,13 +3708,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="P36">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="Q36">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -3741,69 +3726,69 @@
         <v>90</v>
       </c>
       <c r="U36">
-        <v>16857</v>
+        <v>15134</v>
       </c>
       <c r="V36" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="W36">
         <v>2</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:24">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F37" t="s">
         <v>130</v>
       </c>
       <c r="G37" t="s">
+        <v>147</v>
+      </c>
+      <c r="H37" t="s">
+        <v>156</v>
+      </c>
+      <c r="I37" t="s">
+        <v>165</v>
+      </c>
+      <c r="J37">
+        <v>12</v>
+      </c>
+      <c r="K37">
+        <v>74</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" t="s">
+        <v>195</v>
+      </c>
+      <c r="P37">
         <v>146</v>
       </c>
-      <c r="H37" t="s">
-        <v>158</v>
-      </c>
-      <c r="I37" t="s">
-        <v>167</v>
-      </c>
-      <c r="J37">
-        <v>10</v>
-      </c>
-      <c r="K37">
-        <v>5</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37" t="s">
-        <v>198</v>
-      </c>
-      <c r="P37">
-        <v>10</v>
-      </c>
       <c r="Q37">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -3815,51 +3800,51 @@
         <v>90</v>
       </c>
       <c r="U37">
-        <v>16857</v>
+        <v>9638</v>
       </c>
       <c r="V37" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="W37">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="X37">
-        <v>17</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:24">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="F38" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G38" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="H38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I38" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J38">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -3871,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P38">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q38">
         <v>56</v>
@@ -3889,16 +3874,16 @@
         <v>90</v>
       </c>
       <c r="U38">
-        <v>10189</v>
+        <v>15441</v>
       </c>
       <c r="V38" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="W38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X38">
-        <v>131</v>
+        <v>214.17</v>
       </c>
     </row>
     <row r="39" spans="1:24">
@@ -3912,28 +3897,28 @@
         <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E39" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G39" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H39" t="s">
+        <v>156</v>
+      </c>
+      <c r="I39" t="s">
         <v>158</v>
       </c>
-      <c r="I39" t="s">
-        <v>166</v>
-      </c>
       <c r="J39">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K39">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -3945,13 +3930,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P39">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="Q39">
-        <v>230</v>
+        <v>314</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -3963,51 +3948,51 @@
         <v>90</v>
       </c>
       <c r="U39">
-        <v>9638</v>
+        <v>15441</v>
       </c>
       <c r="V39" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="W39">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="X39">
-        <v>100</v>
+        <v>500.25</v>
       </c>
     </row>
     <row r="40" spans="1:24">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C40" t="s">
         <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E40" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="F40" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G40" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="H40" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I40" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K40">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4019,13 +4004,13 @@
         <v>0</v>
       </c>
       <c r="O40" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P40">
-        <v>38</v>
+        <v>236</v>
       </c>
       <c r="Q40">
-        <v>56</v>
+        <v>368</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -4037,51 +4022,51 @@
         <v>90</v>
       </c>
       <c r="U40">
-        <v>15441</v>
+        <v>9379</v>
       </c>
       <c r="V40" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="W40">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="X40">
-        <v>94.17</v>
+        <v>760</v>
       </c>
     </row>
     <row r="41" spans="1:24">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
         <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G41" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J41">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4093,13 +4078,13 @@
         <v>0</v>
       </c>
       <c r="O41" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="P41">
-        <v>202</v>
+        <v>10</v>
       </c>
       <c r="Q41">
-        <v>314</v>
+        <v>15</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -4111,51 +4096,51 @@
         <v>90</v>
       </c>
       <c r="U41">
-        <v>15441</v>
+        <v>15</v>
       </c>
       <c r="V41" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="W41">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="X41">
-        <v>50.25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:24">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
         <v>32</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E42" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H42" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I42" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K42">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4167,13 +4152,13 @@
         <v>0</v>
       </c>
       <c r="O42" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P42">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="Q42">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -4185,52 +4170,52 @@
         <v>90</v>
       </c>
       <c r="U42">
-        <v>10885</v>
+        <v>15134</v>
       </c>
       <c r="V42" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="W42">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X42">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:24">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E43" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G43" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="H43" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I43" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J43">
+        <v>6</v>
+      </c>
+      <c r="K43">
         <v>12</v>
       </c>
-      <c r="K43">
-        <v>181</v>
-      </c>
       <c r="L43">
         <v>0</v>
       </c>
@@ -4241,13 +4226,13 @@
         <v>0</v>
       </c>
       <c r="O43" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="P43">
-        <v>236</v>
+        <v>14</v>
       </c>
       <c r="Q43">
-        <v>368</v>
+        <v>20</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -4259,16 +4244,16 @@
         <v>90</v>
       </c>
       <c r="U43">
-        <v>9379</v>
+        <v>15441</v>
       </c>
       <c r="V43" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="W43">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="X43">
-        <v>760</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:24">
@@ -4279,31 +4264,31 @@
         <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="E44" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="F44" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G44" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H44" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I44" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4315,13 +4300,13 @@
         <v>0</v>
       </c>
       <c r="O44" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="P44">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="Q44">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -4333,48 +4318,48 @@
         <v>90</v>
       </c>
       <c r="U44">
-        <v>15</v>
+        <v>16900</v>
       </c>
       <c r="V44" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="W44">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="X44">
-        <v>58</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="45" spans="1:24">
       <c r="A45" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E45" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F45" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G45" t="s">
         <v>149</v>
       </c>
       <c r="H45" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I45" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J45">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K45">
         <v>26</v>
@@ -4389,13 +4374,13 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P45">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Q45">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -4407,33 +4392,33 @@
         <v>90</v>
       </c>
       <c r="U45">
-        <v>15134</v>
+        <v>12257</v>
       </c>
       <c r="V45" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="W45">
         <v>2</v>
       </c>
       <c r="X45">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:24">
       <c r="A46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C46" t="s">
         <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E46" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F46" t="s">
         <v>130</v>
@@ -4442,16 +4427,16 @@
         <v>150</v>
       </c>
       <c r="H46" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I46" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J46">
         <v>12</v>
       </c>
       <c r="K46">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4463,13 +4448,13 @@
         <v>0</v>
       </c>
       <c r="O46" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P46">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="Q46">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -4481,51 +4466,51 @@
         <v>90</v>
       </c>
       <c r="U46">
-        <v>10181</v>
+        <v>4131</v>
       </c>
       <c r="V46" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="W46">
         <v>2</v>
       </c>
       <c r="X46">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:24">
       <c r="A47" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C47" t="s">
         <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E47" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F47" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G47" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H47" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I47" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J47">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K47">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -4537,13 +4522,13 @@
         <v>0</v>
       </c>
       <c r="O47" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P47">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="Q47">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -4555,16 +4540,16 @@
         <v>90</v>
       </c>
       <c r="U47">
-        <v>15441</v>
+        <v>15520</v>
       </c>
       <c r="V47" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="W47">
         <v>2</v>
       </c>
       <c r="X47">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:24">
@@ -4578,28 +4563,28 @@
         <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E48" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F48" t="s">
         <v>130</v>
       </c>
       <c r="G48" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="H48" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I48" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="J48">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="K48">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4611,13 +4596,13 @@
         <v>0</v>
       </c>
       <c r="O48" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P48">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Q48">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -4629,16 +4614,16 @@
         <v>90</v>
       </c>
       <c r="U48">
-        <v>6703</v>
+        <v>3527</v>
       </c>
       <c r="V48" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="W48">
         <v>2</v>
       </c>
       <c r="X48">
-        <v>19</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:24">
@@ -4646,34 +4631,34 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C49" t="s">
         <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E49" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="F49" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G49" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="H49" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I49" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="J49">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -4685,13 +4670,13 @@
         <v>0</v>
       </c>
       <c r="O49" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="P49">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="Q49">
-        <v>338</v>
+        <v>15</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -4703,16 +4688,16 @@
         <v>90</v>
       </c>
       <c r="U49">
-        <v>10142</v>
+        <v>15</v>
       </c>
       <c r="V49" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="W49">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="X49">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:24">
@@ -4720,34 +4705,34 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
         <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E50" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F50" t="s">
         <v>130</v>
       </c>
       <c r="G50" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="H50" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J50">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K50">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -4759,13 +4744,13 @@
         <v>0</v>
       </c>
       <c r="O50" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="P50">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="Q50">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -4777,16 +4762,16 @@
         <v>90</v>
       </c>
       <c r="U50">
-        <v>16900</v>
+        <v>7995</v>
       </c>
       <c r="V50" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="W50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X50">
-        <v>2022</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:24">
@@ -4797,31 +4782,31 @@
         <v>31</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D51" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E51" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F51" t="s">
         <v>130</v>
       </c>
       <c r="G51" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H51" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I51" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J51">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K51">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -4833,13 +4818,13 @@
         <v>0</v>
       </c>
       <c r="O51" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P51">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q51">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -4851,51 +4836,51 @@
         <v>90</v>
       </c>
       <c r="U51">
-        <v>4131</v>
+        <v>10124</v>
       </c>
       <c r="V51" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="W51">
         <v>2</v>
       </c>
       <c r="X51">
-        <v>37</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:24">
       <c r="A52" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D52" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E52" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F52" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G52" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H52" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I52" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="J52">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K52">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -4907,13 +4892,13 @@
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="P52">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="Q52">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -4925,16 +4910,16 @@
         <v>90</v>
       </c>
       <c r="U52">
-        <v>15520</v>
+        <v>15134</v>
       </c>
       <c r="V52" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="W52">
         <v>2</v>
       </c>
       <c r="X52">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:24">
@@ -4942,34 +4927,34 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="E53" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="F53" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G53" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="H53" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I53" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J53">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K53">
-        <v>49</v>
+        <v>-3</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -4981,13 +4966,13 @@
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="P53">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="Q53">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -4999,51 +4984,51 @@
         <v>90</v>
       </c>
       <c r="U53">
-        <v>10189</v>
+        <v>15</v>
       </c>
       <c r="V53" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="W53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X53">
-        <v>131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:24">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D54" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="E54" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="F54" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G54" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H54" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I54" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="J54">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K54">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5055,13 +5040,13 @@
         <v>0</v>
       </c>
       <c r="O54" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="P54">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="Q54">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -5073,51 +5058,51 @@
         <v>90</v>
       </c>
       <c r="U54">
-        <v>3527</v>
+        <v>15441</v>
       </c>
       <c r="V54" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="W54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X54">
-        <v>82</v>
+        <v>214.17</v>
       </c>
     </row>
     <row r="55" spans="1:24">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D55" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E55" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F55" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G55" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H55" t="s">
+        <v>156</v>
+      </c>
+      <c r="I55" t="s">
         <v>158</v>
       </c>
-      <c r="I55" t="s">
-        <v>161</v>
-      </c>
       <c r="J55">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5129,13 +5114,13 @@
         <v>0</v>
       </c>
       <c r="O55" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="P55">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="Q55">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -5147,90 +5132,90 @@
         <v>90</v>
       </c>
       <c r="U55">
-        <v>15</v>
+        <v>15441</v>
       </c>
       <c r="V55" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="W55">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="X55">
-        <v>58</v>
+        <v>200.25</v>
       </c>
     </row>
     <row r="56" spans="1:24">
       <c r="A56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C56" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="E56" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="F56" t="s">
         <v>130</v>
       </c>
       <c r="G56" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="H56" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I56" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="J56">
+        <v>6</v>
+      </c>
+      <c r="K56">
+        <v>144</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56" t="s">
+        <v>210</v>
+      </c>
+      <c r="P56">
+        <v>182</v>
+      </c>
+      <c r="Q56">
+        <v>284</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>90</v>
+      </c>
+      <c r="U56">
+        <v>15441</v>
+      </c>
+      <c r="V56" t="s">
+        <v>216</v>
+      </c>
+      <c r="W56">
         <v>24</v>
       </c>
-      <c r="K56">
-        <v>15</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56" t="s">
-        <v>215</v>
-      </c>
-      <c r="P56">
-        <v>18</v>
-      </c>
-      <c r="Q56">
-        <v>42</v>
-      </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
-        <v>0</v>
-      </c>
-      <c r="T56">
-        <v>90</v>
-      </c>
-      <c r="U56">
-        <v>10124</v>
-      </c>
-      <c r="V56" t="s">
-        <v>245</v>
-      </c>
-      <c r="W56">
-        <v>2</v>
-      </c>
       <c r="X56">
-        <v>55</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:24">
@@ -5241,7 +5226,7 @@
         <v>30</v>
       </c>
       <c r="C57" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D57" t="s">
         <v>50</v>
@@ -5256,10 +5241,10 @@
         <v>133</v>
       </c>
       <c r="H57" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I57" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -5277,13 +5262,13 @@
         <v>0</v>
       </c>
       <c r="O57" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P57">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q57">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -5298,10 +5283,10 @@
         <v>15</v>
       </c>
       <c r="V57" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="W57">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="X57">
         <v>58</v>
@@ -5309,37 +5294,37 @@
     </row>
     <row r="58" spans="1:24">
       <c r="A58" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C58" t="s">
         <v>46</v>
       </c>
       <c r="D58" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E58" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F58" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G58" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H58" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I58" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="J58">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K58">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5351,13 +5336,13 @@
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="P58">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="Q58">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -5369,51 +5354,51 @@
         <v>90</v>
       </c>
       <c r="U58">
-        <v>15441</v>
+        <v>10885</v>
       </c>
       <c r="V58" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="W58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X58">
-        <v>50.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:24">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C59" t="s">
         <v>46</v>
       </c>
       <c r="D59" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E59" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="F59" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G59" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="H59" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I59" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5425,13 +5410,13 @@
         <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="P59">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="Q59">
-        <v>15</v>
+        <v>268</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -5443,51 +5428,51 @@
         <v>90</v>
       </c>
       <c r="U59">
-        <v>15</v>
+        <v>15441</v>
       </c>
       <c r="V59" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="W59">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="X59">
-        <v>58</v>
+        <v>552.67</v>
       </c>
     </row>
     <row r="60" spans="1:24">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D60" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="E60" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="F60" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G60" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H60" t="s">
+        <v>156</v>
+      </c>
+      <c r="I60" t="s">
         <v>158</v>
       </c>
-      <c r="I60" t="s">
-        <v>166</v>
-      </c>
       <c r="J60">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K60">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5499,13 +5484,13 @@
         <v>0</v>
       </c>
       <c r="O60" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="P60">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="Q60">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -5517,51 +5502,51 @@
         <v>90</v>
       </c>
       <c r="U60">
-        <v>10885</v>
+        <v>15441</v>
       </c>
       <c r="V60" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="W60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X60">
-        <v>6</v>
+        <v>200.25</v>
       </c>
     </row>
     <row r="61" spans="1:24">
       <c r="A61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D61" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="E61" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="F61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G61" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="H61" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I61" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J61">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K61">
-        <v>-3</v>
+        <v>52</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -5573,13 +5558,13 @@
         <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="P61">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="Q61">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="R61">
         <v>0</v>
@@ -5591,51 +5576,51 @@
         <v>90</v>
       </c>
       <c r="U61">
-        <v>10885</v>
+        <v>10721</v>
       </c>
       <c r="V61" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="W61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X61">
-        <v>23</v>
+        <v>340.33</v>
       </c>
     </row>
     <row r="62" spans="1:24">
       <c r="A62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C62" t="s">
         <v>47</v>
       </c>
       <c r="D62" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E62" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F62" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G62" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="H62" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I62" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J62">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K62">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -5647,13 +5632,13 @@
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="P62">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="Q62">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="R62">
         <v>0</v>
@@ -5665,16 +5650,16 @@
         <v>90</v>
       </c>
       <c r="U62">
-        <v>15441</v>
+        <v>10321</v>
       </c>
       <c r="V62" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="W62">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X62">
-        <v>50.25</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="63" spans="1:24">
@@ -5688,46 +5673,46 @@
         <v>47</v>
       </c>
       <c r="D63" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="E63" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="F63" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G63" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="H63" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I63" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <v>4</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63" t="s">
+        <v>172</v>
+      </c>
+      <c r="P63">
         <v>5</v>
       </c>
-      <c r="K63">
-        <v>9</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63" t="s">
-        <v>220</v>
-      </c>
-      <c r="P63">
-        <v>11</v>
-      </c>
       <c r="Q63">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -5739,16 +5724,16 @@
         <v>90</v>
       </c>
       <c r="U63">
-        <v>10321</v>
+        <v>15</v>
       </c>
       <c r="V63" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="W63">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X63">
-        <v>36.4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:24">
@@ -5762,10 +5747,10 @@
         <v>47</v>
       </c>
       <c r="D64" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E64" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F64" t="s">
         <v>129</v>
@@ -5774,16 +5759,16 @@
         <v>133</v>
       </c>
       <c r="H64" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I64" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J64">
         <v>1</v>
       </c>
       <c r="K64">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -5795,13 +5780,13 @@
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P64">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q64">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R64">
         <v>0</v>
@@ -5816,86 +5801,12 @@
         <v>15</v>
       </c>
       <c r="V64" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="W64">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="X64">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="65" spans="1:24">
-      <c r="A65" t="s">
-        <v>25</v>
-      </c>
-      <c r="B65" t="s">
-        <v>30</v>
-      </c>
-      <c r="C65" t="s">
-        <v>47</v>
-      </c>
-      <c r="D65" t="s">
-        <v>50</v>
-      </c>
-      <c r="E65" t="s">
-        <v>90</v>
-      </c>
-      <c r="F65" t="s">
-        <v>129</v>
-      </c>
-      <c r="G65" t="s">
-        <v>133</v>
-      </c>
-      <c r="H65" t="s">
-        <v>158</v>
-      </c>
-      <c r="I65" t="s">
-        <v>161</v>
-      </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65" t="s">
-        <v>174</v>
-      </c>
-      <c r="P65">
-        <v>10</v>
-      </c>
-      <c r="Q65">
-        <v>15</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>90</v>
-      </c>
-      <c r="U65">
-        <v>15</v>
-      </c>
-      <c r="V65" t="s">
-        <v>222</v>
-      </c>
-      <c r="W65">
-        <v>15</v>
-      </c>
-      <c r="X65">
         <v>58</v>
       </c>
     </row>

--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Downloads\Equipes_Agentes\Aplicativos\GAM\bd_saida\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38954F92-A5E5-44C7-ABC2-AA896EFFD2AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8E43AE-FC63-42EE-A3B2-EAB24F3EBC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Z$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Z$58</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="305">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -108,39 +108,33 @@
     <t>Estq_CD_cx</t>
   </si>
   <si>
+    <t>MERCEARIA</t>
+  </si>
+  <si>
     <t>BEBIDAS</t>
   </si>
   <si>
+    <t>PERFUMARIA E LIMPEZA</t>
+  </si>
+  <si>
     <t>PERECIVEIS</t>
   </si>
   <si>
-    <t>MERCEARIA</t>
-  </si>
-  <si>
-    <t>PERFUMARIA E LIMPEZA</t>
-  </si>
-  <si>
-    <t>PRODUTOS PET</t>
+    <t>NIDAL TUBASI</t>
   </si>
   <si>
     <t>NICOLAS AUGUSTO P. BORGES</t>
   </si>
   <si>
+    <t>WETER SONNENFELDET</t>
+  </si>
+  <si>
+    <t>JOAO BATISTA</t>
+  </si>
+  <si>
     <t>SANDRO MARTINS VIANNA</t>
   </si>
   <si>
-    <t>NIDAL TUBASI</t>
-  </si>
-  <si>
-    <t>WETER SONNENFELDET</t>
-  </si>
-  <si>
-    <t>JOAO BATISTA</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
@@ -150,9 +144,6 @@
     <t>004</t>
   </si>
   <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>006</t>
   </si>
   <si>
@@ -180,292 +171,481 @@
     <t>018</t>
   </si>
   <si>
+    <t>REFRIG PEPSI PET 3L</t>
+  </si>
+  <si>
+    <t>MASSA C OVOS NORDESTE 500G</t>
+  </si>
+  <si>
+    <t>FARINHA TAPIOCA DINDA 400G TRAD</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 1 5L</t>
+  </si>
+  <si>
+    <t>CERV HEINEKEN ZERO LN 330ML</t>
+  </si>
+  <si>
+    <t>ERVA MATE PONCHE VERDE 1KG LAMINADO</t>
+  </si>
+  <si>
+    <t>INSET AERO RAID 420ML</t>
+  </si>
+  <si>
+    <t>AGUA SABORIZ H2OH 500ML</t>
+  </si>
+  <si>
+    <t>VH COUNTRY WINE BORDO 750ML</t>
+  </si>
+  <si>
+    <t>CONFEITO BIBS CHOC BCO 40G</t>
+  </si>
+  <si>
+    <t>CONFEITO BIBS PASSAS 40G</t>
+  </si>
+  <si>
+    <t>CONFEITO BIBS PTO BCO 40G</t>
+  </si>
+  <si>
+    <t>FEIJAO PRETO CALDO OURO 500G</t>
+  </si>
+  <si>
+    <t>PEPINO CONSERVA ODERICH VD 300G</t>
+  </si>
+  <si>
+    <t>KETCHUP ODERICH BISN 400G</t>
+  </si>
+  <si>
+    <t>FERM PO BIOL GOOD INSTANT SH 10G</t>
+  </si>
+  <si>
+    <t>SAB BAR FARNESE 180G</t>
+  </si>
+  <si>
+    <t>AMEIXA UNIAGRO PTA C CAROCO KG</t>
+  </si>
+  <si>
+    <t>AMEIXA UNIAGRO PTA S CAROCO KG</t>
+  </si>
+  <si>
+    <t>PASSAS UVA UNIAGRO PTA KG</t>
+  </si>
+  <si>
+    <t>BISC AGUA SAL ORQUIDEA 665GR</t>
+  </si>
+  <si>
+    <t>ATUM RALADO NAUTIQUE 170G</t>
+  </si>
+  <si>
+    <t>AGUA GASEIFICADA CRYSTAL PET 510ML</t>
+  </si>
+  <si>
+    <t>FARINHA TRIGO PANFACIL TP1 1KG</t>
+  </si>
+  <si>
+    <t>REFRIG COCA COLA</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA LARANJA</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA UVA</t>
+  </si>
+  <si>
+    <t>ACHOC PO APTI SH 200G</t>
+  </si>
+  <si>
+    <t>SALG KEVYTOS SHOW 38G BACON</t>
+  </si>
+  <si>
+    <t>SALG OBBA 100G PRESUNTO</t>
+  </si>
+  <si>
+    <t>SALG OBBA 100G REQUEIJAO</t>
+  </si>
+  <si>
+    <t>CERV BUDWEISER ZERO LN 330ML</t>
+  </si>
+  <si>
+    <t>REFRIG PET COCA COLA 3L</t>
+  </si>
+  <si>
+    <t>CERV AMSTEL LAGER LT 473ML</t>
+  </si>
+  <si>
     <t>REFRIG FANTA</t>
   </si>
   <si>
-    <t>LEITE UHT TIROL C TAMP INT 1L</t>
-  </si>
-  <si>
-    <t>AGUA GASEIFICADA CRYSTAL PET 510ML</t>
-  </si>
-  <si>
-    <t>CERV STELLA ARTOIS LN 330ML</t>
-  </si>
-  <si>
-    <t>AGUARD 51 VD 965ML</t>
-  </si>
-  <si>
-    <t>CHOC BARRA GAROTO 80G</t>
-  </si>
-  <si>
-    <t>ARROZ BCO SANO OURO TP1 5KG</t>
-  </si>
-  <si>
-    <t>CERV SKOL BEATS RED LT 269ML MIX</t>
-  </si>
-  <si>
-    <t>CERV STELLA ARTOIS LT 473ML P GOLD</t>
-  </si>
-  <si>
-    <t>BEBIDA NESCAFE PRO ENERGY 270ML</t>
+    <t>MIST P BOLO APTI 400G</t>
+  </si>
+  <si>
+    <t>AZEIT OLIV COCINERO EXT VG 250ML</t>
   </si>
   <si>
     <t>CHOC STICK 25G</t>
   </si>
   <si>
-    <t>TINT COR E TON</t>
+    <t>ERVILHA FUGINI SH 170G</t>
+  </si>
+  <si>
+    <t>SALG OBBA 100G</t>
+  </si>
+  <si>
+    <t>ALCOOL 46 ARAUCARIA 1L</t>
   </si>
   <si>
     <t>ENERG MONSTER LT 473ML</t>
   </si>
   <si>
-    <t>LEITE UHT NINHO INT 1L</t>
-  </si>
-  <si>
-    <t>FARINHA TRIGO ROSESOL 1KG</t>
-  </si>
-  <si>
-    <t>ARROZ BCO SABOROSO TP1 5KG</t>
-  </si>
-  <si>
-    <t>CHOC LACTA RECH 98G</t>
-  </si>
-  <si>
-    <t>ARROZ BCO SANO T1 2K</t>
-  </si>
-  <si>
-    <t>ERVILHA FUGINI SH 170G</t>
-  </si>
-  <si>
-    <t>ACHOC NESQUIK LT 380G</t>
-  </si>
-  <si>
-    <t>SH SEDA 325ML</t>
-  </si>
-  <si>
-    <t>FRALDA BABYSEC ULTRA JUMBINHO G</t>
-  </si>
-  <si>
-    <t>CHOC BARRA GAROTO RECH BATON 90G</t>
-  </si>
-  <si>
-    <t>BISC ORQUIDEA 320G INTEG</t>
-  </si>
-  <si>
-    <t>RACAO DOG CHOW SH 85G</t>
-  </si>
-  <si>
-    <t>LIMP CONC SAIF 120ML</t>
-  </si>
-  <si>
-    <t>MOSTARDA ODERICH TRADICIONAL 190G</t>
-  </si>
-  <si>
-    <t>MAS ESPAG ISABELA SEMOLA 400G</t>
-  </si>
-  <si>
-    <t>SARDINHA NAUTIQUE 125G</t>
-  </si>
-  <si>
-    <t>LEITE UHT ELEGE INT 1L</t>
-  </si>
-  <si>
-    <t>LAVA ROUPA LIQ APYCE SH 800ML</t>
-  </si>
-  <si>
-    <t>ACUCAR MASCAVO GASPARIN 1KG</t>
+    <t>AMAC GOTA LIMPA 5L</t>
+  </si>
+  <si>
+    <t>REFRIG CHARRUA GUARANA PET 3L</t>
+  </si>
+  <si>
+    <t>BISC AGUA E SAL ZEZE 200G</t>
+  </si>
+  <si>
+    <t>BISC RECH SAPECA 120G</t>
+  </si>
+  <si>
+    <t>CAFE VACUO STARBUCKS 250G</t>
+  </si>
+  <si>
+    <t>FARINHA TRIGO NORDESTE 5KG</t>
+  </si>
+  <si>
+    <t>840</t>
+  </si>
+  <si>
+    <t>2856</t>
+  </si>
+  <si>
+    <t>37075</t>
+  </si>
+  <si>
+    <t>39261</t>
+  </si>
+  <si>
+    <t>39262</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>2637</t>
+  </si>
+  <si>
+    <t>6340</t>
+  </si>
+  <si>
+    <t>6828</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>1678</t>
+  </si>
+  <si>
+    <t>1679</t>
+  </si>
+  <si>
+    <t>1681</t>
+  </si>
+  <si>
+    <t>2329</t>
+  </si>
+  <si>
+    <t>2447</t>
+  </si>
+  <si>
+    <t>2497</t>
+  </si>
+  <si>
+    <t>3512</t>
+  </si>
+  <si>
+    <t>10145</t>
+  </si>
+  <si>
+    <t>10555</t>
+  </si>
+  <si>
+    <t>10556</t>
+  </si>
+  <si>
+    <t>11671</t>
+  </si>
+  <si>
+    <t>13277</t>
+  </si>
+  <si>
+    <t>38964</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>2722</t>
+  </si>
+  <si>
+    <t>889</t>
+  </si>
+  <si>
+    <t>896</t>
+  </si>
+  <si>
+    <t>899</t>
+  </si>
+  <si>
+    <t>2942</t>
+  </si>
+  <si>
+    <t>3181</t>
+  </si>
+  <si>
+    <t>3289</t>
+  </si>
+  <si>
+    <t>3298</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>835</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>806</t>
+  </si>
+  <si>
+    <t>3704</t>
+  </si>
+  <si>
+    <t>6339</t>
+  </si>
+  <si>
+    <t>948</t>
+  </si>
+  <si>
+    <t>1369</t>
+  </si>
+  <si>
+    <t>1371</t>
+  </si>
+  <si>
+    <t>2367</t>
+  </si>
+  <si>
+    <t>3272</t>
+  </si>
+  <si>
+    <t>6341</t>
+  </si>
+  <si>
+    <t>12308</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>4212</t>
+  </si>
+  <si>
+    <t>33255</t>
+  </si>
+  <si>
+    <t>386</t>
   </si>
   <si>
     <t>812</t>
   </si>
   <si>
-    <t>6783</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>293</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>1276</t>
-  </si>
-  <si>
-    <t>1280</t>
-  </si>
-  <si>
-    <t>2134</t>
-  </si>
-  <si>
-    <t>3871</t>
-  </si>
-  <si>
-    <t>3872</t>
-  </si>
-  <si>
-    <t>33437</t>
-  </si>
-  <si>
-    <t>1369</t>
-  </si>
-  <si>
-    <t>1371</t>
-  </si>
-  <si>
-    <t>8613</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t>6801</t>
-  </si>
-  <si>
-    <t>2737</t>
-  </si>
-  <si>
-    <t>2177</t>
-  </si>
-  <si>
-    <t>1262</t>
-  </si>
-  <si>
-    <t>2096</t>
-  </si>
-  <si>
-    <t>2367</t>
-  </si>
-  <si>
-    <t>2934</t>
-  </si>
-  <si>
-    <t>8345</t>
-  </si>
-  <si>
-    <t>9539</t>
-  </si>
-  <si>
-    <t>37860</t>
-  </si>
-  <si>
-    <t>1394</t>
-  </si>
-  <si>
-    <t>3997</t>
-  </si>
-  <si>
-    <t>33678</t>
-  </si>
-  <si>
-    <t>3092</t>
-  </si>
-  <si>
-    <t>20609</t>
-  </si>
-  <si>
-    <t>2451</t>
-  </si>
-  <si>
-    <t>6781</t>
-  </si>
-  <si>
-    <t>36264</t>
-  </si>
-  <si>
-    <t>33213</t>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>1454</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2760</t>
+  </si>
+  <si>
+    <t>MASSA C OVOS NORDESTE 500G PENNE</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 1 5L FRUTAS VERM</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 1 5L ABACAXI C HORT</t>
+  </si>
+  <si>
+    <t>INSET AERO RAID 420ML BASE AGUA</t>
+  </si>
+  <si>
+    <t>AGUA SABORIZ H2OH 500ML LIMONETO</t>
+  </si>
+  <si>
+    <t>VH COUNTRY WINE BORDO 750ML SV</t>
+  </si>
+  <si>
+    <t>PEPINO CONSERVA ODERICH VD 300G TRAD</t>
+  </si>
+  <si>
+    <t>KETCHUP ODERICH BISN 400G TRAD</t>
+  </si>
+  <si>
+    <t>SAB BAR FARNESE 180G ERV DOCE VERB</t>
+  </si>
+  <si>
+    <t>ATUM RALADO NAUTIQUE 170G MOLHO TOMATE</t>
+  </si>
+  <si>
+    <t>AGUA GASEIFICADA CRYSTAL PET 510ML FRUTAS VERMELHA</t>
+  </si>
+  <si>
+    <t>REFRIG COCA COLA LT 350ML</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA LARANJA LT 350ML</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA UVA LT 350ML</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA LARANJA PET 2L</t>
+  </si>
+  <si>
+    <t>MIST P BOLO APTI 400G CHOC</t>
+  </si>
+  <si>
+    <t>INSET AERO RAID 420ML BARATA FORMIGA</t>
+  </si>
+  <si>
+    <t>CHOC STICK 25G OURO BCO</t>
+  </si>
+  <si>
+    <t>CHOC STICK 25G SONHO VALSA</t>
+  </si>
+  <si>
+    <t>SALG OBBA 100G PICANHA</t>
+  </si>
+  <si>
+    <t>INSET AERO RAID 420ML CITRONELA</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML GREEN</t>
+  </si>
+  <si>
+    <t>AMAC GOTA LIMPA 5L DELICATA</t>
+  </si>
+  <si>
+    <t>REFRIG CHARRUA PET 3L GUARANA</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML ABSOLUT ZERO</t>
   </si>
   <si>
     <t>REFRIG FANTA UVA PET 2L</t>
   </si>
   <si>
-    <t>AGUA GASEIFICADA CRYSTAL PET 510ML FRUTAS VERMELHA</t>
-  </si>
-  <si>
-    <t>CHOC BARRA GAROTO 80G MEIO AMARGO</t>
-  </si>
-  <si>
-    <t>CHOC BARRA GAROTO 80G AO LEITE</t>
-  </si>
-  <si>
-    <t>BEBIDA NESCAFE PRO ENERGY 270ML CHOCOCINO</t>
-  </si>
-  <si>
-    <t>CHOC STICK 25G OURO BCO</t>
-  </si>
-  <si>
-    <t>CHOC STICK 25G SONHO VALSA</t>
-  </si>
-  <si>
-    <t>TINT COR E TON LOURO CZ M 7 1</t>
-  </si>
-  <si>
-    <t>ENERG MONSTER LT 473ML GREEN</t>
-  </si>
-  <si>
-    <t>CHOC LACTA RECH 98G OURO BRANCO</t>
-  </si>
-  <si>
-    <t>ACHOC NESQUIK LT 380G MORANGO</t>
-  </si>
-  <si>
-    <t>SH SEDA 325ML LISO PERFEITO</t>
-  </si>
-  <si>
-    <t>FRALDA BABYSEC ULTRA JUMBINHO G 16UN</t>
-  </si>
-  <si>
-    <t>RACAO DOG CHOW SH 85G FILH FGO LEITE</t>
-  </si>
-  <si>
-    <t>LIMP CONC SAIF 120ML KAIAK</t>
-  </si>
-  <si>
-    <t>MOSTARDA ODERICH TRADICIONAL 190G BISNAGA</t>
-  </si>
-  <si>
-    <t>SARDINHA NAUTIQUE 125G MOLHO DE TOMATE</t>
-  </si>
-  <si>
-    <t>LAVA ROUPA LIQ APYCE SH 800ML SUPER ACAO</t>
+    <t>BISC RECH SAPECA 120G DOCE LEITE</t>
+  </si>
+  <si>
+    <t>CAFE VACUO STARBUCKS 250G PIKE PLACE</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
-    <t>M</t>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>16/12/2024</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>26/08/2026</t>
+  </si>
+  <si>
+    <t>01/10/2024</t>
+  </si>
+  <si>
+    <t>12/12/2024</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>28/09/2024</t>
+  </si>
+  <si>
+    <t>21/11/2024</t>
+  </si>
+  <si>
+    <t>07/12/2024</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>10/12/2024</t>
+  </si>
+  <si>
+    <t>28/12/2024</t>
+  </si>
+  <si>
+    <t>11/06/2025</t>
+  </si>
+  <si>
+    <t>18/07/2026</t>
+  </si>
+  <si>
+    <t>21/09/2024</t>
+  </si>
+  <si>
+    <t>13/12/2024</t>
+  </si>
+  <si>
+    <t>22/10/2024</t>
+  </si>
+  <si>
+    <t>17/12/2024</t>
+  </si>
+  <si>
+    <t>20/12/2024</t>
+  </si>
+  <si>
+    <t>23/12/2024</t>
+  </si>
+  <si>
+    <t>24/12/2024</t>
+  </si>
+  <si>
+    <t>25/09/2024</t>
   </si>
   <si>
     <t>19/10/2024</t>
   </si>
   <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>21/09/2024</t>
-  </si>
-  <si>
-    <t>01/10/2024</t>
-  </si>
-  <si>
-    <t>04/10/2024</t>
-  </si>
-  <si>
-    <t>07/11/2024</t>
-  </si>
-  <si>
-    <t>04/12/2024</t>
-  </si>
-  <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
-    <t>31/07/2025</t>
+    <t>31/12/2024</t>
+  </si>
+  <si>
+    <t>25/10/2024</t>
   </si>
   <si>
     <t>09/11/2024</t>
@@ -474,250 +654,295 @@
     <t>05/10/2024</t>
   </si>
   <si>
-    <t>13/12/2024</t>
-  </si>
-  <si>
-    <t>05/12/2024</t>
-  </si>
-  <si>
-    <t>09/12/2024</t>
-  </si>
-  <si>
-    <t>17/12/2024</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>11/11/2024</t>
-  </si>
-  <si>
-    <t>19/08/2025</t>
-  </si>
-  <si>
-    <t>19/12/2024</t>
-  </si>
-  <si>
-    <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>23/06/2025</t>
+    <t>07/07/2025</t>
+  </si>
+  <si>
+    <t>28/10/2024</t>
+  </si>
+  <si>
+    <t>12/11/2024</t>
+  </si>
+  <si>
+    <t>30/11/2024</t>
+  </si>
+  <si>
+    <t>14/12/2024</t>
   </si>
   <si>
     <t>Ativo</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>36</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1359</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>461</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>2163</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>19,62</t>
+  </si>
+  <si>
+    <t>20,38</t>
+  </si>
+  <si>
+    <t>29,62</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>1473</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>1435</t>
+  </si>
+  <si>
+    <t>554</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>894</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>1479</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>509</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>133</t>
-  </si>
-  <si>
-    <t>4011</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>407</t>
-  </si>
-  <si>
-    <t>287</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>444</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2520</t>
-  </si>
-  <si>
-    <t>281</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>331</t>
-  </si>
-  <si>
-    <t>686</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>473</t>
-  </si>
-  <si>
-    <t>398</t>
-  </si>
-  <si>
-    <t>328</t>
-  </si>
-  <si>
-    <t>534</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>96</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>85</t>
   </si>
   <si>
     <t>69</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>52</t>
+    <t>CRBS AS CDD PELOTAS</t>
+  </si>
+  <si>
+    <t>MOINHO DO NORDESTE SA</t>
+  </si>
+  <si>
+    <t>ROCHA E FILHOS LTDA</t>
+  </si>
+  <si>
+    <t>BEBIDAS FRUKI LTDA</t>
+  </si>
+  <si>
+    <t>CARLOS CANCIAN E CIA LTDA</t>
+  </si>
+  <si>
+    <t>PONCHE VERDE INDL. DO MATE LTDA.</t>
+  </si>
+  <si>
+    <t>ONIZ DISTRIBUID LTDA SCJ</t>
+  </si>
+  <si>
+    <t>COOP VINICOLA AURORA LTDA</t>
+  </si>
+  <si>
+    <t>VONPAR ALIMENTOS S.A</t>
+  </si>
+  <si>
+    <t>COOP AGRICOLA MISTA NOVA PALMA LTDA</t>
+  </si>
+  <si>
+    <t>CONSERVAS ODERICH SA</t>
+  </si>
+  <si>
+    <t>FERMENTO GOOD INSTANT LTDA.</t>
+  </si>
+  <si>
+    <t>UNIAGRO -IND.E COM.DE PROD.ALIM.LTDA</t>
+  </si>
+  <si>
+    <t>TONDO S/A</t>
+  </si>
+  <si>
+    <t>SMG INDUSTRIAL LTDA</t>
   </si>
   <si>
     <t>SPAL IND BRAS BEBIDAS AS</t>
   </si>
   <si>
-    <t>LATICINIOS TIROL LTDA.</t>
-  </si>
-  <si>
-    <t>CRBS AS CDD PELOTAS</t>
-  </si>
-  <si>
-    <t>COMERCIAL DESTRO LTDA</t>
+    <t>MOINHO ESTRELA LTDA</t>
+  </si>
+  <si>
+    <t>APTI ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>DELAVY ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>FITOS ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>CAMIL ALIMENTOS S/A</t>
+  </si>
+  <si>
+    <t>TOPFLEX DISTRIBUIDOR DE ALIMENTOS</t>
+  </si>
+  <si>
+    <t>FUGINI ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>INDUSTRIA MISSIATO DE BEBIDAS LTDA</t>
+  </si>
+  <si>
+    <t>BERTOLINI INDUSTRIA QUIMICA LTDA</t>
+  </si>
+  <si>
+    <t>IRMAOS RUIVO LTDA</t>
+  </si>
+  <si>
+    <t>GERMANI ALIMENTOS LTDA</t>
   </si>
   <si>
     <t>NESTLE BRASIL LTDA</t>
-  </si>
-  <si>
-    <t>FERRUCCI E MIRANDA LTDA-EPP</t>
-  </si>
-  <si>
-    <t>TOPFLEX DISTRIBUIDOR DE ALIMENTOS</t>
-  </si>
-  <si>
-    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
-  </si>
-  <si>
-    <t>LATICINIOS BELA VISTA LTDA</t>
-  </si>
-  <si>
-    <t>MOINHOS GALOPOLIS S/A</t>
-  </si>
-  <si>
-    <t>COOPERATIVA AGROINDUSTRIAL ALEGRETE LTDA</t>
-  </si>
-  <si>
-    <t>FUGINI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>SEPAC-SERRADOS E PASTA DE CELULOSE LTDA.</t>
-  </si>
-  <si>
-    <t>TONDO S/A</t>
-  </si>
-  <si>
-    <t>MACKERDUZ IND DE PROD DE LIMPEZA LTDA</t>
-  </si>
-  <si>
-    <t>CONSERVAS ODERICH SA</t>
-  </si>
-  <si>
-    <t>M DIAS BRANCO S.A IND E COM DE ALIMENTOS</t>
-  </si>
-  <si>
-    <t>SMG INDUSTRIAL LTDA</t>
-  </si>
-  <si>
-    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
-  </si>
-  <si>
-    <t>GASPARIN CEREAIS LTDA ME</t>
   </si>
 </sst>
 </file>
@@ -1059,11 +1284,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z45"/>
+  <dimension ref="A1:Z58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="5" max="5" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -1148,43 +1373,43 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>625</v>
+        <v>652</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G2" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="I2" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="J2" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K2" t="s">
-        <v>159</v>
+        <v>214</v>
       </c>
       <c r="L2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -1196,13 +1421,13 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
       <c r="R2">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="S2">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -1214,21 +1439,21 @@
         <v>90</v>
       </c>
       <c r="W2">
-        <v>15441</v>
+        <v>9638</v>
       </c>
       <c r="X2" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="Y2">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="Z2">
-        <v>105</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
         <v>32</v>
@@ -1237,52 +1462,52 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>4695</v>
+        <v>2067</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>149</v>
       </c>
       <c r="H3" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I3" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="J3" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K3" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="L3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M3">
-        <v>446</v>
+        <v>20</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="R3">
-        <v>480</v>
+        <v>54</v>
       </c>
       <c r="S3">
-        <v>600</v>
+        <v>84</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -1294,16 +1519,16 @@
         <v>90</v>
       </c>
       <c r="W3">
-        <v>15208</v>
+        <v>10321</v>
       </c>
       <c r="X3" t="s">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="Y3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Z3">
-        <v>448.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -1311,40 +1536,40 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>189</v>
+        <v>55690</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="H4" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="I4" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="J4" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K4" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -1356,13 +1581,13 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="R4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="S4">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -1374,57 +1599,57 @@
         <v>90</v>
       </c>
       <c r="W4">
-        <v>15441</v>
+        <v>21894</v>
       </c>
       <c r="X4" t="s">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="Y4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z4">
-        <v>58</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5">
-        <v>352</v>
+        <v>64427</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="G5" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="H5" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I5" t="s">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="J5" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K5" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="L5">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -1436,13 +1661,13 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="R5">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="S5">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -1454,75 +1679,75 @@
         <v>90</v>
       </c>
       <c r="W5">
-        <v>9638</v>
+        <v>6424</v>
       </c>
       <c r="X5" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="Y5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z5">
-        <v>93</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6">
-        <v>407</v>
+        <v>64427</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="H6" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I6" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="J6" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K6" t="s">
-        <v>160</v>
+        <v>217</v>
       </c>
       <c r="L6">
+        <v>6</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>226</v>
+      </c>
+      <c r="R6">
         <v>12</v>
       </c>
-      <c r="M6">
-        <v>35</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>175</v>
-      </c>
-      <c r="R6">
-        <v>38</v>
-      </c>
       <c r="S6">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -1534,75 +1759,75 @@
         <v>90</v>
       </c>
       <c r="W6">
-        <v>10598</v>
+        <v>6424</v>
       </c>
       <c r="X6" t="s">
-        <v>213</v>
+        <v>280</v>
       </c>
       <c r="Y6">
         <v>3</v>
       </c>
       <c r="Z6">
-        <v>177</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
       </c>
       <c r="D7">
-        <v>36734</v>
+        <v>360</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G7" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="H7" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I7" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="J7" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K7" t="s">
-        <v>163</v>
+        <v>218</v>
       </c>
       <c r="L7">
+        <v>24</v>
+      </c>
+      <c r="M7">
+        <v>11</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>230</v>
+      </c>
+      <c r="R7">
         <v>16</v>
       </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>176</v>
-      </c>
-      <c r="R7">
-        <v>68</v>
-      </c>
       <c r="S7">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -1614,75 +1839,75 @@
         <v>90</v>
       </c>
       <c r="W7">
-        <v>15134</v>
+        <v>14469</v>
       </c>
       <c r="X7" t="s">
-        <v>214</v>
+        <v>281</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z7">
-        <v>93</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
       </c>
       <c r="D8">
-        <v>36734</v>
+        <v>1898</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="G8" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I8" t="s">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="J8" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K8" t="s">
-        <v>163</v>
+        <v>219</v>
       </c>
       <c r="L8">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N8">
         <v>0</v>
       </c>
       <c r="O8">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8" t="s">
-        <v>177</v>
+        <v>231</v>
       </c>
       <c r="R8">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="S8">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -1694,16 +1919,16 @@
         <v>90</v>
       </c>
       <c r="W8">
-        <v>15134</v>
+        <v>9605</v>
       </c>
       <c r="X8" t="s">
-        <v>214</v>
+        <v>282</v>
       </c>
       <c r="Y8">
         <v>2</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -1717,34 +1942,34 @@
         <v>37</v>
       </c>
       <c r="D9">
-        <v>1484</v>
+        <v>4399</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="H9" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I9" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="J9" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K9" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -1756,13 +1981,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="R9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -1774,21 +1999,21 @@
         <v>90</v>
       </c>
       <c r="W9">
-        <v>7918</v>
+        <v>6644</v>
       </c>
       <c r="X9" t="s">
-        <v>215</v>
+        <v>283</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z9">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1797,34 +2022,34 @@
         <v>37</v>
       </c>
       <c r="D10">
-        <v>59033</v>
+        <v>4373</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="H10" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I10" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="J10" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K10" t="s">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="L10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -1836,13 +2061,13 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="R10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="S10">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -1857,72 +2082,72 @@
         <v>9638</v>
       </c>
       <c r="X10" t="s">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="Y10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>28.17</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="H11" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I11" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="J11" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K11" t="s">
-        <v>160</v>
+        <v>217</v>
       </c>
       <c r="L11">
+        <v>6</v>
+      </c>
+      <c r="M11">
+        <v>4</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>234</v>
+      </c>
+      <c r="R11">
+        <v>6</v>
+      </c>
+      <c r="S11">
         <v>12</v>
-      </c>
-      <c r="M11">
-        <v>46</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>180</v>
-      </c>
-      <c r="R11">
-        <v>48</v>
-      </c>
-      <c r="S11">
-        <v>72</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -1934,57 +2159,57 @@
         <v>90</v>
       </c>
       <c r="W11">
-        <v>9638</v>
+        <v>7246</v>
       </c>
       <c r="X11" t="s">
-        <v>212</v>
+        <v>284</v>
       </c>
       <c r="Y11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z11">
-        <v>195</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12">
-        <v>29264</v>
+        <v>36370</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="G12" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I12" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="J12" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K12" t="s">
-        <v>161</v>
+        <v>221</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -1996,13 +2221,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="R12">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="S12">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -2014,16 +2239,16 @@
         <v>90</v>
       </c>
       <c r="W12">
-        <v>15134</v>
+        <v>6703</v>
       </c>
       <c r="X12" t="s">
-        <v>214</v>
+        <v>285</v>
       </c>
       <c r="Y12">
         <v>2</v>
       </c>
       <c r="Z12">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -2031,43 +2256,43 @@
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
         <v>38</v>
       </c>
       <c r="D13">
-        <v>189</v>
+        <v>36372</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="G13" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="H13" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="I13" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="J13" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K13" t="s">
-        <v>161</v>
+        <v>221</v>
       </c>
       <c r="L13">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="M13">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2076,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="Q13" t="s">
-        <v>181</v>
+        <v>236</v>
       </c>
       <c r="R13">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="S13">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="T13">
         <v>0</v>
@@ -2094,57 +2319,57 @@
         <v>90</v>
       </c>
       <c r="W13">
-        <v>15441</v>
+        <v>6703</v>
       </c>
       <c r="X13" t="s">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z13">
-        <v>58</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
         <v>38</v>
       </c>
       <c r="D14">
-        <v>1027</v>
+        <v>36373</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="H14" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I14" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="J14" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K14" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="L14">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="M14">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2156,13 +2381,13 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>178</v>
+        <v>237</v>
       </c>
       <c r="R14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S14">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -2174,75 +2399,75 @@
         <v>90</v>
       </c>
       <c r="W14">
-        <v>13838</v>
+        <v>6703</v>
       </c>
       <c r="X14" t="s">
-        <v>216</v>
+        <v>285</v>
       </c>
       <c r="Y14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z14">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>38</v>
       </c>
       <c r="D15">
-        <v>1027</v>
+        <v>1655</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F15" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="G15" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="H15" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I15" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="J15" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K15" t="s">
-        <v>164</v>
+        <v>219</v>
       </c>
       <c r="L15">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="N15">
         <v>0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="R15">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="S15">
-        <v>69</v>
+        <v>180</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -2254,57 +2479,57 @@
         <v>90</v>
       </c>
       <c r="W15">
-        <v>13838</v>
+        <v>15165</v>
       </c>
       <c r="X15" t="s">
-        <v>216</v>
+        <v>286</v>
       </c>
       <c r="Y15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>38</v>
       </c>
       <c r="D16">
-        <v>5927</v>
+        <v>1763</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G16" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="H16" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="I16" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="J16" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K16" t="s">
-        <v>161</v>
+        <v>215</v>
       </c>
       <c r="L16">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2316,13 +2541,13 @@
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>183</v>
+        <v>239</v>
       </c>
       <c r="R16">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S16">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -2334,16 +2559,16 @@
         <v>90</v>
       </c>
       <c r="W16">
-        <v>5894</v>
+        <v>15520</v>
       </c>
       <c r="X16" t="s">
-        <v>217</v>
+        <v>287</v>
       </c>
       <c r="Y16">
         <v>2</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
@@ -2351,40 +2576,40 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17">
-        <v>409</v>
+        <v>1798</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="G17" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="H17" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="I17" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="J17" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K17" t="s">
-        <v>161</v>
+        <v>218</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M17">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2396,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="R17">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="S17">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="T17">
         <v>0</v>
@@ -2414,57 +2639,57 @@
         <v>90</v>
       </c>
       <c r="W17">
-        <v>15441</v>
+        <v>14671</v>
       </c>
       <c r="X17" t="s">
-        <v>210</v>
+        <v>287</v>
       </c>
       <c r="Y17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z17">
-        <v>109.83</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18">
-        <v>4709</v>
+        <v>2574</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H18" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I18" t="s">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="J18" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K18" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
       <c r="L18">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="M18">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -2476,34 +2701,34 @@
         <v>0</v>
       </c>
       <c r="Q18" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="R18">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="S18">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="V18">
         <v>90</v>
       </c>
       <c r="W18">
-        <v>16169</v>
+        <v>3974</v>
       </c>
       <c r="X18" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="Y18">
         <v>3</v>
       </c>
       <c r="Z18">
-        <v>476</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
@@ -2511,58 +2736,58 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19">
-        <v>1027</v>
+        <v>7117</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F19" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G19" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H19" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I19" t="s">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="J19" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K19" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="L19">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="M19">
+        <v>8</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>242</v>
+      </c>
+      <c r="R19">
         <v>22</v>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>186</v>
-      </c>
-      <c r="R19">
-        <v>39</v>
-      </c>
       <c r="S19">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="T19">
         <v>0</v>
@@ -2574,57 +2799,57 @@
         <v>90</v>
       </c>
       <c r="W19">
-        <v>13838</v>
+        <v>6644</v>
       </c>
       <c r="X19" t="s">
-        <v>216</v>
+        <v>283</v>
       </c>
       <c r="Y19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z19">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D20">
-        <v>1027</v>
+        <v>7417</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H20" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I20" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="J20" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K20" t="s">
-        <v>164</v>
+        <v>219</v>
       </c>
       <c r="L20">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>28</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2636,13 +2861,13 @@
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>187</v>
+        <v>243</v>
       </c>
       <c r="R20">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -2654,57 +2879,57 @@
         <v>90</v>
       </c>
       <c r="W20">
-        <v>13838</v>
+        <v>14718</v>
       </c>
       <c r="X20" t="s">
-        <v>216</v>
+        <v>289</v>
       </c>
       <c r="Y20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D21">
-        <v>1972</v>
+        <v>7418</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="G21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I21" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="J21" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K21" t="s">
-        <v>165</v>
+        <v>219</v>
       </c>
       <c r="L21">
         <v>10</v>
       </c>
       <c r="M21">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -2716,13 +2941,13 @@
         <v>0</v>
       </c>
       <c r="Q21" t="s">
-        <v>188</v>
+        <v>244</v>
       </c>
       <c r="R21">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -2734,57 +2959,57 @@
         <v>90</v>
       </c>
       <c r="W21">
-        <v>14328</v>
+        <v>14718</v>
       </c>
       <c r="X21" t="s">
-        <v>219</v>
+        <v>289</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z21">
-        <v>921</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D22">
-        <v>1516</v>
+        <v>8502</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="G22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H22" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I22" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="J22" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K22" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="L22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>53</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -2796,13 +3021,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>189</v>
+        <v>245</v>
       </c>
       <c r="R22">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="S22">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -2814,57 +3039,57 @@
         <v>90</v>
       </c>
       <c r="W22">
-        <v>10721</v>
+        <v>14718</v>
       </c>
       <c r="X22" t="s">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z22">
-        <v>322</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D23">
-        <v>967</v>
+        <v>9859</v>
       </c>
       <c r="E23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="G23" t="s">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="H23" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I23" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="J23" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K23" t="s">
-        <v>166</v>
+        <v>220</v>
       </c>
       <c r="L23">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M23">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -2876,13 +3101,13 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>190</v>
+        <v>246</v>
       </c>
       <c r="R23">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="T23">
         <v>0</v>
@@ -2894,75 +3119,75 @@
         <v>90</v>
       </c>
       <c r="W23">
-        <v>13838</v>
+        <v>10683</v>
       </c>
       <c r="X23" t="s">
-        <v>216</v>
+        <v>290</v>
       </c>
       <c r="Y23">
         <v>2</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D24">
-        <v>36734</v>
+        <v>1633</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="G24" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="H24" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I24" t="s">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="J24" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K24" t="s">
-        <v>163</v>
+        <v>218</v>
       </c>
       <c r="L24">
+        <v>24</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>226</v>
+      </c>
+      <c r="R24">
         <v>16</v>
       </c>
-      <c r="M24">
-        <v>14</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>191</v>
-      </c>
-      <c r="R24">
-        <v>68</v>
-      </c>
       <c r="S24">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="T24">
         <v>0</v>
@@ -2974,57 +3199,57 @@
         <v>90</v>
       </c>
       <c r="W24">
-        <v>15134</v>
+        <v>4083</v>
       </c>
       <c r="X24" t="s">
-        <v>214</v>
+        <v>291</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z24">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D25">
-        <v>1448</v>
+        <v>189</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F25" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="G25" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c r="H25" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="I25" t="s">
-        <v>143</v>
+        <v>195</v>
       </c>
       <c r="J25" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K25" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="L25">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -3033,16 +3258,16 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="R25">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="S25">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="T25">
         <v>0</v>
@@ -3054,57 +3279,57 @@
         <v>90</v>
       </c>
       <c r="W25">
-        <v>7918</v>
+        <v>15441</v>
       </c>
       <c r="X25" t="s">
-        <v>215</v>
+        <v>292</v>
       </c>
       <c r="Y25">
         <v>2</v>
       </c>
       <c r="Z25">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D26">
-        <v>1691</v>
+        <v>1974</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="G26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H26" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I26" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="J26" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K26" t="s">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="L26">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -3116,13 +3341,13 @@
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>193</v>
+        <v>248</v>
       </c>
       <c r="R26">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="S26">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -3134,57 +3359,57 @@
         <v>90</v>
       </c>
       <c r="W26">
-        <v>5791</v>
+        <v>16900</v>
       </c>
       <c r="X26" t="s">
-        <v>221</v>
+        <v>293</v>
       </c>
       <c r="Y26">
         <v>2</v>
       </c>
       <c r="Z26">
-        <v>192</v>
+        <v>1568.1</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D27">
-        <v>2134</v>
+        <v>41</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G27" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="H27" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I27" t="s">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="J27" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K27" t="s">
-        <v>162</v>
+        <v>220</v>
       </c>
       <c r="L27">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M27">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -3196,13 +3421,13 @@
         <v>0</v>
       </c>
       <c r="Q27" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="R27">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="S27">
-        <v>40</v>
+        <v>298</v>
       </c>
       <c r="T27">
         <v>0</v>
@@ -3214,57 +3439,57 @@
         <v>90</v>
       </c>
       <c r="W27">
-        <v>15134</v>
+        <v>15441</v>
       </c>
       <c r="X27" t="s">
-        <v>214</v>
+        <v>292</v>
       </c>
       <c r="Y27">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D28">
-        <v>59033</v>
+        <v>696</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="G28" t="s">
-        <v>57</v>
+        <v>161</v>
       </c>
       <c r="H28" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I28" t="s">
-        <v>144</v>
+        <v>197</v>
       </c>
       <c r="J28" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K28" t="s">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="L28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -3276,13 +3501,13 @@
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="R28">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S28">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="T28">
         <v>0</v>
@@ -3294,75 +3519,75 @@
         <v>90</v>
       </c>
       <c r="W28">
-        <v>9638</v>
+        <v>15441</v>
       </c>
       <c r="X28" t="s">
-        <v>212</v>
+        <v>292</v>
       </c>
       <c r="Y28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D29">
-        <v>5768</v>
+        <v>700</v>
       </c>
       <c r="E29" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="G29" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="H29" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I29" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="J29" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K29" t="s">
-        <v>160</v>
+        <v>217</v>
       </c>
       <c r="L29">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="N29">
         <v>0</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>196</v>
+        <v>251</v>
       </c>
       <c r="R29">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="S29">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="T29">
         <v>0</v>
@@ -3374,57 +3599,57 @@
         <v>90</v>
       </c>
       <c r="W29">
-        <v>5894</v>
+        <v>15441</v>
       </c>
       <c r="X29" t="s">
-        <v>217</v>
+        <v>292</v>
       </c>
       <c r="Y29">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Z29">
-        <v>377</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D30">
-        <v>6614</v>
+        <v>2141</v>
       </c>
       <c r="E30" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="G30" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="H30" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I30" t="s">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="J30" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K30" t="s">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="L30">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="M30">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -3436,13 +3661,13 @@
         <v>0</v>
       </c>
       <c r="Q30" t="s">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="R30">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="S30">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="T30">
         <v>0</v>
@@ -3454,57 +3679,57 @@
         <v>90</v>
       </c>
       <c r="W30">
-        <v>12839</v>
+        <v>10189</v>
       </c>
       <c r="X30" t="s">
-        <v>222</v>
+        <v>294</v>
       </c>
       <c r="Y30">
         <v>2</v>
       </c>
       <c r="Z30">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D31">
-        <v>58985</v>
+        <v>2350</v>
       </c>
       <c r="E31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="G31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I31" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="J31" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K31" t="s">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="L31">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -3516,13 +3741,13 @@
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="R31">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="S31">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="T31">
         <v>0</v>
@@ -3534,75 +3759,75 @@
         <v>90</v>
       </c>
       <c r="W31">
-        <v>15134</v>
+        <v>2977</v>
       </c>
       <c r="X31" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="Y31">
         <v>2</v>
       </c>
       <c r="Z31">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D32">
-        <v>1041</v>
+        <v>2420</v>
       </c>
       <c r="E32" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F32" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="G32" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H32" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I32" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="J32" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K32" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="L32">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="M32">
+        <v>8</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>254</v>
+      </c>
+      <c r="R32">
         <v>10</v>
       </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>199</v>
-      </c>
-      <c r="R32">
-        <v>14</v>
-      </c>
       <c r="S32">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="T32">
         <v>0</v>
@@ -3614,54 +3839,54 @@
         <v>90</v>
       </c>
       <c r="W32">
-        <v>10683</v>
+        <v>16857</v>
       </c>
       <c r="X32" t="s">
-        <v>223</v>
+        <v>296</v>
       </c>
       <c r="Y32">
         <v>2</v>
       </c>
       <c r="Z32">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D33">
-        <v>2976</v>
+        <v>2432</v>
       </c>
       <c r="E33" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="G33" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="I33" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="J33" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K33" t="s">
-        <v>164</v>
+        <v>219</v>
       </c>
       <c r="L33">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>1</v>
@@ -3676,13 +3901,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="s">
-        <v>173</v>
+        <v>255</v>
       </c>
       <c r="R33">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="T33">
         <v>0</v>
@@ -3694,57 +3919,57 @@
         <v>90</v>
       </c>
       <c r="W33">
-        <v>15134</v>
+        <v>16857</v>
       </c>
       <c r="X33" t="s">
-        <v>214</v>
+        <v>296</v>
       </c>
       <c r="Y33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z33">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D34">
-        <v>30544</v>
+        <v>358</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F34" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="G34" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I34" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="J34" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K34" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="L34">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M34">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -3756,13 +3981,13 @@
         <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>200</v>
+        <v>256</v>
       </c>
       <c r="R34">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="S34">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="T34">
         <v>0</v>
@@ -3774,60 +3999,60 @@
         <v>90</v>
       </c>
       <c r="W34">
-        <v>10525</v>
+        <v>9638</v>
       </c>
       <c r="X34" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="Y34">
         <v>2</v>
       </c>
       <c r="Z34">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D35">
-        <v>189</v>
+        <v>648</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="G35" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="I35" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="J35" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K35" t="s">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="L35">
         <v>6</v>
       </c>
       <c r="M35">
-        <v>4</v>
+        <v>165</v>
       </c>
       <c r="N35">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -3836,13 +4061,13 @@
         <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>195</v>
+        <v>257</v>
       </c>
       <c r="R35">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="S35">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c r="T35">
         <v>0</v>
@@ -3857,54 +4082,54 @@
         <v>15441</v>
       </c>
       <c r="X35" t="s">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="Y35">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Z35">
-        <v>58</v>
+        <v>414</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D36">
-        <v>37331</v>
+        <v>250</v>
       </c>
       <c r="E36" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F36" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="G36" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I36" t="s">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="J36" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K36" t="s">
-        <v>162</v>
+        <v>220</v>
       </c>
       <c r="L36">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M36">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -3916,13 +4141,13 @@
         <v>0</v>
       </c>
       <c r="Q36" t="s">
-        <v>201</v>
+        <v>258</v>
       </c>
       <c r="R36">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="S36">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="T36">
         <v>0</v>
@@ -3934,57 +4159,57 @@
         <v>90</v>
       </c>
       <c r="W36">
-        <v>15520</v>
+        <v>14469</v>
       </c>
       <c r="X36" t="s">
-        <v>225</v>
+        <v>281</v>
       </c>
       <c r="Y36">
         <v>2</v>
       </c>
       <c r="Z36">
-        <v>43</v>
+        <v>875</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D37">
-        <v>15618</v>
+        <v>360</v>
       </c>
       <c r="E37" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="F37" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="G37" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="H37" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I37" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="J37" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K37" t="s">
-        <v>162</v>
+        <v>218</v>
       </c>
       <c r="L37">
         <v>24</v>
       </c>
       <c r="M37">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -3996,13 +4221,13 @@
         <v>0</v>
       </c>
       <c r="Q37" t="s">
-        <v>202</v>
+        <v>259</v>
       </c>
       <c r="R37">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S37">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T37">
         <v>0</v>
@@ -4014,57 +4239,57 @@
         <v>90</v>
       </c>
       <c r="W37">
-        <v>7995</v>
+        <v>14469</v>
       </c>
       <c r="X37" t="s">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="Y37">
         <v>2</v>
       </c>
       <c r="Z37">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D38">
-        <v>1762</v>
+        <v>625</v>
       </c>
       <c r="E38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F38" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="G38" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="H38" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="I38" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="J38" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K38" t="s">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="L38">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="M38">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -4076,13 +4301,13 @@
         <v>0</v>
       </c>
       <c r="Q38" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="R38">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="S38">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="T38">
         <v>0</v>
@@ -4094,16 +4319,16 @@
         <v>90</v>
       </c>
       <c r="W38">
-        <v>4083</v>
+        <v>15441</v>
       </c>
       <c r="X38" t="s">
-        <v>227</v>
+        <v>292</v>
       </c>
       <c r="Y38">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Z38">
-        <v>160</v>
+        <v>646</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
@@ -4111,58 +4336,58 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39">
+        <v>2700</v>
+      </c>
+      <c r="E39" t="s">
+        <v>82</v>
+      </c>
+      <c r="F39" t="s">
+        <v>131</v>
+      </c>
+      <c r="G39" t="s">
+        <v>164</v>
+      </c>
+      <c r="H39" t="s">
+        <v>177</v>
+      </c>
+      <c r="I39" t="s">
+        <v>204</v>
+      </c>
+      <c r="J39" t="s">
+        <v>213</v>
+      </c>
+      <c r="K39" t="s">
+        <v>220</v>
+      </c>
+      <c r="L39">
+        <v>12</v>
+      </c>
+      <c r="M39">
+        <v>42</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>261</v>
+      </c>
+      <c r="R39">
         <v>48</v>
       </c>
-      <c r="D39">
-        <v>189</v>
-      </c>
-      <c r="E39" t="s">
-        <v>52</v>
-      </c>
-      <c r="F39" t="s">
-        <v>84</v>
-      </c>
-      <c r="G39" t="s">
-        <v>117</v>
-      </c>
-      <c r="H39" t="s">
-        <v>134</v>
-      </c>
-      <c r="I39" t="s">
-        <v>139</v>
-      </c>
-      <c r="J39" t="s">
-        <v>158</v>
-      </c>
-      <c r="K39" t="s">
-        <v>161</v>
-      </c>
-      <c r="L39">
-        <v>6</v>
-      </c>
-      <c r="M39">
-        <v>16</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>159</v>
-      </c>
-      <c r="R39">
-        <v>18</v>
-      </c>
       <c r="S39">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="T39">
         <v>0</v>
@@ -4174,58 +4399,58 @@
         <v>90</v>
       </c>
       <c r="W39">
-        <v>15441</v>
+        <v>10189</v>
       </c>
       <c r="X39" t="s">
-        <v>210</v>
+        <v>294</v>
       </c>
       <c r="Y39">
         <v>2</v>
       </c>
       <c r="Z39">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D40">
-        <v>625</v>
+        <v>4399</v>
       </c>
       <c r="E40" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F40" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="G40" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="H40" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="I40" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="J40" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K40" t="s">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="L40">
+        <v>12</v>
+      </c>
+      <c r="M40">
         <v>8</v>
       </c>
-      <c r="M40">
-        <v>53</v>
-      </c>
       <c r="N40">
         <v>0</v>
       </c>
@@ -4236,13 +4461,13 @@
         <v>0</v>
       </c>
       <c r="Q40" t="s">
-        <v>204</v>
+        <v>262</v>
       </c>
       <c r="R40">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="S40">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="T40">
         <v>0</v>
@@ -4254,57 +4479,57 @@
         <v>90</v>
       </c>
       <c r="W40">
-        <v>15441</v>
+        <v>6644</v>
       </c>
       <c r="X40" t="s">
-        <v>210</v>
+        <v>283</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z40">
-        <v>105</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D41">
-        <v>4693</v>
+        <v>744</v>
       </c>
       <c r="E41" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F41" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="G41" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I41" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="J41" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K41" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="L41">
         <v>12</v>
       </c>
       <c r="M41">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -4316,13 +4541,13 @@
         <v>0</v>
       </c>
       <c r="Q41" t="s">
-        <v>205</v>
+        <v>263</v>
       </c>
       <c r="R41">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S41">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="T41">
         <v>0</v>
@@ -4334,75 +4559,75 @@
         <v>90</v>
       </c>
       <c r="W41">
-        <v>9379</v>
+        <v>11411</v>
       </c>
       <c r="X41" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
       <c r="Y41">
         <v>2</v>
       </c>
       <c r="Z41">
-        <v>694</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D42">
-        <v>39892</v>
+        <v>1027</v>
       </c>
       <c r="E42" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F42" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="G42" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="H42" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I42" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J42" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K42" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="L42">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N42">
         <v>0</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P42">
         <v>0</v>
       </c>
       <c r="Q42" t="s">
-        <v>206</v>
+        <v>264</v>
       </c>
       <c r="R42">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="S42">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="T42">
         <v>0</v>
@@ -4414,69 +4639,69 @@
         <v>90</v>
       </c>
       <c r="W42">
-        <v>5894</v>
+        <v>13838</v>
       </c>
       <c r="X42" t="s">
-        <v>217</v>
+        <v>298</v>
       </c>
       <c r="Y42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z42">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D43">
         <v>1027</v>
       </c>
       <c r="E43" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F43" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="G43" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="H43" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I43" t="s">
-        <v>146</v>
+        <v>206</v>
       </c>
       <c r="J43" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K43" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="L43">
         <v>15</v>
       </c>
       <c r="M43">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N43">
         <v>0</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P43">
         <v>0</v>
       </c>
       <c r="Q43" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="R43">
         <v>39</v>
@@ -4497,54 +4722,54 @@
         <v>13838</v>
       </c>
       <c r="X43" t="s">
-        <v>216</v>
+        <v>298</v>
       </c>
       <c r="Y43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z43">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D44">
-        <v>1027</v>
+        <v>1691</v>
       </c>
       <c r="E44" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F44" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="G44" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I44" t="s">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="J44" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K44" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="L44">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="M44">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N44">
         <v>0</v>
@@ -4556,13 +4781,13 @@
         <v>0</v>
       </c>
       <c r="Q44" t="s">
-        <v>208</v>
+        <v>265</v>
       </c>
       <c r="R44">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="S44">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="T44">
         <v>0</v>
@@ -4574,75 +4799,75 @@
         <v>90</v>
       </c>
       <c r="W44">
-        <v>13838</v>
+        <v>5791</v>
       </c>
       <c r="X44" t="s">
-        <v>216</v>
+        <v>299</v>
       </c>
       <c r="Y44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z44">
-        <v>10</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D45">
-        <v>19204</v>
+        <v>2408</v>
       </c>
       <c r="E45" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F45" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="G45" t="s">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="H45" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="I45" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="J45" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="K45" t="s">
-        <v>165</v>
+        <v>219</v>
       </c>
       <c r="L45">
         <v>10</v>
       </c>
       <c r="M45">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="N45">
         <v>0</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P45">
         <v>0</v>
       </c>
       <c r="Q45" t="s">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="R45">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S45">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="T45">
         <v>0</v>
@@ -4654,20 +4879,1060 @@
         <v>90</v>
       </c>
       <c r="W45">
-        <v>6158</v>
+        <v>16857</v>
       </c>
       <c r="X45" t="s">
-        <v>229</v>
+        <v>296</v>
       </c>
       <c r="Y45">
         <v>2</v>
       </c>
       <c r="Z45">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46">
+        <v>4399</v>
+      </c>
+      <c r="E46" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" t="s">
+        <v>138</v>
+      </c>
+      <c r="G46" t="s">
+        <v>169</v>
+      </c>
+      <c r="H46" t="s">
+        <v>177</v>
+      </c>
+      <c r="I46" t="s">
+        <v>186</v>
+      </c>
+      <c r="J46" t="s">
+        <v>213</v>
+      </c>
+      <c r="K46" t="s">
+        <v>220</v>
+      </c>
+      <c r="L46">
+        <v>12</v>
+      </c>
+      <c r="M46">
+        <v>7</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>239</v>
+      </c>
+      <c r="R46">
+        <v>8</v>
+      </c>
+      <c r="S46">
+        <v>20</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>90</v>
+      </c>
+      <c r="W46">
+        <v>6644</v>
+      </c>
+      <c r="X46" t="s">
+        <v>283</v>
+      </c>
+      <c r="Y46">
+        <v>2</v>
+      </c>
+      <c r="Z46">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47">
+        <v>9150</v>
+      </c>
+      <c r="E47" t="s">
+        <v>87</v>
+      </c>
+      <c r="F47" t="s">
+        <v>139</v>
+      </c>
+      <c r="G47" t="s">
+        <v>87</v>
+      </c>
+      <c r="H47" t="s">
+        <v>177</v>
+      </c>
+      <c r="I47" t="s">
+        <v>179</v>
+      </c>
+      <c r="J47" t="s">
+        <v>213</v>
+      </c>
+      <c r="K47" t="s">
+        <v>220</v>
+      </c>
+      <c r="L47">
+        <v>12</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>267</v>
+      </c>
+      <c r="R47">
+        <v>24</v>
+      </c>
+      <c r="S47">
+        <v>48</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>90</v>
+      </c>
+      <c r="W47">
+        <v>16039</v>
+      </c>
+      <c r="X47" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y47">
+        <v>4</v>
+      </c>
+      <c r="Z47">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48">
+        <v>409</v>
+      </c>
+      <c r="E48" t="s">
+        <v>88</v>
+      </c>
+      <c r="F48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G48" t="s">
+        <v>170</v>
+      </c>
+      <c r="H48" t="s">
+        <v>178</v>
+      </c>
+      <c r="I48" t="s">
+        <v>207</v>
+      </c>
+      <c r="J48" t="s">
+        <v>213</v>
+      </c>
+      <c r="K48" t="s">
+        <v>217</v>
+      </c>
+      <c r="L48">
+        <v>6</v>
+      </c>
+      <c r="M48">
+        <v>37</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>268</v>
+      </c>
+      <c r="R48">
+        <v>40</v>
+      </c>
+      <c r="S48">
+        <v>64</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>90</v>
+      </c>
+      <c r="W48">
+        <v>15441</v>
+      </c>
+      <c r="X48" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y48">
+        <v>5</v>
+      </c>
+      <c r="Z48">
+        <v>227.83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49">
+        <v>2067</v>
+      </c>
+      <c r="E49" t="s">
+        <v>48</v>
+      </c>
+      <c r="F49" t="s">
+        <v>96</v>
+      </c>
+      <c r="G49" t="s">
+        <v>149</v>
+      </c>
+      <c r="H49" t="s">
+        <v>177</v>
+      </c>
+      <c r="I49" t="s">
+        <v>181</v>
+      </c>
+      <c r="J49" t="s">
+        <v>213</v>
+      </c>
+      <c r="K49" t="s">
+        <v>215</v>
+      </c>
+      <c r="L49">
+        <v>15</v>
+      </c>
+      <c r="M49">
+        <v>3</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>30</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>247</v>
+      </c>
+      <c r="R49">
+        <v>41</v>
+      </c>
+      <c r="S49">
+        <v>56</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>90</v>
+      </c>
+      <c r="W49">
+        <v>10321</v>
+      </c>
+      <c r="X49" t="s">
+        <v>278</v>
+      </c>
+      <c r="Y49">
+        <v>2</v>
+      </c>
+      <c r="Z49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" t="s">
+        <v>45</v>
+      </c>
+      <c r="D50">
+        <v>3087</v>
+      </c>
+      <c r="E50" t="s">
+        <v>89</v>
+      </c>
+      <c r="F50" t="s">
+        <v>141</v>
+      </c>
+      <c r="G50" t="s">
+        <v>171</v>
+      </c>
+      <c r="H50" t="s">
+        <v>177</v>
+      </c>
+      <c r="I50" t="s">
+        <v>186</v>
+      </c>
+      <c r="J50" t="s">
+        <v>213</v>
+      </c>
+      <c r="K50" t="s">
+        <v>214</v>
+      </c>
+      <c r="L50">
+        <v>4</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>269</v>
+      </c>
+      <c r="R50">
+        <v>16</v>
+      </c>
+      <c r="S50">
+        <v>28</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>90</v>
+      </c>
+      <c r="W50">
+        <v>14468</v>
+      </c>
+      <c r="X50" t="s">
+        <v>301</v>
+      </c>
+      <c r="Y50">
+        <v>7</v>
+      </c>
+      <c r="Z50">
         <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>27</v>
+      </c>
+      <c r="B51" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51">
+        <v>27004</v>
+      </c>
+      <c r="E51" t="s">
+        <v>90</v>
+      </c>
+      <c r="F51" t="s">
+        <v>142</v>
+      </c>
+      <c r="G51" t="s">
+        <v>172</v>
+      </c>
+      <c r="H51" t="s">
+        <v>177</v>
+      </c>
+      <c r="I51" t="s">
+        <v>208</v>
+      </c>
+      <c r="J51" t="s">
+        <v>213</v>
+      </c>
+      <c r="K51" t="s">
+        <v>217</v>
+      </c>
+      <c r="L51">
+        <v>6</v>
+      </c>
+      <c r="M51">
+        <v>166</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>270</v>
+      </c>
+      <c r="R51">
+        <v>172</v>
+      </c>
+      <c r="S51">
+        <v>268</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>90</v>
+      </c>
+      <c r="W51">
+        <v>15441</v>
+      </c>
+      <c r="X51" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y51">
+        <v>17</v>
+      </c>
+      <c r="Z51">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52">
+        <v>409</v>
+      </c>
+      <c r="E52" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52" t="s">
+        <v>143</v>
+      </c>
+      <c r="G52" t="s">
+        <v>173</v>
+      </c>
+      <c r="H52" t="s">
+        <v>178</v>
+      </c>
+      <c r="I52" t="s">
+        <v>207</v>
+      </c>
+      <c r="J52" t="s">
+        <v>213</v>
+      </c>
+      <c r="K52" t="s">
+        <v>217</v>
+      </c>
+      <c r="L52">
+        <v>6</v>
+      </c>
+      <c r="M52">
+        <v>36</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>271</v>
+      </c>
+      <c r="R52">
+        <v>38</v>
+      </c>
+      <c r="S52">
+        <v>56</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>90</v>
+      </c>
+      <c r="W52">
+        <v>15441</v>
+      </c>
+      <c r="X52" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y52">
+        <v>4</v>
+      </c>
+      <c r="Z52">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>27</v>
+      </c>
+      <c r="B53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D53">
+        <v>625</v>
+      </c>
+      <c r="E53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F53" t="s">
+        <v>144</v>
+      </c>
+      <c r="G53" t="s">
+        <v>174</v>
+      </c>
+      <c r="H53" t="s">
+        <v>178</v>
+      </c>
+      <c r="I53" t="s">
+        <v>203</v>
+      </c>
+      <c r="J53" t="s">
+        <v>213</v>
+      </c>
+      <c r="K53" t="s">
+        <v>224</v>
+      </c>
+      <c r="L53">
+        <v>8</v>
+      </c>
+      <c r="M53">
+        <v>44</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>272</v>
+      </c>
+      <c r="R53">
+        <v>58</v>
+      </c>
+      <c r="S53">
+        <v>90</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>90</v>
+      </c>
+      <c r="W53">
+        <v>15441</v>
+      </c>
+      <c r="X53" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y53">
+        <v>6</v>
+      </c>
+      <c r="Z53">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" t="s">
+        <v>46</v>
+      </c>
+      <c r="D54">
+        <v>818</v>
+      </c>
+      <c r="E54" t="s">
+        <v>91</v>
+      </c>
+      <c r="F54" t="s">
+        <v>145</v>
+      </c>
+      <c r="G54" t="s">
+        <v>91</v>
+      </c>
+      <c r="H54" t="s">
+        <v>177</v>
+      </c>
+      <c r="I54" t="s">
+        <v>209</v>
+      </c>
+      <c r="J54" t="s">
+        <v>213</v>
+      </c>
+      <c r="K54" t="s">
+        <v>218</v>
+      </c>
+      <c r="L54">
+        <v>24</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>226</v>
+      </c>
+      <c r="R54">
+        <v>18</v>
+      </c>
+      <c r="S54">
+        <v>42</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>90</v>
+      </c>
+      <c r="W54">
+        <v>14588</v>
+      </c>
+      <c r="X54" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y54">
+        <v>2</v>
+      </c>
+      <c r="Z54">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55">
+        <v>1086</v>
+      </c>
+      <c r="E55" t="s">
+        <v>92</v>
+      </c>
+      <c r="F55" t="s">
+        <v>146</v>
+      </c>
+      <c r="G55" t="s">
+        <v>175</v>
+      </c>
+      <c r="H55" t="s">
+        <v>177</v>
+      </c>
+      <c r="I55" t="s">
+        <v>210</v>
+      </c>
+      <c r="J55" t="s">
+        <v>213</v>
+      </c>
+      <c r="K55" t="s">
+        <v>222</v>
+      </c>
+      <c r="L55">
+        <v>30</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>273</v>
+      </c>
+      <c r="R55">
+        <v>18</v>
+      </c>
+      <c r="S55">
+        <v>48</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>90</v>
+      </c>
+      <c r="W55">
+        <v>16963</v>
+      </c>
+      <c r="X55" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y55">
+        <v>2</v>
+      </c>
+      <c r="Z55">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>26</v>
+      </c>
+      <c r="B56" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" t="s">
+        <v>46</v>
+      </c>
+      <c r="D56">
+        <v>1386</v>
+      </c>
+      <c r="E56" t="s">
+        <v>93</v>
+      </c>
+      <c r="F56" t="s">
+        <v>147</v>
+      </c>
+      <c r="G56" t="s">
+        <v>176</v>
+      </c>
+      <c r="H56" t="s">
+        <v>177</v>
+      </c>
+      <c r="I56" t="s">
+        <v>211</v>
+      </c>
+      <c r="J56" t="s">
+        <v>213</v>
+      </c>
+      <c r="K56" t="s">
+        <v>220</v>
+      </c>
+      <c r="L56">
+        <v>12</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>274</v>
+      </c>
+      <c r="R56">
+        <v>8</v>
+      </c>
+      <c r="S56">
+        <v>20</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>90</v>
+      </c>
+      <c r="W56">
+        <v>15134</v>
+      </c>
+      <c r="X56" t="s">
+        <v>304</v>
+      </c>
+      <c r="Y56">
+        <v>2</v>
+      </c>
+      <c r="Z56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>26</v>
+      </c>
+      <c r="B57" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" t="s">
+        <v>46</v>
+      </c>
+      <c r="D57">
+        <v>2004</v>
+      </c>
+      <c r="E57" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" t="s">
+        <v>148</v>
+      </c>
+      <c r="G57" t="s">
+        <v>94</v>
+      </c>
+      <c r="H57" t="s">
+        <v>177</v>
+      </c>
+      <c r="I57" t="s">
+        <v>212</v>
+      </c>
+      <c r="J57" t="s">
+        <v>213</v>
+      </c>
+      <c r="K57" t="s">
+        <v>225</v>
+      </c>
+      <c r="L57">
+        <v>5</v>
+      </c>
+      <c r="M57">
+        <v>5</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>5</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>275</v>
+      </c>
+      <c r="R57">
+        <v>11</v>
+      </c>
+      <c r="S57">
+        <v>16</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>90</v>
+      </c>
+      <c r="W57">
+        <v>10321</v>
+      </c>
+      <c r="X57" t="s">
+        <v>278</v>
+      </c>
+      <c r="Y57">
+        <v>2</v>
+      </c>
+      <c r="Z57">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58">
+        <v>2067</v>
+      </c>
+      <c r="E58" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58" t="s">
+        <v>96</v>
+      </c>
+      <c r="G58" t="s">
+        <v>149</v>
+      </c>
+      <c r="H58" t="s">
+        <v>177</v>
+      </c>
+      <c r="I58" t="s">
+        <v>181</v>
+      </c>
+      <c r="J58" t="s">
+        <v>213</v>
+      </c>
+      <c r="K58" t="s">
+        <v>215</v>
+      </c>
+      <c r="L58">
+        <v>15</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>30</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>276</v>
+      </c>
+      <c r="R58">
+        <v>41</v>
+      </c>
+      <c r="S58">
+        <v>56</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>90</v>
+      </c>
+      <c r="W58">
+        <v>10321</v>
+      </c>
+      <c r="X58" t="s">
+        <v>278</v>
+      </c>
+      <c r="Y58">
+        <v>2</v>
+      </c>
+      <c r="Z58">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z45" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Z58" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Downloads\Equipes_Agentes\Aplicativos\GAM\bd_saida\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8E43AE-FC63-42EE-A3B2-EAB24F3EBC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Z$58</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="301">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -111,30 +97,33 @@
     <t>MERCEARIA</t>
   </si>
   <si>
+    <t>PERFUMARIA E LIMPEZA</t>
+  </si>
+  <si>
     <t>BEBIDAS</t>
   </si>
   <si>
-    <t>PERFUMARIA E LIMPEZA</t>
-  </si>
-  <si>
     <t>PERECIVEIS</t>
   </si>
   <si>
     <t>NIDAL TUBASI</t>
   </si>
   <si>
+    <t>JOAO BATISTA</t>
+  </si>
+  <si>
     <t>NICOLAS AUGUSTO P. BORGES</t>
   </si>
   <si>
     <t>WETER SONNENFELDET</t>
   </si>
   <si>
-    <t>JOAO BATISTA</t>
-  </si>
-  <si>
     <t>SANDRO MARTINS VIANNA</t>
   </si>
   <si>
+    <t>001</t>
+  </si>
+  <si>
     <t>002</t>
   </si>
   <si>
@@ -144,6 +133,9 @@
     <t>004</t>
   </si>
   <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>006</t>
   </si>
   <si>
@@ -171,10 +163,46 @@
     <t>018</t>
   </si>
   <si>
-    <t>REFRIG PEPSI PET 3L</t>
-  </si>
-  <si>
-    <t>MASSA C OVOS NORDESTE 500G</t>
+    <t>CESTA BASICA PEQ</t>
+  </si>
+  <si>
+    <t>LAVA ROUPA LIQ APYCE 3L LIMP TOTAL</t>
+  </si>
+  <si>
+    <t>REFRIG FRUKI PET 3L</t>
+  </si>
+  <si>
+    <t>CHOC STICK 25G</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SANO TP1 1KG</t>
+  </si>
+  <si>
+    <t>ARROZ BCO TRIVIAL T2 2K</t>
+  </si>
+  <si>
+    <t>FARINHA TRIGO MARIA INES 5KG</t>
+  </si>
+  <si>
+    <t>CESTA BASICA GRD</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 5L</t>
+  </si>
+  <si>
+    <t>CHOC LACTA RECH 98G</t>
+  </si>
+  <si>
+    <t>CHOC LACTA 145G</t>
+  </si>
+  <si>
+    <t>MILHO VERDE OLE LT 170G</t>
+  </si>
+  <si>
+    <t>FAROFA MANDIOCA YOKI 200G</t>
+  </si>
+  <si>
+    <t>LUVA DANNY SILVER GRIP</t>
   </si>
   <si>
     <t>FARINHA TAPIOCA DINDA 400G TRAD</t>
@@ -183,142 +211,139 @@
     <t>AGUA MIN DA PEDRA PET 1 5L</t>
   </si>
   <si>
-    <t>CERV HEINEKEN ZERO LN 330ML</t>
-  </si>
-  <si>
     <t>ERVA MATE PONCHE VERDE 1KG LAMINADO</t>
   </si>
   <si>
     <t>INSET AERO RAID 420ML</t>
   </si>
   <si>
-    <t>AGUA SABORIZ H2OH 500ML</t>
-  </si>
-  <si>
-    <t>VH COUNTRY WINE BORDO 750ML</t>
-  </si>
-  <si>
-    <t>CONFEITO BIBS CHOC BCO 40G</t>
-  </si>
-  <si>
-    <t>CONFEITO BIBS PASSAS 40G</t>
-  </si>
-  <si>
-    <t>CONFEITO BIBS PTO BCO 40G</t>
-  </si>
-  <si>
-    <t>FEIJAO PRETO CALDO OURO 500G</t>
-  </si>
-  <si>
-    <t>PEPINO CONSERVA ODERICH VD 300G</t>
-  </si>
-  <si>
-    <t>KETCHUP ODERICH BISN 400G</t>
-  </si>
-  <si>
-    <t>FERM PO BIOL GOOD INSTANT SH 10G</t>
-  </si>
-  <si>
-    <t>SAB BAR FARNESE 180G</t>
-  </si>
-  <si>
-    <t>AMEIXA UNIAGRO PTA C CAROCO KG</t>
-  </si>
-  <si>
-    <t>AMEIXA UNIAGRO PTA S CAROCO KG</t>
-  </si>
-  <si>
-    <t>PASSAS UVA UNIAGRO PTA KG</t>
-  </si>
-  <si>
-    <t>BISC AGUA SAL ORQUIDEA 665GR</t>
-  </si>
-  <si>
-    <t>ATUM RALADO NAUTIQUE 170G</t>
-  </si>
-  <si>
-    <t>AGUA GASEIFICADA CRYSTAL PET 510ML</t>
-  </si>
-  <si>
-    <t>FARINHA TRIGO PANFACIL TP1 1KG</t>
-  </si>
-  <si>
-    <t>REFRIG COCA COLA</t>
-  </si>
-  <si>
-    <t>REFRIG FANTA LARANJA</t>
-  </si>
-  <si>
-    <t>REFRIG FANTA UVA</t>
+    <t>FARINHA TRIGO ROSESOL 1KG</t>
+  </si>
+  <si>
+    <t>REFRIG PEPSI PET 2L</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SANO TP1 5KG</t>
+  </si>
+  <si>
+    <t>ACUCAR CRISTAL DOCESUCAR 5KG</t>
+  </si>
+  <si>
+    <t>CHOC BARRA NESTLE RECH 90G PRESTIG</t>
   </si>
   <si>
     <t>ACHOC PO APTI SH 200G</t>
   </si>
   <si>
-    <t>SALG KEVYTOS SHOW 38G BACON</t>
-  </si>
-  <si>
     <t>SALG OBBA 100G PRESUNTO</t>
   </si>
   <si>
     <t>SALG OBBA 100G REQUEIJAO</t>
   </si>
   <si>
-    <t>CERV BUDWEISER ZERO LN 330ML</t>
+    <t>ESC DENTAL SORRISO</t>
+  </si>
+  <si>
+    <t>GEL DENT SORRISO FRESH 90G</t>
+  </si>
+  <si>
+    <t>CERV BRAHMA CHOPP GF 1L</t>
+  </si>
+  <si>
+    <t>ARROZ BCO TRIVIAL TP2 5KG</t>
+  </si>
+  <si>
+    <t>LEITE UHT ELEGE INT 1L</t>
+  </si>
+  <si>
+    <t>REMOV ESM AMAZONIA 80ML</t>
   </si>
   <si>
     <t>REFRIG PET COCA COLA 3L</t>
   </si>
   <si>
-    <t>CERV AMSTEL LAGER LT 473ML</t>
+    <t>ENERG MONSTER LT 473ML</t>
   </si>
   <si>
     <t>REFRIG FANTA</t>
   </si>
   <si>
+    <t>ATUM EM PEDACOS NAUTIQUE 170G OLEO</t>
+  </si>
+  <si>
     <t>MIST P BOLO APTI 400G</t>
   </si>
   <si>
+    <t>FLANELA ALG PANOSUL 34X50CM</t>
+  </si>
+  <si>
+    <t>MASSA DOMELLY SEMOLA 1KG</t>
+  </si>
+  <si>
     <t>AZEIT OLIV COCINERO EXT VG 250ML</t>
   </si>
   <si>
-    <t>CHOC STICK 25G</t>
-  </si>
-  <si>
-    <t>ERVILHA FUGINI SH 170G</t>
-  </si>
-  <si>
-    <t>SALG OBBA 100G</t>
-  </si>
-  <si>
-    <t>ALCOOL 46 ARAUCARIA 1L</t>
-  </si>
-  <si>
-    <t>ENERG MONSTER LT 473ML</t>
-  </si>
-  <si>
-    <t>AMAC GOTA LIMPA 5L</t>
+    <t>DESOD AERO GLADE 360ML EMB ECONOMIC</t>
+  </si>
+  <si>
+    <t>TOAL SOCIAL PANOSUL 23X38CM</t>
   </si>
   <si>
     <t>REFRIG CHARRUA GUARANA PET 3L</t>
   </si>
   <si>
-    <t>BISC AGUA E SAL ZEZE 200G</t>
-  </si>
-  <si>
-    <t>BISC RECH SAPECA 120G</t>
-  </si>
-  <si>
-    <t>CAFE VACUO STARBUCKS 250G</t>
-  </si>
-  <si>
-    <t>FARINHA TRIGO NORDESTE 5KG</t>
-  </si>
-  <si>
-    <t>840</t>
-  </si>
-  <si>
-    <t>2856</t>
+    <t>AGUA MIN DA PEDRA PET 500ML</t>
+  </si>
+  <si>
+    <t>ARROZ BCO ALEGRETE TP1 5KG</t>
+  </si>
+  <si>
+    <t>CESTA BASICA MED</t>
+  </si>
+  <si>
+    <t>15765</t>
+  </si>
+  <si>
+    <t>17320</t>
+  </si>
+  <si>
+    <t>838</t>
+  </si>
+  <si>
+    <t>1369</t>
+  </si>
+  <si>
+    <t>1371</t>
+  </si>
+  <si>
+    <t>2074</t>
+  </si>
+  <si>
+    <t>2115</t>
+  </si>
+  <si>
+    <t>2749</t>
+  </si>
+  <si>
+    <t>15762</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>1262</t>
+  </si>
+  <si>
+    <t>1321</t>
+  </si>
+  <si>
+    <t>2396</t>
+  </si>
+  <si>
+    <t>2785</t>
+  </si>
+  <si>
+    <t>20282</t>
   </si>
   <si>
     <t>37075</t>
@@ -330,626 +355,575 @@
     <t>39262</t>
   </si>
   <si>
+    <t>2637</t>
+  </si>
+  <si>
+    <t>6340</t>
+  </si>
+  <si>
+    <t>2737</t>
+  </si>
+  <si>
+    <t>825</t>
+  </si>
+  <si>
+    <t>2140</t>
+  </si>
+  <si>
+    <t>12228</t>
+  </si>
+  <si>
+    <t>36245</t>
+  </si>
+  <si>
+    <t>2942</t>
+  </si>
+  <si>
+    <t>3289</t>
+  </si>
+  <si>
+    <t>3298</t>
+  </si>
+  <si>
+    <t>5857</t>
+  </si>
+  <si>
+    <t>6228</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>2158</t>
+  </si>
+  <si>
+    <t>6781</t>
+  </si>
+  <si>
+    <t>22903</t>
+  </si>
+  <si>
+    <t>835</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>806</t>
+  </si>
+  <si>
+    <t>2319</t>
+  </si>
+  <si>
+    <t>3704</t>
+  </si>
+  <si>
+    <t>6339</t>
+  </si>
+  <si>
+    <t>18564</t>
+  </si>
+  <si>
+    <t>20651</t>
+  </si>
+  <si>
+    <t>948</t>
+  </si>
+  <si>
+    <t>6341</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>5545</t>
+  </si>
+  <si>
+    <t>24984</t>
+  </si>
+  <si>
+    <t>33255</t>
+  </si>
+  <si>
+    <t>39264</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>812</t>
+  </si>
+  <si>
+    <t>2161</t>
+  </si>
+  <si>
+    <t>15764</t>
+  </si>
+  <si>
+    <t>LAVA ROUPA LIQ APYCE 3L LIMP TOTAL ROSA</t>
+  </si>
+  <si>
+    <t>REFRIG FRUKI PET 3L GUARANA</t>
+  </si>
+  <si>
+    <t>CHOC STICK 25G OURO BCO</t>
+  </si>
+  <si>
+    <t>CHOC STICK 25G SONHO VALSA</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 5L S GAS</t>
+  </si>
+  <si>
+    <t>CHOC LACTA RECH 98G OURO BRANCO</t>
+  </si>
+  <si>
+    <t>CHOC LACTA 145G SHOT</t>
+  </si>
+  <si>
+    <t>FAROFA MANDIOCA YOKI 200G C TEMPERO SUAVE</t>
+  </si>
+  <si>
+    <t>LUVA DANNY SILVER GRIP M AZUL</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 1 5L FRUTAS VERM</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 1 5L ABACAXI C HORT</t>
+  </si>
+  <si>
+    <t>INSET AERO RAID 420ML BASE AGUA</t>
+  </si>
+  <si>
+    <t>ESC DENTAL SORRISO MACIA</t>
+  </si>
+  <si>
+    <t>GEL DENT SORRISO FRESH 90G XTRA MINT</t>
+  </si>
+  <si>
+    <t>CERV BRAHMA CHOPP GF 1L RETORNAVEL</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML GREEN ZERO</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA LARANJA PET 2L</t>
+  </si>
+  <si>
+    <t>MIST P BOLO APTI 400G CHOC</t>
+  </si>
+  <si>
+    <t>INSET AERO RAID 420ML BARATA FORMIGA</t>
+  </si>
+  <si>
+    <t>FLANELA ALG PANOSUL 34X50CM AMAR</t>
+  </si>
+  <si>
+    <t>MASSA DOMELLY SEMOLA 1KG PARAF</t>
+  </si>
+  <si>
+    <t>INSET AERO RAID 420ML CITRONELA</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML GREEN</t>
+  </si>
+  <si>
+    <t>DESOD AERO GLADE 360ML EMB ECONOMIC BRISA CITRICA</t>
+  </si>
+  <si>
+    <t>REFRIG CHARRUA PET 3L GUARANA</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 500ML ABACAXI C HORT</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML ABSOLUT ZERO</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA UVA PET 2L</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>09/11/2024</t>
+  </si>
+  <si>
+    <t>03/12/2024</t>
+  </si>
+  <si>
+    <t>04/12/2024</t>
+  </si>
+  <si>
+    <t>14/12/2024</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>07/11/2024</t>
+  </si>
+  <si>
+    <t>08/11/2024</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>16/12/2024</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>26/08/2026</t>
+  </si>
+  <si>
+    <t>12/12/2024</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>13/12/2024</t>
+  </si>
+  <si>
+    <t>28/01/2026</t>
+  </si>
+  <si>
+    <t>17/12/2024</t>
+  </si>
+  <si>
+    <t>23/12/2024</t>
+  </si>
+  <si>
+    <t>24/12/2024</t>
+  </si>
+  <si>
+    <t>23/09/2024</t>
+  </si>
+  <si>
+    <t>05/12/2024</t>
+  </si>
+  <si>
+    <t>05/10/2024</t>
+  </si>
+  <si>
+    <t>19/10/2024</t>
+  </si>
+  <si>
+    <t>07/12/2024</t>
+  </si>
+  <si>
+    <t>31/12/2024</t>
+  </si>
+  <si>
+    <t>25/10/2024</t>
+  </si>
+  <si>
+    <t>07/07/2025</t>
+  </si>
+  <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>709</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>636</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>625</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>1865</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>2536</t>
+  </si>
+  <si>
+    <t>945</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>1432</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>1334</t>
+  </si>
+  <si>
+    <t>2233</t>
+  </si>
+  <si>
+    <t>2904</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>1423</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>885</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
     <t>303</t>
   </si>
   <si>
-    <t>2637</t>
-  </si>
-  <si>
-    <t>6340</t>
-  </si>
-  <si>
-    <t>6828</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>1678</t>
-  </si>
-  <si>
-    <t>1679</t>
-  </si>
-  <si>
-    <t>1681</t>
-  </si>
-  <si>
-    <t>2329</t>
-  </si>
-  <si>
-    <t>2447</t>
-  </si>
-  <si>
-    <t>2497</t>
-  </si>
-  <si>
-    <t>3512</t>
-  </si>
-  <si>
-    <t>10145</t>
-  </si>
-  <si>
-    <t>10555</t>
-  </si>
-  <si>
-    <t>10556</t>
-  </si>
-  <si>
-    <t>11671</t>
-  </si>
-  <si>
-    <t>13277</t>
-  </si>
-  <si>
-    <t>38964</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>2722</t>
-  </si>
-  <si>
-    <t>889</t>
-  </si>
-  <si>
-    <t>896</t>
-  </si>
-  <si>
-    <t>899</t>
-  </si>
-  <si>
-    <t>2942</t>
-  </si>
-  <si>
-    <t>3181</t>
-  </si>
-  <si>
-    <t>3289</t>
-  </si>
-  <si>
-    <t>3298</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>835</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>806</t>
-  </si>
-  <si>
-    <t>3704</t>
-  </si>
-  <si>
-    <t>6339</t>
-  </si>
-  <si>
-    <t>948</t>
-  </si>
-  <si>
-    <t>1369</t>
-  </si>
-  <si>
-    <t>1371</t>
-  </si>
-  <si>
-    <t>2367</t>
-  </si>
-  <si>
-    <t>3272</t>
-  </si>
-  <si>
-    <t>6341</t>
-  </si>
-  <si>
-    <t>12308</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t>4212</t>
-  </si>
-  <si>
-    <t>33255</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>812</t>
-  </si>
-  <si>
-    <t>1028</t>
-  </si>
-  <si>
-    <t>1454</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2760</t>
-  </si>
-  <si>
-    <t>MASSA C OVOS NORDESTE 500G PENNE</t>
-  </si>
-  <si>
-    <t>AGUA MIN DA PEDRA PET 1 5L FRUTAS VERM</t>
-  </si>
-  <si>
-    <t>AGUA MIN DA PEDRA PET 1 5L ABACAXI C HORT</t>
-  </si>
-  <si>
-    <t>INSET AERO RAID 420ML BASE AGUA</t>
-  </si>
-  <si>
-    <t>AGUA SABORIZ H2OH 500ML LIMONETO</t>
-  </si>
-  <si>
-    <t>VH COUNTRY WINE BORDO 750ML SV</t>
-  </si>
-  <si>
-    <t>PEPINO CONSERVA ODERICH VD 300G TRAD</t>
-  </si>
-  <si>
-    <t>KETCHUP ODERICH BISN 400G TRAD</t>
-  </si>
-  <si>
-    <t>SAB BAR FARNESE 180G ERV DOCE VERB</t>
-  </si>
-  <si>
-    <t>ATUM RALADO NAUTIQUE 170G MOLHO TOMATE</t>
-  </si>
-  <si>
-    <t>AGUA GASEIFICADA CRYSTAL PET 510ML FRUTAS VERMELHA</t>
-  </si>
-  <si>
-    <t>REFRIG COCA COLA LT 350ML</t>
-  </si>
-  <si>
-    <t>REFRIG FANTA LARANJA LT 350ML</t>
-  </si>
-  <si>
-    <t>REFRIG FANTA UVA LT 350ML</t>
-  </si>
-  <si>
-    <t>REFRIG FANTA LARANJA PET 2L</t>
-  </si>
-  <si>
-    <t>MIST P BOLO APTI 400G CHOC</t>
-  </si>
-  <si>
-    <t>INSET AERO RAID 420ML BARATA FORMIGA</t>
-  </si>
-  <si>
-    <t>CHOC STICK 25G OURO BCO</t>
-  </si>
-  <si>
-    <t>CHOC STICK 25G SONHO VALSA</t>
-  </si>
-  <si>
-    <t>SALG OBBA 100G PICANHA</t>
-  </si>
-  <si>
-    <t>INSET AERO RAID 420ML CITRONELA</t>
-  </si>
-  <si>
-    <t>ENERG MONSTER LT 473ML GREEN</t>
-  </si>
-  <si>
-    <t>AMAC GOTA LIMPA 5L DELICATA</t>
-  </si>
-  <si>
-    <t>REFRIG CHARRUA PET 3L GUARANA</t>
-  </si>
-  <si>
-    <t>ENERG MONSTER LT 473ML ABSOLUT ZERO</t>
-  </si>
-  <si>
-    <t>REFRIG FANTA UVA PET 2L</t>
-  </si>
-  <si>
-    <t>BISC RECH SAPECA 120G DOCE LEITE</t>
-  </si>
-  <si>
-    <t>CAFE VACUO STARBUCKS 250G PIKE PLACE</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>21/10/2024</t>
-  </si>
-  <si>
-    <t>16/12/2024</t>
-  </si>
-  <si>
-    <t>24/02/2026</t>
-  </si>
-  <si>
-    <t>26/08/2026</t>
-  </si>
-  <si>
-    <t>01/10/2024</t>
-  </si>
-  <si>
-    <t>12/12/2024</t>
-  </si>
-  <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>28/09/2024</t>
-  </si>
-  <si>
-    <t>21/11/2024</t>
-  </si>
-  <si>
-    <t>07/12/2024</t>
-  </si>
-  <si>
-    <t>09/12/2024</t>
-  </si>
-  <si>
-    <t>10/12/2024</t>
-  </si>
-  <si>
-    <t>28/12/2024</t>
-  </si>
-  <si>
-    <t>11/06/2025</t>
-  </si>
-  <si>
-    <t>18/07/2026</t>
-  </si>
-  <si>
-    <t>21/09/2024</t>
-  </si>
-  <si>
-    <t>13/12/2024</t>
-  </si>
-  <si>
-    <t>22/10/2024</t>
-  </si>
-  <si>
-    <t>17/12/2024</t>
-  </si>
-  <si>
-    <t>20/12/2024</t>
-  </si>
-  <si>
-    <t>23/12/2024</t>
-  </si>
-  <si>
-    <t>24/12/2024</t>
-  </si>
-  <si>
-    <t>25/09/2024</t>
-  </si>
-  <si>
-    <t>19/10/2024</t>
-  </si>
-  <si>
-    <t>31/12/2024</t>
-  </si>
-  <si>
-    <t>25/10/2024</t>
-  </si>
-  <si>
-    <t>09/11/2024</t>
-  </si>
-  <si>
-    <t>05/10/2024</t>
-  </si>
-  <si>
-    <t>07/07/2025</t>
-  </si>
-  <si>
-    <t>28/10/2024</t>
-  </si>
-  <si>
-    <t>12/11/2024</t>
-  </si>
-  <si>
-    <t>30/11/2024</t>
-  </si>
-  <si>
-    <t>14/12/2024</t>
-  </si>
-  <si>
-    <t>Ativo</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1359</t>
-  </si>
-  <si>
-    <t>177</t>
-  </si>
-  <si>
-    <t>461</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>2163</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>322</t>
-  </si>
-  <si>
-    <t>19,62</t>
-  </si>
-  <si>
-    <t>20,38</t>
-  </si>
-  <si>
-    <t>29,62</t>
-  </si>
-  <si>
-    <t>153</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>1473</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>363</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>1435</t>
-  </si>
-  <si>
-    <t>554</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>894</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>515</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>1479</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>509</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>69</t>
+    <t>97</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>1475</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>511</t>
+  </si>
+  <si>
+    <t>1914</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO BAKLIZI LTDA</t>
+  </si>
+  <si>
+    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
+  </si>
+  <si>
+    <t>BEBIDAS FRUKI LTDA</t>
+  </si>
+  <si>
+    <t>TOPFLEX DISTRIBUIDOR DE ALIMENTOS</t>
+  </si>
+  <si>
+    <t>FERRUCCI E MIRANDA LTDA-EPP</t>
+  </si>
+  <si>
+    <t>PILECCO E CIA. LTDA</t>
+  </si>
+  <si>
+    <t>ANTONIAZZI &amp; CIA LTDA</t>
+  </si>
+  <si>
+    <t>ANGELO AURICCHIO &amp; CIA LTDA</t>
+  </si>
+  <si>
+    <t>FABIANO ZAFFALON E CIA LTDA</t>
+  </si>
+  <si>
+    <t>DVT COMERCIO IMPORTACAO EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t>ROCHA E FILHOS LTDA</t>
+  </si>
+  <si>
+    <t>PONCHE VERDE INDL. DO MATE LTDA.</t>
+  </si>
+  <si>
+    <t>ONIZ DISTRIBUID LTDA SCJ</t>
+  </si>
+  <si>
+    <t>MOINHOS GALOPOLIS S/A</t>
   </si>
   <si>
     <t>CRBS AS CDD PELOTAS</t>
   </si>
   <si>
-    <t>MOINHO DO NORDESTE SA</t>
-  </si>
-  <si>
-    <t>ROCHA E FILHOS LTDA</t>
-  </si>
-  <si>
-    <t>BEBIDAS FRUKI LTDA</t>
-  </si>
-  <si>
-    <t>CARLOS CANCIAN E CIA LTDA</t>
-  </si>
-  <si>
-    <t>PONCHE VERDE INDL. DO MATE LTDA.</t>
-  </si>
-  <si>
-    <t>ONIZ DISTRIBUID LTDA SCJ</t>
-  </si>
-  <si>
-    <t>COOP VINICOLA AURORA LTDA</t>
-  </si>
-  <si>
-    <t>VONPAR ALIMENTOS S.A</t>
-  </si>
-  <si>
-    <t>COOP AGRICOLA MISTA NOVA PALMA LTDA</t>
-  </si>
-  <si>
-    <t>CONSERVAS ODERICH SA</t>
-  </si>
-  <si>
-    <t>FERMENTO GOOD INSTANT LTDA.</t>
-  </si>
-  <si>
-    <t>UNIAGRO -IND.E COM.DE PROD.ALIM.LTDA</t>
-  </si>
-  <si>
-    <t>TONDO S/A</t>
+    <t>ACUCAREIRA ENERGY LTDA</t>
+  </si>
+  <si>
+    <t>NESTLE BRASIL LTDA</t>
+  </si>
+  <si>
+    <t>APTI ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>FITOS ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>PODAL IND E COM DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
+  </si>
+  <si>
+    <t>AMAZONIA BRASIL COSMETICOS LTDA</t>
+  </si>
+  <si>
+    <t>SPAL IND BRAS BEBIDAS AS</t>
   </si>
   <si>
     <t>SMG INDUSTRIAL LTDA</t>
   </si>
   <si>
-    <t>SPAL IND BRAS BEBIDAS AS</t>
-  </si>
-  <si>
-    <t>MOINHO ESTRELA LTDA</t>
-  </si>
-  <si>
-    <t>APTI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>DELAVY ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>FITOS ALIMENTOS LTDA</t>
+    <t>HIPER TEXTIL LTDA</t>
+  </si>
+  <si>
+    <t>REDOL ALIMENTOS LTDA</t>
   </si>
   <si>
     <t>CAMIL ALIMENTOS S/A</t>
-  </si>
-  <si>
-    <t>TOPFLEX DISTRIBUIDOR DE ALIMENTOS</t>
-  </si>
-  <si>
-    <t>FUGINI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>INDUSTRIA MISSIATO DE BEBIDAS LTDA</t>
-  </si>
-  <si>
-    <t>BERTOLINI INDUSTRIA QUIMICA LTDA</t>
-  </si>
-  <si>
-    <t>IRMAOS RUIVO LTDA</t>
-  </si>
-  <si>
-    <t>GERMANI ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>NESTLE BRASIL LTDA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -986,21 +960,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1038,7 +1004,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1072,7 +1038,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1107,10 +1072,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1283,15 +1247,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1371,45 +1331,45 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
       </c>
       <c r="D2">
-        <v>652</v>
+        <v>12054</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
         <v>95</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -1421,13 +1381,13 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="R2">
-        <v>156</v>
+        <v>5</v>
       </c>
       <c r="S2">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -1439,75 +1399,75 @@
         <v>90</v>
       </c>
       <c r="W2">
-        <v>9638</v>
+        <v>15</v>
       </c>
       <c r="X2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Y2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="Z2">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>2067</v>
+        <v>13166</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
         <v>96</v>
       </c>
       <c r="G3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H3" t="s">
         <v>177</v>
       </c>
       <c r="I3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="R3">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="S3">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -1519,57 +1479,57 @@
         <v>90</v>
       </c>
       <c r="W3">
-        <v>10321</v>
+        <v>5894</v>
       </c>
       <c r="X3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Y3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
         <v>36</v>
       </c>
       <c r="D4">
-        <v>55690</v>
+        <v>650</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
         <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="H4" t="s">
         <v>177</v>
       </c>
       <c r="I4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J4" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K4" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L4">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -1581,13 +1541,13 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="R4">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="S4">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -1599,33 +1559,33 @@
         <v>90</v>
       </c>
       <c r="W4">
-        <v>21894</v>
+        <v>6424</v>
       </c>
       <c r="X4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Y4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>64427</v>
+        <v>1027</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
         <v>98</v>
@@ -1637,19 +1597,19 @@
         <v>177</v>
       </c>
       <c r="I5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J5" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K5" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -1661,13 +1621,13 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="R5">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="S5">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -1679,33 +1639,33 @@
         <v>90</v>
       </c>
       <c r="W5">
-        <v>6424</v>
+        <v>13838</v>
       </c>
       <c r="X5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="Y5">
         <v>3</v>
       </c>
       <c r="Z5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
       </c>
       <c r="D6">
-        <v>64427</v>
+        <v>1027</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
         <v>99</v>
@@ -1717,19 +1677,19 @@
         <v>177</v>
       </c>
       <c r="I6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J6" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K6" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -1741,13 +1701,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="R6">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="S6">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -1759,57 +1719,57 @@
         <v>90</v>
       </c>
       <c r="W6">
-        <v>6424</v>
+        <v>13838</v>
       </c>
       <c r="X6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="Y6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z6">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>360</v>
+        <v>1425</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
         <v>100</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H7" t="s">
         <v>177</v>
       </c>
       <c r="I7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K7" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="L7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M7">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -1821,13 +1781,13 @@
         <v>0</v>
       </c>
       <c r="Q7" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="R7">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="S7">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -1839,19 +1799,19 @@
         <v>90</v>
       </c>
       <c r="W7">
-        <v>14469</v>
+        <v>7918</v>
       </c>
       <c r="X7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Y7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z7">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1859,37 +1819,37 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8">
-        <v>1898</v>
+        <v>1465</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
         <v>101</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H8" t="s">
         <v>177</v>
       </c>
       <c r="I8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J8" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K8" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="L8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M8">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -1901,10 +1861,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="R8">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="S8">
         <v>30</v>
@@ -1919,57 +1879,57 @@
         <v>90</v>
       </c>
       <c r="W8">
-        <v>9605</v>
+        <v>12592</v>
       </c>
       <c r="X8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Y8">
         <v>2</v>
       </c>
       <c r="Z8">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>4399</v>
+        <v>1994</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
         <v>102</v>
       </c>
       <c r="G9" t="s">
-        <v>152</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
         <v>177</v>
       </c>
       <c r="I9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J9" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K9" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="L9">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -1981,13 +1941,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="R9">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="S9">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -1999,57 +1959,57 @@
         <v>90</v>
       </c>
       <c r="W9">
-        <v>6644</v>
+        <v>6560</v>
       </c>
       <c r="X9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="Y9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z9">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10">
-        <v>4373</v>
+        <v>12051</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
         <v>103</v>
       </c>
       <c r="G10" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="H10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I10" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="J10" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K10" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="L10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -2061,13 +2021,13 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="R10">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -2079,57 +2039,57 @@
         <v>90</v>
       </c>
       <c r="W10">
-        <v>9638</v>
+        <v>15</v>
       </c>
       <c r="X10" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Y10">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Z10">
-        <v>28.17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D11">
-        <v>299</v>
+        <v>12054</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G11" t="s">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I11" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="J11" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K11" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -2141,13 +2101,13 @@
         <v>0</v>
       </c>
       <c r="Q11" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="R11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -2159,57 +2119,57 @@
         <v>90</v>
       </c>
       <c r="W11">
-        <v>7246</v>
+        <v>15</v>
       </c>
       <c r="X11" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="Y11">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Z11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12">
-        <v>36370</v>
+        <v>182</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="H12" t="s">
         <v>177</v>
       </c>
       <c r="I12" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J12" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K12" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="L12">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2221,13 +2181,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="R12">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="S12">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -2239,57 +2199,57 @@
         <v>90</v>
       </c>
       <c r="W12">
-        <v>6703</v>
+        <v>6424</v>
       </c>
       <c r="X12" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="Y12">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Z12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
       <c r="A13" t="s">
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13">
-        <v>36372</v>
+        <v>967</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="H13" t="s">
         <v>177</v>
       </c>
       <c r="I13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J13" t="s">
+        <v>207</v>
+      </c>
+      <c r="K13" t="s">
         <v>213</v>
       </c>
-      <c r="K13" t="s">
-        <v>221</v>
-      </c>
       <c r="L13">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2301,13 +2261,13 @@
         <v>0</v>
       </c>
       <c r="Q13" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="R13">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="S13">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="T13">
         <v>0</v>
@@ -2319,75 +2279,75 @@
         <v>90</v>
       </c>
       <c r="W13">
-        <v>6703</v>
+        <v>13838</v>
       </c>
       <c r="X13" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="Y13">
         <v>2</v>
       </c>
       <c r="Z13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14">
-        <v>36373</v>
+        <v>986</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="H14" t="s">
         <v>177</v>
       </c>
       <c r="I14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J14" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K14" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="L14">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="M14">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="R14">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="S14">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -2399,19 +2359,19 @@
         <v>90</v>
       </c>
       <c r="W14">
-        <v>6703</v>
+        <v>13838</v>
       </c>
       <c r="X14" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="Y14">
         <v>2</v>
       </c>
       <c r="Z14">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2419,55 +2379,55 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15">
-        <v>1655</v>
+        <v>1719</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
         <v>177</v>
       </c>
       <c r="I15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J15" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K15" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="L15">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M15">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="N15">
         <v>0</v>
       </c>
       <c r="O15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="R15">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="S15">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -2479,19 +2439,19 @@
         <v>90</v>
       </c>
       <c r="W15">
-        <v>15165</v>
+        <v>7715</v>
       </c>
       <c r="X15" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z15">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2499,16 +2459,16 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16">
-        <v>1763</v>
+        <v>2020</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G16" t="s">
         <v>155</v>
@@ -2517,19 +2477,19 @@
         <v>177</v>
       </c>
       <c r="I16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J16" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M16">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2541,13 +2501,13 @@
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="R16">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="S16">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -2559,19 +2519,19 @@
         <v>90</v>
       </c>
       <c r="W16">
-        <v>15520</v>
+        <v>3527</v>
       </c>
       <c r="X16" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="Y16">
         <v>2</v>
       </c>
       <c r="Z16">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2579,37 +2539,37 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17">
-        <v>1798</v>
+        <v>12051</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G17" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="H17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I17" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="J17" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K17" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="L17">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2621,13 +2581,13 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="R17">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S17">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="T17">
         <v>0</v>
@@ -2639,137 +2599,137 @@
         <v>90</v>
       </c>
       <c r="W17">
-        <v>14671</v>
+        <v>15</v>
       </c>
       <c r="X17" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="Y17">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18">
-        <v>2574</v>
+        <v>15374</v>
       </c>
       <c r="E18" t="s">
         <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G18" t="s">
-        <v>62</v>
+        <v>156</v>
       </c>
       <c r="H18" t="s">
         <v>177</v>
       </c>
       <c r="I18" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="J18" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K18" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="L18">
+        <v>12</v>
+      </c>
+      <c r="M18">
+        <v>7</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>233</v>
+      </c>
+      <c r="R18">
+        <v>10</v>
+      </c>
+      <c r="S18">
+        <v>22</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>90</v>
+      </c>
+      <c r="W18">
+        <v>8986</v>
+      </c>
+      <c r="X18" t="s">
+        <v>283</v>
+      </c>
+      <c r="Y18">
+        <v>2</v>
+      </c>
+      <c r="Z18">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
         <v>30</v>
       </c>
-      <c r="M18">
-        <v>66</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>241</v>
-      </c>
-      <c r="R18">
-        <v>90</v>
-      </c>
-      <c r="S18">
-        <v>150</v>
-      </c>
-      <c r="T18">
-        <v>120</v>
-      </c>
-      <c r="U18">
-        <v>150</v>
-      </c>
-      <c r="V18">
-        <v>90</v>
-      </c>
-      <c r="W18">
-        <v>3974</v>
-      </c>
-      <c r="X18" t="s">
-        <v>288</v>
-      </c>
-      <c r="Y18">
-        <v>3</v>
-      </c>
-      <c r="Z18">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19">
-        <v>7117</v>
+        <v>55690</v>
       </c>
       <c r="E19" t="s">
         <v>63</v>
       </c>
       <c r="F19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G19" t="s">
-        <v>157</v>
+        <v>63</v>
       </c>
       <c r="H19" t="s">
         <v>177</v>
       </c>
       <c r="I19" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J19" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K19" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="L19">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="M19">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -2781,13 +2741,13 @@
         <v>0</v>
       </c>
       <c r="Q19" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="R19">
         <v>22</v>
       </c>
       <c r="S19">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="T19">
         <v>0</v>
@@ -2799,57 +2759,57 @@
         <v>90</v>
       </c>
       <c r="W19">
-        <v>6644</v>
+        <v>21894</v>
       </c>
       <c r="X19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Y19">
         <v>2</v>
       </c>
       <c r="Z19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20">
-        <v>7417</v>
+        <v>64427</v>
       </c>
       <c r="E20" t="s">
         <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G20" t="s">
-        <v>64</v>
+        <v>157</v>
       </c>
       <c r="H20" t="s">
         <v>177</v>
       </c>
       <c r="I20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J20" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>0.44400000000000001</v>
+        <v>0</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2861,13 +2821,13 @@
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="R20">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S20">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -2879,54 +2839,54 @@
         <v>90</v>
       </c>
       <c r="W20">
-        <v>14718</v>
+        <v>6424</v>
       </c>
       <c r="X20" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="Y20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z20">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21">
-        <v>7418</v>
+        <v>64427</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G21" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="H21" t="s">
         <v>177</v>
       </c>
       <c r="I21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J21" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -2941,13 +2901,13 @@
         <v>0</v>
       </c>
       <c r="Q21" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="R21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S21">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -2959,48 +2919,48 @@
         <v>90</v>
       </c>
       <c r="W21">
-        <v>14718</v>
+        <v>6424</v>
       </c>
       <c r="X21" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="Y21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z21">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
         <v>38</v>
       </c>
       <c r="D22">
-        <v>8502</v>
+        <v>1898</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H22" t="s">
         <v>177</v>
       </c>
       <c r="I22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J22" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K22" t="s">
         <v>219</v>
@@ -3009,7 +2969,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>0.25600000000000001</v>
+        <v>18</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -3021,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="R22">
         <v>20</v>
       </c>
       <c r="S22">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -3039,57 +2999,57 @@
         <v>90</v>
       </c>
       <c r="W22">
-        <v>14718</v>
+        <v>9605</v>
       </c>
       <c r="X22" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="Y22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z22">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
       </c>
       <c r="D23">
-        <v>9859</v>
+        <v>4399</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F23" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c r="H23" t="s">
         <v>177</v>
       </c>
       <c r="I23" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="J23" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K23" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="L23">
         <v>12</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -3101,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="R23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T23">
         <v>0</v>
@@ -3119,19 +3079,19 @@
         <v>90</v>
       </c>
       <c r="W23">
-        <v>10683</v>
+        <v>6644</v>
       </c>
       <c r="X23" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="Y23">
         <v>2</v>
       </c>
       <c r="Z23">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -3139,19 +3099,19 @@
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24">
-        <v>1633</v>
+        <v>1972</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G24" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="H24" t="s">
         <v>177</v>
@@ -3160,16 +3120,16 @@
         <v>194</v>
       </c>
       <c r="J24" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L24">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -3181,13 +3141,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="R24">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="S24">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="T24">
         <v>0</v>
@@ -3199,57 +3159,57 @@
         <v>90</v>
       </c>
       <c r="W24">
-        <v>4083</v>
+        <v>14328</v>
       </c>
       <c r="X24" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="Y24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z24">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
         <v>39</v>
       </c>
       <c r="D25">
-        <v>189</v>
+        <v>12054</v>
       </c>
       <c r="E25" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
       <c r="H25" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I25" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="J25" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K25" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -3261,13 +3221,13 @@
         <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="R25">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="S25">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>0</v>
@@ -3279,57 +3239,57 @@
         <v>90</v>
       </c>
       <c r="W25">
-        <v>15441</v>
+        <v>15</v>
       </c>
       <c r="X25" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="Y25">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D26">
-        <v>1974</v>
+        <v>47390</v>
       </c>
       <c r="E26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H26" t="s">
         <v>177</v>
       </c>
       <c r="I26" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="J26" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K26" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -3341,13 +3301,13 @@
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="R26">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="S26">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -3359,58 +3319,58 @@
         <v>90</v>
       </c>
       <c r="W26">
-        <v>16900</v>
+        <v>9638</v>
       </c>
       <c r="X26" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="Y26">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Z26">
-        <v>1568.1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
         <v>40</v>
       </c>
       <c r="D27">
-        <v>41</v>
+        <v>1027</v>
       </c>
       <c r="E27" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="F27" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="G27" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="H27" t="s">
         <v>177</v>
       </c>
       <c r="I27" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="J27" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K27" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="L27">
+        <v>15</v>
+      </c>
+      <c r="M27">
         <v>12</v>
       </c>
-      <c r="M27">
-        <v>116</v>
-      </c>
       <c r="N27">
         <v>0</v>
       </c>
@@ -3421,13 +3381,13 @@
         <v>0</v>
       </c>
       <c r="Q27" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="R27">
-        <v>190</v>
+        <v>39</v>
       </c>
       <c r="S27">
-        <v>298</v>
+        <v>69</v>
       </c>
       <c r="T27">
         <v>0</v>
@@ -3439,57 +3399,57 @@
         <v>90</v>
       </c>
       <c r="W27">
-        <v>15441</v>
+        <v>13838</v>
       </c>
       <c r="X27" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="Y27">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Z27">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
         <v>40</v>
       </c>
       <c r="D28">
-        <v>696</v>
+        <v>1027</v>
       </c>
       <c r="E28" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F28" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="G28" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="H28" t="s">
         <v>177</v>
       </c>
       <c r="I28" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="J28" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K28" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M28">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -3501,13 +3461,13 @@
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="R28">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="S28">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="T28">
         <v>0</v>
@@ -3519,75 +3479,75 @@
         <v>90</v>
       </c>
       <c r="W28">
-        <v>15441</v>
+        <v>13838</v>
       </c>
       <c r="X28" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="Y28">
         <v>3</v>
       </c>
       <c r="Z28">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
         <v>40</v>
       </c>
       <c r="D29">
-        <v>700</v>
+        <v>1489</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F29" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G29" t="s">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="H29" t="s">
         <v>177</v>
       </c>
       <c r="I29" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="J29" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L29">
         <v>6</v>
       </c>
       <c r="M29">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="N29">
         <v>0</v>
       </c>
       <c r="O29">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P29">
         <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="R29">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="S29">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="T29">
         <v>0</v>
@@ -3599,57 +3559,57 @@
         <v>90</v>
       </c>
       <c r="W29">
-        <v>15441</v>
+        <v>7918</v>
       </c>
       <c r="X29" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z29">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26">
       <c r="A30" t="s">
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
         <v>40</v>
       </c>
       <c r="D30">
-        <v>2141</v>
+        <v>12054</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="F30" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="H30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I30" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="J30" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K30" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="L30">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -3661,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="Q30" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="R30">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="T30">
         <v>0</v>
@@ -3679,57 +3639,57 @@
         <v>90</v>
       </c>
       <c r="W30">
-        <v>10189</v>
+        <v>15</v>
       </c>
       <c r="X30" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="Y30">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Z30">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26">
       <c r="A31" t="s">
         <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D31">
-        <v>2350</v>
+        <v>1027</v>
       </c>
       <c r="E31" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="F31" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="H31" t="s">
         <v>177</v>
       </c>
       <c r="I31" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="J31" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K31" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="L31">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M31">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -3741,13 +3701,13 @@
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="R31">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="S31">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="T31">
         <v>0</v>
@@ -3759,137 +3719,137 @@
         <v>90</v>
       </c>
       <c r="W31">
-        <v>2977</v>
+        <v>13838</v>
       </c>
       <c r="X31" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="Y31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26">
       <c r="A32" t="s">
         <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D32">
-        <v>2420</v>
+        <v>1027</v>
       </c>
       <c r="E32" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="F32" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="G32" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="H32" t="s">
         <v>177</v>
       </c>
       <c r="I32" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="J32" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K32" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="L32">
+        <v>15</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>243</v>
+      </c>
+      <c r="R32">
+        <v>39</v>
+      </c>
+      <c r="S32">
+        <v>69</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>90</v>
+      </c>
+      <c r="W32">
+        <v>13838</v>
+      </c>
+      <c r="X32" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y32">
+        <v>5</v>
+      </c>
+      <c r="Z32">
         <v>10</v>
       </c>
-      <c r="M32">
-        <v>8</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>254</v>
-      </c>
-      <c r="R32">
-        <v>10</v>
-      </c>
-      <c r="S32">
-        <v>20</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>90</v>
-      </c>
-      <c r="W32">
-        <v>16857</v>
-      </c>
-      <c r="X32" t="s">
-        <v>296</v>
-      </c>
-      <c r="Y32">
-        <v>2</v>
-      </c>
-      <c r="Z32">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:26">
       <c r="A33" t="s">
         <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D33">
-        <v>2432</v>
+        <v>9079</v>
       </c>
       <c r="E33" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F33" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="G33" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H33" t="s">
         <v>177</v>
       </c>
       <c r="I33" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="J33" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -3901,13 +3861,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="R33">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="S33">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="T33">
         <v>0</v>
@@ -3919,76 +3879,76 @@
         <v>90</v>
       </c>
       <c r="W33">
-        <v>16857</v>
+        <v>15947</v>
       </c>
       <c r="X33" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="Y33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z33">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
         <v>41</v>
       </c>
       <c r="D34">
-        <v>358</v>
+        <v>39790</v>
       </c>
       <c r="E34" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F34" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="G34" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H34" t="s">
         <v>177</v>
       </c>
       <c r="I34" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="J34" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K34" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L34">
+        <v>14</v>
+      </c>
+      <c r="M34">
+        <v>9</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>245</v>
+      </c>
+      <c r="R34">
+        <v>10</v>
+      </c>
+      <c r="S34">
         <v>24</v>
       </c>
-      <c r="M34">
-        <v>15</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>256</v>
-      </c>
-      <c r="R34">
-        <v>22</v>
-      </c>
-      <c r="S34">
-        <v>46</v>
-      </c>
       <c r="T34">
         <v>0</v>
       </c>
@@ -3999,57 +3959,57 @@
         <v>90</v>
       </c>
       <c r="W34">
-        <v>9638</v>
+        <v>15134</v>
       </c>
       <c r="X34" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="Y34">
         <v>2</v>
       </c>
       <c r="Z34">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
         <v>42</v>
       </c>
       <c r="D35">
-        <v>648</v>
+        <v>2141</v>
       </c>
       <c r="E35" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F35" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G35" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H35" t="s">
         <v>177</v>
       </c>
       <c r="I35" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="J35" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K35" t="s">
         <v>217</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M35">
-        <v>165</v>
+        <v>39</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -4061,13 +4021,13 @@
         <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="R35">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="S35">
-        <v>256</v>
+        <v>68</v>
       </c>
       <c r="T35">
         <v>0</v>
@@ -4079,57 +4039,57 @@
         <v>90</v>
       </c>
       <c r="W35">
-        <v>15441</v>
+        <v>10189</v>
       </c>
       <c r="X35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Y35">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Z35">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D36">
-        <v>250</v>
+        <v>2420</v>
       </c>
       <c r="E36" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F36" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H36" t="s">
         <v>177</v>
       </c>
       <c r="I36" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J36" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L36">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -4141,13 +4101,13 @@
         <v>0</v>
       </c>
       <c r="Q36" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="R36">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="T36">
         <v>0</v>
@@ -4159,57 +4119,57 @@
         <v>90</v>
       </c>
       <c r="W36">
-        <v>14469</v>
+        <v>16857</v>
       </c>
       <c r="X36" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="Y36">
         <v>2</v>
       </c>
       <c r="Z36">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37">
-        <v>360</v>
+        <v>2432</v>
       </c>
       <c r="E37" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F37" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="G37" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="H37" t="s">
         <v>177</v>
       </c>
       <c r="I37" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="J37" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L37">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -4221,13 +4181,13 @@
         <v>0</v>
       </c>
       <c r="Q37" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="R37">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="S37">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="T37">
         <v>0</v>
@@ -4239,19 +4199,19 @@
         <v>90</v>
       </c>
       <c r="W37">
-        <v>14469</v>
+        <v>16857</v>
       </c>
       <c r="X37" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="Y37">
         <v>2</v>
       </c>
       <c r="Z37">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -4259,38 +4219,38 @@
         <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D38">
-        <v>625</v>
+        <v>4119</v>
       </c>
       <c r="E38" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F38" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G38" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H38" t="s">
         <v>178</v>
       </c>
       <c r="I38" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="J38" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K38" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="L38">
+        <v>12</v>
+      </c>
+      <c r="M38">
         <v>8</v>
       </c>
-      <c r="M38">
-        <v>114</v>
-      </c>
       <c r="N38">
         <v>0</v>
       </c>
@@ -4301,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="Q38" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="R38">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>198</v>
+        <v>22</v>
       </c>
       <c r="T38">
         <v>0</v>
@@ -4319,57 +4279,57 @@
         <v>90</v>
       </c>
       <c r="W38">
-        <v>15441</v>
+        <v>15318</v>
       </c>
       <c r="X38" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Y38">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Z38">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D39">
-        <v>2700</v>
+        <v>4321</v>
       </c>
       <c r="E39" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F39" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G39" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H39" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I39" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="J39" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K39" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="L39">
         <v>12</v>
       </c>
       <c r="M39">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -4381,13 +4341,13 @@
         <v>0</v>
       </c>
       <c r="Q39" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="R39">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="S39">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="T39">
         <v>0</v>
@@ -4399,57 +4359,57 @@
         <v>90</v>
       </c>
       <c r="W39">
-        <v>10189</v>
+        <v>15318</v>
       </c>
       <c r="X39" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Y39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z39">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26">
       <c r="A40" t="s">
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C40" t="s">
         <v>43</v>
       </c>
       <c r="D40">
-        <v>4399</v>
+        <v>217</v>
       </c>
       <c r="E40" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G40" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H40" t="s">
         <v>177</v>
       </c>
       <c r="I40" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="J40" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K40" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="L40">
         <v>12</v>
       </c>
       <c r="M40">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -4461,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="Q40" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="R40">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="S40">
-        <v>22</v>
+        <v>230</v>
       </c>
       <c r="T40">
         <v>0</v>
@@ -4479,19 +4439,19 @@
         <v>90</v>
       </c>
       <c r="W40">
-        <v>6644</v>
+        <v>9638</v>
       </c>
       <c r="X40" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Y40">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Z40">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26">
       <c r="A41" t="s">
         <v>26</v>
       </c>
@@ -4499,37 +4459,37 @@
         <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D41">
-        <v>744</v>
+        <v>1504</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F41" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="G41" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s">
         <v>177</v>
       </c>
       <c r="I41" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J41" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K41" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L41">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M41">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -4541,13 +4501,13 @@
         <v>0</v>
       </c>
       <c r="Q41" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="R41">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="S41">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="T41">
         <v>0</v>
@@ -4559,218 +4519,218 @@
         <v>90</v>
       </c>
       <c r="W41">
-        <v>11411</v>
+        <v>12592</v>
       </c>
       <c r="X41" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="Y41">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Z41">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D42">
-        <v>1027</v>
+        <v>4693</v>
       </c>
       <c r="E42" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F42" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G42" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s">
         <v>177</v>
       </c>
       <c r="I42" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="J42" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L42">
+        <v>12</v>
+      </c>
+      <c r="M42">
+        <v>191</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>253</v>
+      </c>
+      <c r="R42">
+        <v>236</v>
+      </c>
+      <c r="S42">
+        <v>368</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>90</v>
+      </c>
+      <c r="W42">
+        <v>9379</v>
+      </c>
+      <c r="X42" t="s">
+        <v>294</v>
+      </c>
+      <c r="Y42">
         <v>15</v>
       </c>
-      <c r="M42">
-        <v>1</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>15</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>264</v>
-      </c>
-      <c r="R42">
-        <v>39</v>
-      </c>
-      <c r="S42">
-        <v>69</v>
-      </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42">
-        <v>90</v>
-      </c>
-      <c r="W42">
-        <v>13838</v>
-      </c>
-      <c r="X42" t="s">
-        <v>298</v>
-      </c>
-      <c r="Y42">
-        <v>4</v>
-      </c>
       <c r="Z42">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26">
       <c r="A43" t="s">
         <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D43">
-        <v>1027</v>
+        <v>12054</v>
       </c>
       <c r="E43" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="F43" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="G43" t="s">
-        <v>167</v>
+        <v>49</v>
       </c>
       <c r="H43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I43" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="J43" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K43" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>221</v>
+      </c>
+      <c r="R43">
+        <v>10</v>
+      </c>
+      <c r="S43">
         <v>15</v>
       </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>90</v>
+      </c>
+      <c r="W43">
         <v>15</v>
       </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>215</v>
-      </c>
-      <c r="R43">
-        <v>39</v>
-      </c>
-      <c r="S43">
-        <v>69</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>90</v>
-      </c>
-      <c r="W43">
-        <v>13838</v>
-      </c>
       <c r="X43" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="Y43">
+        <v>15</v>
+      </c>
+      <c r="Z43">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26">
+      <c r="A44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44">
+        <v>17622</v>
+      </c>
+      <c r="E44" t="s">
+        <v>80</v>
+      </c>
+      <c r="F44" t="s">
+        <v>128</v>
+      </c>
+      <c r="G44" t="s">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s">
+        <v>176</v>
+      </c>
+      <c r="I44" t="s">
+        <v>179</v>
+      </c>
+      <c r="J44" t="s">
+        <v>207</v>
+      </c>
+      <c r="K44" t="s">
+        <v>214</v>
+      </c>
+      <c r="L44">
+        <v>12</v>
+      </c>
+      <c r="M44">
         <v>4</v>
       </c>
-      <c r="Z43">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>26</v>
-      </c>
-      <c r="B44" t="s">
-        <v>30</v>
-      </c>
-      <c r="C44" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44">
-        <v>1691</v>
-      </c>
-      <c r="E44" t="s">
-        <v>85</v>
-      </c>
-      <c r="F44" t="s">
-        <v>136</v>
-      </c>
-      <c r="G44" t="s">
-        <v>85</v>
-      </c>
-      <c r="H44" t="s">
-        <v>177</v>
-      </c>
-      <c r="I44" t="s">
-        <v>190</v>
-      </c>
-      <c r="J44" t="s">
-        <v>213</v>
-      </c>
-      <c r="K44" t="s">
-        <v>223</v>
-      </c>
-      <c r="L44">
-        <v>36</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
       <c r="N44">
         <v>0</v>
       </c>
@@ -4781,14 +4741,14 @@
         <v>0</v>
       </c>
       <c r="Q44" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="R44">
+        <v>10</v>
+      </c>
+      <c r="S44">
         <v>22</v>
       </c>
-      <c r="S44">
-        <v>58</v>
-      </c>
       <c r="T44">
         <v>0</v>
       </c>
@@ -4799,21 +4759,21 @@
         <v>90</v>
       </c>
       <c r="W44">
-        <v>5791</v>
+        <v>8425</v>
       </c>
       <c r="X44" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="Y44">
         <v>2</v>
       </c>
       <c r="Z44">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
         <v>32</v>
@@ -4822,52 +4782,52 @@
         <v>44</v>
       </c>
       <c r="D45">
-        <v>2408</v>
+        <v>648</v>
       </c>
       <c r="E45" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F45" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="G45" t="s">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s">
         <v>177</v>
       </c>
       <c r="I45" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="J45" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K45" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L45">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>-8</v>
+        <v>146</v>
       </c>
       <c r="N45">
         <v>0</v>
       </c>
       <c r="O45">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P45">
         <v>0</v>
       </c>
       <c r="Q45" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="R45">
-        <v>12</v>
+        <v>166</v>
       </c>
       <c r="S45">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="T45">
         <v>0</v>
@@ -4879,57 +4839,57 @@
         <v>90</v>
       </c>
       <c r="W45">
-        <v>16857</v>
+        <v>15441</v>
       </c>
       <c r="X45" t="s">
         <v>296</v>
       </c>
       <c r="Y45">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Z45">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C46" t="s">
         <v>44</v>
       </c>
       <c r="D46">
-        <v>4399</v>
+        <v>12051</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F46" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="G46" t="s">
-        <v>169</v>
+        <v>56</v>
       </c>
       <c r="H46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I46" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="J46" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K46" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="L46">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M46">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N46">
         <v>0</v>
@@ -4941,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="Q46" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="R46">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S46">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46">
         <v>0</v>
@@ -4959,57 +4919,57 @@
         <v>90</v>
       </c>
       <c r="W46">
-        <v>6644</v>
+        <v>15</v>
       </c>
       <c r="X46" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="Y46">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Z46">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26">
       <c r="A47" t="s">
         <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D47">
-        <v>9150</v>
+        <v>409</v>
       </c>
       <c r="E47" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F47" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="G47" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="H47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="J47" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L47">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N47">
         <v>0</v>
@@ -5021,13 +4981,13 @@
         <v>0</v>
       </c>
       <c r="Q47" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="R47">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="S47">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="T47">
         <v>0</v>
@@ -5039,57 +4999,57 @@
         <v>90</v>
       </c>
       <c r="W47">
-        <v>16039</v>
+        <v>15441</v>
       </c>
       <c r="X47" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="Y47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z47">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+        <v>211.67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
         <v>45</v>
       </c>
       <c r="D48">
-        <v>409</v>
+        <v>625</v>
       </c>
       <c r="E48" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F48" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="G48" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H48" t="s">
         <v>178</v>
       </c>
       <c r="I48" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="J48" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K48" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="L48">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M48">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="N48">
         <v>0</v>
@@ -5101,13 +5061,13 @@
         <v>0</v>
       </c>
       <c r="Q48" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="R48">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="S48">
-        <v>64</v>
+        <v>198</v>
       </c>
       <c r="T48">
         <v>0</v>
@@ -5122,36 +5082,36 @@
         <v>15441</v>
       </c>
       <c r="X48" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Y48">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Z48">
-        <v>227.83</v>
-      </c>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26">
       <c r="A49" t="s">
         <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C49" t="s">
         <v>45</v>
       </c>
       <c r="D49">
-        <v>2067</v>
+        <v>1027</v>
       </c>
       <c r="E49" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F49" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G49" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H49" t="s">
         <v>177</v>
@@ -5160,60 +5120,60 @@
         <v>181</v>
       </c>
       <c r="J49" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K49" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="L49">
         <v>15</v>
       </c>
       <c r="M49">
+        <v>24</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>258</v>
+      </c>
+      <c r="R49">
+        <v>39</v>
+      </c>
+      <c r="S49">
+        <v>69</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>90</v>
+      </c>
+      <c r="W49">
+        <v>13838</v>
+      </c>
+      <c r="X49" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y49">
         <v>3</v>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>30</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>247</v>
-      </c>
-      <c r="R49">
-        <v>41</v>
-      </c>
-      <c r="S49">
-        <v>56</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
-      <c r="V49">
-        <v>90</v>
-      </c>
-      <c r="W49">
-        <v>10321</v>
-      </c>
-      <c r="X49" t="s">
-        <v>278</v>
-      </c>
-      <c r="Y49">
-        <v>2</v>
-      </c>
       <c r="Z49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26">
       <c r="A50" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B50" t="s">
         <v>33</v>
@@ -5222,114 +5182,114 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>3087</v>
+        <v>1027</v>
       </c>
       <c r="E50" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="F50" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="G50" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="H50" t="s">
         <v>177</v>
       </c>
       <c r="I50" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="J50" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K50" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="L50">
+        <v>15</v>
+      </c>
+      <c r="M50">
+        <v>21</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>259</v>
+      </c>
+      <c r="R50">
+        <v>39</v>
+      </c>
+      <c r="S50">
+        <v>69</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>90</v>
+      </c>
+      <c r="W50">
+        <v>13838</v>
+      </c>
+      <c r="X50" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y50">
         <v>4</v>
       </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>269</v>
-      </c>
-      <c r="R50">
-        <v>16</v>
-      </c>
-      <c r="S50">
-        <v>28</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>90</v>
-      </c>
-      <c r="W50">
-        <v>14468</v>
-      </c>
-      <c r="X50" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y50">
-        <v>7</v>
-      </c>
       <c r="Z50">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C51" t="s">
         <v>45</v>
       </c>
       <c r="D51">
-        <v>27004</v>
+        <v>1646</v>
       </c>
       <c r="E51" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F51" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="G51" t="s">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s">
         <v>177</v>
       </c>
       <c r="I51" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="J51" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K51" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M51">
-        <v>166</v>
+        <v>14</v>
       </c>
       <c r="N51">
         <v>0</v>
@@ -5341,13 +5301,13 @@
         <v>0</v>
       </c>
       <c r="Q51" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R51">
-        <v>172</v>
+        <v>16</v>
       </c>
       <c r="S51">
-        <v>268</v>
+        <v>40</v>
       </c>
       <c r="T51">
         <v>0</v>
@@ -5359,75 +5319,75 @@
         <v>90</v>
       </c>
       <c r="W51">
-        <v>15441</v>
+        <v>4083</v>
       </c>
       <c r="X51" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Y51">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Z51">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D52">
-        <v>409</v>
+        <v>2700</v>
       </c>
       <c r="E52" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F52" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="G52" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="H52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I52" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J52" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K52" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M52">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="N52">
         <v>0</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P52">
         <v>0</v>
       </c>
       <c r="Q52" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="R52">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="S52">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="T52">
         <v>0</v>
@@ -5439,19 +5399,19 @@
         <v>90</v>
       </c>
       <c r="W52">
-        <v>15441</v>
+        <v>10189</v>
       </c>
       <c r="X52" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Y52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z52">
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -5459,117 +5419,117 @@
         <v>31</v>
       </c>
       <c r="C53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D53">
-        <v>625</v>
+        <v>4321</v>
       </c>
       <c r="E53" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F53" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="G53" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="H53" t="s">
         <v>178</v>
       </c>
       <c r="I53" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="J53" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K53" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="L53">
+        <v>12</v>
+      </c>
+      <c r="M53">
+        <v>1</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>249</v>
+      </c>
+      <c r="R53">
+        <v>28</v>
+      </c>
+      <c r="S53">
+        <v>40</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>90</v>
+      </c>
+      <c r="W53">
+        <v>15318</v>
+      </c>
+      <c r="X53" t="s">
+        <v>293</v>
+      </c>
+      <c r="Y53">
+        <v>4</v>
+      </c>
+      <c r="Z53">
         <v>8</v>
       </c>
-      <c r="M53">
-        <v>44</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>0</v>
-      </c>
-      <c r="P53">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>272</v>
-      </c>
-      <c r="R53">
-        <v>58</v>
-      </c>
-      <c r="S53">
-        <v>90</v>
-      </c>
-      <c r="T53">
-        <v>0</v>
-      </c>
-      <c r="U53">
-        <v>0</v>
-      </c>
-      <c r="V53">
-        <v>90</v>
-      </c>
-      <c r="W53">
-        <v>15441</v>
-      </c>
-      <c r="X53" t="s">
-        <v>292</v>
-      </c>
-      <c r="Y53">
-        <v>6</v>
-      </c>
-      <c r="Z53">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:26">
       <c r="A54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D54">
-        <v>818</v>
+        <v>4399</v>
       </c>
       <c r="E54" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F54" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G54" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="H54" t="s">
         <v>177</v>
       </c>
       <c r="I54" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="J54" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K54" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="L54">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N54">
         <v>0</v>
@@ -5581,13 +5541,13 @@
         <v>0</v>
       </c>
       <c r="Q54" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="R54">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="S54">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T54">
         <v>0</v>
@@ -5599,54 +5559,54 @@
         <v>90</v>
       </c>
       <c r="W54">
-        <v>14588</v>
+        <v>6644</v>
       </c>
       <c r="X54" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="Y54">
         <v>2</v>
       </c>
       <c r="Z54">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26">
       <c r="A55" t="s">
         <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D55">
-        <v>1086</v>
+        <v>12054</v>
       </c>
       <c r="E55" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="F55" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="G55" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="H55" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I55" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="J55" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K55" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="L55">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -5661,13 +5621,13 @@
         <v>0</v>
       </c>
       <c r="Q55" t="s">
-        <v>273</v>
+        <v>221</v>
       </c>
       <c r="R55">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="S55">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="T55">
         <v>0</v>
@@ -5679,57 +5639,57 @@
         <v>90</v>
       </c>
       <c r="W55">
-        <v>16963</v>
+        <v>15</v>
       </c>
       <c r="X55" t="s">
-        <v>303</v>
+        <v>274</v>
       </c>
       <c r="Y55">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Z55">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D56">
-        <v>1386</v>
+        <v>14123</v>
       </c>
       <c r="E56" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F56" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="G56" t="s">
+        <v>167</v>
+      </c>
+      <c r="H56" t="s">
         <v>176</v>
       </c>
-      <c r="H56" t="s">
-        <v>177</v>
-      </c>
       <c r="I56" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="J56" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K56" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="L56">
         <v>12</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N56">
         <v>0</v>
@@ -5741,13 +5701,13 @@
         <v>0</v>
       </c>
       <c r="Q56" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="R56">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S56">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T56">
         <v>0</v>
@@ -5759,75 +5719,75 @@
         <v>90</v>
       </c>
       <c r="W56">
-        <v>15134</v>
+        <v>10885</v>
       </c>
       <c r="X56" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="Y56">
         <v>2</v>
       </c>
       <c r="Z56">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26">
       <c r="A57" t="s">
         <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D57">
-        <v>2004</v>
+        <v>15579</v>
       </c>
       <c r="E57" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F57" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="G57" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="H57" t="s">
         <v>177</v>
       </c>
       <c r="I57" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="J57" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K57" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="L57">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M57">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N57">
         <v>0</v>
       </c>
       <c r="O57">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P57">
         <v>0</v>
       </c>
       <c r="Q57" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="R57">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="S57">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="T57">
         <v>0</v>
@@ -5839,75 +5799,75 @@
         <v>90</v>
       </c>
       <c r="W57">
-        <v>10321</v>
+        <v>15886</v>
       </c>
       <c r="X57" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="Y57">
         <v>2</v>
       </c>
       <c r="Z57">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26">
       <c r="A58" t="s">
         <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C58" t="s">
         <v>46</v>
       </c>
       <c r="D58">
-        <v>2067</v>
+        <v>744</v>
       </c>
       <c r="E58" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F58" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="G58" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s">
         <v>177</v>
       </c>
       <c r="I58" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="J58" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L58">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N58">
         <v>0</v>
       </c>
       <c r="O58">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P58">
         <v>0</v>
       </c>
       <c r="Q58" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="R58">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="S58">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="T58">
         <v>0</v>
@@ -5919,20 +5879,1379 @@
         <v>90</v>
       </c>
       <c r="W58">
-        <v>10321</v>
+        <v>11411</v>
       </c>
       <c r="X58" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="Y58">
         <v>2</v>
       </c>
       <c r="Z58">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26">
+      <c r="A59" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59">
+        <v>4399</v>
+      </c>
+      <c r="E59" t="s">
+        <v>66</v>
+      </c>
+      <c r="F59" t="s">
+        <v>138</v>
+      </c>
+      <c r="G59" t="s">
+        <v>169</v>
+      </c>
+      <c r="H59" t="s">
+        <v>177</v>
+      </c>
+      <c r="I59" t="s">
+        <v>193</v>
+      </c>
+      <c r="J59" t="s">
+        <v>207</v>
+      </c>
+      <c r="K59" t="s">
+        <v>214</v>
+      </c>
+      <c r="L59">
+        <v>12</v>
+      </c>
+      <c r="M59">
+        <v>7</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>245</v>
+      </c>
+      <c r="R59">
+        <v>8</v>
+      </c>
+      <c r="S59">
+        <v>20</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>90</v>
+      </c>
+      <c r="W59">
+        <v>6644</v>
+      </c>
+      <c r="X59" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y59">
+        <v>2</v>
+      </c>
+      <c r="Z59">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26">
+      <c r="A60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60">
+        <v>12051</v>
+      </c>
+      <c r="E60" t="s">
+        <v>56</v>
+      </c>
+      <c r="F60" t="s">
+        <v>103</v>
+      </c>
+      <c r="G60" t="s">
+        <v>56</v>
+      </c>
+      <c r="H60" t="s">
+        <v>176</v>
+      </c>
+      <c r="I60" t="s">
+        <v>179</v>
+      </c>
+      <c r="J60" t="s">
+        <v>207</v>
+      </c>
+      <c r="K60" t="s">
+        <v>208</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>221</v>
+      </c>
+      <c r="R60">
         <v>5</v>
       </c>
+      <c r="S60">
+        <v>10</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>90</v>
+      </c>
+      <c r="W60">
+        <v>15</v>
+      </c>
+      <c r="X60" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y60">
+        <v>10</v>
+      </c>
+      <c r="Z60">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26">
+      <c r="A61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61">
+        <v>12054</v>
+      </c>
+      <c r="E61" t="s">
+        <v>49</v>
+      </c>
+      <c r="F61" t="s">
+        <v>95</v>
+      </c>
+      <c r="G61" t="s">
+        <v>49</v>
+      </c>
+      <c r="H61" t="s">
+        <v>176</v>
+      </c>
+      <c r="I61" t="s">
+        <v>179</v>
+      </c>
+      <c r="J61" t="s">
+        <v>207</v>
+      </c>
+      <c r="K61" t="s">
+        <v>208</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="M61">
+        <v>-11</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>221</v>
+      </c>
+      <c r="R61">
+        <v>3</v>
+      </c>
+      <c r="S61">
+        <v>4</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>90</v>
+      </c>
+      <c r="W61">
+        <v>15</v>
+      </c>
+      <c r="X61" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y61">
+        <v>4</v>
+      </c>
+      <c r="Z61">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26">
+      <c r="A62" t="s">
+        <v>28</v>
+      </c>
+      <c r="B62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" t="s">
+        <v>47</v>
+      </c>
+      <c r="D62">
+        <v>409</v>
+      </c>
+      <c r="E62" t="s">
+        <v>82</v>
+      </c>
+      <c r="F62" t="s">
+        <v>139</v>
+      </c>
+      <c r="G62" t="s">
+        <v>170</v>
+      </c>
+      <c r="H62" t="s">
+        <v>178</v>
+      </c>
+      <c r="I62" t="s">
+        <v>201</v>
+      </c>
+      <c r="J62" t="s">
+        <v>207</v>
+      </c>
+      <c r="K62" t="s">
+        <v>218</v>
+      </c>
+      <c r="L62">
+        <v>6</v>
+      </c>
+      <c r="M62">
+        <v>32</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>266</v>
+      </c>
+      <c r="R62">
+        <v>40</v>
+      </c>
+      <c r="S62">
+        <v>64</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>90</v>
+      </c>
+      <c r="W62">
+        <v>15441</v>
+      </c>
+      <c r="X62" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y62">
+        <v>6</v>
+      </c>
+      <c r="Z62">
+        <v>227.83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26">
+      <c r="A63" t="s">
+        <v>26</v>
+      </c>
+      <c r="B63" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" t="s">
+        <v>47</v>
+      </c>
+      <c r="D63">
+        <v>1027</v>
+      </c>
+      <c r="E63" t="s">
+        <v>52</v>
+      </c>
+      <c r="F63" t="s">
+        <v>98</v>
+      </c>
+      <c r="G63" t="s">
+        <v>150</v>
+      </c>
+      <c r="H63" t="s">
+        <v>177</v>
+      </c>
+      <c r="I63" t="s">
+        <v>181</v>
+      </c>
+      <c r="J63" t="s">
+        <v>207</v>
+      </c>
+      <c r="K63" t="s">
+        <v>210</v>
+      </c>
+      <c r="L63">
+        <v>15</v>
+      </c>
+      <c r="M63">
+        <v>14</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>267</v>
+      </c>
+      <c r="R63">
+        <v>39</v>
+      </c>
+      <c r="S63">
+        <v>69</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>90</v>
+      </c>
+      <c r="W63">
+        <v>13838</v>
+      </c>
+      <c r="X63" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y63">
+        <v>4</v>
+      </c>
+      <c r="Z63">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26">
+      <c r="A64" t="s">
+        <v>26</v>
+      </c>
+      <c r="B64" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" t="s">
+        <v>47</v>
+      </c>
+      <c r="D64">
+        <v>1027</v>
+      </c>
+      <c r="E64" t="s">
+        <v>52</v>
+      </c>
+      <c r="F64" t="s">
+        <v>99</v>
+      </c>
+      <c r="G64" t="s">
+        <v>151</v>
+      </c>
+      <c r="H64" t="s">
+        <v>177</v>
+      </c>
+      <c r="I64" t="s">
+        <v>181</v>
+      </c>
+      <c r="J64" t="s">
+        <v>207</v>
+      </c>
+      <c r="K64" t="s">
+        <v>210</v>
+      </c>
+      <c r="L64">
+        <v>15</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>221</v>
+      </c>
+      <c r="R64">
+        <v>45</v>
+      </c>
+      <c r="S64">
+        <v>60</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>90</v>
+      </c>
+      <c r="W64">
+        <v>13838</v>
+      </c>
+      <c r="X64" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y64">
+        <v>4</v>
+      </c>
+      <c r="Z64">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26">
+      <c r="A65" t="s">
+        <v>27</v>
+      </c>
+      <c r="B65" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" t="s">
+        <v>47</v>
+      </c>
+      <c r="D65">
+        <v>3926</v>
+      </c>
+      <c r="E65" t="s">
+        <v>89</v>
+      </c>
+      <c r="F65" t="s">
+        <v>140</v>
+      </c>
+      <c r="G65" t="s">
+        <v>171</v>
+      </c>
+      <c r="H65" t="s">
+        <v>177</v>
+      </c>
+      <c r="I65" t="s">
+        <v>193</v>
+      </c>
+      <c r="J65" t="s">
+        <v>207</v>
+      </c>
+      <c r="K65" t="s">
+        <v>214</v>
+      </c>
+      <c r="L65">
+        <v>12</v>
+      </c>
+      <c r="M65">
+        <v>6</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>240</v>
+      </c>
+      <c r="R65">
+        <v>8</v>
+      </c>
+      <c r="S65">
+        <v>20</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>90</v>
+      </c>
+      <c r="W65">
+        <v>6644</v>
+      </c>
+      <c r="X65" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y65">
+        <v>2</v>
+      </c>
+      <c r="Z65">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26">
+      <c r="A66" t="s">
+        <v>27</v>
+      </c>
+      <c r="B66" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" t="s">
+        <v>47</v>
+      </c>
+      <c r="D66">
+        <v>4399</v>
+      </c>
+      <c r="E66" t="s">
+        <v>66</v>
+      </c>
+      <c r="F66" t="s">
+        <v>134</v>
+      </c>
+      <c r="G66" t="s">
+        <v>166</v>
+      </c>
+      <c r="H66" t="s">
+        <v>177</v>
+      </c>
+      <c r="I66" t="s">
+        <v>193</v>
+      </c>
+      <c r="J66" t="s">
+        <v>207</v>
+      </c>
+      <c r="K66" t="s">
+        <v>214</v>
+      </c>
+      <c r="L66">
+        <v>12</v>
+      </c>
+      <c r="M66">
+        <v>16</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>268</v>
+      </c>
+      <c r="R66">
+        <v>18</v>
+      </c>
+      <c r="S66">
+        <v>30</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>90</v>
+      </c>
+      <c r="W66">
+        <v>6644</v>
+      </c>
+      <c r="X66" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y66">
+        <v>2</v>
+      </c>
+      <c r="Z66">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26">
+      <c r="A67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67">
+        <v>12054</v>
+      </c>
+      <c r="E67" t="s">
+        <v>49</v>
+      </c>
+      <c r="F67" t="s">
+        <v>95</v>
+      </c>
+      <c r="G67" t="s">
+        <v>49</v>
+      </c>
+      <c r="H67" t="s">
+        <v>176</v>
+      </c>
+      <c r="I67" t="s">
+        <v>179</v>
+      </c>
+      <c r="J67" t="s">
+        <v>207</v>
+      </c>
+      <c r="K67" t="s">
+        <v>208</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>221</v>
+      </c>
+      <c r="R67">
+        <v>10</v>
+      </c>
+      <c r="S67">
+        <v>15</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>90</v>
+      </c>
+      <c r="W67">
+        <v>15</v>
+      </c>
+      <c r="X67" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y67">
+        <v>15</v>
+      </c>
+      <c r="Z67">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26">
+      <c r="A68" t="s">
+        <v>27</v>
+      </c>
+      <c r="B68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" t="s">
+        <v>47</v>
+      </c>
+      <c r="D68">
+        <v>18909</v>
+      </c>
+      <c r="E68" t="s">
+        <v>90</v>
+      </c>
+      <c r="F68" t="s">
+        <v>141</v>
+      </c>
+      <c r="G68" t="s">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s">
+        <v>176</v>
+      </c>
+      <c r="I68" t="s">
+        <v>179</v>
+      </c>
+      <c r="J68" t="s">
+        <v>207</v>
+      </c>
+      <c r="K68" t="s">
+        <v>215</v>
+      </c>
+      <c r="L68">
+        <v>24</v>
+      </c>
+      <c r="M68">
+        <v>15</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>269</v>
+      </c>
+      <c r="R68">
+        <v>18</v>
+      </c>
+      <c r="S68">
+        <v>42</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>90</v>
+      </c>
+      <c r="W68">
+        <v>10885</v>
+      </c>
+      <c r="X68" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y68">
+        <v>2</v>
+      </c>
+      <c r="Z68">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26">
+      <c r="A69" t="s">
+        <v>28</v>
+      </c>
+      <c r="B69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" t="s">
+        <v>47</v>
+      </c>
+      <c r="D69">
+        <v>27004</v>
+      </c>
+      <c r="E69" t="s">
+        <v>91</v>
+      </c>
+      <c r="F69" t="s">
+        <v>142</v>
+      </c>
+      <c r="G69" t="s">
+        <v>172</v>
+      </c>
+      <c r="H69" t="s">
+        <v>177</v>
+      </c>
+      <c r="I69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J69" t="s">
+        <v>207</v>
+      </c>
+      <c r="K69" t="s">
+        <v>218</v>
+      </c>
+      <c r="L69">
+        <v>6</v>
+      </c>
+      <c r="M69">
+        <v>135</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>270</v>
+      </c>
+      <c r="R69">
+        <v>172</v>
+      </c>
+      <c r="S69">
+        <v>268</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>90</v>
+      </c>
+      <c r="W69">
+        <v>15441</v>
+      </c>
+      <c r="X69" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y69">
+        <v>23</v>
+      </c>
+      <c r="Z69">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26">
+      <c r="A70" t="s">
+        <v>28</v>
+      </c>
+      <c r="B70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" t="s">
+        <v>47</v>
+      </c>
+      <c r="D70">
+        <v>64428</v>
+      </c>
+      <c r="E70" t="s">
+        <v>92</v>
+      </c>
+      <c r="F70" t="s">
+        <v>143</v>
+      </c>
+      <c r="G70" t="s">
+        <v>173</v>
+      </c>
+      <c r="H70" t="s">
+        <v>177</v>
+      </c>
+      <c r="I70" t="s">
+        <v>191</v>
+      </c>
+      <c r="J70" t="s">
+        <v>207</v>
+      </c>
+      <c r="K70" t="s">
+        <v>214</v>
+      </c>
+      <c r="L70">
+        <v>12</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>221</v>
+      </c>
+      <c r="R70">
+        <v>12</v>
+      </c>
+      <c r="S70">
+        <v>24</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>90</v>
+      </c>
+      <c r="W70">
+        <v>6424</v>
+      </c>
+      <c r="X70" t="s">
+        <v>276</v>
+      </c>
+      <c r="Y70">
+        <v>2</v>
+      </c>
+      <c r="Z70">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26">
+      <c r="A71" t="s">
+        <v>28</v>
+      </c>
+      <c r="B71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" t="s">
+        <v>48</v>
+      </c>
+      <c r="D71">
+        <v>409</v>
+      </c>
+      <c r="E71" t="s">
+        <v>82</v>
+      </c>
+      <c r="F71" t="s">
+        <v>144</v>
+      </c>
+      <c r="G71" t="s">
+        <v>174</v>
+      </c>
+      <c r="H71" t="s">
+        <v>178</v>
+      </c>
+      <c r="I71" t="s">
+        <v>201</v>
+      </c>
+      <c r="J71" t="s">
+        <v>207</v>
+      </c>
+      <c r="K71" t="s">
+        <v>218</v>
+      </c>
+      <c r="L71">
+        <v>6</v>
+      </c>
+      <c r="M71">
+        <v>36</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>271</v>
+      </c>
+      <c r="R71">
+        <v>38</v>
+      </c>
+      <c r="S71">
+        <v>56</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>90</v>
+      </c>
+      <c r="W71">
+        <v>15441</v>
+      </c>
+      <c r="X71" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y71">
+        <v>4</v>
+      </c>
+      <c r="Z71">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26">
+      <c r="A72" t="s">
+        <v>28</v>
+      </c>
+      <c r="B72" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72" t="s">
+        <v>48</v>
+      </c>
+      <c r="D72">
+        <v>625</v>
+      </c>
+      <c r="E72" t="s">
+        <v>83</v>
+      </c>
+      <c r="F72" t="s">
+        <v>145</v>
+      </c>
+      <c r="G72" t="s">
+        <v>175</v>
+      </c>
+      <c r="H72" t="s">
+        <v>178</v>
+      </c>
+      <c r="I72" t="s">
+        <v>202</v>
+      </c>
+      <c r="J72" t="s">
+        <v>207</v>
+      </c>
+      <c r="K72" t="s">
+        <v>220</v>
+      </c>
+      <c r="L72">
+        <v>8</v>
+      </c>
+      <c r="M72">
+        <v>30</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>272</v>
+      </c>
+      <c r="R72">
+        <v>58</v>
+      </c>
+      <c r="S72">
+        <v>90</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>90</v>
+      </c>
+      <c r="W72">
+        <v>15441</v>
+      </c>
+      <c r="X72" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y72">
+        <v>8</v>
+      </c>
+      <c r="Z72">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26">
+      <c r="A73" t="s">
+        <v>26</v>
+      </c>
+      <c r="B73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" t="s">
+        <v>48</v>
+      </c>
+      <c r="D73">
+        <v>1507</v>
+      </c>
+      <c r="E73" t="s">
+        <v>93</v>
+      </c>
+      <c r="F73" t="s">
+        <v>146</v>
+      </c>
+      <c r="G73" t="s">
+        <v>93</v>
+      </c>
+      <c r="H73" t="s">
+        <v>177</v>
+      </c>
+      <c r="I73" t="s">
+        <v>200</v>
+      </c>
+      <c r="J73" t="s">
+        <v>207</v>
+      </c>
+      <c r="K73" t="s">
+        <v>218</v>
+      </c>
+      <c r="L73">
+        <v>6</v>
+      </c>
+      <c r="M73">
+        <v>123</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>273</v>
+      </c>
+      <c r="R73">
+        <v>144</v>
+      </c>
+      <c r="S73">
+        <v>222</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>90</v>
+      </c>
+      <c r="W73">
+        <v>12592</v>
+      </c>
+      <c r="X73" t="s">
+        <v>279</v>
+      </c>
+      <c r="Y73">
+        <v>17</v>
+      </c>
+      <c r="Z73">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26">
+      <c r="A74" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74" t="s">
+        <v>30</v>
+      </c>
+      <c r="C74" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74">
+        <v>12053</v>
+      </c>
+      <c r="E74" t="s">
+        <v>94</v>
+      </c>
+      <c r="F74" t="s">
+        <v>147</v>
+      </c>
+      <c r="G74" t="s">
+        <v>94</v>
+      </c>
+      <c r="H74" t="s">
+        <v>176</v>
+      </c>
+      <c r="I74" t="s">
+        <v>179</v>
+      </c>
+      <c r="J74" t="s">
+        <v>207</v>
+      </c>
+      <c r="K74" t="s">
+        <v>208</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74">
+        <v>4</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>221</v>
+      </c>
+      <c r="R74">
+        <v>5</v>
+      </c>
+      <c r="S74">
+        <v>10</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <v>90</v>
+      </c>
+      <c r="W74">
+        <v>15</v>
+      </c>
+      <c r="X74" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y74">
+        <v>6</v>
+      </c>
+      <c r="Z74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26">
+      <c r="A75" t="s">
+        <v>26</v>
+      </c>
+      <c r="B75" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75">
+        <v>12054</v>
+      </c>
+      <c r="E75" t="s">
+        <v>49</v>
+      </c>
+      <c r="F75" t="s">
+        <v>95</v>
+      </c>
+      <c r="G75" t="s">
+        <v>49</v>
+      </c>
+      <c r="H75" t="s">
+        <v>176</v>
+      </c>
+      <c r="I75" t="s">
+        <v>179</v>
+      </c>
+      <c r="J75" t="s">
+        <v>207</v>
+      </c>
+      <c r="K75" t="s">
+        <v>208</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>221</v>
+      </c>
+      <c r="R75">
+        <v>10</v>
+      </c>
+      <c r="S75">
+        <v>15</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>90</v>
+      </c>
+      <c r="W75">
+        <v>15</v>
+      </c>
+      <c r="X75" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y75">
+        <v>15</v>
+      </c>
+      <c r="Z75">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z58" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Aplicativos/GAM/bd_saida/digitar.xlsx
+++ b/Aplicativos/GAM/bd_saida/digitar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Downloads\Equipes_Agentes\Aplicativos\GAM\bd_saida\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7208DDE8-D161-4C8D-B87C-E34E6022D84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5777ECB8-D9D6-4295-8DED-349943741452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Z$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Z$57</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="274">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -108,6 +108,9 @@
     <t>Estq_CD_cx</t>
   </si>
   <si>
+    <t>PERECIVEIS</t>
+  </si>
+  <si>
     <t>MERCEARIA</t>
   </si>
   <si>
@@ -117,10 +120,7 @@
     <t>PERFUMARIA E LIMPEZA</t>
   </si>
   <si>
-    <t>PRODUTOS PET</t>
-  </si>
-  <si>
-    <t>PERECIVEIS</t>
+    <t>SANDRO MARTINS VIANNA</t>
   </si>
   <si>
     <t>NIDAL TUBASI</t>
@@ -129,13 +129,13 @@
     <t>LUANA CRISTINA DA CRUZ</t>
   </si>
   <si>
+    <t>WETER SONNENFELDET</t>
+  </si>
+  <si>
     <t>JOAO BATISTA</t>
   </si>
   <si>
-    <t>WETER SONNENFELDET</t>
-  </si>
-  <si>
-    <t>SANDRO MARTINS VIANNA</t>
+    <t>001</t>
   </si>
   <si>
     <t>002</t>
@@ -177,496 +177,679 @@
     <t>018</t>
   </si>
   <si>
-    <t>AGUA MIN CRYSTAL PET 500ML S GAS</t>
-  </si>
-  <si>
-    <t>AGUA MIN DA PEDRA PET 5L</t>
-  </si>
-  <si>
-    <t>ARROZ BCO REQUINTE TP1 5KG</t>
-  </si>
-  <si>
-    <t>PROT SOLAR CORP JAY LUC FPS 60 120G</t>
-  </si>
-  <si>
-    <t>PROT SOLAR CORPORAL FPS 60 200G</t>
-  </si>
-  <si>
-    <t>CERV STELLA ARTOIS LN 330ML</t>
+    <t>LEITE UHT STA CLARA INT 1L</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SANO TP1 1KG</t>
+  </si>
+  <si>
+    <t>AGUA GASEIFICADA CRYSTAL PET 510ML</t>
+  </si>
+  <si>
+    <t>CERV STELLA ARTOIS LT 473ML</t>
+  </si>
+  <si>
+    <t>ACUCAR CRISTAL GASPARIN 1KG</t>
+  </si>
+  <si>
+    <t>CERV SKOL BEATS GREEN LN 269ML MIX</t>
+  </si>
+  <si>
+    <t>MILHO SALSARETTI A VAPOR LT 170G</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA</t>
+  </si>
+  <si>
+    <t>ARROZ BCO SANO T1 2K</t>
+  </si>
+  <si>
+    <t>CANJICA TRIGO CORTESI 500G</t>
+  </si>
+  <si>
+    <t>CERV BELLAVISTA PILSEN LT 473ML</t>
+  </si>
+  <si>
+    <t>BALA DORI PESC GIRAFA 30G</t>
+  </si>
+  <si>
+    <t>CONF AMEND DORI 70G</t>
+  </si>
+  <si>
+    <t>DOCE DOCITO 990G CREMOSO C LEITE</t>
+  </si>
+  <si>
+    <t>AMEND JAPONES DORI 70G SALGADO</t>
+  </si>
+  <si>
+    <t>SALG KEVYTOS 80G BACONYTOS</t>
+  </si>
+  <si>
+    <t>LIMP UAU LV1L PG800ML</t>
+  </si>
+  <si>
+    <t>CR DEN COLGATE MPA 180G</t>
+  </si>
+  <si>
+    <t>ESFR SANI ALL ACO 2UN</t>
+  </si>
+  <si>
+    <t>SAB BAR FARNESE 180G</t>
+  </si>
+  <si>
+    <t>ABS MILI SUAVE PROT TOT C ABAS C 32</t>
+  </si>
+  <si>
+    <t>ESC ANATOMICA LIMPAMANIA</t>
+  </si>
+  <si>
+    <t>ESFREGAO ACO GOTA LIMPA</t>
+  </si>
+  <si>
+    <t>FRALDA DESC MILI GIGA XG C 62</t>
+  </si>
+  <si>
+    <t>OLEO IPIRANGA F1 MASTER 15W40 1L</t>
+  </si>
+  <si>
+    <t>PAPEL HIG MAXPEL PREM FS 60M LV12</t>
+  </si>
+  <si>
+    <t>SAB LIQ BEM ESTAR RF 300ML</t>
+  </si>
+  <si>
+    <t>LAVA AUTO CONC MIL MILHAS 500ML</t>
+  </si>
+  <si>
+    <t>SALG OBBA 100G CEBOLA E SALSA</t>
+  </si>
+  <si>
+    <t>ACHOC PO APTI SH 200G</t>
+  </si>
+  <si>
+    <t>ADOCANTE ZERO CAL 100ML</t>
+  </si>
+  <si>
+    <t>MASSA GERMANI C VEG 500G</t>
+  </si>
+  <si>
+    <t>MIST P BOLO APTI 380G</t>
+  </si>
+  <si>
+    <t>REFRIG PET COCA COLA 3L</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 1 5L</t>
   </si>
   <si>
     <t>ENERG MONSTER LT 473ML</t>
   </si>
   <si>
-    <t>RACAO DOG CHOW SH 85G</t>
-  </si>
-  <si>
-    <t>RACAO FRISKIES SH 85G</t>
-  </si>
-  <si>
-    <t>ESC BANHO CCA SPA</t>
-  </si>
-  <si>
-    <t>CERV BRAHMA ZERO LT 350ML</t>
-  </si>
-  <si>
-    <t>REFRIG FANTA</t>
-  </si>
-  <si>
-    <t>ARROZ BCO REQUINTE TP1 1KG</t>
-  </si>
-  <si>
-    <t>ARROZ BCO REQUINTE TP1 2KG</t>
-  </si>
-  <si>
-    <t>FARINHA MILHO SAUDAVEL 1KG</t>
-  </si>
-  <si>
-    <t>BALA DORI PESC GIRAFA 30G</t>
-  </si>
-  <si>
-    <t>BISC RECH DANIX 130G</t>
-  </si>
-  <si>
-    <t>CONF AMEND DORI 70G</t>
-  </si>
-  <si>
-    <t>MASSA C OVOS ORQUIDEA 500G</t>
-  </si>
-  <si>
-    <t>SALG KEVYTOS SHOW 38G BACON</t>
-  </si>
-  <si>
-    <t>MIST P BOLO APTI 400G</t>
-  </si>
-  <si>
-    <t>REFRIG PET COCA COLA 3L</t>
-  </si>
-  <si>
-    <t>MASSA C OVOS ISABELA 500G ESPAGUETE</t>
-  </si>
-  <si>
-    <t>ACHOC PO APTI SH 700G INSTANT POWER</t>
-  </si>
-  <si>
-    <t>CACAU PO CBS 200G 100</t>
-  </si>
-  <si>
-    <t>INSET AERO RAID 420ML</t>
-  </si>
-  <si>
-    <t>LEITE UHT STA CLARA INT 1L</t>
+    <t>SALG KEVYTOS SHOW 38G QUEIJO</t>
   </si>
   <si>
     <t>ACUCAR CRISTAL DOCESUCAR 5KG</t>
   </si>
   <si>
+    <t>MARSHMALLOWS FOFS 220G</t>
+  </si>
+  <si>
+    <t>QJO RALADO DA SERRA 40G</t>
+  </si>
+  <si>
+    <t>SALG KEVYTOS SHOW 38G PIZZA</t>
+  </si>
+  <si>
     <t>MILHO VERDE OLE LT 170G</t>
   </si>
   <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>2150</t>
-  </si>
-  <si>
-    <t>22366</t>
-  </si>
-  <si>
-    <t>22367</t>
+    <t>LEITE UHT ELEGE INT 1L</t>
+  </si>
+  <si>
+    <t>9751</t>
+  </si>
+  <si>
+    <t>2074</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>746</t>
+  </si>
+  <si>
+    <t>35161</t>
+  </si>
+  <si>
+    <t>39389</t>
+  </si>
+  <si>
+    <t>806</t>
+  </si>
+  <si>
+    <t>2096</t>
+  </si>
+  <si>
+    <t>2285</t>
+  </si>
+  <si>
+    <t>34496</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <t>2538</t>
+  </si>
+  <si>
+    <t>3084</t>
+  </si>
+  <si>
+    <t>3153</t>
+  </si>
+  <si>
+    <t>3841</t>
+  </si>
+  <si>
+    <t>5196</t>
+  </si>
+  <si>
+    <t>9346</t>
+  </si>
+  <si>
+    <t>10145</t>
+  </si>
+  <si>
+    <t>12183</t>
+  </si>
+  <si>
+    <t>17717</t>
+  </si>
+  <si>
+    <t>17916</t>
+  </si>
+  <si>
+    <t>18761</t>
+  </si>
+  <si>
+    <t>21379</t>
+  </si>
+  <si>
+    <t>21679</t>
+  </si>
+  <si>
+    <t>23028</t>
+  </si>
+  <si>
+    <t>33962</t>
+  </si>
+  <si>
+    <t>3252</t>
+  </si>
+  <si>
+    <t>2942</t>
+  </si>
+  <si>
+    <t>3024</t>
+  </si>
+  <si>
+    <t>20679</t>
+  </si>
+  <si>
+    <t>33371</t>
+  </si>
+  <si>
+    <t>33372</t>
+  </si>
+  <si>
+    <t>835</t>
+  </si>
+  <si>
+    <t>39261</t>
+  </si>
+  <si>
+    <t>39262</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>3295</t>
+  </si>
+  <si>
+    <t>12228</t>
+  </si>
+  <si>
+    <t>1695</t>
+  </si>
+  <si>
+    <t>22630</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>3283</t>
+  </si>
+  <si>
+    <t>2396</t>
+  </si>
+  <si>
+    <t>6781</t>
+  </si>
+  <si>
+    <t>AGUA GASEIFICADA CRYSTAL PET 510ML FRUTAS VERMELHA</t>
+  </si>
+  <si>
+    <t>REFRIG FANTA LARANJA PET 2L</t>
+  </si>
+  <si>
+    <t>BALA DORI PESC GIRAFA 30G YOGURTE</t>
+  </si>
+  <si>
+    <t>CONF AMEND DORI 70G CHOC</t>
+  </si>
+  <si>
+    <t>LIMP UAU LV1L PG800ML PERF REQUINTE</t>
+  </si>
+  <si>
+    <t>SAB BAR FARNESE 180G ERV DOCE VERB</t>
+  </si>
+  <si>
+    <t>OLEO IPIRANGA F1 MASTER PERF 15W40 1L</t>
+  </si>
+  <si>
+    <t>PAPEL HIG MAXPEL PREMIUM FS 60M L12P11</t>
+  </si>
+  <si>
+    <t>SAB LIQ BEM ESTAR RF 300ML ERVA DOCE</t>
+  </si>
+  <si>
+    <t>MASSA GERMANI C VEG 500G PENNE</t>
+  </si>
+  <si>
+    <t>MIST P BOLO APTI 380G CHOC E COCO</t>
+  </si>
+  <si>
+    <t>MIST P BOLO APTI 380G CHOC C MOR</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 1 5L FRUTAS VERM</t>
+  </si>
+  <si>
+    <t>AGUA MIN DA PEDRA PET 1 5L ABACAXI C HORT</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML GREEN ZERO</t>
+  </si>
+  <si>
+    <t>MARSHMALLOWS FOFS 220G TWIST COLORIDO</t>
+  </si>
+  <si>
+    <t>ENERG MONSTER LT 473ML ABSOLUT ZERO</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>03/12/2024</t>
+  </si>
+  <si>
+    <t>21/09/2024</t>
+  </si>
+  <si>
+    <t>28/09/2024</t>
+  </si>
+  <si>
+    <t>17/10/2024</t>
+  </si>
+  <si>
+    <t>29/12/2025</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>19/10/2024</t>
+  </si>
+  <si>
+    <t>04/12/2024</t>
+  </si>
+  <si>
+    <t>06/12/2024</t>
+  </si>
+  <si>
+    <t>28/10/2025</t>
+  </si>
+  <si>
+    <t>28/10/2024</t>
+  </si>
+  <si>
+    <t>16/11/2024</t>
+  </si>
+  <si>
+    <t>10/12/2024</t>
+  </si>
+  <si>
+    <t>19/12/2024</t>
+  </si>
+  <si>
+    <t>20/12/2024</t>
+  </si>
+  <si>
+    <t>13/01/2025</t>
+  </si>
+  <si>
+    <t>06/09/2025</t>
+  </si>
+  <si>
+    <t>23/12/2024</t>
+  </si>
+  <si>
+    <t>17/12/2024</t>
+  </si>
+  <si>
+    <t>18/12/2024</t>
+  </si>
+  <si>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>26/08/2026</t>
+  </si>
+  <si>
+    <t>05/10/2024</t>
+  </si>
+  <si>
+    <t>24/12/2024</t>
+  </si>
+  <si>
+    <t>21/11/2024</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>3384</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>3098</t>
+  </si>
+  <si>
+    <t>4115</t>
+  </si>
+  <si>
+    <t>756</t>
+  </si>
+  <si>
+    <t>868</t>
+  </si>
+  <si>
+    <t>11697</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>11551</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>489</t>
   </si>
   <si>
     <t>293</t>
   </si>
   <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>3991</t>
-  </si>
-  <si>
-    <t>3994</t>
-  </si>
-  <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>4044</t>
-  </si>
-  <si>
-    <t>5776</t>
-  </si>
-  <si>
-    <t>39321</t>
-  </si>
-  <si>
-    <t>299</t>
-  </si>
-  <si>
-    <t>806</t>
-  </si>
-  <si>
-    <t>2084</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2688</t>
-  </si>
-  <si>
-    <t>1050</t>
-  </si>
-  <si>
-    <t>1488</t>
-  </si>
-  <si>
-    <t>1600</t>
-  </si>
-  <si>
-    <t>2869</t>
-  </si>
-  <si>
-    <t>3181</t>
-  </si>
-  <si>
-    <t>3712</t>
-  </si>
-  <si>
-    <t>835</t>
-  </si>
-  <si>
-    <t>3995</t>
-  </si>
-  <si>
-    <t>2879</t>
-  </si>
-  <si>
-    <t>2953</t>
-  </si>
-  <si>
-    <t>3068</t>
-  </si>
-  <si>
-    <t>6342</t>
-  </si>
-  <si>
-    <t>9751</t>
-  </si>
-  <si>
-    <t>12228</t>
-  </si>
-  <si>
-    <t>2396</t>
-  </si>
-  <si>
-    <t>AGUA MIN DA PEDRA PET 5L S GAS</t>
-  </si>
-  <si>
-    <t>ENERG MONSTER LT 473ML GREEN ZERO</t>
-  </si>
-  <si>
-    <t>RACAO DOG CHOW SH 85G MULTI PROTEINAS</t>
-  </si>
-  <si>
-    <t>RACAO DOG CHOW SH 85G AD CAR ARROZ</t>
-  </si>
-  <si>
-    <t>RACAO DOG CHOW SH 85G AD CAR FGO SALM</t>
-  </si>
-  <si>
-    <t>RACAO FRISKIES SH 85G ATUM MOLHO</t>
-  </si>
-  <si>
-    <t>RACAO DOG CHOW SH 85G ALTA PROTEINA</t>
-  </si>
-  <si>
-    <t>REFRIG FANTA LARANJA PET 2L</t>
-  </si>
-  <si>
-    <t>FARINHA MILHO SAUDAVEL 1KG MEDIA</t>
-  </si>
-  <si>
-    <t>BALA DORI PESC GIRAFA 30G MORANGO</t>
-  </si>
-  <si>
-    <t>BISC RECH DANIX 130G CHOC</t>
-  </si>
-  <si>
-    <t>CONF AMEND DORI 70G CHOC</t>
-  </si>
-  <si>
-    <t>MASSA C OVOS ORQUIDEA 500G ESPAGUETE</t>
-  </si>
-  <si>
-    <t>MIST P BOLO APTI 400G QUATRO LEITES</t>
-  </si>
-  <si>
-    <t>RACAO DOG CHOW SH 85G CORD E ARROZ</t>
-  </si>
-  <si>
-    <t>INSET AERO RAID 420ML EUCALIPTO</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>18/09/2024</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>05/12/2024</t>
-  </si>
-  <si>
-    <t>01/10/2024</t>
-  </si>
-  <si>
-    <t>05/10/2024</t>
-  </si>
-  <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>27/08/2026</t>
-  </si>
-  <si>
-    <t>19/10/2024</t>
-  </si>
-  <si>
-    <t>03/12/2024</t>
-  </si>
-  <si>
-    <t>04/12/2024</t>
-  </si>
-  <si>
-    <t>13/12/2024</t>
-  </si>
-  <si>
-    <t>29/10/2024</t>
-  </si>
-  <si>
-    <t>13/11/2024</t>
-  </si>
-  <si>
-    <t>16/11/2024</t>
-  </si>
-  <si>
-    <t>16/12/2024</t>
-  </si>
-  <si>
-    <t>20/12/2024</t>
-  </si>
-  <si>
-    <t>31/12/2024</t>
-  </si>
-  <si>
-    <t>21/10/2024</t>
-  </si>
-  <si>
-    <t>17/12/2024</t>
-  </si>
-  <si>
-    <t>19/12/2024</t>
-  </si>
-  <si>
-    <t>09/12/2024</t>
-  </si>
-  <si>
-    <t>Ativo</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1653</t>
-  </si>
-  <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>567</t>
-  </si>
-  <si>
-    <t>1131</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>506</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>890</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>153</t>
-  </si>
-  <si>
-    <t>1140</t>
-  </si>
-  <si>
-    <t>504</t>
-  </si>
-  <si>
-    <t>761</t>
-  </si>
-  <si>
-    <t>538</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>364</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>499</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>30635</t>
-  </si>
-  <si>
-    <t>12000</t>
-  </si>
-  <si>
-    <t>489</t>
+    <t>165</t>
+  </si>
+  <si>
+    <t>2603</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>682</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>847</t>
+  </si>
+  <si>
+    <t>751</t>
+  </si>
+  <si>
+    <t>COOP SANTA CLARA LTDA IND DE LATICINIOS</t>
+  </si>
+  <si>
+    <t>FERRUCCI E MIRANDA LTDA-EPP</t>
   </si>
   <si>
     <t>SPAL IND BRAS BEBIDAS AS</t>
   </si>
   <si>
+    <t>CRBS AS CDD PELOTAS</t>
+  </si>
+  <si>
+    <t>GASPARIN CEREAIS LTDA ME</t>
+  </si>
+  <si>
+    <t>STELLA DORO ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>GERMANI ALIMENTOS LTDA</t>
+  </si>
+  <si>
     <t>BEBIDAS FRUKI LTDA</t>
   </si>
   <si>
-    <t>GENESIO CEOLIN E CIA LTDA</t>
-  </si>
-  <si>
-    <t>CDC INDUSTRIA DE COSMETICOS LTDA</t>
-  </si>
-  <si>
-    <t>CRBS AS CDD PELOTAS</t>
-  </si>
-  <si>
-    <t>NESTLE BRASIL LTDA</t>
+    <t>DORI IND COM PROD ALIM LTDA</t>
+  </si>
+  <si>
+    <t>INDUSTRIA MIRIAM LTDA</t>
+  </si>
+  <si>
+    <t>DELAVY ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>NILO TOZZO DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
+  </si>
+  <si>
+    <t>ADESUL IND E COM LTDA</t>
+  </si>
+  <si>
+    <t>ONIZ DISTRIBUID LTDA SCJ</t>
+  </si>
+  <si>
+    <t>MILI S/A</t>
   </si>
   <si>
     <t>LIMPAMANIA INDUSTRIAL EIRELI - EPP</t>
   </si>
   <si>
-    <t>CARLOS ENRIQUE WATERMANN EIRELI</t>
-  </si>
-  <si>
-    <t>DORI IND COM PROD ALIM LTDA</t>
-  </si>
-  <si>
-    <t>KASADOCE DISTRIBUIDORA DE ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>TONDO S/A</t>
-  </si>
-  <si>
-    <t>DELAVY ALIMENTOS LTDA</t>
+    <t>BERTOLINI INDUSTRIA QUIMICA LTDA</t>
+  </si>
+  <si>
+    <t>MAKENA MAQ. EQUIP. E LUBRIF LTDA</t>
+  </si>
+  <si>
+    <t>NATURAPEL IND DE PAPEIS LTDA</t>
+  </si>
+  <si>
+    <t>DI HELLEN IND. DE COSMETICO LTDA</t>
+  </si>
+  <si>
+    <t>SUPERAUTO PRODUTOS AUTOMOTIVOS LTDA</t>
+  </si>
+  <si>
+    <t>FITOS ALIMENTOS LTDA</t>
   </si>
   <si>
     <t>APTI ALIMENTOS LTDA</t>
   </si>
   <si>
-    <t>M DIAS BRANCO S.A IND E COM DE ALIMENTOS</t>
-  </si>
-  <si>
-    <t>UNIDASUL DISTRIBUIDORA ALIMENTICIA S/A</t>
-  </si>
-  <si>
-    <t>ONIZ DISTRIBUID LTDA SCJ</t>
-  </si>
-  <si>
-    <t>COOP SANTA CLARA LTDA IND DE LATICINIOS</t>
+    <t>DISBAL RS DISTRIBUIDORA BALESTRIN LTDA</t>
   </si>
   <si>
     <t>ACUCAREIRA ENERGY LTDA</t>
   </si>
   <si>
+    <t>FLORESTAL ALIMENTOS S.A.</t>
+  </si>
+  <si>
+    <t>EPG COMERCIO DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
     <t>ANGELO AURICCHIO &amp; CIA LTDA</t>
+  </si>
+  <si>
+    <t>LACTALIS BRASIL COM IMP EXP LTDA</t>
   </si>
 </sst>
 </file>
@@ -1008,10 +1191,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z58"/>
+  <dimension ref="A1:Z57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="54.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -1096,43 +1280,43 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>36393</v>
+        <v>6798</v>
       </c>
       <c r="E2" t="s">
         <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G2" t="s">
         <v>49</v>
       </c>
       <c r="H2" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I2" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="J2" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K2" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="L2">
         <v>12</v>
       </c>
       <c r="M2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -1144,13 +1328,13 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="R2">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="S2">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -1162,16 +1346,16 @@
         <v>90</v>
       </c>
       <c r="W2">
-        <v>15441</v>
+        <v>10421</v>
       </c>
       <c r="X2" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="Y2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z2">
-        <v>54</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -1179,41 +1363,41 @@
         <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
         <v>36</v>
       </c>
       <c r="D3">
-        <v>182</v>
+        <v>1425</v>
       </c>
       <c r="E3" t="s">
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="H3" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L3">
+        <v>30</v>
+      </c>
+      <c r="M3">
         <v>131</v>
       </c>
-      <c r="J3" t="s">
-        <v>151</v>
-      </c>
-      <c r="K3" t="s">
-        <v>154</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>30</v>
-      </c>
       <c r="N3">
         <v>0</v>
       </c>
@@ -1224,13 +1408,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="R3">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="S3">
-        <v>52</v>
+        <v>192</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -1242,60 +1426,60 @@
         <v>90</v>
       </c>
       <c r="W3">
-        <v>6424</v>
+        <v>7918</v>
       </c>
       <c r="X3" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="Y3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z3">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4">
-        <v>1495</v>
+        <v>189</v>
       </c>
       <c r="E4" t="s">
         <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="H4" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="I4" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="J4" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K4" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="L4">
         <v>6</v>
       </c>
       <c r="M4">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1304,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="R4">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="S4">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -1322,16 +1506,16 @@
         <v>90</v>
       </c>
       <c r="W4">
-        <v>13087</v>
+        <v>15441</v>
       </c>
       <c r="X4" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z4">
-        <v>332</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -1339,58 +1523,58 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5">
-        <v>17151</v>
+        <v>55070</v>
       </c>
       <c r="E5" t="s">
         <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G5" t="s">
         <v>52</v>
       </c>
       <c r="H5" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I5" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="J5" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K5" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="N5">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="R5">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="S5">
-        <v>22</v>
+        <v>538</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -1402,75 +1586,75 @@
         <v>90</v>
       </c>
       <c r="W5">
-        <v>18958</v>
+        <v>9638</v>
       </c>
       <c r="X5" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="Y5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Z5">
-        <v>60</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>17152</v>
+        <v>575</v>
       </c>
       <c r="E6" t="s">
         <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G6" t="s">
         <v>53</v>
       </c>
       <c r="H6" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I6" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="J6" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K6" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="N6">
         <v>0</v>
       </c>
       <c r="O6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="R6">
-        <v>10</v>
+        <v>254</v>
       </c>
       <c r="S6">
-        <v>22</v>
+        <v>384</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -1482,21 +1666,21 @@
         <v>90</v>
       </c>
       <c r="W6">
-        <v>18958</v>
+        <v>6158</v>
       </c>
       <c r="X6" t="s">
-        <v>197</v>
+        <v>248</v>
       </c>
       <c r="Y6">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Z6">
-        <v>24</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
@@ -1505,34 +1689,34 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>352</v>
+        <v>36972</v>
       </c>
       <c r="E7" t="s">
         <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G7" t="s">
         <v>54</v>
       </c>
       <c r="H7" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I7" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="J7" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K7" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="L7">
         <v>24</v>
       </c>
       <c r="M7">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -1544,13 +1728,13 @@
         <v>0</v>
       </c>
       <c r="Q7" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="R7">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="S7">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -1565,13 +1749,13 @@
         <v>9638</v>
       </c>
       <c r="X7" t="s">
-        <v>198</v>
+        <v>247</v>
       </c>
       <c r="Y7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z7">
-        <v>80</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -1579,40 +1763,40 @@
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
       </c>
       <c r="D8">
-        <v>409</v>
+        <v>64633</v>
       </c>
       <c r="E8" t="s">
         <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="G8" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="H8" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I8" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="J8" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K8" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="L8">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M8">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -1624,13 +1808,13 @@
         <v>0</v>
       </c>
       <c r="Q8" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="R8">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="S8">
-        <v>186</v>
+        <v>40</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -1642,57 +1826,57 @@
         <v>90</v>
       </c>
       <c r="W8">
-        <v>15441</v>
+        <v>11515</v>
       </c>
       <c r="X8" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Z8">
-        <v>226</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9">
-        <v>2976</v>
+        <v>625</v>
       </c>
       <c r="E9" t="s">
         <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="G9" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="H9" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="I9" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="J9" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K9" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="L9">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -1704,13 +1888,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="R9">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="S9">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -1722,137 +1906,137 @@
         <v>90</v>
       </c>
       <c r="W9">
-        <v>15134</v>
+        <v>15441</v>
       </c>
       <c r="X9" t="s">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="Y9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z9">
-        <v>20</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10">
-        <v>2976</v>
+        <v>6798</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G10" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="H10" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I10" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="J10" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K10" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="L10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M10">
+        <v>603</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>210</v>
+      </c>
+      <c r="R10">
+        <v>720</v>
+      </c>
+      <c r="S10">
+        <v>1020</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>90</v>
+      </c>
+      <c r="W10">
+        <v>10421</v>
+      </c>
+      <c r="X10" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y10">
         <v>35</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>169</v>
-      </c>
-      <c r="R10">
-        <v>45</v>
-      </c>
-      <c r="S10">
-        <v>60</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>90</v>
-      </c>
-      <c r="W10">
-        <v>15134</v>
-      </c>
-      <c r="X10" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y10">
-        <v>2</v>
-      </c>
       <c r="Z10">
-        <v>40</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D11">
-        <v>2976</v>
+        <v>1448</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G11" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="H11" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I11" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="J11" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K11" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="L11">
         <v>15</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1864,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="Q11" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="R11">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="S11">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -1882,57 +2066,57 @@
         <v>90</v>
       </c>
       <c r="W11">
-        <v>15134</v>
+        <v>7918</v>
       </c>
       <c r="X11" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="Y11">
         <v>2</v>
       </c>
       <c r="Z11">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D12">
-        <v>3003</v>
+        <v>1613</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="G12" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="H12" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I12" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="J12" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K12" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="L12">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -1944,13 +2128,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="R12">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="S12">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -1962,16 +2146,16 @@
         <v>90</v>
       </c>
       <c r="W12">
-        <v>15134</v>
+        <v>16963</v>
       </c>
       <c r="X12" t="s">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z12">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -1979,34 +2163,34 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13">
-        <v>4046</v>
+        <v>37272</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H13" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I13" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="J13" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K13" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -2021,96 +2205,96 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="s">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="R13">
+        <v>62</v>
+      </c>
+      <c r="S13">
+        <v>98</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>90</v>
+      </c>
+      <c r="W13">
+        <v>6424</v>
+      </c>
+      <c r="X13" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y13">
         <v>7</v>
       </c>
-      <c r="S13">
-        <v>10</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>90</v>
-      </c>
-      <c r="W13">
-        <v>8243</v>
-      </c>
-      <c r="X13" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y13">
-        <v>1</v>
-      </c>
       <c r="Z13">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D14">
-        <v>17151</v>
+        <v>828</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="H14" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I14" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="J14" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K14" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
       <c r="O14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="R14">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="S14">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -2122,75 +2306,75 @@
         <v>90</v>
       </c>
       <c r="W14">
-        <v>18958</v>
+        <v>8539</v>
       </c>
       <c r="X14" t="s">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z14">
-        <v>60</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D15">
-        <v>17152</v>
+        <v>1160</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="H15" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I15" t="s">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="J15" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K15" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N15">
         <v>0</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="R15">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="S15">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -2202,57 +2386,57 @@
         <v>90</v>
       </c>
       <c r="W15">
-        <v>18958</v>
+        <v>8539</v>
       </c>
       <c r="X15" t="s">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z15">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D16">
-        <v>64230</v>
+        <v>1823</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="G16" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="H16" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I16" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="J16" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K16" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="L16">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2264,13 +2448,13 @@
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="R16">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -2282,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="W16">
-        <v>15134</v>
+        <v>12457</v>
       </c>
       <c r="X16" t="s">
-        <v>199</v>
+        <v>253</v>
       </c>
       <c r="Y16">
         <v>2</v>
       </c>
       <c r="Z16">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
@@ -2299,40 +2483,40 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17">
-        <v>409</v>
+        <v>2278</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="G17" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="H17" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I17" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="J17" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K17" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="M17">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2344,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
       <c r="R17">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="S17">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="T17">
         <v>0</v>
@@ -2362,16 +2546,16 @@
         <v>90</v>
       </c>
       <c r="W17">
-        <v>15441</v>
+        <v>8539</v>
       </c>
       <c r="X17" t="s">
-        <v>194</v>
+        <v>252</v>
       </c>
       <c r="Y17">
         <v>2</v>
       </c>
       <c r="Z17">
-        <v>226</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
@@ -2379,40 +2563,40 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18">
-        <v>357</v>
+        <v>2332</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G18" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H18" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I18" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="J18" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K18" t="s">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="L18">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -2424,13 +2608,13 @@
         <v>0</v>
       </c>
       <c r="Q18" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="R18">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="T18">
         <v>0</v>
@@ -2442,75 +2626,75 @@
         <v>90</v>
       </c>
       <c r="W18">
-        <v>9638</v>
+        <v>2977</v>
       </c>
       <c r="X18" t="s">
-        <v>198</v>
+        <v>254</v>
       </c>
       <c r="Y18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z18">
-        <v>122</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19">
-        <v>625</v>
+        <v>4794</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="G19" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="H19" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I19" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="J19" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K19" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="L19">
+        <v>12</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>217</v>
+      </c>
+      <c r="R19">
         <v>8</v>
       </c>
-      <c r="M19">
-        <v>113</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>174</v>
-      </c>
-      <c r="R19">
-        <v>128</v>
-      </c>
       <c r="S19">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="T19">
         <v>0</v>
@@ -2522,58 +2706,58 @@
         <v>90</v>
       </c>
       <c r="W19">
-        <v>15441</v>
+        <v>3266</v>
       </c>
       <c r="X19" t="s">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="Y19">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Z19">
-        <v>496</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20">
+        <v>3751</v>
+      </c>
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" t="s">
+        <v>155</v>
+      </c>
+      <c r="I20" t="s">
+        <v>158</v>
+      </c>
+      <c r="J20" t="s">
+        <v>187</v>
+      </c>
+      <c r="K20" t="s">
+        <v>196</v>
+      </c>
+      <c r="L20">
+        <v>72</v>
+      </c>
+      <c r="M20">
         <v>31</v>
       </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20">
-        <v>1437</v>
-      </c>
-      <c r="E20" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" t="s">
-        <v>127</v>
-      </c>
-      <c r="I20" t="s">
-        <v>138</v>
-      </c>
-      <c r="J20" t="s">
-        <v>151</v>
-      </c>
-      <c r="K20" t="s">
-        <v>159</v>
-      </c>
-      <c r="L20">
-        <v>30</v>
-      </c>
-      <c r="M20">
-        <v>8</v>
-      </c>
       <c r="N20">
         <v>0</v>
       </c>
@@ -2584,13 +2768,13 @@
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="R20">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="S20">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -2602,137 +2786,137 @@
         <v>90</v>
       </c>
       <c r="W20">
-        <v>13087</v>
+        <v>5894</v>
       </c>
       <c r="X20" t="s">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="Y20">
         <v>2</v>
       </c>
       <c r="Z20">
-        <v>49</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21">
-        <v>1453</v>
+        <v>6537</v>
       </c>
       <c r="E21" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="G21" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H21" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I21" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="J21" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K21" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="L21">
+        <v>72</v>
+      </c>
+      <c r="M21">
+        <v>30</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>219</v>
+      </c>
+      <c r="R21">
+        <v>44</v>
+      </c>
+      <c r="S21">
+        <v>116</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>90</v>
+      </c>
+      <c r="W21">
+        <v>5866</v>
+      </c>
+      <c r="X21" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y21">
+        <v>2</v>
+      </c>
+      <c r="Z21">
         <v>15</v>
-      </c>
-      <c r="M21">
-        <v>-6</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>176</v>
-      </c>
-      <c r="R21">
-        <v>45</v>
-      </c>
-      <c r="S21">
-        <v>75</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>90</v>
-      </c>
-      <c r="W21">
-        <v>13087</v>
-      </c>
-      <c r="X21" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y21">
-        <v>5</v>
-      </c>
-      <c r="Z21">
-        <v>84.33</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D22">
-        <v>1945</v>
+        <v>7117</v>
       </c>
       <c r="E22" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="G22" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="H22" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I22" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="J22" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K22" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="L22">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M22">
-        <v>26</v>
+        <v>-11</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -2744,13 +2928,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="R22">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="S22">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -2762,54 +2946,54 @@
         <v>90</v>
       </c>
       <c r="W22">
-        <v>15301</v>
+        <v>6644</v>
       </c>
       <c r="X22" t="s">
-        <v>201</v>
+        <v>258</v>
       </c>
       <c r="Y22">
         <v>2</v>
       </c>
       <c r="Z22">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D23">
-        <v>17151</v>
+        <v>9034</v>
       </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="G23" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="H23" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I23" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="J23" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K23" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -2818,19 +3002,19 @@
         <v>0</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P23">
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="R23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T23">
         <v>0</v>
@@ -2842,75 +3026,75 @@
         <v>90</v>
       </c>
       <c r="W23">
-        <v>18958</v>
+        <v>10190</v>
       </c>
       <c r="X23" t="s">
-        <v>197</v>
+        <v>259</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z23">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D24">
-        <v>17152</v>
+        <v>13525</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="G24" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="H24" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I24" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="J24" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K24" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="O24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24">
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>162</v>
+        <v>222</v>
       </c>
       <c r="R24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T24">
         <v>0</v>
@@ -2922,75 +3106,75 @@
         <v>90</v>
       </c>
       <c r="W24">
-        <v>18958</v>
+        <v>8243</v>
       </c>
       <c r="X24" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z24">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
       <c r="D25">
-        <v>17152</v>
+        <v>13718</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="G25" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H25" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I25" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="J25" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K25" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25">
         <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>162</v>
+        <v>223</v>
       </c>
       <c r="R25">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="S25">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="T25">
         <v>0</v>
@@ -3002,75 +3186,75 @@
         <v>90</v>
       </c>
       <c r="W25">
-        <v>18958</v>
+        <v>14468</v>
       </c>
       <c r="X25" t="s">
-        <v>197</v>
+        <v>261</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z25">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D26">
-        <v>17151</v>
+        <v>36510</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F26" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="G26" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="H26" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I26" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="J26" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K26" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N26">
         <v>0</v>
       </c>
       <c r="O26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="R26">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="S26">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -3082,75 +3266,75 @@
         <v>90</v>
       </c>
       <c r="W26">
-        <v>18958</v>
+        <v>10190</v>
       </c>
       <c r="X26" t="s">
-        <v>197</v>
+        <v>259</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z26">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D27">
-        <v>17152</v>
+        <v>16269</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F27" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="G27" t="s">
-        <v>53</v>
+        <v>144</v>
       </c>
       <c r="H27" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I27" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="J27" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K27" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N27">
         <v>0</v>
       </c>
       <c r="O27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
       <c r="Q27" t="s">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="R27">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="S27">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T27">
         <v>0</v>
@@ -3162,57 +3346,57 @@
         <v>90</v>
       </c>
       <c r="W27">
-        <v>18958</v>
+        <v>14458</v>
       </c>
       <c r="X27" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z27">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D28">
-        <v>409</v>
+        <v>16514</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="G28" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="H28" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I28" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="J28" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K28" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="L28">
         <v>6</v>
       </c>
       <c r="M28">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -3224,10 +3408,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="R28">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="S28">
         <v>28</v>
@@ -3242,75 +3426,75 @@
         <v>90</v>
       </c>
       <c r="W28">
-        <v>15441</v>
+        <v>8305</v>
       </c>
       <c r="X28" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="Y28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z28">
-        <v>226</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D29">
-        <v>828</v>
+        <v>17713</v>
       </c>
       <c r="E29" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="G29" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="H29" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="I29" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="J29" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K29" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="L29">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="M29">
+        <v>9</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>200</v>
+      </c>
+      <c r="R29">
         <v>10</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>179</v>
-      </c>
-      <c r="R29">
-        <v>36</v>
-      </c>
       <c r="S29">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="T29">
         <v>0</v>
@@ -3322,10 +3506,10 @@
         <v>90</v>
       </c>
       <c r="W29">
-        <v>8539</v>
+        <v>7436</v>
       </c>
       <c r="X29" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="Y29">
         <v>2</v>
@@ -3336,43 +3520,43 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D30">
-        <v>1099</v>
+        <v>32784</v>
       </c>
       <c r="E30" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F30" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="G30" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I30" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="J30" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K30" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="L30">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M30">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -3384,14 +3568,14 @@
         <v>0</v>
       </c>
       <c r="Q30" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="R30">
+        <v>16</v>
+      </c>
+      <c r="S30">
         <v>36</v>
       </c>
-      <c r="S30">
-        <v>96</v>
-      </c>
       <c r="T30">
         <v>0</v>
       </c>
@@ -3402,57 +3586,57 @@
         <v>90</v>
       </c>
       <c r="W30">
-        <v>10142</v>
+        <v>17027</v>
       </c>
       <c r="X30" t="s">
-        <v>203</v>
+        <v>265</v>
       </c>
       <c r="Y30">
         <v>2</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D31">
-        <v>1160</v>
+        <v>64633</v>
       </c>
       <c r="E31" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="F31" t="s">
         <v>98</v>
       </c>
       <c r="G31" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="H31" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I31" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="J31" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K31" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="L31">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M31">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -3464,13 +3648,13 @@
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="R31">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S31">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="T31">
         <v>0</v>
@@ -3482,57 +3666,57 @@
         <v>90</v>
       </c>
       <c r="W31">
-        <v>8539</v>
+        <v>11515</v>
       </c>
       <c r="X31" t="s">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="Y31">
         <v>2</v>
       </c>
       <c r="Z31">
-        <v>24</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D32">
-        <v>2076</v>
+        <v>2395</v>
       </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G32" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I32" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="J32" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K32" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="L32">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -3544,13 +3728,13 @@
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="R32">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="S32">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="T32">
         <v>0</v>
@@ -3562,75 +3746,75 @@
         <v>90</v>
       </c>
       <c r="W32">
-        <v>10683</v>
+        <v>16857</v>
       </c>
       <c r="X32" t="s">
-        <v>204</v>
+        <v>266</v>
       </c>
       <c r="Y32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z32">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
         <v>42</v>
       </c>
       <c r="D33">
-        <v>2350</v>
+        <v>1448</v>
       </c>
       <c r="E33" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F33" t="s">
         <v>100</v>
       </c>
       <c r="G33" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="H33" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I33" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="J33" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K33" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="L33">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M33">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N33">
         <v>0</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P33">
         <v>0</v>
       </c>
       <c r="Q33" t="s">
-        <v>182</v>
+        <v>227</v>
       </c>
       <c r="R33">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S33">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T33">
         <v>0</v>
@@ -3642,75 +3826,75 @@
         <v>90</v>
       </c>
       <c r="W33">
-        <v>2977</v>
+        <v>7918</v>
       </c>
       <c r="X33" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
       <c r="Y33">
         <v>2</v>
       </c>
       <c r="Z33">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
         <v>42</v>
       </c>
       <c r="D34">
-        <v>2700</v>
+        <v>1613</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F34" t="s">
         <v>101</v>
       </c>
       <c r="G34" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="H34" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I34" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="J34" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K34" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="L34">
         <v>12</v>
       </c>
       <c r="M34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>0</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="R34">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="S34">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="T34">
         <v>0</v>
@@ -3722,21 +3906,21 @@
         <v>90</v>
       </c>
       <c r="W34">
-        <v>10189</v>
+        <v>16963</v>
       </c>
       <c r="X34" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="Y34">
         <v>2</v>
       </c>
       <c r="Z34">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
         <v>33</v>
@@ -3745,52 +3929,52 @@
         <v>42</v>
       </c>
       <c r="D35">
-        <v>17151</v>
+        <v>2141</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F35" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="G35" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I35" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="J35" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K35" t="s">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="L35">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="N35">
         <v>0</v>
       </c>
       <c r="O35">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P35">
         <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="R35">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="S35">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="T35">
         <v>0</v>
@@ -3802,16 +3986,16 @@
         <v>90</v>
       </c>
       <c r="W35">
-        <v>18958</v>
+        <v>10189</v>
       </c>
       <c r="X35" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="Y35">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Z35">
-        <v>60</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
@@ -3819,40 +4003,40 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D36">
-        <v>648</v>
+        <v>2223</v>
       </c>
       <c r="E36" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F36" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="G36" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I36" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="J36" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K36" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="L36">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M36">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -3864,13 +4048,13 @@
         <v>0</v>
       </c>
       <c r="Q36" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="R36">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="S36">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="T36">
         <v>0</v>
@@ -3882,155 +4066,155 @@
         <v>90</v>
       </c>
       <c r="W36">
-        <v>15441</v>
+        <v>9274</v>
       </c>
       <c r="X36" t="s">
-        <v>194</v>
+        <v>268</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z36">
-        <v>416</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37">
-        <v>2976</v>
+        <v>6798</v>
       </c>
       <c r="E37" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F37" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="H37" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I37" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="J37" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K37" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="L37">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M37">
-        <v>33</v>
+        <v>281</v>
       </c>
       <c r="N37">
         <v>0</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="P37">
         <v>0</v>
       </c>
       <c r="Q37" t="s">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="R37">
+        <v>720</v>
+      </c>
+      <c r="S37">
+        <v>1020</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>90</v>
+      </c>
+      <c r="W37">
+        <v>10421</v>
+      </c>
+      <c r="X37" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y37">
         <v>35</v>
       </c>
-      <c r="S37">
-        <v>50</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-      <c r="U37">
-        <v>0</v>
-      </c>
-      <c r="V37">
-        <v>90</v>
-      </c>
-      <c r="W37">
-        <v>15134</v>
-      </c>
-      <c r="X37" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y37">
-        <v>2</v>
-      </c>
       <c r="Z37">
-        <v>40</v>
+        <v>541</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
         <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D38">
-        <v>17151</v>
+        <v>15661</v>
       </c>
       <c r="E38" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="F38" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="G38" t="s">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="H38" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I38" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="J38" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K38" t="s">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N38">
         <v>0</v>
       </c>
       <c r="O38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P38">
         <v>0</v>
       </c>
       <c r="Q38" t="s">
-        <v>162</v>
+        <v>232</v>
       </c>
       <c r="R38">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="S38">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="T38">
         <v>0</v>
@@ -4042,134 +4226,134 @@
         <v>90</v>
       </c>
       <c r="W38">
-        <v>18958</v>
+        <v>16963</v>
       </c>
       <c r="X38" t="s">
-        <v>197</v>
+        <v>250</v>
       </c>
       <c r="Y38">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z38">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
         <v>33</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D39">
-        <v>17152</v>
+        <v>2699</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="F39" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="G39" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H39" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I39" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="J39" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K39" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>0</v>
       </c>
       <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>215</v>
+      </c>
+      <c r="R39">
+        <v>8</v>
+      </c>
+      <c r="S39">
+        <v>20</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>90</v>
+      </c>
+      <c r="W39">
+        <v>10189</v>
+      </c>
+      <c r="X39" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y39">
         <v>2</v>
       </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>162</v>
-      </c>
-      <c r="R39">
-        <v>10</v>
-      </c>
-      <c r="S39">
+      <c r="Z39">
         <v>22</v>
-      </c>
-      <c r="T39">
-        <v>0</v>
-      </c>
-      <c r="U39">
-        <v>0</v>
-      </c>
-      <c r="V39">
-        <v>90</v>
-      </c>
-      <c r="W39">
-        <v>18958</v>
-      </c>
-      <c r="X39" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y39">
-        <v>20</v>
-      </c>
-      <c r="Z39">
-        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
         <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D40">
-        <v>2976</v>
+        <v>2699</v>
       </c>
       <c r="E40" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="F40" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="G40" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="H40" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I40" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="J40" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K40" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="L40">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -4184,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="Q40" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="R40">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="S40">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T40">
         <v>0</v>
@@ -4202,16 +4386,16 @@
         <v>90</v>
       </c>
       <c r="W40">
-        <v>15134</v>
+        <v>10189</v>
       </c>
       <c r="X40" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="Y40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z40">
-        <v>40</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
@@ -4219,58 +4403,58 @@
         <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D41">
-        <v>17151</v>
+        <v>648</v>
       </c>
       <c r="E41" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="F41" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="G41" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I41" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="J41" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K41" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="L41">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N41">
         <v>0</v>
       </c>
       <c r="O41">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="P41">
         <v>0</v>
       </c>
       <c r="Q41" t="s">
-        <v>162</v>
+        <v>234</v>
       </c>
       <c r="R41">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="S41">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="T41">
         <v>0</v>
@@ -4282,16 +4466,16 @@
         <v>90</v>
       </c>
       <c r="W41">
-        <v>18958</v>
+        <v>15441</v>
       </c>
       <c r="X41" t="s">
-        <v>197</v>
+        <v>246</v>
       </c>
       <c r="Y41">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Z41">
-        <v>60</v>
+        <v>410</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
@@ -4299,200 +4483,200 @@
         <v>28</v>
       </c>
       <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42">
+        <v>64427</v>
+      </c>
+      <c r="E42" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" t="s">
+        <v>127</v>
+      </c>
+      <c r="G42" t="s">
+        <v>150</v>
+      </c>
+      <c r="H42" t="s">
+        <v>155</v>
+      </c>
+      <c r="I42" t="s">
+        <v>182</v>
+      </c>
+      <c r="J42" t="s">
+        <v>187</v>
+      </c>
+      <c r="K42" t="s">
+        <v>190</v>
+      </c>
+      <c r="L42">
+        <v>6</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>203</v>
+      </c>
+      <c r="R42">
+        <v>12</v>
+      </c>
+      <c r="S42">
+        <v>18</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>90</v>
+      </c>
+      <c r="W42">
+        <v>6424</v>
+      </c>
+      <c r="X42" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y42">
+        <v>3</v>
+      </c>
+      <c r="Z42">
         <v>33</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42">
-        <v>17152</v>
-      </c>
-      <c r="E42" t="s">
-        <v>53</v>
-      </c>
-      <c r="F42" t="s">
-        <v>82</v>
-      </c>
-      <c r="G42" t="s">
-        <v>53</v>
-      </c>
-      <c r="H42" t="s">
-        <v>127</v>
-      </c>
-      <c r="I42" t="s">
-        <v>129</v>
-      </c>
-      <c r="J42" t="s">
-        <v>151</v>
-      </c>
-      <c r="K42" t="s">
-        <v>152</v>
-      </c>
-      <c r="L42">
-        <v>1</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>2</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>162</v>
-      </c>
-      <c r="R42">
-        <v>10</v>
-      </c>
-      <c r="S42">
-        <v>22</v>
-      </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42">
-        <v>90</v>
-      </c>
-      <c r="W42">
-        <v>18958</v>
-      </c>
-      <c r="X42" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y42">
-        <v>20</v>
-      </c>
-      <c r="Z42">
-        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D43">
-        <v>2087</v>
+        <v>64427</v>
       </c>
       <c r="E43" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F43" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="G43" t="s">
-        <v>71</v>
+        <v>151</v>
       </c>
       <c r="H43" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I43" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="J43" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K43" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="L43">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>203</v>
+      </c>
+      <c r="R43">
+        <v>12</v>
+      </c>
+      <c r="S43">
+        <v>18</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>90</v>
+      </c>
+      <c r="W43">
+        <v>6424</v>
+      </c>
+      <c r="X43" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y43">
+        <v>3</v>
+      </c>
+      <c r="Z43">
         <v>30</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>187</v>
-      </c>
-      <c r="R43">
-        <v>34</v>
-      </c>
-      <c r="S43">
-        <v>54</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>90</v>
-      </c>
-      <c r="W43">
-        <v>7995</v>
-      </c>
-      <c r="X43" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y43">
-        <v>2</v>
-      </c>
-      <c r="Z43">
-        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D44">
-        <v>2154</v>
+        <v>409</v>
       </c>
       <c r="E44" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="G44" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="H44" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="I44" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="J44" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K44" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="L44">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M44">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="N44">
         <v>0</v>
@@ -4504,13 +4688,13 @@
         <v>0</v>
       </c>
       <c r="Q44" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="R44">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="S44">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="T44">
         <v>0</v>
@@ -4522,76 +4706,76 @@
         <v>90</v>
       </c>
       <c r="W44">
-        <v>10189</v>
+        <v>15441</v>
       </c>
       <c r="X44" t="s">
-        <v>206</v>
+        <v>246</v>
       </c>
       <c r="Y44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z44">
-        <v>14</v>
+        <v>159.33000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45">
+        <v>2429</v>
+      </c>
+      <c r="E45" t="s">
+        <v>85</v>
+      </c>
+      <c r="F45" t="s">
+        <v>130</v>
+      </c>
+      <c r="G45" t="s">
+        <v>85</v>
+      </c>
+      <c r="H45" t="s">
+        <v>155</v>
+      </c>
+      <c r="I45" t="s">
+        <v>184</v>
+      </c>
+      <c r="J45" t="s">
+        <v>187</v>
+      </c>
+      <c r="K45" t="s">
+        <v>200</v>
+      </c>
+      <c r="L45">
+        <v>20</v>
+      </c>
+      <c r="M45">
+        <v>13</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>236</v>
+      </c>
+      <c r="R45">
+        <v>14</v>
+      </c>
+      <c r="S45">
         <v>34</v>
       </c>
-      <c r="C45" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45">
-        <v>2264</v>
-      </c>
-      <c r="E45" t="s">
-        <v>73</v>
-      </c>
-      <c r="F45" t="s">
-        <v>106</v>
-      </c>
-      <c r="G45" t="s">
-        <v>73</v>
-      </c>
-      <c r="H45" t="s">
-        <v>127</v>
-      </c>
-      <c r="I45" t="s">
-        <v>149</v>
-      </c>
-      <c r="J45" t="s">
-        <v>151</v>
-      </c>
-      <c r="K45" t="s">
-        <v>153</v>
-      </c>
-      <c r="L45">
-        <v>12</v>
-      </c>
-      <c r="M45">
-        <v>11</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>189</v>
-      </c>
-      <c r="R45">
-        <v>12</v>
-      </c>
-      <c r="S45">
-        <v>24</v>
-      </c>
       <c r="T45">
         <v>0</v>
       </c>
@@ -4602,155 +4786,155 @@
         <v>90</v>
       </c>
       <c r="W45">
-        <v>5894</v>
+        <v>2977</v>
       </c>
       <c r="X45" t="s">
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="Y45">
         <v>2</v>
       </c>
       <c r="Z45">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D46">
-        <v>4399</v>
+        <v>9079</v>
       </c>
       <c r="E46" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F46" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="G46" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I46" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="J46" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K46" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="L46">
+        <v>6</v>
+      </c>
+      <c r="M46">
+        <v>110</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>237</v>
+      </c>
+      <c r="R46">
+        <v>116</v>
+      </c>
+      <c r="S46">
+        <v>182</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>90</v>
+      </c>
+      <c r="W46">
+        <v>15947</v>
+      </c>
+      <c r="X46" t="s">
+        <v>269</v>
+      </c>
+      <c r="Y46">
         <v>12</v>
       </c>
-      <c r="M46">
-        <v>7</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>190</v>
-      </c>
-      <c r="R46">
-        <v>8</v>
-      </c>
-      <c r="S46">
-        <v>20</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46">
-        <v>0</v>
-      </c>
-      <c r="V46">
-        <v>90</v>
-      </c>
-      <c r="W46">
-        <v>6644</v>
-      </c>
-      <c r="X46" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y46">
-        <v>2</v>
-      </c>
       <c r="Z46">
-        <v>14</v>
+        <v>283.33</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D47">
-        <v>6798</v>
+        <v>64427</v>
       </c>
       <c r="E47" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F47" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="G47" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="H47" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I47" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="J47" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K47" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="L47">
+        <v>6</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>203</v>
+      </c>
+      <c r="R47">
         <v>12</v>
       </c>
-      <c r="M47">
-        <v>1434</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>191</v>
-      </c>
-      <c r="R47">
-        <v>1438</v>
-      </c>
       <c r="S47">
-        <v>2218</v>
+        <v>18</v>
       </c>
       <c r="T47">
         <v>0</v>
@@ -4762,16 +4946,16 @@
         <v>90</v>
       </c>
       <c r="W47">
-        <v>10421</v>
+        <v>6424</v>
       </c>
       <c r="X47" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="Y47">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="Z47">
-        <v>1229</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
@@ -4779,37 +4963,37 @@
         <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D48">
-        <v>17151</v>
+        <v>64427</v>
       </c>
       <c r="E48" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="F48" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="G48" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="H48" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I48" t="s">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="J48" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K48" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -4818,45 +5002,45 @@
         <v>0</v>
       </c>
       <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>203</v>
+      </c>
+      <c r="R48">
+        <v>12</v>
+      </c>
+      <c r="S48">
+        <v>18</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>90</v>
+      </c>
+      <c r="W48">
+        <v>6424</v>
+      </c>
+      <c r="X48" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y48">
         <v>3</v>
       </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>162</v>
-      </c>
-      <c r="R48">
-        <v>5</v>
-      </c>
-      <c r="S48">
-        <v>10</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>90</v>
-      </c>
-      <c r="W48">
-        <v>18958</v>
-      </c>
-      <c r="X48" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y48">
-        <v>7</v>
-      </c>
       <c r="Z48">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
         <v>33</v>
@@ -4865,52 +5049,52 @@
         <v>45</v>
       </c>
       <c r="D49">
-        <v>17152</v>
+        <v>1154</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F49" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="G49" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="H49" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I49" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="J49" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K49" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N49">
         <v>0</v>
       </c>
       <c r="O49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49">
         <v>0</v>
       </c>
       <c r="Q49" t="s">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="R49">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S49">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T49">
         <v>0</v>
@@ -4922,57 +5106,57 @@
         <v>90</v>
       </c>
       <c r="W49">
-        <v>18958</v>
+        <v>7493</v>
       </c>
       <c r="X49" t="s">
-        <v>197</v>
+        <v>270</v>
       </c>
       <c r="Y49">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z49">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C50" t="s">
         <v>46</v>
       </c>
       <c r="D50">
-        <v>6798</v>
+        <v>17391</v>
       </c>
       <c r="E50" t="s">
+        <v>88</v>
+      </c>
+      <c r="F50" t="s">
+        <v>133</v>
+      </c>
+      <c r="G50" t="s">
+        <v>88</v>
+      </c>
+      <c r="H50" t="s">
+        <v>155</v>
+      </c>
+      <c r="I50" t="s">
+        <v>159</v>
+      </c>
+      <c r="J50" t="s">
+        <v>187</v>
+      </c>
+      <c r="K50" t="s">
+        <v>201</v>
+      </c>
+      <c r="L50">
         <v>75</v>
       </c>
-      <c r="F50" t="s">
-        <v>108</v>
-      </c>
-      <c r="G50" t="s">
-        <v>75</v>
-      </c>
-      <c r="H50" t="s">
-        <v>127</v>
-      </c>
-      <c r="I50" t="s">
-        <v>135</v>
-      </c>
-      <c r="J50" t="s">
-        <v>151</v>
-      </c>
-      <c r="K50" t="s">
-        <v>153</v>
-      </c>
-      <c r="L50">
-        <v>12</v>
-      </c>
       <c r="M50">
-        <v>697</v>
+        <v>38</v>
       </c>
       <c r="N50">
         <v>0</v>
@@ -4984,13 +5168,13 @@
         <v>0</v>
       </c>
       <c r="Q50" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="R50">
-        <v>720</v>
+        <v>47</v>
       </c>
       <c r="S50">
-        <v>1020</v>
+        <v>122</v>
       </c>
       <c r="T50">
         <v>0</v>
@@ -5002,57 +5186,57 @@
         <v>90</v>
       </c>
       <c r="W50">
-        <v>10421</v>
+        <v>19525</v>
       </c>
       <c r="X50" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="Y50">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="Z50">
-        <v>1229</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C51" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D51">
-        <v>9079</v>
+        <v>409</v>
       </c>
       <c r="E51" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F51" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="G51" t="s">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="H51" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="I51" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="J51" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K51" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="L51">
         <v>6</v>
       </c>
       <c r="M51">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="N51">
         <v>0</v>
@@ -5064,13 +5248,13 @@
         <v>0</v>
       </c>
       <c r="Q51" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="R51">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="S51">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="T51">
         <v>0</v>
@@ -5082,75 +5266,75 @@
         <v>90</v>
       </c>
       <c r="W51">
-        <v>15947</v>
+        <v>15441</v>
       </c>
       <c r="X51" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="Y51">
         <v>3</v>
       </c>
       <c r="Z51">
-        <v>288</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
         <v>33</v>
       </c>
       <c r="C52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D52">
-        <v>17151</v>
+        <v>2416</v>
       </c>
       <c r="E52" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="F52" t="s">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="G52" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I52" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="J52" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K52" t="s">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="L52">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N52">
         <v>0</v>
       </c>
       <c r="O52">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P52">
         <v>0</v>
       </c>
       <c r="Q52" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="R52">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="S52">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="T52">
         <v>0</v>
@@ -5162,16 +5346,16 @@
         <v>90</v>
       </c>
       <c r="W52">
-        <v>18958</v>
+        <v>2977</v>
       </c>
       <c r="X52" t="s">
-        <v>197</v>
+        <v>254</v>
       </c>
       <c r="Y52">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Z52">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
@@ -5179,120 +5363,120 @@
         <v>28</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D53">
-        <v>17152</v>
+        <v>37272</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F53" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="G53" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H53" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I53" t="s">
+        <v>169</v>
+      </c>
+      <c r="J53" t="s">
+        <v>187</v>
+      </c>
+      <c r="K53" t="s">
+        <v>188</v>
+      </c>
+      <c r="L53">
+        <v>12</v>
+      </c>
+      <c r="M53">
+        <v>32</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="s">
         <v>129</v>
       </c>
-      <c r="J53" t="s">
-        <v>151</v>
-      </c>
-      <c r="K53" t="s">
-        <v>152</v>
-      </c>
-      <c r="L53">
-        <v>1</v>
-      </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
+      <c r="R53">
+        <v>40</v>
+      </c>
+      <c r="S53">
+        <v>52</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>90</v>
+      </c>
+      <c r="W53">
+        <v>6424</v>
+      </c>
+      <c r="X53" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y53">
         <v>2</v>
       </c>
-      <c r="P53">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>162</v>
-      </c>
-      <c r="R53">
-        <v>10</v>
-      </c>
-      <c r="S53">
-        <v>22</v>
-      </c>
-      <c r="T53">
-        <v>0</v>
-      </c>
-      <c r="U53">
-        <v>0</v>
-      </c>
-      <c r="V53">
-        <v>90</v>
-      </c>
-      <c r="W53">
-        <v>18958</v>
-      </c>
-      <c r="X53" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y53">
+      <c r="Z53">
         <v>20</v>
-      </c>
-      <c r="Z53">
-        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
         <v>47</v>
       </c>
       <c r="D54">
-        <v>1719</v>
+        <v>64427</v>
       </c>
       <c r="E54" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F54" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="G54" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="H54" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I54" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="J54" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K54" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="L54">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M54">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="N54">
         <v>0</v>
@@ -5304,13 +5488,13 @@
         <v>0</v>
       </c>
       <c r="Q54" t="s">
-        <v>84</v>
+        <v>203</v>
       </c>
       <c r="R54">
-        <v>152</v>
+        <v>12</v>
       </c>
       <c r="S54">
-        <v>224</v>
+        <v>18</v>
       </c>
       <c r="T54">
         <v>0</v>
@@ -5322,16 +5506,16 @@
         <v>90</v>
       </c>
       <c r="W54">
-        <v>7715</v>
+        <v>6424</v>
       </c>
       <c r="X54" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
       <c r="Y54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z54">
-        <v>357</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
@@ -5339,37 +5523,37 @@
         <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C55" t="s">
         <v>47</v>
       </c>
       <c r="D55">
-        <v>17151</v>
+        <v>64427</v>
       </c>
       <c r="E55" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="F55" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="G55" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="H55" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I55" t="s">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="J55" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K55" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -5378,19 +5562,19 @@
         <v>0</v>
       </c>
       <c r="O55">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P55">
         <v>0</v>
       </c>
       <c r="Q55" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="R55">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S55">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="T55">
         <v>0</v>
@@ -5402,75 +5586,75 @@
         <v>90</v>
       </c>
       <c r="W55">
-        <v>18958</v>
+        <v>6424</v>
       </c>
       <c r="X55" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="Y55">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Z55">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C56" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D56">
-        <v>17152</v>
+        <v>1719</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="F56" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="G56" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I56" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="J56" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K56" t="s">
+        <v>192</v>
+      </c>
+      <c r="L56">
+        <v>24</v>
+      </c>
+      <c r="M56">
+        <v>147</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>242</v>
+      </c>
+      <c r="R56">
         <v>152</v>
       </c>
-      <c r="L56">
-        <v>1</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>2</v>
-      </c>
-      <c r="P56">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>162</v>
-      </c>
-      <c r="R56">
-        <v>10</v>
-      </c>
       <c r="S56">
-        <v>22</v>
+        <v>224</v>
       </c>
       <c r="T56">
         <v>0</v>
@@ -5482,75 +5666,75 @@
         <v>90</v>
       </c>
       <c r="W56">
-        <v>18958</v>
+        <v>7715</v>
       </c>
       <c r="X56" t="s">
-        <v>197</v>
+        <v>272</v>
       </c>
       <c r="Y56">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Z56">
-        <v>24</v>
+        <v>352</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C57" t="s">
         <v>48</v>
       </c>
       <c r="D57">
-        <v>17151</v>
+        <v>4693</v>
       </c>
       <c r="E57" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="F57" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="G57" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="I57" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="J57" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="K57" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="L57">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="N57">
         <v>0</v>
       </c>
       <c r="O57">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P57">
         <v>0</v>
       </c>
       <c r="Q57" t="s">
-        <v>162</v>
+        <v>243</v>
       </c>
       <c r="R57">
-        <v>10</v>
+        <v>244</v>
       </c>
       <c r="S57">
-        <v>22</v>
+        <v>376</v>
       </c>
       <c r="T57">
         <v>0</v>
@@ -5562,100 +5746,20 @@
         <v>90</v>
       </c>
       <c r="W57">
-        <v>18958</v>
+        <v>9379</v>
       </c>
       <c r="X57" t="s">
-        <v>197</v>
+        <v>273</v>
       </c>
       <c r="Y57">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z57">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>28</v>
-      </c>
-      <c r="B58" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" t="s">
-        <v>48</v>
-      </c>
-      <c r="D58">
-        <v>17152</v>
-      </c>
-      <c r="E58" t="s">
-        <v>53</v>
-      </c>
-      <c r="F58" t="s">
-        <v>82</v>
-      </c>
-      <c r="G58" t="s">
-        <v>53</v>
-      </c>
-      <c r="H58" t="s">
-        <v>127</v>
-      </c>
-      <c r="I58" t="s">
-        <v>129</v>
-      </c>
-      <c r="J58" t="s">
-        <v>151</v>
-      </c>
-      <c r="K58" t="s">
-        <v>152</v>
-      </c>
-      <c r="L58">
-        <v>1</v>
-      </c>
-      <c r="M58">
-        <v>0</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>2</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>162</v>
-      </c>
-      <c r="R58">
-        <v>10</v>
-      </c>
-      <c r="S58">
-        <v>22</v>
-      </c>
-      <c r="T58">
-        <v>0</v>
-      </c>
-      <c r="U58">
-        <v>0</v>
-      </c>
-      <c r="V58">
-        <v>90</v>
-      </c>
-      <c r="W58">
-        <v>18958</v>
-      </c>
-      <c r="X58" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y58">
-        <v>20</v>
-      </c>
-      <c r="Z58">
-        <v>24</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z58" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Z57" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>